--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="359">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1069,10 +1069,10 @@
     <t>['21', '44', '45+3', '55']</t>
   </si>
   <si>
-    <t>['39', '69']</t>
+    <t>['50', '90+6']</t>
   </si>
   <si>
-    <t>['50', '90+6']</t>
+    <t>['39', '69']</t>
   </si>
   <si>
     <t>['40', '71']</t>
@@ -1088,6 +1088,9 @@
   </si>
   <si>
     <t>['54', '73']</t>
+  </si>
+  <si>
+    <t>['42', '62', '90']</t>
   </si>
 </sst>
 </file>
@@ -1449,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP264"/>
+  <dimension ref="A1:BP265"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3843,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ12">
         <v>0.25</v>
@@ -4670,7 +4673,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ16">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR16">
         <v>1.33</v>
@@ -7963,7 +7966,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ32">
         <v>0.54</v>
@@ -10023,7 +10026,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ42">
         <v>1.62</v>
@@ -12704,7 +12707,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ55">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR55">
         <v>1.39</v>
@@ -13525,7 +13528,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ59">
         <v>1.42</v>
@@ -16618,7 +16621,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ74">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR74">
         <v>1.54</v>
@@ -18060,7 +18063,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ81">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
         <v>1.07</v>
@@ -19293,7 +19296,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ87">
         <v>1.25</v>
@@ -24652,7 +24655,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ113">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -25061,7 +25064,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ115">
         <v>1.46</v>
@@ -29596,7 +29599,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ137">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR137">
         <v>1.67</v>
@@ -32683,7 +32686,7 @@
         <v>1.14</v>
       </c>
       <c r="AP152">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ152">
         <v>1.08</v>
@@ -33510,7 +33513,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ156">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR156">
         <v>1.44</v>
@@ -34743,7 +34746,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ162">
         <v>1.25</v>
@@ -38248,7 +38251,7 @@
         <v>2</v>
       </c>
       <c r="AQ179">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR179">
         <v>1.71</v>
@@ -39481,7 +39484,7 @@
         <v>0.86</v>
       </c>
       <c r="AP185">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ185">
         <v>0.91</v>
@@ -43395,7 +43398,7 @@
         <v>1.13</v>
       </c>
       <c r="AP204">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ204">
         <v>1.27</v>
@@ -43604,7 +43607,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ205">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR205">
         <v>1.69</v>
@@ -46900,7 +46903,7 @@
         <v>2</v>
       </c>
       <c r="AQ221">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR221">
         <v>1.48</v>
@@ -51223,7 +51226,7 @@
         <v>0.5</v>
       </c>
       <c r="AP242">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ242">
         <v>0.67</v>
@@ -51635,7 +51638,7 @@
         <v>1</v>
       </c>
       <c r="AP244">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ244">
         <v>1.18</v>
@@ -51721,7 +51724,7 @@
         <v>244</v>
       </c>
       <c r="B245">
-        <v>7728445</v>
+        <v>7728447</v>
       </c>
       <c r="C245" t="s">
         <v>68</v>
@@ -51736,10 +51739,10 @@
         <v>23</v>
       </c>
       <c r="G245" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H245" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I245">
         <v>1</v>
@@ -51760,166 +51763,166 @@
         <v>2</v>
       </c>
       <c r="O245" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>258</v>
+        <v>306</v>
       </c>
       <c r="Q245">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="R245">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="S245">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="T245">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U245">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V245">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="W245">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X245">
         <v>10</v>
       </c>
       <c r="Y245">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z245">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="AA245">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AB245">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AC245">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AD245">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AE245">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AF245">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AG245">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AH245">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AI245">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ245">
+        <v>1.63</v>
+      </c>
+      <c r="AK245">
+        <v>1.32</v>
+      </c>
+      <c r="AL245">
+        <v>1.34</v>
+      </c>
+      <c r="AM245">
+        <v>1.61</v>
+      </c>
+      <c r="AN245">
         <v>1.73</v>
       </c>
-      <c r="AK245">
-        <v>1.24</v>
-      </c>
-      <c r="AL245">
-        <v>1.31</v>
-      </c>
-      <c r="AM245">
-        <v>1.8</v>
-      </c>
-      <c r="AN245">
-        <v>2.09</v>
-      </c>
       <c r="AO245">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AP245">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ245">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AR245">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AS245">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AT245">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="AU245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV245">
         <v>5</v>
       </c>
       <c r="AW245">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX245">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY245">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ245">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA245">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB245">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC245">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BD245">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="BE245">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="BF245">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="BG245">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BH245">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="BI245">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="BJ245">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="BK245">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="BL245">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="BM245">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="BN245">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="BO245">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BP245">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="246" spans="1:68">
@@ -51927,7 +51930,7 @@
         <v>245</v>
       </c>
       <c r="B246">
-        <v>7728447</v>
+        <v>7728445</v>
       </c>
       <c r="C246" t="s">
         <v>68</v>
@@ -51942,10 +51945,10 @@
         <v>23</v>
       </c>
       <c r="G246" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H246" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I246">
         <v>1</v>
@@ -51966,166 +51969,166 @@
         <v>2</v>
       </c>
       <c r="O246" t="s">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="P246" t="s">
-        <v>306</v>
+        <v>258</v>
       </c>
       <c r="Q246">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R246">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S246">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="T246">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="U246">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V246">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="W246">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X246">
         <v>10</v>
       </c>
       <c r="Y246">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z246">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AA246">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AB246">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC246">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AD246">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AE246">
+        <v>1.42</v>
+      </c>
+      <c r="AF246">
+        <v>2.8</v>
+      </c>
+      <c r="AG246">
+        <v>2.15</v>
+      </c>
+      <c r="AH246">
+        <v>1.62</v>
+      </c>
+      <c r="AI246">
+        <v>2</v>
+      </c>
+      <c r="AJ246">
+        <v>1.73</v>
+      </c>
+      <c r="AK246">
+        <v>1.24</v>
+      </c>
+      <c r="AL246">
+        <v>1.31</v>
+      </c>
+      <c r="AM246">
+        <v>1.8</v>
+      </c>
+      <c r="AN246">
+        <v>2.09</v>
+      </c>
+      <c r="AO246">
+        <v>1.09</v>
+      </c>
+      <c r="AP246">
+        <v>2</v>
+      </c>
+      <c r="AQ246">
+        <v>1.08</v>
+      </c>
+      <c r="AR246">
         <v>1.49</v>
       </c>
-      <c r="AF246">
-        <v>2.4</v>
-      </c>
-      <c r="AG246">
-        <v>2.55</v>
-      </c>
-      <c r="AH246">
-        <v>1.46</v>
-      </c>
-      <c r="AI246">
-        <v>2.1</v>
-      </c>
-      <c r="AJ246">
-        <v>1.63</v>
-      </c>
-      <c r="AK246">
-        <v>1.32</v>
-      </c>
-      <c r="AL246">
-        <v>1.34</v>
-      </c>
-      <c r="AM246">
-        <v>1.61</v>
-      </c>
-      <c r="AN246">
-        <v>1.73</v>
-      </c>
-      <c r="AO246">
-        <v>1.3</v>
-      </c>
-      <c r="AP246">
-        <v>1.67</v>
-      </c>
-      <c r="AQ246">
-        <v>1.27</v>
-      </c>
-      <c r="AR246">
-        <v>1.56</v>
-      </c>
       <c r="AS246">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AT246">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AU246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV246">
         <v>5</v>
       </c>
       <c r="AW246">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX246">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY246">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ246">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA246">
+        <v>3</v>
+      </c>
+      <c r="BB246">
+        <v>1</v>
+      </c>
+      <c r="BC246">
         <v>4</v>
       </c>
-      <c r="BB246">
-        <v>5</v>
-      </c>
-      <c r="BC246">
-        <v>9</v>
-      </c>
       <c r="BD246">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="BE246">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="BF246">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="BG246">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BH246">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="BI246">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="BJ246">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="BK246">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="BL246">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="BM246">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="BN246">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BO246">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BP246">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="247" spans="1:68">
@@ -52256,7 +52259,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ247">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR247">
         <v>1.54</v>
@@ -52751,7 +52754,7 @@
         <v>249</v>
       </c>
       <c r="B250">
-        <v>7728451</v>
+        <v>7728444</v>
       </c>
       <c r="C250" t="s">
         <v>68</v>
@@ -52766,31 +52769,31 @@
         <v>23</v>
       </c>
       <c r="G250" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H250" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K250">
         <v>1</v>
       </c>
       <c r="L250">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M250">
         <v>2</v>
       </c>
       <c r="N250">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O250" t="s">
-        <v>251</v>
+        <v>124</v>
       </c>
       <c r="P250" t="s">
         <v>351</v>
@@ -52799,157 +52802,157 @@
         <v>2.4</v>
       </c>
       <c r="R250">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="S250">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="T250">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="U250">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
       <c r="V250">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="W250">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="X250">
-        <v>8.5</v>
+        <v>5.45</v>
       </c>
       <c r="Y250">
+        <v>1.12</v>
+      </c>
+      <c r="Z250">
+        <v>1.91</v>
+      </c>
+      <c r="AA250">
+        <v>3.6</v>
+      </c>
+      <c r="AB250">
+        <v>3.7</v>
+      </c>
+      <c r="AC250">
         <v>1.04</v>
       </c>
-      <c r="Z250">
-        <v>1.75</v>
-      </c>
-      <c r="AA250">
-        <v>3.48</v>
-      </c>
-      <c r="AB250">
-        <v>5.15</v>
-      </c>
-      <c r="AC250">
-        <v>1.11</v>
-      </c>
       <c r="AD250">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="AE250">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AF250">
-        <v>2.55</v>
+        <v>4.33</v>
       </c>
       <c r="AG250">
+        <v>1.61</v>
+      </c>
+      <c r="AH250">
+        <v>2.1</v>
+      </c>
+      <c r="AI250">
+        <v>1.57</v>
+      </c>
+      <c r="AJ250">
         <v>2.3</v>
       </c>
-      <c r="AH250">
-        <v>1.5</v>
-      </c>
-      <c r="AI250">
-        <v>2.15</v>
-      </c>
-      <c r="AJ250">
-        <v>1.6</v>
-      </c>
       <c r="AK250">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AL250">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AM250">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AN250">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AO250">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
       <c r="AP250">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ250">
-        <v>0.25</v>
+        <v>0.67</v>
       </c>
       <c r="AR250">
         <v>1.68</v>
       </c>
       <c r="AS250">
-        <v>1</v>
+        <v>1.32</v>
       </c>
       <c r="AT250">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="AU250">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV250">
         <v>5</v>
       </c>
       <c r="AW250">
+        <v>9</v>
+      </c>
+      <c r="AX250">
         <v>5</v>
       </c>
-      <c r="AX250">
-        <v>9</v>
-      </c>
       <c r="AY250">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AZ250">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA250">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB250">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC250">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD250">
+        <v>1.84</v>
+      </c>
+      <c r="BE250">
+        <v>6.4</v>
+      </c>
+      <c r="BF250">
+        <v>2.59</v>
+      </c>
+      <c r="BG250">
         <v>1.31</v>
       </c>
-      <c r="BE250">
-        <v>12.5</v>
-      </c>
-      <c r="BF250">
-        <v>4.14</v>
-      </c>
-      <c r="BG250">
-        <v>1.33</v>
-      </c>
       <c r="BH250">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="BI250">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BJ250">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="BK250">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="BL250">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BM250">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BN250">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BO250">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="BP250">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="251" spans="1:68">
@@ -52957,7 +52960,7 @@
         <v>250</v>
       </c>
       <c r="B251">
-        <v>7728444</v>
+        <v>7728451</v>
       </c>
       <c r="C251" t="s">
         <v>68</v>
@@ -52972,31 +52975,31 @@
         <v>23</v>
       </c>
       <c r="G251" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H251" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I251">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K251">
         <v>1</v>
       </c>
       <c r="L251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M251">
         <v>2</v>
       </c>
       <c r="N251">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O251" t="s">
-        <v>124</v>
+        <v>251</v>
       </c>
       <c r="P251" t="s">
         <v>352</v>
@@ -53005,157 +53008,157 @@
         <v>2.4</v>
       </c>
       <c r="R251">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="S251">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="T251">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="U251">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="V251">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="W251">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="X251">
-        <v>5.45</v>
+        <v>8.5</v>
       </c>
       <c r="Y251">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Z251">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AA251">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="AB251">
-        <v>3.7</v>
+        <v>5.15</v>
       </c>
       <c r="AC251">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AD251">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="AE251">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AF251">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="AG251">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AH251">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AI251">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AJ251">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AK251">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AL251">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AM251">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AN251">
+        <v>1.3</v>
+      </c>
+      <c r="AO251">
+        <v>0.18</v>
+      </c>
+      <c r="AP251">
         <v>1.27</v>
       </c>
-      <c r="AO251">
-        <v>0.45</v>
-      </c>
-      <c r="AP251">
-        <v>1.17</v>
-      </c>
       <c r="AQ251">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="AR251">
         <v>1.68</v>
       </c>
       <c r="AS251">
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="AT251">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="AU251">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV251">
         <v>5</v>
       </c>
       <c r="AW251">
+        <v>5</v>
+      </c>
+      <c r="AX251">
         <v>9</v>
       </c>
-      <c r="AX251">
+      <c r="AY251">
+        <v>14</v>
+      </c>
+      <c r="AZ251">
+        <v>17</v>
+      </c>
+      <c r="BA251">
         <v>5</v>
       </c>
-      <c r="AY251">
-        <v>18</v>
-      </c>
-      <c r="AZ251">
-        <v>10</v>
-      </c>
-      <c r="BA251">
+      <c r="BB251">
         <v>3</v>
       </c>
-      <c r="BB251">
-        <v>4</v>
-      </c>
       <c r="BC251">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD251">
-        <v>1.84</v>
+        <v>1.31</v>
       </c>
       <c r="BE251">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BF251">
-        <v>2.59</v>
+        <v>4.14</v>
       </c>
       <c r="BG251">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BH251">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="BI251">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="BJ251">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BK251">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="BL251">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BM251">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="BN251">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BO251">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="BP251">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="252" spans="1:68">
@@ -53987,7 +53990,7 @@
         <v>255</v>
       </c>
       <c r="B256">
-        <v>7728459</v>
+        <v>7728455</v>
       </c>
       <c r="C256" t="s">
         <v>68</v>
@@ -54002,190 +54005,190 @@
         <v>24</v>
       </c>
       <c r="G256" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H256" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J256">
         <v>0</v>
       </c>
       <c r="K256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L256">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N256">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O256" t="s">
-        <v>255</v>
+        <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>94</v>
+        <v>355</v>
       </c>
       <c r="Q256">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="R256">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S256">
-        <v>6.25</v>
+        <v>3.75</v>
       </c>
       <c r="T256">
+        <v>1.43</v>
+      </c>
+      <c r="U256">
+        <v>2.65</v>
+      </c>
+      <c r="V256">
+        <v>2.85</v>
+      </c>
+      <c r="W256">
+        <v>1.37</v>
+      </c>
+      <c r="X256">
+        <v>6.95</v>
+      </c>
+      <c r="Y256">
+        <v>1.07</v>
+      </c>
+      <c r="Z256">
+        <v>2.05</v>
+      </c>
+      <c r="AA256">
+        <v>3.05</v>
+      </c>
+      <c r="AB256">
+        <v>3.25</v>
+      </c>
+      <c r="AC256">
+        <v>1.06</v>
+      </c>
+      <c r="AD256">
+        <v>8.5</v>
+      </c>
+      <c r="AE256">
+        <v>1.3</v>
+      </c>
+      <c r="AF256">
+        <v>3.3</v>
+      </c>
+      <c r="AG256">
+        <v>1.9</v>
+      </c>
+      <c r="AH256">
+        <v>1.8</v>
+      </c>
+      <c r="AI256">
+        <v>1.72</v>
+      </c>
+      <c r="AJ256">
+        <v>2.05</v>
+      </c>
+      <c r="AK256">
+        <v>1.3</v>
+      </c>
+      <c r="AL256">
+        <v>1.28</v>
+      </c>
+      <c r="AM256">
+        <v>1.66</v>
+      </c>
+      <c r="AN256">
+        <v>1.18</v>
+      </c>
+      <c r="AO256">
+        <v>1.33</v>
+      </c>
+      <c r="AP256">
+        <v>1.08</v>
+      </c>
+      <c r="AQ256">
+        <v>1.46</v>
+      </c>
+      <c r="AR256">
+        <v>1.43</v>
+      </c>
+      <c r="AS256">
+        <v>1.25</v>
+      </c>
+      <c r="AT256">
+        <v>2.68</v>
+      </c>
+      <c r="AU256">
+        <v>5</v>
+      </c>
+      <c r="AV256">
+        <v>3</v>
+      </c>
+      <c r="AW256">
+        <v>20</v>
+      </c>
+      <c r="AX256">
+        <v>6</v>
+      </c>
+      <c r="AY256">
+        <v>37</v>
+      </c>
+      <c r="AZ256">
+        <v>12</v>
+      </c>
+      <c r="BA256">
+        <v>9</v>
+      </c>
+      <c r="BB256">
+        <v>5</v>
+      </c>
+      <c r="BC256">
+        <v>14</v>
+      </c>
+      <c r="BD256">
+        <v>1.65</v>
+      </c>
+      <c r="BE256">
+        <v>6.75</v>
+      </c>
+      <c r="BF256">
+        <v>2.48</v>
+      </c>
+      <c r="BG256">
+        <v>1.28</v>
+      </c>
+      <c r="BH256">
+        <v>3.2</v>
+      </c>
+      <c r="BI256">
+        <v>1.48</v>
+      </c>
+      <c r="BJ256">
+        <v>2.38</v>
+      </c>
+      <c r="BK256">
+        <v>1.79</v>
+      </c>
+      <c r="BL256">
+        <v>1.87</v>
+      </c>
+      <c r="BM256">
+        <v>2.25</v>
+      </c>
+      <c r="BN256">
         <v>1.55</v>
       </c>
-      <c r="U256">
-        <v>2.25</v>
-      </c>
-      <c r="V256">
-        <v>3.5</v>
-      </c>
-      <c r="W256">
-        <v>1.26</v>
-      </c>
-      <c r="X256">
-        <v>10</v>
-      </c>
-      <c r="Y256">
-        <v>1.04</v>
-      </c>
-      <c r="Z256">
-        <v>1.57</v>
-      </c>
-      <c r="AA256">
-        <v>3.15</v>
-      </c>
-      <c r="AB256">
-        <v>6</v>
-      </c>
-      <c r="AC256">
-        <v>1.11</v>
-      </c>
-      <c r="AD256">
-        <v>6.5</v>
-      </c>
-      <c r="AE256">
-        <v>1.55</v>
-      </c>
-      <c r="AF256">
-        <v>2.2</v>
-      </c>
-      <c r="AG256">
-        <v>2.6</v>
-      </c>
-      <c r="AH256">
-        <v>1.44</v>
-      </c>
-      <c r="AI256">
-        <v>2.5</v>
-      </c>
-      <c r="AJ256">
-        <v>1.46</v>
-      </c>
-      <c r="AK256">
-        <v>1.12</v>
-      </c>
-      <c r="AL256">
-        <v>1.31</v>
-      </c>
-      <c r="AM256">
-        <v>2.15</v>
-      </c>
-      <c r="AN256">
-        <v>2</v>
-      </c>
-      <c r="AO256">
-        <v>0.58</v>
-      </c>
-      <c r="AP256">
-        <v>2.08</v>
-      </c>
-      <c r="AQ256">
-        <v>0.54</v>
-      </c>
-      <c r="AR256">
-        <v>1.24</v>
-      </c>
-      <c r="AS256">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AT256">
-        <v>2.18</v>
-      </c>
-      <c r="AU256">
-        <v>6</v>
-      </c>
-      <c r="AV256">
-        <v>4</v>
-      </c>
-      <c r="AW256">
-        <v>6</v>
-      </c>
-      <c r="AX256">
-        <v>5</v>
-      </c>
-      <c r="AY256">
-        <v>13</v>
-      </c>
-      <c r="AZ256">
-        <v>9</v>
-      </c>
-      <c r="BA256">
-        <v>6</v>
-      </c>
-      <c r="BB256">
-        <v>4</v>
-      </c>
-      <c r="BC256">
-        <v>10</v>
-      </c>
-      <c r="BD256">
-        <v>1.38</v>
-      </c>
-      <c r="BE256">
-        <v>7</v>
-      </c>
-      <c r="BF256">
-        <v>3.45</v>
-      </c>
-      <c r="BG256">
-        <v>1.46</v>
-      </c>
-      <c r="BH256">
-        <v>2.45</v>
-      </c>
-      <c r="BI256">
-        <v>1.78</v>
-      </c>
-      <c r="BJ256">
-        <v>1.88</v>
-      </c>
-      <c r="BK256">
-        <v>2.25</v>
-      </c>
-      <c r="BL256">
-        <v>1.54</v>
-      </c>
-      <c r="BM256">
+      <c r="BO256">
         <v>2.9</v>
       </c>
-      <c r="BN256">
+      <c r="BP256">
         <v>1.34</v>
-      </c>
-      <c r="BO256">
-        <v>3.9</v>
-      </c>
-      <c r="BP256">
-        <v>1.19</v>
       </c>
     </row>
     <row r="257" spans="1:68">
@@ -54193,7 +54196,7 @@
         <v>256</v>
       </c>
       <c r="B257">
-        <v>7728455</v>
+        <v>7728459</v>
       </c>
       <c r="C257" t="s">
         <v>68</v>
@@ -54208,190 +54211,190 @@
         <v>24</v>
       </c>
       <c r="G257" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H257" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J257">
         <v>0</v>
       </c>
       <c r="K257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L257">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M257">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N257">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O257" t="s">
-        <v>117</v>
+        <v>255</v>
       </c>
       <c r="P257" t="s">
-        <v>355</v>
+        <v>94</v>
       </c>
       <c r="Q257">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="R257">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S257">
-        <v>3.75</v>
+        <v>6.25</v>
       </c>
       <c r="T257">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="U257">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="V257">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="W257">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="X257">
-        <v>6.95</v>
+        <v>10</v>
       </c>
       <c r="Y257">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z257">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AA257">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AB257">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AC257">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AD257">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AE257">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AF257">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG257">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AH257">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AI257">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="AJ257">
-        <v>2.05</v>
+        <v>1.46</v>
       </c>
       <c r="AK257">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AL257">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AM257">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AN257">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="AO257">
-        <v>1.33</v>
+        <v>0.58</v>
       </c>
       <c r="AP257">
-        <v>1.08</v>
+        <v>2.08</v>
       </c>
       <c r="AQ257">
+        <v>0.54</v>
+      </c>
+      <c r="AR257">
+        <v>1.24</v>
+      </c>
+      <c r="AS257">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT257">
+        <v>2.18</v>
+      </c>
+      <c r="AU257">
+        <v>6</v>
+      </c>
+      <c r="AV257">
+        <v>4</v>
+      </c>
+      <c r="AW257">
+        <v>6</v>
+      </c>
+      <c r="AX257">
+        <v>5</v>
+      </c>
+      <c r="AY257">
+        <v>13</v>
+      </c>
+      <c r="AZ257">
+        <v>9</v>
+      </c>
+      <c r="BA257">
+        <v>6</v>
+      </c>
+      <c r="BB257">
+        <v>4</v>
+      </c>
+      <c r="BC257">
+        <v>10</v>
+      </c>
+      <c r="BD257">
+        <v>1.38</v>
+      </c>
+      <c r="BE257">
+        <v>7</v>
+      </c>
+      <c r="BF257">
+        <v>3.45</v>
+      </c>
+      <c r="BG257">
         <v>1.46</v>
       </c>
-      <c r="AR257">
-        <v>1.43</v>
-      </c>
-      <c r="AS257">
-        <v>1.25</v>
-      </c>
-      <c r="AT257">
-        <v>2.68</v>
-      </c>
-      <c r="AU257">
-        <v>5</v>
-      </c>
-      <c r="AV257">
-        <v>3</v>
-      </c>
-      <c r="AW257">
-        <v>20</v>
-      </c>
-      <c r="AX257">
-        <v>6</v>
-      </c>
-      <c r="AY257">
-        <v>37</v>
-      </c>
-      <c r="AZ257">
-        <v>12</v>
-      </c>
-      <c r="BA257">
-        <v>9</v>
-      </c>
-      <c r="BB257">
-        <v>5</v>
-      </c>
-      <c r="BC257">
-        <v>14</v>
-      </c>
-      <c r="BD257">
-        <v>1.65</v>
-      </c>
-      <c r="BE257">
-        <v>6.75</v>
-      </c>
-      <c r="BF257">
-        <v>2.48</v>
-      </c>
-      <c r="BG257">
-        <v>1.28</v>
-      </c>
       <c r="BH257">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="BI257">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="BJ257">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="BK257">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="BL257">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="BM257">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="BN257">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="BO257">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="BP257">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="258" spans="1:68">
@@ -55834,6 +55837,212 @@
       </c>
       <c r="BP264">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="265" spans="1:68">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>7728466</v>
+      </c>
+      <c r="C265" t="s">
+        <v>68</v>
+      </c>
+      <c r="D265" t="s">
+        <v>69</v>
+      </c>
+      <c r="E265" s="2">
+        <v>45688.6875</v>
+      </c>
+      <c r="F265">
+        <v>25</v>
+      </c>
+      <c r="G265" t="s">
+        <v>80</v>
+      </c>
+      <c r="H265" t="s">
+        <v>70</v>
+      </c>
+      <c r="I265">
+        <v>0</v>
+      </c>
+      <c r="J265">
+        <v>1</v>
+      </c>
+      <c r="K265">
+        <v>1</v>
+      </c>
+      <c r="L265">
+        <v>0</v>
+      </c>
+      <c r="M265">
+        <v>3</v>
+      </c>
+      <c r="N265">
+        <v>3</v>
+      </c>
+      <c r="O265" t="s">
+        <v>94</v>
+      </c>
+      <c r="P265" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q265">
+        <v>3.2</v>
+      </c>
+      <c r="R265">
+        <v>1.98</v>
+      </c>
+      <c r="S265">
+        <v>3.3</v>
+      </c>
+      <c r="T265">
+        <v>1.46</v>
+      </c>
+      <c r="U265">
+        <v>2.5</v>
+      </c>
+      <c r="V265">
+        <v>3.1</v>
+      </c>
+      <c r="W265">
+        <v>1.32</v>
+      </c>
+      <c r="X265">
+        <v>8.25</v>
+      </c>
+      <c r="Y265">
+        <v>1.06</v>
+      </c>
+      <c r="Z265">
+        <v>2.52</v>
+      </c>
+      <c r="AA265">
+        <v>3.24</v>
+      </c>
+      <c r="AB265">
+        <v>2.86</v>
+      </c>
+      <c r="AC265">
+        <v>1.08</v>
+      </c>
+      <c r="AD265">
+        <v>7.5</v>
+      </c>
+      <c r="AE265">
+        <v>1.42</v>
+      </c>
+      <c r="AF265">
+        <v>2.8</v>
+      </c>
+      <c r="AG265">
+        <v>2.25</v>
+      </c>
+      <c r="AH265">
+        <v>1.64</v>
+      </c>
+      <c r="AI265">
+        <v>1.88</v>
+      </c>
+      <c r="AJ265">
+        <v>1.8</v>
+      </c>
+      <c r="AK265">
+        <v>1.42</v>
+      </c>
+      <c r="AL265">
+        <v>1.34</v>
+      </c>
+      <c r="AM265">
+        <v>1.47</v>
+      </c>
+      <c r="AN265">
+        <v>1.25</v>
+      </c>
+      <c r="AO265">
+        <v>1.36</v>
+      </c>
+      <c r="AP265">
+        <v>1.15</v>
+      </c>
+      <c r="AQ265">
+        <v>1.5</v>
+      </c>
+      <c r="AR265">
+        <v>1.45</v>
+      </c>
+      <c r="AS265">
+        <v>1.12</v>
+      </c>
+      <c r="AT265">
+        <v>2.57</v>
+      </c>
+      <c r="AU265">
+        <v>5</v>
+      </c>
+      <c r="AV265">
+        <v>7</v>
+      </c>
+      <c r="AW265">
+        <v>12</v>
+      </c>
+      <c r="AX265">
+        <v>7</v>
+      </c>
+      <c r="AY265">
+        <v>20</v>
+      </c>
+      <c r="AZ265">
+        <v>16</v>
+      </c>
+      <c r="BA265">
+        <v>8</v>
+      </c>
+      <c r="BB265">
+        <v>3</v>
+      </c>
+      <c r="BC265">
+        <v>11</v>
+      </c>
+      <c r="BD265">
+        <v>1.7</v>
+      </c>
+      <c r="BE265">
+        <v>6.4</v>
+      </c>
+      <c r="BF265">
+        <v>2.4</v>
+      </c>
+      <c r="BG265">
+        <v>1.36</v>
+      </c>
+      <c r="BH265">
+        <v>2.8</v>
+      </c>
+      <c r="BI265">
+        <v>1.6</v>
+      </c>
+      <c r="BJ265">
+        <v>2.14</v>
+      </c>
+      <c r="BK265">
+        <v>1.98</v>
+      </c>
+      <c r="BL265">
+        <v>1.71</v>
+      </c>
+      <c r="BM265">
+        <v>2.55</v>
+      </c>
+      <c r="BN265">
+        <v>1.43</v>
+      </c>
+      <c r="BO265">
+        <v>3.3</v>
+      </c>
+      <c r="BP265">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="363">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -796,6 +796,15 @@
     <t>['5', '27', '75']</t>
   </si>
   <si>
+    <t>['39', '50', '64']</t>
+  </si>
+  <si>
+    <t>['52', '83']</t>
+  </si>
+  <si>
+    <t>['15', '28']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1091,6 +1100,9 @@
   </si>
   <si>
     <t>['42', '62', '90']</t>
+  </si>
+  <si>
+    <t>['6']</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP265"/>
+  <dimension ref="A1:BP271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1708,7 +1720,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1992,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ3">
         <v>0.67</v>
@@ -2120,7 +2132,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2404,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ5">
         <v>1.25</v>
@@ -2613,7 +2625,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ6">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2819,7 +2831,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ7">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2944,7 +2956,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3022,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ8">
         <v>1.46</v>
@@ -3150,7 +3162,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3228,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ9">
         <v>1.62</v>
@@ -3643,7 +3655,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ11">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3974,7 +3986,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4052,7 +4064,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ13">
         <v>0.67</v>
@@ -4180,7 +4192,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4261,7 +4273,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ14">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4464,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ15">
         <v>0.75</v>
@@ -5210,7 +5222,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5497,7 +5509,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ20">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5700,10 +5712,10 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ21">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5828,7 +5840,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6034,7 +6046,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6115,7 +6127,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ23">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6240,7 +6252,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6321,7 +6333,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ24">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR24">
         <v>2.51</v>
@@ -6446,7 +6458,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6652,7 +6664,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6858,7 +6870,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7142,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7270,7 +7282,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7760,7 +7772,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ31">
         <v>1.46</v>
@@ -7888,7 +7900,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8094,7 +8106,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8172,7 +8184,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ33">
         <v>1.46</v>
@@ -8506,7 +8518,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8793,7 +8805,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ36">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR36">
         <v>2.09</v>
@@ -8999,7 +9011,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ37">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR37">
         <v>1.35</v>
@@ -9202,10 +9214,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ38">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR38">
         <v>1.41</v>
@@ -9411,7 +9423,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ39">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR39">
         <v>1.32</v>
@@ -10235,7 +10247,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ43">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR43">
         <v>0</v>
@@ -10360,7 +10372,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10438,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ44">
         <v>1.18</v>
@@ -10853,7 +10865,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ46">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -10978,7 +10990,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11262,7 +11274,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ48">
         <v>0.25</v>
@@ -11471,7 +11483,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ49">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR49">
         <v>1.38</v>
@@ -11674,7 +11686,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11880,7 +11892,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ51">
         <v>1.08</v>
@@ -12626,7 +12638,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12832,7 +12844,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -12910,7 +12922,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ56">
         <v>1.25</v>
@@ -13038,7 +13050,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13119,7 +13131,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ57">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -13244,7 +13256,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13531,7 +13543,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ59">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR59">
         <v>1.51</v>
@@ -13656,7 +13668,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13737,7 +13749,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ60">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -14274,7 +14286,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14558,7 +14570,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ64">
         <v>2.17</v>
@@ -14892,7 +14904,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14970,7 +14982,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ66">
         <v>0.67</v>
@@ -15304,7 +15316,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15385,7 +15397,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR68">
         <v>1.07</v>
@@ -15510,7 +15522,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15794,10 +15806,10 @@
         <v>2</v>
       </c>
       <c r="AP70">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ70">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR70">
         <v>1.04</v>
@@ -16000,7 +16012,7 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ71">
         <v>1.46</v>
@@ -16128,7 +16140,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16209,7 +16221,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ72">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR72">
         <v>1.35</v>
@@ -16334,7 +16346,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16540,7 +16552,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16824,7 +16836,7 @@
         <v>0.33</v>
       </c>
       <c r="AP75">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ75">
         <v>0.25</v>
@@ -17364,7 +17376,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17442,7 +17454,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ78">
         <v>0.54</v>
@@ -17570,7 +17582,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17857,7 +17869,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ80">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR80">
         <v>1.23</v>
@@ -17982,7 +17994,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18060,7 +18072,7 @@
         <v>1.67</v>
       </c>
       <c r="AP81">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ81">
         <v>1.5</v>
@@ -18188,7 +18200,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18266,7 +18278,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ82">
         <v>1</v>
@@ -18394,7 +18406,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18678,10 +18690,10 @@
         <v>2.33</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ84">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR84">
         <v>1.79</v>
@@ -19093,7 +19105,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ86">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19218,7 +19230,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19505,7 +19517,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ88">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR88">
         <v>1.96</v>
@@ -19630,7 +19642,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19836,7 +19848,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20248,7 +20260,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20329,7 +20341,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ92">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR92">
         <v>1.42</v>
@@ -20532,7 +20544,7 @@
         <v>1.33</v>
       </c>
       <c r="AP93">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ93">
         <v>0.75</v>
@@ -20660,7 +20672,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20866,7 +20878,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21150,7 +21162,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ96">
         <v>1.46</v>
@@ -21771,7 +21783,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ99">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR99">
         <v>1.46</v>
@@ -21896,7 +21908,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21974,7 +21986,7 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ100">
         <v>1.25</v>
@@ -22389,7 +22401,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ102">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR102">
         <v>1.13</v>
@@ -23004,7 +23016,7 @@
         <v>1.4</v>
       </c>
       <c r="AP105">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ105">
         <v>1.46</v>
@@ -23210,7 +23222,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ106">
         <v>0.67</v>
@@ -23338,7 +23350,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23625,7 +23637,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ108">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR108">
         <v>1.17</v>
@@ -23956,7 +23968,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24243,7 +24255,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR111">
         <v>1.54</v>
@@ -24368,7 +24380,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24574,7 +24586,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24652,7 +24664,7 @@
         <v>2</v>
       </c>
       <c r="AP113">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ113">
         <v>1.5</v>
@@ -24858,7 +24870,7 @@
         <v>1.75</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ114">
         <v>1.18</v>
@@ -24986,7 +24998,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25270,7 +25282,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ116">
         <v>0.67</v>
@@ -25479,7 +25491,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ117">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR117">
         <v>1.16</v>
@@ -25682,7 +25694,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ118">
         <v>1.08</v>
@@ -25810,7 +25822,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -25891,7 +25903,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ119">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR119">
         <v>1.68</v>
@@ -26094,10 +26106,10 @@
         <v>1.4</v>
       </c>
       <c r="AP120">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ120">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR120">
         <v>1.6</v>
@@ -26303,7 +26315,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ121">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR121">
         <v>1.32</v>
@@ -26428,7 +26440,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26715,7 +26727,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ123">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR123">
         <v>1.53</v>
@@ -26840,7 +26852,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -26918,7 +26930,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ124">
         <v>0.54</v>
@@ -27252,7 +27264,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27664,7 +27676,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27951,7 +27963,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ129">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -28076,7 +28088,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28282,7 +28294,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28488,7 +28500,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28900,7 +28912,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -28978,10 +28990,10 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ134">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR134">
         <v>1.4</v>
@@ -29106,7 +29118,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29187,7 +29199,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ135">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR135">
         <v>1.12</v>
@@ -29390,7 +29402,7 @@
         <v>1.4</v>
       </c>
       <c r="AP136">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ136">
         <v>1.18</v>
@@ -29724,7 +29736,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29802,7 +29814,7 @@
         <v>1.17</v>
       </c>
       <c r="AP138">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ138">
         <v>1.08</v>
@@ -30011,7 +30023,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ139">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR139">
         <v>1.66</v>
@@ -30342,7 +30354,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30548,7 +30560,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30626,7 +30638,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ142">
         <v>1.18</v>
@@ -30754,7 +30766,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30960,7 +30972,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31372,7 +31384,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31784,7 +31796,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32071,7 +32083,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ149">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR149">
         <v>1.82</v>
@@ -32480,7 +32492,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ151">
         <v>0.91</v>
@@ -32814,7 +32826,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32892,7 +32904,7 @@
         <v>0.83</v>
       </c>
       <c r="AP153">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ153">
         <v>1.17</v>
@@ -33101,7 +33113,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ154">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR154">
         <v>1.67</v>
@@ -33304,10 +33316,10 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ155">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR155">
         <v>1.59</v>
@@ -33432,7 +33444,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33510,7 +33522,7 @@
         <v>1.83</v>
       </c>
       <c r="AP156">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ156">
         <v>1.5</v>
@@ -34128,10 +34140,10 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ159">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR159">
         <v>1.75</v>
@@ -34337,7 +34349,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ160">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34543,7 +34555,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ161">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR161">
         <v>1.62</v>
@@ -34749,7 +34761,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ162">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR162">
         <v>1.47</v>
@@ -35080,7 +35092,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35698,7 +35710,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36110,7 +36122,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36600,7 +36612,7 @@
         <v>0.71</v>
       </c>
       <c r="AP171">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ171">
         <v>0.75</v>
@@ -36728,7 +36740,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37015,7 +37027,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ173">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR173">
         <v>1.44</v>
@@ -37218,7 +37230,7 @@
         <v>0.14</v>
       </c>
       <c r="AP174">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ174">
         <v>0.67</v>
@@ -37346,7 +37358,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37427,7 +37439,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ175">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR175">
         <v>1.58</v>
@@ -37630,7 +37642,7 @@
         <v>0.83</v>
       </c>
       <c r="AP176">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ176">
         <v>0.91</v>
@@ -37758,7 +37770,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -37839,7 +37851,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ177">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR177">
         <v>1.68</v>
@@ -38170,7 +38182,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38248,7 +38260,7 @@
         <v>2</v>
       </c>
       <c r="AP179">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ179">
         <v>1.5</v>
@@ -38376,7 +38388,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38457,7 +38469,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ180">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR180">
         <v>1.48</v>
@@ -38660,7 +38672,7 @@
         <v>1.14</v>
       </c>
       <c r="AP181">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ181">
         <v>1.17</v>
@@ -38869,7 +38881,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ182">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR182">
         <v>1.26</v>
@@ -39072,10 +39084,10 @@
         <v>0.88</v>
       </c>
       <c r="AP183">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ183">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR183">
         <v>1.63</v>
@@ -39200,7 +39212,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39281,7 +39293,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ184">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR184">
         <v>1.69</v>
@@ -39690,7 +39702,7 @@
         <v>0.13</v>
       </c>
       <c r="AP186">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ186">
         <v>0.67</v>
@@ -39896,7 +39908,7 @@
         <v>0.75</v>
       </c>
       <c r="AP187">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ187">
         <v>0.54</v>
@@ -40024,7 +40036,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40102,7 +40114,7 @@
         <v>1.38</v>
       </c>
       <c r="AP188">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ188">
         <v>1.46</v>
@@ -40642,7 +40654,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40848,7 +40860,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41054,7 +41066,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41135,7 +41147,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ193">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR193">
         <v>1.13</v>
@@ -41260,7 +41272,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42368,7 +42380,7 @@
         <v>1.38</v>
       </c>
       <c r="AP199">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ199">
         <v>1.17</v>
@@ -42496,7 +42508,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42908,7 +42920,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -42986,7 +42998,7 @@
         <v>0.67</v>
       </c>
       <c r="AP202">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ202">
         <v>0.54</v>
@@ -43114,7 +43126,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43192,7 +43204,7 @@
         <v>1.6</v>
       </c>
       <c r="AP203">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ203">
         <v>1.46</v>
@@ -43401,7 +43413,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ204">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR204">
         <v>1.41</v>
@@ -43732,7 +43744,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43810,7 +43822,7 @@
         <v>0.88</v>
       </c>
       <c r="AP206">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ206">
         <v>0.91</v>
@@ -44019,7 +44031,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ207">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR207">
         <v>1.45</v>
@@ -44144,7 +44156,7 @@
         <v>94</v>
       </c>
       <c r="P208" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44222,10 +44234,10 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ208">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR208">
         <v>1.46</v>
@@ -44762,7 +44774,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44968,7 +44980,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45049,7 +45061,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ212">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR212">
         <v>1.69</v>
@@ -45174,7 +45186,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45380,7 +45392,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45458,7 +45470,7 @@
         <v>1.11</v>
       </c>
       <c r="AP214">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ214">
         <v>1</v>
@@ -45792,7 +45804,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -45873,7 +45885,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ216">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR216">
         <v>1.46</v>
@@ -46900,7 +46912,7 @@
         <v>1.56</v>
       </c>
       <c r="AP221">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ221">
         <v>1.5</v>
@@ -47028,7 +47040,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47440,7 +47452,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47518,10 +47530,10 @@
         <v>0.8</v>
       </c>
       <c r="AP224">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ224">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR224">
         <v>1.5</v>
@@ -47852,7 +47864,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -47930,10 +47942,10 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
+        <v>1.08</v>
+      </c>
+      <c r="AQ226">
         <v>1.17</v>
-      </c>
-      <c r="AQ226">
-        <v>1.27</v>
       </c>
       <c r="AR226">
         <v>1.73</v>
@@ -48058,7 +48070,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48136,7 +48148,7 @@
         <v>1</v>
       </c>
       <c r="AP227">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ227">
         <v>1.18</v>
@@ -48342,7 +48354,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ228">
         <v>0.75</v>
@@ -48470,7 +48482,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48676,7 +48688,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48757,7 +48769,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ230">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR230">
         <v>1.54</v>
@@ -48882,7 +48894,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49169,7 +49181,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ232">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR232">
         <v>1.73</v>
@@ -49706,7 +49718,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50199,7 +50211,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ237">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR237">
         <v>1.37</v>
@@ -50530,7 +50542,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51148,7 +51160,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51435,7 +51447,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ243">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR243">
         <v>1.18</v>
@@ -51560,7 +51572,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51766,7 +51778,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -51844,10 +51856,10 @@
         <v>1.3</v>
       </c>
       <c r="AP245">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ245">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR245">
         <v>1.56</v>
@@ -52050,7 +52062,7 @@
         <v>1.09</v>
       </c>
       <c r="AP246">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ246">
         <v>1.08</v>
@@ -52465,7 +52477,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ248">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR248">
         <v>1.41</v>
@@ -52668,7 +52680,7 @@
         <v>1</v>
       </c>
       <c r="AP249">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ249">
         <v>0.91</v>
@@ -52796,7 +52808,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -52874,7 +52886,7 @@
         <v>0.45</v>
       </c>
       <c r="AP250">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ250">
         <v>0.67</v>
@@ -53002,7 +53014,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53286,10 +53298,10 @@
         <v>1.27</v>
       </c>
       <c r="AP252">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ252">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR252">
         <v>1.71</v>
@@ -53414,7 +53426,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53492,10 +53504,10 @@
         <v>1</v>
       </c>
       <c r="AP253">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ253">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR253">
         <v>1.15</v>
@@ -53826,7 +53838,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54032,7 +54044,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54444,7 +54456,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -55062,7 +55074,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55268,7 +55280,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55761,7 +55773,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ264">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR264">
         <v>1.24</v>
@@ -55886,7 +55898,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56042,6 +56054,1242 @@
         <v>3.3</v>
       </c>
       <c r="BP265">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="266" spans="1:68">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>7728471</v>
+      </c>
+      <c r="C266" t="s">
+        <v>68</v>
+      </c>
+      <c r="D266" t="s">
+        <v>69</v>
+      </c>
+      <c r="E266" s="2">
+        <v>45689.41666666666</v>
+      </c>
+      <c r="F266">
+        <v>25</v>
+      </c>
+      <c r="G266" t="s">
+        <v>71</v>
+      </c>
+      <c r="H266" t="s">
+        <v>79</v>
+      </c>
+      <c r="I266">
+        <v>1</v>
+      </c>
+      <c r="J266">
+        <v>0</v>
+      </c>
+      <c r="K266">
+        <v>1</v>
+      </c>
+      <c r="L266">
+        <v>3</v>
+      </c>
+      <c r="M266">
+        <v>0</v>
+      </c>
+      <c r="N266">
+        <v>3</v>
+      </c>
+      <c r="O266" t="s">
+        <v>260</v>
+      </c>
+      <c r="P266" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q266">
+        <v>4</v>
+      </c>
+      <c r="R266">
+        <v>1.83</v>
+      </c>
+      <c r="S266">
+        <v>3.5</v>
+      </c>
+      <c r="T266">
+        <v>1.67</v>
+      </c>
+      <c r="U266">
+        <v>2.1</v>
+      </c>
+      <c r="V266">
+        <v>4.33</v>
+      </c>
+      <c r="W266">
+        <v>1.2</v>
+      </c>
+      <c r="X266">
+        <v>15</v>
+      </c>
+      <c r="Y266">
+        <v>1.03</v>
+      </c>
+      <c r="Z266">
+        <v>2.63</v>
+      </c>
+      <c r="AA266">
+        <v>3.17</v>
+      </c>
+      <c r="AB266">
+        <v>2.95</v>
+      </c>
+      <c r="AC266">
+        <v>1.12</v>
+      </c>
+      <c r="AD266">
+        <v>5.5</v>
+      </c>
+      <c r="AE266">
+        <v>1.53</v>
+      </c>
+      <c r="AF266">
+        <v>2.25</v>
+      </c>
+      <c r="AG266">
+        <v>2.85</v>
+      </c>
+      <c r="AH266">
+        <v>1.37</v>
+      </c>
+      <c r="AI266">
+        <v>2.38</v>
+      </c>
+      <c r="AJ266">
+        <v>1.53</v>
+      </c>
+      <c r="AK266">
+        <v>1.47</v>
+      </c>
+      <c r="AL266">
+        <v>1.38</v>
+      </c>
+      <c r="AM266">
+        <v>1.38</v>
+      </c>
+      <c r="AN266">
+        <v>2.25</v>
+      </c>
+      <c r="AO266">
+        <v>1.27</v>
+      </c>
+      <c r="AP266">
+        <v>2.31</v>
+      </c>
+      <c r="AQ266">
+        <v>1.17</v>
+      </c>
+      <c r="AR266">
+        <v>1.24</v>
+      </c>
+      <c r="AS266">
+        <v>1.22</v>
+      </c>
+      <c r="AT266">
+        <v>2.46</v>
+      </c>
+      <c r="AU266">
+        <v>7</v>
+      </c>
+      <c r="AV266">
+        <v>4</v>
+      </c>
+      <c r="AW266">
+        <v>12</v>
+      </c>
+      <c r="AX266">
+        <v>8</v>
+      </c>
+      <c r="AY266">
+        <v>24</v>
+      </c>
+      <c r="AZ266">
+        <v>15</v>
+      </c>
+      <c r="BA266">
+        <v>4</v>
+      </c>
+      <c r="BB266">
+        <v>3</v>
+      </c>
+      <c r="BC266">
+        <v>7</v>
+      </c>
+      <c r="BD266">
+        <v>2.05</v>
+      </c>
+      <c r="BE266">
+        <v>6.25</v>
+      </c>
+      <c r="BF266">
+        <v>1.97</v>
+      </c>
+      <c r="BG266">
+        <v>1.38</v>
+      </c>
+      <c r="BH266">
+        <v>2.7</v>
+      </c>
+      <c r="BI266">
+        <v>1.65</v>
+      </c>
+      <c r="BJ266">
+        <v>2.05</v>
+      </c>
+      <c r="BK266">
+        <v>2.05</v>
+      </c>
+      <c r="BL266">
+        <v>1.65</v>
+      </c>
+      <c r="BM266">
+        <v>2.65</v>
+      </c>
+      <c r="BN266">
+        <v>1.4</v>
+      </c>
+      <c r="BO266">
+        <v>3.55</v>
+      </c>
+      <c r="BP266">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="267" spans="1:68">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7728468</v>
+      </c>
+      <c r="C267" t="s">
+        <v>68</v>
+      </c>
+      <c r="D267" t="s">
+        <v>69</v>
+      </c>
+      <c r="E267" s="2">
+        <v>45689.51041666666</v>
+      </c>
+      <c r="F267">
+        <v>25</v>
+      </c>
+      <c r="G267" t="s">
+        <v>76</v>
+      </c>
+      <c r="H267" t="s">
+        <v>78</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>0</v>
+      </c>
+      <c r="K267">
+        <v>0</v>
+      </c>
+      <c r="L267">
+        <v>2</v>
+      </c>
+      <c r="M267">
+        <v>0</v>
+      </c>
+      <c r="N267">
+        <v>2</v>
+      </c>
+      <c r="O267" t="s">
+        <v>261</v>
+      </c>
+      <c r="P267" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q267">
+        <v>2.75</v>
+      </c>
+      <c r="R267">
+        <v>1.91</v>
+      </c>
+      <c r="S267">
+        <v>5</v>
+      </c>
+      <c r="T267">
+        <v>1.62</v>
+      </c>
+      <c r="U267">
+        <v>2.2</v>
+      </c>
+      <c r="V267">
+        <v>4</v>
+      </c>
+      <c r="W267">
+        <v>1.22</v>
+      </c>
+      <c r="X267">
+        <v>13</v>
+      </c>
+      <c r="Y267">
+        <v>1.04</v>
+      </c>
+      <c r="Z267">
+        <v>2.01</v>
+      </c>
+      <c r="AA267">
+        <v>3.28</v>
+      </c>
+      <c r="AB267">
+        <v>4.3</v>
+      </c>
+      <c r="AC267">
+        <v>1.11</v>
+      </c>
+      <c r="AD267">
+        <v>6.59</v>
+      </c>
+      <c r="AE267">
+        <v>1.55</v>
+      </c>
+      <c r="AF267">
+        <v>2.3</v>
+      </c>
+      <c r="AG267">
+        <v>2.25</v>
+      </c>
+      <c r="AH267">
+        <v>1.53</v>
+      </c>
+      <c r="AI267">
+        <v>2.38</v>
+      </c>
+      <c r="AJ267">
+        <v>1.53</v>
+      </c>
+      <c r="AK267">
+        <v>1.22</v>
+      </c>
+      <c r="AL267">
+        <v>1.34</v>
+      </c>
+      <c r="AM267">
+        <v>1.78</v>
+      </c>
+      <c r="AN267">
+        <v>1.67</v>
+      </c>
+      <c r="AO267">
+        <v>0.82</v>
+      </c>
+      <c r="AP267">
+        <v>1.77</v>
+      </c>
+      <c r="AQ267">
+        <v>0.75</v>
+      </c>
+      <c r="AR267">
+        <v>1.55</v>
+      </c>
+      <c r="AS267">
+        <v>1.2</v>
+      </c>
+      <c r="AT267">
+        <v>2.75</v>
+      </c>
+      <c r="AU267">
+        <v>4</v>
+      </c>
+      <c r="AV267">
+        <v>2</v>
+      </c>
+      <c r="AW267">
+        <v>7</v>
+      </c>
+      <c r="AX267">
+        <v>8</v>
+      </c>
+      <c r="AY267">
+        <v>11</v>
+      </c>
+      <c r="AZ267">
+        <v>10</v>
+      </c>
+      <c r="BA267">
+        <v>3</v>
+      </c>
+      <c r="BB267">
+        <v>3</v>
+      </c>
+      <c r="BC267">
+        <v>6</v>
+      </c>
+      <c r="BD267">
+        <v>1.65</v>
+      </c>
+      <c r="BE267">
+        <v>6.4</v>
+      </c>
+      <c r="BF267">
+        <v>2.5</v>
+      </c>
+      <c r="BG267">
+        <v>1.47</v>
+      </c>
+      <c r="BH267">
+        <v>2.43</v>
+      </c>
+      <c r="BI267">
+        <v>1.79</v>
+      </c>
+      <c r="BJ267">
+        <v>1.87</v>
+      </c>
+      <c r="BK267">
+        <v>2.25</v>
+      </c>
+      <c r="BL267">
+        <v>1.55</v>
+      </c>
+      <c r="BM267">
+        <v>2.9</v>
+      </c>
+      <c r="BN267">
+        <v>1.34</v>
+      </c>
+      <c r="BO267">
+        <v>3.9</v>
+      </c>
+      <c r="BP267">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="268" spans="1:68">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>7728463</v>
+      </c>
+      <c r="C268" t="s">
+        <v>68</v>
+      </c>
+      <c r="D268" t="s">
+        <v>69</v>
+      </c>
+      <c r="E268" s="2">
+        <v>45689.60416666666</v>
+      </c>
+      <c r="F268">
+        <v>25</v>
+      </c>
+      <c r="G268" t="s">
+        <v>90</v>
+      </c>
+      <c r="H268" t="s">
+        <v>89</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+      <c r="J268">
+        <v>1</v>
+      </c>
+      <c r="K268">
+        <v>1</v>
+      </c>
+      <c r="L268">
+        <v>1</v>
+      </c>
+      <c r="M268">
+        <v>1</v>
+      </c>
+      <c r="N268">
+        <v>2</v>
+      </c>
+      <c r="O268" t="s">
+        <v>238</v>
+      </c>
+      <c r="P268" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q268">
+        <v>2.5</v>
+      </c>
+      <c r="R268">
+        <v>2.2</v>
+      </c>
+      <c r="S268">
+        <v>4.5</v>
+      </c>
+      <c r="T268">
+        <v>1.4</v>
+      </c>
+      <c r="U268">
+        <v>2.75</v>
+      </c>
+      <c r="V268">
+        <v>3</v>
+      </c>
+      <c r="W268">
+        <v>1.36</v>
+      </c>
+      <c r="X268">
+        <v>8</v>
+      </c>
+      <c r="Y268">
+        <v>1.08</v>
+      </c>
+      <c r="Z268">
+        <v>2.01</v>
+      </c>
+      <c r="AA268">
+        <v>3.57</v>
+      </c>
+      <c r="AB268">
+        <v>3.87</v>
+      </c>
+      <c r="AC268">
+        <v>1.06</v>
+      </c>
+      <c r="AD268">
+        <v>8.5</v>
+      </c>
+      <c r="AE268">
+        <v>1.3</v>
+      </c>
+      <c r="AF268">
+        <v>3.3</v>
+      </c>
+      <c r="AG268">
+        <v>1.96</v>
+      </c>
+      <c r="AH268">
+        <v>1.85</v>
+      </c>
+      <c r="AI268">
+        <v>1.8</v>
+      </c>
+      <c r="AJ268">
+        <v>1.91</v>
+      </c>
+      <c r="AK268">
+        <v>1.22</v>
+      </c>
+      <c r="AL268">
+        <v>1.29</v>
+      </c>
+      <c r="AM268">
+        <v>1.9</v>
+      </c>
+      <c r="AN268">
+        <v>2</v>
+      </c>
+      <c r="AO268">
+        <v>1.42</v>
+      </c>
+      <c r="AP268">
+        <v>1.92</v>
+      </c>
+      <c r="AQ268">
+        <v>1.38</v>
+      </c>
+      <c r="AR268">
+        <v>1.8</v>
+      </c>
+      <c r="AS268">
+        <v>1.34</v>
+      </c>
+      <c r="AT268">
+        <v>3.14</v>
+      </c>
+      <c r="AU268">
+        <v>5</v>
+      </c>
+      <c r="AV268">
+        <v>3</v>
+      </c>
+      <c r="AW268">
+        <v>5</v>
+      </c>
+      <c r="AX268">
+        <v>8</v>
+      </c>
+      <c r="AY268">
+        <v>10</v>
+      </c>
+      <c r="AZ268">
+        <v>13</v>
+      </c>
+      <c r="BA268">
+        <v>1</v>
+      </c>
+      <c r="BB268">
+        <v>3</v>
+      </c>
+      <c r="BC268">
+        <v>4</v>
+      </c>
+      <c r="BD268">
+        <v>1.54</v>
+      </c>
+      <c r="BE268">
+        <v>6.75</v>
+      </c>
+      <c r="BF268">
+        <v>2.7</v>
+      </c>
+      <c r="BG268">
+        <v>1.4</v>
+      </c>
+      <c r="BH268">
+        <v>2.82</v>
+      </c>
+      <c r="BI268">
+        <v>1.68</v>
+      </c>
+      <c r="BJ268">
+        <v>2.12</v>
+      </c>
+      <c r="BK268">
+        <v>2.11</v>
+      </c>
+      <c r="BL268">
+        <v>1.68</v>
+      </c>
+      <c r="BM268">
+        <v>2.75</v>
+      </c>
+      <c r="BN268">
+        <v>1.42</v>
+      </c>
+      <c r="BO268">
+        <v>3.8</v>
+      </c>
+      <c r="BP268">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="269" spans="1:68">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>7728473</v>
+      </c>
+      <c r="C269" t="s">
+        <v>68</v>
+      </c>
+      <c r="D269" t="s">
+        <v>69</v>
+      </c>
+      <c r="E269" s="2">
+        <v>45689.70833333334</v>
+      </c>
+      <c r="F269">
+        <v>25</v>
+      </c>
+      <c r="G269" t="s">
+        <v>77</v>
+      </c>
+      <c r="H269" t="s">
+        <v>83</v>
+      </c>
+      <c r="I269">
+        <v>2</v>
+      </c>
+      <c r="J269">
+        <v>1</v>
+      </c>
+      <c r="K269">
+        <v>3</v>
+      </c>
+      <c r="L269">
+        <v>2</v>
+      </c>
+      <c r="M269">
+        <v>1</v>
+      </c>
+      <c r="N269">
+        <v>3</v>
+      </c>
+      <c r="O269" t="s">
+        <v>262</v>
+      </c>
+      <c r="P269" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q269">
+        <v>2.25</v>
+      </c>
+      <c r="R269">
+        <v>2.1</v>
+      </c>
+      <c r="S269">
+        <v>4.8</v>
+      </c>
+      <c r="T269">
+        <v>1.4</v>
+      </c>
+      <c r="U269">
+        <v>2.7</v>
+      </c>
+      <c r="V269">
+        <v>2.8</v>
+      </c>
+      <c r="W269">
+        <v>1.37</v>
+      </c>
+      <c r="X269">
+        <v>7.25</v>
+      </c>
+      <c r="Y269">
+        <v>1.08</v>
+      </c>
+      <c r="Z269">
+        <v>1.7</v>
+      </c>
+      <c r="AA269">
+        <v>3.91</v>
+      </c>
+      <c r="AB269">
+        <v>5.2</v>
+      </c>
+      <c r="AC269">
+        <v>1.05</v>
+      </c>
+      <c r="AD269">
+        <v>9</v>
+      </c>
+      <c r="AE269">
+        <v>1.3</v>
+      </c>
+      <c r="AF269">
+        <v>3.35</v>
+      </c>
+      <c r="AG269">
+        <v>1.97</v>
+      </c>
+      <c r="AH269">
+        <v>1.84</v>
+      </c>
+      <c r="AI269">
+        <v>1.9</v>
+      </c>
+      <c r="AJ269">
+        <v>1.78</v>
+      </c>
+      <c r="AK269">
+        <v>1.18</v>
+      </c>
+      <c r="AL269">
+        <v>1.25</v>
+      </c>
+      <c r="AM269">
+        <v>2.1</v>
+      </c>
+      <c r="AN269">
+        <v>1.58</v>
+      </c>
+      <c r="AO269">
+        <v>0.92</v>
+      </c>
+      <c r="AP269">
+        <v>1.69</v>
+      </c>
+      <c r="AQ269">
+        <v>0.85</v>
+      </c>
+      <c r="AR269">
+        <v>1.57</v>
+      </c>
+      <c r="AS269">
+        <v>1.09</v>
+      </c>
+      <c r="AT269">
+        <v>2.66</v>
+      </c>
+      <c r="AU269">
+        <v>6</v>
+      </c>
+      <c r="AV269">
+        <v>6</v>
+      </c>
+      <c r="AW269">
+        <v>16</v>
+      </c>
+      <c r="AX269">
+        <v>7</v>
+      </c>
+      <c r="AY269">
+        <v>27</v>
+      </c>
+      <c r="AZ269">
+        <v>15</v>
+      </c>
+      <c r="BA269">
+        <v>8</v>
+      </c>
+      <c r="BB269">
+        <v>4</v>
+      </c>
+      <c r="BC269">
+        <v>12</v>
+      </c>
+      <c r="BD269">
+        <v>1.42</v>
+      </c>
+      <c r="BE269">
+        <v>7</v>
+      </c>
+      <c r="BF269">
+        <v>3.15</v>
+      </c>
+      <c r="BG269">
+        <v>1.33</v>
+      </c>
+      <c r="BH269">
+        <v>2.9</v>
+      </c>
+      <c r="BI269">
+        <v>1.58</v>
+      </c>
+      <c r="BJ269">
+        <v>2.18</v>
+      </c>
+      <c r="BK269">
+        <v>1.93</v>
+      </c>
+      <c r="BL269">
+        <v>1.74</v>
+      </c>
+      <c r="BM269">
+        <v>2.48</v>
+      </c>
+      <c r="BN269">
+        <v>1.45</v>
+      </c>
+      <c r="BO269">
+        <v>3.2</v>
+      </c>
+      <c r="BP269">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="270" spans="1:68">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>7728465</v>
+      </c>
+      <c r="C270" t="s">
+        <v>68</v>
+      </c>
+      <c r="D270" t="s">
+        <v>69</v>
+      </c>
+      <c r="E270" s="2">
+        <v>45690.41666666666</v>
+      </c>
+      <c r="F270">
+        <v>25</v>
+      </c>
+      <c r="G270" t="s">
+        <v>86</v>
+      </c>
+      <c r="H270" t="s">
+        <v>81</v>
+      </c>
+      <c r="I270">
+        <v>0</v>
+      </c>
+      <c r="J270">
+        <v>1</v>
+      </c>
+      <c r="K270">
+        <v>1</v>
+      </c>
+      <c r="L270">
+        <v>0</v>
+      </c>
+      <c r="M270">
+        <v>1</v>
+      </c>
+      <c r="N270">
+        <v>1</v>
+      </c>
+      <c r="O270" t="s">
+        <v>94</v>
+      </c>
+      <c r="P270" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q270">
+        <v>2.6</v>
+      </c>
+      <c r="R270">
+        <v>2</v>
+      </c>
+      <c r="S270">
+        <v>4.2</v>
+      </c>
+      <c r="T270">
+        <v>1.45</v>
+      </c>
+      <c r="U270">
+        <v>2.55</v>
+      </c>
+      <c r="V270">
+        <v>3.1</v>
+      </c>
+      <c r="W270">
+        <v>1.33</v>
+      </c>
+      <c r="X270">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y270">
+        <v>1.03</v>
+      </c>
+      <c r="Z270">
+        <v>1.98</v>
+      </c>
+      <c r="AA270">
+        <v>3.38</v>
+      </c>
+      <c r="AB270">
+        <v>4.3</v>
+      </c>
+      <c r="AC270">
+        <v>1.08</v>
+      </c>
+      <c r="AD270">
+        <v>7.5</v>
+      </c>
+      <c r="AE270">
+        <v>1.42</v>
+      </c>
+      <c r="AF270">
+        <v>2.85</v>
+      </c>
+      <c r="AG270">
+        <v>2.15</v>
+      </c>
+      <c r="AH270">
+        <v>1.57</v>
+      </c>
+      <c r="AI270">
+        <v>1.91</v>
+      </c>
+      <c r="AJ270">
+        <v>1.77</v>
+      </c>
+      <c r="AK270">
+        <v>1.25</v>
+      </c>
+      <c r="AL270">
+        <v>1.28</v>
+      </c>
+      <c r="AM270">
+        <v>1.77</v>
+      </c>
+      <c r="AN270">
+        <v>1.17</v>
+      </c>
+      <c r="AO270">
+        <v>1.25</v>
+      </c>
+      <c r="AP270">
+        <v>1.08</v>
+      </c>
+      <c r="AQ270">
+        <v>1.38</v>
+      </c>
+      <c r="AR270">
+        <v>1.69</v>
+      </c>
+      <c r="AS270">
+        <v>1.07</v>
+      </c>
+      <c r="AT270">
+        <v>2.76</v>
+      </c>
+      <c r="AU270">
+        <v>3</v>
+      </c>
+      <c r="AV270">
+        <v>3</v>
+      </c>
+      <c r="AW270">
+        <v>14</v>
+      </c>
+      <c r="AX270">
+        <v>6</v>
+      </c>
+      <c r="AY270">
+        <v>21</v>
+      </c>
+      <c r="AZ270">
+        <v>12</v>
+      </c>
+      <c r="BA270">
+        <v>7</v>
+      </c>
+      <c r="BB270">
+        <v>7</v>
+      </c>
+      <c r="BC270">
+        <v>14</v>
+      </c>
+      <c r="BD270">
+        <v>1.5</v>
+      </c>
+      <c r="BE270">
+        <v>6.75</v>
+      </c>
+      <c r="BF270">
+        <v>2.9</v>
+      </c>
+      <c r="BG270">
+        <v>1.38</v>
+      </c>
+      <c r="BH270">
+        <v>2.7</v>
+      </c>
+      <c r="BI270">
+        <v>1.65</v>
+      </c>
+      <c r="BJ270">
+        <v>2.06</v>
+      </c>
+      <c r="BK270">
+        <v>2.04</v>
+      </c>
+      <c r="BL270">
+        <v>1.66</v>
+      </c>
+      <c r="BM270">
+        <v>2.55</v>
+      </c>
+      <c r="BN270">
+        <v>1.43</v>
+      </c>
+      <c r="BO270">
+        <v>3.4</v>
+      </c>
+      <c r="BP270">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="271" spans="1:68">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>7728470</v>
+      </c>
+      <c r="C271" t="s">
+        <v>68</v>
+      </c>
+      <c r="D271" t="s">
+        <v>69</v>
+      </c>
+      <c r="E271" s="2">
+        <v>45690.51041666666</v>
+      </c>
+      <c r="F271">
+        <v>25</v>
+      </c>
+      <c r="G271" t="s">
+        <v>73</v>
+      </c>
+      <c r="H271" t="s">
+        <v>75</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
+        <v>1</v>
+      </c>
+      <c r="K271">
+        <v>1</v>
+      </c>
+      <c r="L271">
+        <v>0</v>
+      </c>
+      <c r="M271">
+        <v>1</v>
+      </c>
+      <c r="N271">
+        <v>1</v>
+      </c>
+      <c r="O271" t="s">
+        <v>94</v>
+      </c>
+      <c r="P271" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q271">
+        <v>3.2</v>
+      </c>
+      <c r="R271">
+        <v>2</v>
+      </c>
+      <c r="S271">
+        <v>3.75</v>
+      </c>
+      <c r="T271">
+        <v>1.5</v>
+      </c>
+      <c r="U271">
+        <v>2.5</v>
+      </c>
+      <c r="V271">
+        <v>3.5</v>
+      </c>
+      <c r="W271">
+        <v>1.29</v>
+      </c>
+      <c r="X271">
+        <v>11</v>
+      </c>
+      <c r="Y271">
+        <v>1.05</v>
+      </c>
+      <c r="Z271">
+        <v>2.43</v>
+      </c>
+      <c r="AA271">
+        <v>3.34</v>
+      </c>
+      <c r="AB271">
+        <v>3.08</v>
+      </c>
+      <c r="AC271">
+        <v>1.08</v>
+      </c>
+      <c r="AD271">
+        <v>7.5</v>
+      </c>
+      <c r="AE271">
+        <v>1.4</v>
+      </c>
+      <c r="AF271">
+        <v>2.8</v>
+      </c>
+      <c r="AG271">
+        <v>2.27</v>
+      </c>
+      <c r="AH271">
+        <v>1.6</v>
+      </c>
+      <c r="AI271">
+        <v>2</v>
+      </c>
+      <c r="AJ271">
+        <v>1.73</v>
+      </c>
+      <c r="AK271">
+        <v>1.36</v>
+      </c>
+      <c r="AL271">
+        <v>1.3</v>
+      </c>
+      <c r="AM271">
+        <v>1.55</v>
+      </c>
+      <c r="AN271">
+        <v>2</v>
+      </c>
+      <c r="AO271">
+        <v>1.33</v>
+      </c>
+      <c r="AP271">
+        <v>1.85</v>
+      </c>
+      <c r="AQ271">
+        <v>1.46</v>
+      </c>
+      <c r="AR271">
+        <v>1.48</v>
+      </c>
+      <c r="AS271">
+        <v>1.36</v>
+      </c>
+      <c r="AT271">
+        <v>2.84</v>
+      </c>
+      <c r="AU271">
+        <v>6</v>
+      </c>
+      <c r="AV271">
+        <v>3</v>
+      </c>
+      <c r="AW271">
+        <v>17</v>
+      </c>
+      <c r="AX271">
+        <v>4</v>
+      </c>
+      <c r="AY271">
+        <v>24</v>
+      </c>
+      <c r="AZ271">
+        <v>8</v>
+      </c>
+      <c r="BA271">
+        <v>12</v>
+      </c>
+      <c r="BB271">
+        <v>1</v>
+      </c>
+      <c r="BC271">
+        <v>13</v>
+      </c>
+      <c r="BD271">
+        <v>1.71</v>
+      </c>
+      <c r="BE271">
+        <v>6.4</v>
+      </c>
+      <c r="BF271">
+        <v>2.38</v>
+      </c>
+      <c r="BG271">
+        <v>1.36</v>
+      </c>
+      <c r="BH271">
+        <v>2.98</v>
+      </c>
+      <c r="BI271">
+        <v>1.62</v>
+      </c>
+      <c r="BJ271">
+        <v>2.22</v>
+      </c>
+      <c r="BK271">
+        <v>2.02</v>
+      </c>
+      <c r="BL271">
+        <v>1.74</v>
+      </c>
+      <c r="BM271">
+        <v>2.6</v>
+      </c>
+      <c r="BN271">
+        <v>1.46</v>
+      </c>
+      <c r="BO271">
+        <v>3.58</v>
+      </c>
+      <c r="BP271">
         <v>1.27</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="365">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -805,6 +805,9 @@
     <t>['15', '28']</t>
   </si>
   <si>
+    <t>['7', '49', '90+5']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1103,6 +1106,9 @@
   </si>
   <si>
     <t>['6']</t>
+  </si>
+  <si>
+    <t>['34']</t>
   </si>
 </sst>
 </file>
@@ -1464,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP271"/>
+  <dimension ref="A1:BP275"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1720,7 +1726,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1801,7 +1807,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ2">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2007,7 +2013,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ3">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2132,7 +2138,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2956,7 +2962,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3162,7 +3168,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3986,7 +3992,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4192,7 +4198,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4888,10 +4894,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5222,7 +5228,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5300,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ19">
         <v>1.62</v>
@@ -5840,7 +5846,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5918,7 +5924,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ22">
         <v>1.46</v>
@@ -6046,7 +6052,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6252,7 +6258,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6458,7 +6464,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6664,7 +6670,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6870,7 +6876,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6951,7 +6957,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ27">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.25</v>
@@ -7282,7 +7288,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7569,7 +7575,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ30">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR30">
         <v>1.73</v>
@@ -7900,7 +7906,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8106,7 +8112,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8393,7 +8399,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ34">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR34">
         <v>1.17</v>
@@ -8518,7 +8524,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8596,7 +8602,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ35">
         <v>2.17</v>
@@ -9832,7 +9838,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ41">
         <v>1.46</v>
@@ -10244,7 +10250,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ43">
         <v>1.17</v>
@@ -10372,7 +10378,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10453,7 +10459,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ44">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -10990,7 +10996,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11068,7 +11074,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ47">
         <v>0.75</v>
@@ -11895,7 +11901,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ51">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>0.76</v>
@@ -12513,7 +12519,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ54">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12638,7 +12644,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12844,7 +12850,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13050,7 +13056,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13256,7 +13262,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13337,7 +13343,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ58">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR58">
         <v>1.22</v>
@@ -13668,7 +13674,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13952,7 +13958,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ61">
         <v>1.46</v>
@@ -14158,7 +14164,7 @@
         <v>0.5</v>
       </c>
       <c r="AP62">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14286,7 +14292,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14364,10 +14370,10 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ63">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR63">
         <v>1.13</v>
@@ -14904,7 +14910,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15191,7 +15197,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ67">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR67">
         <v>1.16</v>
@@ -15316,7 +15322,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15522,7 +15528,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16140,7 +16146,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16346,7 +16352,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16424,7 +16430,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ73">
         <v>1.62</v>
@@ -16552,7 +16558,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17045,7 +17051,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ76">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -17376,7 +17382,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17582,7 +17588,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17663,7 +17669,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ79">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR79">
         <v>1.18</v>
@@ -17994,7 +18000,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18200,7 +18206,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18406,7 +18412,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18484,7 +18490,7 @@
         <v>3</v>
       </c>
       <c r="AP83">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ83">
         <v>2.17</v>
@@ -18896,7 +18902,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ85">
         <v>0.54</v>
@@ -19230,7 +19236,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19514,7 +19520,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ88">
         <v>1.38</v>
@@ -19642,7 +19648,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19723,7 +19729,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ89">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -19848,7 +19854,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19926,7 +19932,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ90">
         <v>1.46</v>
@@ -20132,10 +20138,10 @@
         <v>0.33</v>
       </c>
       <c r="AP91">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ91">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20260,7 +20266,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20672,7 +20678,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20753,7 +20759,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ94">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.16</v>
@@ -20878,7 +20884,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21371,7 +21377,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ97">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -21908,7 +21914,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23350,7 +23356,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23968,7 +23974,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24046,7 +24052,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ110">
         <v>1.62</v>
@@ -24380,7 +24386,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24586,7 +24592,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24873,7 +24879,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ114">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -24998,7 +25004,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25285,7 +25291,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ116">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -25488,7 +25494,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ117">
         <v>1.17</v>
@@ -25697,7 +25703,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ118">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>1.69</v>
@@ -25822,7 +25828,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -25900,7 +25906,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ119">
         <v>1.46</v>
@@ -26312,7 +26318,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ121">
         <v>0.85</v>
@@ -26440,7 +26446,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26521,7 +26527,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ122">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR122">
         <v>1.4</v>
@@ -26852,7 +26858,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27264,7 +27270,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27342,7 +27348,7 @@
         <v>1.8</v>
       </c>
       <c r="AP126">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ126">
         <v>1.25</v>
@@ -27676,7 +27682,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28088,7 +28094,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28294,7 +28300,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28500,7 +28506,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28912,7 +28918,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29118,7 +29124,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29196,7 +29202,7 @@
         <v>0.83</v>
       </c>
       <c r="AP135">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ135">
         <v>1.46</v>
@@ -29405,7 +29411,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ136">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -29608,7 +29614,7 @@
         <v>2.2</v>
       </c>
       <c r="AP137">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ137">
         <v>1.5</v>
@@ -29736,7 +29742,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29817,7 +29823,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ138">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR138">
         <v>1.52</v>
@@ -30226,7 +30232,7 @@
         <v>1</v>
       </c>
       <c r="AP140">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ140">
         <v>1.17</v>
@@ -30354,7 +30360,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30560,7 +30566,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30641,7 +30647,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ142">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR142">
         <v>1.16</v>
@@ -30766,7 +30772,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30972,7 +30978,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31384,7 +31390,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31796,7 +31802,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32495,7 +32501,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ151">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR151">
         <v>1.43</v>
@@ -32701,7 +32707,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ152">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>1.54</v>
@@ -32826,7 +32832,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33110,7 +33116,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ154">
         <v>1.17</v>
@@ -33444,7 +33450,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33731,7 +33737,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ157">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR157">
         <v>1.49</v>
@@ -34346,7 +34352,7 @@
         <v>1.17</v>
       </c>
       <c r="AP160">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ160">
         <v>1.38</v>
@@ -34552,7 +34558,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ161">
         <v>0.85</v>
@@ -35092,7 +35098,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35170,7 +35176,7 @@
         <v>1.38</v>
       </c>
       <c r="AP164">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ164">
         <v>1.62</v>
@@ -35379,7 +35385,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ165">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR165">
         <v>1.7</v>
@@ -35710,7 +35716,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36122,7 +36128,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36740,7 +36746,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37233,7 +37239,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ174">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR174">
         <v>1.76</v>
@@ -37358,7 +37364,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37436,7 +37442,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ175">
         <v>0.85</v>
@@ -37645,7 +37651,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ176">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR176">
         <v>1.6</v>
@@ -37770,7 +37776,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38054,10 +38060,10 @@
         <v>1</v>
       </c>
       <c r="AP178">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ178">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR178">
         <v>1.71</v>
@@ -38182,7 +38188,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38388,7 +38394,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38878,7 +38884,7 @@
         <v>1.14</v>
       </c>
       <c r="AP182">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ182">
         <v>1.17</v>
@@ -39212,7 +39218,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39290,7 +39296,7 @@
         <v>0.88</v>
       </c>
       <c r="AP184">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ184">
         <v>0.75</v>
@@ -39499,7 +39505,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ185">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR185">
         <v>1.42</v>
@@ -39705,7 +39711,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ186">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR186">
         <v>1.44</v>
@@ -40036,7 +40042,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40323,7 +40329,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ189">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR189">
         <v>1.53</v>
@@ -40654,7 +40660,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40860,7 +40866,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41066,7 +41072,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41272,7 +41278,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42174,7 +42180,7 @@
         <v>1.25</v>
       </c>
       <c r="AP198">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42508,7 +42514,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42586,10 +42592,10 @@
         <v>0.11</v>
       </c>
       <c r="AP200">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ200">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR200">
         <v>1.61</v>
@@ -42795,7 +42801,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ201">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR201">
         <v>1.46</v>
@@ -42920,7 +42926,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43126,7 +43132,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43744,7 +43750,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43825,7 +43831,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ206">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR206">
         <v>1.42</v>
@@ -44156,7 +44162,7 @@
         <v>94</v>
       </c>
       <c r="P208" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44774,7 +44780,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44980,7 +44986,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45058,7 +45064,7 @@
         <v>1.1</v>
       </c>
       <c r="AP212">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ212">
         <v>1.38</v>
@@ -45186,7 +45192,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45392,7 +45398,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45804,7 +45810,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46706,10 +46712,10 @@
         <v>1.1</v>
       </c>
       <c r="AP220">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ220">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR220">
         <v>1.23</v>
@@ -47040,7 +47046,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47121,7 +47127,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ222">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR222">
         <v>1.64</v>
@@ -47324,10 +47330,10 @@
         <v>1.11</v>
       </c>
       <c r="AP223">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ223">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR223">
         <v>1.71</v>
@@ -47452,7 +47458,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47864,7 +47870,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48070,7 +48076,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48151,7 +48157,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ227">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR227">
         <v>1.67</v>
@@ -48482,7 +48488,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48688,7 +48694,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48766,7 +48772,7 @@
         <v>1.3</v>
       </c>
       <c r="AP230">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ230">
         <v>1.38</v>
@@ -48894,7 +48900,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -48972,7 +48978,7 @@
         <v>1.2</v>
       </c>
       <c r="AP231">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ231">
         <v>1.46</v>
@@ -49718,7 +49724,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50002,7 +50008,7 @@
         <v>1.5</v>
       </c>
       <c r="AP236">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ236">
         <v>1.25</v>
@@ -50542,7 +50548,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51160,7 +51166,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51444,7 +51450,7 @@
         <v>1.27</v>
       </c>
       <c r="AP243">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ243">
         <v>1.38</v>
@@ -51572,7 +51578,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51653,7 +51659,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ244">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR244">
         <v>1.4</v>
@@ -51778,7 +51784,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -52065,7 +52071,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ246">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR246">
         <v>1.49</v>
@@ -52268,7 +52274,7 @@
         <v>1.5</v>
       </c>
       <c r="AP247">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ247">
         <v>1.5</v>
@@ -52683,7 +52689,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ249">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR249">
         <v>1.51</v>
@@ -52808,7 +52814,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -52889,7 +52895,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ250">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR250">
         <v>1.68</v>
@@ -53014,7 +53020,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53092,7 +53098,7 @@
         <v>0.18</v>
       </c>
       <c r="AP251">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ251">
         <v>0.25</v>
@@ -53426,7 +53432,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53838,7 +53844,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54044,7 +54050,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54456,7 +54462,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -54534,7 +54540,7 @@
         <v>0.55</v>
       </c>
       <c r="AP258">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ258">
         <v>0.75</v>
@@ -55074,7 +55080,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55280,7 +55286,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55770,7 +55776,7 @@
         <v>1.36</v>
       </c>
       <c r="AP264">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ264">
         <v>1.46</v>
@@ -55898,7 +55904,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56722,7 +56728,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57291,6 +57297,830 @@
       </c>
       <c r="BP271">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="272" spans="1:68">
+      <c r="A272" s="1">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>7728469</v>
+      </c>
+      <c r="C272" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" t="s">
+        <v>69</v>
+      </c>
+      <c r="E272" s="2">
+        <v>45690.60416666666</v>
+      </c>
+      <c r="F272">
+        <v>25</v>
+      </c>
+      <c r="G272" t="s">
+        <v>91</v>
+      </c>
+      <c r="H272" t="s">
+        <v>72</v>
+      </c>
+      <c r="I272">
+        <v>0</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>0</v>
+      </c>
+      <c r="L272">
+        <v>0</v>
+      </c>
+      <c r="M272">
+        <v>0</v>
+      </c>
+      <c r="N272">
+        <v>0</v>
+      </c>
+      <c r="O272" t="s">
+        <v>94</v>
+      </c>
+      <c r="P272" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q272">
+        <v>3</v>
+      </c>
+      <c r="R272">
+        <v>1.95</v>
+      </c>
+      <c r="S272">
+        <v>4.33</v>
+      </c>
+      <c r="T272">
+        <v>1.53</v>
+      </c>
+      <c r="U272">
+        <v>2.38</v>
+      </c>
+      <c r="V272">
+        <v>3.5</v>
+      </c>
+      <c r="W272">
+        <v>1.29</v>
+      </c>
+      <c r="X272">
+        <v>11</v>
+      </c>
+      <c r="Y272">
+        <v>1.05</v>
+      </c>
+      <c r="Z272">
+        <v>1.95</v>
+      </c>
+      <c r="AA272">
+        <v>3.41</v>
+      </c>
+      <c r="AB272">
+        <v>4.33</v>
+      </c>
+      <c r="AC272">
+        <v>1.1</v>
+      </c>
+      <c r="AD272">
+        <v>6.5</v>
+      </c>
+      <c r="AE272">
+        <v>1.44</v>
+      </c>
+      <c r="AF272">
+        <v>2.65</v>
+      </c>
+      <c r="AG272">
+        <v>1.96</v>
+      </c>
+      <c r="AH272">
+        <v>1.85</v>
+      </c>
+      <c r="AI272">
+        <v>2</v>
+      </c>
+      <c r="AJ272">
+        <v>1.73</v>
+      </c>
+      <c r="AK272">
+        <v>1.28</v>
+      </c>
+      <c r="AL272">
+        <v>1.33</v>
+      </c>
+      <c r="AM272">
+        <v>1.68</v>
+      </c>
+      <c r="AN272">
+        <v>1.27</v>
+      </c>
+      <c r="AO272">
+        <v>1.18</v>
+      </c>
+      <c r="AP272">
+        <v>1.25</v>
+      </c>
+      <c r="AQ272">
+        <v>1.17</v>
+      </c>
+      <c r="AR272">
+        <v>1.65</v>
+      </c>
+      <c r="AS272">
+        <v>1.24</v>
+      </c>
+      <c r="AT272">
+        <v>2.89</v>
+      </c>
+      <c r="AU272">
+        <v>3</v>
+      </c>
+      <c r="AV272">
+        <v>2</v>
+      </c>
+      <c r="AW272">
+        <v>5</v>
+      </c>
+      <c r="AX272">
+        <v>9</v>
+      </c>
+      <c r="AY272">
+        <v>11</v>
+      </c>
+      <c r="AZ272">
+        <v>15</v>
+      </c>
+      <c r="BA272">
+        <v>4</v>
+      </c>
+      <c r="BB272">
+        <v>2</v>
+      </c>
+      <c r="BC272">
+        <v>6</v>
+      </c>
+      <c r="BD272">
+        <v>1.61</v>
+      </c>
+      <c r="BE272">
+        <v>6.75</v>
+      </c>
+      <c r="BF272">
+        <v>2.55</v>
+      </c>
+      <c r="BG272">
+        <v>1.4</v>
+      </c>
+      <c r="BH272">
+        <v>2.82</v>
+      </c>
+      <c r="BI272">
+        <v>1.68</v>
+      </c>
+      <c r="BJ272">
+        <v>2.12</v>
+      </c>
+      <c r="BK272">
+        <v>2.11</v>
+      </c>
+      <c r="BL272">
+        <v>1.68</v>
+      </c>
+      <c r="BM272">
+        <v>2.75</v>
+      </c>
+      <c r="BN272">
+        <v>1.42</v>
+      </c>
+      <c r="BO272">
+        <v>3.8</v>
+      </c>
+      <c r="BP272">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="273" spans="1:68">
+      <c r="A273" s="1">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>7728464</v>
+      </c>
+      <c r="C273" t="s">
+        <v>68</v>
+      </c>
+      <c r="D273" t="s">
+        <v>69</v>
+      </c>
+      <c r="E273" s="2">
+        <v>45690.60416666666</v>
+      </c>
+      <c r="F273">
+        <v>25</v>
+      </c>
+      <c r="G273" t="s">
+        <v>87</v>
+      </c>
+      <c r="H273" t="s">
+        <v>88</v>
+      </c>
+      <c r="I273">
+        <v>0</v>
+      </c>
+      <c r="J273">
+        <v>1</v>
+      </c>
+      <c r="K273">
+        <v>1</v>
+      </c>
+      <c r="L273">
+        <v>0</v>
+      </c>
+      <c r="M273">
+        <v>1</v>
+      </c>
+      <c r="N273">
+        <v>1</v>
+      </c>
+      <c r="O273" t="s">
+        <v>94</v>
+      </c>
+      <c r="P273" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q273">
+        <v>4</v>
+      </c>
+      <c r="R273">
+        <v>2.05</v>
+      </c>
+      <c r="S273">
+        <v>2.6</v>
+      </c>
+      <c r="T273">
+        <v>1.42</v>
+      </c>
+      <c r="U273">
+        <v>2.65</v>
+      </c>
+      <c r="V273">
+        <v>2.88</v>
+      </c>
+      <c r="W273">
+        <v>1.36</v>
+      </c>
+      <c r="X273">
+        <v>7.6</v>
+      </c>
+      <c r="Y273">
+        <v>1.05</v>
+      </c>
+      <c r="Z273">
+        <v>3.98</v>
+      </c>
+      <c r="AA273">
+        <v>3.4</v>
+      </c>
+      <c r="AB273">
+        <v>2.04</v>
+      </c>
+      <c r="AC273">
+        <v>1.07</v>
+      </c>
+      <c r="AD273">
+        <v>8</v>
+      </c>
+      <c r="AE273">
+        <v>1.36</v>
+      </c>
+      <c r="AF273">
+        <v>3.1</v>
+      </c>
+      <c r="AG273">
+        <v>2</v>
+      </c>
+      <c r="AH273">
+        <v>1.67</v>
+      </c>
+      <c r="AI273">
+        <v>1.83</v>
+      </c>
+      <c r="AJ273">
+        <v>1.85</v>
+      </c>
+      <c r="AK273">
+        <v>1.75</v>
+      </c>
+      <c r="AL273">
+        <v>1.25</v>
+      </c>
+      <c r="AM273">
+        <v>1.25</v>
+      </c>
+      <c r="AN273">
+        <v>0.73</v>
+      </c>
+      <c r="AO273">
+        <v>0.67</v>
+      </c>
+      <c r="AP273">
+        <v>0.67</v>
+      </c>
+      <c r="AQ273">
+        <v>0.85</v>
+      </c>
+      <c r="AR273">
+        <v>1.18</v>
+      </c>
+      <c r="AS273">
+        <v>1.33</v>
+      </c>
+      <c r="AT273">
+        <v>2.51</v>
+      </c>
+      <c r="AU273">
+        <v>2</v>
+      </c>
+      <c r="AV273">
+        <v>6</v>
+      </c>
+      <c r="AW273">
+        <v>8</v>
+      </c>
+      <c r="AX273">
+        <v>17</v>
+      </c>
+      <c r="AY273">
+        <v>11</v>
+      </c>
+      <c r="AZ273">
+        <v>28</v>
+      </c>
+      <c r="BA273">
+        <v>8</v>
+      </c>
+      <c r="BB273">
+        <v>6</v>
+      </c>
+      <c r="BC273">
+        <v>14</v>
+      </c>
+      <c r="BD273">
+        <v>2.55</v>
+      </c>
+      <c r="BE273">
+        <v>6.4</v>
+      </c>
+      <c r="BF273">
+        <v>1.63</v>
+      </c>
+      <c r="BG273">
+        <v>1.41</v>
+      </c>
+      <c r="BH273">
+        <v>2.6</v>
+      </c>
+      <c r="BI273">
+        <v>1.71</v>
+      </c>
+      <c r="BJ273">
+        <v>1.98</v>
+      </c>
+      <c r="BK273">
+        <v>2.14</v>
+      </c>
+      <c r="BL273">
+        <v>1.6</v>
+      </c>
+      <c r="BM273">
+        <v>2.8</v>
+      </c>
+      <c r="BN273">
+        <v>1.36</v>
+      </c>
+      <c r="BO273">
+        <v>3.65</v>
+      </c>
+      <c r="BP273">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="274" spans="1:68">
+      <c r="A274" s="1">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>7728467</v>
+      </c>
+      <c r="C274" t="s">
+        <v>68</v>
+      </c>
+      <c r="D274" t="s">
+        <v>69</v>
+      </c>
+      <c r="E274" s="2">
+        <v>45690.70833333334</v>
+      </c>
+      <c r="F274">
+        <v>25</v>
+      </c>
+      <c r="G274" t="s">
+        <v>84</v>
+      </c>
+      <c r="H274" t="s">
+        <v>85</v>
+      </c>
+      <c r="I274">
+        <v>1</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274">
+        <v>1</v>
+      </c>
+      <c r="L274">
+        <v>3</v>
+      </c>
+      <c r="M274">
+        <v>1</v>
+      </c>
+      <c r="N274">
+        <v>4</v>
+      </c>
+      <c r="O274" t="s">
+        <v>263</v>
+      </c>
+      <c r="P274" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q274">
+        <v>3</v>
+      </c>
+      <c r="R274">
+        <v>1.95</v>
+      </c>
+      <c r="S274">
+        <v>4.33</v>
+      </c>
+      <c r="T274">
+        <v>1.53</v>
+      </c>
+      <c r="U274">
+        <v>2.38</v>
+      </c>
+      <c r="V274">
+        <v>3.75</v>
+      </c>
+      <c r="W274">
+        <v>1.25</v>
+      </c>
+      <c r="X274">
+        <v>11</v>
+      </c>
+      <c r="Y274">
+        <v>1.05</v>
+      </c>
+      <c r="Z274">
+        <v>2.77</v>
+      </c>
+      <c r="AA274">
+        <v>3.19</v>
+      </c>
+      <c r="AB274">
+        <v>2.77</v>
+      </c>
+      <c r="AC274">
+        <v>1.09</v>
+      </c>
+      <c r="AD274">
+        <v>7</v>
+      </c>
+      <c r="AE274">
+        <v>1.5</v>
+      </c>
+      <c r="AF274">
+        <v>2.4</v>
+      </c>
+      <c r="AG274">
+        <v>2.1</v>
+      </c>
+      <c r="AH274">
+        <v>1.6</v>
+      </c>
+      <c r="AI274">
+        <v>2.1</v>
+      </c>
+      <c r="AJ274">
+        <v>1.67</v>
+      </c>
+      <c r="AK274">
+        <v>1.3</v>
+      </c>
+      <c r="AL274">
+        <v>1.3</v>
+      </c>
+      <c r="AM274">
+        <v>1.63</v>
+      </c>
+      <c r="AN274">
+        <v>1.08</v>
+      </c>
+      <c r="AO274">
+        <v>1.08</v>
+      </c>
+      <c r="AP274">
+        <v>1.23</v>
+      </c>
+      <c r="AQ274">
+        <v>1</v>
+      </c>
+      <c r="AR274">
+        <v>1.29</v>
+      </c>
+      <c r="AS274">
+        <v>1.29</v>
+      </c>
+      <c r="AT274">
+        <v>2.58</v>
+      </c>
+      <c r="AU274">
+        <v>6</v>
+      </c>
+      <c r="AV274">
+        <v>3</v>
+      </c>
+      <c r="AW274">
+        <v>10</v>
+      </c>
+      <c r="AX274">
+        <v>5</v>
+      </c>
+      <c r="AY274">
+        <v>18</v>
+      </c>
+      <c r="AZ274">
+        <v>9</v>
+      </c>
+      <c r="BA274">
+        <v>3</v>
+      </c>
+      <c r="BB274">
+        <v>2</v>
+      </c>
+      <c r="BC274">
+        <v>5</v>
+      </c>
+      <c r="BD274">
+        <v>1.81</v>
+      </c>
+      <c r="BE274">
+        <v>6.4</v>
+      </c>
+      <c r="BF274">
+        <v>2.18</v>
+      </c>
+      <c r="BG274">
+        <v>1.4</v>
+      </c>
+      <c r="BH274">
+        <v>2.82</v>
+      </c>
+      <c r="BI274">
+        <v>1.68</v>
+      </c>
+      <c r="BJ274">
+        <v>2.12</v>
+      </c>
+      <c r="BK274">
+        <v>2.11</v>
+      </c>
+      <c r="BL274">
+        <v>1.68</v>
+      </c>
+      <c r="BM274">
+        <v>2.75</v>
+      </c>
+      <c r="BN274">
+        <v>1.42</v>
+      </c>
+      <c r="BO274">
+        <v>3.8</v>
+      </c>
+      <c r="BP274">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="275" spans="1:68">
+      <c r="A275" s="1">
+        <v>274</v>
+      </c>
+      <c r="B275">
+        <v>7728472</v>
+      </c>
+      <c r="C275" t="s">
+        <v>68</v>
+      </c>
+      <c r="D275" t="s">
+        <v>69</v>
+      </c>
+      <c r="E275" s="2">
+        <v>45691.6875</v>
+      </c>
+      <c r="F275">
+        <v>25</v>
+      </c>
+      <c r="G275" t="s">
+        <v>82</v>
+      </c>
+      <c r="H275" t="s">
+        <v>74</v>
+      </c>
+      <c r="I275">
+        <v>0</v>
+      </c>
+      <c r="J275">
+        <v>1</v>
+      </c>
+      <c r="K275">
+        <v>1</v>
+      </c>
+      <c r="L275">
+        <v>0</v>
+      </c>
+      <c r="M275">
+        <v>1</v>
+      </c>
+      <c r="N275">
+        <v>1</v>
+      </c>
+      <c r="O275" t="s">
+        <v>94</v>
+      </c>
+      <c r="P275" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q275">
+        <v>2</v>
+      </c>
+      <c r="R275">
+        <v>2.3</v>
+      </c>
+      <c r="S275">
+        <v>7</v>
+      </c>
+      <c r="T275">
+        <v>1.4</v>
+      </c>
+      <c r="U275">
+        <v>2.75</v>
+      </c>
+      <c r="V275">
+        <v>2.75</v>
+      </c>
+      <c r="W275">
+        <v>1.4</v>
+      </c>
+      <c r="X275">
+        <v>8</v>
+      </c>
+      <c r="Y275">
+        <v>1.08</v>
+      </c>
+      <c r="Z275">
+        <v>1.49</v>
+      </c>
+      <c r="AA275">
+        <v>4.6</v>
+      </c>
+      <c r="AB275">
+        <v>6.8</v>
+      </c>
+      <c r="AC275">
+        <v>1</v>
+      </c>
+      <c r="AD275">
+        <v>11.3</v>
+      </c>
+      <c r="AE275">
+        <v>1.3</v>
+      </c>
+      <c r="AF275">
+        <v>3.5</v>
+      </c>
+      <c r="AG275">
+        <v>1.9</v>
+      </c>
+      <c r="AH275">
+        <v>1.9</v>
+      </c>
+      <c r="AI275">
+        <v>2.1</v>
+      </c>
+      <c r="AJ275">
+        <v>1.67</v>
+      </c>
+      <c r="AK275">
+        <v>1.04</v>
+      </c>
+      <c r="AL275">
+        <v>1.16</v>
+      </c>
+      <c r="AM275">
+        <v>2.8</v>
+      </c>
+      <c r="AN275">
+        <v>2.09</v>
+      </c>
+      <c r="AO275">
+        <v>0.91</v>
+      </c>
+      <c r="AP275">
+        <v>1.92</v>
+      </c>
+      <c r="AQ275">
+        <v>1.08</v>
+      </c>
+      <c r="AR275">
+        <v>1.57</v>
+      </c>
+      <c r="AS275">
+        <v>0.86</v>
+      </c>
+      <c r="AT275">
+        <v>2.43</v>
+      </c>
+      <c r="AU275">
+        <v>9</v>
+      </c>
+      <c r="AV275">
+        <v>4</v>
+      </c>
+      <c r="AW275">
+        <v>16</v>
+      </c>
+      <c r="AX275">
+        <v>2</v>
+      </c>
+      <c r="AY275">
+        <v>32</v>
+      </c>
+      <c r="AZ275">
+        <v>7</v>
+      </c>
+      <c r="BA275">
+        <v>11</v>
+      </c>
+      <c r="BB275">
+        <v>2</v>
+      </c>
+      <c r="BC275">
+        <v>13</v>
+      </c>
+      <c r="BD275">
+        <v>1.43</v>
+      </c>
+      <c r="BE275">
+        <v>6.75</v>
+      </c>
+      <c r="BF275">
+        <v>3.15</v>
+      </c>
+      <c r="BG275">
+        <v>1.28</v>
+      </c>
+      <c r="BH275">
+        <v>3.05</v>
+      </c>
+      <c r="BI275">
+        <v>1.55</v>
+      </c>
+      <c r="BJ275">
+        <v>2.23</v>
+      </c>
+      <c r="BK275">
+        <v>1.96</v>
+      </c>
+      <c r="BL275">
+        <v>1.75</v>
+      </c>
+      <c r="BM275">
+        <v>2.57</v>
+      </c>
+      <c r="BN275">
+        <v>1.42</v>
+      </c>
+      <c r="BO275">
+        <v>3.5</v>
+      </c>
+      <c r="BP275">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="366">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -808,6 +808,9 @@
     <t>['7', '49', '90+5']</t>
   </si>
   <si>
+    <t>['46', '58']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1470,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP275"/>
+  <dimension ref="A1:BP276"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1726,7 +1729,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2138,7 +2141,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2219,7 +2222,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ4">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2962,7 +2965,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3168,7 +3171,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3992,7 +3995,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4198,7 +4201,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -5228,7 +5231,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5512,7 +5515,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ20">
         <v>1.17</v>
@@ -5846,7 +5849,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5927,7 +5930,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ22">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6052,7 +6055,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6258,7 +6261,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6464,7 +6467,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6670,7 +6673,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6876,7 +6879,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7288,7 +7291,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7781,7 +7784,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ31">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR31">
         <v>0.48</v>
@@ -7906,7 +7909,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8112,7 +8115,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8524,7 +8527,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -10378,7 +10381,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10662,7 +10665,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ45">
         <v>0.67</v>
@@ -10996,7 +10999,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12313,7 +12316,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ53">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR53">
         <v>1.46</v>
@@ -12644,7 +12647,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12850,7 +12853,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13056,7 +13059,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13262,7 +13265,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13674,7 +13677,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14292,7 +14295,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14910,7 +14913,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15322,7 +15325,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15400,7 +15403,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ68">
         <v>1.46</v>
@@ -15528,7 +15531,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16021,7 +16024,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ71">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR71">
         <v>1.44</v>
@@ -16146,7 +16149,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16352,7 +16355,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16558,7 +16561,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17382,7 +17385,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17588,7 +17591,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18000,7 +18003,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18206,7 +18209,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18412,7 +18415,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19236,7 +19239,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19648,7 +19651,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19726,7 +19729,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ89">
         <v>0.85</v>
@@ -19854,7 +19857,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19935,7 +19938,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ90">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR90">
         <v>1.45</v>
@@ -20266,7 +20269,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20678,7 +20681,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20884,7 +20887,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21914,7 +21917,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23356,7 +23359,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23974,7 +23977,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24258,7 +24261,7 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ111">
         <v>0.75</v>
@@ -24386,7 +24389,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24592,7 +24595,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25004,7 +25007,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25085,7 +25088,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ115">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR115">
         <v>1.49</v>
@@ -25828,7 +25831,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26446,7 +26449,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26858,7 +26861,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27270,7 +27273,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27682,7 +27685,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28094,7 +28097,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28172,7 +28175,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28300,7 +28303,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28506,7 +28509,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28918,7 +28921,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29124,7 +29127,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29742,7 +29745,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30360,7 +30363,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30566,7 +30569,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30772,7 +30775,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30853,7 +30856,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ143">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR143">
         <v>1.11</v>
@@ -30978,7 +30981,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31390,7 +31393,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31802,7 +31805,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32086,7 +32089,7 @@
         <v>1</v>
       </c>
       <c r="AP149">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ149">
         <v>1.38</v>
@@ -32832,7 +32835,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33450,7 +33453,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -35098,7 +35101,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35716,7 +35719,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35797,7 +35800,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ167">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR167">
         <v>1.65</v>
@@ -36128,7 +36131,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36206,7 +36209,7 @@
         <v>0.29</v>
       </c>
       <c r="AP169">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ169">
         <v>0.25</v>
@@ -36746,7 +36749,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37364,7 +37367,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37776,7 +37779,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38188,7 +38191,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38394,7 +38397,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39218,7 +39221,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40042,7 +40045,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40660,7 +40663,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40741,7 +40744,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ191">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR191">
         <v>1.48</v>
@@ -40866,7 +40869,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41072,7 +41075,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41278,7 +41281,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41562,7 +41565,7 @@
         <v>1.75</v>
       </c>
       <c r="AP195">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ195">
         <v>1.25</v>
@@ -42514,7 +42517,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42926,7 +42929,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43132,7 +43135,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43213,7 +43216,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ203">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR203">
         <v>1.49</v>
@@ -43750,7 +43753,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44162,7 +44165,7 @@
         <v>94</v>
       </c>
       <c r="P208" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44652,7 +44655,7 @@
         <v>1.22</v>
       </c>
       <c r="AP210">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ210">
         <v>1.46</v>
@@ -44780,7 +44783,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44986,7 +44989,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45192,7 +45195,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45398,7 +45401,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45810,7 +45813,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -47046,7 +47049,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47458,7 +47461,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47870,7 +47873,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48076,7 +48079,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48488,7 +48491,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48694,7 +48697,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48900,7 +48903,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49724,7 +49727,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -49802,7 +49805,7 @@
         <v>2.2</v>
       </c>
       <c r="AP235">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ235">
         <v>2.17</v>
@@ -50548,7 +50551,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51041,7 +51044,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ241">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR241">
         <v>1.63</v>
@@ -51166,7 +51169,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51578,7 +51581,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51784,7 +51787,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -52814,7 +52817,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53020,7 +53023,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53432,7 +53435,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53844,7 +53847,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54050,7 +54053,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54462,7 +54465,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -55080,7 +55083,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55158,7 +55161,7 @@
         <v>1.75</v>
       </c>
       <c r="AP261">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ261">
         <v>1.62</v>
@@ -55286,7 +55289,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55367,7 +55370,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ262">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR262">
         <v>1.34</v>
@@ -55904,7 +55907,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56728,7 +56731,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57552,7 +57555,7 @@
         <v>94</v>
       </c>
       <c r="P273" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q273">
         <v>4</v>
@@ -58121,6 +58124,212 @@
       </c>
       <c r="BP275">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="276" spans="1:68">
+      <c r="A276" s="1">
+        <v>275</v>
+      </c>
+      <c r="B276">
+        <v>7728474</v>
+      </c>
+      <c r="C276" t="s">
+        <v>68</v>
+      </c>
+      <c r="D276" t="s">
+        <v>69</v>
+      </c>
+      <c r="E276" s="2">
+        <v>45695.6875</v>
+      </c>
+      <c r="F276">
+        <v>26</v>
+      </c>
+      <c r="G276" t="s">
+        <v>85</v>
+      </c>
+      <c r="H276" t="s">
+        <v>91</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>0</v>
+      </c>
+      <c r="L276">
+        <v>2</v>
+      </c>
+      <c r="M276">
+        <v>1</v>
+      </c>
+      <c r="N276">
+        <v>3</v>
+      </c>
+      <c r="O276" t="s">
+        <v>264</v>
+      </c>
+      <c r="P276" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q276">
+        <v>3.1</v>
+      </c>
+      <c r="R276">
+        <v>2</v>
+      </c>
+      <c r="S276">
+        <v>4</v>
+      </c>
+      <c r="T276">
+        <v>1.53</v>
+      </c>
+      <c r="U276">
+        <v>2.38</v>
+      </c>
+      <c r="V276">
+        <v>3.5</v>
+      </c>
+      <c r="W276">
+        <v>1.29</v>
+      </c>
+      <c r="X276">
+        <v>11</v>
+      </c>
+      <c r="Y276">
+        <v>1.05</v>
+      </c>
+      <c r="Z276">
+        <v>2.43</v>
+      </c>
+      <c r="AA276">
+        <v>3.15</v>
+      </c>
+      <c r="AB276">
+        <v>3.26</v>
+      </c>
+      <c r="AC276">
+        <v>1.09</v>
+      </c>
+      <c r="AD276">
+        <v>7</v>
+      </c>
+      <c r="AE276">
+        <v>1.44</v>
+      </c>
+      <c r="AF276">
+        <v>2.75</v>
+      </c>
+      <c r="AG276">
+        <v>2.2</v>
+      </c>
+      <c r="AH276">
+        <v>1.55</v>
+      </c>
+      <c r="AI276">
+        <v>2</v>
+      </c>
+      <c r="AJ276">
+        <v>1.73</v>
+      </c>
+      <c r="AK276">
+        <v>1.35</v>
+      </c>
+      <c r="AL276">
+        <v>1.34</v>
+      </c>
+      <c r="AM276">
+        <v>1.57</v>
+      </c>
+      <c r="AN276">
+        <v>1.5</v>
+      </c>
+      <c r="AO276">
+        <v>1.46</v>
+      </c>
+      <c r="AP276">
+        <v>1.62</v>
+      </c>
+      <c r="AQ276">
+        <v>1.36</v>
+      </c>
+      <c r="AR276">
+        <v>1.54</v>
+      </c>
+      <c r="AS276">
+        <v>1.33</v>
+      </c>
+      <c r="AT276">
+        <v>2.87</v>
+      </c>
+      <c r="AU276">
+        <v>4</v>
+      </c>
+      <c r="AV276">
+        <v>7</v>
+      </c>
+      <c r="AW276">
+        <v>11</v>
+      </c>
+      <c r="AX276">
+        <v>8</v>
+      </c>
+      <c r="AY276">
+        <v>19</v>
+      </c>
+      <c r="AZ276">
+        <v>15</v>
+      </c>
+      <c r="BA276">
+        <v>6</v>
+      </c>
+      <c r="BB276">
+        <v>2</v>
+      </c>
+      <c r="BC276">
+        <v>8</v>
+      </c>
+      <c r="BD276">
+        <v>1.76</v>
+      </c>
+      <c r="BE276">
+        <v>6.5</v>
+      </c>
+      <c r="BF276">
+        <v>2.28</v>
+      </c>
+      <c r="BG276">
+        <v>1.36</v>
+      </c>
+      <c r="BH276">
+        <v>2.8</v>
+      </c>
+      <c r="BI276">
+        <v>1.62</v>
+      </c>
+      <c r="BJ276">
+        <v>2.1</v>
+      </c>
+      <c r="BK276">
+        <v>2</v>
+      </c>
+      <c r="BL276">
+        <v>1.68</v>
+      </c>
+      <c r="BM276">
+        <v>2.55</v>
+      </c>
+      <c r="BN276">
+        <v>1.42</v>
+      </c>
+      <c r="BO276">
+        <v>3.4</v>
+      </c>
+      <c r="BP276">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="367">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -811,6 +811,9 @@
     <t>['46', '58']</t>
   </si>
   <si>
+    <t>['68']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1039,9 +1042,6 @@
     <t>['15', '27', '44']</t>
   </si>
   <si>
-    <t>['68']</t>
-  </si>
-  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -1112,6 +1112,9 @@
   </si>
   <si>
     <t>['34']</t>
+  </si>
+  <si>
+    <t>['4', '14', '78']</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP276"/>
+  <dimension ref="A1:BP280"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1729,7 +1732,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1807,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -2141,7 +2144,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2428,7 +2431,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ5">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2631,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ6">
         <v>0.85</v>
@@ -2965,7 +2968,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3043,10 +3046,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ8">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3171,7 +3174,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3995,7 +3998,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4076,7 +4079,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ13">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR13">
         <v>1.32</v>
@@ -4201,7 +4204,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4485,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ15">
         <v>0.75</v>
@@ -4691,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ16">
         <v>1.5</v>
@@ -5103,10 +5106,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5231,7 +5234,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5849,7 +5852,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6055,7 +6058,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6261,7 +6264,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6339,7 +6342,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ24">
         <v>1.38</v>
@@ -6467,7 +6470,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6673,7 +6676,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6879,7 +6882,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6957,7 +6960,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7291,7 +7294,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7372,7 +7375,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR29">
         <v>1.44</v>
@@ -7909,7 +7912,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8115,7 +8118,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8196,7 +8199,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ33">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR33">
         <v>0.95</v>
@@ -8527,7 +8530,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8811,7 +8814,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ36">
         <v>1.46</v>
@@ -9223,7 +9226,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ38">
         <v>1.38</v>
@@ -9635,10 +9638,10 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ40">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -9844,7 +9847,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ41">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR41">
         <v>1</v>
@@ -10381,7 +10384,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10668,7 +10671,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ45">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR45">
         <v>0.96</v>
@@ -10999,7 +11002,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11489,7 +11492,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ49">
         <v>1.38</v>
@@ -12647,7 +12650,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12853,7 +12856,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -12934,7 +12937,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ56">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR56">
         <v>1.94</v>
@@ -13059,7 +13062,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13137,7 +13140,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ57">
         <v>0.85</v>
@@ -13265,7 +13268,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13343,7 +13346,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13677,7 +13680,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13964,7 +13967,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ61">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -14295,7 +14298,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14788,7 +14791,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ65">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR65">
         <v>1.25</v>
@@ -14913,7 +14916,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14994,7 +14997,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ66">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR66">
         <v>1.93</v>
@@ -15325,7 +15328,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15531,7 +15534,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16021,7 +16024,7 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ71">
         <v>1.36</v>
@@ -16149,7 +16152,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16227,7 +16230,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ72">
         <v>1.17</v>
@@ -16355,7 +16358,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16561,7 +16564,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17260,7 +17263,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ77">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR77">
         <v>1.33</v>
@@ -17385,7 +17388,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17591,7 +17594,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17875,7 +17878,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ80">
         <v>1.17</v>
@@ -18003,7 +18006,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18209,7 +18212,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18415,7 +18418,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19239,7 +19242,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19320,7 +19323,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ87">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR87">
         <v>1.47</v>
@@ -19651,7 +19654,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19857,7 +19860,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20269,7 +20272,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20681,7 +20684,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20887,7 +20890,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21174,7 +21177,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ96">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR96">
         <v>1.53</v>
@@ -21377,7 +21380,7 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ97">
         <v>0.85</v>
@@ -21586,7 +21589,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ98">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR98">
         <v>1.35</v>
@@ -21917,7 +21920,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21995,10 +21998,10 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ100">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -22407,7 +22410,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ102">
         <v>1.38</v>
@@ -22819,7 +22822,7 @@
         <v>0.25</v>
       </c>
       <c r="AP104">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ104">
         <v>0.25</v>
@@ -23028,7 +23031,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ105">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR105">
         <v>1.64</v>
@@ -23234,7 +23237,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ106">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR106">
         <v>1.12</v>
@@ -23359,7 +23362,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23643,7 +23646,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ108">
         <v>1.38</v>
@@ -23977,7 +23980,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24389,7 +24392,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24470,7 +24473,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ112">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR112">
         <v>1.61</v>
@@ -24595,7 +24598,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25007,7 +25010,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25831,7 +25834,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26115,7 +26118,7 @@
         <v>1.4</v>
       </c>
       <c r="AP120">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ120">
         <v>1.38</v>
@@ -26449,7 +26452,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26861,7 +26864,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27273,7 +27276,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27354,7 +27357,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ126">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR126">
         <v>1.8</v>
@@ -27557,10 +27560,10 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ127">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR127">
         <v>1.1</v>
@@ -27685,7 +27688,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28097,7 +28100,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28303,7 +28306,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28509,7 +28512,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28587,10 +28590,10 @@
         <v>1.17</v>
       </c>
       <c r="AP132">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ132">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR132">
         <v>1.78</v>
@@ -28793,7 +28796,7 @@
         <v>0.2</v>
       </c>
       <c r="AP133">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ133">
         <v>0.25</v>
@@ -28921,7 +28924,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29127,7 +29130,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29411,7 +29414,7 @@
         <v>1.4</v>
       </c>
       <c r="AP136">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ136">
         <v>1.17</v>
@@ -29745,7 +29748,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30238,7 +30241,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ140">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR140">
         <v>1.34</v>
@@ -30363,7 +30366,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30569,7 +30572,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30775,7 +30778,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30981,7 +30984,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31059,7 +31062,7 @@
         <v>0.83</v>
       </c>
       <c r="AP144">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ144">
         <v>0.75</v>
@@ -31265,7 +31268,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ145">
         <v>0.54</v>
@@ -31393,7 +31396,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31474,7 +31477,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ146">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR146">
         <v>1.62</v>
@@ -31805,7 +31808,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -31883,7 +31886,7 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ148">
         <v>2.17</v>
@@ -32298,7 +32301,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ150">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR150">
         <v>1.6</v>
@@ -32835,7 +32838,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32916,7 +32919,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ153">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR153">
         <v>1.58</v>
@@ -33453,7 +33456,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33531,7 +33534,7 @@
         <v>1.83</v>
       </c>
       <c r="AP156">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ156">
         <v>1.5</v>
@@ -34973,10 +34976,10 @@
         <v>1.43</v>
       </c>
       <c r="AP163">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ163">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR163">
         <v>1.14</v>
@@ -35101,7 +35104,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35385,7 +35388,7 @@
         <v>1.14</v>
       </c>
       <c r="AP165">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ165">
         <v>1.17</v>
@@ -35594,7 +35597,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ166">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR166">
         <v>1.42</v>
@@ -35719,7 +35722,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36003,7 +36006,7 @@
         <v>3</v>
       </c>
       <c r="AP168">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ168">
         <v>2.17</v>
@@ -36131,7 +36134,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36749,7 +36752,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -36830,7 +36833,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ172">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR172">
         <v>1.15</v>
@@ -37367,7 +37370,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37779,7 +37782,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38191,7 +38194,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38397,7 +38400,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38684,7 +38687,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ181">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR181">
         <v>1.48</v>
@@ -39221,7 +39224,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39711,7 +39714,7 @@
         <v>0.13</v>
       </c>
       <c r="AP186">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ186">
         <v>0.85</v>
@@ -40045,7 +40048,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40126,7 +40129,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ188">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR188">
         <v>1.17</v>
@@ -40535,7 +40538,7 @@
         <v>2.75</v>
       </c>
       <c r="AP190">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ190">
         <v>2.17</v>
@@ -40663,7 +40666,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40869,7 +40872,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -40950,7 +40953,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ192">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR192">
         <v>1.15</v>
@@ -41075,7 +41078,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41153,7 +41156,7 @@
         <v>0.89</v>
       </c>
       <c r="AP193">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ193">
         <v>1.38</v>
@@ -41281,7 +41284,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41359,7 +41362,7 @@
         <v>1.56</v>
       </c>
       <c r="AP194">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ194">
         <v>1.62</v>
@@ -41568,7 +41571,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ195">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR195">
         <v>1.66</v>
@@ -42392,7 +42395,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ199">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR199">
         <v>1.74</v>
@@ -42517,7 +42520,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42929,7 +42932,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43135,7 +43138,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43753,7 +43756,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43831,7 +43834,7 @@
         <v>0.88</v>
       </c>
       <c r="AP206">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ206">
         <v>1.08</v>
@@ -44165,7 +44168,7 @@
         <v>94</v>
       </c>
       <c r="P208" t="s">
-        <v>341</v>
+        <v>265</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44449,7 +44452,7 @@
         <v>0.6</v>
       </c>
       <c r="AP209">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ209">
         <v>0.54</v>
@@ -44658,7 +44661,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ210">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR210">
         <v>1.59</v>
@@ -44864,7 +44867,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ211">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR211">
         <v>1.69</v>
@@ -45273,7 +45276,7 @@
         <v>1.5</v>
       </c>
       <c r="AP213">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ213">
         <v>1.62</v>
@@ -45401,7 +45404,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45685,7 +45688,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP215">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ215">
         <v>0.75</v>
@@ -45813,7 +45816,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46306,7 +46309,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ218">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR218">
         <v>1.41</v>
@@ -47539,7 +47542,7 @@
         <v>0.8</v>
       </c>
       <c r="AP224">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ224">
         <v>0.85</v>
@@ -48572,7 +48575,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ229">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR229">
         <v>1.48</v>
@@ -48984,7 +48987,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ231">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR231">
         <v>1.26</v>
@@ -49187,7 +49190,7 @@
         <v>0.8</v>
       </c>
       <c r="AP232">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ232">
         <v>0.75</v>
@@ -49393,7 +49396,7 @@
         <v>0.55</v>
       </c>
       <c r="AP233">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ233">
         <v>0.54</v>
@@ -49602,7 +49605,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ234">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR234">
         <v>1.16</v>
@@ -50014,7 +50017,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ236">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR236">
         <v>1.23</v>
@@ -50217,7 +50220,7 @@
         <v>1.22</v>
       </c>
       <c r="AP237">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ237">
         <v>1.46</v>
@@ -50838,7 +50841,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ240">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR240">
         <v>1.44</v>
@@ -51250,7 +51253,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ242">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR242">
         <v>1.37</v>
@@ -51787,7 +51790,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -51865,7 +51868,7 @@
         <v>1.3</v>
       </c>
       <c r="AP245">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ245">
         <v>1.17</v>
@@ -53722,7 +53725,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ254">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR254">
         <v>1.63</v>
@@ -54134,7 +54137,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ256">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR256">
         <v>1.43</v>
@@ -54749,7 +54752,7 @@
         <v>1.09</v>
       </c>
       <c r="AP259">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ259">
         <v>1</v>
@@ -54958,7 +54961,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ260">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR260">
         <v>1.59</v>
@@ -55083,7 +55086,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55367,7 +55370,7 @@
         <v>1.33</v>
       </c>
       <c r="AP262">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ262">
         <v>1.36</v>
@@ -55576,7 +55579,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ263">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR263">
         <v>1.43</v>
@@ -56397,7 +56400,7 @@
         <v>0.82</v>
       </c>
       <c r="AP267">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ267">
         <v>0.75</v>
@@ -58330,6 +58333,830 @@
       </c>
       <c r="BP276">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="277" spans="1:68">
+      <c r="A277" s="1">
+        <v>276</v>
+      </c>
+      <c r="B277">
+        <v>7728481</v>
+      </c>
+      <c r="C277" t="s">
+        <v>68</v>
+      </c>
+      <c r="D277" t="s">
+        <v>69</v>
+      </c>
+      <c r="E277" s="2">
+        <v>45696.41666666666</v>
+      </c>
+      <c r="F277">
+        <v>26</v>
+      </c>
+      <c r="G277" t="s">
+        <v>74</v>
+      </c>
+      <c r="H277" t="s">
+        <v>86</v>
+      </c>
+      <c r="I277">
+        <v>0</v>
+      </c>
+      <c r="J277">
+        <v>2</v>
+      </c>
+      <c r="K277">
+        <v>2</v>
+      </c>
+      <c r="L277">
+        <v>1</v>
+      </c>
+      <c r="M277">
+        <v>3</v>
+      </c>
+      <c r="N277">
+        <v>4</v>
+      </c>
+      <c r="O277" t="s">
+        <v>265</v>
+      </c>
+      <c r="P277" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q277">
+        <v>3.2</v>
+      </c>
+      <c r="R277">
+        <v>1.98</v>
+      </c>
+      <c r="S277">
+        <v>3.3</v>
+      </c>
+      <c r="T277">
+        <v>1.44</v>
+      </c>
+      <c r="U277">
+        <v>2.63</v>
+      </c>
+      <c r="V277">
+        <v>3.4</v>
+      </c>
+      <c r="W277">
+        <v>1.3</v>
+      </c>
+      <c r="X277">
+        <v>10</v>
+      </c>
+      <c r="Y277">
+        <v>1.06</v>
+      </c>
+      <c r="Z277">
+        <v>2.85</v>
+      </c>
+      <c r="AA277">
+        <v>3.39</v>
+      </c>
+      <c r="AB277">
+        <v>2.57</v>
+      </c>
+      <c r="AC277">
+        <v>1.07</v>
+      </c>
+      <c r="AD277">
+        <v>8</v>
+      </c>
+      <c r="AE277">
+        <v>1.38</v>
+      </c>
+      <c r="AF277">
+        <v>3</v>
+      </c>
+      <c r="AG277">
+        <v>1.95</v>
+      </c>
+      <c r="AH277">
+        <v>1.7</v>
+      </c>
+      <c r="AI277">
+        <v>1.83</v>
+      </c>
+      <c r="AJ277">
+        <v>1.83</v>
+      </c>
+      <c r="AK277">
+        <v>1.44</v>
+      </c>
+      <c r="AL277">
+        <v>1.33</v>
+      </c>
+      <c r="AM277">
+        <v>1.47</v>
+      </c>
+      <c r="AN277">
+        <v>0.75</v>
+      </c>
+      <c r="AO277">
+        <v>1.25</v>
+      </c>
+      <c r="AP277">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ277">
+        <v>1.38</v>
+      </c>
+      <c r="AR277">
+        <v>1.22</v>
+      </c>
+      <c r="AS277">
+        <v>1.24</v>
+      </c>
+      <c r="AT277">
+        <v>2.46</v>
+      </c>
+      <c r="AU277">
+        <v>4</v>
+      </c>
+      <c r="AV277">
+        <v>7</v>
+      </c>
+      <c r="AW277">
+        <v>10</v>
+      </c>
+      <c r="AX277">
+        <v>4</v>
+      </c>
+      <c r="AY277">
+        <v>15</v>
+      </c>
+      <c r="AZ277">
+        <v>12</v>
+      </c>
+      <c r="BA277">
+        <v>6</v>
+      </c>
+      <c r="BB277">
+        <v>3</v>
+      </c>
+      <c r="BC277">
+        <v>9</v>
+      </c>
+      <c r="BD277">
+        <v>1.82</v>
+      </c>
+      <c r="BE277">
+        <v>8</v>
+      </c>
+      <c r="BF277">
+        <v>2.39</v>
+      </c>
+      <c r="BG277">
+        <v>1.32</v>
+      </c>
+      <c r="BH277">
+        <v>3.22</v>
+      </c>
+      <c r="BI277">
+        <v>1.56</v>
+      </c>
+      <c r="BJ277">
+        <v>2.33</v>
+      </c>
+      <c r="BK277">
+        <v>1.93</v>
+      </c>
+      <c r="BL277">
+        <v>1.82</v>
+      </c>
+      <c r="BM277">
+        <v>2.47</v>
+      </c>
+      <c r="BN277">
+        <v>1.51</v>
+      </c>
+      <c r="BO277">
+        <v>3.35</v>
+      </c>
+      <c r="BP277">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:68">
+      <c r="A278" s="1">
+        <v>277</v>
+      </c>
+      <c r="B278">
+        <v>7728479</v>
+      </c>
+      <c r="C278" t="s">
+        <v>68</v>
+      </c>
+      <c r="D278" t="s">
+        <v>69</v>
+      </c>
+      <c r="E278" s="2">
+        <v>45696.51041666666</v>
+      </c>
+      <c r="F278">
+        <v>26</v>
+      </c>
+      <c r="G278" t="s">
+        <v>70</v>
+      </c>
+      <c r="H278" t="s">
+        <v>71</v>
+      </c>
+      <c r="I278">
+        <v>0</v>
+      </c>
+      <c r="J278">
+        <v>0</v>
+      </c>
+      <c r="K278">
+        <v>0</v>
+      </c>
+      <c r="L278">
+        <v>0</v>
+      </c>
+      <c r="M278">
+        <v>0</v>
+      </c>
+      <c r="N278">
+        <v>0</v>
+      </c>
+      <c r="O278" t="s">
+        <v>94</v>
+      </c>
+      <c r="P278" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q278">
+        <v>2.3</v>
+      </c>
+      <c r="R278">
+        <v>2</v>
+      </c>
+      <c r="S278">
+        <v>5.25</v>
+      </c>
+      <c r="T278">
+        <v>1.48</v>
+      </c>
+      <c r="U278">
+        <v>2.45</v>
+      </c>
+      <c r="V278">
+        <v>3.25</v>
+      </c>
+      <c r="W278">
+        <v>1.3</v>
+      </c>
+      <c r="X278">
+        <v>9.4</v>
+      </c>
+      <c r="Y278">
+        <v>1.02</v>
+      </c>
+      <c r="Z278">
+        <v>1.8</v>
+      </c>
+      <c r="AA278">
+        <v>3.53</v>
+      </c>
+      <c r="AB278">
+        <v>5.1</v>
+      </c>
+      <c r="AC278">
+        <v>1.08</v>
+      </c>
+      <c r="AD278">
+        <v>7.5</v>
+      </c>
+      <c r="AE278">
+        <v>1.45</v>
+      </c>
+      <c r="AF278">
+        <v>2.7</v>
+      </c>
+      <c r="AG278">
+        <v>2.15</v>
+      </c>
+      <c r="AH278">
+        <v>1.57</v>
+      </c>
+      <c r="AI278">
+        <v>2.15</v>
+      </c>
+      <c r="AJ278">
+        <v>1.6</v>
+      </c>
+      <c r="AK278">
+        <v>1.15</v>
+      </c>
+      <c r="AL278">
+        <v>1.25</v>
+      </c>
+      <c r="AM278">
+        <v>2.1</v>
+      </c>
+      <c r="AN278">
+        <v>1.69</v>
+      </c>
+      <c r="AO278">
+        <v>1.17</v>
+      </c>
+      <c r="AP278">
+        <v>1.64</v>
+      </c>
+      <c r="AQ278">
+        <v>1.15</v>
+      </c>
+      <c r="AR278">
+        <v>1.69</v>
+      </c>
+      <c r="AS278">
+        <v>1.13</v>
+      </c>
+      <c r="AT278">
+        <v>2.82</v>
+      </c>
+      <c r="AU278">
+        <v>5</v>
+      </c>
+      <c r="AV278">
+        <v>7</v>
+      </c>
+      <c r="AW278">
+        <v>10</v>
+      </c>
+      <c r="AX278">
+        <v>6</v>
+      </c>
+      <c r="AY278">
+        <v>22</v>
+      </c>
+      <c r="AZ278">
+        <v>13</v>
+      </c>
+      <c r="BA278">
+        <v>6</v>
+      </c>
+      <c r="BB278">
+        <v>4</v>
+      </c>
+      <c r="BC278">
+        <v>10</v>
+      </c>
+      <c r="BD278">
+        <v>1.49</v>
+      </c>
+      <c r="BE278">
+        <v>6.75</v>
+      </c>
+      <c r="BF278">
+        <v>2.9</v>
+      </c>
+      <c r="BG278">
+        <v>1.4</v>
+      </c>
+      <c r="BH278">
+        <v>2.65</v>
+      </c>
+      <c r="BI278">
+        <v>1.68</v>
+      </c>
+      <c r="BJ278">
+        <v>2</v>
+      </c>
+      <c r="BK278">
+        <v>2.12</v>
+      </c>
+      <c r="BL278">
+        <v>1.62</v>
+      </c>
+      <c r="BM278">
+        <v>2.7</v>
+      </c>
+      <c r="BN278">
+        <v>1.38</v>
+      </c>
+      <c r="BO278">
+        <v>3.55</v>
+      </c>
+      <c r="BP278">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="279" spans="1:68">
+      <c r="A279" s="1">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>7728484</v>
+      </c>
+      <c r="C279" t="s">
+        <v>68</v>
+      </c>
+      <c r="D279" t="s">
+        <v>69</v>
+      </c>
+      <c r="E279" s="2">
+        <v>45696.60416666666</v>
+      </c>
+      <c r="F279">
+        <v>26</v>
+      </c>
+      <c r="G279" t="s">
+        <v>83</v>
+      </c>
+      <c r="H279" t="s">
+        <v>82</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>1</v>
+      </c>
+      <c r="K279">
+        <v>1</v>
+      </c>
+      <c r="L279">
+        <v>1</v>
+      </c>
+      <c r="M279">
+        <v>1</v>
+      </c>
+      <c r="N279">
+        <v>2</v>
+      </c>
+      <c r="O279" t="s">
+        <v>265</v>
+      </c>
+      <c r="P279" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q279">
+        <v>3.6</v>
+      </c>
+      <c r="R279">
+        <v>2</v>
+      </c>
+      <c r="S279">
+        <v>3.25</v>
+      </c>
+      <c r="T279">
+        <v>1.5</v>
+      </c>
+      <c r="U279">
+        <v>2.5</v>
+      </c>
+      <c r="V279">
+        <v>3.5</v>
+      </c>
+      <c r="W279">
+        <v>1.29</v>
+      </c>
+      <c r="X279">
+        <v>11</v>
+      </c>
+      <c r="Y279">
+        <v>1.05</v>
+      </c>
+      <c r="Z279">
+        <v>2.77</v>
+      </c>
+      <c r="AA279">
+        <v>3.4</v>
+      </c>
+      <c r="AB279">
+        <v>2.63</v>
+      </c>
+      <c r="AC279">
+        <v>1.08</v>
+      </c>
+      <c r="AD279">
+        <v>7.5</v>
+      </c>
+      <c r="AE279">
+        <v>1.42</v>
+      </c>
+      <c r="AF279">
+        <v>2.8</v>
+      </c>
+      <c r="AG279">
+        <v>2.1</v>
+      </c>
+      <c r="AH279">
+        <v>1.6</v>
+      </c>
+      <c r="AI279">
+        <v>2</v>
+      </c>
+      <c r="AJ279">
+        <v>1.73</v>
+      </c>
+      <c r="AK279">
+        <v>1.47</v>
+      </c>
+      <c r="AL279">
+        <v>1.34</v>
+      </c>
+      <c r="AM279">
+        <v>1.42</v>
+      </c>
+      <c r="AN279">
+        <v>1.67</v>
+      </c>
+      <c r="AO279">
+        <v>1.46</v>
+      </c>
+      <c r="AP279">
+        <v>1.62</v>
+      </c>
+      <c r="AQ279">
+        <v>1.43</v>
+      </c>
+      <c r="AR279">
+        <v>1.34</v>
+      </c>
+      <c r="AS279">
+        <v>1.23</v>
+      </c>
+      <c r="AT279">
+        <v>2.57</v>
+      </c>
+      <c r="AU279">
+        <v>4</v>
+      </c>
+      <c r="AV279">
+        <v>5</v>
+      </c>
+      <c r="AW279">
+        <v>10</v>
+      </c>
+      <c r="AX279">
+        <v>7</v>
+      </c>
+      <c r="AY279">
+        <v>17</v>
+      </c>
+      <c r="AZ279">
+        <v>15</v>
+      </c>
+      <c r="BA279">
+        <v>8</v>
+      </c>
+      <c r="BB279">
+        <v>5</v>
+      </c>
+      <c r="BC279">
+        <v>13</v>
+      </c>
+      <c r="BD279">
+        <v>2.1</v>
+      </c>
+      <c r="BE279">
+        <v>7.5</v>
+      </c>
+      <c r="BF279">
+        <v>2</v>
+      </c>
+      <c r="BG279">
+        <v>1.4</v>
+      </c>
+      <c r="BH279">
+        <v>2.82</v>
+      </c>
+      <c r="BI279">
+        <v>1.68</v>
+      </c>
+      <c r="BJ279">
+        <v>2.12</v>
+      </c>
+      <c r="BK279">
+        <v>2.11</v>
+      </c>
+      <c r="BL279">
+        <v>1.68</v>
+      </c>
+      <c r="BM279">
+        <v>2.75</v>
+      </c>
+      <c r="BN279">
+        <v>1.42</v>
+      </c>
+      <c r="BO279">
+        <v>3.8</v>
+      </c>
+      <c r="BP279">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="280" spans="1:68">
+      <c r="A280" s="1">
+        <v>279</v>
+      </c>
+      <c r="B280">
+        <v>7728482</v>
+      </c>
+      <c r="C280" t="s">
+        <v>68</v>
+      </c>
+      <c r="D280" t="s">
+        <v>69</v>
+      </c>
+      <c r="E280" s="2">
+        <v>45696.60416666666</v>
+      </c>
+      <c r="F280">
+        <v>26</v>
+      </c>
+      <c r="G280" t="s">
+        <v>76</v>
+      </c>
+      <c r="H280" t="s">
+        <v>73</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280">
+        <v>0</v>
+      </c>
+      <c r="L280">
+        <v>0</v>
+      </c>
+      <c r="M280">
+        <v>0</v>
+      </c>
+      <c r="N280">
+        <v>0</v>
+      </c>
+      <c r="O280" t="s">
+        <v>94</v>
+      </c>
+      <c r="P280" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q280">
+        <v>2.75</v>
+      </c>
+      <c r="R280">
+        <v>2</v>
+      </c>
+      <c r="S280">
+        <v>4.75</v>
+      </c>
+      <c r="T280">
+        <v>1.5</v>
+      </c>
+      <c r="U280">
+        <v>2.5</v>
+      </c>
+      <c r="V280">
+        <v>3.5</v>
+      </c>
+      <c r="W280">
+        <v>1.29</v>
+      </c>
+      <c r="X280">
+        <v>11</v>
+      </c>
+      <c r="Y280">
+        <v>1.05</v>
+      </c>
+      <c r="Z280">
+        <v>2.09</v>
+      </c>
+      <c r="AA280">
+        <v>3.39</v>
+      </c>
+      <c r="AB280">
+        <v>3.83</v>
+      </c>
+      <c r="AC280">
+        <v>1.09</v>
+      </c>
+      <c r="AD280">
+        <v>7</v>
+      </c>
+      <c r="AE280">
+        <v>1.44</v>
+      </c>
+      <c r="AF280">
+        <v>2.7</v>
+      </c>
+      <c r="AG280">
+        <v>2.15</v>
+      </c>
+      <c r="AH280">
+        <v>1.57</v>
+      </c>
+      <c r="AI280">
+        <v>2.1</v>
+      </c>
+      <c r="AJ280">
+        <v>1.67</v>
+      </c>
+      <c r="AK280">
+        <v>1.26</v>
+      </c>
+      <c r="AL280">
+        <v>1.32</v>
+      </c>
+      <c r="AM280">
+        <v>1.75</v>
+      </c>
+      <c r="AN280">
+        <v>1.77</v>
+      </c>
+      <c r="AO280">
+        <v>0.67</v>
+      </c>
+      <c r="AP280">
+        <v>1.71</v>
+      </c>
+      <c r="AQ280">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR280">
+        <v>1.52</v>
+      </c>
+      <c r="AS280">
+        <v>1.2</v>
+      </c>
+      <c r="AT280">
+        <v>2.72</v>
+      </c>
+      <c r="AU280">
+        <v>3</v>
+      </c>
+      <c r="AV280">
+        <v>3</v>
+      </c>
+      <c r="AW280">
+        <v>8</v>
+      </c>
+      <c r="AX280">
+        <v>10</v>
+      </c>
+      <c r="AY280">
+        <v>12</v>
+      </c>
+      <c r="AZ280">
+        <v>16</v>
+      </c>
+      <c r="BA280">
+        <v>7</v>
+      </c>
+      <c r="BB280">
+        <v>2</v>
+      </c>
+      <c r="BC280">
+        <v>9</v>
+      </c>
+      <c r="BD280">
+        <v>1.64</v>
+      </c>
+      <c r="BE280">
+        <v>8</v>
+      </c>
+      <c r="BF280">
+        <v>2.77</v>
+      </c>
+      <c r="BG280">
+        <v>1.36</v>
+      </c>
+      <c r="BH280">
+        <v>2.98</v>
+      </c>
+      <c r="BI280">
+        <v>1.62</v>
+      </c>
+      <c r="BJ280">
+        <v>2.22</v>
+      </c>
+      <c r="BK280">
+        <v>2.02</v>
+      </c>
+      <c r="BL280">
+        <v>1.74</v>
+      </c>
+      <c r="BM280">
+        <v>2.6</v>
+      </c>
+      <c r="BN280">
+        <v>1.46</v>
+      </c>
+      <c r="BO280">
+        <v>3.58</v>
+      </c>
+      <c r="BP280">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="372">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -814,6 +814,15 @@
     <t>['68']</t>
   </si>
   <si>
+    <t>['14', '90+3']</t>
+  </si>
+  <si>
+    <t>['12', '29', '37', '78', '90+5']</t>
+  </si>
+  <si>
+    <t>['19', '26', '31']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1115,6 +1124,12 @@
   </si>
   <si>
     <t>['4', '14', '78']</t>
+  </si>
+  <si>
+    <t>['49', '67']</t>
+  </si>
+  <si>
+    <t>['44', '60']</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP280"/>
+  <dimension ref="A1:BP285"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1732,7 +1747,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2144,7 +2159,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2222,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ4">
         <v>1.36</v>
@@ -2840,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ7">
         <v>1.38</v>
@@ -2968,7 +2983,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3174,7 +3189,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3255,7 +3270,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ9">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3458,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ10">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3664,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ11">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3873,7 +3888,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ12">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3998,7 +4013,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4204,7 +4219,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -5234,7 +5249,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5315,7 +5330,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ19">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5852,7 +5867,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6058,7 +6073,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6136,7 +6151,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ23">
         <v>0.75</v>
@@ -6264,7 +6279,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6345,7 +6360,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ24">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
         <v>2.51</v>
@@ -6470,7 +6485,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6551,7 +6566,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ25">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6676,7 +6691,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6754,10 +6769,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ26">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR26">
         <v>1.33</v>
@@ -6882,7 +6897,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7294,7 +7309,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7372,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ29">
         <v>1.38</v>
@@ -7578,7 +7593,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ30">
         <v>1.08</v>
@@ -7912,7 +7927,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7993,7 +8008,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ32">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR32">
         <v>1.31</v>
@@ -8118,7 +8133,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8402,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ34">
         <v>0.85</v>
@@ -8530,7 +8545,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8611,7 +8626,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ35">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR35">
         <v>1.42</v>
@@ -9432,7 +9447,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ39">
         <v>0.85</v>
@@ -10053,7 +10068,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ42">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR42">
         <v>1.8</v>
@@ -10384,7 +10399,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10874,7 +10889,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ46">
         <v>1.46</v>
@@ -11002,7 +11017,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11289,7 +11304,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ48">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR48">
         <v>1.67</v>
@@ -11495,7 +11510,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ49">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR49">
         <v>1.38</v>
@@ -12113,7 +12128,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ52">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR52">
         <v>1.28</v>
@@ -12316,7 +12331,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ53">
         <v>1.36</v>
@@ -12522,7 +12537,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ54">
         <v>1.08</v>
@@ -12650,7 +12665,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12728,7 +12743,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ55">
         <v>1.5</v>
@@ -12856,7 +12871,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13062,7 +13077,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13268,7 +13283,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13680,7 +13695,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13758,7 +13773,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ60">
         <v>0.75</v>
@@ -14298,7 +14313,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14585,7 +14600,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ64">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR64">
         <v>1.39</v>
@@ -14788,7 +14803,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ65">
         <v>1.15</v>
@@ -14916,7 +14931,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15328,7 +15343,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15534,7 +15549,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15612,7 +15627,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ69">
         <v>0.75</v>
@@ -15821,7 +15836,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ70">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR70">
         <v>1.04</v>
@@ -16152,7 +16167,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16358,7 +16373,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16439,7 +16454,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ73">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR73">
         <v>2.06</v>
@@ -16564,7 +16579,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16642,7 +16657,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ74">
         <v>1.5</v>
@@ -16851,7 +16866,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ75">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR75">
         <v>1.58</v>
@@ -17054,7 +17069,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ76">
         <v>1.08</v>
@@ -17388,7 +17403,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17469,7 +17484,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ78">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR78">
         <v>1.42</v>
@@ -17594,7 +17609,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18006,7 +18021,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18212,7 +18227,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18418,7 +18433,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18499,7 +18514,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ83">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR83">
         <v>1.8</v>
@@ -18911,7 +18926,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ85">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -19114,7 +19129,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ86">
         <v>0.85</v>
@@ -19242,7 +19257,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19654,7 +19669,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19860,7 +19875,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20272,7 +20287,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20350,7 +20365,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ92">
         <v>0.85</v>
@@ -20684,7 +20699,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20890,7 +20905,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -20971,7 +20986,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ95">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR95">
         <v>1.44</v>
@@ -21586,7 +21601,7 @@
         <v>0.67</v>
       </c>
       <c r="AP98">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ98">
         <v>1.15</v>
@@ -21792,7 +21807,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ99">
         <v>1.46</v>
@@ -21920,7 +21935,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22204,10 +22219,10 @@
         <v>1.2</v>
       </c>
       <c r="AP101">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ101">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR101">
         <v>1.58</v>
@@ -22616,7 +22631,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ103">
         <v>0.75</v>
@@ -22825,7 +22840,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR104">
         <v>1.71</v>
@@ -23362,7 +23377,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23440,10 +23455,10 @@
         <v>3</v>
       </c>
       <c r="AP107">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ107">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR107">
         <v>1.53</v>
@@ -23649,7 +23664,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ108">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR108">
         <v>1.17</v>
@@ -23852,7 +23867,7 @@
         <v>1.25</v>
       </c>
       <c r="AP109">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23980,7 +23995,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24061,7 +24076,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ110">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR110">
         <v>1.96</v>
@@ -24392,7 +24407,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24598,7 +24613,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25010,7 +25025,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25834,7 +25849,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26121,7 +26136,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ120">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR120">
         <v>1.6</v>
@@ -26452,7 +26467,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26530,7 +26545,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ122">
         <v>1.08</v>
@@ -26736,7 +26751,7 @@
         <v>1.17</v>
       </c>
       <c r="AP123">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ123">
         <v>1.38</v>
@@ -26864,7 +26879,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -26945,7 +26960,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ124">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR124">
         <v>1.12</v>
@@ -27148,7 +27163,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ125">
         <v>0.75</v>
@@ -27276,7 +27291,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27688,7 +27703,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27766,10 +27781,10 @@
         <v>3</v>
       </c>
       <c r="AP128">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ128">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR128">
         <v>1.61</v>
@@ -27972,7 +27987,7 @@
         <v>1.4</v>
       </c>
       <c r="AP129">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ129">
         <v>0.75</v>
@@ -28100,7 +28115,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28306,7 +28321,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28387,7 +28402,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ131">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR131">
         <v>1.16</v>
@@ -28512,7 +28527,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28799,7 +28814,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ133">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR133">
         <v>1.15</v>
@@ -28924,7 +28939,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29130,7 +29145,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29748,7 +29763,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30366,7 +30381,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30444,10 +30459,10 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ141">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR141">
         <v>1.42</v>
@@ -30572,7 +30587,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30778,7 +30793,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30984,7 +30999,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31271,7 +31286,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ145">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR145">
         <v>1.15</v>
@@ -31396,7 +31411,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31474,7 +31489,7 @@
         <v>2</v>
       </c>
       <c r="AP146">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ146">
         <v>1.38</v>
@@ -31680,7 +31695,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ147">
         <v>1</v>
@@ -31808,7 +31823,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -31889,7 +31904,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ148">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR148">
         <v>1.13</v>
@@ -32298,7 +32313,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ150">
         <v>0.6899999999999999</v>
@@ -32838,7 +32853,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33456,7 +33471,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33740,7 +33755,7 @@
         <v>0.17</v>
       </c>
       <c r="AP157">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ157">
         <v>0.85</v>
@@ -33949,7 +33964,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ158">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR158">
         <v>1.68</v>
@@ -34361,7 +34376,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ160">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34773,7 +34788,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ162">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR162">
         <v>1.47</v>
@@ -35104,7 +35119,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35185,7 +35200,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ164">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR164">
         <v>1.2</v>
@@ -35594,7 +35609,7 @@
         <v>0.71</v>
       </c>
       <c r="AP166">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ166">
         <v>0.6899999999999999</v>
@@ -35722,7 +35737,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35800,7 +35815,7 @@
         <v>1.75</v>
       </c>
       <c r="AP167">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ167">
         <v>1.36</v>
@@ -36009,7 +36024,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ168">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR168">
         <v>1.29</v>
@@ -36134,7 +36149,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36215,7 +36230,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ169">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR169">
         <v>1.71</v>
@@ -36418,7 +36433,7 @@
         <v>1.29</v>
       </c>
       <c r="AP170">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36752,7 +36767,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37036,7 +37051,7 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ173">
         <v>1.38</v>
@@ -37370,7 +37385,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37782,7 +37797,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -37863,7 +37878,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ177">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR177">
         <v>1.68</v>
@@ -38194,7 +38209,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38400,7 +38415,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38478,7 +38493,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ180">
         <v>1.46</v>
@@ -39224,7 +39239,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39923,7 +39938,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ187">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR187">
         <v>1.45</v>
@@ -40048,7 +40063,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40332,7 +40347,7 @@
         <v>1.13</v>
       </c>
       <c r="AP189">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ189">
         <v>1.17</v>
@@ -40541,7 +40556,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ190">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR190">
         <v>1.74</v>
@@ -40666,7 +40681,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40744,7 +40759,7 @@
         <v>1.67</v>
       </c>
       <c r="AP191">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ191">
         <v>1.36</v>
@@ -40872,7 +40887,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41078,7 +41093,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41284,7 +41299,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41365,7 +41380,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ194">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR194">
         <v>1.4</v>
@@ -41774,7 +41789,7 @@
         <v>0.63</v>
       </c>
       <c r="AP196">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ196">
         <v>0.75</v>
@@ -41980,10 +41995,10 @@
         <v>0.25</v>
       </c>
       <c r="AP197">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ197">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR197">
         <v>1.63</v>
@@ -42520,7 +42535,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42804,7 +42819,7 @@
         <v>1.22</v>
       </c>
       <c r="AP201">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ201">
         <v>1</v>
@@ -42932,7 +42947,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43013,7 +43028,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ202">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR202">
         <v>1.63</v>
@@ -43138,7 +43153,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43756,7 +43771,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44040,7 +44055,7 @@
         <v>0.78</v>
       </c>
       <c r="AP207">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ207">
         <v>0.85</v>
@@ -44249,7 +44264,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ208">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR208">
         <v>1.46</v>
@@ -44455,7 +44470,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ209">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR209">
         <v>1.74</v>
@@ -44786,7 +44801,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44864,7 +44879,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP211">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ211">
         <v>0.6899999999999999</v>
@@ -44992,7 +45007,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45198,7 +45213,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45279,7 +45294,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ213">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR213">
         <v>1.08</v>
@@ -45404,7 +45419,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45816,7 +45831,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -45894,7 +45909,7 @@
         <v>0.78</v>
       </c>
       <c r="AP216">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ216">
         <v>0.75</v>
@@ -46100,10 +46115,10 @@
         <v>2.44</v>
       </c>
       <c r="AP217">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ217">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR217">
         <v>1.61</v>
@@ -46306,7 +46321,7 @@
         <v>1.67</v>
       </c>
       <c r="AP218">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ218">
         <v>1.38</v>
@@ -46515,7 +46530,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ219">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR219">
         <v>1.15</v>
@@ -47052,7 +47067,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47464,7 +47479,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47748,10 +47763,10 @@
         <v>0.2</v>
       </c>
       <c r="AP225">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ225">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR225">
         <v>1.43</v>
@@ -47876,7 +47891,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48082,7 +48097,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48494,7 +48509,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48572,7 +48587,7 @@
         <v>1.22</v>
       </c>
       <c r="AP229">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ229">
         <v>1.15</v>
@@ -48700,7 +48715,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48781,7 +48796,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ230">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR230">
         <v>1.54</v>
@@ -48906,7 +48921,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49399,7 +49414,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ233">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR233">
         <v>1.18</v>
@@ -49730,7 +49745,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -49811,7 +49826,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ235">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR235">
         <v>1.56</v>
@@ -50554,7 +50569,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50632,10 +50647,10 @@
         <v>1.64</v>
       </c>
       <c r="AP239">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ239">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR239">
         <v>1.67</v>
@@ -50838,7 +50853,7 @@
         <v>1.36</v>
       </c>
       <c r="AP240">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ240">
         <v>1.43</v>
@@ -51044,7 +51059,7 @@
         <v>1.45</v>
       </c>
       <c r="AP241">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ241">
         <v>1.36</v>
@@ -51172,7 +51187,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51584,7 +51599,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51790,7 +51805,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -52486,7 +52501,7 @@
         <v>1.2</v>
       </c>
       <c r="AP248">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ248">
         <v>1.46</v>
@@ -52820,7 +52835,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53026,7 +53041,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53107,7 +53122,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ251">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR251">
         <v>1.68</v>
@@ -53313,7 +53328,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ252">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR252">
         <v>1.71</v>
@@ -53438,7 +53453,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53722,7 +53737,7 @@
         <v>0.73</v>
       </c>
       <c r="AP254">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ254">
         <v>0.6899999999999999</v>
@@ -53850,7 +53865,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -53928,10 +53943,10 @@
         <v>2.09</v>
       </c>
       <c r="AP255">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ255">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR255">
         <v>1.61</v>
@@ -54056,7 +54071,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54134,7 +54149,7 @@
         <v>1.33</v>
       </c>
       <c r="AP256">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ256">
         <v>1.43</v>
@@ -54343,7 +54358,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ257">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR257">
         <v>1.24</v>
@@ -54468,7 +54483,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -55086,7 +55101,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55167,7 +55182,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ261">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR261">
         <v>1.52</v>
@@ -55292,7 +55307,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55576,7 +55591,7 @@
         <v>1.27</v>
       </c>
       <c r="AP263">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ263">
         <v>1.15</v>
@@ -55910,7 +55925,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56734,7 +56749,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57021,7 +57036,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ270">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR270">
         <v>1.69</v>
@@ -57558,7 +57573,7 @@
         <v>94</v>
       </c>
       <c r="P273" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q273">
         <v>4</v>
@@ -58382,7 +58397,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59157,6 +59172,1036 @@
       </c>
       <c r="BP280">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="281" spans="1:68">
+      <c r="A281" s="1">
+        <v>280</v>
+      </c>
+      <c r="B281">
+        <v>7728478</v>
+      </c>
+      <c r="C281" t="s">
+        <v>68</v>
+      </c>
+      <c r="D281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E281" s="2">
+        <v>45697.41666666666</v>
+      </c>
+      <c r="F281">
+        <v>26</v>
+      </c>
+      <c r="G281" t="s">
+        <v>79</v>
+      </c>
+      <c r="H281" t="s">
+        <v>84</v>
+      </c>
+      <c r="I281">
+        <v>1</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281">
+        <v>1</v>
+      </c>
+      <c r="L281">
+        <v>2</v>
+      </c>
+      <c r="M281">
+        <v>0</v>
+      </c>
+      <c r="N281">
+        <v>2</v>
+      </c>
+      <c r="O281" t="s">
+        <v>266</v>
+      </c>
+      <c r="P281" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q281">
+        <v>2.4</v>
+      </c>
+      <c r="R281">
+        <v>1.95</v>
+      </c>
+      <c r="S281">
+        <v>6.5</v>
+      </c>
+      <c r="T281">
+        <v>1.57</v>
+      </c>
+      <c r="U281">
+        <v>2.25</v>
+      </c>
+      <c r="V281">
+        <v>3.75</v>
+      </c>
+      <c r="W281">
+        <v>1.25</v>
+      </c>
+      <c r="X281">
+        <v>11</v>
+      </c>
+      <c r="Y281">
+        <v>1.05</v>
+      </c>
+      <c r="Z281">
+        <v>1.73</v>
+      </c>
+      <c r="AA281">
+        <v>3.57</v>
+      </c>
+      <c r="AB281">
+        <v>5.7</v>
+      </c>
+      <c r="AC281">
+        <v>1.08</v>
+      </c>
+      <c r="AD281">
+        <v>7.5</v>
+      </c>
+      <c r="AE281">
+        <v>1.48</v>
+      </c>
+      <c r="AF281">
+        <v>2.62</v>
+      </c>
+      <c r="AG281">
+        <v>2.37</v>
+      </c>
+      <c r="AH281">
+        <v>1.48</v>
+      </c>
+      <c r="AI281">
+        <v>2.5</v>
+      </c>
+      <c r="AJ281">
+        <v>1.5</v>
+      </c>
+      <c r="AK281">
+        <v>1.15</v>
+      </c>
+      <c r="AL281">
+        <v>1.22</v>
+      </c>
+      <c r="AM281">
+        <v>2.1</v>
+      </c>
+      <c r="AN281">
+        <v>2.23</v>
+      </c>
+      <c r="AO281">
+        <v>0.25</v>
+      </c>
+      <c r="AP281">
+        <v>2.29</v>
+      </c>
+      <c r="AQ281">
+        <v>0.23</v>
+      </c>
+      <c r="AR281">
+        <v>1.65</v>
+      </c>
+      <c r="AS281">
+        <v>1.05</v>
+      </c>
+      <c r="AT281">
+        <v>2.7</v>
+      </c>
+      <c r="AU281">
+        <v>4</v>
+      </c>
+      <c r="AV281">
+        <v>5</v>
+      </c>
+      <c r="AW281">
+        <v>5</v>
+      </c>
+      <c r="AX281">
+        <v>11</v>
+      </c>
+      <c r="AY281">
+        <v>9</v>
+      </c>
+      <c r="AZ281">
+        <v>16</v>
+      </c>
+      <c r="BA281">
+        <v>3</v>
+      </c>
+      <c r="BB281">
+        <v>6</v>
+      </c>
+      <c r="BC281">
+        <v>9</v>
+      </c>
+      <c r="BD281">
+        <v>1.33</v>
+      </c>
+      <c r="BE281">
+        <v>7</v>
+      </c>
+      <c r="BF281">
+        <v>3.65</v>
+      </c>
+      <c r="BG281">
+        <v>1.36</v>
+      </c>
+      <c r="BH281">
+        <v>2.8</v>
+      </c>
+      <c r="BI281">
+        <v>1.62</v>
+      </c>
+      <c r="BJ281">
+        <v>2.1</v>
+      </c>
+      <c r="BK281">
+        <v>2</v>
+      </c>
+      <c r="BL281">
+        <v>1.68</v>
+      </c>
+      <c r="BM281">
+        <v>2.55</v>
+      </c>
+      <c r="BN281">
+        <v>1.43</v>
+      </c>
+      <c r="BO281">
+        <v>3.3</v>
+      </c>
+      <c r="BP281">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="282" spans="1:68">
+      <c r="A282" s="1">
+        <v>281</v>
+      </c>
+      <c r="B282">
+        <v>7728477</v>
+      </c>
+      <c r="C282" t="s">
+        <v>68</v>
+      </c>
+      <c r="D282" t="s">
+        <v>69</v>
+      </c>
+      <c r="E282" s="2">
+        <v>45697.51041666666</v>
+      </c>
+      <c r="F282">
+        <v>26</v>
+      </c>
+      <c r="G282" t="s">
+        <v>88</v>
+      </c>
+      <c r="H282" t="s">
+        <v>81</v>
+      </c>
+      <c r="I282">
+        <v>1</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>1</v>
+      </c>
+      <c r="L282">
+        <v>1</v>
+      </c>
+      <c r="M282">
+        <v>2</v>
+      </c>
+      <c r="N282">
+        <v>3</v>
+      </c>
+      <c r="O282" t="s">
+        <v>186</v>
+      </c>
+      <c r="P282" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q282">
+        <v>2.75</v>
+      </c>
+      <c r="R282">
+        <v>2</v>
+      </c>
+      <c r="S282">
+        <v>4.75</v>
+      </c>
+      <c r="T282">
+        <v>1.53</v>
+      </c>
+      <c r="U282">
+        <v>2.38</v>
+      </c>
+      <c r="V282">
+        <v>3.5</v>
+      </c>
+      <c r="W282">
+        <v>1.29</v>
+      </c>
+      <c r="X282">
+        <v>11</v>
+      </c>
+      <c r="Y282">
+        <v>1.05</v>
+      </c>
+      <c r="Z282">
+        <v>2.03</v>
+      </c>
+      <c r="AA282">
+        <v>3.15</v>
+      </c>
+      <c r="AB282">
+        <v>4.4</v>
+      </c>
+      <c r="AC282">
+        <v>1.1</v>
+      </c>
+      <c r="AD282">
+        <v>6.5</v>
+      </c>
+      <c r="AE282">
+        <v>1.48</v>
+      </c>
+      <c r="AF282">
+        <v>2.6</v>
+      </c>
+      <c r="AG282">
+        <v>2.3</v>
+      </c>
+      <c r="AH282">
+        <v>1.5</v>
+      </c>
+      <c r="AI282">
+        <v>2.1</v>
+      </c>
+      <c r="AJ282">
+        <v>1.67</v>
+      </c>
+      <c r="AK282">
+        <v>1.25</v>
+      </c>
+      <c r="AL282">
+        <v>1.3</v>
+      </c>
+      <c r="AM282">
+        <v>1.73</v>
+      </c>
+      <c r="AN282">
+        <v>1.83</v>
+      </c>
+      <c r="AO282">
+        <v>1.38</v>
+      </c>
+      <c r="AP282">
+        <v>1.69</v>
+      </c>
+      <c r="AQ282">
+        <v>1.5</v>
+      </c>
+      <c r="AR282">
+        <v>1.67</v>
+      </c>
+      <c r="AS282">
+        <v>1.06</v>
+      </c>
+      <c r="AT282">
+        <v>2.73</v>
+      </c>
+      <c r="AU282">
+        <v>5</v>
+      </c>
+      <c r="AV282">
+        <v>3</v>
+      </c>
+      <c r="AW282">
+        <v>4</v>
+      </c>
+      <c r="AX282">
+        <v>4</v>
+      </c>
+      <c r="AY282">
+        <v>11</v>
+      </c>
+      <c r="AZ282">
+        <v>9</v>
+      </c>
+      <c r="BA282">
+        <v>4</v>
+      </c>
+      <c r="BB282">
+        <v>6</v>
+      </c>
+      <c r="BC282">
+        <v>10</v>
+      </c>
+      <c r="BD282">
+        <v>1.41</v>
+      </c>
+      <c r="BE282">
+        <v>7</v>
+      </c>
+      <c r="BF282">
+        <v>3.2</v>
+      </c>
+      <c r="BG282">
+        <v>1.34</v>
+      </c>
+      <c r="BH282">
+        <v>2.88</v>
+      </c>
+      <c r="BI282">
+        <v>1.58</v>
+      </c>
+      <c r="BJ282">
+        <v>2.16</v>
+      </c>
+      <c r="BK282">
+        <v>1.96</v>
+      </c>
+      <c r="BL282">
+        <v>1.72</v>
+      </c>
+      <c r="BM282">
+        <v>2.5</v>
+      </c>
+      <c r="BN282">
+        <v>1.44</v>
+      </c>
+      <c r="BO282">
+        <v>3.3</v>
+      </c>
+      <c r="BP282">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="283" spans="1:68">
+      <c r="A283" s="1">
+        <v>282</v>
+      </c>
+      <c r="B283">
+        <v>7728475</v>
+      </c>
+      <c r="C283" t="s">
+        <v>68</v>
+      </c>
+      <c r="D283" t="s">
+        <v>69</v>
+      </c>
+      <c r="E283" s="2">
+        <v>45697.51041666666</v>
+      </c>
+      <c r="F283">
+        <v>26</v>
+      </c>
+      <c r="G283" t="s">
+        <v>78</v>
+      </c>
+      <c r="H283" t="s">
+        <v>77</v>
+      </c>
+      <c r="I283">
+        <v>0</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>0</v>
+      </c>
+      <c r="L283">
+        <v>2</v>
+      </c>
+      <c r="M283">
+        <v>1</v>
+      </c>
+      <c r="N283">
+        <v>3</v>
+      </c>
+      <c r="O283" t="s">
+        <v>141</v>
+      </c>
+      <c r="P283" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q283">
+        <v>3.2</v>
+      </c>
+      <c r="R283">
+        <v>2.1</v>
+      </c>
+      <c r="S283">
+        <v>3.5</v>
+      </c>
+      <c r="T283">
+        <v>1.44</v>
+      </c>
+      <c r="U283">
+        <v>2.63</v>
+      </c>
+      <c r="V283">
+        <v>3</v>
+      </c>
+      <c r="W283">
+        <v>1.36</v>
+      </c>
+      <c r="X283">
+        <v>9</v>
+      </c>
+      <c r="Y283">
+        <v>1.07</v>
+      </c>
+      <c r="Z283">
+        <v>2.57</v>
+      </c>
+      <c r="AA283">
+        <v>3.19</v>
+      </c>
+      <c r="AB283">
+        <v>3.01</v>
+      </c>
+      <c r="AC283">
+        <v>1.07</v>
+      </c>
+      <c r="AD283">
+        <v>8</v>
+      </c>
+      <c r="AE283">
+        <v>1.33</v>
+      </c>
+      <c r="AF283">
+        <v>3.2</v>
+      </c>
+      <c r="AG283">
+        <v>2.01</v>
+      </c>
+      <c r="AH283">
+        <v>1.81</v>
+      </c>
+      <c r="AI283">
+        <v>1.73</v>
+      </c>
+      <c r="AJ283">
+        <v>2</v>
+      </c>
+      <c r="AK283">
+        <v>1.4</v>
+      </c>
+      <c r="AL283">
+        <v>1.3</v>
+      </c>
+      <c r="AM283">
+        <v>1.5</v>
+      </c>
+      <c r="AN283">
+        <v>1.5</v>
+      </c>
+      <c r="AO283">
+        <v>2.17</v>
+      </c>
+      <c r="AP283">
+        <v>1.62</v>
+      </c>
+      <c r="AQ283">
+        <v>2</v>
+      </c>
+      <c r="AR283">
+        <v>1.44</v>
+      </c>
+      <c r="AS283">
+        <v>1.4</v>
+      </c>
+      <c r="AT283">
+        <v>2.84</v>
+      </c>
+      <c r="AU283">
+        <v>4</v>
+      </c>
+      <c r="AV283">
+        <v>2</v>
+      </c>
+      <c r="AW283">
+        <v>7</v>
+      </c>
+      <c r="AX283">
+        <v>2</v>
+      </c>
+      <c r="AY283">
+        <v>11</v>
+      </c>
+      <c r="AZ283">
+        <v>6</v>
+      </c>
+      <c r="BA283">
+        <v>3</v>
+      </c>
+      <c r="BB283">
+        <v>3</v>
+      </c>
+      <c r="BC283">
+        <v>6</v>
+      </c>
+      <c r="BD283">
+        <v>1.86</v>
+      </c>
+      <c r="BE283">
+        <v>6.4</v>
+      </c>
+      <c r="BF283">
+        <v>2.15</v>
+      </c>
+      <c r="BG283">
+        <v>1.33</v>
+      </c>
+      <c r="BH283">
+        <v>2.95</v>
+      </c>
+      <c r="BI283">
+        <v>1.57</v>
+      </c>
+      <c r="BJ283">
+        <v>2.2</v>
+      </c>
+      <c r="BK283">
+        <v>1.91</v>
+      </c>
+      <c r="BL283">
+        <v>1.76</v>
+      </c>
+      <c r="BM283">
+        <v>2.43</v>
+      </c>
+      <c r="BN283">
+        <v>1.47</v>
+      </c>
+      <c r="BO283">
+        <v>3.15</v>
+      </c>
+      <c r="BP283">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="284" spans="1:68">
+      <c r="A284" s="1">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>7728476</v>
+      </c>
+      <c r="C284" t="s">
+        <v>68</v>
+      </c>
+      <c r="D284" t="s">
+        <v>69</v>
+      </c>
+      <c r="E284" s="2">
+        <v>45697.60416666666</v>
+      </c>
+      <c r="F284">
+        <v>26</v>
+      </c>
+      <c r="G284" t="s">
+        <v>72</v>
+      </c>
+      <c r="H284" t="s">
+        <v>87</v>
+      </c>
+      <c r="I284">
+        <v>3</v>
+      </c>
+      <c r="J284">
+        <v>1</v>
+      </c>
+      <c r="K284">
+        <v>4</v>
+      </c>
+      <c r="L284">
+        <v>5</v>
+      </c>
+      <c r="M284">
+        <v>2</v>
+      </c>
+      <c r="N284">
+        <v>7</v>
+      </c>
+      <c r="O284" t="s">
+        <v>267</v>
+      </c>
+      <c r="P284" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q284">
+        <v>2.05</v>
+      </c>
+      <c r="R284">
+        <v>2.2</v>
+      </c>
+      <c r="S284">
+        <v>7.5</v>
+      </c>
+      <c r="T284">
+        <v>1.44</v>
+      </c>
+      <c r="U284">
+        <v>2.63</v>
+      </c>
+      <c r="V284">
+        <v>3.25</v>
+      </c>
+      <c r="W284">
+        <v>1.33</v>
+      </c>
+      <c r="X284">
+        <v>9</v>
+      </c>
+      <c r="Y284">
+        <v>1.07</v>
+      </c>
+      <c r="Z284">
+        <v>1.45</v>
+      </c>
+      <c r="AA284">
+        <v>4.5</v>
+      </c>
+      <c r="AB284">
+        <v>8.4</v>
+      </c>
+      <c r="AC284">
+        <v>1.06</v>
+      </c>
+      <c r="AD284">
+        <v>8.5</v>
+      </c>
+      <c r="AE284">
+        <v>1.36</v>
+      </c>
+      <c r="AF284">
+        <v>3.1</v>
+      </c>
+      <c r="AG284">
+        <v>1.95</v>
+      </c>
+      <c r="AH284">
+        <v>1.7</v>
+      </c>
+      <c r="AI284">
+        <v>2.38</v>
+      </c>
+      <c r="AJ284">
+        <v>1.53</v>
+      </c>
+      <c r="AK284">
+        <v>1.09</v>
+      </c>
+      <c r="AL284">
+        <v>1.17</v>
+      </c>
+      <c r="AM284">
+        <v>2.65</v>
+      </c>
+      <c r="AN284">
+        <v>1.31</v>
+      </c>
+      <c r="AO284">
+        <v>0.54</v>
+      </c>
+      <c r="AP284">
+        <v>1.43</v>
+      </c>
+      <c r="AQ284">
+        <v>0.5</v>
+      </c>
+      <c r="AR284">
+        <v>1.39</v>
+      </c>
+      <c r="AS284">
+        <v>0.95</v>
+      </c>
+      <c r="AT284">
+        <v>2.34</v>
+      </c>
+      <c r="AU284">
+        <v>11</v>
+      </c>
+      <c r="AV284">
+        <v>4</v>
+      </c>
+      <c r="AW284">
+        <v>6</v>
+      </c>
+      <c r="AX284">
+        <v>1</v>
+      </c>
+      <c r="AY284">
+        <v>18</v>
+      </c>
+      <c r="AZ284">
+        <v>5</v>
+      </c>
+      <c r="BA284">
+        <v>3</v>
+      </c>
+      <c r="BB284">
+        <v>1</v>
+      </c>
+      <c r="BC284">
+        <v>4</v>
+      </c>
+      <c r="BD284">
+        <v>1.21</v>
+      </c>
+      <c r="BE284">
+        <v>10</v>
+      </c>
+      <c r="BF284">
+        <v>5.65</v>
+      </c>
+      <c r="BG284">
+        <v>1.51</v>
+      </c>
+      <c r="BH284">
+        <v>2.45</v>
+      </c>
+      <c r="BI284">
+        <v>1.87</v>
+      </c>
+      <c r="BJ284">
+        <v>1.87</v>
+      </c>
+      <c r="BK284">
+        <v>2.42</v>
+      </c>
+      <c r="BL284">
+        <v>1.53</v>
+      </c>
+      <c r="BM284">
+        <v>3.3</v>
+      </c>
+      <c r="BN284">
+        <v>1.3</v>
+      </c>
+      <c r="BO284">
+        <v>4.65</v>
+      </c>
+      <c r="BP284">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="285" spans="1:68">
+      <c r="A285" s="1">
+        <v>284</v>
+      </c>
+      <c r="B285">
+        <v>7728480</v>
+      </c>
+      <c r="C285" t="s">
+        <v>68</v>
+      </c>
+      <c r="D285" t="s">
+        <v>69</v>
+      </c>
+      <c r="E285" s="2">
+        <v>45697.60416666666</v>
+      </c>
+      <c r="F285">
+        <v>26</v>
+      </c>
+      <c r="G285" t="s">
+        <v>75</v>
+      </c>
+      <c r="H285" t="s">
+        <v>90</v>
+      </c>
+      <c r="I285">
+        <v>3</v>
+      </c>
+      <c r="J285">
+        <v>0</v>
+      </c>
+      <c r="K285">
+        <v>3</v>
+      </c>
+      <c r="L285">
+        <v>3</v>
+      </c>
+      <c r="M285">
+        <v>1</v>
+      </c>
+      <c r="N285">
+        <v>4</v>
+      </c>
+      <c r="O285" t="s">
+        <v>268</v>
+      </c>
+      <c r="P285" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q285">
+        <v>3.1</v>
+      </c>
+      <c r="R285">
+        <v>2.2</v>
+      </c>
+      <c r="S285">
+        <v>3.25</v>
+      </c>
+      <c r="T285">
+        <v>1.4</v>
+      </c>
+      <c r="U285">
+        <v>2.75</v>
+      </c>
+      <c r="V285">
+        <v>2.75</v>
+      </c>
+      <c r="W285">
+        <v>1.4</v>
+      </c>
+      <c r="X285">
+        <v>8</v>
+      </c>
+      <c r="Y285">
+        <v>1.08</v>
+      </c>
+      <c r="Z285">
+        <v>2.47</v>
+      </c>
+      <c r="AA285">
+        <v>3.3</v>
+      </c>
+      <c r="AB285">
+        <v>3.05</v>
+      </c>
+      <c r="AC285">
+        <v>1.06</v>
+      </c>
+      <c r="AD285">
+        <v>8.5</v>
+      </c>
+      <c r="AE285">
+        <v>1.28</v>
+      </c>
+      <c r="AF285">
+        <v>3.5</v>
+      </c>
+      <c r="AG285">
+        <v>1.9</v>
+      </c>
+      <c r="AH285">
+        <v>1.9</v>
+      </c>
+      <c r="AI285">
+        <v>1.67</v>
+      </c>
+      <c r="AJ285">
+        <v>2.1</v>
+      </c>
+      <c r="AK285">
+        <v>1.42</v>
+      </c>
+      <c r="AL285">
+        <v>1.28</v>
+      </c>
+      <c r="AM285">
+        <v>1.5</v>
+      </c>
+      <c r="AN285">
+        <v>1.08</v>
+      </c>
+      <c r="AO285">
+        <v>1.62</v>
+      </c>
+      <c r="AP285">
+        <v>1.23</v>
+      </c>
+      <c r="AQ285">
+        <v>1.5</v>
+      </c>
+      <c r="AR285">
+        <v>1.52</v>
+      </c>
+      <c r="AS285">
+        <v>1.49</v>
+      </c>
+      <c r="AT285">
+        <v>3.01</v>
+      </c>
+      <c r="AU285">
+        <v>6</v>
+      </c>
+      <c r="AV285">
+        <v>9</v>
+      </c>
+      <c r="AW285">
+        <v>5</v>
+      </c>
+      <c r="AX285">
+        <v>12</v>
+      </c>
+      <c r="AY285">
+        <v>11</v>
+      </c>
+      <c r="AZ285">
+        <v>21</v>
+      </c>
+      <c r="BA285">
+        <v>3</v>
+      </c>
+      <c r="BB285">
+        <v>8</v>
+      </c>
+      <c r="BC285">
+        <v>11</v>
+      </c>
+      <c r="BD285">
+        <v>1.91</v>
+      </c>
+      <c r="BE285">
+        <v>8</v>
+      </c>
+      <c r="BF285">
+        <v>2.2</v>
+      </c>
+      <c r="BG285">
+        <v>1.27</v>
+      </c>
+      <c r="BH285">
+        <v>3.5</v>
+      </c>
+      <c r="BI285">
+        <v>1.5</v>
+      </c>
+      <c r="BJ285">
+        <v>2.5</v>
+      </c>
+      <c r="BK285">
+        <v>1.82</v>
+      </c>
+      <c r="BL285">
+        <v>1.93</v>
+      </c>
+      <c r="BM285">
+        <v>2.3</v>
+      </c>
+      <c r="BN285">
+        <v>1.57</v>
+      </c>
+      <c r="BO285">
+        <v>3</v>
+      </c>
+      <c r="BP285">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="372">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1491,7 +1491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP285"/>
+  <dimension ref="A1:BP286"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4506,7 +4506,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ15">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR15">
         <v>1.13</v>
@@ -6563,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>2</v>
@@ -11098,7 +11098,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ47">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR47">
         <v>1.72</v>
@@ -12125,7 +12125,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
         <v>0.5</v>
@@ -15630,7 +15630,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ69">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR69">
         <v>1.25</v>
@@ -17275,7 +17275,7 @@
         <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>0.6899999999999999</v>
@@ -20574,7 +20574,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ93">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR93">
         <v>1.5</v>
@@ -20983,7 +20983,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
         <v>1.5</v>
@@ -22634,7 +22634,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ103">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR103">
         <v>1.55</v>
@@ -24485,7 +24485,7 @@
         <v>1.25</v>
       </c>
       <c r="AP112">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ112">
         <v>1.15</v>
@@ -27166,7 +27166,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ125">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR125">
         <v>1.56</v>
@@ -30047,7 +30047,7 @@
         <v>1.17</v>
       </c>
       <c r="AP139">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ139">
         <v>0.75</v>
@@ -31080,7 +31080,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ144">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR144">
         <v>1.75</v>
@@ -33961,7 +33961,7 @@
         <v>0.33</v>
       </c>
       <c r="AP158">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ158">
         <v>0.23</v>
@@ -36642,7 +36642,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ171">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR171">
         <v>1.18</v>
@@ -37875,7 +37875,7 @@
         <v>0.88</v>
       </c>
       <c r="AP177">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ177">
         <v>1.5</v>
@@ -41792,7 +41792,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ196">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR196">
         <v>1.42</v>
@@ -43643,7 +43643,7 @@
         <v>1.75</v>
       </c>
       <c r="AP205">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ205">
         <v>1.5</v>
@@ -45706,7 +45706,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ215">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR215">
         <v>1.3</v>
@@ -47145,7 +47145,7 @@
         <v>0.2</v>
       </c>
       <c r="AP222">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ222">
         <v>0.85</v>
@@ -48384,7 +48384,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ228">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR228">
         <v>1.5</v>
@@ -50441,7 +50441,7 @@
         <v>1.1</v>
       </c>
       <c r="AP238">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ238">
         <v>1</v>
@@ -54564,7 +54564,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ258">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR258">
         <v>1.2</v>
@@ -54973,7 +54973,7 @@
         <v>1.36</v>
       </c>
       <c r="AP260">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ260">
         <v>1.38</v>
@@ -60202,6 +60202,212 @@
       </c>
       <c r="BP285">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="286" spans="1:68">
+      <c r="A286" s="1">
+        <v>285</v>
+      </c>
+      <c r="B286">
+        <v>7728483</v>
+      </c>
+      <c r="C286" t="s">
+        <v>68</v>
+      </c>
+      <c r="D286" t="s">
+        <v>69</v>
+      </c>
+      <c r="E286" s="2">
+        <v>45698.6875</v>
+      </c>
+      <c r="F286">
+        <v>26</v>
+      </c>
+      <c r="G286" t="s">
+        <v>89</v>
+      </c>
+      <c r="H286" t="s">
+        <v>80</v>
+      </c>
+      <c r="I286">
+        <v>0</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
+      </c>
+      <c r="K286">
+        <v>0</v>
+      </c>
+      <c r="L286">
+        <v>0</v>
+      </c>
+      <c r="M286">
+        <v>0</v>
+      </c>
+      <c r="N286">
+        <v>0</v>
+      </c>
+      <c r="O286" t="s">
+        <v>94</v>
+      </c>
+      <c r="P286" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q286">
+        <v>2.3</v>
+      </c>
+      <c r="R286">
+        <v>2.05</v>
+      </c>
+      <c r="S286">
+        <v>6.5</v>
+      </c>
+      <c r="T286">
+        <v>1.5</v>
+      </c>
+      <c r="U286">
+        <v>2.5</v>
+      </c>
+      <c r="V286">
+        <v>3.5</v>
+      </c>
+      <c r="W286">
+        <v>1.29</v>
+      </c>
+      <c r="X286">
+        <v>11</v>
+      </c>
+      <c r="Y286">
+        <v>1.05</v>
+      </c>
+      <c r="Z286">
+        <v>1.63</v>
+      </c>
+      <c r="AA286">
+        <v>3.85</v>
+      </c>
+      <c r="AB286">
+        <v>6.2</v>
+      </c>
+      <c r="AC286">
+        <v>1.08</v>
+      </c>
+      <c r="AD286">
+        <v>7.5</v>
+      </c>
+      <c r="AE286">
+        <v>1.44</v>
+      </c>
+      <c r="AF286">
+        <v>2.7</v>
+      </c>
+      <c r="AG286">
+        <v>2.15</v>
+      </c>
+      <c r="AH286">
+        <v>1.57</v>
+      </c>
+      <c r="AI286">
+        <v>2.25</v>
+      </c>
+      <c r="AJ286">
+        <v>1.57</v>
+      </c>
+      <c r="AK286">
+        <v>1.1</v>
+      </c>
+      <c r="AL286">
+        <v>1.22</v>
+      </c>
+      <c r="AM286">
+        <v>2.2</v>
+      </c>
+      <c r="AN286">
+        <v>2.08</v>
+      </c>
+      <c r="AO286">
+        <v>0.75</v>
+      </c>
+      <c r="AP286">
+        <v>2</v>
+      </c>
+      <c r="AQ286">
+        <v>0.77</v>
+      </c>
+      <c r="AR286">
+        <v>1.59</v>
+      </c>
+      <c r="AS286">
+        <v>1.16</v>
+      </c>
+      <c r="AT286">
+        <v>2.75</v>
+      </c>
+      <c r="AU286">
+        <v>5</v>
+      </c>
+      <c r="AV286">
+        <v>0</v>
+      </c>
+      <c r="AW286">
+        <v>8</v>
+      </c>
+      <c r="AX286">
+        <v>5</v>
+      </c>
+      <c r="AY286">
+        <v>14</v>
+      </c>
+      <c r="AZ286">
+        <v>5</v>
+      </c>
+      <c r="BA286">
+        <v>8</v>
+      </c>
+      <c r="BB286">
+        <v>0</v>
+      </c>
+      <c r="BC286">
+        <v>8</v>
+      </c>
+      <c r="BD286">
+        <v>1.37</v>
+      </c>
+      <c r="BE286">
+        <v>9</v>
+      </c>
+      <c r="BF286">
+        <v>3.7</v>
+      </c>
+      <c r="BG286">
+        <v>1.29</v>
+      </c>
+      <c r="BH286">
+        <v>3.35</v>
+      </c>
+      <c r="BI286">
+        <v>1.53</v>
+      </c>
+      <c r="BJ286">
+        <v>2.41</v>
+      </c>
+      <c r="BK286">
+        <v>1.87</v>
+      </c>
+      <c r="BL286">
+        <v>1.87</v>
+      </c>
+      <c r="BM286">
+        <v>2.38</v>
+      </c>
+      <c r="BN286">
+        <v>1.54</v>
+      </c>
+      <c r="BO286">
+        <v>3.2</v>
+      </c>
+      <c r="BP286">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="373">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -823,6 +823,9 @@
     <t>['19', '26', '31']</t>
   </si>
   <si>
+    <t>['9', '23', '62', '90+2']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1491,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP286"/>
+  <dimension ref="A1:BP287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1747,7 +1750,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2031,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ3">
         <v>0.85</v>
@@ -2159,7 +2162,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2983,7 +2986,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3189,7 +3192,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4013,7 +4016,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4219,7 +4222,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -5249,7 +5252,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5867,7 +5870,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6073,7 +6076,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6279,7 +6282,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6485,7 +6488,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6691,7 +6694,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6897,7 +6900,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7309,7 +7312,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7596,7 +7599,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ30">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>1.73</v>
@@ -7799,7 +7802,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ31">
         <v>1.36</v>
@@ -7927,7 +7930,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8133,7 +8136,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8545,7 +8548,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -10399,7 +10402,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11017,7 +11020,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11919,7 +11922,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -12540,7 +12543,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ54">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12665,7 +12668,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12871,7 +12874,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13077,7 +13080,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13283,7 +13286,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13695,7 +13698,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14313,7 +14316,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14931,7 +14934,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15343,7 +15346,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15549,7 +15552,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15833,7 +15836,7 @@
         <v>2</v>
       </c>
       <c r="AP70">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ70">
         <v>1.5</v>
@@ -16167,7 +16170,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16373,7 +16376,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16579,7 +16582,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17072,7 +17075,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ76">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -17403,7 +17406,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17609,7 +17612,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18021,7 +18024,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18099,7 +18102,7 @@
         <v>1.67</v>
       </c>
       <c r="AP81">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ81">
         <v>1.5</v>
@@ -18227,7 +18230,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18433,7 +18436,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19257,7 +19260,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19669,7 +19672,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19875,7 +19878,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20162,7 +20165,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ91">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20287,7 +20290,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20699,7 +20702,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20905,7 +20908,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21935,7 +21938,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23249,7 +23252,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ106">
         <v>0.6899999999999999</v>
@@ -23377,7 +23380,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23995,7 +23998,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24407,7 +24410,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24613,7 +24616,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25025,7 +25028,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25849,7 +25852,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26467,7 +26470,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26548,7 +26551,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ122">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR122">
         <v>1.4</v>
@@ -26879,7 +26882,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -26957,7 +26960,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ124">
         <v>0.5</v>
@@ -27291,7 +27294,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27703,7 +27706,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28115,7 +28118,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28321,7 +28324,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28527,7 +28530,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28939,7 +28942,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29145,7 +29148,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29763,7 +29766,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30381,7 +30384,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30587,7 +30590,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30665,7 +30668,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ142">
         <v>1.17</v>
@@ -30793,7 +30796,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30999,7 +31002,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31411,7 +31414,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31823,7 +31826,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32522,7 +32525,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ151">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR151">
         <v>1.43</v>
@@ -32853,7 +32856,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33471,7 +33474,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -35119,7 +35122,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35737,7 +35740,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36149,7 +36152,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36639,7 +36642,7 @@
         <v>0.71</v>
       </c>
       <c r="AP171">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ171">
         <v>0.77</v>
@@ -36767,7 +36770,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37385,7 +37388,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37672,7 +37675,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ176">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR176">
         <v>1.6</v>
@@ -37797,7 +37800,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38209,7 +38212,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38415,7 +38418,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39239,7 +39242,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39526,7 +39529,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ185">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR185">
         <v>1.42</v>
@@ -40063,7 +40066,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40141,7 +40144,7 @@
         <v>1.38</v>
       </c>
       <c r="AP188">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ188">
         <v>1.43</v>
@@ -40681,7 +40684,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40887,7 +40890,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41093,7 +41096,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41299,7 +41302,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42535,7 +42538,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42947,7 +42950,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43153,7 +43156,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43771,7 +43774,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43852,7 +43855,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ206">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR206">
         <v>1.42</v>
@@ -44801,7 +44804,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45007,7 +45010,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45213,7 +45216,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45419,7 +45422,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45497,7 +45500,7 @@
         <v>1.11</v>
       </c>
       <c r="AP214">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ214">
         <v>1</v>
@@ -45831,7 +45834,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -47067,7 +47070,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47354,7 +47357,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ223">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR223">
         <v>1.71</v>
@@ -47479,7 +47482,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47891,7 +47894,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48097,7 +48100,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48509,7 +48512,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48715,7 +48718,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48921,7 +48924,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49745,7 +49748,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50569,7 +50572,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51187,7 +51190,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51599,7 +51602,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51805,7 +51808,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -52710,7 +52713,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ249">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR249">
         <v>1.51</v>
@@ -52835,7 +52838,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53041,7 +53044,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53453,7 +53456,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53531,7 +53534,7 @@
         <v>1</v>
       </c>
       <c r="AP253">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ253">
         <v>0.85</v>
@@ -53865,7 +53868,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54071,7 +54074,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54483,7 +54486,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -55101,7 +55104,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55307,7 +55310,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55925,7 +55928,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56209,7 +56212,7 @@
         <v>1.27</v>
       </c>
       <c r="AP266">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ266">
         <v>1.17</v>
@@ -56749,7 +56752,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57573,7 +57576,7 @@
         <v>94</v>
       </c>
       <c r="P273" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q273">
         <v>4</v>
@@ -58066,7 +58069,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ275">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR275">
         <v>1.57</v>
@@ -58397,7 +58400,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59427,7 +59430,7 @@
         <v>186</v>
       </c>
       <c r="P282" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59839,7 +59842,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60408,6 +60411,212 @@
       </c>
       <c r="BP286">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="287" spans="1:68">
+      <c r="A287" s="1">
+        <v>286</v>
+      </c>
+      <c r="B287">
+        <v>7728493</v>
+      </c>
+      <c r="C287" t="s">
+        <v>68</v>
+      </c>
+      <c r="D287" t="s">
+        <v>69</v>
+      </c>
+      <c r="E287" s="2">
+        <v>45702.6875</v>
+      </c>
+      <c r="F287">
+        <v>27</v>
+      </c>
+      <c r="G287" t="s">
+        <v>71</v>
+      </c>
+      <c r="H287" t="s">
+        <v>74</v>
+      </c>
+      <c r="I287">
+        <v>2</v>
+      </c>
+      <c r="J287">
+        <v>1</v>
+      </c>
+      <c r="K287">
+        <v>3</v>
+      </c>
+      <c r="L287">
+        <v>4</v>
+      </c>
+      <c r="M287">
+        <v>1</v>
+      </c>
+      <c r="N287">
+        <v>5</v>
+      </c>
+      <c r="O287" t="s">
+        <v>269</v>
+      </c>
+      <c r="P287" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q287">
+        <v>2.4</v>
+      </c>
+      <c r="R287">
+        <v>1.93</v>
+      </c>
+      <c r="S287">
+        <v>5.5</v>
+      </c>
+      <c r="T287">
+        <v>1.55</v>
+      </c>
+      <c r="U287">
+        <v>2.3</v>
+      </c>
+      <c r="V287">
+        <v>3.6</v>
+      </c>
+      <c r="W287">
+        <v>1.25</v>
+      </c>
+      <c r="X287">
+        <v>10.5</v>
+      </c>
+      <c r="Y287">
+        <v>1.04</v>
+      </c>
+      <c r="Z287">
+        <v>1.76</v>
+      </c>
+      <c r="AA287">
+        <v>3.41</v>
+      </c>
+      <c r="AB287">
+        <v>5.7</v>
+      </c>
+      <c r="AC287">
+        <v>1.11</v>
+      </c>
+      <c r="AD287">
+        <v>6.4</v>
+      </c>
+      <c r="AE287">
+        <v>1.5</v>
+      </c>
+      <c r="AF287">
+        <v>2.3</v>
+      </c>
+      <c r="AG287">
+        <v>2.56</v>
+      </c>
+      <c r="AH287">
+        <v>1.45</v>
+      </c>
+      <c r="AI287">
+        <v>2.4</v>
+      </c>
+      <c r="AJ287">
+        <v>1.5</v>
+      </c>
+      <c r="AK287">
+        <v>1.16</v>
+      </c>
+      <c r="AL287">
+        <v>1.31</v>
+      </c>
+      <c r="AM287">
+        <v>2.05</v>
+      </c>
+      <c r="AN287">
+        <v>2.31</v>
+      </c>
+      <c r="AO287">
+        <v>1.08</v>
+      </c>
+      <c r="AP287">
+        <v>2.36</v>
+      </c>
+      <c r="AQ287">
+        <v>1</v>
+      </c>
+      <c r="AR287">
+        <v>1.29</v>
+      </c>
+      <c r="AS287">
+        <v>0.86</v>
+      </c>
+      <c r="AT287">
+        <v>2.15</v>
+      </c>
+      <c r="AU287">
+        <v>7</v>
+      </c>
+      <c r="AV287">
+        <v>2</v>
+      </c>
+      <c r="AW287">
+        <v>17</v>
+      </c>
+      <c r="AX287">
+        <v>9</v>
+      </c>
+      <c r="AY287">
+        <v>31</v>
+      </c>
+      <c r="AZ287">
+        <v>11</v>
+      </c>
+      <c r="BA287">
+        <v>7</v>
+      </c>
+      <c r="BB287">
+        <v>3</v>
+      </c>
+      <c r="BC287">
+        <v>10</v>
+      </c>
+      <c r="BD287">
+        <v>1.49</v>
+      </c>
+      <c r="BE287">
+        <v>6.75</v>
+      </c>
+      <c r="BF287">
+        <v>2.95</v>
+      </c>
+      <c r="BG287">
+        <v>1.43</v>
+      </c>
+      <c r="BH287">
+        <v>2.55</v>
+      </c>
+      <c r="BI287">
+        <v>1.74</v>
+      </c>
+      <c r="BJ287">
+        <v>1.93</v>
+      </c>
+      <c r="BK287">
+        <v>2.18</v>
+      </c>
+      <c r="BL287">
+        <v>1.58</v>
+      </c>
+      <c r="BM287">
+        <v>2.88</v>
+      </c>
+      <c r="BN287">
+        <v>1.34</v>
+      </c>
+      <c r="BO287">
+        <v>3.8</v>
+      </c>
+      <c r="BP287">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="378">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -826,6 +826,15 @@
     <t>['9', '23', '62', '90+2']</t>
   </si>
   <si>
+    <t>['18', '57']</t>
+  </si>
+  <si>
+    <t>['61', '80']</t>
+  </si>
+  <si>
+    <t>['9', '42']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1133,6 +1142,12 @@
   </si>
   <si>
     <t>['44', '60']</t>
+  </si>
+  <si>
+    <t>['40', '51', '57']</t>
+  </si>
+  <si>
+    <t>['6', '45+2', '79']</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP287"/>
+  <dimension ref="A1:BP291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1750,7 +1765,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2037,7 +2052,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ3">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2162,7 +2177,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2655,7 +2670,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ6">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2986,7 +3001,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3192,7 +3207,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3270,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ9">
         <v>1.5</v>
@@ -4016,7 +4031,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4094,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ13">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR13">
         <v>1.32</v>
@@ -4222,7 +4237,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4921,7 +4936,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ17">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5252,7 +5267,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5330,7 +5345,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ19">
         <v>1.5</v>
@@ -5742,7 +5757,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ21">
         <v>1.38</v>
@@ -5870,7 +5885,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5948,7 +5963,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ22">
         <v>1.36</v>
@@ -6076,7 +6091,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6282,7 +6297,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6488,7 +6503,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6694,7 +6709,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6900,7 +6915,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7312,7 +7327,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7930,7 +7945,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8136,7 +8151,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8423,7 +8438,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ34">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.17</v>
@@ -8548,7 +8563,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8626,7 +8641,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ35">
         <v>2</v>
@@ -9453,7 +9468,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ39">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.32</v>
@@ -9862,7 +9877,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ41">
         <v>1.43</v>
@@ -10402,7 +10417,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10480,10 +10495,10 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ44">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -10689,7 +10704,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ45">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR45">
         <v>0.96</v>
@@ -11020,7 +11035,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11716,7 +11731,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -12668,7 +12683,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12874,7 +12889,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13080,7 +13095,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13161,7 +13176,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ57">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -13286,7 +13301,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13698,7 +13713,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14188,7 +14203,7 @@
         <v>0.5</v>
       </c>
       <c r="AP62">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14316,7 +14331,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14394,10 +14409,10 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ63">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR63">
         <v>1.13</v>
@@ -14600,7 +14615,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ64">
         <v>2</v>
@@ -14934,7 +14949,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15015,7 +15030,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ66">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR66">
         <v>1.93</v>
@@ -15221,7 +15236,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ67">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR67">
         <v>1.16</v>
@@ -15346,7 +15361,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15552,7 +15567,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16170,7 +16185,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16376,7 +16391,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16582,7 +16597,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16866,7 +16881,7 @@
         <v>0.33</v>
       </c>
       <c r="AP75">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ75">
         <v>0.23</v>
@@ -17281,7 +17296,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR77">
         <v>1.33</v>
@@ -17406,7 +17421,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17484,7 +17499,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ78">
         <v>0.5</v>
@@ -17612,7 +17627,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17693,7 +17708,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ79">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR79">
         <v>1.18</v>
@@ -18024,7 +18039,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18230,7 +18245,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18436,7 +18451,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18926,7 +18941,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ85">
         <v>0.5</v>
@@ -19135,7 +19150,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ86">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19260,7 +19275,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19672,7 +19687,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19753,7 +19768,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ89">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -19878,7 +19893,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19956,7 +19971,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ90">
         <v>1.36</v>
@@ -20162,7 +20177,7 @@
         <v>0.33</v>
       </c>
       <c r="AP91">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -20290,7 +20305,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20371,7 +20386,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ92">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.42</v>
@@ -20702,7 +20717,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20908,7 +20923,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21192,7 +21207,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ96">
         <v>1.43</v>
@@ -21401,7 +21416,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ97">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -21938,7 +21953,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23046,7 +23061,7 @@
         <v>1.4</v>
       </c>
       <c r="AP105">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ105">
         <v>1.43</v>
@@ -23255,7 +23270,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ106">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR106">
         <v>1.12</v>
@@ -23380,7 +23395,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23998,7 +24013,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24410,7 +24425,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24616,7 +24631,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24694,7 +24709,7 @@
         <v>2</v>
       </c>
       <c r="AP113">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ113">
         <v>1.5</v>
@@ -24903,7 +24918,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ114">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -25028,7 +25043,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25312,10 +25327,10 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ116">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -25518,7 +25533,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ117">
         <v>1.17</v>
@@ -25852,7 +25867,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26342,10 +26357,10 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ121">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR121">
         <v>1.32</v>
@@ -26470,7 +26485,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26882,7 +26897,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27294,7 +27309,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27581,7 +27596,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ127">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR127">
         <v>1.1</v>
@@ -27706,7 +27721,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28118,7 +28133,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28324,7 +28339,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28530,7 +28545,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28942,7 +28957,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29148,7 +29163,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29226,7 +29241,7 @@
         <v>0.83</v>
       </c>
       <c r="AP135">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ135">
         <v>1.46</v>
@@ -29435,7 +29450,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ136">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -29766,7 +29781,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29844,7 +29859,7 @@
         <v>1.17</v>
       </c>
       <c r="AP138">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -30256,7 +30271,7 @@
         <v>1</v>
       </c>
       <c r="AP140">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ140">
         <v>1.15</v>
@@ -30384,7 +30399,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30590,7 +30605,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30671,7 +30686,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ142">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR142">
         <v>1.16</v>
@@ -30796,7 +30811,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31002,7 +31017,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31414,7 +31429,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31826,7 +31841,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32319,7 +32334,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ150">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR150">
         <v>1.6</v>
@@ -32856,7 +32871,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32934,7 +32949,7 @@
         <v>0.83</v>
       </c>
       <c r="AP153">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ153">
         <v>1.15</v>
@@ -33346,7 +33361,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ155">
         <v>0.75</v>
@@ -33474,7 +33489,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33761,7 +33776,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ157">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR157">
         <v>1.49</v>
@@ -34376,7 +34391,7 @@
         <v>1.17</v>
       </c>
       <c r="AP160">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ160">
         <v>1.5</v>
@@ -34585,7 +34600,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ161">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR161">
         <v>1.62</v>
@@ -35122,7 +35137,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35200,7 +35215,7 @@
         <v>1.38</v>
       </c>
       <c r="AP164">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ164">
         <v>1.5</v>
@@ -35409,7 +35424,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ165">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR165">
         <v>1.7</v>
@@ -35615,7 +35630,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ166">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR166">
         <v>1.42</v>
@@ -35740,7 +35755,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36152,7 +36167,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36770,7 +36785,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37263,7 +37278,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ174">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR174">
         <v>1.76</v>
@@ -37388,7 +37403,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37469,7 +37484,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ175">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR175">
         <v>1.58</v>
@@ -37672,7 +37687,7 @@
         <v>0.83</v>
       </c>
       <c r="AP176">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ176">
         <v>1</v>
@@ -37800,7 +37815,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38212,7 +38227,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38418,7 +38433,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38702,7 +38717,7 @@
         <v>1.14</v>
       </c>
       <c r="AP181">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ181">
         <v>1.15</v>
@@ -38908,7 +38923,7 @@
         <v>1.14</v>
       </c>
       <c r="AP182">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ182">
         <v>1.17</v>
@@ -39114,10 +39129,10 @@
         <v>0.88</v>
       </c>
       <c r="AP183">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ183">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR183">
         <v>1.63</v>
@@ -39242,7 +39257,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39735,7 +39750,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ186">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR186">
         <v>1.44</v>
@@ -40066,7 +40081,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40353,7 +40368,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ189">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR189">
         <v>1.53</v>
@@ -40684,7 +40699,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40890,7 +40905,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -40971,7 +40986,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ192">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR192">
         <v>1.15</v>
@@ -41096,7 +41111,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41302,7 +41317,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42204,7 +42219,7 @@
         <v>1.25</v>
       </c>
       <c r="AP198">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42538,7 +42553,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42619,7 +42634,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ200">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR200">
         <v>1.61</v>
@@ -42950,7 +42965,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43028,7 +43043,7 @@
         <v>0.67</v>
       </c>
       <c r="AP202">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ202">
         <v>0.5</v>
@@ -43156,7 +43171,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43774,7 +43789,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44061,7 +44076,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ207">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR207">
         <v>1.45</v>
@@ -44264,7 +44279,7 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ208">
         <v>1.5</v>
@@ -44804,7 +44819,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44885,7 +44900,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ211">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR211">
         <v>1.69</v>
@@ -45010,7 +45025,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45216,7 +45231,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45422,7 +45437,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45834,7 +45849,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46736,7 +46751,7 @@
         <v>1.1</v>
       </c>
       <c r="AP220">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ220">
         <v>1</v>
@@ -47070,7 +47085,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47151,7 +47166,7 @@
         <v>2</v>
       </c>
       <c r="AQ222">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR222">
         <v>1.64</v>
@@ -47482,7 +47497,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47563,7 +47578,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ224">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR224">
         <v>1.5</v>
@@ -47894,7 +47909,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -47972,7 +47987,7 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ226">
         <v>1.17</v>
@@ -48100,7 +48115,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48181,7 +48196,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ227">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR227">
         <v>1.67</v>
@@ -48384,7 +48399,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ228">
         <v>0.77</v>
@@ -48512,7 +48527,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48718,7 +48733,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48924,7 +48939,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49002,7 +49017,7 @@
         <v>1.2</v>
       </c>
       <c r="AP231">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ231">
         <v>1.43</v>
@@ -49748,7 +49763,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50032,7 +50047,7 @@
         <v>1.5</v>
       </c>
       <c r="AP236">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ236">
         <v>1.38</v>
@@ -50572,7 +50587,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51190,7 +51205,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51271,7 +51286,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ242">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR242">
         <v>1.37</v>
@@ -51474,7 +51489,7 @@
         <v>1.27</v>
       </c>
       <c r="AP243">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ243">
         <v>1.38</v>
@@ -51602,7 +51617,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51683,7 +51698,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ244">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR244">
         <v>1.4</v>
@@ -51808,7 +51823,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -52710,7 +52725,7 @@
         <v>1</v>
       </c>
       <c r="AP249">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ249">
         <v>1</v>
@@ -52838,7 +52853,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -52916,10 +52931,10 @@
         <v>0.45</v>
       </c>
       <c r="AP250">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ250">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR250">
         <v>1.68</v>
@@ -53044,7 +53059,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53456,7 +53471,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53537,7 +53552,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ253">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR253">
         <v>1.15</v>
@@ -53743,7 +53758,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ254">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR254">
         <v>1.63</v>
@@ -53868,7 +53883,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54074,7 +54089,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54486,7 +54501,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -54564,7 +54579,7 @@
         <v>0.55</v>
       </c>
       <c r="AP258">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ258">
         <v>0.77</v>
@@ -55104,7 +55119,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55310,7 +55325,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55800,7 +55815,7 @@
         <v>1.36</v>
       </c>
       <c r="AP264">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ264">
         <v>1.46</v>
@@ -55928,7 +55943,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56752,7 +56767,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -56830,10 +56845,10 @@
         <v>0.92</v>
       </c>
       <c r="AP269">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ269">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR269">
         <v>1.57</v>
@@ -57036,7 +57051,7 @@
         <v>1.25</v>
       </c>
       <c r="AP270">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ270">
         <v>1.5</v>
@@ -57451,7 +57466,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ272">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR272">
         <v>1.65</v>
@@ -57576,7 +57591,7 @@
         <v>94</v>
       </c>
       <c r="P273" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q273">
         <v>4</v>
@@ -57654,10 +57669,10 @@
         <v>0.67</v>
       </c>
       <c r="AP273">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ273">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR273">
         <v>1.18</v>
@@ -57860,7 +57875,7 @@
         <v>1.08</v>
       </c>
       <c r="AP274">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ274">
         <v>1</v>
@@ -58400,7 +58415,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59099,7 +59114,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ280">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR280">
         <v>1.52</v>
@@ -59430,7 +59445,7 @@
         <v>186</v>
       </c>
       <c r="P282" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59842,7 +59857,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60460,7 +60475,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -60617,6 +60632,830 @@
       </c>
       <c r="BP287">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:68">
+      <c r="A288" s="1">
+        <v>287</v>
+      </c>
+      <c r="B288">
+        <v>7728487</v>
+      </c>
+      <c r="C288" t="s">
+        <v>68</v>
+      </c>
+      <c r="D288" t="s">
+        <v>69</v>
+      </c>
+      <c r="E288" s="2">
+        <v>45703.41666666666</v>
+      </c>
+      <c r="F288">
+        <v>27</v>
+      </c>
+      <c r="G288" t="s">
+        <v>86</v>
+      </c>
+      <c r="H288" t="s">
+        <v>73</v>
+      </c>
+      <c r="I288">
+        <v>1</v>
+      </c>
+      <c r="J288">
+        <v>0</v>
+      </c>
+      <c r="K288">
+        <v>1</v>
+      </c>
+      <c r="L288">
+        <v>2</v>
+      </c>
+      <c r="M288">
+        <v>0</v>
+      </c>
+      <c r="N288">
+        <v>2</v>
+      </c>
+      <c r="O288" t="s">
+        <v>270</v>
+      </c>
+      <c r="P288" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q288">
+        <v>2.5</v>
+      </c>
+      <c r="R288">
+        <v>2.18</v>
+      </c>
+      <c r="S288">
+        <v>4.3</v>
+      </c>
+      <c r="T288">
+        <v>1.4</v>
+      </c>
+      <c r="U288">
+        <v>2.75</v>
+      </c>
+      <c r="V288">
+        <v>2.75</v>
+      </c>
+      <c r="W288">
+        <v>1.4</v>
+      </c>
+      <c r="X288">
+        <v>6.55</v>
+      </c>
+      <c r="Y288">
+        <v>1.05</v>
+      </c>
+      <c r="Z288">
+        <v>2.09</v>
+      </c>
+      <c r="AA288">
+        <v>3.45</v>
+      </c>
+      <c r="AB288">
+        <v>3.76</v>
+      </c>
+      <c r="AC288">
+        <v>1.06</v>
+      </c>
+      <c r="AD288">
+        <v>8.5</v>
+      </c>
+      <c r="AE288">
+        <v>1.3</v>
+      </c>
+      <c r="AF288">
+        <v>3.2</v>
+      </c>
+      <c r="AG288">
+        <v>1.89</v>
+      </c>
+      <c r="AH288">
+        <v>1.92</v>
+      </c>
+      <c r="AI288">
+        <v>1.77</v>
+      </c>
+      <c r="AJ288">
+        <v>1.94</v>
+      </c>
+      <c r="AK288">
+        <v>1.26</v>
+      </c>
+      <c r="AL288">
+        <v>1.28</v>
+      </c>
+      <c r="AM288">
+        <v>1.78</v>
+      </c>
+      <c r="AN288">
+        <v>1.08</v>
+      </c>
+      <c r="AO288">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP288">
+        <v>1.21</v>
+      </c>
+      <c r="AQ288">
+        <v>0.64</v>
+      </c>
+      <c r="AR288">
+        <v>1.7</v>
+      </c>
+      <c r="AS288">
+        <v>1.21</v>
+      </c>
+      <c r="AT288">
+        <v>2.91</v>
+      </c>
+      <c r="AU288">
+        <v>4</v>
+      </c>
+      <c r="AV288">
+        <v>5</v>
+      </c>
+      <c r="AW288">
+        <v>8</v>
+      </c>
+      <c r="AX288">
+        <v>8</v>
+      </c>
+      <c r="AY288">
+        <v>13</v>
+      </c>
+      <c r="AZ288">
+        <v>15</v>
+      </c>
+      <c r="BA288">
+        <v>2</v>
+      </c>
+      <c r="BB288">
+        <v>3</v>
+      </c>
+      <c r="BC288">
+        <v>5</v>
+      </c>
+      <c r="BD288">
+        <v>1.58</v>
+      </c>
+      <c r="BE288">
+        <v>6.5</v>
+      </c>
+      <c r="BF288">
+        <v>2.63</v>
+      </c>
+      <c r="BG288">
+        <v>1.37</v>
+      </c>
+      <c r="BH288">
+        <v>2.75</v>
+      </c>
+      <c r="BI288">
+        <v>1.64</v>
+      </c>
+      <c r="BJ288">
+        <v>2.07</v>
+      </c>
+      <c r="BK288">
+        <v>2.02</v>
+      </c>
+      <c r="BL288">
+        <v>1.67</v>
+      </c>
+      <c r="BM288">
+        <v>2.6</v>
+      </c>
+      <c r="BN288">
+        <v>1.41</v>
+      </c>
+      <c r="BO288">
+        <v>3.4</v>
+      </c>
+      <c r="BP288">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="289" spans="1:68">
+      <c r="A289" s="1">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>7728486</v>
+      </c>
+      <c r="C289" t="s">
+        <v>68</v>
+      </c>
+      <c r="D289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E289" s="2">
+        <v>45703.51041666666</v>
+      </c>
+      <c r="F289">
+        <v>27</v>
+      </c>
+      <c r="G289" t="s">
+        <v>87</v>
+      </c>
+      <c r="H289" t="s">
+        <v>83</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>0</v>
+      </c>
+      <c r="L289">
+        <v>0</v>
+      </c>
+      <c r="M289">
+        <v>1</v>
+      </c>
+      <c r="N289">
+        <v>1</v>
+      </c>
+      <c r="O289" t="s">
+        <v>94</v>
+      </c>
+      <c r="P289" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q289">
+        <v>4.2</v>
+      </c>
+      <c r="R289">
+        <v>1.9</v>
+      </c>
+      <c r="S289">
+        <v>2.75</v>
+      </c>
+      <c r="T289">
+        <v>1.53</v>
+      </c>
+      <c r="U289">
+        <v>2.3</v>
+      </c>
+      <c r="V289">
+        <v>3.5</v>
+      </c>
+      <c r="W289">
+        <v>1.26</v>
+      </c>
+      <c r="X289">
+        <v>10</v>
+      </c>
+      <c r="Y289">
+        <v>1.04</v>
+      </c>
+      <c r="Z289">
+        <v>3.79</v>
+      </c>
+      <c r="AA289">
+        <v>3.05</v>
+      </c>
+      <c r="AB289">
+        <v>2.26</v>
+      </c>
+      <c r="AC289">
+        <v>1.1</v>
+      </c>
+      <c r="AD289">
+        <v>6.6</v>
+      </c>
+      <c r="AE289">
+        <v>1.5</v>
+      </c>
+      <c r="AF289">
+        <v>2.4</v>
+      </c>
+      <c r="AG289">
+        <v>2.37</v>
+      </c>
+      <c r="AH289">
+        <v>1.48</v>
+      </c>
+      <c r="AI289">
+        <v>2.15</v>
+      </c>
+      <c r="AJ289">
+        <v>1.62</v>
+      </c>
+      <c r="AK289">
+        <v>1.7</v>
+      </c>
+      <c r="AL289">
+        <v>1.33</v>
+      </c>
+      <c r="AM289">
+        <v>1.27</v>
+      </c>
+      <c r="AN289">
+        <v>0.67</v>
+      </c>
+      <c r="AO289">
+        <v>0.85</v>
+      </c>
+      <c r="AP289">
+        <v>0.62</v>
+      </c>
+      <c r="AQ289">
+        <v>1</v>
+      </c>
+      <c r="AR289">
+        <v>1.17</v>
+      </c>
+      <c r="AS289">
+        <v>1.13</v>
+      </c>
+      <c r="AT289">
+        <v>2.3</v>
+      </c>
+      <c r="AU289">
+        <v>5</v>
+      </c>
+      <c r="AV289">
+        <v>8</v>
+      </c>
+      <c r="AW289">
+        <v>7</v>
+      </c>
+      <c r="AX289">
+        <v>8</v>
+      </c>
+      <c r="AY289">
+        <v>14</v>
+      </c>
+      <c r="AZ289">
+        <v>17</v>
+      </c>
+      <c r="BA289">
+        <v>6</v>
+      </c>
+      <c r="BB289">
+        <v>5</v>
+      </c>
+      <c r="BC289">
+        <v>11</v>
+      </c>
+      <c r="BD289">
+        <v>2.32</v>
+      </c>
+      <c r="BE289">
+        <v>6.25</v>
+      </c>
+      <c r="BF289">
+        <v>1.75</v>
+      </c>
+      <c r="BG289">
+        <v>1.47</v>
+      </c>
+      <c r="BH289">
+        <v>2.4</v>
+      </c>
+      <c r="BI289">
+        <v>1.8</v>
+      </c>
+      <c r="BJ289">
+        <v>1.86</v>
+      </c>
+      <c r="BK289">
+        <v>2.28</v>
+      </c>
+      <c r="BL289">
+        <v>1.52</v>
+      </c>
+      <c r="BM289">
+        <v>3.05</v>
+      </c>
+      <c r="BN289">
+        <v>1.3</v>
+      </c>
+      <c r="BO289">
+        <v>4</v>
+      </c>
+      <c r="BP289">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="290" spans="1:68">
+      <c r="A290" s="1">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>7728491</v>
+      </c>
+      <c r="C290" t="s">
+        <v>68</v>
+      </c>
+      <c r="D290" t="s">
+        <v>69</v>
+      </c>
+      <c r="E290" s="2">
+        <v>45703.60416666666</v>
+      </c>
+      <c r="F290">
+        <v>27</v>
+      </c>
+      <c r="G290" t="s">
+        <v>77</v>
+      </c>
+      <c r="H290" t="s">
+        <v>72</v>
+      </c>
+      <c r="I290">
+        <v>0</v>
+      </c>
+      <c r="J290">
+        <v>1</v>
+      </c>
+      <c r="K290">
+        <v>1</v>
+      </c>
+      <c r="L290">
+        <v>2</v>
+      </c>
+      <c r="M290">
+        <v>3</v>
+      </c>
+      <c r="N290">
+        <v>5</v>
+      </c>
+      <c r="O290" t="s">
+        <v>271</v>
+      </c>
+      <c r="P290" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q290">
+        <v>2.6</v>
+      </c>
+      <c r="R290">
+        <v>2</v>
+      </c>
+      <c r="S290">
+        <v>4.1</v>
+      </c>
+      <c r="T290">
+        <v>1.44</v>
+      </c>
+      <c r="U290">
+        <v>2.55</v>
+      </c>
+      <c r="V290">
+        <v>3.1</v>
+      </c>
+      <c r="W290">
+        <v>1.32</v>
+      </c>
+      <c r="X290">
+        <v>8.25</v>
+      </c>
+      <c r="Y290">
+        <v>1.06</v>
+      </c>
+      <c r="Z290">
+        <v>1.9</v>
+      </c>
+      <c r="AA290">
+        <v>3.67</v>
+      </c>
+      <c r="AB290">
+        <v>4.2</v>
+      </c>
+      <c r="AC290">
+        <v>1.07</v>
+      </c>
+      <c r="AD290">
+        <v>8</v>
+      </c>
+      <c r="AE290">
+        <v>1.36</v>
+      </c>
+      <c r="AF290">
+        <v>2.9</v>
+      </c>
+      <c r="AG290">
+        <v>2</v>
+      </c>
+      <c r="AH290">
+        <v>1.82</v>
+      </c>
+      <c r="AI290">
+        <v>1.93</v>
+      </c>
+      <c r="AJ290">
+        <v>1.77</v>
+      </c>
+      <c r="AK290">
+        <v>1.27</v>
+      </c>
+      <c r="AL290">
+        <v>1.3</v>
+      </c>
+      <c r="AM290">
+        <v>1.77</v>
+      </c>
+      <c r="AN290">
+        <v>1.69</v>
+      </c>
+      <c r="AO290">
+        <v>1.17</v>
+      </c>
+      <c r="AP290">
+        <v>1.57</v>
+      </c>
+      <c r="AQ290">
+        <v>1.31</v>
+      </c>
+      <c r="AR290">
+        <v>1.62</v>
+      </c>
+      <c r="AS290">
+        <v>1.22</v>
+      </c>
+      <c r="AT290">
+        <v>2.84</v>
+      </c>
+      <c r="AU290">
+        <v>6</v>
+      </c>
+      <c r="AV290">
+        <v>11</v>
+      </c>
+      <c r="AW290">
+        <v>6</v>
+      </c>
+      <c r="AX290">
+        <v>9</v>
+      </c>
+      <c r="AY290">
+        <v>17</v>
+      </c>
+      <c r="AZ290">
+        <v>24</v>
+      </c>
+      <c r="BA290">
+        <v>5</v>
+      </c>
+      <c r="BB290">
+        <v>3</v>
+      </c>
+      <c r="BC290">
+        <v>8</v>
+      </c>
+      <c r="BD290">
+        <v>1.58</v>
+      </c>
+      <c r="BE290">
+        <v>6.75</v>
+      </c>
+      <c r="BF290">
+        <v>2.65</v>
+      </c>
+      <c r="BG290">
+        <v>1.4</v>
+      </c>
+      <c r="BH290">
+        <v>2.65</v>
+      </c>
+      <c r="BI290">
+        <v>1.66</v>
+      </c>
+      <c r="BJ290">
+        <v>2.04</v>
+      </c>
+      <c r="BK290">
+        <v>2.07</v>
+      </c>
+      <c r="BL290">
+        <v>1.64</v>
+      </c>
+      <c r="BM290">
+        <v>2.65</v>
+      </c>
+      <c r="BN290">
+        <v>1.4</v>
+      </c>
+      <c r="BO290">
+        <v>3.55</v>
+      </c>
+      <c r="BP290">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="291" spans="1:68">
+      <c r="A291" s="1">
+        <v>290</v>
+      </c>
+      <c r="B291">
+        <v>7728492</v>
+      </c>
+      <c r="C291" t="s">
+        <v>68</v>
+      </c>
+      <c r="D291" t="s">
+        <v>69</v>
+      </c>
+      <c r="E291" s="2">
+        <v>45703.70833333334</v>
+      </c>
+      <c r="F291">
+        <v>27</v>
+      </c>
+      <c r="G291" t="s">
+        <v>84</v>
+      </c>
+      <c r="H291" t="s">
+        <v>88</v>
+      </c>
+      <c r="I291">
+        <v>2</v>
+      </c>
+      <c r="J291">
+        <v>2</v>
+      </c>
+      <c r="K291">
+        <v>4</v>
+      </c>
+      <c r="L291">
+        <v>2</v>
+      </c>
+      <c r="M291">
+        <v>3</v>
+      </c>
+      <c r="N291">
+        <v>5</v>
+      </c>
+      <c r="O291" t="s">
+        <v>272</v>
+      </c>
+      <c r="P291" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q291">
+        <v>2.75</v>
+      </c>
+      <c r="R291">
+        <v>1.95</v>
+      </c>
+      <c r="S291">
+        <v>4.2</v>
+      </c>
+      <c r="T291">
+        <v>1.48</v>
+      </c>
+      <c r="U291">
+        <v>2.45</v>
+      </c>
+      <c r="V291">
+        <v>3.2</v>
+      </c>
+      <c r="W291">
+        <v>1.3</v>
+      </c>
+      <c r="X291">
+        <v>9.9</v>
+      </c>
+      <c r="Y291">
+        <v>1.02</v>
+      </c>
+      <c r="Z291">
+        <v>2.43</v>
+      </c>
+      <c r="AA291">
+        <v>3.18</v>
+      </c>
+      <c r="AB291">
+        <v>3.25</v>
+      </c>
+      <c r="AC291">
+        <v>1.09</v>
+      </c>
+      <c r="AD291">
+        <v>7</v>
+      </c>
+      <c r="AE291">
+        <v>1.42</v>
+      </c>
+      <c r="AF291">
+        <v>2.8</v>
+      </c>
+      <c r="AG291">
+        <v>2.15</v>
+      </c>
+      <c r="AH291">
+        <v>1.57</v>
+      </c>
+      <c r="AI291">
+        <v>1.91</v>
+      </c>
+      <c r="AJ291">
+        <v>1.77</v>
+      </c>
+      <c r="AK291">
+        <v>1.28</v>
+      </c>
+      <c r="AL291">
+        <v>1.3</v>
+      </c>
+      <c r="AM291">
+        <v>1.67</v>
+      </c>
+      <c r="AN291">
+        <v>1.23</v>
+      </c>
+      <c r="AO291">
+        <v>0.85</v>
+      </c>
+      <c r="AP291">
+        <v>1.14</v>
+      </c>
+      <c r="AQ291">
+        <v>1</v>
+      </c>
+      <c r="AR291">
+        <v>1.32</v>
+      </c>
+      <c r="AS291">
+        <v>1.4</v>
+      </c>
+      <c r="AT291">
+        <v>2.72</v>
+      </c>
+      <c r="AU291">
+        <v>4</v>
+      </c>
+      <c r="AV291">
+        <v>8</v>
+      </c>
+      <c r="AW291">
+        <v>8</v>
+      </c>
+      <c r="AX291">
+        <v>11</v>
+      </c>
+      <c r="AY291">
+        <v>14</v>
+      </c>
+      <c r="AZ291">
+        <v>19</v>
+      </c>
+      <c r="BA291">
+        <v>3</v>
+      </c>
+      <c r="BB291">
+        <v>4</v>
+      </c>
+      <c r="BC291">
+        <v>7</v>
+      </c>
+      <c r="BD291">
+        <v>1.84</v>
+      </c>
+      <c r="BE291">
+        <v>6.4</v>
+      </c>
+      <c r="BF291">
+        <v>2.17</v>
+      </c>
+      <c r="BG291">
+        <v>1.36</v>
+      </c>
+      <c r="BH291">
+        <v>2.8</v>
+      </c>
+      <c r="BI291">
+        <v>1.61</v>
+      </c>
+      <c r="BJ291">
+        <v>2.12</v>
+      </c>
+      <c r="BK291">
+        <v>1.98</v>
+      </c>
+      <c r="BL291">
+        <v>1.7</v>
+      </c>
+      <c r="BM291">
+        <v>2.55</v>
+      </c>
+      <c r="BN291">
+        <v>1.43</v>
+      </c>
+      <c r="BO291">
+        <v>3.3</v>
+      </c>
+      <c r="BP291">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="379">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -835,6 +835,15 @@
     <t>['9', '42']</t>
   </si>
   <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['58', '65']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1027,9 +1036,6 @@
     <t>['16', '56']</t>
   </si>
   <si>
-    <t>['76']</t>
-  </si>
-  <si>
     <t>['70']</t>
   </si>
   <si>
@@ -1079,9 +1085,6 @@
   </si>
   <si>
     <t>['27', '45+1']</t>
-  </si>
-  <si>
-    <t>['43']</t>
   </si>
   <si>
     <t>['36', '40', '55', '63']</t>
@@ -1509,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP291"/>
+  <dimension ref="A1:BP296"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1765,7 +1768,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1846,7 +1849,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2177,7 +2180,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3001,7 +3004,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3207,7 +3210,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3903,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ12">
         <v>0.23</v>
@@ -4031,7 +4034,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4237,7 +4240,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4315,10 +4318,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4730,7 +4733,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ16">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR16">
         <v>1.33</v>
@@ -4933,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ17">
         <v>1.31</v>
@@ -5267,7 +5270,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5885,7 +5888,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6091,7 +6094,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6172,7 +6175,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ23">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6297,7 +6300,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6503,7 +6506,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6581,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ25">
         <v>2</v>
@@ -6709,7 +6712,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6915,7 +6918,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6996,7 +6999,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR27">
         <v>1.25</v>
@@ -7327,7 +7330,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7945,7 +7948,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8023,7 +8026,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ32">
         <v>0.5</v>
@@ -8151,7 +8154,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8563,7 +8566,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8850,7 +8853,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ36">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR36">
         <v>2.09</v>
@@ -9053,10 +9056,10 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR37">
         <v>1.35</v>
@@ -10083,7 +10086,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ42">
         <v>1.5</v>
@@ -10289,7 +10292,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ43">
         <v>1.17</v>
@@ -10417,7 +10420,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10910,7 +10913,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ46">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -11035,7 +11038,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11113,7 +11116,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ47">
         <v>0.77</v>
@@ -11940,7 +11943,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR51">
         <v>0.76</v>
@@ -12143,7 +12146,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ52">
         <v>0.5</v>
@@ -12683,7 +12686,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12764,7 +12767,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ55">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR55">
         <v>1.39</v>
@@ -12889,7 +12892,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13095,7 +13098,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13301,7 +13304,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13382,7 +13385,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR58">
         <v>1.22</v>
@@ -13585,7 +13588,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ59">
         <v>1.38</v>
@@ -13713,7 +13716,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13794,7 +13797,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ60">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -13997,7 +14000,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ61">
         <v>1.43</v>
@@ -14331,7 +14334,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14949,7 +14952,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15233,7 +15236,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -15361,7 +15364,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15442,7 +15445,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ68">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR68">
         <v>1.07</v>
@@ -15567,7 +15570,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16185,7 +16188,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16391,7 +16394,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16469,7 +16472,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ73">
         <v>1.5</v>
@@ -16597,7 +16600,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16678,7 +16681,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ74">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR74">
         <v>1.54</v>
@@ -17293,7 +17296,7 @@
         <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ77">
         <v>0.64</v>
@@ -17421,7 +17424,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17627,7 +17630,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17705,7 +17708,7 @@
         <v>2.33</v>
       </c>
       <c r="AP79">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>1.31</v>
@@ -18039,7 +18042,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18120,7 +18123,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR81">
         <v>1.07</v>
@@ -18245,7 +18248,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18451,7 +18454,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18529,7 +18532,7 @@
         <v>3</v>
       </c>
       <c r="AP83">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ83">
         <v>2</v>
@@ -18738,7 +18741,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ84">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR84">
         <v>1.79</v>
@@ -19275,7 +19278,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19353,7 +19356,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ87">
         <v>1.38</v>
@@ -19559,7 +19562,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ88">
         <v>1.38</v>
@@ -19687,7 +19690,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19893,7 +19896,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20305,7 +20308,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20717,7 +20720,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20795,10 +20798,10 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR94">
         <v>1.16</v>
@@ -20923,7 +20926,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21001,7 +21004,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ95">
         <v>1.5</v>
@@ -21828,7 +21831,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ99">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR99">
         <v>1.46</v>
@@ -21953,7 +21956,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23395,7 +23398,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24013,7 +24016,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24091,7 +24094,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ110">
         <v>1.5</v>
@@ -24300,7 +24303,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ111">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR111">
         <v>1.54</v>
@@ -24425,7 +24428,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24503,7 +24506,7 @@
         <v>1.25</v>
       </c>
       <c r="AP112">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ112">
         <v>1.15</v>
@@ -24631,7 +24634,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24712,7 +24715,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ113">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -25043,7 +25046,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25121,7 +25124,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ115">
         <v>1.36</v>
@@ -25742,7 +25745,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR118">
         <v>1.69</v>
@@ -25867,7 +25870,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -25945,10 +25948,10 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ119">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR119">
         <v>1.68</v>
@@ -26485,7 +26488,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26897,7 +26900,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27309,7 +27312,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27387,7 +27390,7 @@
         <v>1.8</v>
       </c>
       <c r="AP126">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ126">
         <v>1.38</v>
@@ -27721,7 +27724,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28008,7 +28011,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ129">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -28133,7 +28136,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28339,7 +28342,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28417,7 +28420,7 @@
         <v>1.17</v>
       </c>
       <c r="AP131">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
         <v>1.5</v>
@@ -28545,7 +28548,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28957,7 +28960,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29163,7 +29166,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29244,7 +29247,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ135">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR135">
         <v>1.12</v>
@@ -29653,10 +29656,10 @@
         <v>2.2</v>
       </c>
       <c r="AP137">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ137">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR137">
         <v>1.67</v>
@@ -29781,7 +29784,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29862,7 +29865,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR138">
         <v>1.52</v>
@@ -30065,10 +30068,10 @@
         <v>1.17</v>
       </c>
       <c r="AP139">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ139">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR139">
         <v>1.66</v>
@@ -30399,7 +30402,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30605,7 +30608,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30811,7 +30814,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30889,7 +30892,7 @@
         <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ143">
         <v>1.36</v>
@@ -31017,7 +31020,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31429,7 +31432,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31841,7 +31844,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32743,10 +32746,10 @@
         <v>1.14</v>
       </c>
       <c r="AP152">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ152">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR152">
         <v>1.54</v>
@@ -32871,7 +32874,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33155,7 +33158,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ154">
         <v>1.17</v>
@@ -33364,7 +33367,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ155">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR155">
         <v>1.59</v>
@@ -33489,7 +33492,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33570,7 +33573,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ156">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR156">
         <v>1.44</v>
@@ -33979,7 +33982,7 @@
         <v>0.33</v>
       </c>
       <c r="AP158">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ158">
         <v>0.23</v>
@@ -34188,7 +34191,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ159">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR159">
         <v>1.75</v>
@@ -34597,7 +34600,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ161">
         <v>1</v>
@@ -34803,7 +34806,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ162">
         <v>1.5</v>
@@ -35137,7 +35140,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35755,7 +35758,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36167,7 +36170,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>337</v>
+        <v>273</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36785,7 +36788,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -36863,7 +36866,7 @@
         <v>1.86</v>
       </c>
       <c r="AP172">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ172">
         <v>1.38</v>
@@ -37403,7 +37406,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37481,7 +37484,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ175">
         <v>1</v>
@@ -37815,7 +37818,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -37893,7 +37896,7 @@
         <v>0.88</v>
       </c>
       <c r="AP177">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ177">
         <v>1.5</v>
@@ -38099,10 +38102,10 @@
         <v>1</v>
       </c>
       <c r="AP178">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ178">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR178">
         <v>1.71</v>
@@ -38227,7 +38230,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38308,7 +38311,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ179">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR179">
         <v>1.71</v>
@@ -38433,7 +38436,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38514,7 +38517,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ180">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR180">
         <v>1.48</v>
@@ -39257,7 +39260,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39335,10 +39338,10 @@
         <v>0.88</v>
       </c>
       <c r="AP184">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ184">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR184">
         <v>1.69</v>
@@ -39541,7 +39544,7 @@
         <v>0.86</v>
       </c>
       <c r="AP185">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -40081,7 +40084,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40699,7 +40702,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40905,7 +40908,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -40983,7 +40986,7 @@
         <v>0.63</v>
       </c>
       <c r="AP192">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ192">
         <v>0.64</v>
@@ -41111,7 +41114,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41317,7 +41320,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42553,7 +42556,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42631,7 +42634,7 @@
         <v>0.11</v>
       </c>
       <c r="AP200">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ200">
         <v>1</v>
@@ -42840,7 +42843,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ201">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR201">
         <v>1.46</v>
@@ -42965,7 +42968,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43171,7 +43174,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43455,7 +43458,7 @@
         <v>1.13</v>
       </c>
       <c r="AP204">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ204">
         <v>1.17</v>
@@ -43661,10 +43664,10 @@
         <v>1.75</v>
       </c>
       <c r="AP205">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ205">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR205">
         <v>1.69</v>
@@ -43789,7 +43792,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44819,7 +44822,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45025,7 +45028,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45103,7 +45106,7 @@
         <v>1.1</v>
       </c>
       <c r="AP212">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ212">
         <v>1.38</v>
@@ -45231,7 +45234,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45437,7 +45440,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45849,7 +45852,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -45930,7 +45933,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ216">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR216">
         <v>1.46</v>
@@ -46545,7 +46548,7 @@
         <v>0.22</v>
       </c>
       <c r="AP219">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ219">
         <v>0.23</v>
@@ -46754,7 +46757,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ220">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR220">
         <v>1.23</v>
@@ -46960,7 +46963,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ221">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR221">
         <v>1.48</v>
@@ -47085,7 +47088,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47163,7 +47166,7 @@
         <v>0.2</v>
       </c>
       <c r="AP222">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ222">
         <v>1</v>
@@ -47369,7 +47372,7 @@
         <v>1.11</v>
       </c>
       <c r="AP223">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ223">
         <v>1</v>
@@ -47497,7 +47500,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47909,7 +47912,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48115,7 +48118,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>355</v>
+        <v>275</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48527,7 +48530,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48733,7 +48736,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48811,7 +48814,7 @@
         <v>1.3</v>
       </c>
       <c r="AP230">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ230">
         <v>1.5</v>
@@ -48939,7 +48942,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49226,7 +49229,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ232">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR232">
         <v>1.73</v>
@@ -49635,7 +49638,7 @@
         <v>1.4</v>
       </c>
       <c r="AP234">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ234">
         <v>1.15</v>
@@ -49763,7 +49766,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50256,7 +50259,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ237">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR237">
         <v>1.37</v>
@@ -50459,7 +50462,7 @@
         <v>1.1</v>
       </c>
       <c r="AP238">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ238">
         <v>1</v>
@@ -50587,7 +50590,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51205,7 +51208,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51283,7 +51286,7 @@
         <v>0.5</v>
       </c>
       <c r="AP242">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ242">
         <v>0.64</v>
@@ -51617,7 +51620,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51695,7 +51698,7 @@
         <v>1</v>
       </c>
       <c r="AP244">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ244">
         <v>1.31</v>
@@ -51823,7 +51826,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -52110,7 +52113,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ246">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR246">
         <v>1.49</v>
@@ -52313,10 +52316,10 @@
         <v>1.5</v>
       </c>
       <c r="AP247">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ247">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR247">
         <v>1.54</v>
@@ -52522,7 +52525,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ248">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR248">
         <v>1.41</v>
@@ -52853,7 +52856,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53059,7 +53062,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53137,7 +53140,7 @@
         <v>0.18</v>
       </c>
       <c r="AP251">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ251">
         <v>0.23</v>
@@ -53471,7 +53474,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53883,7 +53886,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54089,7 +54092,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54373,7 +54376,7 @@
         <v>0.58</v>
       </c>
       <c r="AP257">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ257">
         <v>0.5</v>
@@ -54501,7 +54504,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -54991,7 +54994,7 @@
         <v>1.36</v>
       </c>
       <c r="AP260">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ260">
         <v>1.38</v>
@@ -55119,7 +55122,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55325,7 +55328,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55818,7 +55821,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ264">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR264">
         <v>1.24</v>
@@ -55943,7 +55946,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56021,10 +56024,10 @@
         <v>1.36</v>
       </c>
       <c r="AP265">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ265">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR265">
         <v>1.45</v>
@@ -56436,7 +56439,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ267">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR267">
         <v>1.55</v>
@@ -56767,7 +56770,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57260,7 +57263,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ271">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR271">
         <v>1.48</v>
@@ -57463,7 +57466,7 @@
         <v>1.18</v>
       </c>
       <c r="AP272">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ272">
         <v>1.31</v>
@@ -57591,7 +57594,7 @@
         <v>94</v>
       </c>
       <c r="P273" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q273">
         <v>4</v>
@@ -57878,7 +57881,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ274">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR274">
         <v>1.29</v>
@@ -58081,7 +58084,7 @@
         <v>0.91</v>
       </c>
       <c r="AP275">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ275">
         <v>1</v>
@@ -58415,7 +58418,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59445,7 +59448,7 @@
         <v>186</v>
       </c>
       <c r="P282" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59857,7 +59860,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60347,7 +60350,7 @@
         <v>0.75</v>
       </c>
       <c r="AP286">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ286">
         <v>0.77</v>
@@ -60475,7 +60478,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61093,7 +61096,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61299,7 +61302,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61456,6 +61459,1036 @@
       </c>
       <c r="BP291">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="292" spans="1:68">
+      <c r="A292" s="1">
+        <v>291</v>
+      </c>
+      <c r="B292">
+        <v>7728488</v>
+      </c>
+      <c r="C292" t="s">
+        <v>68</v>
+      </c>
+      <c r="D292" t="s">
+        <v>69</v>
+      </c>
+      <c r="E292" s="2">
+        <v>45704.41666666666</v>
+      </c>
+      <c r="F292">
+        <v>27</v>
+      </c>
+      <c r="G292" t="s">
+        <v>82</v>
+      </c>
+      <c r="H292" t="s">
+        <v>76</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>0</v>
+      </c>
+      <c r="L292">
+        <v>0</v>
+      </c>
+      <c r="M292">
+        <v>0</v>
+      </c>
+      <c r="N292">
+        <v>0</v>
+      </c>
+      <c r="O292" t="s">
+        <v>94</v>
+      </c>
+      <c r="P292" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q292">
+        <v>2.7</v>
+      </c>
+      <c r="R292">
+        <v>2</v>
+      </c>
+      <c r="S292">
+        <v>3.9</v>
+      </c>
+      <c r="T292">
+        <v>1.44</v>
+      </c>
+      <c r="U292">
+        <v>2.55</v>
+      </c>
+      <c r="V292">
+        <v>3</v>
+      </c>
+      <c r="W292">
+        <v>1.33</v>
+      </c>
+      <c r="X292">
+        <v>8.25</v>
+      </c>
+      <c r="Y292">
+        <v>1.06</v>
+      </c>
+      <c r="Z292">
+        <v>2.08</v>
+      </c>
+      <c r="AA292">
+        <v>3.45</v>
+      </c>
+      <c r="AB292">
+        <v>3.8</v>
+      </c>
+      <c r="AC292">
+        <v>1.08</v>
+      </c>
+      <c r="AD292">
+        <v>7.5</v>
+      </c>
+      <c r="AE292">
+        <v>1.39</v>
+      </c>
+      <c r="AF292">
+        <v>2.75</v>
+      </c>
+      <c r="AG292">
+        <v>1.95</v>
+      </c>
+      <c r="AH292">
+        <v>1.7</v>
+      </c>
+      <c r="AI292">
+        <v>1.93</v>
+      </c>
+      <c r="AJ292">
+        <v>1.77</v>
+      </c>
+      <c r="AK292">
+        <v>1.3</v>
+      </c>
+      <c r="AL292">
+        <v>1.31</v>
+      </c>
+      <c r="AM292">
+        <v>1.68</v>
+      </c>
+      <c r="AN292">
+        <v>1.92</v>
+      </c>
+      <c r="AO292">
+        <v>1</v>
+      </c>
+      <c r="AP292">
+        <v>1.85</v>
+      </c>
+      <c r="AQ292">
+        <v>1</v>
+      </c>
+      <c r="AR292">
+        <v>1.67</v>
+      </c>
+      <c r="AS292">
+        <v>1.18</v>
+      </c>
+      <c r="AT292">
+        <v>2.85</v>
+      </c>
+      <c r="AU292">
+        <v>7</v>
+      </c>
+      <c r="AV292">
+        <v>3</v>
+      </c>
+      <c r="AW292">
+        <v>7</v>
+      </c>
+      <c r="AX292">
+        <v>4</v>
+      </c>
+      <c r="AY292">
+        <v>16</v>
+      </c>
+      <c r="AZ292">
+        <v>8</v>
+      </c>
+      <c r="BA292">
+        <v>8</v>
+      </c>
+      <c r="BB292">
+        <v>2</v>
+      </c>
+      <c r="BC292">
+        <v>10</v>
+      </c>
+      <c r="BD292">
+        <v>1.64</v>
+      </c>
+      <c r="BE292">
+        <v>6.5</v>
+      </c>
+      <c r="BF292">
+        <v>2.55</v>
+      </c>
+      <c r="BG292">
+        <v>1.38</v>
+      </c>
+      <c r="BH292">
+        <v>2.7</v>
+      </c>
+      <c r="BI292">
+        <v>1.64</v>
+      </c>
+      <c r="BJ292">
+        <v>2.06</v>
+      </c>
+      <c r="BK292">
+        <v>2.04</v>
+      </c>
+      <c r="BL292">
+        <v>1.66</v>
+      </c>
+      <c r="BM292">
+        <v>2.6</v>
+      </c>
+      <c r="BN292">
+        <v>1.41</v>
+      </c>
+      <c r="BO292">
+        <v>3.4</v>
+      </c>
+      <c r="BP292">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="293" spans="1:68">
+      <c r="A293" s="1">
+        <v>292</v>
+      </c>
+      <c r="B293">
+        <v>7728494</v>
+      </c>
+      <c r="C293" t="s">
+        <v>68</v>
+      </c>
+      <c r="D293" t="s">
+        <v>69</v>
+      </c>
+      <c r="E293" s="2">
+        <v>45704.51041666666</v>
+      </c>
+      <c r="F293">
+        <v>27</v>
+      </c>
+      <c r="G293" t="s">
+        <v>81</v>
+      </c>
+      <c r="H293" t="s">
+        <v>70</v>
+      </c>
+      <c r="I293">
+        <v>0</v>
+      </c>
+      <c r="J293">
+        <v>0</v>
+      </c>
+      <c r="K293">
+        <v>0</v>
+      </c>
+      <c r="L293">
+        <v>1</v>
+      </c>
+      <c r="M293">
+        <v>1</v>
+      </c>
+      <c r="N293">
+        <v>2</v>
+      </c>
+      <c r="O293" t="s">
+        <v>273</v>
+      </c>
+      <c r="P293" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q293">
+        <v>3.3</v>
+      </c>
+      <c r="R293">
+        <v>1.93</v>
+      </c>
+      <c r="S293">
+        <v>3.9</v>
+      </c>
+      <c r="T293">
+        <v>1.58</v>
+      </c>
+      <c r="U293">
+        <v>2.26</v>
+      </c>
+      <c r="V293">
+        <v>3.55</v>
+      </c>
+      <c r="W293">
+        <v>1.26</v>
+      </c>
+      <c r="X293">
+        <v>9</v>
+      </c>
+      <c r="Y293">
+        <v>1.01</v>
+      </c>
+      <c r="Z293">
+        <v>2.66</v>
+      </c>
+      <c r="AA293">
+        <v>2.9</v>
+      </c>
+      <c r="AB293">
+        <v>3.18</v>
+      </c>
+      <c r="AC293">
+        <v>1.11</v>
+      </c>
+      <c r="AD293">
+        <v>6.4</v>
+      </c>
+      <c r="AE293">
+        <v>1.48</v>
+      </c>
+      <c r="AF293">
+        <v>2.37</v>
+      </c>
+      <c r="AG293">
+        <v>2.44</v>
+      </c>
+      <c r="AH293">
+        <v>1.49</v>
+      </c>
+      <c r="AI293">
+        <v>2.07</v>
+      </c>
+      <c r="AJ293">
+        <v>1.68</v>
+      </c>
+      <c r="AK293">
+        <v>1.36</v>
+      </c>
+      <c r="AL293">
+        <v>1.37</v>
+      </c>
+      <c r="AM293">
+        <v>1.49</v>
+      </c>
+      <c r="AN293">
+        <v>2.08</v>
+      </c>
+      <c r="AO293">
+        <v>1.5</v>
+      </c>
+      <c r="AP293">
+        <v>2</v>
+      </c>
+      <c r="AQ293">
+        <v>1.46</v>
+      </c>
+      <c r="AR293">
+        <v>1.27</v>
+      </c>
+      <c r="AS293">
+        <v>1.17</v>
+      </c>
+      <c r="AT293">
+        <v>2.44</v>
+      </c>
+      <c r="AU293">
+        <v>4</v>
+      </c>
+      <c r="AV293">
+        <v>2</v>
+      </c>
+      <c r="AW293">
+        <v>7</v>
+      </c>
+      <c r="AX293">
+        <v>6</v>
+      </c>
+      <c r="AY293">
+        <v>13</v>
+      </c>
+      <c r="AZ293">
+        <v>8</v>
+      </c>
+      <c r="BA293">
+        <v>3</v>
+      </c>
+      <c r="BB293">
+        <v>7</v>
+      </c>
+      <c r="BC293">
+        <v>10</v>
+      </c>
+      <c r="BD293">
+        <v>1.74</v>
+      </c>
+      <c r="BE293">
+        <v>6.4</v>
+      </c>
+      <c r="BF293">
+        <v>2.32</v>
+      </c>
+      <c r="BG293">
+        <v>1.43</v>
+      </c>
+      <c r="BH293">
+        <v>2.55</v>
+      </c>
+      <c r="BI293">
+        <v>1.74</v>
+      </c>
+      <c r="BJ293">
+        <v>1.93</v>
+      </c>
+      <c r="BK293">
+        <v>2.2</v>
+      </c>
+      <c r="BL293">
+        <v>1.56</v>
+      </c>
+      <c r="BM293">
+        <v>2.9</v>
+      </c>
+      <c r="BN293">
+        <v>1.34</v>
+      </c>
+      <c r="BO293">
+        <v>3.9</v>
+      </c>
+      <c r="BP293">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="294" spans="1:68">
+      <c r="A294" s="1">
+        <v>293</v>
+      </c>
+      <c r="B294">
+        <v>7728843</v>
+      </c>
+      <c r="C294" t="s">
+        <v>68</v>
+      </c>
+      <c r="D294" t="s">
+        <v>69</v>
+      </c>
+      <c r="E294" s="2">
+        <v>45704.51041666666</v>
+      </c>
+      <c r="F294">
+        <v>27</v>
+      </c>
+      <c r="G294" t="s">
+        <v>80</v>
+      </c>
+      <c r="H294" t="s">
+        <v>75</v>
+      </c>
+      <c r="I294">
+        <v>0</v>
+      </c>
+      <c r="J294">
+        <v>0</v>
+      </c>
+      <c r="K294">
+        <v>0</v>
+      </c>
+      <c r="L294">
+        <v>2</v>
+      </c>
+      <c r="M294">
+        <v>0</v>
+      </c>
+      <c r="N294">
+        <v>2</v>
+      </c>
+      <c r="O294" t="s">
+        <v>274</v>
+      </c>
+      <c r="P294" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q294">
+        <v>3.2</v>
+      </c>
+      <c r="R294">
+        <v>1.93</v>
+      </c>
+      <c r="S294">
+        <v>3.4</v>
+      </c>
+      <c r="T294">
+        <v>1.49</v>
+      </c>
+      <c r="U294">
+        <v>2.4</v>
+      </c>
+      <c r="V294">
+        <v>3.2</v>
+      </c>
+      <c r="W294">
+        <v>1.3</v>
+      </c>
+      <c r="X294">
+        <v>8.75</v>
+      </c>
+      <c r="Y294">
+        <v>1.06</v>
+      </c>
+      <c r="Z294">
+        <v>2.56</v>
+      </c>
+      <c r="AA294">
+        <v>3.28</v>
+      </c>
+      <c r="AB294">
+        <v>2.95</v>
+      </c>
+      <c r="AC294">
+        <v>1.09</v>
+      </c>
+      <c r="AD294">
+        <v>7</v>
+      </c>
+      <c r="AE294">
+        <v>1.44</v>
+      </c>
+      <c r="AF294">
+        <v>2.55</v>
+      </c>
+      <c r="AG294">
+        <v>1.95</v>
+      </c>
+      <c r="AH294">
+        <v>1.7</v>
+      </c>
+      <c r="AI294">
+        <v>1.95</v>
+      </c>
+      <c r="AJ294">
+        <v>1.75</v>
+      </c>
+      <c r="AK294">
+        <v>1.4</v>
+      </c>
+      <c r="AL294">
+        <v>1.36</v>
+      </c>
+      <c r="AM294">
+        <v>1.47</v>
+      </c>
+      <c r="AN294">
+        <v>1.15</v>
+      </c>
+      <c r="AO294">
+        <v>1.46</v>
+      </c>
+      <c r="AP294">
+        <v>1.29</v>
+      </c>
+      <c r="AQ294">
+        <v>1.36</v>
+      </c>
+      <c r="AR294">
+        <v>1.47</v>
+      </c>
+      <c r="AS294">
+        <v>1.32</v>
+      </c>
+      <c r="AT294">
+        <v>2.79</v>
+      </c>
+      <c r="AU294">
+        <v>8</v>
+      </c>
+      <c r="AV294">
+        <v>3</v>
+      </c>
+      <c r="AW294">
+        <v>13</v>
+      </c>
+      <c r="AX294">
+        <v>7</v>
+      </c>
+      <c r="AY294">
+        <v>25</v>
+      </c>
+      <c r="AZ294">
+        <v>12</v>
+      </c>
+      <c r="BA294">
+        <v>8</v>
+      </c>
+      <c r="BB294">
+        <v>1</v>
+      </c>
+      <c r="BC294">
+        <v>9</v>
+      </c>
+      <c r="BD294">
+        <v>1.72</v>
+      </c>
+      <c r="BE294">
+        <v>6.75</v>
+      </c>
+      <c r="BF294">
+        <v>2.33</v>
+      </c>
+      <c r="BG294">
+        <v>1.3</v>
+      </c>
+      <c r="BH294">
+        <v>3.05</v>
+      </c>
+      <c r="BI294">
+        <v>1.54</v>
+      </c>
+      <c r="BJ294">
+        <v>2.25</v>
+      </c>
+      <c r="BK294">
+        <v>1.87</v>
+      </c>
+      <c r="BL294">
+        <v>1.79</v>
+      </c>
+      <c r="BM294">
+        <v>2.35</v>
+      </c>
+      <c r="BN294">
+        <v>1.5</v>
+      </c>
+      <c r="BO294">
+        <v>3.05</v>
+      </c>
+      <c r="BP294">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:68">
+      <c r="A295" s="1">
+        <v>294</v>
+      </c>
+      <c r="B295">
+        <v>7728490</v>
+      </c>
+      <c r="C295" t="s">
+        <v>68</v>
+      </c>
+      <c r="D295" t="s">
+        <v>69</v>
+      </c>
+      <c r="E295" s="2">
+        <v>45704.60416666666</v>
+      </c>
+      <c r="F295">
+        <v>27</v>
+      </c>
+      <c r="G295" t="s">
+        <v>91</v>
+      </c>
+      <c r="H295" t="s">
+        <v>78</v>
+      </c>
+      <c r="I295">
+        <v>0</v>
+      </c>
+      <c r="J295">
+        <v>0</v>
+      </c>
+      <c r="K295">
+        <v>0</v>
+      </c>
+      <c r="L295">
+        <v>0</v>
+      </c>
+      <c r="M295">
+        <v>1</v>
+      </c>
+      <c r="N295">
+        <v>1</v>
+      </c>
+      <c r="O295" t="s">
+        <v>94</v>
+      </c>
+      <c r="P295" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q295">
+        <v>2.8</v>
+      </c>
+      <c r="R295">
+        <v>1.93</v>
+      </c>
+      <c r="S295">
+        <v>4.8</v>
+      </c>
+      <c r="T295">
+        <v>1.59</v>
+      </c>
+      <c r="U295">
+        <v>2.24</v>
+      </c>
+      <c r="V295">
+        <v>3.6</v>
+      </c>
+      <c r="W295">
+        <v>1.25</v>
+      </c>
+      <c r="X295">
+        <v>10.75</v>
+      </c>
+      <c r="Y295">
+        <v>1.01</v>
+      </c>
+      <c r="Z295">
+        <v>2.17</v>
+      </c>
+      <c r="AA295">
+        <v>3.11</v>
+      </c>
+      <c r="AB295">
+        <v>3.97</v>
+      </c>
+      <c r="AC295">
+        <v>1.11</v>
+      </c>
+      <c r="AD295">
+        <v>6.2</v>
+      </c>
+      <c r="AE295">
+        <v>1.5</v>
+      </c>
+      <c r="AF295">
+        <v>2.3</v>
+      </c>
+      <c r="AG295">
+        <v>2.5</v>
+      </c>
+      <c r="AH295">
+        <v>1.53</v>
+      </c>
+      <c r="AI295">
+        <v>2.19</v>
+      </c>
+      <c r="AJ295">
+        <v>1.61</v>
+      </c>
+      <c r="AK295">
+        <v>1.25</v>
+      </c>
+      <c r="AL295">
+        <v>1.34</v>
+      </c>
+      <c r="AM295">
+        <v>1.69</v>
+      </c>
+      <c r="AN295">
+        <v>1.25</v>
+      </c>
+      <c r="AO295">
+        <v>0.75</v>
+      </c>
+      <c r="AP295">
+        <v>1.15</v>
+      </c>
+      <c r="AQ295">
+        <v>0.92</v>
+      </c>
+      <c r="AR295">
+        <v>1.6</v>
+      </c>
+      <c r="AS295">
+        <v>1.19</v>
+      </c>
+      <c r="AT295">
+        <v>2.79</v>
+      </c>
+      <c r="AU295">
+        <v>3</v>
+      </c>
+      <c r="AV295">
+        <v>4</v>
+      </c>
+      <c r="AW295">
+        <v>4</v>
+      </c>
+      <c r="AX295">
+        <v>7</v>
+      </c>
+      <c r="AY295">
+        <v>7</v>
+      </c>
+      <c r="AZ295">
+        <v>13</v>
+      </c>
+      <c r="BA295">
+        <v>2</v>
+      </c>
+      <c r="BB295">
+        <v>3</v>
+      </c>
+      <c r="BC295">
+        <v>5</v>
+      </c>
+      <c r="BD295">
+        <v>1.63</v>
+      </c>
+      <c r="BE295">
+        <v>6.75</v>
+      </c>
+      <c r="BF295">
+        <v>2.55</v>
+      </c>
+      <c r="BG295">
+        <v>1.4</v>
+      </c>
+      <c r="BH295">
+        <v>2.65</v>
+      </c>
+      <c r="BI295">
+        <v>1.66</v>
+      </c>
+      <c r="BJ295">
+        <v>2.04</v>
+      </c>
+      <c r="BK295">
+        <v>2.06</v>
+      </c>
+      <c r="BL295">
+        <v>1.64</v>
+      </c>
+      <c r="BM295">
+        <v>2.65</v>
+      </c>
+      <c r="BN295">
+        <v>1.4</v>
+      </c>
+      <c r="BO295">
+        <v>3.45</v>
+      </c>
+      <c r="BP295">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="296" spans="1:68">
+      <c r="A296" s="1">
+        <v>295</v>
+      </c>
+      <c r="B296">
+        <v>7728489</v>
+      </c>
+      <c r="C296" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296" t="s">
+        <v>69</v>
+      </c>
+      <c r="E296" s="2">
+        <v>45704.70833333334</v>
+      </c>
+      <c r="F296">
+        <v>27</v>
+      </c>
+      <c r="G296" t="s">
+        <v>89</v>
+      </c>
+      <c r="H296" t="s">
+        <v>85</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296">
+        <v>1</v>
+      </c>
+      <c r="L296">
+        <v>1</v>
+      </c>
+      <c r="M296">
+        <v>0</v>
+      </c>
+      <c r="N296">
+        <v>1</v>
+      </c>
+      <c r="O296" t="s">
+        <v>275</v>
+      </c>
+      <c r="P296" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q296">
+        <v>2.25</v>
+      </c>
+      <c r="R296">
+        <v>2.1</v>
+      </c>
+      <c r="S296">
+        <v>5</v>
+      </c>
+      <c r="T296">
+        <v>1.42</v>
+      </c>
+      <c r="U296">
+        <v>2.65</v>
+      </c>
+      <c r="V296">
+        <v>2.88</v>
+      </c>
+      <c r="W296">
+        <v>1.36</v>
+      </c>
+      <c r="X296">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y296">
+        <v>1.01</v>
+      </c>
+      <c r="Z296">
+        <v>1.89</v>
+      </c>
+      <c r="AA296">
+        <v>3.52</v>
+      </c>
+      <c r="AB296">
+        <v>4.5</v>
+      </c>
+      <c r="AC296">
+        <v>1.07</v>
+      </c>
+      <c r="AD296">
+        <v>8</v>
+      </c>
+      <c r="AE296">
+        <v>1.36</v>
+      </c>
+      <c r="AF296">
+        <v>3.1</v>
+      </c>
+      <c r="AG296">
+        <v>2.01</v>
+      </c>
+      <c r="AH296">
+        <v>1.81</v>
+      </c>
+      <c r="AI296">
+        <v>1.93</v>
+      </c>
+      <c r="AJ296">
+        <v>1.75</v>
+      </c>
+      <c r="AK296">
+        <v>1.17</v>
+      </c>
+      <c r="AL296">
+        <v>1.25</v>
+      </c>
+      <c r="AM296">
+        <v>2.05</v>
+      </c>
+      <c r="AN296">
+        <v>2</v>
+      </c>
+      <c r="AO296">
+        <v>1</v>
+      </c>
+      <c r="AP296">
+        <v>2.07</v>
+      </c>
+      <c r="AQ296">
+        <v>0.93</v>
+      </c>
+      <c r="AR296">
+        <v>1.6</v>
+      </c>
+      <c r="AS296">
+        <v>1.26</v>
+      </c>
+      <c r="AT296">
+        <v>2.86</v>
+      </c>
+      <c r="AU296">
+        <v>7</v>
+      </c>
+      <c r="AV296">
+        <v>4</v>
+      </c>
+      <c r="AW296">
+        <v>13</v>
+      </c>
+      <c r="AX296">
+        <v>6</v>
+      </c>
+      <c r="AY296">
+        <v>23</v>
+      </c>
+      <c r="AZ296">
+        <v>13</v>
+      </c>
+      <c r="BA296">
+        <v>7</v>
+      </c>
+      <c r="BB296">
+        <v>2</v>
+      </c>
+      <c r="BC296">
+        <v>9</v>
+      </c>
+      <c r="BD296">
+        <v>1.5</v>
+      </c>
+      <c r="BE296">
+        <v>6.75</v>
+      </c>
+      <c r="BF296">
+        <v>2.8</v>
+      </c>
+      <c r="BG296">
+        <v>1.38</v>
+      </c>
+      <c r="BH296">
+        <v>2.7</v>
+      </c>
+      <c r="BI296">
+        <v>1.65</v>
+      </c>
+      <c r="BJ296">
+        <v>2.06</v>
+      </c>
+      <c r="BK296">
+        <v>2.04</v>
+      </c>
+      <c r="BL296">
+        <v>1.65</v>
+      </c>
+      <c r="BM296">
+        <v>2.63</v>
+      </c>
+      <c r="BN296">
+        <v>1.4</v>
+      </c>
+      <c r="BO296">
+        <v>3.4</v>
+      </c>
+      <c r="BP296">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="380">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -844,6 +844,9 @@
     <t>['43']</t>
   </si>
   <si>
+    <t>['85']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1512,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP296"/>
+  <dimension ref="A1:BP297"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1768,7 +1771,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2180,7 +2183,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3004,7 +3007,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3210,7 +3213,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4034,7 +4037,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4240,7 +4243,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -5270,7 +5273,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5557,7 +5560,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ20">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5888,7 +5891,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6094,7 +6097,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6300,7 +6303,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6506,7 +6509,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6712,7 +6715,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6918,7 +6921,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7202,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7330,7 +7333,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7948,7 +7951,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8154,7 +8157,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8566,7 +8569,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -10295,7 +10298,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ43">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR43">
         <v>0</v>
@@ -10420,7 +10423,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11038,7 +11041,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12686,7 +12689,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12892,7 +12895,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -12970,7 +12973,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ56">
         <v>1.38</v>
@@ -13098,7 +13101,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13304,7 +13307,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13716,7 +13719,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14334,7 +14337,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14952,7 +14955,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15030,7 +15033,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ66">
         <v>0.64</v>
@@ -15364,7 +15367,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15570,7 +15573,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16188,7 +16191,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16269,7 +16272,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ72">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR72">
         <v>1.35</v>
@@ -16394,7 +16397,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16600,7 +16603,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17424,7 +17427,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17630,7 +17633,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17917,7 +17920,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ80">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR80">
         <v>1.23</v>
@@ -18042,7 +18045,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18248,7 +18251,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18454,7 +18457,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18738,7 +18741,7 @@
         <v>2.33</v>
       </c>
       <c r="AP84">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ84">
         <v>0.92</v>
@@ -19278,7 +19281,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19690,7 +19693,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19896,7 +19899,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20308,7 +20311,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20720,7 +20723,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20926,7 +20929,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21956,7 +21959,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23398,7 +23401,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24016,7 +24019,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24428,7 +24431,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24634,7 +24637,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25046,7 +25049,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25539,7 +25542,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ117">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR117">
         <v>1.16</v>
@@ -25742,7 +25745,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ118">
         <v>0.93</v>
@@ -25870,7 +25873,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26488,7 +26491,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26900,7 +26903,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27312,7 +27315,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27724,7 +27727,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28136,7 +28139,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28342,7 +28345,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28548,7 +28551,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28960,7 +28963,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29041,7 +29044,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ134">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR134">
         <v>1.4</v>
@@ -29166,7 +29169,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29784,7 +29787,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30402,7 +30405,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30608,7 +30611,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30814,7 +30817,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31020,7 +31023,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31432,7 +31435,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31844,7 +31847,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32874,7 +32877,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33161,7 +33164,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ154">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR154">
         <v>1.67</v>
@@ -33492,7 +33495,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34188,7 +34191,7 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ159">
         <v>1.36</v>
@@ -35140,7 +35143,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35758,7 +35761,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36788,7 +36791,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37278,7 +37281,7 @@
         <v>0.14</v>
       </c>
       <c r="AP174">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ174">
         <v>1</v>
@@ -37406,7 +37409,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37818,7 +37821,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38230,7 +38233,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38308,7 +38311,7 @@
         <v>2</v>
       </c>
       <c r="AP179">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ179">
         <v>1.46</v>
@@ -38436,7 +38439,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38929,7 +38932,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ182">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR182">
         <v>1.26</v>
@@ -39260,7 +39263,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40084,7 +40087,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40702,7 +40705,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40908,7 +40911,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41114,7 +41117,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41320,7 +41323,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42428,7 +42431,7 @@
         <v>1.38</v>
       </c>
       <c r="AP199">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ199">
         <v>1.15</v>
@@ -42556,7 +42559,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42968,7 +42971,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43174,7 +43177,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43461,7 +43464,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ204">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR204">
         <v>1.41</v>
@@ -43792,7 +43795,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44822,7 +44825,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45028,7 +45031,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45234,7 +45237,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45440,7 +45443,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45852,7 +45855,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -47088,7 +47091,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47500,7 +47503,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47912,7 +47915,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -47993,7 +47996,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ226">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR226">
         <v>1.73</v>
@@ -48196,7 +48199,7 @@
         <v>1</v>
       </c>
       <c r="AP227">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ227">
         <v>1.31</v>
@@ -48530,7 +48533,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48736,7 +48739,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48942,7 +48945,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49766,7 +49769,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50590,7 +50593,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51208,7 +51211,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51620,7 +51623,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51826,7 +51829,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -51907,7 +51910,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ245">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR245">
         <v>1.56</v>
@@ -52856,7 +52859,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53062,7 +53065,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53346,7 +53349,7 @@
         <v>1.27</v>
       </c>
       <c r="AP252">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ252">
         <v>1.5</v>
@@ -53474,7 +53477,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53886,7 +53889,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54092,7 +54095,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54504,7 +54507,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -55122,7 +55125,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55328,7 +55331,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55946,7 +55949,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56233,7 +56236,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ266">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR266">
         <v>1.24</v>
@@ -56642,7 +56645,7 @@
         <v>1.42</v>
       </c>
       <c r="AP268">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ268">
         <v>1.38</v>
@@ -56770,7 +56773,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57594,7 +57597,7 @@
         <v>94</v>
       </c>
       <c r="P273" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q273">
         <v>4</v>
@@ -58418,7 +58421,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59448,7 +59451,7 @@
         <v>186</v>
       </c>
       <c r="P282" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59860,7 +59863,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60478,7 +60481,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61096,7 +61099,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61302,7 +61305,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -62489,6 +62492,212 @@
       </c>
       <c r="BP296">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="297" spans="1:68">
+      <c r="A297" s="1">
+        <v>296</v>
+      </c>
+      <c r="B297">
+        <v>7728485</v>
+      </c>
+      <c r="C297" t="s">
+        <v>68</v>
+      </c>
+      <c r="D297" t="s">
+        <v>69</v>
+      </c>
+      <c r="E297" s="2">
+        <v>45705.6875</v>
+      </c>
+      <c r="F297">
+        <v>27</v>
+      </c>
+      <c r="G297" t="s">
+        <v>90</v>
+      </c>
+      <c r="H297" t="s">
+        <v>79</v>
+      </c>
+      <c r="I297">
+        <v>0</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>0</v>
+      </c>
+      <c r="L297">
+        <v>1</v>
+      </c>
+      <c r="M297">
+        <v>1</v>
+      </c>
+      <c r="N297">
+        <v>2</v>
+      </c>
+      <c r="O297" t="s">
+        <v>276</v>
+      </c>
+      <c r="P297" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q297">
+        <v>2.75</v>
+      </c>
+      <c r="R297">
+        <v>2.1</v>
+      </c>
+      <c r="S297">
+        <v>4</v>
+      </c>
+      <c r="T297">
+        <v>1.44</v>
+      </c>
+      <c r="U297">
+        <v>2.63</v>
+      </c>
+      <c r="V297">
+        <v>3.25</v>
+      </c>
+      <c r="W297">
+        <v>1.33</v>
+      </c>
+      <c r="X297">
+        <v>9</v>
+      </c>
+      <c r="Y297">
+        <v>1.07</v>
+      </c>
+      <c r="Z297">
+        <v>2.18</v>
+      </c>
+      <c r="AA297">
+        <v>3.21</v>
+      </c>
+      <c r="AB297">
+        <v>3.78</v>
+      </c>
+      <c r="AC297">
+        <v>1.07</v>
+      </c>
+      <c r="AD297">
+        <v>8</v>
+      </c>
+      <c r="AE297">
+        <v>1.33</v>
+      </c>
+      <c r="AF297">
+        <v>3.05</v>
+      </c>
+      <c r="AG297">
+        <v>2.01</v>
+      </c>
+      <c r="AH297">
+        <v>1.81</v>
+      </c>
+      <c r="AI297">
+        <v>1.83</v>
+      </c>
+      <c r="AJ297">
+        <v>1.83</v>
+      </c>
+      <c r="AK297">
+        <v>1.3</v>
+      </c>
+      <c r="AL297">
+        <v>1.3</v>
+      </c>
+      <c r="AM297">
+        <v>1.67</v>
+      </c>
+      <c r="AN297">
+        <v>1.92</v>
+      </c>
+      <c r="AO297">
+        <v>1.17</v>
+      </c>
+      <c r="AP297">
+        <v>1.85</v>
+      </c>
+      <c r="AQ297">
+        <v>1.15</v>
+      </c>
+      <c r="AR297">
+        <v>1.76</v>
+      </c>
+      <c r="AS297">
+        <v>1.23</v>
+      </c>
+      <c r="AT297">
+        <v>2.99</v>
+      </c>
+      <c r="AU297">
+        <v>4</v>
+      </c>
+      <c r="AV297">
+        <v>7</v>
+      </c>
+      <c r="AW297">
+        <v>3</v>
+      </c>
+      <c r="AX297">
+        <v>5</v>
+      </c>
+      <c r="AY297">
+        <v>7</v>
+      </c>
+      <c r="AZ297">
+        <v>13</v>
+      </c>
+      <c r="BA297">
+        <v>4</v>
+      </c>
+      <c r="BB297">
+        <v>3</v>
+      </c>
+      <c r="BC297">
+        <v>7</v>
+      </c>
+      <c r="BD297">
+        <v>1.71</v>
+      </c>
+      <c r="BE297">
+        <v>6.4</v>
+      </c>
+      <c r="BF297">
+        <v>2.4</v>
+      </c>
+      <c r="BG297">
+        <v>1.43</v>
+      </c>
+      <c r="BH297">
+        <v>2.55</v>
+      </c>
+      <c r="BI297">
+        <v>1.7</v>
+      </c>
+      <c r="BJ297">
+        <v>1.98</v>
+      </c>
+      <c r="BK297">
+        <v>2.12</v>
+      </c>
+      <c r="BL297">
+        <v>1.61</v>
+      </c>
+      <c r="BM297">
+        <v>2.7</v>
+      </c>
+      <c r="BN297">
+        <v>1.38</v>
+      </c>
+      <c r="BO297">
+        <v>3.65</v>
+      </c>
+      <c r="BP297">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="381">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -847,6 +847,9 @@
     <t>['85']</t>
   </si>
   <si>
+    <t>['53']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1515,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP297"/>
+  <dimension ref="A1:BP298"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1771,7 +1774,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2183,7 +2186,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3007,7 +3010,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3213,7 +3216,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3912,7 +3915,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ12">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4037,7 +4040,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4243,7 +4246,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -5145,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ18">
         <v>1.15</v>
@@ -5273,7 +5276,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5891,7 +5894,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6097,7 +6100,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6303,7 +6306,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6509,7 +6512,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6715,7 +6718,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6796,7 +6799,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ26">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR26">
         <v>1.33</v>
@@ -6921,7 +6924,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6999,7 +7002,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ27">
         <v>0.93</v>
@@ -7333,7 +7336,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7951,7 +7954,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8157,7 +8160,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8569,7 +8572,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -10423,7 +10426,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11041,7 +11044,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11328,7 +11331,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ48">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR48">
         <v>1.67</v>
@@ -11531,7 +11534,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ49">
         <v>1.5</v>
@@ -12689,7 +12692,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12895,7 +12898,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13101,7 +13104,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13307,7 +13310,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13719,7 +13722,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14337,7 +14340,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14955,7 +14958,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15367,7 +15370,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15573,7 +15576,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16191,7 +16194,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16269,7 +16272,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ72">
         <v>1.15</v>
@@ -16397,7 +16400,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16603,7 +16606,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16890,7 +16893,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ75">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR75">
         <v>1.58</v>
@@ -17427,7 +17430,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17633,7 +17636,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18045,7 +18048,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18251,7 +18254,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18457,7 +18460,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19281,7 +19284,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19693,7 +19696,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19899,7 +19902,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20311,7 +20314,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20723,7 +20726,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20929,7 +20932,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21959,7 +21962,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22449,7 +22452,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ102">
         <v>1.38</v>
@@ -22864,7 +22867,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR104">
         <v>1.71</v>
@@ -23401,7 +23404,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24019,7 +24022,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24431,7 +24434,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24637,7 +24640,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25049,7 +25052,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25873,7 +25876,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26491,7 +26494,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26903,7 +26906,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27315,7 +27318,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27599,7 +27602,7 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ127">
         <v>0.64</v>
@@ -27727,7 +27730,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28139,7 +28142,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28345,7 +28348,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28551,7 +28554,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28838,7 +28841,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ133">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR133">
         <v>1.15</v>
@@ -28963,7 +28966,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29169,7 +29172,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29787,7 +29790,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30405,7 +30408,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30611,7 +30614,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30817,7 +30820,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31023,7 +31026,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31307,7 +31310,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ145">
         <v>0.5</v>
@@ -31435,7 +31438,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31847,7 +31850,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32877,7 +32880,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33495,7 +33498,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33988,7 +33991,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ158">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR158">
         <v>1.68</v>
@@ -35143,7 +35146,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35761,7 +35764,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36045,7 +36048,7 @@
         <v>3</v>
       </c>
       <c r="AP168">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ168">
         <v>2</v>
@@ -36254,7 +36257,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ169">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR169">
         <v>1.71</v>
@@ -36791,7 +36794,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37409,7 +37412,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37821,7 +37824,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38233,7 +38236,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38439,7 +38442,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39263,7 +39266,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40087,7 +40090,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40705,7 +40708,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40911,7 +40914,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41117,7 +41120,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41323,7 +41326,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41401,7 +41404,7 @@
         <v>1.56</v>
       </c>
       <c r="AP194">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ194">
         <v>1.5</v>
@@ -42022,7 +42025,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ197">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR197">
         <v>1.63</v>
@@ -42559,7 +42562,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42971,7 +42974,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43177,7 +43180,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43795,7 +43798,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44825,7 +44828,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45031,7 +45034,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45237,7 +45240,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45443,7 +45446,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45727,7 +45730,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP215">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ215">
         <v>0.77</v>
@@ -45855,7 +45858,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46554,7 +46557,7 @@
         <v>2</v>
       </c>
       <c r="AQ219">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR219">
         <v>1.15</v>
@@ -47091,7 +47094,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47503,7 +47506,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47790,7 +47793,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ225">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR225">
         <v>1.43</v>
@@ -47915,7 +47918,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48533,7 +48536,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48739,7 +48742,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48945,7 +48948,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49769,7 +49772,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50259,7 +50262,7 @@
         <v>1.22</v>
       </c>
       <c r="AP237">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ237">
         <v>1.36</v>
@@ -50593,7 +50596,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51211,7 +51214,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51623,7 +51626,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51829,7 +51832,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -52859,7 +52862,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53065,7 +53068,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53146,7 +53149,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ251">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR251">
         <v>1.68</v>
@@ -53477,7 +53480,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53889,7 +53892,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54095,7 +54098,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54507,7 +54510,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -55125,7 +55128,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55331,7 +55334,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55409,7 +55412,7 @@
         <v>1.33</v>
       </c>
       <c r="AP262">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ262">
         <v>1.36</v>
@@ -55949,7 +55952,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56773,7 +56776,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57597,7 +57600,7 @@
         <v>94</v>
       </c>
       <c r="P273" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q273">
         <v>4</v>
@@ -58421,7 +58424,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58911,7 +58914,7 @@
         <v>1.46</v>
       </c>
       <c r="AP279">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ279">
         <v>1.43</v>
@@ -59326,7 +59329,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ281">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR281">
         <v>1.65</v>
@@ -59451,7 +59454,7 @@
         <v>186</v>
       </c>
       <c r="P282" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59863,7 +59866,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60481,7 +60484,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61099,7 +61102,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61305,7 +61308,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -62698,6 +62701,212 @@
       </c>
       <c r="BP297">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="298" spans="1:68">
+      <c r="A298" s="1">
+        <v>297</v>
+      </c>
+      <c r="B298">
+        <v>7728501</v>
+      </c>
+      <c r="C298" t="s">
+        <v>68</v>
+      </c>
+      <c r="D298" t="s">
+        <v>69</v>
+      </c>
+      <c r="E298" s="2">
+        <v>45709.6875</v>
+      </c>
+      <c r="F298">
+        <v>28</v>
+      </c>
+      <c r="G298" t="s">
+        <v>83</v>
+      </c>
+      <c r="H298" t="s">
+        <v>84</v>
+      </c>
+      <c r="I298">
+        <v>0</v>
+      </c>
+      <c r="J298">
+        <v>0</v>
+      </c>
+      <c r="K298">
+        <v>0</v>
+      </c>
+      <c r="L298">
+        <v>1</v>
+      </c>
+      <c r="M298">
+        <v>0</v>
+      </c>
+      <c r="N298">
+        <v>1</v>
+      </c>
+      <c r="O298" t="s">
+        <v>277</v>
+      </c>
+      <c r="P298" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q298">
+        <v>3</v>
+      </c>
+      <c r="R298">
+        <v>1.85</v>
+      </c>
+      <c r="S298">
+        <v>4</v>
+      </c>
+      <c r="T298">
+        <v>1.58</v>
+      </c>
+      <c r="U298">
+        <v>2.2</v>
+      </c>
+      <c r="V298">
+        <v>3.7</v>
+      </c>
+      <c r="W298">
+        <v>1.24</v>
+      </c>
+      <c r="X298">
+        <v>11</v>
+      </c>
+      <c r="Y298">
+        <v>1.03</v>
+      </c>
+      <c r="Z298">
+        <v>2.41</v>
+      </c>
+      <c r="AA298">
+        <v>3.1</v>
+      </c>
+      <c r="AB298">
+        <v>3.37</v>
+      </c>
+      <c r="AC298">
+        <v>1.11</v>
+      </c>
+      <c r="AD298">
+        <v>6.2</v>
+      </c>
+      <c r="AE298">
+        <v>1.5</v>
+      </c>
+      <c r="AF298">
+        <v>2.3</v>
+      </c>
+      <c r="AG298">
+        <v>2.59</v>
+      </c>
+      <c r="AH298">
+        <v>1.44</v>
+      </c>
+      <c r="AI298">
+        <v>2.2</v>
+      </c>
+      <c r="AJ298">
+        <v>1.6</v>
+      </c>
+      <c r="AK298">
+        <v>1.31</v>
+      </c>
+      <c r="AL298">
+        <v>1.37</v>
+      </c>
+      <c r="AM298">
+        <v>1.58</v>
+      </c>
+      <c r="AN298">
+        <v>1.62</v>
+      </c>
+      <c r="AO298">
+        <v>0.23</v>
+      </c>
+      <c r="AP298">
+        <v>1.71</v>
+      </c>
+      <c r="AQ298">
+        <v>0.21</v>
+      </c>
+      <c r="AR298">
+        <v>1.37</v>
+      </c>
+      <c r="AS298">
+        <v>1.1</v>
+      </c>
+      <c r="AT298">
+        <v>2.47</v>
+      </c>
+      <c r="AU298">
+        <v>4</v>
+      </c>
+      <c r="AV298">
+        <v>5</v>
+      </c>
+      <c r="AW298">
+        <v>10</v>
+      </c>
+      <c r="AX298">
+        <v>2</v>
+      </c>
+      <c r="AY298">
+        <v>18</v>
+      </c>
+      <c r="AZ298">
+        <v>7</v>
+      </c>
+      <c r="BA298">
+        <v>9</v>
+      </c>
+      <c r="BB298">
+        <v>0</v>
+      </c>
+      <c r="BC298">
+        <v>9</v>
+      </c>
+      <c r="BD298">
+        <v>1.53</v>
+      </c>
+      <c r="BE298">
+        <v>6.75</v>
+      </c>
+      <c r="BF298">
+        <v>2.8</v>
+      </c>
+      <c r="BG298">
+        <v>1.45</v>
+      </c>
+      <c r="BH298">
+        <v>2.48</v>
+      </c>
+      <c r="BI298">
+        <v>1.76</v>
+      </c>
+      <c r="BJ298">
+        <v>1.9</v>
+      </c>
+      <c r="BK298">
+        <v>2.23</v>
+      </c>
+      <c r="BL298">
+        <v>1.56</v>
+      </c>
+      <c r="BM298">
+        <v>2.9</v>
+      </c>
+      <c r="BN298">
+        <v>1.34</v>
+      </c>
+      <c r="BO298">
+        <v>3.9</v>
+      </c>
+      <c r="BP298">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="386">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -850,6 +850,12 @@
     <t>['53']</t>
   </si>
   <si>
+    <t>['10', '62']</t>
+  </si>
+  <si>
+    <t>['23', '48']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1157,6 +1163,15 @@
   </si>
   <si>
     <t>['6', '45+2', '79']</t>
+  </si>
+  <si>
+    <t>['40', '55']</t>
+  </si>
+  <si>
+    <t>['31', '78']</t>
+  </si>
+  <si>
+    <t>['90+2', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1518,7 +1533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP298"/>
+  <dimension ref="A1:BP303"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1774,7 +1789,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1852,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ2">
         <v>0.93</v>
@@ -2061,7 +2076,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2186,7 +2201,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2267,7 +2282,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2470,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ5">
         <v>1.38</v>
@@ -2676,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -2885,7 +2900,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ7">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3010,7 +3025,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3088,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8">
         <v>1.43</v>
@@ -3216,7 +3231,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3297,7 +3312,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ9">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3500,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>0.5</v>
@@ -4040,7 +4055,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4246,7 +4261,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4530,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ15">
         <v>0.77</v>
@@ -4736,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ16">
         <v>1.46</v>
@@ -5276,7 +5291,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5357,7 +5372,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ19">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5769,7 +5784,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ21">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5894,7 +5909,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5975,7 +5990,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ22">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6100,7 +6115,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6306,7 +6321,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6384,7 +6399,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ24">
         <v>1.5</v>
@@ -6512,7 +6527,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6593,7 +6608,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ25">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6718,7 +6733,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6924,7 +6939,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7336,7 +7351,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7414,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>1.38</v>
@@ -7829,7 +7844,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR31">
         <v>0.48</v>
@@ -7954,7 +7969,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8160,7 +8175,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8238,7 +8253,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ33">
         <v>1.43</v>
@@ -8447,7 +8462,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR34">
         <v>1.17</v>
@@ -8572,7 +8587,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8653,7 +8668,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ35">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR35">
         <v>1.42</v>
@@ -8856,7 +8871,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ36">
         <v>1.36</v>
@@ -9268,10 +9283,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR38">
         <v>1.41</v>
@@ -9680,7 +9695,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ40">
         <v>1.15</v>
@@ -10095,7 +10110,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR42">
         <v>1.8</v>
@@ -10426,7 +10441,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11044,7 +11059,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11328,7 +11343,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ48">
         <v>0.21</v>
@@ -12358,10 +12373,10 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ53">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR53">
         <v>1.46</v>
@@ -12692,7 +12707,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12898,7 +12913,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13104,7 +13119,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13182,7 +13197,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -13310,7 +13325,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13388,7 +13403,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ58">
         <v>0.93</v>
@@ -13597,7 +13612,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ59">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR59">
         <v>1.51</v>
@@ -13722,7 +13737,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14340,7 +14355,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14627,7 +14642,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ64">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR64">
         <v>1.39</v>
@@ -14958,7 +14973,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15245,7 +15260,7 @@
         <v>2</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR67">
         <v>1.16</v>
@@ -15370,7 +15385,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15576,7 +15591,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16066,10 +16081,10 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ71">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR71">
         <v>1.44</v>
@@ -16194,7 +16209,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16400,7 +16415,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16481,7 +16496,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ73">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR73">
         <v>2.06</v>
@@ -16606,7 +16621,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16684,7 +16699,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ74">
         <v>1.46</v>
@@ -17430,7 +17445,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17636,7 +17651,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17920,7 +17935,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ80">
         <v>1.15</v>
@@ -18048,7 +18063,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18254,7 +18269,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18332,7 +18347,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ82">
         <v>1</v>
@@ -18460,7 +18475,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18541,7 +18556,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ83">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR83">
         <v>1.8</v>
@@ -19284,7 +19299,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19571,7 +19586,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ88">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR88">
         <v>1.96</v>
@@ -19696,7 +19711,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19777,7 +19792,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -19902,7 +19917,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19983,7 +19998,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ90">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR90">
         <v>1.45</v>
@@ -20314,7 +20329,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20598,7 +20613,7 @@
         <v>1.33</v>
       </c>
       <c r="AP93">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ93">
         <v>0.77</v>
@@ -20726,7 +20741,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20932,7 +20947,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21013,7 +21028,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ95">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR95">
         <v>1.44</v>
@@ -21422,10 +21437,10 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -21628,7 +21643,7 @@
         <v>0.67</v>
       </c>
       <c r="AP98">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ98">
         <v>1.15</v>
@@ -21962,7 +21977,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22040,7 +22055,7 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100">
         <v>1.38</v>
@@ -22455,7 +22470,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ102">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR102">
         <v>1.13</v>
@@ -22864,7 +22879,7 @@
         <v>0.25</v>
       </c>
       <c r="AP104">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ104">
         <v>0.21</v>
@@ -23404,7 +23419,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23485,7 +23500,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ107">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR107">
         <v>1.53</v>
@@ -23688,7 +23703,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ108">
         <v>1.5</v>
@@ -24022,7 +24037,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24103,7 +24118,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ110">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR110">
         <v>1.96</v>
@@ -24434,7 +24449,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24640,7 +24655,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24924,7 +24939,7 @@
         <v>1.75</v>
       </c>
       <c r="AP114">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ114">
         <v>1.31</v>
@@ -25052,7 +25067,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25133,7 +25148,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ115">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
         <v>1.49</v>
@@ -25339,7 +25354,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ116">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -25876,7 +25891,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26160,7 +26175,7 @@
         <v>1.4</v>
       </c>
       <c r="AP120">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120">
         <v>1.5</v>
@@ -26494,7 +26509,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26572,7 +26587,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26781,7 +26796,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ123">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR123">
         <v>1.53</v>
@@ -26906,7 +26921,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27318,7 +27333,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27730,7 +27745,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27811,7 +27826,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ128">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR128">
         <v>1.61</v>
@@ -28142,7 +28157,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28348,7 +28363,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28429,7 +28444,7 @@
         <v>2</v>
       </c>
       <c r="AQ131">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR131">
         <v>1.16</v>
@@ -28554,7 +28569,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28632,7 +28647,7 @@
         <v>1.17</v>
       </c>
       <c r="AP132">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ132">
         <v>1.43</v>
@@ -28838,7 +28853,7 @@
         <v>0.2</v>
       </c>
       <c r="AP133">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ133">
         <v>0.21</v>
@@ -28966,7 +28981,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29044,7 +29059,7 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ134">
         <v>1.15</v>
@@ -29172,7 +29187,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29456,7 +29471,7 @@
         <v>1.4</v>
       </c>
       <c r="AP136">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ136">
         <v>1.31</v>
@@ -29790,7 +29805,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30408,7 +30423,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30489,7 +30504,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ141">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR141">
         <v>1.42</v>
@@ -30614,7 +30629,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30820,7 +30835,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30901,7 +30916,7 @@
         <v>2</v>
       </c>
       <c r="AQ143">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR143">
         <v>1.11</v>
@@ -31026,7 +31041,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31104,7 +31119,7 @@
         <v>0.83</v>
       </c>
       <c r="AP144">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ144">
         <v>0.77</v>
@@ -31438,7 +31453,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31722,7 +31737,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ147">
         <v>1</v>
@@ -31850,7 +31865,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -31928,10 +31943,10 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ148">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR148">
         <v>1.13</v>
@@ -32137,7 +32152,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ149">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR149">
         <v>1.82</v>
@@ -32546,7 +32561,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ151">
         <v>1</v>
@@ -32880,7 +32895,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33498,7 +33513,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33576,7 +33591,7 @@
         <v>1.83</v>
       </c>
       <c r="AP156">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ156">
         <v>1.46</v>
@@ -33785,7 +33800,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR157">
         <v>1.49</v>
@@ -35018,7 +35033,7 @@
         <v>1.43</v>
       </c>
       <c r="AP163">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ163">
         <v>1.43</v>
@@ -35146,7 +35161,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35227,7 +35242,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ164">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR164">
         <v>1.2</v>
@@ -35430,7 +35445,7 @@
         <v>1.14</v>
       </c>
       <c r="AP165">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ165">
         <v>1.31</v>
@@ -35636,7 +35651,7 @@
         <v>0.71</v>
       </c>
       <c r="AP166">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ166">
         <v>0.64</v>
@@ -35764,7 +35779,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35845,7 +35860,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ167">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR167">
         <v>1.65</v>
@@ -36051,7 +36066,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ168">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR168">
         <v>1.29</v>
@@ -36794,7 +36809,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37081,7 +37096,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ173">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR173">
         <v>1.44</v>
@@ -37287,7 +37302,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ174">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR174">
         <v>1.76</v>
@@ -37412,7 +37427,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37824,7 +37839,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38236,7 +38251,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38442,7 +38457,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39266,7 +39281,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39756,10 +39771,10 @@
         <v>0.13</v>
       </c>
       <c r="AP186">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ186">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR186">
         <v>1.44</v>
@@ -39962,7 +39977,7 @@
         <v>0.75</v>
       </c>
       <c r="AP187">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ187">
         <v>0.5</v>
@@ -40090,7 +40105,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40580,10 +40595,10 @@
         <v>2.75</v>
       </c>
       <c r="AP190">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ190">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR190">
         <v>1.74</v>
@@ -40708,7 +40723,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40789,7 +40804,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ191">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR191">
         <v>1.48</v>
@@ -40914,7 +40929,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41120,7 +41135,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41198,10 +41213,10 @@
         <v>0.89</v>
       </c>
       <c r="AP193">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ193">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR193">
         <v>1.13</v>
@@ -41326,7 +41341,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41407,7 +41422,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ194">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR194">
         <v>1.4</v>
@@ -41816,7 +41831,7 @@
         <v>0.63</v>
       </c>
       <c r="AP196">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ196">
         <v>0.77</v>
@@ -42562,7 +42577,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42643,7 +42658,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ200">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR200">
         <v>1.61</v>
@@ -42974,7 +42989,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43180,7 +43195,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43258,10 +43273,10 @@
         <v>1.6</v>
       </c>
       <c r="AP203">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ203">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR203">
         <v>1.49</v>
@@ -43798,7 +43813,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43876,7 +43891,7 @@
         <v>0.88</v>
       </c>
       <c r="AP206">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ206">
         <v>1</v>
@@ -44082,7 +44097,7 @@
         <v>0.78</v>
       </c>
       <c r="AP207">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ207">
         <v>1</v>
@@ -44494,7 +44509,7 @@
         <v>0.6</v>
       </c>
       <c r="AP209">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ209">
         <v>0.5</v>
@@ -44828,7 +44843,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45034,7 +45049,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45115,7 +45130,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ212">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR212">
         <v>1.69</v>
@@ -45240,7 +45255,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45318,10 +45333,10 @@
         <v>1.5</v>
       </c>
       <c r="AP213">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ213">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR213">
         <v>1.08</v>
@@ -45446,7 +45461,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45858,7 +45873,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46145,7 +46160,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ217">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR217">
         <v>1.61</v>
@@ -46966,7 +46981,7 @@
         <v>1.56</v>
       </c>
       <c r="AP221">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ221">
         <v>1.46</v>
@@ -47094,7 +47109,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47175,7 +47190,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ222">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR222">
         <v>1.64</v>
@@ -47506,7 +47521,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47584,7 +47599,7 @@
         <v>0.8</v>
       </c>
       <c r="AP224">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ224">
         <v>1</v>
@@ -47790,7 +47805,7 @@
         <v>0.2</v>
       </c>
       <c r="AP225">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ225">
         <v>0.21</v>
@@ -47918,7 +47933,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48536,7 +48551,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48742,7 +48757,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48948,7 +48963,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49232,7 +49247,7 @@
         <v>0.8</v>
       </c>
       <c r="AP232">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ232">
         <v>0.92</v>
@@ -49438,7 +49453,7 @@
         <v>0.55</v>
       </c>
       <c r="AP233">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ233">
         <v>0.5</v>
@@ -49772,7 +49787,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -49853,7 +49868,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ235">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR235">
         <v>1.56</v>
@@ -50596,7 +50611,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50677,7 +50692,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ239">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR239">
         <v>1.67</v>
@@ -51089,7 +51104,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ241">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR241">
         <v>1.63</v>
@@ -51214,7 +51229,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51501,7 +51516,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ243">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR243">
         <v>1.18</v>
@@ -51626,7 +51641,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51832,7 +51847,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -51910,7 +51925,7 @@
         <v>1.3</v>
       </c>
       <c r="AP245">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ245">
         <v>1.15</v>
@@ -52116,7 +52131,7 @@
         <v>1.09</v>
       </c>
       <c r="AP246">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ246">
         <v>0.93</v>
@@ -52528,7 +52543,7 @@
         <v>1.2</v>
       </c>
       <c r="AP248">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ248">
         <v>1.36</v>
@@ -52862,7 +52877,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -52943,7 +52958,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ250">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR250">
         <v>1.68</v>
@@ -53068,7 +53083,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53480,7 +53495,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53892,7 +53907,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -53973,7 +53988,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ255">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR255">
         <v>1.61</v>
@@ -54098,7 +54113,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54510,7 +54525,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -54794,7 +54809,7 @@
         <v>1.09</v>
       </c>
       <c r="AP259">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ259">
         <v>1</v>
@@ -55128,7 +55143,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55209,7 +55224,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ261">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR261">
         <v>1.52</v>
@@ -55334,7 +55349,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55415,7 +55430,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ262">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR262">
         <v>1.34</v>
@@ -55952,7 +55967,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56442,7 +56457,7 @@
         <v>0.82</v>
       </c>
       <c r="AP267">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ267">
         <v>0.92</v>
@@ -56651,7 +56666,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ268">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR268">
         <v>1.8</v>
@@ -56776,7 +56791,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57266,7 +57281,7 @@
         <v>1.33</v>
       </c>
       <c r="AP271">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ271">
         <v>1.36</v>
@@ -57600,7 +57615,7 @@
         <v>94</v>
       </c>
       <c r="P273" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q273">
         <v>4</v>
@@ -57681,7 +57696,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ273">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR273">
         <v>1.18</v>
@@ -58299,7 +58314,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ276">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR276">
         <v>1.54</v>
@@ -58424,7 +58439,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58502,7 +58517,7 @@
         <v>1.25</v>
       </c>
       <c r="AP277">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ277">
         <v>1.38</v>
@@ -58708,7 +58723,7 @@
         <v>1.17</v>
       </c>
       <c r="AP278">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ278">
         <v>1.15</v>
@@ -59120,7 +59135,7 @@
         <v>0.67</v>
       </c>
       <c r="AP280">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ280">
         <v>0.64</v>
@@ -59454,7 +59469,7 @@
         <v>186</v>
       </c>
       <c r="P282" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59738,10 +59753,10 @@
         <v>2.17</v>
       </c>
       <c r="AP283">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ283">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR283">
         <v>1.44</v>
@@ -59866,7 +59881,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60153,7 +60168,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ285">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR285">
         <v>1.52</v>
@@ -60484,7 +60499,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61102,7 +61117,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61308,7 +61323,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61389,7 +61404,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ291">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR291">
         <v>1.32</v>
@@ -62907,6 +62922,1036 @@
       </c>
       <c r="BP298">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="299" spans="1:68">
+      <c r="A299" s="1">
+        <v>298</v>
+      </c>
+      <c r="B299">
+        <v>7728504</v>
+      </c>
+      <c r="C299" t="s">
+        <v>68</v>
+      </c>
+      <c r="D299" t="s">
+        <v>69</v>
+      </c>
+      <c r="E299" s="2">
+        <v>45710.41666666666</v>
+      </c>
+      <c r="F299">
+        <v>28</v>
+      </c>
+      <c r="G299" t="s">
+        <v>74</v>
+      </c>
+      <c r="H299" t="s">
+        <v>88</v>
+      </c>
+      <c r="I299">
+        <v>0</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>0</v>
+      </c>
+      <c r="L299">
+        <v>0</v>
+      </c>
+      <c r="M299">
+        <v>1</v>
+      </c>
+      <c r="N299">
+        <v>1</v>
+      </c>
+      <c r="O299" t="s">
+        <v>94</v>
+      </c>
+      <c r="P299" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q299">
+        <v>3.65</v>
+      </c>
+      <c r="R299">
+        <v>2.03</v>
+      </c>
+      <c r="S299">
+        <v>3.2</v>
+      </c>
+      <c r="T299">
+        <v>1.49</v>
+      </c>
+      <c r="U299">
+        <v>2.45</v>
+      </c>
+      <c r="V299">
+        <v>3.1</v>
+      </c>
+      <c r="W299">
+        <v>1.32</v>
+      </c>
+      <c r="X299">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y299">
+        <v>1.01</v>
+      </c>
+      <c r="Z299">
+        <v>2.97</v>
+      </c>
+      <c r="AA299">
+        <v>3.16</v>
+      </c>
+      <c r="AB299">
+        <v>2.62</v>
+      </c>
+      <c r="AC299">
+        <v>1.09</v>
+      </c>
+      <c r="AD299">
+        <v>7</v>
+      </c>
+      <c r="AE299">
+        <v>1.39</v>
+      </c>
+      <c r="AF299">
+        <v>2.75</v>
+      </c>
+      <c r="AG299">
+        <v>2.15</v>
+      </c>
+      <c r="AH299">
+        <v>1.57</v>
+      </c>
+      <c r="AI299">
+        <v>1.88</v>
+      </c>
+      <c r="AJ299">
+        <v>1.84</v>
+      </c>
+      <c r="AK299">
+        <v>1.5</v>
+      </c>
+      <c r="AL299">
+        <v>1.33</v>
+      </c>
+      <c r="AM299">
+        <v>1.39</v>
+      </c>
+      <c r="AN299">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO299">
+        <v>1</v>
+      </c>
+      <c r="AP299">
+        <v>0.64</v>
+      </c>
+      <c r="AQ299">
+        <v>1.13</v>
+      </c>
+      <c r="AR299">
+        <v>1.24</v>
+      </c>
+      <c r="AS299">
+        <v>1.45</v>
+      </c>
+      <c r="AT299">
+        <v>2.69</v>
+      </c>
+      <c r="AU299">
+        <v>0</v>
+      </c>
+      <c r="AV299">
+        <v>7</v>
+      </c>
+      <c r="AW299">
+        <v>6</v>
+      </c>
+      <c r="AX299">
+        <v>7</v>
+      </c>
+      <c r="AY299">
+        <v>9</v>
+      </c>
+      <c r="AZ299">
+        <v>17</v>
+      </c>
+      <c r="BA299">
+        <v>4</v>
+      </c>
+      <c r="BB299">
+        <v>2</v>
+      </c>
+      <c r="BC299">
+        <v>6</v>
+      </c>
+      <c r="BD299">
+        <v>1.95</v>
+      </c>
+      <c r="BE299">
+        <v>6.4</v>
+      </c>
+      <c r="BF299">
+        <v>2.05</v>
+      </c>
+      <c r="BG299">
+        <v>1.36</v>
+      </c>
+      <c r="BH299">
+        <v>2.8</v>
+      </c>
+      <c r="BI299">
+        <v>1.6</v>
+      </c>
+      <c r="BJ299">
+        <v>2.14</v>
+      </c>
+      <c r="BK299">
+        <v>1.95</v>
+      </c>
+      <c r="BL299">
+        <v>1.72</v>
+      </c>
+      <c r="BM299">
+        <v>2.5</v>
+      </c>
+      <c r="BN299">
+        <v>1.44</v>
+      </c>
+      <c r="BO299">
+        <v>3.3</v>
+      </c>
+      <c r="BP299">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="300" spans="1:68">
+      <c r="A300" s="1">
+        <v>299</v>
+      </c>
+      <c r="B300">
+        <v>7728844</v>
+      </c>
+      <c r="C300" t="s">
+        <v>68</v>
+      </c>
+      <c r="D300" t="s">
+        <v>69</v>
+      </c>
+      <c r="E300" s="2">
+        <v>45710.51041666666</v>
+      </c>
+      <c r="F300">
+        <v>28</v>
+      </c>
+      <c r="G300" t="s">
+        <v>78</v>
+      </c>
+      <c r="H300" t="s">
+        <v>89</v>
+      </c>
+      <c r="I300">
+        <v>1</v>
+      </c>
+      <c r="J300">
+        <v>1</v>
+      </c>
+      <c r="K300">
+        <v>2</v>
+      </c>
+      <c r="L300">
+        <v>1</v>
+      </c>
+      <c r="M300">
+        <v>2</v>
+      </c>
+      <c r="N300">
+        <v>3</v>
+      </c>
+      <c r="O300" t="s">
+        <v>147</v>
+      </c>
+      <c r="P300" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q300">
+        <v>3.6</v>
+      </c>
+      <c r="R300">
+        <v>1.8</v>
+      </c>
+      <c r="S300">
+        <v>3.5</v>
+      </c>
+      <c r="T300">
+        <v>1.62</v>
+      </c>
+      <c r="U300">
+        <v>2.15</v>
+      </c>
+      <c r="V300">
+        <v>3.9</v>
+      </c>
+      <c r="W300">
+        <v>1.22</v>
+      </c>
+      <c r="X300">
+        <v>11.5</v>
+      </c>
+      <c r="Y300">
+        <v>1.03</v>
+      </c>
+      <c r="Z300">
+        <v>2.91</v>
+      </c>
+      <c r="AA300">
+        <v>2.95</v>
+      </c>
+      <c r="AB300">
+        <v>2.84</v>
+      </c>
+      <c r="AC300">
+        <v>1.12</v>
+      </c>
+      <c r="AD300">
+        <v>5.75</v>
+      </c>
+      <c r="AE300">
+        <v>1.57</v>
+      </c>
+      <c r="AF300">
+        <v>2.25</v>
+      </c>
+      <c r="AG300">
+        <v>2.37</v>
+      </c>
+      <c r="AH300">
+        <v>1.48</v>
+      </c>
+      <c r="AI300">
+        <v>2.2</v>
+      </c>
+      <c r="AJ300">
+        <v>1.6</v>
+      </c>
+      <c r="AK300">
+        <v>1.44</v>
+      </c>
+      <c r="AL300">
+        <v>1.39</v>
+      </c>
+      <c r="AM300">
+        <v>1.4</v>
+      </c>
+      <c r="AN300">
+        <v>1.62</v>
+      </c>
+      <c r="AO300">
+        <v>1.38</v>
+      </c>
+      <c r="AP300">
+        <v>1.5</v>
+      </c>
+      <c r="AQ300">
+        <v>1.5</v>
+      </c>
+      <c r="AR300">
+        <v>1.42</v>
+      </c>
+      <c r="AS300">
+        <v>1.33</v>
+      </c>
+      <c r="AT300">
+        <v>2.75</v>
+      </c>
+      <c r="AU300">
+        <v>5</v>
+      </c>
+      <c r="AV300">
+        <v>5</v>
+      </c>
+      <c r="AW300">
+        <v>3</v>
+      </c>
+      <c r="AX300">
+        <v>4</v>
+      </c>
+      <c r="AY300">
+        <v>9</v>
+      </c>
+      <c r="AZ300">
+        <v>11</v>
+      </c>
+      <c r="BA300">
+        <v>4</v>
+      </c>
+      <c r="BB300">
+        <v>2</v>
+      </c>
+      <c r="BC300">
+        <v>6</v>
+      </c>
+      <c r="BD300">
+        <v>1.74</v>
+      </c>
+      <c r="BE300">
+        <v>6.5</v>
+      </c>
+      <c r="BF300">
+        <v>2.3</v>
+      </c>
+      <c r="BG300">
+        <v>1.41</v>
+      </c>
+      <c r="BH300">
+        <v>2.6</v>
+      </c>
+      <c r="BI300">
+        <v>1.7</v>
+      </c>
+      <c r="BJ300">
+        <v>1.98</v>
+      </c>
+      <c r="BK300">
+        <v>2.14</v>
+      </c>
+      <c r="BL300">
+        <v>1.6</v>
+      </c>
+      <c r="BM300">
+        <v>2.8</v>
+      </c>
+      <c r="BN300">
+        <v>1.36</v>
+      </c>
+      <c r="BO300">
+        <v>3.7</v>
+      </c>
+      <c r="BP300">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="301" spans="1:68">
+      <c r="A301" s="1">
+        <v>300</v>
+      </c>
+      <c r="B301">
+        <v>7728498</v>
+      </c>
+      <c r="C301" t="s">
+        <v>68</v>
+      </c>
+      <c r="D301" t="s">
+        <v>69</v>
+      </c>
+      <c r="E301" s="2">
+        <v>45710.51041666666</v>
+      </c>
+      <c r="F301">
+        <v>28</v>
+      </c>
+      <c r="G301" t="s">
+        <v>73</v>
+      </c>
+      <c r="H301" t="s">
+        <v>77</v>
+      </c>
+      <c r="I301">
+        <v>1</v>
+      </c>
+      <c r="J301">
+        <v>1</v>
+      </c>
+      <c r="K301">
+        <v>2</v>
+      </c>
+      <c r="L301">
+        <v>2</v>
+      </c>
+      <c r="M301">
+        <v>2</v>
+      </c>
+      <c r="N301">
+        <v>4</v>
+      </c>
+      <c r="O301" t="s">
+        <v>278</v>
+      </c>
+      <c r="P301" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q301">
+        <v>2.85</v>
+      </c>
+      <c r="R301">
+        <v>2.12</v>
+      </c>
+      <c r="S301">
+        <v>3.9</v>
+      </c>
+      <c r="T301">
+        <v>1.43</v>
+      </c>
+      <c r="U301">
+        <v>2.65</v>
+      </c>
+      <c r="V301">
+        <v>2.85</v>
+      </c>
+      <c r="W301">
+        <v>1.37</v>
+      </c>
+      <c r="X301">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y301">
+        <v>1.02</v>
+      </c>
+      <c r="Z301">
+        <v>2.34</v>
+      </c>
+      <c r="AA301">
+        <v>3.36</v>
+      </c>
+      <c r="AB301">
+        <v>3.23</v>
+      </c>
+      <c r="AC301">
+        <v>1.06</v>
+      </c>
+      <c r="AD301">
+        <v>8.5</v>
+      </c>
+      <c r="AE301">
+        <v>1.33</v>
+      </c>
+      <c r="AF301">
+        <v>3.05</v>
+      </c>
+      <c r="AG301">
+        <v>2.02</v>
+      </c>
+      <c r="AH301">
+        <v>1.8</v>
+      </c>
+      <c r="AI301">
+        <v>1.79</v>
+      </c>
+      <c r="AJ301">
+        <v>1.93</v>
+      </c>
+      <c r="AK301">
+        <v>1.32</v>
+      </c>
+      <c r="AL301">
+        <v>1.3</v>
+      </c>
+      <c r="AM301">
+        <v>1.63</v>
+      </c>
+      <c r="AN301">
+        <v>1.85</v>
+      </c>
+      <c r="AO301">
+        <v>2</v>
+      </c>
+      <c r="AP301">
+        <v>1.79</v>
+      </c>
+      <c r="AQ301">
+        <v>1.93</v>
+      </c>
+      <c r="AR301">
+        <v>1.54</v>
+      </c>
+      <c r="AS301">
+        <v>1.34</v>
+      </c>
+      <c r="AT301">
+        <v>2.88</v>
+      </c>
+      <c r="AU301">
+        <v>6</v>
+      </c>
+      <c r="AV301">
+        <v>5</v>
+      </c>
+      <c r="AW301">
+        <v>6</v>
+      </c>
+      <c r="AX301">
+        <v>10</v>
+      </c>
+      <c r="AY301">
+        <v>13</v>
+      </c>
+      <c r="AZ301">
+        <v>19</v>
+      </c>
+      <c r="BA301">
+        <v>2</v>
+      </c>
+      <c r="BB301">
+        <v>3</v>
+      </c>
+      <c r="BC301">
+        <v>5</v>
+      </c>
+      <c r="BD301">
+        <v>1.79</v>
+      </c>
+      <c r="BE301">
+        <v>6.4</v>
+      </c>
+      <c r="BF301">
+        <v>2.23</v>
+      </c>
+      <c r="BG301">
+        <v>1.36</v>
+      </c>
+      <c r="BH301">
+        <v>2.8</v>
+      </c>
+      <c r="BI301">
+        <v>1.63</v>
+      </c>
+      <c r="BJ301">
+        <v>2.08</v>
+      </c>
+      <c r="BK301">
+        <v>2.04</v>
+      </c>
+      <c r="BL301">
+        <v>1.66</v>
+      </c>
+      <c r="BM301">
+        <v>2.6</v>
+      </c>
+      <c r="BN301">
+        <v>1.41</v>
+      </c>
+      <c r="BO301">
+        <v>3.4</v>
+      </c>
+      <c r="BP301">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="302" spans="1:68">
+      <c r="A302" s="1">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>7728499</v>
+      </c>
+      <c r="C302" t="s">
+        <v>68</v>
+      </c>
+      <c r="D302" t="s">
+        <v>69</v>
+      </c>
+      <c r="E302" s="2">
+        <v>45710.60416666666</v>
+      </c>
+      <c r="F302">
+        <v>28</v>
+      </c>
+      <c r="G302" t="s">
+        <v>70</v>
+      </c>
+      <c r="H302" t="s">
+        <v>91</v>
+      </c>
+      <c r="I302">
+        <v>1</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>1</v>
+      </c>
+      <c r="L302">
+        <v>2</v>
+      </c>
+      <c r="M302">
+        <v>2</v>
+      </c>
+      <c r="N302">
+        <v>4</v>
+      </c>
+      <c r="O302" t="s">
+        <v>279</v>
+      </c>
+      <c r="P302" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q302">
+        <v>2.6</v>
+      </c>
+      <c r="R302">
+        <v>2</v>
+      </c>
+      <c r="S302">
+        <v>4.2</v>
+      </c>
+      <c r="T302">
+        <v>1.46</v>
+      </c>
+      <c r="U302">
+        <v>2.5</v>
+      </c>
+      <c r="V302">
+        <v>3.1</v>
+      </c>
+      <c r="W302">
+        <v>1.31</v>
+      </c>
+      <c r="X302">
+        <v>8.5</v>
+      </c>
+      <c r="Y302">
+        <v>1.06</v>
+      </c>
+      <c r="Z302">
+        <v>2.01</v>
+      </c>
+      <c r="AA302">
+        <v>3.41</v>
+      </c>
+      <c r="AB302">
+        <v>4.1</v>
+      </c>
+      <c r="AC302">
+        <v>1.07</v>
+      </c>
+      <c r="AD302">
+        <v>8</v>
+      </c>
+      <c r="AE302">
+        <v>1.4</v>
+      </c>
+      <c r="AF302">
+        <v>2.88</v>
+      </c>
+      <c r="AG302">
+        <v>2.1</v>
+      </c>
+      <c r="AH302">
+        <v>1.6</v>
+      </c>
+      <c r="AI302">
+        <v>1.98</v>
+      </c>
+      <c r="AJ302">
+        <v>1.73</v>
+      </c>
+      <c r="AK302">
+        <v>1.26</v>
+      </c>
+      <c r="AL302">
+        <v>1.31</v>
+      </c>
+      <c r="AM302">
+        <v>1.77</v>
+      </c>
+      <c r="AN302">
+        <v>1.64</v>
+      </c>
+      <c r="AO302">
+        <v>1.36</v>
+      </c>
+      <c r="AP302">
+        <v>1.6</v>
+      </c>
+      <c r="AQ302">
+        <v>1.33</v>
+      </c>
+      <c r="AR302">
+        <v>1.7</v>
+      </c>
+      <c r="AS302">
+        <v>1.36</v>
+      </c>
+      <c r="AT302">
+        <v>3.06</v>
+      </c>
+      <c r="AU302">
+        <v>5</v>
+      </c>
+      <c r="AV302">
+        <v>5</v>
+      </c>
+      <c r="AW302">
+        <v>5</v>
+      </c>
+      <c r="AX302">
+        <v>10</v>
+      </c>
+      <c r="AY302">
+        <v>12</v>
+      </c>
+      <c r="AZ302">
+        <v>17</v>
+      </c>
+      <c r="BA302">
+        <v>4</v>
+      </c>
+      <c r="BB302">
+        <v>7</v>
+      </c>
+      <c r="BC302">
+        <v>11</v>
+      </c>
+      <c r="BD302">
+        <v>1.66</v>
+      </c>
+      <c r="BE302">
+        <v>6.4</v>
+      </c>
+      <c r="BF302">
+        <v>2.48</v>
+      </c>
+      <c r="BG302">
+        <v>1.34</v>
+      </c>
+      <c r="BH302">
+        <v>2.88</v>
+      </c>
+      <c r="BI302">
+        <v>1.58</v>
+      </c>
+      <c r="BJ302">
+        <v>2.15</v>
+      </c>
+      <c r="BK302">
+        <v>1.96</v>
+      </c>
+      <c r="BL302">
+        <v>1.71</v>
+      </c>
+      <c r="BM302">
+        <v>2.5</v>
+      </c>
+      <c r="BN302">
+        <v>1.44</v>
+      </c>
+      <c r="BO302">
+        <v>3.3</v>
+      </c>
+      <c r="BP302">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="303" spans="1:68">
+      <c r="A303" s="1">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>7728502</v>
+      </c>
+      <c r="C303" t="s">
+        <v>68</v>
+      </c>
+      <c r="D303" t="s">
+        <v>69</v>
+      </c>
+      <c r="E303" s="2">
+        <v>45710.70833333334</v>
+      </c>
+      <c r="F303">
+        <v>28</v>
+      </c>
+      <c r="G303" t="s">
+        <v>76</v>
+      </c>
+      <c r="H303" t="s">
+        <v>90</v>
+      </c>
+      <c r="I303">
+        <v>0</v>
+      </c>
+      <c r="J303">
+        <v>1</v>
+      </c>
+      <c r="K303">
+        <v>1</v>
+      </c>
+      <c r="L303">
+        <v>1</v>
+      </c>
+      <c r="M303">
+        <v>1</v>
+      </c>
+      <c r="N303">
+        <v>2</v>
+      </c>
+      <c r="O303" t="s">
+        <v>200</v>
+      </c>
+      <c r="P303" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q303">
+        <v>3.25</v>
+      </c>
+      <c r="R303">
+        <v>2</v>
+      </c>
+      <c r="S303">
+        <v>3.6</v>
+      </c>
+      <c r="T303">
+        <v>1.5</v>
+      </c>
+      <c r="U303">
+        <v>2.5</v>
+      </c>
+      <c r="V303">
+        <v>3.5</v>
+      </c>
+      <c r="W303">
+        <v>1.29</v>
+      </c>
+      <c r="X303">
+        <v>11</v>
+      </c>
+      <c r="Y303">
+        <v>1.05</v>
+      </c>
+      <c r="Z303">
+        <v>2.53</v>
+      </c>
+      <c r="AA303">
+        <v>3.38</v>
+      </c>
+      <c r="AB303">
+        <v>2.9</v>
+      </c>
+      <c r="AC303">
+        <v>1.08</v>
+      </c>
+      <c r="AD303">
+        <v>7.5</v>
+      </c>
+      <c r="AE303">
+        <v>1.42</v>
+      </c>
+      <c r="AF303">
+        <v>2.8</v>
+      </c>
+      <c r="AG303">
+        <v>2.37</v>
+      </c>
+      <c r="AH303">
+        <v>1.48</v>
+      </c>
+      <c r="AI303">
+        <v>2</v>
+      </c>
+      <c r="AJ303">
+        <v>1.73</v>
+      </c>
+      <c r="AK303">
+        <v>1.4</v>
+      </c>
+      <c r="AL303">
+        <v>1.33</v>
+      </c>
+      <c r="AM303">
+        <v>1.52</v>
+      </c>
+      <c r="AN303">
+        <v>1.71</v>
+      </c>
+      <c r="AO303">
+        <v>1.5</v>
+      </c>
+      <c r="AP303">
+        <v>1.67</v>
+      </c>
+      <c r="AQ303">
+        <v>1.47</v>
+      </c>
+      <c r="AR303">
+        <v>1.51</v>
+      </c>
+      <c r="AS303">
+        <v>1.56</v>
+      </c>
+      <c r="AT303">
+        <v>3.07</v>
+      </c>
+      <c r="AU303">
+        <v>6</v>
+      </c>
+      <c r="AV303">
+        <v>8</v>
+      </c>
+      <c r="AW303">
+        <v>10</v>
+      </c>
+      <c r="AX303">
+        <v>14</v>
+      </c>
+      <c r="AY303">
+        <v>18</v>
+      </c>
+      <c r="AZ303">
+        <v>24</v>
+      </c>
+      <c r="BA303">
+        <v>10</v>
+      </c>
+      <c r="BB303">
+        <v>4</v>
+      </c>
+      <c r="BC303">
+        <v>14</v>
+      </c>
+      <c r="BD303">
+        <v>1.82</v>
+      </c>
+      <c r="BE303">
+        <v>8</v>
+      </c>
+      <c r="BF303">
+        <v>2.33</v>
+      </c>
+      <c r="BG303">
+        <v>1.31</v>
+      </c>
+      <c r="BH303">
+        <v>3.15</v>
+      </c>
+      <c r="BI303">
+        <v>1.56</v>
+      </c>
+      <c r="BJ303">
+        <v>2.33</v>
+      </c>
+      <c r="BK303">
+        <v>1.93</v>
+      </c>
+      <c r="BL303">
+        <v>1.82</v>
+      </c>
+      <c r="BM303">
+        <v>2.43</v>
+      </c>
+      <c r="BN303">
+        <v>1.49</v>
+      </c>
+      <c r="BO303">
+        <v>3.22</v>
+      </c>
+      <c r="BP303">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="387">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -835,10 +835,10 @@
     <t>['9', '42']</t>
   </si>
   <si>
-    <t>['76']</t>
+    <t>['58', '65']</t>
   </si>
   <si>
-    <t>['58', '65']</t>
+    <t>['76']</t>
   </si>
   <si>
     <t>['43']</t>
@@ -854,6 +854,9 @@
   </si>
   <si>
     <t>['23', '48']</t>
+  </si>
+  <si>
+    <t>['60', '63']</t>
   </si>
   <si>
     <t>['42', '45+3']</t>
@@ -1165,10 +1168,10 @@
     <t>['6', '45+2', '79']</t>
   </si>
   <si>
-    <t>['40', '55']</t>
+    <t>['31', '78']</t>
   </si>
   <si>
-    <t>['31', '78']</t>
+    <t>['40', '55']</t>
   </si>
   <si>
     <t>['90+2', '90+4']</t>
@@ -1533,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP303"/>
+  <dimension ref="A1:BP308"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1789,7 +1792,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2201,7 +2204,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2279,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ4">
         <v>1.33</v>
@@ -2488,7 +2491,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2897,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ7">
         <v>1.5</v>
@@ -3025,7 +3028,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3231,7 +3234,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3518,7 +3521,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ10">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3721,10 +3724,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4055,7 +4058,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4261,7 +4264,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4548,7 +4551,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ15">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR15">
         <v>1.13</v>
@@ -4957,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ17">
         <v>1.31</v>
@@ -5166,7 +5169,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ18">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5291,7 +5294,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5575,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
         <v>1.15</v>
@@ -5909,7 +5912,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6115,7 +6118,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6321,7 +6324,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6402,7 +6405,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR24">
         <v>2.51</v>
@@ -6527,7 +6530,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6733,7 +6736,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6811,7 +6814,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26">
         <v>0.21</v>
@@ -6939,7 +6942,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7351,7 +7354,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7432,7 +7435,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR29">
         <v>1.44</v>
@@ -7635,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ30">
         <v>1</v>
@@ -7969,7 +7972,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8050,7 +8053,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ32">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR32">
         <v>1.31</v>
@@ -8175,7 +8178,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8459,7 +8462,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ34">
         <v>1.13</v>
@@ -8587,7 +8590,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9698,7 +9701,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ40">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -10441,7 +10444,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10725,7 +10728,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ45">
         <v>0.64</v>
@@ -11059,7 +11062,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11137,10 +11140,10 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ47">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR47">
         <v>1.72</v>
@@ -11552,7 +11555,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ49">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR49">
         <v>1.38</v>
@@ -12170,7 +12173,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ52">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR52">
         <v>1.28</v>
@@ -12579,7 +12582,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12707,7 +12710,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12785,7 +12788,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ55">
         <v>1.46</v>
@@ -12913,7 +12916,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -12994,7 +12997,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ56">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR56">
         <v>1.94</v>
@@ -13119,7 +13122,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13325,7 +13328,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13737,7 +13740,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13815,7 +13818,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ60">
         <v>0.92</v>
@@ -14355,7 +14358,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14845,10 +14848,10 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ65">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR65">
         <v>1.25</v>
@@ -14973,7 +14976,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15385,7 +15388,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15463,7 +15466,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ68">
         <v>1.36</v>
@@ -15591,7 +15594,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15669,10 +15672,10 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ69">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR69">
         <v>1.25</v>
@@ -15878,7 +15881,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR70">
         <v>1.04</v>
@@ -16209,7 +16212,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16415,7 +16418,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16493,7 +16496,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ73">
         <v>1.47</v>
@@ -16621,7 +16624,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17445,7 +17448,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17526,7 +17529,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR78">
         <v>1.42</v>
@@ -17651,7 +17654,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18063,7 +18066,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18269,7 +18272,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18475,7 +18478,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18968,7 +18971,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ85">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -19171,7 +19174,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ86">
         <v>1</v>
@@ -19299,7 +19302,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19380,7 +19383,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ87">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR87">
         <v>1.47</v>
@@ -19583,7 +19586,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ88">
         <v>1.5</v>
@@ -19711,7 +19714,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19789,7 +19792,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ89">
         <v>1.13</v>
@@ -19917,7 +19920,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20329,7 +20332,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20407,7 +20410,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20616,7 +20619,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ93">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR93">
         <v>1.5</v>
@@ -20741,7 +20744,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20947,7 +20950,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21646,7 +21649,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ98">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR98">
         <v>1.35</v>
@@ -21849,7 +21852,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ99">
         <v>1.36</v>
@@ -21977,7 +21980,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22058,7 +22061,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -22264,7 +22267,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ101">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR101">
         <v>1.58</v>
@@ -22673,10 +22676,10 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ103">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR103">
         <v>1.55</v>
@@ -23419,7 +23422,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23497,7 +23500,7 @@
         <v>3</v>
       </c>
       <c r="AP107">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ107">
         <v>1.93</v>
@@ -23706,7 +23709,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ108">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR108">
         <v>1.17</v>
@@ -23909,7 +23912,7 @@
         <v>1.25</v>
       </c>
       <c r="AP109">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -24037,7 +24040,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24321,7 +24324,7 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111">
         <v>0.92</v>
@@ -24449,7 +24452,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24530,7 +24533,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ112">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR112">
         <v>1.61</v>
@@ -24655,7 +24658,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25067,7 +25070,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25891,7 +25894,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -25969,7 +25972,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ119">
         <v>1.36</v>
@@ -26178,7 +26181,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ120">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR120">
         <v>1.6</v>
@@ -26509,7 +26512,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26793,7 +26796,7 @@
         <v>1.17</v>
       </c>
       <c r="AP123">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ123">
         <v>1.5</v>
@@ -26921,7 +26924,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27002,7 +27005,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ124">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR124">
         <v>1.12</v>
@@ -27208,7 +27211,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ125">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR125">
         <v>1.56</v>
@@ -27333,7 +27336,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27414,7 +27417,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ126">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR126">
         <v>1.8</v>
@@ -27745,7 +27748,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27823,7 +27826,7 @@
         <v>3</v>
       </c>
       <c r="AP128">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ128">
         <v>1.93</v>
@@ -28029,7 +28032,7 @@
         <v>1.4</v>
       </c>
       <c r="AP129">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ129">
         <v>0.92</v>
@@ -28157,7 +28160,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28235,7 +28238,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28363,7 +28366,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28569,7 +28572,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28981,7 +28984,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29187,7 +29190,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29805,7 +29808,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30298,7 +30301,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ140">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR140">
         <v>1.34</v>
@@ -30423,7 +30426,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30501,7 +30504,7 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ141">
         <v>1.47</v>
@@ -30629,7 +30632,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30835,7 +30838,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31041,7 +31044,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31122,7 +31125,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ144">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR144">
         <v>1.75</v>
@@ -31328,7 +31331,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ145">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR145">
         <v>1.15</v>
@@ -31453,7 +31456,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31534,7 +31537,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ146">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR146">
         <v>1.62</v>
@@ -31865,7 +31868,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32149,7 +32152,7 @@
         <v>1</v>
       </c>
       <c r="AP149">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ149">
         <v>1.5</v>
@@ -32355,7 +32358,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ150">
         <v>0.64</v>
@@ -32895,7 +32898,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32976,7 +32979,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ153">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR153">
         <v>1.58</v>
@@ -33179,7 +33182,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ154">
         <v>1.15</v>
@@ -33513,7 +33516,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33797,7 +33800,7 @@
         <v>0.17</v>
       </c>
       <c r="AP157">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ157">
         <v>1.13</v>
@@ -34418,7 +34421,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ160">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34830,7 +34833,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ162">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR162">
         <v>1.47</v>
@@ -35161,7 +35164,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35779,7 +35782,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36191,7 +36194,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36269,7 +36272,7 @@
         <v>0.29</v>
       </c>
       <c r="AP169">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ169">
         <v>0.21</v>
@@ -36475,7 +36478,7 @@
         <v>1.29</v>
       </c>
       <c r="AP170">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36684,7 +36687,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ171">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR171">
         <v>1.18</v>
@@ -36809,7 +36812,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -36890,7 +36893,7 @@
         <v>2</v>
       </c>
       <c r="AQ172">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR172">
         <v>1.15</v>
@@ -37093,7 +37096,7 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ173">
         <v>1.5</v>
@@ -37427,7 +37430,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37505,7 +37508,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ175">
         <v>1</v>
@@ -37839,7 +37842,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -37920,7 +37923,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ177">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR177">
         <v>1.68</v>
@@ -38251,7 +38254,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38457,7 +38460,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38535,7 +38538,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ180">
         <v>1.36</v>
@@ -38744,7 +38747,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ181">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR181">
         <v>1.48</v>
@@ -39281,7 +39284,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39359,7 +39362,7 @@
         <v>0.88</v>
       </c>
       <c r="AP184">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ184">
         <v>0.92</v>
@@ -39980,7 +39983,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ187">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR187">
         <v>1.45</v>
@@ -40105,7 +40108,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40389,7 +40392,7 @@
         <v>1.13</v>
       </c>
       <c r="AP189">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ189">
         <v>1.31</v>
@@ -40723,7 +40726,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40801,7 +40804,7 @@
         <v>1.67</v>
       </c>
       <c r="AP191">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ191">
         <v>1.33</v>
@@ -40929,7 +40932,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41135,7 +41138,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41341,7 +41344,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41625,10 +41628,10 @@
         <v>1.75</v>
       </c>
       <c r="AP195">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ195">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR195">
         <v>1.66</v>
@@ -41834,7 +41837,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ196">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR196">
         <v>1.42</v>
@@ -42452,7 +42455,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ199">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR199">
         <v>1.74</v>
@@ -42577,7 +42580,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42655,7 +42658,7 @@
         <v>0.11</v>
       </c>
       <c r="AP200">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ200">
         <v>1.13</v>
@@ -42861,7 +42864,7 @@
         <v>1.22</v>
       </c>
       <c r="AP201">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ201">
         <v>0.93</v>
@@ -42989,7 +42992,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43070,7 +43073,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ202">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR202">
         <v>1.63</v>
@@ -43195,7 +43198,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43813,7 +43816,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44306,7 +44309,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ208">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR208">
         <v>1.46</v>
@@ -44512,7 +44515,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ209">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR209">
         <v>1.74</v>
@@ -44715,7 +44718,7 @@
         <v>1.22</v>
       </c>
       <c r="AP210">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ210">
         <v>1.43</v>
@@ -44843,7 +44846,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45049,7 +45052,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45255,7 +45258,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45461,7 +45464,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45748,7 +45751,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ215">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR215">
         <v>1.3</v>
@@ -45873,7 +45876,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -45951,7 +45954,7 @@
         <v>0.78</v>
       </c>
       <c r="AP216">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ216">
         <v>0.92</v>
@@ -46157,7 +46160,7 @@
         <v>2.44</v>
       </c>
       <c r="AP217">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ217">
         <v>1.93</v>
@@ -46363,10 +46366,10 @@
         <v>1.67</v>
       </c>
       <c r="AP218">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ218">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR218">
         <v>1.41</v>
@@ -47109,7 +47112,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47521,7 +47524,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47933,7 +47936,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48426,7 +48429,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ228">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR228">
         <v>1.5</v>
@@ -48551,7 +48554,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48629,10 +48632,10 @@
         <v>1.22</v>
       </c>
       <c r="AP229">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ229">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR229">
         <v>1.48</v>
@@ -48757,7 +48760,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48835,10 +48838,10 @@
         <v>1.3</v>
       </c>
       <c r="AP230">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ230">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR230">
         <v>1.54</v>
@@ -48963,7 +48966,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49456,7 +49459,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ233">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR233">
         <v>1.18</v>
@@ -49662,7 +49665,7 @@
         <v>2</v>
       </c>
       <c r="AQ234">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR234">
         <v>1.16</v>
@@ -49787,7 +49790,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -49865,7 +49868,7 @@
         <v>2.2</v>
       </c>
       <c r="AP235">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ235">
         <v>1.93</v>
@@ -50074,7 +50077,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ236">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR236">
         <v>1.23</v>
@@ -50611,7 +50614,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50895,7 +50898,7 @@
         <v>1.36</v>
       </c>
       <c r="AP240">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ240">
         <v>1.43</v>
@@ -51101,7 +51104,7 @@
         <v>1.45</v>
       </c>
       <c r="AP241">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ241">
         <v>1.33</v>
@@ -51229,7 +51232,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51641,7 +51644,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51847,7 +51850,7 @@
         <v>248</v>
       </c>
       <c r="P245" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q245">
         <v>2.9</v>
@@ -52337,7 +52340,7 @@
         <v>1.5</v>
       </c>
       <c r="AP247">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ247">
         <v>1.46</v>
@@ -52877,7 +52880,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53083,7 +53086,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53370,7 +53373,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ252">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR252">
         <v>1.71</v>
@@ -53495,7 +53498,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53779,7 +53782,7 @@
         <v>0.73</v>
       </c>
       <c r="AP254">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ254">
         <v>0.64</v>
@@ -53907,7 +53910,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54113,7 +54116,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54191,7 +54194,7 @@
         <v>1.33</v>
       </c>
       <c r="AP256">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ256">
         <v>1.43</v>
@@ -54400,7 +54403,7 @@
         <v>2</v>
       </c>
       <c r="AQ257">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR257">
         <v>1.24</v>
@@ -54525,7 +54528,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -54606,7 +54609,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ258">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR258">
         <v>1.2</v>
@@ -55018,7 +55021,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ260">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR260">
         <v>1.59</v>
@@ -55143,7 +55146,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55221,7 +55224,7 @@
         <v>1.75</v>
       </c>
       <c r="AP261">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ261">
         <v>1.47</v>
@@ -55349,7 +55352,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55633,10 +55636,10 @@
         <v>1.27</v>
       </c>
       <c r="AP263">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ263">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR263">
         <v>1.43</v>
@@ -55967,7 +55970,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56791,7 +56794,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57078,7 +57081,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ270">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR270">
         <v>1.69</v>
@@ -57615,7 +57618,7 @@
         <v>94</v>
       </c>
       <c r="P273" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q273">
         <v>4</v>
@@ -58105,7 +58108,7 @@
         <v>0.91</v>
       </c>
       <c r="AP275">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ275">
         <v>1</v>
@@ -58311,7 +58314,7 @@
         <v>1.46</v>
       </c>
       <c r="AP276">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ276">
         <v>1.33</v>
@@ -58439,7 +58442,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58520,7 +58523,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ277">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR277">
         <v>1.22</v>
@@ -58726,7 +58729,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ278">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR278">
         <v>1.69</v>
@@ -59341,7 +59344,7 @@
         <v>0.25</v>
       </c>
       <c r="AP281">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ281">
         <v>0.21</v>
@@ -59469,7 +59472,7 @@
         <v>186</v>
       </c>
       <c r="P282" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59550,7 +59553,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ282">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR282">
         <v>1.67</v>
@@ -59881,7 +59884,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -59959,10 +59962,10 @@
         <v>0.54</v>
       </c>
       <c r="AP284">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ284">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR284">
         <v>1.39</v>
@@ -60165,7 +60168,7 @@
         <v>1.62</v>
       </c>
       <c r="AP285">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ285">
         <v>1.47</v>
@@ -60374,7 +60377,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ286">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR286">
         <v>1.59</v>
@@ -60499,7 +60502,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61117,7 +61120,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61323,7 +61326,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61607,7 +61610,7 @@
         <v>1</v>
       </c>
       <c r="AP292">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ292">
         <v>1</v>
@@ -61693,7 +61696,7 @@
         <v>292</v>
       </c>
       <c r="B293">
-        <v>7728494</v>
+        <v>7728843</v>
       </c>
       <c r="C293" t="s">
         <v>68</v>
@@ -61708,10 +61711,10 @@
         <v>27</v>
       </c>
       <c r="G293" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H293" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I293">
         <v>0</v>
@@ -61723,10 +61726,10 @@
         <v>0</v>
       </c>
       <c r="L293">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N293">
         <v>2</v>
@@ -61735,163 +61738,163 @@
         <v>273</v>
       </c>
       <c r="P293" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="Q293">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R293">
         <v>1.93</v>
       </c>
       <c r="S293">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="T293">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="U293">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="V293">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="W293">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X293">
+        <v>8.75</v>
+      </c>
+      <c r="Y293">
+        <v>1.06</v>
+      </c>
+      <c r="Z293">
+        <v>2.56</v>
+      </c>
+      <c r="AA293">
+        <v>3.28</v>
+      </c>
+      <c r="AB293">
+        <v>2.95</v>
+      </c>
+      <c r="AC293">
+        <v>1.09</v>
+      </c>
+      <c r="AD293">
+        <v>7</v>
+      </c>
+      <c r="AE293">
+        <v>1.44</v>
+      </c>
+      <c r="AF293">
+        <v>2.55</v>
+      </c>
+      <c r="AG293">
+        <v>1.95</v>
+      </c>
+      <c r="AH293">
+        <v>1.7</v>
+      </c>
+      <c r="AI293">
+        <v>1.95</v>
+      </c>
+      <c r="AJ293">
+        <v>1.75</v>
+      </c>
+      <c r="AK293">
+        <v>1.4</v>
+      </c>
+      <c r="AL293">
+        <v>1.36</v>
+      </c>
+      <c r="AM293">
+        <v>1.47</v>
+      </c>
+      <c r="AN293">
+        <v>1.15</v>
+      </c>
+      <c r="AO293">
+        <v>1.46</v>
+      </c>
+      <c r="AP293">
+        <v>1.29</v>
+      </c>
+      <c r="AQ293">
+        <v>1.36</v>
+      </c>
+      <c r="AR293">
+        <v>1.47</v>
+      </c>
+      <c r="AS293">
+        <v>1.32</v>
+      </c>
+      <c r="AT293">
+        <v>2.79</v>
+      </c>
+      <c r="AU293">
+        <v>8</v>
+      </c>
+      <c r="AV293">
+        <v>3</v>
+      </c>
+      <c r="AW293">
+        <v>13</v>
+      </c>
+      <c r="AX293">
+        <v>7</v>
+      </c>
+      <c r="AY293">
+        <v>25</v>
+      </c>
+      <c r="AZ293">
+        <v>12</v>
+      </c>
+      <c r="BA293">
+        <v>8</v>
+      </c>
+      <c r="BB293">
+        <v>1</v>
+      </c>
+      <c r="BC293">
         <v>9</v>
       </c>
-      <c r="Y293">
-        <v>1.01</v>
-      </c>
-      <c r="Z293">
-        <v>2.66</v>
-      </c>
-      <c r="AA293">
-        <v>2.9</v>
-      </c>
-      <c r="AB293">
-        <v>3.18</v>
-      </c>
-      <c r="AC293">
-        <v>1.11</v>
-      </c>
-      <c r="AD293">
-        <v>6.4</v>
-      </c>
-      <c r="AE293">
-        <v>1.48</v>
-      </c>
-      <c r="AF293">
-        <v>2.37</v>
-      </c>
-      <c r="AG293">
-        <v>2.44</v>
-      </c>
-      <c r="AH293">
-        <v>1.49</v>
-      </c>
-      <c r="AI293">
-        <v>2.07</v>
-      </c>
-      <c r="AJ293">
-        <v>1.68</v>
-      </c>
-      <c r="AK293">
-        <v>1.36</v>
-      </c>
-      <c r="AL293">
-        <v>1.37</v>
-      </c>
-      <c r="AM293">
-        <v>1.49</v>
-      </c>
-      <c r="AN293">
-        <v>2.08</v>
-      </c>
-      <c r="AO293">
+      <c r="BD293">
+        <v>1.72</v>
+      </c>
+      <c r="BE293">
+        <v>6.75</v>
+      </c>
+      <c r="BF293">
+        <v>2.33</v>
+      </c>
+      <c r="BG293">
+        <v>1.3</v>
+      </c>
+      <c r="BH293">
+        <v>3.05</v>
+      </c>
+      <c r="BI293">
+        <v>1.54</v>
+      </c>
+      <c r="BJ293">
+        <v>2.25</v>
+      </c>
+      <c r="BK293">
+        <v>1.87</v>
+      </c>
+      <c r="BL293">
+        <v>1.79</v>
+      </c>
+      <c r="BM293">
+        <v>2.35</v>
+      </c>
+      <c r="BN293">
         <v>1.5</v>
       </c>
-      <c r="AP293">
-        <v>2</v>
-      </c>
-      <c r="AQ293">
-        <v>1.46</v>
-      </c>
-      <c r="AR293">
-        <v>1.27</v>
-      </c>
-      <c r="AS293">
-        <v>1.17</v>
-      </c>
-      <c r="AT293">
-        <v>2.44</v>
-      </c>
-      <c r="AU293">
-        <v>4</v>
-      </c>
-      <c r="AV293">
-        <v>2</v>
-      </c>
-      <c r="AW293">
-        <v>7</v>
-      </c>
-      <c r="AX293">
-        <v>6</v>
-      </c>
-      <c r="AY293">
-        <v>13</v>
-      </c>
-      <c r="AZ293">
-        <v>8</v>
-      </c>
-      <c r="BA293">
-        <v>3</v>
-      </c>
-      <c r="BB293">
-        <v>7</v>
-      </c>
-      <c r="BC293">
-        <v>10</v>
-      </c>
-      <c r="BD293">
-        <v>1.74</v>
-      </c>
-      <c r="BE293">
-        <v>6.4</v>
-      </c>
-      <c r="BF293">
-        <v>2.32</v>
-      </c>
-      <c r="BG293">
-        <v>1.43</v>
-      </c>
-      <c r="BH293">
-        <v>2.55</v>
-      </c>
-      <c r="BI293">
-        <v>1.74</v>
-      </c>
-      <c r="BJ293">
-        <v>1.93</v>
-      </c>
-      <c r="BK293">
-        <v>2.2</v>
-      </c>
-      <c r="BL293">
-        <v>1.56</v>
-      </c>
-      <c r="BM293">
-        <v>2.9</v>
-      </c>
-      <c r="BN293">
-        <v>1.34</v>
-      </c>
       <c r="BO293">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="BP293">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="294" spans="1:68">
@@ -61899,7 +61902,7 @@
         <v>293</v>
       </c>
       <c r="B294">
-        <v>7728843</v>
+        <v>7728494</v>
       </c>
       <c r="C294" t="s">
         <v>68</v>
@@ -61914,10 +61917,10 @@
         <v>27</v>
       </c>
       <c r="G294" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H294" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I294">
         <v>0</v>
@@ -61929,10 +61932,10 @@
         <v>0</v>
       </c>
       <c r="L294">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N294">
         <v>2</v>
@@ -61941,163 +61944,163 @@
         <v>274</v>
       </c>
       <c r="P294" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="Q294">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R294">
         <v>1.93</v>
       </c>
       <c r="S294">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="T294">
+        <v>1.58</v>
+      </c>
+      <c r="U294">
+        <v>2.26</v>
+      </c>
+      <c r="V294">
+        <v>3.55</v>
+      </c>
+      <c r="W294">
+        <v>1.26</v>
+      </c>
+      <c r="X294">
+        <v>9</v>
+      </c>
+      <c r="Y294">
+        <v>1.01</v>
+      </c>
+      <c r="Z294">
+        <v>2.66</v>
+      </c>
+      <c r="AA294">
+        <v>2.9</v>
+      </c>
+      <c r="AB294">
+        <v>3.18</v>
+      </c>
+      <c r="AC294">
+        <v>1.11</v>
+      </c>
+      <c r="AD294">
+        <v>6.4</v>
+      </c>
+      <c r="AE294">
+        <v>1.48</v>
+      </c>
+      <c r="AF294">
+        <v>2.37</v>
+      </c>
+      <c r="AG294">
+        <v>2.44</v>
+      </c>
+      <c r="AH294">
         <v>1.49</v>
       </c>
-      <c r="U294">
-        <v>2.4</v>
-      </c>
-      <c r="V294">
-        <v>3.2</v>
-      </c>
-      <c r="W294">
-        <v>1.3</v>
-      </c>
-      <c r="X294">
-        <v>8.75</v>
-      </c>
-      <c r="Y294">
-        <v>1.06</v>
-      </c>
-      <c r="Z294">
-        <v>2.56</v>
-      </c>
-      <c r="AA294">
-        <v>3.28</v>
-      </c>
-      <c r="AB294">
-        <v>2.95</v>
-      </c>
-      <c r="AC294">
-        <v>1.09</v>
-      </c>
-      <c r="AD294">
+      <c r="AI294">
+        <v>2.07</v>
+      </c>
+      <c r="AJ294">
+        <v>1.68</v>
+      </c>
+      <c r="AK294">
+        <v>1.36</v>
+      </c>
+      <c r="AL294">
+        <v>1.37</v>
+      </c>
+      <c r="AM294">
+        <v>1.49</v>
+      </c>
+      <c r="AN294">
+        <v>2.08</v>
+      </c>
+      <c r="AO294">
+        <v>1.5</v>
+      </c>
+      <c r="AP294">
+        <v>2</v>
+      </c>
+      <c r="AQ294">
+        <v>1.46</v>
+      </c>
+      <c r="AR294">
+        <v>1.27</v>
+      </c>
+      <c r="AS294">
+        <v>1.17</v>
+      </c>
+      <c r="AT294">
+        <v>2.44</v>
+      </c>
+      <c r="AU294">
+        <v>4</v>
+      </c>
+      <c r="AV294">
+        <v>2</v>
+      </c>
+      <c r="AW294">
         <v>7</v>
       </c>
-      <c r="AE294">
-        <v>1.44</v>
-      </c>
-      <c r="AF294">
+      <c r="AX294">
+        <v>6</v>
+      </c>
+      <c r="AY294">
+        <v>13</v>
+      </c>
+      <c r="AZ294">
+        <v>8</v>
+      </c>
+      <c r="BA294">
+        <v>3</v>
+      </c>
+      <c r="BB294">
+        <v>7</v>
+      </c>
+      <c r="BC294">
+        <v>10</v>
+      </c>
+      <c r="BD294">
+        <v>1.74</v>
+      </c>
+      <c r="BE294">
+        <v>6.4</v>
+      </c>
+      <c r="BF294">
+        <v>2.32</v>
+      </c>
+      <c r="BG294">
+        <v>1.43</v>
+      </c>
+      <c r="BH294">
         <v>2.55</v>
       </c>
-      <c r="AG294">
-        <v>1.95</v>
-      </c>
-      <c r="AH294">
-        <v>1.7</v>
-      </c>
-      <c r="AI294">
-        <v>1.95</v>
-      </c>
-      <c r="AJ294">
-        <v>1.75</v>
-      </c>
-      <c r="AK294">
-        <v>1.4</v>
-      </c>
-      <c r="AL294">
-        <v>1.36</v>
-      </c>
-      <c r="AM294">
-        <v>1.47</v>
-      </c>
-      <c r="AN294">
-        <v>1.15</v>
-      </c>
-      <c r="AO294">
-        <v>1.46</v>
-      </c>
-      <c r="AP294">
-        <v>1.29</v>
-      </c>
-      <c r="AQ294">
-        <v>1.36</v>
-      </c>
-      <c r="AR294">
-        <v>1.47</v>
-      </c>
-      <c r="AS294">
-        <v>1.32</v>
-      </c>
-      <c r="AT294">
-        <v>2.79</v>
-      </c>
-      <c r="AU294">
-        <v>8</v>
-      </c>
-      <c r="AV294">
-        <v>3</v>
-      </c>
-      <c r="AW294">
-        <v>13</v>
-      </c>
-      <c r="AX294">
-        <v>7</v>
-      </c>
-      <c r="AY294">
-        <v>25</v>
-      </c>
-      <c r="AZ294">
-        <v>12</v>
-      </c>
-      <c r="BA294">
-        <v>8</v>
-      </c>
-      <c r="BB294">
-        <v>1</v>
-      </c>
-      <c r="BC294">
-        <v>9</v>
-      </c>
-      <c r="BD294">
-        <v>1.72</v>
-      </c>
-      <c r="BE294">
-        <v>6.75</v>
-      </c>
-      <c r="BF294">
-        <v>2.33</v>
-      </c>
-      <c r="BG294">
-        <v>1.3</v>
-      </c>
-      <c r="BH294">
-        <v>3.05</v>
-      </c>
       <c r="BI294">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BJ294">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="BK294">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="BL294">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="BM294">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="BN294">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="BO294">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="BP294">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="295" spans="1:68">
@@ -63135,7 +63138,7 @@
         <v>299</v>
       </c>
       <c r="B300">
-        <v>7728844</v>
+        <v>7728498</v>
       </c>
       <c r="C300" t="s">
         <v>68</v>
@@ -63150,10 +63153,10 @@
         <v>28</v>
       </c>
       <c r="G300" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H300" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I300">
         <v>1</v>
@@ -63165,175 +63168,175 @@
         <v>2</v>
       </c>
       <c r="L300">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M300">
         <v>2</v>
       </c>
       <c r="N300">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O300" t="s">
-        <v>147</v>
+        <v>278</v>
       </c>
       <c r="P300" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q300">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="R300">
+        <v>2.12</v>
+      </c>
+      <c r="S300">
+        <v>3.9</v>
+      </c>
+      <c r="T300">
+        <v>1.43</v>
+      </c>
+      <c r="U300">
+        <v>2.65</v>
+      </c>
+      <c r="V300">
+        <v>2.85</v>
+      </c>
+      <c r="W300">
+        <v>1.37</v>
+      </c>
+      <c r="X300">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y300">
+        <v>1.02</v>
+      </c>
+      <c r="Z300">
+        <v>2.34</v>
+      </c>
+      <c r="AA300">
+        <v>3.36</v>
+      </c>
+      <c r="AB300">
+        <v>3.23</v>
+      </c>
+      <c r="AC300">
+        <v>1.06</v>
+      </c>
+      <c r="AD300">
+        <v>8.5</v>
+      </c>
+      <c r="AE300">
+        <v>1.33</v>
+      </c>
+      <c r="AF300">
+        <v>3.05</v>
+      </c>
+      <c r="AG300">
+        <v>2.02</v>
+      </c>
+      <c r="AH300">
         <v>1.8</v>
       </c>
-      <c r="S300">
-        <v>3.5</v>
-      </c>
-      <c r="T300">
-        <v>1.62</v>
-      </c>
-      <c r="U300">
-        <v>2.15</v>
-      </c>
-      <c r="V300">
-        <v>3.9</v>
-      </c>
-      <c r="W300">
-        <v>1.22</v>
-      </c>
-      <c r="X300">
-        <v>11.5</v>
-      </c>
-      <c r="Y300">
-        <v>1.03</v>
-      </c>
-      <c r="Z300">
-        <v>2.91</v>
-      </c>
-      <c r="AA300">
-        <v>2.95</v>
-      </c>
-      <c r="AB300">
-        <v>2.84</v>
-      </c>
-      <c r="AC300">
-        <v>1.12</v>
-      </c>
-      <c r="AD300">
-        <v>5.75</v>
-      </c>
-      <c r="AE300">
-        <v>1.57</v>
-      </c>
-      <c r="AF300">
-        <v>2.25</v>
-      </c>
-      <c r="AG300">
-        <v>2.37</v>
-      </c>
-      <c r="AH300">
-        <v>1.48</v>
-      </c>
       <c r="AI300">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AJ300">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AK300">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL300">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AM300">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AN300">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AO300">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="AP300">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ300">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AR300">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AS300">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AT300">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AU300">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV300">
         <v>5</v>
       </c>
       <c r="AW300">
+        <v>6</v>
+      </c>
+      <c r="AX300">
+        <v>10</v>
+      </c>
+      <c r="AY300">
+        <v>13</v>
+      </c>
+      <c r="AZ300">
+        <v>19</v>
+      </c>
+      <c r="BA300">
+        <v>2</v>
+      </c>
+      <c r="BB300">
         <v>3</v>
       </c>
-      <c r="AX300">
-        <v>4</v>
-      </c>
-      <c r="AY300">
-        <v>9</v>
-      </c>
-      <c r="AZ300">
-        <v>11</v>
-      </c>
-      <c r="BA300">
-        <v>4</v>
-      </c>
-      <c r="BB300">
-        <v>2</v>
-      </c>
       <c r="BC300">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD300">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="BE300">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF300">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="BG300">
+        <v>1.36</v>
+      </c>
+      <c r="BH300">
+        <v>2.8</v>
+      </c>
+      <c r="BI300">
+        <v>1.63</v>
+      </c>
+      <c r="BJ300">
+        <v>2.08</v>
+      </c>
+      <c r="BK300">
+        <v>2.04</v>
+      </c>
+      <c r="BL300">
+        <v>1.66</v>
+      </c>
+      <c r="BM300">
+        <v>2.6</v>
+      </c>
+      <c r="BN300">
         <v>1.41</v>
       </c>
-      <c r="BH300">
-        <v>2.6</v>
-      </c>
-      <c r="BI300">
-        <v>1.7</v>
-      </c>
-      <c r="BJ300">
-        <v>1.98</v>
-      </c>
-      <c r="BK300">
-        <v>2.14</v>
-      </c>
-      <c r="BL300">
-        <v>1.6</v>
-      </c>
-      <c r="BM300">
-        <v>2.8</v>
-      </c>
-      <c r="BN300">
-        <v>1.36</v>
-      </c>
       <c r="BO300">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BP300">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="301" spans="1:68">
@@ -63341,7 +63344,7 @@
         <v>300</v>
       </c>
       <c r="B301">
-        <v>7728498</v>
+        <v>7728844</v>
       </c>
       <c r="C301" t="s">
         <v>68</v>
@@ -63356,10 +63359,10 @@
         <v>28</v>
       </c>
       <c r="G301" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H301" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I301">
         <v>1</v>
@@ -63371,175 +63374,175 @@
         <v>2</v>
       </c>
       <c r="L301">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M301">
         <v>2</v>
       </c>
       <c r="N301">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O301" t="s">
-        <v>278</v>
+        <v>147</v>
       </c>
       <c r="P301" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q301">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="R301">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="S301">
+        <v>3.5</v>
+      </c>
+      <c r="T301">
+        <v>1.62</v>
+      </c>
+      <c r="U301">
+        <v>2.15</v>
+      </c>
+      <c r="V301">
         <v>3.9</v>
       </c>
-      <c r="T301">
-        <v>1.43</v>
-      </c>
-      <c r="U301">
-        <v>2.65</v>
-      </c>
-      <c r="V301">
-        <v>2.85</v>
-      </c>
       <c r="W301">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="X301">
-        <v>8.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Y301">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z301">
-        <v>2.34</v>
+        <v>2.91</v>
       </c>
       <c r="AA301">
-        <v>3.36</v>
+        <v>2.95</v>
       </c>
       <c r="AB301">
-        <v>3.23</v>
+        <v>2.84</v>
       </c>
       <c r="AC301">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AD301">
-        <v>8.5</v>
+        <v>5.75</v>
       </c>
       <c r="AE301">
+        <v>1.57</v>
+      </c>
+      <c r="AF301">
+        <v>2.25</v>
+      </c>
+      <c r="AG301">
+        <v>2.37</v>
+      </c>
+      <c r="AH301">
+        <v>1.48</v>
+      </c>
+      <c r="AI301">
+        <v>2.2</v>
+      </c>
+      <c r="AJ301">
+        <v>1.6</v>
+      </c>
+      <c r="AK301">
+        <v>1.44</v>
+      </c>
+      <c r="AL301">
+        <v>1.39</v>
+      </c>
+      <c r="AM301">
+        <v>1.4</v>
+      </c>
+      <c r="AN301">
+        <v>1.62</v>
+      </c>
+      <c r="AO301">
+        <v>1.38</v>
+      </c>
+      <c r="AP301">
+        <v>1.5</v>
+      </c>
+      <c r="AQ301">
+        <v>1.5</v>
+      </c>
+      <c r="AR301">
+        <v>1.42</v>
+      </c>
+      <c r="AS301">
         <v>1.33</v>
       </c>
-      <c r="AF301">
-        <v>3.05</v>
-      </c>
-      <c r="AG301">
-        <v>2.02</v>
-      </c>
-      <c r="AH301">
-        <v>1.8</v>
-      </c>
-      <c r="AI301">
-        <v>1.79</v>
-      </c>
-      <c r="AJ301">
-        <v>1.93</v>
-      </c>
-      <c r="AK301">
-        <v>1.32</v>
-      </c>
-      <c r="AL301">
-        <v>1.3</v>
-      </c>
-      <c r="AM301">
-        <v>1.63</v>
-      </c>
-      <c r="AN301">
-        <v>1.85</v>
-      </c>
-      <c r="AO301">
-        <v>2</v>
-      </c>
-      <c r="AP301">
-        <v>1.79</v>
-      </c>
-      <c r="AQ301">
-        <v>1.93</v>
-      </c>
-      <c r="AR301">
-        <v>1.54</v>
-      </c>
-      <c r="AS301">
-        <v>1.34</v>
-      </c>
       <c r="AT301">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AU301">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV301">
         <v>5</v>
       </c>
       <c r="AW301">
+        <v>3</v>
+      </c>
+      <c r="AX301">
+        <v>4</v>
+      </c>
+      <c r="AY301">
+        <v>9</v>
+      </c>
+      <c r="AZ301">
+        <v>11</v>
+      </c>
+      <c r="BA301">
+        <v>4</v>
+      </c>
+      <c r="BB301">
+        <v>2</v>
+      </c>
+      <c r="BC301">
         <v>6</v>
       </c>
-      <c r="AX301">
-        <v>10</v>
-      </c>
-      <c r="AY301">
-        <v>13</v>
-      </c>
-      <c r="AZ301">
-        <v>19</v>
-      </c>
-      <c r="BA301">
-        <v>2</v>
-      </c>
-      <c r="BB301">
-        <v>3</v>
-      </c>
-      <c r="BC301">
-        <v>5</v>
-      </c>
       <c r="BD301">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BE301">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF301">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="BG301">
+        <v>1.41</v>
+      </c>
+      <c r="BH301">
+        <v>2.6</v>
+      </c>
+      <c r="BI301">
+        <v>1.7</v>
+      </c>
+      <c r="BJ301">
+        <v>1.98</v>
+      </c>
+      <c r="BK301">
+        <v>2.14</v>
+      </c>
+      <c r="BL301">
+        <v>1.6</v>
+      </c>
+      <c r="BM301">
+        <v>2.8</v>
+      </c>
+      <c r="BN301">
         <v>1.36</v>
       </c>
-      <c r="BH301">
-        <v>2.8</v>
-      </c>
-      <c r="BI301">
-        <v>1.63</v>
-      </c>
-      <c r="BJ301">
-        <v>2.08</v>
-      </c>
-      <c r="BK301">
-        <v>2.04</v>
-      </c>
-      <c r="BL301">
-        <v>1.66</v>
-      </c>
-      <c r="BM301">
-        <v>2.6</v>
-      </c>
-      <c r="BN301">
-        <v>1.41</v>
-      </c>
       <c r="BO301">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BP301">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="302" spans="1:68">
@@ -63589,7 +63592,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -63952,6 +63955,1036 @@
       </c>
       <c r="BP303">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="304" spans="1:68">
+      <c r="A304" s="1">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>7728497</v>
+      </c>
+      <c r="C304" t="s">
+        <v>68</v>
+      </c>
+      <c r="D304" t="s">
+        <v>69</v>
+      </c>
+      <c r="E304" s="2">
+        <v>45711.41666666666</v>
+      </c>
+      <c r="F304">
+        <v>28</v>
+      </c>
+      <c r="G304" t="s">
+        <v>75</v>
+      </c>
+      <c r="H304" t="s">
+        <v>81</v>
+      </c>
+      <c r="I304">
+        <v>0</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304">
+        <v>0</v>
+      </c>
+      <c r="L304">
+        <v>0</v>
+      </c>
+      <c r="M304">
+        <v>0</v>
+      </c>
+      <c r="N304">
+        <v>0</v>
+      </c>
+      <c r="O304" t="s">
+        <v>94</v>
+      </c>
+      <c r="P304" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q304">
+        <v>2.65</v>
+      </c>
+      <c r="R304">
+        <v>2.02</v>
+      </c>
+      <c r="S304">
+        <v>4.7</v>
+      </c>
+      <c r="T304">
+        <v>1.51</v>
+      </c>
+      <c r="U304">
+        <v>2.4</v>
+      </c>
+      <c r="V304">
+        <v>3.25</v>
+      </c>
+      <c r="W304">
+        <v>1.3</v>
+      </c>
+      <c r="X304">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y304">
+        <v>1.02</v>
+      </c>
+      <c r="Z304">
+        <v>1.99</v>
+      </c>
+      <c r="AA304">
+        <v>3.41</v>
+      </c>
+      <c r="AB304">
+        <v>4.2</v>
+      </c>
+      <c r="AC304">
+        <v>1.09</v>
+      </c>
+      <c r="AD304">
+        <v>7</v>
+      </c>
+      <c r="AE304">
+        <v>1.42</v>
+      </c>
+      <c r="AF304">
+        <v>2.6</v>
+      </c>
+      <c r="AG304">
+        <v>2.25</v>
+      </c>
+      <c r="AH304">
+        <v>1.53</v>
+      </c>
+      <c r="AI304">
+        <v>2.02</v>
+      </c>
+      <c r="AJ304">
+        <v>1.72</v>
+      </c>
+      <c r="AK304">
+        <v>1.24</v>
+      </c>
+      <c r="AL304">
+        <v>1.31</v>
+      </c>
+      <c r="AM304">
+        <v>1.75</v>
+      </c>
+      <c r="AN304">
+        <v>1.23</v>
+      </c>
+      <c r="AO304">
+        <v>1.5</v>
+      </c>
+      <c r="AP304">
+        <v>1.21</v>
+      </c>
+      <c r="AQ304">
+        <v>1.47</v>
+      </c>
+      <c r="AR304">
+        <v>1.51</v>
+      </c>
+      <c r="AS304">
+        <v>1.05</v>
+      </c>
+      <c r="AT304">
+        <v>2.56</v>
+      </c>
+      <c r="AU304">
+        <v>8</v>
+      </c>
+      <c r="AV304">
+        <v>3</v>
+      </c>
+      <c r="AW304">
+        <v>12</v>
+      </c>
+      <c r="AX304">
+        <v>2</v>
+      </c>
+      <c r="AY304">
+        <v>22</v>
+      </c>
+      <c r="AZ304">
+        <v>5</v>
+      </c>
+      <c r="BA304">
+        <v>7</v>
+      </c>
+      <c r="BB304">
+        <v>0</v>
+      </c>
+      <c r="BC304">
+        <v>7</v>
+      </c>
+      <c r="BD304">
+        <v>1.49</v>
+      </c>
+      <c r="BE304">
+        <v>6.75</v>
+      </c>
+      <c r="BF304">
+        <v>2.9</v>
+      </c>
+      <c r="BG304">
+        <v>1.29</v>
+      </c>
+      <c r="BH304">
+        <v>3.15</v>
+      </c>
+      <c r="BI304">
+        <v>1.49</v>
+      </c>
+      <c r="BJ304">
+        <v>2.38</v>
+      </c>
+      <c r="BK304">
+        <v>1.8</v>
+      </c>
+      <c r="BL304">
+        <v>1.86</v>
+      </c>
+      <c r="BM304">
+        <v>2.25</v>
+      </c>
+      <c r="BN304">
+        <v>1.54</v>
+      </c>
+      <c r="BO304">
+        <v>2.9</v>
+      </c>
+      <c r="BP304">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="305" spans="1:68">
+      <c r="A305" s="1">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>7728503</v>
+      </c>
+      <c r="C305" t="s">
+        <v>68</v>
+      </c>
+      <c r="D305" t="s">
+        <v>69</v>
+      </c>
+      <c r="E305" s="2">
+        <v>45711.51041666666</v>
+      </c>
+      <c r="F305">
+        <v>28</v>
+      </c>
+      <c r="G305" t="s">
+        <v>79</v>
+      </c>
+      <c r="H305" t="s">
+        <v>87</v>
+      </c>
+      <c r="I305">
+        <v>0</v>
+      </c>
+      <c r="J305">
+        <v>0</v>
+      </c>
+      <c r="K305">
+        <v>0</v>
+      </c>
+      <c r="L305">
+        <v>2</v>
+      </c>
+      <c r="M305">
+        <v>1</v>
+      </c>
+      <c r="N305">
+        <v>3</v>
+      </c>
+      <c r="O305" t="s">
+        <v>280</v>
+      </c>
+      <c r="P305" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q305">
+        <v>1.73</v>
+      </c>
+      <c r="R305">
+        <v>2.4</v>
+      </c>
+      <c r="S305">
+        <v>12</v>
+      </c>
+      <c r="T305">
+        <v>1.36</v>
+      </c>
+      <c r="U305">
+        <v>3</v>
+      </c>
+      <c r="V305">
+        <v>2.75</v>
+      </c>
+      <c r="W305">
+        <v>1.4</v>
+      </c>
+      <c r="X305">
+        <v>8</v>
+      </c>
+      <c r="Y305">
+        <v>1.08</v>
+      </c>
+      <c r="Z305">
+        <v>1.25</v>
+      </c>
+      <c r="AA305">
+        <v>6</v>
+      </c>
+      <c r="AB305">
+        <v>14</v>
+      </c>
+      <c r="AC305">
+        <v>1.05</v>
+      </c>
+      <c r="AD305">
+        <v>9.5</v>
+      </c>
+      <c r="AE305">
+        <v>1.28</v>
+      </c>
+      <c r="AF305">
+        <v>3.55</v>
+      </c>
+      <c r="AG305">
+        <v>1.92</v>
+      </c>
+      <c r="AH305">
+        <v>1.89</v>
+      </c>
+      <c r="AI305">
+        <v>2.63</v>
+      </c>
+      <c r="AJ305">
+        <v>1.44</v>
+      </c>
+      <c r="AK305">
+        <v>1.03</v>
+      </c>
+      <c r="AL305">
+        <v>1.14</v>
+      </c>
+      <c r="AM305">
+        <v>3.8</v>
+      </c>
+      <c r="AN305">
+        <v>2.29</v>
+      </c>
+      <c r="AO305">
+        <v>0.5</v>
+      </c>
+      <c r="AP305">
+        <v>2.33</v>
+      </c>
+      <c r="AQ305">
+        <v>0.47</v>
+      </c>
+      <c r="AR305">
+        <v>1.62</v>
+      </c>
+      <c r="AS305">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT305">
+        <v>2.56</v>
+      </c>
+      <c r="AU305">
+        <v>11</v>
+      </c>
+      <c r="AV305">
+        <v>2</v>
+      </c>
+      <c r="AW305">
+        <v>9</v>
+      </c>
+      <c r="AX305">
+        <v>8</v>
+      </c>
+      <c r="AY305">
+        <v>21</v>
+      </c>
+      <c r="AZ305">
+        <v>11</v>
+      </c>
+      <c r="BA305">
+        <v>10</v>
+      </c>
+      <c r="BB305">
+        <v>3</v>
+      </c>
+      <c r="BC305">
+        <v>13</v>
+      </c>
+      <c r="BD305">
+        <v>1.13</v>
+      </c>
+      <c r="BE305">
+        <v>9.5</v>
+      </c>
+      <c r="BF305">
+        <v>6.4</v>
+      </c>
+      <c r="BG305">
+        <v>1.4</v>
+      </c>
+      <c r="BH305">
+        <v>2.65</v>
+      </c>
+      <c r="BI305">
+        <v>1.66</v>
+      </c>
+      <c r="BJ305">
+        <v>2.04</v>
+      </c>
+      <c r="BK305">
+        <v>2.04</v>
+      </c>
+      <c r="BL305">
+        <v>1.66</v>
+      </c>
+      <c r="BM305">
+        <v>2.63</v>
+      </c>
+      <c r="BN305">
+        <v>1.41</v>
+      </c>
+      <c r="BO305">
+        <v>3.4</v>
+      </c>
+      <c r="BP305">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="306" spans="1:68">
+      <c r="A306" s="1">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>7728495</v>
+      </c>
+      <c r="C306" t="s">
+        <v>68</v>
+      </c>
+      <c r="D306" t="s">
+        <v>69</v>
+      </c>
+      <c r="E306" s="2">
+        <v>45711.60416666666</v>
+      </c>
+      <c r="F306">
+        <v>28</v>
+      </c>
+      <c r="G306" t="s">
+        <v>85</v>
+      </c>
+      <c r="H306" t="s">
+        <v>80</v>
+      </c>
+      <c r="I306">
+        <v>0</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306">
+        <v>0</v>
+      </c>
+      <c r="L306">
+        <v>0</v>
+      </c>
+      <c r="M306">
+        <v>1</v>
+      </c>
+      <c r="N306">
+        <v>1</v>
+      </c>
+      <c r="O306" t="s">
+        <v>94</v>
+      </c>
+      <c r="P306" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q306">
+        <v>2.62</v>
+      </c>
+      <c r="R306">
+        <v>2</v>
+      </c>
+      <c r="S306">
+        <v>4.2</v>
+      </c>
+      <c r="T306">
+        <v>1.45</v>
+      </c>
+      <c r="U306">
+        <v>2.55</v>
+      </c>
+      <c r="V306">
+        <v>3</v>
+      </c>
+      <c r="W306">
+        <v>1.33</v>
+      </c>
+      <c r="X306">
+        <v>8.1</v>
+      </c>
+      <c r="Y306">
+        <v>1.02</v>
+      </c>
+      <c r="Z306">
+        <v>2.05</v>
+      </c>
+      <c r="AA306">
+        <v>3.37</v>
+      </c>
+      <c r="AB306">
+        <v>4</v>
+      </c>
+      <c r="AC306">
+        <v>1.08</v>
+      </c>
+      <c r="AD306">
+        <v>7.5</v>
+      </c>
+      <c r="AE306">
+        <v>1.4</v>
+      </c>
+      <c r="AF306">
+        <v>2.9</v>
+      </c>
+      <c r="AG306">
+        <v>2.1</v>
+      </c>
+      <c r="AH306">
+        <v>1.6</v>
+      </c>
+      <c r="AI306">
+        <v>1.9</v>
+      </c>
+      <c r="AJ306">
+        <v>1.77</v>
+      </c>
+      <c r="AK306">
+        <v>1.25</v>
+      </c>
+      <c r="AL306">
+        <v>1.28</v>
+      </c>
+      <c r="AM306">
+        <v>1.75</v>
+      </c>
+      <c r="AN306">
+        <v>1.62</v>
+      </c>
+      <c r="AO306">
+        <v>0.77</v>
+      </c>
+      <c r="AP306">
+        <v>1.5</v>
+      </c>
+      <c r="AQ306">
+        <v>0.93</v>
+      </c>
+      <c r="AR306">
+        <v>1.53</v>
+      </c>
+      <c r="AS306">
+        <v>1.11</v>
+      </c>
+      <c r="AT306">
+        <v>2.64</v>
+      </c>
+      <c r="AU306">
+        <v>5</v>
+      </c>
+      <c r="AV306">
+        <v>4</v>
+      </c>
+      <c r="AW306">
+        <v>7</v>
+      </c>
+      <c r="AX306">
+        <v>10</v>
+      </c>
+      <c r="AY306">
+        <v>15</v>
+      </c>
+      <c r="AZ306">
+        <v>18</v>
+      </c>
+      <c r="BA306">
+        <v>4</v>
+      </c>
+      <c r="BB306">
+        <v>7</v>
+      </c>
+      <c r="BC306">
+        <v>11</v>
+      </c>
+      <c r="BD306">
+        <v>1.61</v>
+      </c>
+      <c r="BE306">
+        <v>6.4</v>
+      </c>
+      <c r="BF306">
+        <v>2.55</v>
+      </c>
+      <c r="BG306">
+        <v>1.36</v>
+      </c>
+      <c r="BH306">
+        <v>2.8</v>
+      </c>
+      <c r="BI306">
+        <v>1.62</v>
+      </c>
+      <c r="BJ306">
+        <v>2.1</v>
+      </c>
+      <c r="BK306">
+        <v>2</v>
+      </c>
+      <c r="BL306">
+        <v>1.68</v>
+      </c>
+      <c r="BM306">
+        <v>2.55</v>
+      </c>
+      <c r="BN306">
+        <v>1.42</v>
+      </c>
+      <c r="BO306">
+        <v>3.4</v>
+      </c>
+      <c r="BP306">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="307" spans="1:68">
+      <c r="A307" s="1">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>7728500</v>
+      </c>
+      <c r="C307" t="s">
+        <v>68</v>
+      </c>
+      <c r="D307" t="s">
+        <v>69</v>
+      </c>
+      <c r="E307" s="2">
+        <v>45711.60416666666</v>
+      </c>
+      <c r="F307">
+        <v>28</v>
+      </c>
+      <c r="G307" t="s">
+        <v>82</v>
+      </c>
+      <c r="H307" t="s">
+        <v>71</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
+        <v>0</v>
+      </c>
+      <c r="K307">
+        <v>0</v>
+      </c>
+      <c r="L307">
+        <v>1</v>
+      </c>
+      <c r="M307">
+        <v>0</v>
+      </c>
+      <c r="N307">
+        <v>1</v>
+      </c>
+      <c r="O307" t="s">
+        <v>137</v>
+      </c>
+      <c r="P307" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q307">
+        <v>2.45</v>
+      </c>
+      <c r="R307">
+        <v>2.1</v>
+      </c>
+      <c r="S307">
+        <v>4.33</v>
+      </c>
+      <c r="T307">
+        <v>1.42</v>
+      </c>
+      <c r="U307">
+        <v>2.65</v>
+      </c>
+      <c r="V307">
+        <v>2.9</v>
+      </c>
+      <c r="W307">
+        <v>1.36</v>
+      </c>
+      <c r="X307">
+        <v>7.2</v>
+      </c>
+      <c r="Y307">
+        <v>1.03</v>
+      </c>
+      <c r="Z307">
+        <v>2.03</v>
+      </c>
+      <c r="AA307">
+        <v>3.45</v>
+      </c>
+      <c r="AB307">
+        <v>3.98</v>
+      </c>
+      <c r="AC307">
+        <v>1.06</v>
+      </c>
+      <c r="AD307">
+        <v>8.5</v>
+      </c>
+      <c r="AE307">
+        <v>1.36</v>
+      </c>
+      <c r="AF307">
+        <v>3.1</v>
+      </c>
+      <c r="AG307">
+        <v>2.01</v>
+      </c>
+      <c r="AH307">
+        <v>1.81</v>
+      </c>
+      <c r="AI307">
+        <v>1.85</v>
+      </c>
+      <c r="AJ307">
+        <v>1.83</v>
+      </c>
+      <c r="AK307">
+        <v>1.22</v>
+      </c>
+      <c r="AL307">
+        <v>1.28</v>
+      </c>
+      <c r="AM307">
+        <v>1.77</v>
+      </c>
+      <c r="AN307">
+        <v>1.85</v>
+      </c>
+      <c r="AO307">
+        <v>1.15</v>
+      </c>
+      <c r="AP307">
+        <v>1.93</v>
+      </c>
+      <c r="AQ307">
+        <v>1.07</v>
+      </c>
+      <c r="AR307">
+        <v>1.68</v>
+      </c>
+      <c r="AS307">
+        <v>1.16</v>
+      </c>
+      <c r="AT307">
+        <v>2.84</v>
+      </c>
+      <c r="AU307">
+        <v>3</v>
+      </c>
+      <c r="AV307">
+        <v>3</v>
+      </c>
+      <c r="AW307">
+        <v>9</v>
+      </c>
+      <c r="AX307">
+        <v>9</v>
+      </c>
+      <c r="AY307">
+        <v>16</v>
+      </c>
+      <c r="AZ307">
+        <v>15</v>
+      </c>
+      <c r="BA307">
+        <v>5</v>
+      </c>
+      <c r="BB307">
+        <v>5</v>
+      </c>
+      <c r="BC307">
+        <v>10</v>
+      </c>
+      <c r="BD307">
+        <v>1.6</v>
+      </c>
+      <c r="BE307">
+        <v>6.75</v>
+      </c>
+      <c r="BF307">
+        <v>2.55</v>
+      </c>
+      <c r="BG307">
+        <v>1.33</v>
+      </c>
+      <c r="BH307">
+        <v>2.95</v>
+      </c>
+      <c r="BI307">
+        <v>1.56</v>
+      </c>
+      <c r="BJ307">
+        <v>2.23</v>
+      </c>
+      <c r="BK307">
+        <v>1.9</v>
+      </c>
+      <c r="BL307">
+        <v>1.77</v>
+      </c>
+      <c r="BM307">
+        <v>2.4</v>
+      </c>
+      <c r="BN307">
+        <v>1.48</v>
+      </c>
+      <c r="BO307">
+        <v>3.15</v>
+      </c>
+      <c r="BP307">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="308" spans="1:68">
+      <c r="A308" s="1">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>7728496</v>
+      </c>
+      <c r="C308" t="s">
+        <v>68</v>
+      </c>
+      <c r="D308" t="s">
+        <v>69</v>
+      </c>
+      <c r="E308" s="2">
+        <v>45711.70833333334</v>
+      </c>
+      <c r="F308">
+        <v>28</v>
+      </c>
+      <c r="G308" t="s">
+        <v>72</v>
+      </c>
+      <c r="H308" t="s">
+        <v>86</v>
+      </c>
+      <c r="I308">
+        <v>0</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>0</v>
+      </c>
+      <c r="L308">
+        <v>0</v>
+      </c>
+      <c r="M308">
+        <v>0</v>
+      </c>
+      <c r="N308">
+        <v>0</v>
+      </c>
+      <c r="O308" t="s">
+        <v>94</v>
+      </c>
+      <c r="P308" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q308">
+        <v>2.55</v>
+      </c>
+      <c r="R308">
+        <v>2.1</v>
+      </c>
+      <c r="S308">
+        <v>4</v>
+      </c>
+      <c r="T308">
+        <v>1.38</v>
+      </c>
+      <c r="U308">
+        <v>2.8</v>
+      </c>
+      <c r="V308">
+        <v>2.75</v>
+      </c>
+      <c r="W308">
+        <v>1.4</v>
+      </c>
+      <c r="X308">
+        <v>7.1</v>
+      </c>
+      <c r="Y308">
+        <v>1.04</v>
+      </c>
+      <c r="Z308">
+        <v>2.09</v>
+      </c>
+      <c r="AA308">
+        <v>3.45</v>
+      </c>
+      <c r="AB308">
+        <v>3.76</v>
+      </c>
+      <c r="AC308">
+        <v>1.06</v>
+      </c>
+      <c r="AD308">
+        <v>8.5</v>
+      </c>
+      <c r="AE308">
+        <v>1.33</v>
+      </c>
+      <c r="AF308">
+        <v>3.3</v>
+      </c>
+      <c r="AG308">
+        <v>1.9</v>
+      </c>
+      <c r="AH308">
+        <v>1.9</v>
+      </c>
+      <c r="AI308">
+        <v>1.75</v>
+      </c>
+      <c r="AJ308">
+        <v>1.93</v>
+      </c>
+      <c r="AK308">
+        <v>1.25</v>
+      </c>
+      <c r="AL308">
+        <v>1.25</v>
+      </c>
+      <c r="AM308">
+        <v>1.75</v>
+      </c>
+      <c r="AN308">
+        <v>1.43</v>
+      </c>
+      <c r="AO308">
+        <v>1.38</v>
+      </c>
+      <c r="AP308">
+        <v>1.4</v>
+      </c>
+      <c r="AQ308">
+        <v>1.36</v>
+      </c>
+      <c r="AR308">
+        <v>1.45</v>
+      </c>
+      <c r="AS308">
+        <v>1.26</v>
+      </c>
+      <c r="AT308">
+        <v>2.71</v>
+      </c>
+      <c r="AU308">
+        <v>5</v>
+      </c>
+      <c r="AV308">
+        <v>0</v>
+      </c>
+      <c r="AW308">
+        <v>6</v>
+      </c>
+      <c r="AX308">
+        <v>9</v>
+      </c>
+      <c r="AY308">
+        <v>12</v>
+      </c>
+      <c r="AZ308">
+        <v>9</v>
+      </c>
+      <c r="BA308">
+        <v>6</v>
+      </c>
+      <c r="BB308">
+        <v>3</v>
+      </c>
+      <c r="BC308">
+        <v>9</v>
+      </c>
+      <c r="BD308">
+        <v>1.65</v>
+      </c>
+      <c r="BE308">
+        <v>6.4</v>
+      </c>
+      <c r="BF308">
+        <v>2.5</v>
+      </c>
+      <c r="BG308">
+        <v>1.4</v>
+      </c>
+      <c r="BH308">
+        <v>2.65</v>
+      </c>
+      <c r="BI308">
+        <v>1.67</v>
+      </c>
+      <c r="BJ308">
+        <v>2.02</v>
+      </c>
+      <c r="BK308">
+        <v>2.08</v>
+      </c>
+      <c r="BL308">
+        <v>1.63</v>
+      </c>
+      <c r="BM308">
+        <v>2.65</v>
+      </c>
+      <c r="BN308">
+        <v>1.4</v>
+      </c>
+      <c r="BO308">
+        <v>3.55</v>
+      </c>
+      <c r="BP308">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="388">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1176,6 +1176,9 @@
   <si>
     <t>['90+2', '90+4']</t>
   </si>
+  <si>
+    <t>['24', '27']</t>
+  </si>
 </sst>
 </file>
 
@@ -1536,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP308"/>
+  <dimension ref="A1:BP309"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4139,7 +4142,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ13">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR13">
         <v>1.32</v>
@@ -5990,7 +5993,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ22">
         <v>1.33</v>
@@ -9904,7 +9907,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ41">
         <v>1.43</v>
@@ -10731,7 +10734,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR45">
         <v>0.96</v>
@@ -14436,7 +14439,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ63">
         <v>1.31</v>
@@ -15057,7 +15060,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ66">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR66">
         <v>1.93</v>
@@ -17323,7 +17326,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ77">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR77">
         <v>1.33</v>
@@ -20204,7 +20207,7 @@
         <v>0.33</v>
       </c>
       <c r="AP91">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -23297,7 +23300,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ106">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR106">
         <v>1.12</v>
@@ -25560,7 +25563,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ117">
         <v>1.15</v>
@@ -27623,7 +27626,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ127">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR127">
         <v>1.1</v>
@@ -29268,7 +29271,7 @@
         <v>0.83</v>
       </c>
       <c r="AP135">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ135">
         <v>1.36</v>
@@ -32361,7 +32364,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ150">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR150">
         <v>1.6</v>
@@ -34418,7 +34421,7 @@
         <v>1.17</v>
       </c>
       <c r="AP160">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ160">
         <v>1.47</v>
@@ -35242,7 +35245,7 @@
         <v>1.38</v>
       </c>
       <c r="AP164">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ164">
         <v>1.47</v>
@@ -35657,7 +35660,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ166">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR166">
         <v>1.42</v>
@@ -41013,7 +41016,7 @@
         <v>2</v>
       </c>
       <c r="AQ192">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR192">
         <v>1.15</v>
@@ -42246,7 +42249,7 @@
         <v>1.25</v>
       </c>
       <c r="AP198">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -44927,7 +44930,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ211">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR211">
         <v>1.69</v>
@@ -46778,7 +46781,7 @@
         <v>1.1</v>
       </c>
       <c r="AP220">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ220">
         <v>0.93</v>
@@ -51313,7 +51316,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ242">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR242">
         <v>1.37</v>
@@ -51516,7 +51519,7 @@
         <v>1.27</v>
       </c>
       <c r="AP243">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ243">
         <v>1.5</v>
@@ -53785,7 +53788,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ254">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR254">
         <v>1.63</v>
@@ -57696,7 +57699,7 @@
         <v>0.67</v>
       </c>
       <c r="AP273">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ273">
         <v>1.13</v>
@@ -59141,7 +59144,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ280">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR280">
         <v>1.52</v>
@@ -60789,7 +60792,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ288">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR288">
         <v>1.7</v>
@@ -60992,7 +60995,7 @@
         <v>0.85</v>
       </c>
       <c r="AP289">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ289">
         <v>1</v>
@@ -64985,6 +64988,212 @@
       </c>
       <c r="BP308">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="309" spans="1:68">
+      <c r="A309" s="1">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>7728507</v>
+      </c>
+      <c r="C309" t="s">
+        <v>68</v>
+      </c>
+      <c r="D309" t="s">
+        <v>69</v>
+      </c>
+      <c r="E309" s="2">
+        <v>45716.6875</v>
+      </c>
+      <c r="F309">
+        <v>29</v>
+      </c>
+      <c r="G309" t="s">
+        <v>87</v>
+      </c>
+      <c r="H309" t="s">
+        <v>73</v>
+      </c>
+      <c r="I309">
+        <v>0</v>
+      </c>
+      <c r="J309">
+        <v>2</v>
+      </c>
+      <c r="K309">
+        <v>2</v>
+      </c>
+      <c r="L309">
+        <v>0</v>
+      </c>
+      <c r="M309">
+        <v>2</v>
+      </c>
+      <c r="N309">
+        <v>2</v>
+      </c>
+      <c r="O309" t="s">
+        <v>94</v>
+      </c>
+      <c r="P309" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q309">
+        <v>4.8</v>
+      </c>
+      <c r="R309">
+        <v>1.9</v>
+      </c>
+      <c r="S309">
+        <v>2.85</v>
+      </c>
+      <c r="T309">
+        <v>1.61</v>
+      </c>
+      <c r="U309">
+        <v>2.2</v>
+      </c>
+      <c r="V309">
+        <v>3.75</v>
+      </c>
+      <c r="W309">
+        <v>1.24</v>
+      </c>
+      <c r="X309">
+        <v>11</v>
+      </c>
+      <c r="Y309">
+        <v>1.02</v>
+      </c>
+      <c r="Z309">
+        <v>4.2</v>
+      </c>
+      <c r="AA309">
+        <v>3.27</v>
+      </c>
+      <c r="AB309">
+        <v>2.04</v>
+      </c>
+      <c r="AC309">
+        <v>1.12</v>
+      </c>
+      <c r="AD309">
+        <v>6</v>
+      </c>
+      <c r="AE309">
+        <v>1.55</v>
+      </c>
+      <c r="AF309">
+        <v>2.3</v>
+      </c>
+      <c r="AG309">
+        <v>2.3</v>
+      </c>
+      <c r="AH309">
+        <v>1.5</v>
+      </c>
+      <c r="AI309">
+        <v>2.24</v>
+      </c>
+      <c r="AJ309">
+        <v>1.59</v>
+      </c>
+      <c r="AK309">
+        <v>1.67</v>
+      </c>
+      <c r="AL309">
+        <v>1.34</v>
+      </c>
+      <c r="AM309">
+        <v>1.25</v>
+      </c>
+      <c r="AN309">
+        <v>0.62</v>
+      </c>
+      <c r="AO309">
+        <v>0.64</v>
+      </c>
+      <c r="AP309">
+        <v>0.57</v>
+      </c>
+      <c r="AQ309">
+        <v>0.8</v>
+      </c>
+      <c r="AR309">
+        <v>1.18</v>
+      </c>
+      <c r="AS309">
+        <v>1.23</v>
+      </c>
+      <c r="AT309">
+        <v>2.41</v>
+      </c>
+      <c r="AU309">
+        <v>2</v>
+      </c>
+      <c r="AV309">
+        <v>7</v>
+      </c>
+      <c r="AW309">
+        <v>5</v>
+      </c>
+      <c r="AX309">
+        <v>8</v>
+      </c>
+      <c r="AY309">
+        <v>8</v>
+      </c>
+      <c r="AZ309">
+        <v>18</v>
+      </c>
+      <c r="BA309">
+        <v>9</v>
+      </c>
+      <c r="BB309">
+        <v>6</v>
+      </c>
+      <c r="BC309">
+        <v>15</v>
+      </c>
+      <c r="BD309">
+        <v>2.48</v>
+      </c>
+      <c r="BE309">
+        <v>6.25</v>
+      </c>
+      <c r="BF309">
+        <v>1.68</v>
+      </c>
+      <c r="BG309">
+        <v>1.57</v>
+      </c>
+      <c r="BH309">
+        <v>2.2</v>
+      </c>
+      <c r="BI309">
+        <v>1.95</v>
+      </c>
+      <c r="BJ309">
+        <v>1.72</v>
+      </c>
+      <c r="BK309">
+        <v>2.5</v>
+      </c>
+      <c r="BL309">
+        <v>1.44</v>
+      </c>
+      <c r="BM309">
+        <v>3.4</v>
+      </c>
+      <c r="BN309">
+        <v>1.26</v>
+      </c>
+      <c r="BO309">
+        <v>4.6</v>
+      </c>
+      <c r="BP309">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="393">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -859,6 +859,18 @@
     <t>['60', '63']</t>
   </si>
   <si>
+    <t>['24', '36', '50']</t>
+  </si>
+  <si>
+    <t>['39', '85']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['11', '53']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1138,9 +1150,6 @@
     <t>['51', '84']</t>
   </si>
   <si>
-    <t>['50']</t>
-  </si>
-  <si>
     <t>['54', '73']</t>
   </si>
   <si>
@@ -1168,16 +1177,22 @@
     <t>['6', '45+2', '79']</t>
   </si>
   <si>
-    <t>['31', '78']</t>
+    <t>['40', '55']</t>
   </si>
   <si>
-    <t>['40', '55']</t>
+    <t>['31', '78']</t>
   </si>
   <si>
     <t>['90+2', '90+4']</t>
   </si>
   <si>
     <t>['24', '27']</t>
+  </si>
+  <si>
+    <t>['1']</t>
+  </si>
+  <si>
+    <t>['55', '62']</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP309"/>
+  <dimension ref="A1:BP313"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1795,7 +1810,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2207,7 +2222,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3031,7 +3046,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3237,7 +3252,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4061,7 +4076,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4267,7 +4282,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4345,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ14">
         <v>1.36</v>
@@ -5297,7 +5312,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5787,7 +5802,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21">
         <v>1.5</v>
@@ -5915,7 +5930,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6121,7 +6136,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6202,7 +6217,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ23">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6327,7 +6342,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6533,7 +6548,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6739,7 +6754,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6945,7 +6960,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7229,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7357,7 +7372,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7644,7 +7659,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR30">
         <v>1.73</v>
@@ -7975,7 +7990,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8181,7 +8196,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8593,7 +8608,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9083,10 +9098,10 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ37">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR37">
         <v>1.35</v>
@@ -10319,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ43">
         <v>1.15</v>
@@ -10447,7 +10462,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10525,7 +10540,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ44">
         <v>1.31</v>
@@ -11065,7 +11080,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12588,7 +12603,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12713,7 +12728,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12919,7 +12934,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -12997,7 +13012,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ56">
         <v>1.36</v>
@@ -13125,7 +13140,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13331,7 +13346,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13743,7 +13758,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13824,7 +13839,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ60">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -14027,7 +14042,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ61">
         <v>1.43</v>
@@ -14361,7 +14376,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14645,7 +14660,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ64">
         <v>1.93</v>
@@ -14979,7 +14994,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15057,7 +15072,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ66">
         <v>0.8</v>
@@ -15263,7 +15278,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ67">
         <v>1.13</v>
@@ -15391,7 +15406,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15597,7 +15612,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16215,7 +16230,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16421,7 +16436,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16627,7 +16642,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16911,7 +16926,7 @@
         <v>0.33</v>
       </c>
       <c r="AP75">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ75">
         <v>0.21</v>
@@ -17120,7 +17135,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -17451,7 +17466,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17657,7 +17672,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17735,7 +17750,7 @@
         <v>2.33</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ79">
         <v>1.31</v>
@@ -18069,7 +18084,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18275,7 +18290,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18481,7 +18496,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18559,7 +18574,7 @@
         <v>3</v>
       </c>
       <c r="AP83">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ83">
         <v>1.93</v>
@@ -18765,10 +18780,10 @@
         <v>2.33</v>
       </c>
       <c r="AP84">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ84">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR84">
         <v>1.79</v>
@@ -19305,7 +19320,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19717,7 +19732,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19923,7 +19938,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20210,7 +20225,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ91">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20335,7 +20350,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20747,7 +20762,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20825,7 +20840,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ94">
         <v>0.93</v>
@@ -20953,7 +20968,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21983,7 +21998,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23091,7 +23106,7 @@
         <v>1.4</v>
       </c>
       <c r="AP105">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ105">
         <v>1.43</v>
@@ -23425,7 +23440,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24043,7 +24058,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24121,7 +24136,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ110">
         <v>1.47</v>
@@ -24330,7 +24345,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR111">
         <v>1.54</v>
@@ -24455,7 +24470,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24661,7 +24676,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24739,7 +24754,7 @@
         <v>2</v>
       </c>
       <c r="AP113">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ113">
         <v>1.46</v>
@@ -25073,7 +25088,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25769,7 +25784,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ118">
         <v>0.93</v>
@@ -25897,7 +25912,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26515,7 +26530,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26596,7 +26611,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR122">
         <v>1.4</v>
@@ -26927,7 +26942,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27339,7 +27354,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27417,7 +27432,7 @@
         <v>1.8</v>
       </c>
       <c r="AP126">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ126">
         <v>1.36</v>
@@ -27751,7 +27766,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28038,7 +28053,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ129">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -28163,7 +28178,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28369,7 +28384,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28447,7 +28462,7 @@
         <v>1.17</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ131">
         <v>1.47</v>
@@ -28575,7 +28590,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28987,7 +29002,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29193,7 +29208,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29683,7 +29698,7 @@
         <v>2.2</v>
       </c>
       <c r="AP137">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ137">
         <v>1.46</v>
@@ -29811,7 +29826,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30098,7 +30113,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ139">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR139">
         <v>1.66</v>
@@ -30429,7 +30444,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30635,7 +30650,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30841,7 +30856,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30919,7 +30934,7 @@
         <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ143">
         <v>1.33</v>
@@ -31047,7 +31062,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31459,7 +31474,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31871,7 +31886,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32570,7 +32585,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ151">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR151">
         <v>1.43</v>
@@ -32901,7 +32916,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32979,7 +32994,7 @@
         <v>0.83</v>
       </c>
       <c r="AP153">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ153">
         <v>1.07</v>
@@ -33394,7 +33409,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ155">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR155">
         <v>1.59</v>
@@ -33519,7 +33534,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34215,7 +34230,7 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ159">
         <v>1.36</v>
@@ -34627,7 +34642,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ161">
         <v>1</v>
@@ -35167,7 +35182,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35785,7 +35800,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36815,7 +36830,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -36893,7 +36908,7 @@
         <v>1.86</v>
       </c>
       <c r="AP172">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ172">
         <v>1.36</v>
@@ -37305,7 +37320,7 @@
         <v>0.14</v>
       </c>
       <c r="AP174">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ174">
         <v>1.13</v>
@@ -37433,7 +37448,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37717,10 +37732,10 @@
         <v>0.83</v>
       </c>
       <c r="AP176">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ176">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR176">
         <v>1.6</v>
@@ -37845,7 +37860,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38129,7 +38144,7 @@
         <v>1</v>
       </c>
       <c r="AP178">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ178">
         <v>0.93</v>
@@ -38257,7 +38272,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38335,7 +38350,7 @@
         <v>2</v>
       </c>
       <c r="AP179">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ179">
         <v>1.46</v>
@@ -38463,7 +38478,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39159,7 +39174,7 @@
         <v>0.88</v>
       </c>
       <c r="AP183">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ183">
         <v>1</v>
@@ -39287,7 +39302,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39368,7 +39383,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ184">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR184">
         <v>1.69</v>
@@ -39574,7 +39589,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ185">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR185">
         <v>1.42</v>
@@ -40111,7 +40126,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40729,7 +40744,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40935,7 +40950,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41013,7 +41028,7 @@
         <v>0.63</v>
       </c>
       <c r="AP192">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ192">
         <v>0.8</v>
@@ -41141,7 +41156,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41347,7 +41362,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42455,7 +42470,7 @@
         <v>1.38</v>
       </c>
       <c r="AP199">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ199">
         <v>1.07</v>
@@ -42583,7 +42598,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42995,7 +43010,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43073,7 +43088,7 @@
         <v>0.67</v>
       </c>
       <c r="AP202">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ202">
         <v>0.47</v>
@@ -43201,7 +43216,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43819,7 +43834,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43900,7 +43915,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ206">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR206">
         <v>1.42</v>
@@ -44849,7 +44864,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45055,7 +45070,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45133,7 +45148,7 @@
         <v>1.1</v>
       </c>
       <c r="AP212">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ212">
         <v>1.5</v>
@@ -45261,7 +45276,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45467,7 +45482,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45879,7 +45894,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -45960,7 +45975,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ216">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR216">
         <v>1.46</v>
@@ -46575,7 +46590,7 @@
         <v>0.22</v>
       </c>
       <c r="AP219">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ219">
         <v>0.21</v>
@@ -47115,7 +47130,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47399,10 +47414,10 @@
         <v>1.11</v>
       </c>
       <c r="AP223">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ223">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR223">
         <v>1.71</v>
@@ -47527,7 +47542,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47939,7 +47954,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48017,7 +48032,7 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ226">
         <v>1.15</v>
@@ -48223,7 +48238,7 @@
         <v>1</v>
       </c>
       <c r="AP227">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ227">
         <v>1.31</v>
@@ -48557,7 +48572,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48763,7 +48778,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48969,7 +48984,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49256,7 +49271,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ232">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR232">
         <v>1.73</v>
@@ -49665,7 +49680,7 @@
         <v>1.4</v>
       </c>
       <c r="AP234">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ234">
         <v>1.07</v>
@@ -49793,7 +49808,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50617,7 +50632,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51235,7 +51250,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51647,7 +51662,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51811,7 +51826,7 @@
         <v>244</v>
       </c>
       <c r="B245">
-        <v>7728447</v>
+        <v>7728445</v>
       </c>
       <c r="C245" t="s">
         <v>68</v>
@@ -51826,10 +51841,10 @@
         <v>23</v>
       </c>
       <c r="G245" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H245" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I245">
         <v>1</v>
@@ -51850,166 +51865,166 @@
         <v>2</v>
       </c>
       <c r="O245" t="s">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="P245" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="Q245">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R245">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S245">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="T245">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="U245">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V245">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="W245">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X245">
         <v>10</v>
       </c>
       <c r="Y245">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z245">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AA245">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AB245">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC245">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AD245">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AE245">
+        <v>1.42</v>
+      </c>
+      <c r="AF245">
+        <v>2.8</v>
+      </c>
+      <c r="AG245">
+        <v>2.15</v>
+      </c>
+      <c r="AH245">
+        <v>1.62</v>
+      </c>
+      <c r="AI245">
+        <v>2</v>
+      </c>
+      <c r="AJ245">
+        <v>1.73</v>
+      </c>
+      <c r="AK245">
+        <v>1.24</v>
+      </c>
+      <c r="AL245">
+        <v>1.31</v>
+      </c>
+      <c r="AM245">
+        <v>1.8</v>
+      </c>
+      <c r="AN245">
+        <v>2.09</v>
+      </c>
+      <c r="AO245">
+        <v>1.09</v>
+      </c>
+      <c r="AP245">
+        <v>1.79</v>
+      </c>
+      <c r="AQ245">
+        <v>0.93</v>
+      </c>
+      <c r="AR245">
         <v>1.49</v>
       </c>
-      <c r="AF245">
-        <v>2.4</v>
-      </c>
-      <c r="AG245">
-        <v>2.55</v>
-      </c>
-      <c r="AH245">
-        <v>1.46</v>
-      </c>
-      <c r="AI245">
-        <v>2.1</v>
-      </c>
-      <c r="AJ245">
-        <v>1.63</v>
-      </c>
-      <c r="AK245">
-        <v>1.32</v>
-      </c>
-      <c r="AL245">
-        <v>1.34</v>
-      </c>
-      <c r="AM245">
-        <v>1.61</v>
-      </c>
-      <c r="AN245">
-        <v>1.73</v>
-      </c>
-      <c r="AO245">
-        <v>1.3</v>
-      </c>
-      <c r="AP245">
-        <v>1.67</v>
-      </c>
-      <c r="AQ245">
-        <v>1.15</v>
-      </c>
-      <c r="AR245">
-        <v>1.56</v>
-      </c>
       <c r="AS245">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AT245">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AU245">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV245">
         <v>5</v>
       </c>
       <c r="AW245">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX245">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY245">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ245">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA245">
+        <v>3</v>
+      </c>
+      <c r="BB245">
+        <v>1</v>
+      </c>
+      <c r="BC245">
         <v>4</v>
       </c>
-      <c r="BB245">
-        <v>5</v>
-      </c>
-      <c r="BC245">
-        <v>9</v>
-      </c>
       <c r="BD245">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="BE245">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="BF245">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="BG245">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BH245">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="BI245">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="BJ245">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="BK245">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="BL245">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="BM245">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="BN245">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BO245">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BP245">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="246" spans="1:68">
@@ -52017,7 +52032,7 @@
         <v>245</v>
       </c>
       <c r="B246">
-        <v>7728445</v>
+        <v>7728447</v>
       </c>
       <c r="C246" t="s">
         <v>68</v>
@@ -52032,10 +52047,10 @@
         <v>23</v>
       </c>
       <c r="G246" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H246" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I246">
         <v>1</v>
@@ -52056,166 +52071,166 @@
         <v>2</v>
       </c>
       <c r="O246" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>258</v>
+        <v>331</v>
       </c>
       <c r="Q246">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="R246">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="S246">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="T246">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U246">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V246">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="W246">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X246">
         <v>10</v>
       </c>
       <c r="Y246">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z246">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="AA246">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AB246">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AC246">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AD246">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AE246">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AF246">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AG246">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AH246">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AI246">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ246">
+        <v>1.63</v>
+      </c>
+      <c r="AK246">
+        <v>1.32</v>
+      </c>
+      <c r="AL246">
+        <v>1.34</v>
+      </c>
+      <c r="AM246">
+        <v>1.61</v>
+      </c>
+      <c r="AN246">
         <v>1.73</v>
       </c>
-      <c r="AK246">
-        <v>1.24</v>
-      </c>
-      <c r="AL246">
-        <v>1.31</v>
-      </c>
-      <c r="AM246">
-        <v>1.8</v>
-      </c>
-      <c r="AN246">
-        <v>2.09</v>
-      </c>
       <c r="AO246">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AP246">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ246">
-        <v>0.93</v>
+        <v>1.15</v>
       </c>
       <c r="AR246">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AS246">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AT246">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="AU246">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV246">
         <v>5</v>
       </c>
       <c r="AW246">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX246">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY246">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ246">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA246">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB246">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC246">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BD246">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="BE246">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="BF246">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="BG246">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BH246">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="BI246">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="BJ246">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="BK246">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="BL246">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="BM246">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="BN246">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="BO246">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BP246">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="247" spans="1:68">
@@ -52758,7 +52773,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ249">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR249">
         <v>1.51</v>
@@ -52883,7 +52898,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -52961,7 +52976,7 @@
         <v>0.45</v>
       </c>
       <c r="AP250">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ250">
         <v>1.13</v>
@@ -53089,7 +53104,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53167,7 +53182,7 @@
         <v>0.18</v>
       </c>
       <c r="AP251">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ251">
         <v>0.21</v>
@@ -53373,7 +53388,7 @@
         <v>1.27</v>
       </c>
       <c r="AP252">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ252">
         <v>1.47</v>
@@ -53501,7 +53516,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53913,7 +53928,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54119,7 +54134,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54403,7 +54418,7 @@
         <v>0.58</v>
       </c>
       <c r="AP257">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ257">
         <v>0.47</v>
@@ -54531,7 +54546,7 @@
         <v>94</v>
       </c>
       <c r="P258" t="s">
-        <v>374</v>
+        <v>283</v>
       </c>
       <c r="Q258">
         <v>2.75</v>
@@ -55149,7 +55164,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55355,7 +55370,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55973,7 +55988,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56466,7 +56481,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ267">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR267">
         <v>1.55</v>
@@ -56669,7 +56684,7 @@
         <v>1.42</v>
       </c>
       <c r="AP268">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ268">
         <v>1.5</v>
@@ -56797,7 +56812,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57081,7 +57096,7 @@
         <v>1.25</v>
       </c>
       <c r="AP270">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ270">
         <v>1.47</v>
@@ -57373,7 +57388,7 @@
         <v>271</v>
       </c>
       <c r="B272">
-        <v>7728469</v>
+        <v>7728464</v>
       </c>
       <c r="C272" t="s">
         <v>68</v>
@@ -57388,190 +57403,190 @@
         <v>25</v>
       </c>
       <c r="G272" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H272" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="I272">
         <v>0</v>
       </c>
       <c r="J272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L272">
         <v>0</v>
       </c>
       <c r="M272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O272" t="s">
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>94</v>
+        <v>381</v>
       </c>
       <c r="Q272">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R272">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S272">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="T272">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="U272">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="V272">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="W272">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="X272">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="Y272">
         <v>1.05</v>
       </c>
       <c r="Z272">
-        <v>1.95</v>
+        <v>3.98</v>
       </c>
       <c r="AA272">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="AB272">
-        <v>4.33</v>
+        <v>2.04</v>
       </c>
       <c r="AC272">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AD272">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AE272">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AF272">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AG272">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH272">
+        <v>1.67</v>
+      </c>
+      <c r="AI272">
+        <v>1.83</v>
+      </c>
+      <c r="AJ272">
         <v>1.85</v>
       </c>
-      <c r="AI272">
-        <v>2</v>
-      </c>
-      <c r="AJ272">
-        <v>1.73</v>
-      </c>
       <c r="AK272">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="AL272">
+        <v>1.25</v>
+      </c>
+      <c r="AM272">
+        <v>1.25</v>
+      </c>
+      <c r="AN272">
+        <v>0.73</v>
+      </c>
+      <c r="AO272">
+        <v>0.67</v>
+      </c>
+      <c r="AP272">
+        <v>0.57</v>
+      </c>
+      <c r="AQ272">
+        <v>1.13</v>
+      </c>
+      <c r="AR272">
+        <v>1.18</v>
+      </c>
+      <c r="AS272">
         <v>1.33</v>
       </c>
-      <c r="AM272">
-        <v>1.68</v>
-      </c>
-      <c r="AN272">
-        <v>1.27</v>
-      </c>
-      <c r="AO272">
-        <v>1.18</v>
-      </c>
-      <c r="AP272">
-        <v>1.15</v>
-      </c>
-      <c r="AQ272">
-        <v>1.31</v>
-      </c>
-      <c r="AR272">
-        <v>1.65</v>
-      </c>
-      <c r="AS272">
-        <v>1.24</v>
-      </c>
       <c r="AT272">
-        <v>2.89</v>
+        <v>2.51</v>
       </c>
       <c r="AU272">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV272">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW272">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX272">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AY272">
         <v>11</v>
       </c>
       <c r="AZ272">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BA272">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BB272">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BC272">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BD272">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="BE272">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF272">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="BG272">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BH272">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="BI272">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="BJ272">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="BK272">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="BL272">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="BM272">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="BN272">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BO272">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BP272">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="273" spans="1:68">
@@ -57579,7 +57594,7 @@
         <v>272</v>
       </c>
       <c r="B273">
-        <v>7728464</v>
+        <v>7728469</v>
       </c>
       <c r="C273" t="s">
         <v>68</v>
@@ -57594,190 +57609,190 @@
         <v>25</v>
       </c>
       <c r="G273" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H273" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="I273">
         <v>0</v>
       </c>
       <c r="J273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L273">
         <v>0</v>
       </c>
       <c r="M273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O273" t="s">
         <v>94</v>
       </c>
       <c r="P273" t="s">
-        <v>378</v>
+        <v>94</v>
       </c>
       <c r="Q273">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R273">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S273">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="T273">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="U273">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="V273">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="W273">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="X273">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="Y273">
         <v>1.05</v>
       </c>
       <c r="Z273">
-        <v>3.98</v>
+        <v>1.95</v>
       </c>
       <c r="AA273">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="AB273">
-        <v>2.04</v>
+        <v>4.33</v>
       </c>
       <c r="AC273">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AD273">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AE273">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AF273">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="AG273">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH273">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AI273">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AJ273">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AK273">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AL273">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AM273">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AN273">
-        <v>0.73</v>
+        <v>1.27</v>
       </c>
       <c r="AO273">
-        <v>0.67</v>
+        <v>1.18</v>
       </c>
       <c r="AP273">
-        <v>0.57</v>
+        <v>1.14</v>
       </c>
       <c r="AQ273">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AR273">
-        <v>1.18</v>
+        <v>1.65</v>
       </c>
       <c r="AS273">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AT273">
-        <v>2.51</v>
+        <v>2.89</v>
       </c>
       <c r="AU273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV273">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW273">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX273">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AY273">
         <v>11</v>
       </c>
       <c r="AZ273">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BA273">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BB273">
+        <v>2</v>
+      </c>
+      <c r="BC273">
         <v>6</v>
       </c>
-      <c r="BC273">
-        <v>14</v>
-      </c>
       <c r="BD273">
+        <v>1.61</v>
+      </c>
+      <c r="BE273">
+        <v>6.75</v>
+      </c>
+      <c r="BF273">
         <v>2.55</v>
       </c>
-      <c r="BE273">
-        <v>6.4</v>
-      </c>
-      <c r="BF273">
-        <v>1.63</v>
-      </c>
       <c r="BG273">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BH273">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="BI273">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BJ273">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="BK273">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="BL273">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="BM273">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="BN273">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BO273">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BP273">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="274" spans="1:68">
@@ -58114,7 +58129,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ275">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR275">
         <v>1.57</v>
@@ -58445,7 +58460,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59433,7 +59448,7 @@
         <v>281</v>
       </c>
       <c r="B282">
-        <v>7728477</v>
+        <v>7728475</v>
       </c>
       <c r="C282" t="s">
         <v>68</v>
@@ -59448,190 +59463,190 @@
         <v>26</v>
       </c>
       <c r="G282" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H282" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I282">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J282">
         <v>0</v>
       </c>
       <c r="K282">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L282">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M282">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N282">
         <v>3</v>
       </c>
       <c r="O282" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
       <c r="P282" t="s">
-        <v>380</v>
+        <v>242</v>
       </c>
       <c r="Q282">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R282">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S282">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="T282">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="U282">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V282">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="W282">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="X282">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y282">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z282">
-        <v>2.03</v>
+        <v>2.57</v>
       </c>
       <c r="AA282">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AB282">
-        <v>4.4</v>
+        <v>3.01</v>
       </c>
       <c r="AC282">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AD282">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AE282">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF282">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AG282">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="AH282">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AI282">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AJ282">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AK282">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL282">
         <v>1.3</v>
       </c>
       <c r="AM282">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AN282">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AO282">
-        <v>1.38</v>
+        <v>2.17</v>
       </c>
       <c r="AP282">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AQ282">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AR282">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AS282">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="AT282">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="AU282">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV282">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW282">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX282">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY282">
         <v>11</v>
       </c>
       <c r="AZ282">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA282">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB282">
+        <v>3</v>
+      </c>
+      <c r="BC282">
         <v>6</v>
       </c>
-      <c r="BC282">
-        <v>10</v>
-      </c>
       <c r="BD282">
-        <v>1.41</v>
+        <v>1.86</v>
       </c>
       <c r="BE282">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BF282">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="BG282">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BH282">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="BI282">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BJ282">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BK282">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="BL282">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="BM282">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BN282">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO282">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BP282">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="283" spans="1:68">
@@ -59639,7 +59654,7 @@
         <v>282</v>
       </c>
       <c r="B283">
-        <v>7728475</v>
+        <v>7728477</v>
       </c>
       <c r="C283" t="s">
         <v>68</v>
@@ -59654,190 +59669,190 @@
         <v>26</v>
       </c>
       <c r="G283" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H283" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J283">
         <v>0</v>
       </c>
       <c r="K283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L283">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M283">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N283">
         <v>3</v>
       </c>
       <c r="O283" t="s">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>242</v>
+        <v>383</v>
       </c>
       <c r="Q283">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R283">
+        <v>2</v>
+      </c>
+      <c r="S283">
+        <v>4.75</v>
+      </c>
+      <c r="T283">
+        <v>1.53</v>
+      </c>
+      <c r="U283">
+        <v>2.38</v>
+      </c>
+      <c r="V283">
+        <v>3.5</v>
+      </c>
+      <c r="W283">
+        <v>1.29</v>
+      </c>
+      <c r="X283">
+        <v>11</v>
+      </c>
+      <c r="Y283">
+        <v>1.05</v>
+      </c>
+      <c r="Z283">
+        <v>2.03</v>
+      </c>
+      <c r="AA283">
+        <v>3.15</v>
+      </c>
+      <c r="AB283">
+        <v>4.4</v>
+      </c>
+      <c r="AC283">
+        <v>1.1</v>
+      </c>
+      <c r="AD283">
+        <v>6.5</v>
+      </c>
+      <c r="AE283">
+        <v>1.48</v>
+      </c>
+      <c r="AF283">
+        <v>2.6</v>
+      </c>
+      <c r="AG283">
+        <v>2.3</v>
+      </c>
+      <c r="AH283">
+        <v>1.5</v>
+      </c>
+      <c r="AI283">
         <v>2.1</v>
       </c>
-      <c r="S283">
-        <v>3.5</v>
-      </c>
-      <c r="T283">
-        <v>1.44</v>
-      </c>
-      <c r="U283">
-        <v>2.63</v>
-      </c>
-      <c r="V283">
-        <v>3</v>
-      </c>
-      <c r="W283">
-        <v>1.36</v>
-      </c>
-      <c r="X283">
-        <v>9</v>
-      </c>
-      <c r="Y283">
-        <v>1.07</v>
-      </c>
-      <c r="Z283">
-        <v>2.57</v>
-      </c>
-      <c r="AA283">
-        <v>3.19</v>
-      </c>
-      <c r="AB283">
-        <v>3.01</v>
-      </c>
-      <c r="AC283">
-        <v>1.07</v>
-      </c>
-      <c r="AD283">
-        <v>8</v>
-      </c>
-      <c r="AE283">
-        <v>1.33</v>
-      </c>
-      <c r="AF283">
-        <v>3.2</v>
-      </c>
-      <c r="AG283">
-        <v>2.01</v>
-      </c>
-      <c r="AH283">
-        <v>1.81</v>
-      </c>
-      <c r="AI283">
-        <v>1.73</v>
-      </c>
       <c r="AJ283">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AK283">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AL283">
         <v>1.3</v>
       </c>
       <c r="AM283">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AN283">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AO283">
-        <v>2.17</v>
+        <v>1.38</v>
       </c>
       <c r="AP283">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AQ283">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AR283">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AS283">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="AT283">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="AU283">
+        <v>5</v>
+      </c>
+      <c r="AV283">
+        <v>3</v>
+      </c>
+      <c r="AW283">
         <v>4</v>
       </c>
-      <c r="AV283">
-        <v>2</v>
-      </c>
-      <c r="AW283">
-        <v>7</v>
-      </c>
       <c r="AX283">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY283">
         <v>11</v>
       </c>
       <c r="AZ283">
+        <v>9</v>
+      </c>
+      <c r="BA283">
+        <v>4</v>
+      </c>
+      <c r="BB283">
         <v>6</v>
       </c>
-      <c r="BA283">
-        <v>3</v>
-      </c>
-      <c r="BB283">
-        <v>3</v>
-      </c>
       <c r="BC283">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD283">
-        <v>1.86</v>
+        <v>1.41</v>
       </c>
       <c r="BE283">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF283">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="BG283">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BH283">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="BI283">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BJ283">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BK283">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BL283">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="BM283">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BN283">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO283">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BP283">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="284" spans="1:68">
@@ -59887,7 +59902,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60505,7 +60520,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -60586,7 +60601,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ287">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR287">
         <v>1.29</v>
@@ -60789,7 +60804,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP288">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ288">
         <v>0.8</v>
@@ -61123,7 +61138,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61329,7 +61344,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -62025,7 +62040,7 @@
         <v>1.5</v>
       </c>
       <c r="AP294">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ294">
         <v>1.46</v>
@@ -62231,10 +62246,10 @@
         <v>0.75</v>
       </c>
       <c r="AP295">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ295">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR295">
         <v>1.6</v>
@@ -62643,7 +62658,7 @@
         <v>1.17</v>
       </c>
       <c r="AP297">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ297">
         <v>1.15</v>
@@ -63141,7 +63156,7 @@
         <v>299</v>
       </c>
       <c r="B300">
-        <v>7728498</v>
+        <v>7728844</v>
       </c>
       <c r="C300" t="s">
         <v>68</v>
@@ -63156,10 +63171,10 @@
         <v>28</v>
       </c>
       <c r="G300" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H300" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I300">
         <v>1</v>
@@ -63171,175 +63186,175 @@
         <v>2</v>
       </c>
       <c r="L300">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M300">
         <v>2</v>
       </c>
       <c r="N300">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O300" t="s">
-        <v>278</v>
+        <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q300">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="R300">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="S300">
+        <v>3.5</v>
+      </c>
+      <c r="T300">
+        <v>1.62</v>
+      </c>
+      <c r="U300">
+        <v>2.15</v>
+      </c>
+      <c r="V300">
         <v>3.9</v>
       </c>
-      <c r="T300">
-        <v>1.43</v>
-      </c>
-      <c r="U300">
-        <v>2.65</v>
-      </c>
-      <c r="V300">
-        <v>2.85</v>
-      </c>
       <c r="W300">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="X300">
-        <v>8.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Y300">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z300">
-        <v>2.34</v>
+        <v>2.91</v>
       </c>
       <c r="AA300">
-        <v>3.36</v>
+        <v>2.95</v>
       </c>
       <c r="AB300">
-        <v>3.23</v>
+        <v>2.84</v>
       </c>
       <c r="AC300">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AD300">
-        <v>8.5</v>
+        <v>5.75</v>
       </c>
       <c r="AE300">
+        <v>1.57</v>
+      </c>
+      <c r="AF300">
+        <v>2.25</v>
+      </c>
+      <c r="AG300">
+        <v>2.37</v>
+      </c>
+      <c r="AH300">
+        <v>1.48</v>
+      </c>
+      <c r="AI300">
+        <v>2.2</v>
+      </c>
+      <c r="AJ300">
+        <v>1.6</v>
+      </c>
+      <c r="AK300">
+        <v>1.44</v>
+      </c>
+      <c r="AL300">
+        <v>1.39</v>
+      </c>
+      <c r="AM300">
+        <v>1.4</v>
+      </c>
+      <c r="AN300">
+        <v>1.62</v>
+      </c>
+      <c r="AO300">
+        <v>1.38</v>
+      </c>
+      <c r="AP300">
+        <v>1.5</v>
+      </c>
+      <c r="AQ300">
+        <v>1.5</v>
+      </c>
+      <c r="AR300">
+        <v>1.42</v>
+      </c>
+      <c r="AS300">
         <v>1.33</v>
       </c>
-      <c r="AF300">
-        <v>3.05</v>
-      </c>
-      <c r="AG300">
-        <v>2.02</v>
-      </c>
-      <c r="AH300">
-        <v>1.8</v>
-      </c>
-      <c r="AI300">
-        <v>1.79</v>
-      </c>
-      <c r="AJ300">
-        <v>1.93</v>
-      </c>
-      <c r="AK300">
-        <v>1.32</v>
-      </c>
-      <c r="AL300">
-        <v>1.3</v>
-      </c>
-      <c r="AM300">
-        <v>1.63</v>
-      </c>
-      <c r="AN300">
-        <v>1.85</v>
-      </c>
-      <c r="AO300">
-        <v>2</v>
-      </c>
-      <c r="AP300">
-        <v>1.79</v>
-      </c>
-      <c r="AQ300">
-        <v>1.93</v>
-      </c>
-      <c r="AR300">
-        <v>1.54</v>
-      </c>
-      <c r="AS300">
-        <v>1.34</v>
-      </c>
       <c r="AT300">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AU300">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV300">
         <v>5</v>
       </c>
       <c r="AW300">
+        <v>3</v>
+      </c>
+      <c r="AX300">
+        <v>4</v>
+      </c>
+      <c r="AY300">
+        <v>9</v>
+      </c>
+      <c r="AZ300">
+        <v>11</v>
+      </c>
+      <c r="BA300">
+        <v>4</v>
+      </c>
+      <c r="BB300">
+        <v>2</v>
+      </c>
+      <c r="BC300">
         <v>6</v>
       </c>
-      <c r="AX300">
-        <v>10</v>
-      </c>
-      <c r="AY300">
-        <v>13</v>
-      </c>
-      <c r="AZ300">
-        <v>19</v>
-      </c>
-      <c r="BA300">
-        <v>2</v>
-      </c>
-      <c r="BB300">
-        <v>3</v>
-      </c>
-      <c r="BC300">
-        <v>5</v>
-      </c>
       <c r="BD300">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BE300">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF300">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="BG300">
+        <v>1.41</v>
+      </c>
+      <c r="BH300">
+        <v>2.6</v>
+      </c>
+      <c r="BI300">
+        <v>1.7</v>
+      </c>
+      <c r="BJ300">
+        <v>1.98</v>
+      </c>
+      <c r="BK300">
+        <v>2.14</v>
+      </c>
+      <c r="BL300">
+        <v>1.6</v>
+      </c>
+      <c r="BM300">
+        <v>2.8</v>
+      </c>
+      <c r="BN300">
         <v>1.36</v>
       </c>
-      <c r="BH300">
-        <v>2.8</v>
-      </c>
-      <c r="BI300">
-        <v>1.63</v>
-      </c>
-      <c r="BJ300">
-        <v>2.08</v>
-      </c>
-      <c r="BK300">
-        <v>2.04</v>
-      </c>
-      <c r="BL300">
-        <v>1.66</v>
-      </c>
-      <c r="BM300">
-        <v>2.6</v>
-      </c>
-      <c r="BN300">
-        <v>1.41</v>
-      </c>
       <c r="BO300">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BP300">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="301" spans="1:68">
@@ -63347,7 +63362,7 @@
         <v>300</v>
       </c>
       <c r="B301">
-        <v>7728844</v>
+        <v>7728498</v>
       </c>
       <c r="C301" t="s">
         <v>68</v>
@@ -63362,10 +63377,10 @@
         <v>28</v>
       </c>
       <c r="G301" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H301" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I301">
         <v>1</v>
@@ -63377,175 +63392,175 @@
         <v>2</v>
       </c>
       <c r="L301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M301">
         <v>2</v>
       </c>
       <c r="N301">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O301" t="s">
-        <v>147</v>
+        <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q301">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="R301">
+        <v>2.12</v>
+      </c>
+      <c r="S301">
+        <v>3.9</v>
+      </c>
+      <c r="T301">
+        <v>1.43</v>
+      </c>
+      <c r="U301">
+        <v>2.65</v>
+      </c>
+      <c r="V301">
+        <v>2.85</v>
+      </c>
+      <c r="W301">
+        <v>1.37</v>
+      </c>
+      <c r="X301">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y301">
+        <v>1.02</v>
+      </c>
+      <c r="Z301">
+        <v>2.34</v>
+      </c>
+      <c r="AA301">
+        <v>3.36</v>
+      </c>
+      <c r="AB301">
+        <v>3.23</v>
+      </c>
+      <c r="AC301">
+        <v>1.06</v>
+      </c>
+      <c r="AD301">
+        <v>8.5</v>
+      </c>
+      <c r="AE301">
+        <v>1.33</v>
+      </c>
+      <c r="AF301">
+        <v>3.05</v>
+      </c>
+      <c r="AG301">
+        <v>2.02</v>
+      </c>
+      <c r="AH301">
         <v>1.8</v>
       </c>
-      <c r="S301">
-        <v>3.5</v>
-      </c>
-      <c r="T301">
-        <v>1.62</v>
-      </c>
-      <c r="U301">
-        <v>2.15</v>
-      </c>
-      <c r="V301">
-        <v>3.9</v>
-      </c>
-      <c r="W301">
-        <v>1.22</v>
-      </c>
-      <c r="X301">
-        <v>11.5</v>
-      </c>
-      <c r="Y301">
-        <v>1.03</v>
-      </c>
-      <c r="Z301">
-        <v>2.91</v>
-      </c>
-      <c r="AA301">
-        <v>2.95</v>
-      </c>
-      <c r="AB301">
-        <v>2.84</v>
-      </c>
-      <c r="AC301">
-        <v>1.12</v>
-      </c>
-      <c r="AD301">
-        <v>5.75</v>
-      </c>
-      <c r="AE301">
-        <v>1.57</v>
-      </c>
-      <c r="AF301">
-        <v>2.25</v>
-      </c>
-      <c r="AG301">
-        <v>2.37</v>
-      </c>
-      <c r="AH301">
-        <v>1.48</v>
-      </c>
       <c r="AI301">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AJ301">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AK301">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL301">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AM301">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AN301">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AO301">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="AP301">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ301">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AR301">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AS301">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AT301">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AU301">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV301">
         <v>5</v>
       </c>
       <c r="AW301">
+        <v>6</v>
+      </c>
+      <c r="AX301">
+        <v>10</v>
+      </c>
+      <c r="AY301">
+        <v>13</v>
+      </c>
+      <c r="AZ301">
+        <v>19</v>
+      </c>
+      <c r="BA301">
+        <v>2</v>
+      </c>
+      <c r="BB301">
         <v>3</v>
       </c>
-      <c r="AX301">
-        <v>4</v>
-      </c>
-      <c r="AY301">
-        <v>9</v>
-      </c>
-      <c r="AZ301">
-        <v>11</v>
-      </c>
-      <c r="BA301">
-        <v>4</v>
-      </c>
-      <c r="BB301">
-        <v>2</v>
-      </c>
       <c r="BC301">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD301">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="BE301">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF301">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="BG301">
+        <v>1.36</v>
+      </c>
+      <c r="BH301">
+        <v>2.8</v>
+      </c>
+      <c r="BI301">
+        <v>1.63</v>
+      </c>
+      <c r="BJ301">
+        <v>2.08</v>
+      </c>
+      <c r="BK301">
+        <v>2.04</v>
+      </c>
+      <c r="BL301">
+        <v>1.66</v>
+      </c>
+      <c r="BM301">
+        <v>2.6</v>
+      </c>
+      <c r="BN301">
         <v>1.41</v>
       </c>
-      <c r="BH301">
-        <v>2.6</v>
-      </c>
-      <c r="BI301">
-        <v>1.7</v>
-      </c>
-      <c r="BJ301">
-        <v>1.98</v>
-      </c>
-      <c r="BK301">
-        <v>2.14</v>
-      </c>
-      <c r="BL301">
-        <v>1.6</v>
-      </c>
-      <c r="BM301">
-        <v>2.8</v>
-      </c>
-      <c r="BN301">
-        <v>1.36</v>
-      </c>
       <c r="BO301">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BP301">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="302" spans="1:68">
@@ -63595,7 +63610,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -64377,7 +64392,7 @@
         <v>305</v>
       </c>
       <c r="B306">
-        <v>7728495</v>
+        <v>7728500</v>
       </c>
       <c r="C306" t="s">
         <v>68</v>
@@ -64392,10 +64407,10 @@
         <v>28</v>
       </c>
       <c r="G306" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H306" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="I306">
         <v>0</v>
@@ -64407,175 +64422,175 @@
         <v>0</v>
       </c>
       <c r="L306">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M306">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N306">
         <v>1</v>
       </c>
       <c r="O306" t="s">
+        <v>137</v>
+      </c>
+      <c r="P306" t="s">
         <v>94</v>
       </c>
-      <c r="P306" t="s">
-        <v>210</v>
-      </c>
       <c r="Q306">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R306">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S306">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="T306">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U306">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="V306">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="W306">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X306">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="Y306">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z306">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AA306">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="AB306">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AC306">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AD306">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AE306">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF306">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AG306">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AH306">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AI306">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AJ306">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AK306">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL306">
         <v>1.28</v>
       </c>
       <c r="AM306">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AN306">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AO306">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AP306">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AQ306">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR306">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AS306">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AT306">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="AU306">
+        <v>3</v>
+      </c>
+      <c r="AV306">
+        <v>3</v>
+      </c>
+      <c r="AW306">
+        <v>9</v>
+      </c>
+      <c r="AX306">
+        <v>9</v>
+      </c>
+      <c r="AY306">
+        <v>16</v>
+      </c>
+      <c r="AZ306">
+        <v>15</v>
+      </c>
+      <c r="BA306">
         <v>5</v>
       </c>
-      <c r="AV306">
-        <v>4</v>
-      </c>
-      <c r="AW306">
-        <v>7</v>
-      </c>
-      <c r="AX306">
+      <c r="BB306">
+        <v>5</v>
+      </c>
+      <c r="BC306">
         <v>10</v>
       </c>
-      <c r="AY306">
-        <v>15</v>
-      </c>
-      <c r="AZ306">
-        <v>18</v>
-      </c>
-      <c r="BA306">
-        <v>4</v>
-      </c>
-      <c r="BB306">
-        <v>7</v>
-      </c>
-      <c r="BC306">
-        <v>11</v>
-      </c>
       <c r="BD306">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BE306">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF306">
         <v>2.55</v>
       </c>
       <c r="BG306">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BH306">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="BI306">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BJ306">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="BK306">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BL306">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="BM306">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="BN306">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="BO306">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BP306">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="307" spans="1:68">
@@ -64583,7 +64598,7 @@
         <v>306</v>
       </c>
       <c r="B307">
-        <v>7728500</v>
+        <v>7728495</v>
       </c>
       <c r="C307" t="s">
         <v>68</v>
@@ -64598,10 +64613,10 @@
         <v>28</v>
       </c>
       <c r="G307" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H307" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I307">
         <v>0</v>
@@ -64613,175 +64628,175 @@
         <v>0</v>
       </c>
       <c r="L307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M307">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N307">
         <v>1</v>
       </c>
       <c r="O307" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="P307" t="s">
-        <v>94</v>
+        <v>210</v>
       </c>
       <c r="Q307">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R307">
+        <v>2</v>
+      </c>
+      <c r="S307">
+        <v>4.2</v>
+      </c>
+      <c r="T307">
+        <v>1.45</v>
+      </c>
+      <c r="U307">
+        <v>2.55</v>
+      </c>
+      <c r="V307">
+        <v>3</v>
+      </c>
+      <c r="W307">
+        <v>1.33</v>
+      </c>
+      <c r="X307">
+        <v>8.1</v>
+      </c>
+      <c r="Y307">
+        <v>1.02</v>
+      </c>
+      <c r="Z307">
+        <v>2.05</v>
+      </c>
+      <c r="AA307">
+        <v>3.37</v>
+      </c>
+      <c r="AB307">
+        <v>4</v>
+      </c>
+      <c r="AC307">
+        <v>1.08</v>
+      </c>
+      <c r="AD307">
+        <v>7.5</v>
+      </c>
+      <c r="AE307">
+        <v>1.4</v>
+      </c>
+      <c r="AF307">
+        <v>2.9</v>
+      </c>
+      <c r="AG307">
         <v>2.1</v>
       </c>
-      <c r="S307">
-        <v>4.33</v>
-      </c>
-      <c r="T307">
-        <v>1.42</v>
-      </c>
-      <c r="U307">
-        <v>2.65</v>
-      </c>
-      <c r="V307">
-        <v>2.9</v>
-      </c>
-      <c r="W307">
-        <v>1.36</v>
-      </c>
-      <c r="X307">
-        <v>7.2</v>
-      </c>
-      <c r="Y307">
-        <v>1.03</v>
-      </c>
-      <c r="Z307">
-        <v>2.03</v>
-      </c>
-      <c r="AA307">
-        <v>3.45</v>
-      </c>
-      <c r="AB307">
-        <v>3.98</v>
-      </c>
-      <c r="AC307">
-        <v>1.06</v>
-      </c>
-      <c r="AD307">
-        <v>8.5</v>
-      </c>
-      <c r="AE307">
-        <v>1.36</v>
-      </c>
-      <c r="AF307">
-        <v>3.1</v>
-      </c>
-      <c r="AG307">
-        <v>2.01</v>
-      </c>
       <c r="AH307">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AI307">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AJ307">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AK307">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL307">
         <v>1.28</v>
       </c>
       <c r="AM307">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AN307">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AO307">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AP307">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AQ307">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AR307">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AS307">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AT307">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="AU307">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV307">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW307">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX307">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY307">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ307">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA307">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB307">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC307">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD307">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BE307">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF307">
         <v>2.55</v>
       </c>
       <c r="BG307">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BH307">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="BI307">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="BJ307">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="BK307">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BL307">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="BM307">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BN307">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BO307">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BP307">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="308" spans="1:68">
@@ -65037,7 +65052,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65194,6 +65209,830 @@
       </c>
       <c r="BP309">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="310" spans="1:68">
+      <c r="A310" s="1">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>7728514</v>
+      </c>
+      <c r="C310" t="s">
+        <v>68</v>
+      </c>
+      <c r="D310" t="s">
+        <v>69</v>
+      </c>
+      <c r="E310" s="2">
+        <v>45717.51041666666</v>
+      </c>
+      <c r="F310">
+        <v>29</v>
+      </c>
+      <c r="G310" t="s">
+        <v>81</v>
+      </c>
+      <c r="H310" t="s">
+        <v>74</v>
+      </c>
+      <c r="I310">
+        <v>2</v>
+      </c>
+      <c r="J310">
+        <v>1</v>
+      </c>
+      <c r="K310">
+        <v>3</v>
+      </c>
+      <c r="L310">
+        <v>3</v>
+      </c>
+      <c r="M310">
+        <v>1</v>
+      </c>
+      <c r="N310">
+        <v>4</v>
+      </c>
+      <c r="O310" t="s">
+        <v>281</v>
+      </c>
+      <c r="P310" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q310">
+        <v>2.31</v>
+      </c>
+      <c r="R310">
+        <v>2.01</v>
+      </c>
+      <c r="S310">
+        <v>6.6</v>
+      </c>
+      <c r="T310">
+        <v>1.56</v>
+      </c>
+      <c r="U310">
+        <v>2.3</v>
+      </c>
+      <c r="V310">
+        <v>3.55</v>
+      </c>
+      <c r="W310">
+        <v>1.26</v>
+      </c>
+      <c r="X310">
+        <v>9</v>
+      </c>
+      <c r="Y310">
+        <v>1.01</v>
+      </c>
+      <c r="Z310">
+        <v>1.79</v>
+      </c>
+      <c r="AA310">
+        <v>3.41</v>
+      </c>
+      <c r="AB310">
+        <v>5.4</v>
+      </c>
+      <c r="AC310">
+        <v>1.11</v>
+      </c>
+      <c r="AD310">
+        <v>6.4</v>
+      </c>
+      <c r="AE310">
+        <v>1.48</v>
+      </c>
+      <c r="AF310">
+        <v>2.37</v>
+      </c>
+      <c r="AG310">
+        <v>2.65</v>
+      </c>
+      <c r="AH310">
+        <v>1.42</v>
+      </c>
+      <c r="AI310">
+        <v>2.46</v>
+      </c>
+      <c r="AJ310">
+        <v>1.5</v>
+      </c>
+      <c r="AK310">
+        <v>1.14</v>
+      </c>
+      <c r="AL310">
+        <v>1.28</v>
+      </c>
+      <c r="AM310">
+        <v>2.09</v>
+      </c>
+      <c r="AN310">
+        <v>2</v>
+      </c>
+      <c r="AO310">
+        <v>1</v>
+      </c>
+      <c r="AP310">
+        <v>2.07</v>
+      </c>
+      <c r="AQ310">
+        <v>0.93</v>
+      </c>
+      <c r="AR310">
+        <v>1.27</v>
+      </c>
+      <c r="AS310">
+        <v>0.87</v>
+      </c>
+      <c r="AT310">
+        <v>2.14</v>
+      </c>
+      <c r="AU310">
+        <v>5</v>
+      </c>
+      <c r="AV310">
+        <v>4</v>
+      </c>
+      <c r="AW310">
+        <v>5</v>
+      </c>
+      <c r="AX310">
+        <v>6</v>
+      </c>
+      <c r="AY310">
+        <v>12</v>
+      </c>
+      <c r="AZ310">
+        <v>12</v>
+      </c>
+      <c r="BA310">
+        <v>4</v>
+      </c>
+      <c r="BB310">
+        <v>6</v>
+      </c>
+      <c r="BC310">
+        <v>10</v>
+      </c>
+      <c r="BD310">
+        <v>1.55</v>
+      </c>
+      <c r="BE310">
+        <v>6.75</v>
+      </c>
+      <c r="BF310">
+        <v>2.7</v>
+      </c>
+      <c r="BG310">
+        <v>1.43</v>
+      </c>
+      <c r="BH310">
+        <v>2.55</v>
+      </c>
+      <c r="BI310">
+        <v>1.71</v>
+      </c>
+      <c r="BJ310">
+        <v>1.97</v>
+      </c>
+      <c r="BK310">
+        <v>2.12</v>
+      </c>
+      <c r="BL310">
+        <v>1.6</v>
+      </c>
+      <c r="BM310">
+        <v>2.75</v>
+      </c>
+      <c r="BN310">
+        <v>1.37</v>
+      </c>
+      <c r="BO310">
+        <v>3.65</v>
+      </c>
+      <c r="BP310">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="311" spans="1:68">
+      <c r="A311" s="1">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>7728511</v>
+      </c>
+      <c r="C311" t="s">
+        <v>68</v>
+      </c>
+      <c r="D311" t="s">
+        <v>69</v>
+      </c>
+      <c r="E311" s="2">
+        <v>45717.51041666666</v>
+      </c>
+      <c r="F311">
+        <v>29</v>
+      </c>
+      <c r="G311" t="s">
+        <v>86</v>
+      </c>
+      <c r="H311" t="s">
+        <v>78</v>
+      </c>
+      <c r="I311">
+        <v>1</v>
+      </c>
+      <c r="J311">
+        <v>1</v>
+      </c>
+      <c r="K311">
+        <v>2</v>
+      </c>
+      <c r="L311">
+        <v>2</v>
+      </c>
+      <c r="M311">
+        <v>1</v>
+      </c>
+      <c r="N311">
+        <v>3</v>
+      </c>
+      <c r="O311" t="s">
+        <v>282</v>
+      </c>
+      <c r="P311" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q311">
+        <v>2.6</v>
+      </c>
+      <c r="R311">
+        <v>1.98</v>
+      </c>
+      <c r="S311">
+        <v>4.4</v>
+      </c>
+      <c r="T311">
+        <v>1.47</v>
+      </c>
+      <c r="U311">
+        <v>2.45</v>
+      </c>
+      <c r="V311">
+        <v>3.1</v>
+      </c>
+      <c r="W311">
+        <v>1.31</v>
+      </c>
+      <c r="X311">
+        <v>8.5</v>
+      </c>
+      <c r="Y311">
+        <v>1.06</v>
+      </c>
+      <c r="Z311">
+        <v>1.95</v>
+      </c>
+      <c r="AA311">
+        <v>3.64</v>
+      </c>
+      <c r="AB311">
+        <v>4</v>
+      </c>
+      <c r="AC311">
+        <v>1.08</v>
+      </c>
+      <c r="AD311">
+        <v>7.5</v>
+      </c>
+      <c r="AE311">
+        <v>1.38</v>
+      </c>
+      <c r="AF311">
+        <v>2.8</v>
+      </c>
+      <c r="AG311">
+        <v>1.93</v>
+      </c>
+      <c r="AH311">
+        <v>1.88</v>
+      </c>
+      <c r="AI311">
+        <v>1.98</v>
+      </c>
+      <c r="AJ311">
+        <v>1.71</v>
+      </c>
+      <c r="AK311">
+        <v>1.23</v>
+      </c>
+      <c r="AL311">
+        <v>1.32</v>
+      </c>
+      <c r="AM311">
+        <v>1.8</v>
+      </c>
+      <c r="AN311">
+        <v>1.21</v>
+      </c>
+      <c r="AO311">
+        <v>0.92</v>
+      </c>
+      <c r="AP311">
+        <v>1.33</v>
+      </c>
+      <c r="AQ311">
+        <v>0.86</v>
+      </c>
+      <c r="AR311">
+        <v>1.67</v>
+      </c>
+      <c r="AS311">
+        <v>1.2</v>
+      </c>
+      <c r="AT311">
+        <v>2.87</v>
+      </c>
+      <c r="AU311">
+        <v>4</v>
+      </c>
+      <c r="AV311">
+        <v>5</v>
+      </c>
+      <c r="AW311">
+        <v>12</v>
+      </c>
+      <c r="AX311">
+        <v>12</v>
+      </c>
+      <c r="AY311">
+        <v>19</v>
+      </c>
+      <c r="AZ311">
+        <v>22</v>
+      </c>
+      <c r="BA311">
+        <v>7</v>
+      </c>
+      <c r="BB311">
+        <v>4</v>
+      </c>
+      <c r="BC311">
+        <v>11</v>
+      </c>
+      <c r="BD311">
+        <v>1.54</v>
+      </c>
+      <c r="BE311">
+        <v>6.4</v>
+      </c>
+      <c r="BF311">
+        <v>2.8</v>
+      </c>
+      <c r="BG311">
+        <v>1.41</v>
+      </c>
+      <c r="BH311">
+        <v>2.63</v>
+      </c>
+      <c r="BI311">
+        <v>1.7</v>
+      </c>
+      <c r="BJ311">
+        <v>1.98</v>
+      </c>
+      <c r="BK311">
+        <v>2.14</v>
+      </c>
+      <c r="BL311">
+        <v>1.6</v>
+      </c>
+      <c r="BM311">
+        <v>2.75</v>
+      </c>
+      <c r="BN311">
+        <v>1.37</v>
+      </c>
+      <c r="BO311">
+        <v>3.65</v>
+      </c>
+      <c r="BP311">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="312" spans="1:68">
+      <c r="A312" s="1">
+        <v>311</v>
+      </c>
+      <c r="B312">
+        <v>7728515</v>
+      </c>
+      <c r="C312" t="s">
+        <v>68</v>
+      </c>
+      <c r="D312" t="s">
+        <v>69</v>
+      </c>
+      <c r="E312" s="2">
+        <v>45717.60416666666</v>
+      </c>
+      <c r="F312">
+        <v>29</v>
+      </c>
+      <c r="G312" t="s">
+        <v>91</v>
+      </c>
+      <c r="H312" t="s">
+        <v>76</v>
+      </c>
+      <c r="I312">
+        <v>0</v>
+      </c>
+      <c r="J312">
+        <v>0</v>
+      </c>
+      <c r="K312">
+        <v>0</v>
+      </c>
+      <c r="L312">
+        <v>1</v>
+      </c>
+      <c r="M312">
+        <v>1</v>
+      </c>
+      <c r="N312">
+        <v>2</v>
+      </c>
+      <c r="O312" t="s">
+        <v>283</v>
+      </c>
+      <c r="P312" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q312">
+        <v>3.4</v>
+      </c>
+      <c r="R312">
+        <v>1.91</v>
+      </c>
+      <c r="S312">
+        <v>4</v>
+      </c>
+      <c r="T312">
+        <v>1.57</v>
+      </c>
+      <c r="U312">
+        <v>2.25</v>
+      </c>
+      <c r="V312">
+        <v>3.75</v>
+      </c>
+      <c r="W312">
+        <v>1.25</v>
+      </c>
+      <c r="X312">
+        <v>13</v>
+      </c>
+      <c r="Y312">
+        <v>1.04</v>
+      </c>
+      <c r="Z312">
+        <v>2.52</v>
+      </c>
+      <c r="AA312">
+        <v>3.08</v>
+      </c>
+      <c r="AB312">
+        <v>3.2</v>
+      </c>
+      <c r="AC312">
+        <v>1.11</v>
+      </c>
+      <c r="AD312">
+        <v>6.4</v>
+      </c>
+      <c r="AE312">
+        <v>1.5</v>
+      </c>
+      <c r="AF312">
+        <v>2.4</v>
+      </c>
+      <c r="AG312">
+        <v>2.1</v>
+      </c>
+      <c r="AH312">
+        <v>1.6</v>
+      </c>
+      <c r="AI312">
+        <v>2.2</v>
+      </c>
+      <c r="AJ312">
+        <v>1.62</v>
+      </c>
+      <c r="AK312">
+        <v>1.36</v>
+      </c>
+      <c r="AL312">
+        <v>1.37</v>
+      </c>
+      <c r="AM312">
+        <v>1.52</v>
+      </c>
+      <c r="AN312">
+        <v>1.15</v>
+      </c>
+      <c r="AO312">
+        <v>1</v>
+      </c>
+      <c r="AP312">
+        <v>1.14</v>
+      </c>
+      <c r="AQ312">
+        <v>1</v>
+      </c>
+      <c r="AR312">
+        <v>1.54</v>
+      </c>
+      <c r="AS312">
+        <v>1.15</v>
+      </c>
+      <c r="AT312">
+        <v>2.69</v>
+      </c>
+      <c r="AU312">
+        <v>9</v>
+      </c>
+      <c r="AV312">
+        <v>7</v>
+      </c>
+      <c r="AW312">
+        <v>9</v>
+      </c>
+      <c r="AX312">
+        <v>7</v>
+      </c>
+      <c r="AY312">
+        <v>19</v>
+      </c>
+      <c r="AZ312">
+        <v>14</v>
+      </c>
+      <c r="BA312">
+        <v>6</v>
+      </c>
+      <c r="BB312">
+        <v>4</v>
+      </c>
+      <c r="BC312">
+        <v>10</v>
+      </c>
+      <c r="BD312">
+        <v>1.76</v>
+      </c>
+      <c r="BE312">
+        <v>6.4</v>
+      </c>
+      <c r="BF312">
+        <v>2.3</v>
+      </c>
+      <c r="BG312">
+        <v>1.43</v>
+      </c>
+      <c r="BH312">
+        <v>2.55</v>
+      </c>
+      <c r="BI312">
+        <v>1.71</v>
+      </c>
+      <c r="BJ312">
+        <v>1.98</v>
+      </c>
+      <c r="BK312">
+        <v>2.12</v>
+      </c>
+      <c r="BL312">
+        <v>1.61</v>
+      </c>
+      <c r="BM312">
+        <v>2.75</v>
+      </c>
+      <c r="BN312">
+        <v>1.37</v>
+      </c>
+      <c r="BO312">
+        <v>3.65</v>
+      </c>
+      <c r="BP312">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="313" spans="1:68">
+      <c r="A313" s="1">
+        <v>312</v>
+      </c>
+      <c r="B313">
+        <v>7728506</v>
+      </c>
+      <c r="C313" t="s">
+        <v>68</v>
+      </c>
+      <c r="D313" t="s">
+        <v>69</v>
+      </c>
+      <c r="E313" s="2">
+        <v>45717.70833333334</v>
+      </c>
+      <c r="F313">
+        <v>29</v>
+      </c>
+      <c r="G313" t="s">
+        <v>90</v>
+      </c>
+      <c r="H313" t="s">
+        <v>83</v>
+      </c>
+      <c r="I313">
+        <v>1</v>
+      </c>
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313">
+        <v>1</v>
+      </c>
+      <c r="L313">
+        <v>2</v>
+      </c>
+      <c r="M313">
+        <v>2</v>
+      </c>
+      <c r="N313">
+        <v>4</v>
+      </c>
+      <c r="O313" t="s">
+        <v>284</v>
+      </c>
+      <c r="P313" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q313">
+        <v>1.92</v>
+      </c>
+      <c r="R313">
+        <v>2.49</v>
+      </c>
+      <c r="S313">
+        <v>6.2</v>
+      </c>
+      <c r="T313">
+        <v>1.3</v>
+      </c>
+      <c r="U313">
+        <v>3.25</v>
+      </c>
+      <c r="V313">
+        <v>2.39</v>
+      </c>
+      <c r="W313">
+        <v>1.52</v>
+      </c>
+      <c r="X313">
+        <v>5.5</v>
+      </c>
+      <c r="Y313">
+        <v>1.12</v>
+      </c>
+      <c r="Z313">
+        <v>1.5</v>
+      </c>
+      <c r="AA313">
+        <v>4.6</v>
+      </c>
+      <c r="AB313">
+        <v>6.7</v>
+      </c>
+      <c r="AC313">
+        <v>1.04</v>
+      </c>
+      <c r="AD313">
+        <v>10</v>
+      </c>
+      <c r="AE313">
+        <v>1.22</v>
+      </c>
+      <c r="AF313">
+        <v>3.9</v>
+      </c>
+      <c r="AG313">
+        <v>1.81</v>
+      </c>
+      <c r="AH313">
+        <v>2.01</v>
+      </c>
+      <c r="AI313">
+        <v>1.82</v>
+      </c>
+      <c r="AJ313">
+        <v>1.88</v>
+      </c>
+      <c r="AK313">
+        <v>1.12</v>
+      </c>
+      <c r="AL313">
+        <v>1.19</v>
+      </c>
+      <c r="AM313">
+        <v>2.49</v>
+      </c>
+      <c r="AN313">
+        <v>1.85</v>
+      </c>
+      <c r="AO313">
+        <v>1</v>
+      </c>
+      <c r="AP313">
+        <v>1.79</v>
+      </c>
+      <c r="AQ313">
+        <v>1</v>
+      </c>
+      <c r="AR313">
+        <v>1.7</v>
+      </c>
+      <c r="AS313">
+        <v>1.19</v>
+      </c>
+      <c r="AT313">
+        <v>2.89</v>
+      </c>
+      <c r="AU313">
+        <v>6</v>
+      </c>
+      <c r="AV313">
+        <v>4</v>
+      </c>
+      <c r="AW313">
+        <v>15</v>
+      </c>
+      <c r="AX313">
+        <v>6</v>
+      </c>
+      <c r="AY313">
+        <v>25</v>
+      </c>
+      <c r="AZ313">
+        <v>13</v>
+      </c>
+      <c r="BA313">
+        <v>7</v>
+      </c>
+      <c r="BB313">
+        <v>3</v>
+      </c>
+      <c r="BC313">
+        <v>10</v>
+      </c>
+      <c r="BD313">
+        <v>1.36</v>
+      </c>
+      <c r="BE313">
+        <v>7</v>
+      </c>
+      <c r="BF313">
+        <v>3.45</v>
+      </c>
+      <c r="BG313">
+        <v>1.35</v>
+      </c>
+      <c r="BH313">
+        <v>2.85</v>
+      </c>
+      <c r="BI313">
+        <v>1.6</v>
+      </c>
+      <c r="BJ313">
+        <v>2.15</v>
+      </c>
+      <c r="BK313">
+        <v>1.96</v>
+      </c>
+      <c r="BL313">
+        <v>1.71</v>
+      </c>
+      <c r="BM313">
+        <v>2.5</v>
+      </c>
+      <c r="BN313">
+        <v>1.44</v>
+      </c>
+      <c r="BO313">
+        <v>3.3</v>
+      </c>
+      <c r="BP313">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="394">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -871,6 +871,9 @@
     <t>['11', '53']</t>
   </si>
   <si>
+    <t>['7', '25', '49', '78', '84']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1554,7 +1557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP313"/>
+  <dimension ref="A1:BP314"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1810,7 +1813,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2222,7 +2225,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3046,7 +3049,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3252,7 +3255,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4076,7 +4079,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4282,7 +4285,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4775,7 +4778,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ16">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR16">
         <v>1.33</v>
@@ -5312,7 +5315,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5930,7 +5933,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6136,7 +6139,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6214,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ23">
         <v>0.86</v>
@@ -6342,7 +6345,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6548,7 +6551,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6754,7 +6757,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6960,7 +6963,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7372,7 +7375,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7990,7 +7993,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8196,7 +8199,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8608,7 +8611,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9510,7 +9513,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -10462,7 +10465,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10952,7 +10955,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ46">
         <v>1.36</v>
@@ -11080,7 +11083,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12728,7 +12731,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12809,7 +12812,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ55">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR55">
         <v>1.39</v>
@@ -12934,7 +12937,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13140,7 +13143,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13346,7 +13349,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13758,7 +13761,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14376,7 +14379,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14994,7 +14997,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15406,7 +15409,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15612,7 +15615,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16230,7 +16233,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16436,7 +16439,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16642,7 +16645,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16723,7 +16726,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ74">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR74">
         <v>1.54</v>
@@ -17132,7 +17135,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ76">
         <v>0.93</v>
@@ -17466,7 +17469,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17672,7 +17675,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18084,7 +18087,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18165,7 +18168,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ81">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR81">
         <v>1.07</v>
@@ -18290,7 +18293,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18496,7 +18499,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19320,7 +19323,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19732,7 +19735,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19938,7 +19941,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20350,7 +20353,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20762,7 +20765,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20968,7 +20971,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21998,7 +22001,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22282,7 +22285,7 @@
         <v>1.2</v>
       </c>
       <c r="AP101">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ101">
         <v>0.47</v>
@@ -23440,7 +23443,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24058,7 +24061,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24470,7 +24473,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24676,7 +24679,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24757,7 +24760,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ113">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -25088,7 +25091,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25912,7 +25915,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26530,7 +26533,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26942,7 +26945,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27226,7 +27229,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ125">
         <v>0.93</v>
@@ -27354,7 +27357,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27766,7 +27769,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28178,7 +28181,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28384,7 +28387,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28590,7 +28593,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29002,7 +29005,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29208,7 +29211,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29701,7 +29704,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ137">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR137">
         <v>1.67</v>
@@ -29826,7 +29829,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30444,7 +30447,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30650,7 +30653,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30856,7 +30859,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31062,7 +31065,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31474,7 +31477,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31552,7 +31555,7 @@
         <v>2</v>
       </c>
       <c r="AP146">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ146">
         <v>1.36</v>
@@ -31886,7 +31889,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32916,7 +32919,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33534,7 +33537,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33615,7 +33618,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ156">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR156">
         <v>1.44</v>
@@ -35182,7 +35185,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35800,7 +35803,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35878,7 +35881,7 @@
         <v>1.75</v>
       </c>
       <c r="AP167">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ167">
         <v>1.33</v>
@@ -36830,7 +36833,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37448,7 +37451,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37860,7 +37863,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38272,7 +38275,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38353,7 +38356,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ179">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR179">
         <v>1.71</v>
@@ -38478,7 +38481,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39302,7 +39305,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40126,7 +40129,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40744,7 +40747,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40950,7 +40953,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41156,7 +41159,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41362,7 +41365,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42058,7 +42061,7 @@
         <v>0.25</v>
       </c>
       <c r="AP197">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ197">
         <v>0.21</v>
@@ -42598,7 +42601,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43010,7 +43013,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43216,7 +43219,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43709,7 +43712,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ205">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR205">
         <v>1.69</v>
@@ -43834,7 +43837,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44864,7 +44867,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44942,7 +44945,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP211">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ211">
         <v>0.8</v>
@@ -45070,7 +45073,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45276,7 +45279,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45482,7 +45485,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45894,7 +45897,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -47005,7 +47008,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ221">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR221">
         <v>1.48</v>
@@ -47130,7 +47133,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47542,7 +47545,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47954,7 +47957,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48572,7 +48575,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48778,7 +48781,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48984,7 +48987,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49808,7 +49811,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50632,7 +50635,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50710,7 +50713,7 @@
         <v>1.64</v>
       </c>
       <c r="AP239">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ239">
         <v>1.47</v>
@@ -51250,7 +51253,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51662,7 +51665,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52074,7 +52077,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52361,7 +52364,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ247">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR247">
         <v>1.54</v>
@@ -52898,7 +52901,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53104,7 +53107,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53516,7 +53519,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53928,7 +53931,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54006,7 +54009,7 @@
         <v>2.09</v>
       </c>
       <c r="AP255">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ255">
         <v>1.93</v>
@@ -54134,7 +54137,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -55164,7 +55167,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55370,7 +55373,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55988,7 +55991,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56069,7 +56072,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ265">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR265">
         <v>1.45</v>
@@ -56812,7 +56815,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57430,7 +57433,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -58460,7 +58463,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59696,7 +59699,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59774,7 +59777,7 @@
         <v>1.38</v>
       </c>
       <c r="AP283">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ283">
         <v>1.47</v>
@@ -59902,7 +59905,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60520,7 +60523,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61138,7 +61141,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61344,7 +61347,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -62043,7 +62046,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ294">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR294">
         <v>1.27</v>
@@ -63198,7 +63201,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63404,7 +63407,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63610,7 +63613,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -65052,7 +65055,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65258,7 +65261,7 @@
         <v>281</v>
       </c>
       <c r="P310" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q310">
         <v>2.31</v>
@@ -65876,7 +65879,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66032,6 +66035,212 @@
         <v>3.3</v>
       </c>
       <c r="BP313">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="314" spans="1:68">
+      <c r="A314" s="1">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>7728508</v>
+      </c>
+      <c r="C314" t="s">
+        <v>68</v>
+      </c>
+      <c r="D314" t="s">
+        <v>69</v>
+      </c>
+      <c r="E314" s="2">
+        <v>45718.41666666666</v>
+      </c>
+      <c r="F314">
+        <v>29</v>
+      </c>
+      <c r="G314" t="s">
+        <v>88</v>
+      </c>
+      <c r="H314" t="s">
+        <v>70</v>
+      </c>
+      <c r="I314">
+        <v>2</v>
+      </c>
+      <c r="J314">
+        <v>0</v>
+      </c>
+      <c r="K314">
+        <v>2</v>
+      </c>
+      <c r="L314">
+        <v>5</v>
+      </c>
+      <c r="M314">
+        <v>0</v>
+      </c>
+      <c r="N314">
+        <v>5</v>
+      </c>
+      <c r="O314" t="s">
+        <v>285</v>
+      </c>
+      <c r="P314" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q314">
+        <v>3.1</v>
+      </c>
+      <c r="R314">
+        <v>2.12</v>
+      </c>
+      <c r="S314">
+        <v>3.5</v>
+      </c>
+      <c r="T314">
+        <v>1.43</v>
+      </c>
+      <c r="U314">
+        <v>2.65</v>
+      </c>
+      <c r="V314">
+        <v>2.85</v>
+      </c>
+      <c r="W314">
+        <v>1.38</v>
+      </c>
+      <c r="X314">
+        <v>7.2</v>
+      </c>
+      <c r="Y314">
+        <v>1.03</v>
+      </c>
+      <c r="Z314">
+        <v>2.44</v>
+      </c>
+      <c r="AA314">
+        <v>3.36</v>
+      </c>
+      <c r="AB314">
+        <v>3.06</v>
+      </c>
+      <c r="AC314">
+        <v>1.07</v>
+      </c>
+      <c r="AD314">
+        <v>8</v>
+      </c>
+      <c r="AE314">
+        <v>1.32</v>
+      </c>
+      <c r="AF314">
+        <v>3.1</v>
+      </c>
+      <c r="AG314">
+        <v>2</v>
+      </c>
+      <c r="AH314">
+        <v>1.82</v>
+      </c>
+      <c r="AI314">
+        <v>1.75</v>
+      </c>
+      <c r="AJ314">
+        <v>1.98</v>
+      </c>
+      <c r="AK314">
+        <v>1.39</v>
+      </c>
+      <c r="AL314">
+        <v>1.31</v>
+      </c>
+      <c r="AM314">
+        <v>1.52</v>
+      </c>
+      <c r="AN314">
+        <v>1.69</v>
+      </c>
+      <c r="AO314">
+        <v>1.46</v>
+      </c>
+      <c r="AP314">
+        <v>1.79</v>
+      </c>
+      <c r="AQ314">
+        <v>1.36</v>
+      </c>
+      <c r="AR314">
+        <v>1.64</v>
+      </c>
+      <c r="AS314">
+        <v>1.15</v>
+      </c>
+      <c r="AT314">
+        <v>2.79</v>
+      </c>
+      <c r="AU314">
+        <v>-1</v>
+      </c>
+      <c r="AV314">
+        <v>-1</v>
+      </c>
+      <c r="AW314">
+        <v>-1</v>
+      </c>
+      <c r="AX314">
+        <v>-1</v>
+      </c>
+      <c r="AY314">
+        <v>-1</v>
+      </c>
+      <c r="AZ314">
+        <v>-1</v>
+      </c>
+      <c r="BA314">
+        <v>-1</v>
+      </c>
+      <c r="BB314">
+        <v>-1</v>
+      </c>
+      <c r="BC314">
+        <v>-1</v>
+      </c>
+      <c r="BD314">
+        <v>1.65</v>
+      </c>
+      <c r="BE314">
+        <v>6.5</v>
+      </c>
+      <c r="BF314">
+        <v>2.5</v>
+      </c>
+      <c r="BG314">
+        <v>1.36</v>
+      </c>
+      <c r="BH314">
+        <v>2.8</v>
+      </c>
+      <c r="BI314">
+        <v>1.6</v>
+      </c>
+      <c r="BJ314">
+        <v>2.14</v>
+      </c>
+      <c r="BK314">
+        <v>1.98</v>
+      </c>
+      <c r="BL314">
+        <v>1.7</v>
+      </c>
+      <c r="BM314">
+        <v>2.55</v>
+      </c>
+      <c r="BN314">
+        <v>1.43</v>
+      </c>
+      <c r="BO314">
+        <v>3.3</v>
+      </c>
+      <c r="BP314">
         <v>1.27</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="395">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1197,6 +1197,9 @@
   <si>
     <t>['55', '62']</t>
   </si>
+  <si>
+    <t>['23', '90+1']</t>
+  </si>
 </sst>
 </file>
 
@@ -1557,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP314"/>
+  <dimension ref="A1:BP315"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4366,7 +4369,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ14">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -6629,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ25">
         <v>1.93</v>
@@ -8898,7 +8901,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ36">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR36">
         <v>2.09</v>
@@ -10958,7 +10961,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ46">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -12191,7 +12194,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ52">
         <v>0.47</v>
@@ -15490,7 +15493,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR68">
         <v>1.07</v>
@@ -17341,7 +17344,7 @@
         <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ77">
         <v>0.8</v>
@@ -21049,7 +21052,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ95">
         <v>1.47</v>
@@ -21876,7 +21879,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ99">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR99">
         <v>1.46</v>
@@ -24551,7 +24554,7 @@
         <v>1.25</v>
       </c>
       <c r="AP112">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ112">
         <v>1.07</v>
@@ -25996,7 +25999,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ119">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR119">
         <v>1.68</v>
@@ -29292,7 +29295,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ135">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR135">
         <v>1.12</v>
@@ -30113,7 +30116,7 @@
         <v>1.17</v>
       </c>
       <c r="AP139">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ139">
         <v>0.86</v>
@@ -34027,7 +34030,7 @@
         <v>0.33</v>
       </c>
       <c r="AP158">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ158">
         <v>0.21</v>
@@ -34236,7 +34239,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ159">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR159">
         <v>1.75</v>
@@ -37941,7 +37944,7 @@
         <v>0.88</v>
       </c>
       <c r="AP177">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ177">
         <v>1.47</v>
@@ -38562,7 +38565,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ180">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR180">
         <v>1.48</v>
@@ -43709,7 +43712,7 @@
         <v>1.75</v>
       </c>
       <c r="AP205">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ205">
         <v>1.36</v>
@@ -47211,7 +47214,7 @@
         <v>0.2</v>
       </c>
       <c r="AP222">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ222">
         <v>1.13</v>
@@ -50304,7 +50307,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ237">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR237">
         <v>1.37</v>
@@ -50507,7 +50510,7 @@
         <v>1.1</v>
       </c>
       <c r="AP238">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ238">
         <v>1</v>
@@ -52570,7 +52573,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ248">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR248">
         <v>1.41</v>
@@ -55039,7 +55042,7 @@
         <v>1.36</v>
       </c>
       <c r="AP260">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ260">
         <v>1.36</v>
@@ -55866,7 +55869,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ264">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR264">
         <v>1.24</v>
@@ -57308,7 +57311,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ271">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR271">
         <v>1.48</v>
@@ -60395,7 +60398,7 @@
         <v>0.75</v>
       </c>
       <c r="AP286">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ286">
         <v>0.93</v>
@@ -61840,7 +61843,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ293">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR293">
         <v>1.47</v>
@@ -62455,7 +62458,7 @@
         <v>1</v>
       </c>
       <c r="AP296">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ296">
         <v>0.93</v>
@@ -66178,31 +66181,31 @@
         <v>2.79</v>
       </c>
       <c r="AU314">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AV314">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW314">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX314">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AY314">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AZ314">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="BA314">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB314">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC314">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD314">
         <v>1.65</v>
@@ -66242,6 +66245,212 @@
       </c>
       <c r="BP314">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="315" spans="1:68">
+      <c r="A315" s="1">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>7728512</v>
+      </c>
+      <c r="C315" t="s">
+        <v>68</v>
+      </c>
+      <c r="D315" t="s">
+        <v>69</v>
+      </c>
+      <c r="E315" s="2">
+        <v>45718.51041666666</v>
+      </c>
+      <c r="F315">
+        <v>29</v>
+      </c>
+      <c r="G315" t="s">
+        <v>89</v>
+      </c>
+      <c r="H315" t="s">
+        <v>75</v>
+      </c>
+      <c r="I315">
+        <v>1</v>
+      </c>
+      <c r="J315">
+        <v>1</v>
+      </c>
+      <c r="K315">
+        <v>2</v>
+      </c>
+      <c r="L315">
+        <v>1</v>
+      </c>
+      <c r="M315">
+        <v>2</v>
+      </c>
+      <c r="N315">
+        <v>3</v>
+      </c>
+      <c r="O315" t="s">
+        <v>138</v>
+      </c>
+      <c r="P315" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q315">
+        <v>2.49</v>
+      </c>
+      <c r="R315">
+        <v>2.07</v>
+      </c>
+      <c r="S315">
+        <v>5</v>
+      </c>
+      <c r="T315">
+        <v>1.48</v>
+      </c>
+      <c r="U315">
+        <v>2.45</v>
+      </c>
+      <c r="V315">
+        <v>3.1</v>
+      </c>
+      <c r="W315">
+        <v>1.32</v>
+      </c>
+      <c r="X315">
+        <v>9</v>
+      </c>
+      <c r="Y315">
+        <v>1.01</v>
+      </c>
+      <c r="Z315">
+        <v>1.91</v>
+      </c>
+      <c r="AA315">
+        <v>3.5</v>
+      </c>
+      <c r="AB315">
+        <v>4.4</v>
+      </c>
+      <c r="AC315">
+        <v>1.08</v>
+      </c>
+      <c r="AD315">
+        <v>7.5</v>
+      </c>
+      <c r="AE315">
+        <v>1.39</v>
+      </c>
+      <c r="AF315">
+        <v>2.7</v>
+      </c>
+      <c r="AG315">
+        <v>2.1</v>
+      </c>
+      <c r="AH315">
+        <v>1.6</v>
+      </c>
+      <c r="AI315">
+        <v>2</v>
+      </c>
+      <c r="AJ315">
+        <v>1.73</v>
+      </c>
+      <c r="AK315">
+        <v>1.21</v>
+      </c>
+      <c r="AL315">
+        <v>1.29</v>
+      </c>
+      <c r="AM315">
+        <v>1.85</v>
+      </c>
+      <c r="AN315">
+        <v>2.07</v>
+      </c>
+      <c r="AO315">
+        <v>1.36</v>
+      </c>
+      <c r="AP315">
+        <v>1.93</v>
+      </c>
+      <c r="AQ315">
+        <v>1.47</v>
+      </c>
+      <c r="AR315">
+        <v>1.64</v>
+      </c>
+      <c r="AS315">
+        <v>1.31</v>
+      </c>
+      <c r="AT315">
+        <v>2.95</v>
+      </c>
+      <c r="AU315">
+        <v>4</v>
+      </c>
+      <c r="AV315">
+        <v>3</v>
+      </c>
+      <c r="AW315">
+        <v>3</v>
+      </c>
+      <c r="AX315">
+        <v>7</v>
+      </c>
+      <c r="AY315">
+        <v>7</v>
+      </c>
+      <c r="AZ315">
+        <v>15</v>
+      </c>
+      <c r="BA315">
+        <v>6</v>
+      </c>
+      <c r="BB315">
+        <v>7</v>
+      </c>
+      <c r="BC315">
+        <v>13</v>
+      </c>
+      <c r="BD315">
+        <v>1.48</v>
+      </c>
+      <c r="BE315">
+        <v>7</v>
+      </c>
+      <c r="BF315">
+        <v>2.9</v>
+      </c>
+      <c r="BG315">
+        <v>1.27</v>
+      </c>
+      <c r="BH315">
+        <v>3.3</v>
+      </c>
+      <c r="BI315">
+        <v>1.44</v>
+      </c>
+      <c r="BJ315">
+        <v>2.5</v>
+      </c>
+      <c r="BK315">
+        <v>1.71</v>
+      </c>
+      <c r="BL315">
+        <v>1.96</v>
+      </c>
+      <c r="BM315">
+        <v>2.12</v>
+      </c>
+      <c r="BN315">
+        <v>1.61</v>
+      </c>
+      <c r="BO315">
+        <v>2.7</v>
+      </c>
+      <c r="BP315">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="398">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -874,6 +874,12 @@
     <t>['7', '25', '49', '78', '84']</t>
   </si>
   <si>
+    <t>['66', '74', '89']</t>
+  </si>
+  <si>
+    <t>['5', '23']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1199,6 +1205,9 @@
   </si>
   <si>
     <t>['23', '90+1']</t>
+  </si>
+  <si>
+    <t>['90+1', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP315"/>
+  <dimension ref="A1:BP318"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1816,7 +1825,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2228,7 +2237,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3052,7 +3061,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3133,7 +3142,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ8">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3258,7 +3267,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3336,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9">
         <v>1.47</v>
@@ -3954,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ12">
         <v>0.21</v>
@@ -4082,7 +4091,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4160,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ13">
         <v>0.8</v>
@@ -4288,7 +4297,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4987,7 +4996,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ17">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5318,7 +5327,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5602,10 +5611,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ20">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5936,7 +5945,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6142,7 +6151,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6348,7 +6357,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6554,7 +6563,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6760,7 +6769,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6966,7 +6975,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7378,7 +7387,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7996,7 +8005,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8074,7 +8083,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ32">
         <v>0.47</v>
@@ -8202,7 +8211,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8283,7 +8292,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ33">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR33">
         <v>0.95</v>
@@ -8614,7 +8623,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9931,7 +9940,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ41">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR41">
         <v>1</v>
@@ -10134,7 +10143,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ42">
         <v>1.47</v>
@@ -10343,7 +10352,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ43">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR43">
         <v>0</v>
@@ -10468,7 +10477,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10549,7 +10558,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ44">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -10752,7 +10761,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ45">
         <v>0.8</v>
@@ -11086,7 +11095,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11782,7 +11791,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -12734,7 +12743,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12940,7 +12949,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13146,7 +13155,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13352,7 +13361,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13636,7 +13645,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ59">
         <v>1.5</v>
@@ -13764,7 +13773,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14051,7 +14060,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ61">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -14382,7 +14391,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14463,7 +14472,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ63">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR63">
         <v>1.13</v>
@@ -15000,7 +15009,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15412,7 +15421,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15490,7 +15499,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ68">
         <v>1.47</v>
@@ -15618,7 +15627,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16236,7 +16245,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16317,7 +16326,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ72">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR72">
         <v>1.35</v>
@@ -16442,7 +16451,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16648,7 +16657,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17472,7 +17481,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17550,7 +17559,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ78">
         <v>0.47</v>
@@ -17678,7 +17687,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17759,7 +17768,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ79">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR79">
         <v>1.18</v>
@@ -17965,7 +17974,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ80">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR80">
         <v>1.23</v>
@@ -18090,7 +18099,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18296,7 +18305,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18502,7 +18511,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19326,7 +19335,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19404,7 +19413,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ87">
         <v>1.36</v>
@@ -19738,7 +19747,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19816,7 +19825,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ89">
         <v>1.13</v>
@@ -19944,7 +19953,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20356,7 +20365,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20768,7 +20777,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20974,7 +20983,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21258,10 +21267,10 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ96">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR96">
         <v>1.53</v>
@@ -22004,7 +22013,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23115,7 +23124,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ105">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR105">
         <v>1.64</v>
@@ -23446,7 +23455,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24064,7 +24073,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24348,7 +24357,7 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ111">
         <v>0.86</v>
@@ -24476,7 +24485,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24682,7 +24691,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24969,7 +24978,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ114">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -25094,7 +25103,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25172,7 +25181,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -25378,7 +25387,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ116">
         <v>1.13</v>
@@ -25587,7 +25596,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ117">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR117">
         <v>1.16</v>
@@ -25918,7 +25927,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26536,7 +26545,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26948,7 +26957,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27360,7 +27369,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27772,7 +27781,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28184,7 +28193,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28262,7 +28271,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28390,7 +28399,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28596,7 +28605,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28677,7 +28686,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ132">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR132">
         <v>1.78</v>
@@ -29008,7 +29017,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29089,7 +29098,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ134">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR134">
         <v>1.4</v>
@@ -29214,7 +29223,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29501,7 +29510,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ136">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -29832,7 +29841,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29910,7 +29919,7 @@
         <v>1.17</v>
       </c>
       <c r="AP138">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ138">
         <v>0.93</v>
@@ -30450,7 +30459,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30656,7 +30665,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30737,7 +30746,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ142">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR142">
         <v>1.16</v>
@@ -30862,7 +30871,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31068,7 +31077,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31480,7 +31489,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31892,7 +31901,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32176,7 +32185,7 @@
         <v>1</v>
       </c>
       <c r="AP149">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ149">
         <v>1.5</v>
@@ -32794,7 +32803,7 @@
         <v>1.14</v>
       </c>
       <c r="AP152">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ152">
         <v>0.93</v>
@@ -32922,7 +32931,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33209,7 +33218,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ154">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR154">
         <v>1.67</v>
@@ -33412,7 +33421,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ155">
         <v>0.86</v>
@@ -33540,7 +33549,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34854,7 +34863,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ162">
         <v>1.47</v>
@@ -35063,7 +35072,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ163">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR163">
         <v>1.14</v>
@@ -35188,7 +35197,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35475,7 +35484,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ165">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR165">
         <v>1.7</v>
@@ -35806,7 +35815,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36296,7 +36305,7 @@
         <v>0.29</v>
       </c>
       <c r="AP169">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ169">
         <v>0.21</v>
@@ -36836,7 +36845,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37454,7 +37463,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37866,7 +37875,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38278,7 +38287,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38484,7 +38493,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38768,7 +38777,7 @@
         <v>1.14</v>
       </c>
       <c r="AP181">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ181">
         <v>1.07</v>
@@ -38977,7 +38986,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ182">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR182">
         <v>1.26</v>
@@ -39308,7 +39317,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39592,7 +39601,7 @@
         <v>0.86</v>
       </c>
       <c r="AP185">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ185">
         <v>0.93</v>
@@ -40132,7 +40141,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40213,7 +40222,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ188">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR188">
         <v>1.17</v>
@@ -40419,7 +40428,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ189">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR189">
         <v>1.53</v>
@@ -40750,7 +40759,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40956,7 +40965,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41162,7 +41171,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41368,7 +41377,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41652,7 +41661,7 @@
         <v>1.75</v>
       </c>
       <c r="AP195">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ195">
         <v>1.36</v>
@@ -42604,7 +42613,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43016,7 +43025,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43222,7 +43231,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43506,10 +43515,10 @@
         <v>1.13</v>
       </c>
       <c r="AP204">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ204">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR204">
         <v>1.41</v>
@@ -43840,7 +43849,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44330,7 +44339,7 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ208">
         <v>1.47</v>
@@ -44742,10 +44751,10 @@
         <v>1.22</v>
       </c>
       <c r="AP210">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ210">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR210">
         <v>1.59</v>
@@ -44870,7 +44879,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45076,7 +45085,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45282,7 +45291,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45488,7 +45497,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45900,7 +45909,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -47136,7 +47145,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47548,7 +47557,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47960,7 +47969,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48041,7 +48050,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ226">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR226">
         <v>1.73</v>
@@ -48247,7 +48256,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ227">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR227">
         <v>1.67</v>
@@ -48450,7 +48459,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ228">
         <v>0.93</v>
@@ -48578,7 +48587,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48784,7 +48793,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48990,7 +48999,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49071,7 +49080,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ231">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR231">
         <v>1.26</v>
@@ -49814,7 +49823,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -49892,7 +49901,7 @@
         <v>2.2</v>
       </c>
       <c r="AP235">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ235">
         <v>1.93</v>
@@ -50638,7 +50647,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50925,7 +50934,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ240">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR240">
         <v>1.44</v>
@@ -51256,7 +51265,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51334,7 +51343,7 @@
         <v>0.5</v>
       </c>
       <c r="AP242">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ242">
         <v>0.8</v>
@@ -51668,7 +51677,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51746,10 +51755,10 @@
         <v>1</v>
       </c>
       <c r="AP244">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ244">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR244">
         <v>1.4</v>
@@ -52080,7 +52089,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52161,7 +52170,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ246">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR246">
         <v>1.56</v>
@@ -52776,7 +52785,7 @@
         <v>1</v>
       </c>
       <c r="AP249">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ249">
         <v>0.93</v>
@@ -52904,7 +52913,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53110,7 +53119,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53522,7 +53531,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53934,7 +53943,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54140,7 +54149,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54221,7 +54230,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ256">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR256">
         <v>1.43</v>
@@ -55170,7 +55179,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55248,7 +55257,7 @@
         <v>1.75</v>
       </c>
       <c r="AP261">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ261">
         <v>1.47</v>
@@ -55376,7 +55385,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55994,7 +56003,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56072,7 +56081,7 @@
         <v>1.36</v>
       </c>
       <c r="AP265">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ265">
         <v>1.36</v>
@@ -56281,7 +56290,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ266">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR266">
         <v>1.24</v>
@@ -56818,7 +56827,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -56896,7 +56905,7 @@
         <v>0.92</v>
       </c>
       <c r="AP269">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ269">
         <v>1</v>
@@ -57436,7 +57445,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -57723,7 +57732,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ273">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR273">
         <v>1.65</v>
@@ -58338,7 +58347,7 @@
         <v>1.46</v>
       </c>
       <c r="AP276">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ276">
         <v>1.33</v>
@@ -58466,7 +58475,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58959,7 +58968,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ279">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR279">
         <v>1.34</v>
@@ -59702,7 +59711,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59908,7 +59917,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60526,7 +60535,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61144,7 +61153,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61222,10 +61231,10 @@
         <v>1.17</v>
       </c>
       <c r="AP290">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ290">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR290">
         <v>1.62</v>
@@ -61350,7 +61359,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61840,7 +61849,7 @@
         <v>1.46</v>
       </c>
       <c r="AP293">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ293">
         <v>1.47</v>
@@ -62667,7 +62676,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ297">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR297">
         <v>1.76</v>
@@ -63204,7 +63213,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63410,7 +63419,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63616,7 +63625,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -64724,7 +64733,7 @@
         <v>0.77</v>
       </c>
       <c r="AP307">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ307">
         <v>0.93</v>
@@ -65058,7 +65067,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65264,7 +65273,7 @@
         <v>281</v>
       </c>
       <c r="P310" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q310">
         <v>2.31</v>
@@ -65882,7 +65891,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66294,7 +66303,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66451,6 +66460,624 @@
       </c>
       <c r="BP315">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="316" spans="1:68">
+      <c r="A316" s="1">
+        <v>315</v>
+      </c>
+      <c r="B316">
+        <v>7728509</v>
+      </c>
+      <c r="C316" t="s">
+        <v>68</v>
+      </c>
+      <c r="D316" t="s">
+        <v>69</v>
+      </c>
+      <c r="E316" s="2">
+        <v>45718.60416666666</v>
+      </c>
+      <c r="F316">
+        <v>29</v>
+      </c>
+      <c r="G316" t="s">
+        <v>80</v>
+      </c>
+      <c r="H316" t="s">
+        <v>82</v>
+      </c>
+      <c r="I316">
+        <v>1</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>1</v>
+      </c>
+      <c r="L316">
+        <v>1</v>
+      </c>
+      <c r="M316">
+        <v>2</v>
+      </c>
+      <c r="N316">
+        <v>3</v>
+      </c>
+      <c r="O316" t="s">
+        <v>130</v>
+      </c>
+      <c r="P316" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q316">
+        <v>3.45</v>
+      </c>
+      <c r="R316">
+        <v>2.06</v>
+      </c>
+      <c r="S316">
+        <v>3.3</v>
+      </c>
+      <c r="T316">
+        <v>1.46</v>
+      </c>
+      <c r="U316">
+        <v>2.55</v>
+      </c>
+      <c r="V316">
+        <v>3</v>
+      </c>
+      <c r="W316">
+        <v>1.34</v>
+      </c>
+      <c r="X316">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y316">
+        <v>1</v>
+      </c>
+      <c r="Z316">
+        <v>2.87</v>
+      </c>
+      <c r="AA316">
+        <v>3.26</v>
+      </c>
+      <c r="AB316">
+        <v>2.64</v>
+      </c>
+      <c r="AC316">
+        <v>1.08</v>
+      </c>
+      <c r="AD316">
+        <v>7.5</v>
+      </c>
+      <c r="AE316">
+        <v>1.36</v>
+      </c>
+      <c r="AF316">
+        <v>2.85</v>
+      </c>
+      <c r="AG316">
+        <v>2.05</v>
+      </c>
+      <c r="AH316">
+        <v>1.61</v>
+      </c>
+      <c r="AI316">
+        <v>1.83</v>
+      </c>
+      <c r="AJ316">
+        <v>1.88</v>
+      </c>
+      <c r="AK316">
+        <v>1.47</v>
+      </c>
+      <c r="AL316">
+        <v>1.33</v>
+      </c>
+      <c r="AM316">
+        <v>1.43</v>
+      </c>
+      <c r="AN316">
+        <v>1.29</v>
+      </c>
+      <c r="AO316">
+        <v>1.43</v>
+      </c>
+      <c r="AP316">
+        <v>1.2</v>
+      </c>
+      <c r="AQ316">
+        <v>1.53</v>
+      </c>
+      <c r="AR316">
+        <v>1.53</v>
+      </c>
+      <c r="AS316">
+        <v>1.24</v>
+      </c>
+      <c r="AT316">
+        <v>2.77</v>
+      </c>
+      <c r="AU316">
+        <v>3</v>
+      </c>
+      <c r="AV316">
+        <v>5</v>
+      </c>
+      <c r="AW316">
+        <v>11</v>
+      </c>
+      <c r="AX316">
+        <v>11</v>
+      </c>
+      <c r="AY316">
+        <v>15</v>
+      </c>
+      <c r="AZ316">
+        <v>18</v>
+      </c>
+      <c r="BA316">
+        <v>5</v>
+      </c>
+      <c r="BB316">
+        <v>7</v>
+      </c>
+      <c r="BC316">
+        <v>12</v>
+      </c>
+      <c r="BD316">
+        <v>1.84</v>
+      </c>
+      <c r="BE316">
+        <v>6.75</v>
+      </c>
+      <c r="BF316">
+        <v>2.15</v>
+      </c>
+      <c r="BG316">
+        <v>1.3</v>
+      </c>
+      <c r="BH316">
+        <v>3.05</v>
+      </c>
+      <c r="BI316">
+        <v>1.53</v>
+      </c>
+      <c r="BJ316">
+        <v>2.28</v>
+      </c>
+      <c r="BK316">
+        <v>1.88</v>
+      </c>
+      <c r="BL316">
+        <v>1.79</v>
+      </c>
+      <c r="BM316">
+        <v>2.38</v>
+      </c>
+      <c r="BN316">
+        <v>1.48</v>
+      </c>
+      <c r="BO316">
+        <v>3.05</v>
+      </c>
+      <c r="BP316">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="317" spans="1:68">
+      <c r="A317" s="1">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>7728505</v>
+      </c>
+      <c r="C317" t="s">
+        <v>68</v>
+      </c>
+      <c r="D317" t="s">
+        <v>69</v>
+      </c>
+      <c r="E317" s="2">
+        <v>45718.60416666666</v>
+      </c>
+      <c r="F317">
+        <v>29</v>
+      </c>
+      <c r="G317" t="s">
+        <v>85</v>
+      </c>
+      <c r="H317" t="s">
+        <v>72</v>
+      </c>
+      <c r="I317">
+        <v>0</v>
+      </c>
+      <c r="J317">
+        <v>0</v>
+      </c>
+      <c r="K317">
+        <v>0</v>
+      </c>
+      <c r="L317">
+        <v>3</v>
+      </c>
+      <c r="M317">
+        <v>0</v>
+      </c>
+      <c r="N317">
+        <v>3</v>
+      </c>
+      <c r="O317" t="s">
+        <v>286</v>
+      </c>
+      <c r="P317" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q317">
+        <v>3.3</v>
+      </c>
+      <c r="R317">
+        <v>2.01</v>
+      </c>
+      <c r="S317">
+        <v>3.6</v>
+      </c>
+      <c r="T317">
+        <v>1.51</v>
+      </c>
+      <c r="U317">
+        <v>2.4</v>
+      </c>
+      <c r="V317">
+        <v>3.2</v>
+      </c>
+      <c r="W317">
+        <v>1.31</v>
+      </c>
+      <c r="X317">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y317">
+        <v>1.04</v>
+      </c>
+      <c r="Z317">
+        <v>2.65</v>
+      </c>
+      <c r="AA317">
+        <v>3.04</v>
+      </c>
+      <c r="AB317">
+        <v>3.04</v>
+      </c>
+      <c r="AC317">
+        <v>1.09</v>
+      </c>
+      <c r="AD317">
+        <v>7</v>
+      </c>
+      <c r="AE317">
+        <v>1.41</v>
+      </c>
+      <c r="AF317">
+        <v>2.65</v>
+      </c>
+      <c r="AG317">
+        <v>2.2</v>
+      </c>
+      <c r="AH317">
+        <v>1.57</v>
+      </c>
+      <c r="AI317">
+        <v>1.91</v>
+      </c>
+      <c r="AJ317">
+        <v>1.81</v>
+      </c>
+      <c r="AK317">
+        <v>1.4</v>
+      </c>
+      <c r="AL317">
+        <v>1.35</v>
+      </c>
+      <c r="AM317">
+        <v>1.47</v>
+      </c>
+      <c r="AN317">
+        <v>1.5</v>
+      </c>
+      <c r="AO317">
+        <v>1.31</v>
+      </c>
+      <c r="AP317">
+        <v>1.6</v>
+      </c>
+      <c r="AQ317">
+        <v>1.21</v>
+      </c>
+      <c r="AR317">
+        <v>1.53</v>
+      </c>
+      <c r="AS317">
+        <v>1.3</v>
+      </c>
+      <c r="AT317">
+        <v>2.83</v>
+      </c>
+      <c r="AU317">
+        <v>6</v>
+      </c>
+      <c r="AV317">
+        <v>3</v>
+      </c>
+      <c r="AW317">
+        <v>9</v>
+      </c>
+      <c r="AX317">
+        <v>3</v>
+      </c>
+      <c r="AY317">
+        <v>18</v>
+      </c>
+      <c r="AZ317">
+        <v>8</v>
+      </c>
+      <c r="BA317">
+        <v>4</v>
+      </c>
+      <c r="BB317">
+        <v>2</v>
+      </c>
+      <c r="BC317">
+        <v>6</v>
+      </c>
+      <c r="BD317">
+        <v>1.84</v>
+      </c>
+      <c r="BE317">
+        <v>6.25</v>
+      </c>
+      <c r="BF317">
+        <v>2.18</v>
+      </c>
+      <c r="BG317">
+        <v>1.53</v>
+      </c>
+      <c r="BH317">
+        <v>2.28</v>
+      </c>
+      <c r="BI317">
+        <v>1.9</v>
+      </c>
+      <c r="BJ317">
+        <v>1.77</v>
+      </c>
+      <c r="BK317">
+        <v>2.43</v>
+      </c>
+      <c r="BL317">
+        <v>1.46</v>
+      </c>
+      <c r="BM317">
+        <v>3.25</v>
+      </c>
+      <c r="BN317">
+        <v>1.27</v>
+      </c>
+      <c r="BO317">
+        <v>4.35</v>
+      </c>
+      <c r="BP317">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="318" spans="1:68">
+      <c r="A318" s="1">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>7728513</v>
+      </c>
+      <c r="C318" t="s">
+        <v>68</v>
+      </c>
+      <c r="D318" t="s">
+        <v>69</v>
+      </c>
+      <c r="E318" s="2">
+        <v>45718.70833333334</v>
+      </c>
+      <c r="F318">
+        <v>29</v>
+      </c>
+      <c r="G318" t="s">
+        <v>77</v>
+      </c>
+      <c r="H318" t="s">
+        <v>79</v>
+      </c>
+      <c r="I318">
+        <v>2</v>
+      </c>
+      <c r="J318">
+        <v>0</v>
+      </c>
+      <c r="K318">
+        <v>2</v>
+      </c>
+      <c r="L318">
+        <v>2</v>
+      </c>
+      <c r="M318">
+        <v>0</v>
+      </c>
+      <c r="N318">
+        <v>2</v>
+      </c>
+      <c r="O318" t="s">
+        <v>287</v>
+      </c>
+      <c r="P318" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q318">
+        <v>3.2</v>
+      </c>
+      <c r="R318">
+        <v>2.12</v>
+      </c>
+      <c r="S318">
+        <v>3.4</v>
+      </c>
+      <c r="T318">
+        <v>1.43</v>
+      </c>
+      <c r="U318">
+        <v>2.65</v>
+      </c>
+      <c r="V318">
+        <v>2.85</v>
+      </c>
+      <c r="W318">
+        <v>1.38</v>
+      </c>
+      <c r="X318">
+        <v>6.9</v>
+      </c>
+      <c r="Y318">
+        <v>1.04</v>
+      </c>
+      <c r="Z318">
+        <v>2.6</v>
+      </c>
+      <c r="AA318">
+        <v>3.2</v>
+      </c>
+      <c r="AB318">
+        <v>2.96</v>
+      </c>
+      <c r="AC318">
+        <v>1.07</v>
+      </c>
+      <c r="AD318">
+        <v>8</v>
+      </c>
+      <c r="AE318">
+        <v>1.32</v>
+      </c>
+      <c r="AF318">
+        <v>3.1</v>
+      </c>
+      <c r="AG318">
+        <v>2</v>
+      </c>
+      <c r="AH318">
+        <v>1.82</v>
+      </c>
+      <c r="AI318">
+        <v>1.74</v>
+      </c>
+      <c r="AJ318">
+        <v>1.98</v>
+      </c>
+      <c r="AK318">
+        <v>1.42</v>
+      </c>
+      <c r="AL318">
+        <v>1.32</v>
+      </c>
+      <c r="AM318">
+        <v>1.48</v>
+      </c>
+      <c r="AN318">
+        <v>1.57</v>
+      </c>
+      <c r="AO318">
+        <v>1.15</v>
+      </c>
+      <c r="AP318">
+        <v>1.67</v>
+      </c>
+      <c r="AQ318">
+        <v>1.07</v>
+      </c>
+      <c r="AR318">
+        <v>1.61</v>
+      </c>
+      <c r="AS318">
+        <v>1.25</v>
+      </c>
+      <c r="AT318">
+        <v>2.86</v>
+      </c>
+      <c r="AU318">
+        <v>5</v>
+      </c>
+      <c r="AV318">
+        <v>2</v>
+      </c>
+      <c r="AW318">
+        <v>7</v>
+      </c>
+      <c r="AX318">
+        <v>9</v>
+      </c>
+      <c r="AY318">
+        <v>12</v>
+      </c>
+      <c r="AZ318">
+        <v>11</v>
+      </c>
+      <c r="BA318">
+        <v>5</v>
+      </c>
+      <c r="BB318">
+        <v>9</v>
+      </c>
+      <c r="BC318">
+        <v>14</v>
+      </c>
+      <c r="BD318">
+        <v>1.8</v>
+      </c>
+      <c r="BE318">
+        <v>6.4</v>
+      </c>
+      <c r="BF318">
+        <v>2.23</v>
+      </c>
+      <c r="BG318">
+        <v>1.38</v>
+      </c>
+      <c r="BH318">
+        <v>2.65</v>
+      </c>
+      <c r="BI318">
+        <v>1.67</v>
+      </c>
+      <c r="BJ318">
+        <v>2.02</v>
+      </c>
+      <c r="BK318">
+        <v>2.08</v>
+      </c>
+      <c r="BL318">
+        <v>1.63</v>
+      </c>
+      <c r="BM318">
+        <v>2.65</v>
+      </c>
+      <c r="BN318">
+        <v>1.4</v>
+      </c>
+      <c r="BO318">
+        <v>3.55</v>
+      </c>
+      <c r="BP318">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="399">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -880,6 +880,9 @@
     <t>['5', '23']</t>
   </si>
   <si>
+    <t>['25', '68']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1569,7 +1572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP318"/>
+  <dimension ref="A1:BP319"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1825,7 +1828,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2109,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ3">
         <v>1.13</v>
@@ -2237,7 +2240,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3061,7 +3064,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3267,7 +3270,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3966,7 +3969,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ12">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4091,7 +4094,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4297,7 +4300,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -5327,7 +5330,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5945,7 +5948,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6151,7 +6154,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6357,7 +6360,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6563,7 +6566,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6769,7 +6772,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6850,7 +6853,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ26">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR26">
         <v>1.33</v>
@@ -6975,7 +6978,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7387,7 +7390,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7877,7 +7880,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ31">
         <v>1.33</v>
@@ -8005,7 +8008,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8211,7 +8214,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8623,7 +8626,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -10477,7 +10480,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11095,7 +11098,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11382,7 +11385,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ48">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR48">
         <v>1.67</v>
@@ -11997,7 +12000,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ51">
         <v>0.93</v>
@@ -12743,7 +12746,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12949,7 +12952,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13155,7 +13158,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13361,7 +13364,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13773,7 +13776,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14391,7 +14394,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -15009,7 +15012,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15421,7 +15424,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15627,7 +15630,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15911,7 +15914,7 @@
         <v>2</v>
       </c>
       <c r="AP70">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ70">
         <v>1.47</v>
@@ -16245,7 +16248,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16451,7 +16454,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16657,7 +16660,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16944,7 +16947,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ75">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR75">
         <v>1.58</v>
@@ -17481,7 +17484,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17687,7 +17690,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18099,7 +18102,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18177,7 +18180,7 @@
         <v>1.67</v>
       </c>
       <c r="AP81">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ81">
         <v>1.36</v>
@@ -18305,7 +18308,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18511,7 +18514,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19335,7 +19338,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19747,7 +19750,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19953,7 +19956,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20365,7 +20368,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20777,7 +20780,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20983,7 +20986,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -22013,7 +22016,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22918,7 +22921,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ104">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR104">
         <v>1.71</v>
@@ -23327,7 +23330,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ106">
         <v>0.8</v>
@@ -23455,7 +23458,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24073,7 +24076,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24485,7 +24488,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24691,7 +24694,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25103,7 +25106,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25927,7 +25930,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26545,7 +26548,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26957,7 +26960,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27035,7 +27038,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ124">
         <v>0.47</v>
@@ -27369,7 +27372,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27781,7 +27784,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28193,7 +28196,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28399,7 +28402,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28605,7 +28608,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28892,7 +28895,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ133">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR133">
         <v>1.15</v>
@@ -29017,7 +29020,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29223,7 +29226,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29841,7 +29844,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30459,7 +30462,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30665,7 +30668,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30743,7 +30746,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ142">
         <v>1.21</v>
@@ -30871,7 +30874,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31077,7 +31080,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31489,7 +31492,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31901,7 +31904,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32931,7 +32934,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33549,7 +33552,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34042,7 +34045,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ158">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR158">
         <v>1.68</v>
@@ -35197,7 +35200,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35815,7 +35818,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36308,7 +36311,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ169">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR169">
         <v>1.71</v>
@@ -36717,7 +36720,7 @@
         <v>0.71</v>
       </c>
       <c r="AP171">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ171">
         <v>0.93</v>
@@ -36845,7 +36848,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37463,7 +37466,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37875,7 +37878,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38287,7 +38290,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38493,7 +38496,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39317,7 +39320,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40141,7 +40144,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40219,7 +40222,7 @@
         <v>1.38</v>
       </c>
       <c r="AP188">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ188">
         <v>1.53</v>
@@ -40759,7 +40762,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40965,7 +40968,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41171,7 +41174,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41377,7 +41380,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42076,7 +42079,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ197">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR197">
         <v>1.63</v>
@@ -42613,7 +42616,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43025,7 +43028,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43231,7 +43234,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43849,7 +43852,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44879,7 +44882,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45085,7 +45088,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45291,7 +45294,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45497,7 +45500,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45575,7 +45578,7 @@
         <v>1.11</v>
       </c>
       <c r="AP214">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ214">
         <v>1</v>
@@ -45909,7 +45912,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46608,7 +46611,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ219">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR219">
         <v>1.15</v>
@@ -47145,7 +47148,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47557,7 +47560,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47844,7 +47847,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ225">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR225">
         <v>1.43</v>
@@ -47969,7 +47972,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48587,7 +48590,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48793,7 +48796,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48999,7 +49002,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49823,7 +49826,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50647,7 +50650,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51265,7 +51268,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51677,7 +51680,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52089,7 +52092,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52913,7 +52916,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53119,7 +53122,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53200,7 +53203,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ251">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR251">
         <v>1.68</v>
@@ -53531,7 +53534,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53609,7 +53612,7 @@
         <v>1</v>
       </c>
       <c r="AP253">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ253">
         <v>1</v>
@@ -53943,7 +53946,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54149,7 +54152,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -55179,7 +55182,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55385,7 +55388,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -56003,7 +56006,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56287,7 +56290,7 @@
         <v>1.27</v>
       </c>
       <c r="AP266">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ266">
         <v>1.07</v>
@@ -56827,7 +56830,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57445,7 +57448,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -58475,7 +58478,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59380,7 +59383,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ281">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR281">
         <v>1.65</v>
@@ -59711,7 +59714,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59917,7 +59920,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60535,7 +60538,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -60613,7 +60616,7 @@
         <v>1.08</v>
       </c>
       <c r="AP287">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ287">
         <v>0.93</v>
@@ -61153,7 +61156,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61359,7 +61362,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -62882,7 +62885,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ298">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR298">
         <v>1.37</v>
@@ -63213,7 +63216,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63419,7 +63422,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63625,7 +63628,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -65067,7 +65070,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65273,7 +65276,7 @@
         <v>281</v>
       </c>
       <c r="P310" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q310">
         <v>2.31</v>
@@ -65891,7 +65894,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66303,7 +66306,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66509,7 +66512,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -67078,6 +67081,212 @@
       </c>
       <c r="BP318">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="319" spans="1:68">
+      <c r="A319" s="1">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>7728510</v>
+      </c>
+      <c r="C319" t="s">
+        <v>68</v>
+      </c>
+      <c r="D319" t="s">
+        <v>69</v>
+      </c>
+      <c r="E319" s="2">
+        <v>45719.6875</v>
+      </c>
+      <c r="F319">
+        <v>29</v>
+      </c>
+      <c r="G319" t="s">
+        <v>71</v>
+      </c>
+      <c r="H319" t="s">
+        <v>84</v>
+      </c>
+      <c r="I319">
+        <v>1</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+      <c r="K319">
+        <v>1</v>
+      </c>
+      <c r="L319">
+        <v>2</v>
+      </c>
+      <c r="M319">
+        <v>0</v>
+      </c>
+      <c r="N319">
+        <v>2</v>
+      </c>
+      <c r="O319" t="s">
+        <v>288</v>
+      </c>
+      <c r="P319" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q319">
+        <v>2.63</v>
+      </c>
+      <c r="R319">
+        <v>1.91</v>
+      </c>
+      <c r="S319">
+        <v>5.5</v>
+      </c>
+      <c r="T319">
+        <v>1.62</v>
+      </c>
+      <c r="U319">
+        <v>2.2</v>
+      </c>
+      <c r="V319">
+        <v>4</v>
+      </c>
+      <c r="W319">
+        <v>1.22</v>
+      </c>
+      <c r="X319">
+        <v>13</v>
+      </c>
+      <c r="Y319">
+        <v>1.04</v>
+      </c>
+      <c r="Z319">
+        <v>1.88</v>
+      </c>
+      <c r="AA319">
+        <v>3.27</v>
+      </c>
+      <c r="AB319">
+        <v>5.1</v>
+      </c>
+      <c r="AC319">
+        <v>1.12</v>
+      </c>
+      <c r="AD319">
+        <v>6</v>
+      </c>
+      <c r="AE319">
+        <v>1.53</v>
+      </c>
+      <c r="AF319">
+        <v>2.25</v>
+      </c>
+      <c r="AG319">
+        <v>2.26</v>
+      </c>
+      <c r="AH319">
+        <v>1.54</v>
+      </c>
+      <c r="AI319">
+        <v>2.38</v>
+      </c>
+      <c r="AJ319">
+        <v>1.53</v>
+      </c>
+      <c r="AK319">
+        <v>1.19</v>
+      </c>
+      <c r="AL319">
+        <v>1.32</v>
+      </c>
+      <c r="AM319">
+        <v>1.83</v>
+      </c>
+      <c r="AN319">
+        <v>2.36</v>
+      </c>
+      <c r="AO319">
+        <v>0.21</v>
+      </c>
+      <c r="AP319">
+        <v>2.4</v>
+      </c>
+      <c r="AQ319">
+        <v>0.2</v>
+      </c>
+      <c r="AR319">
+        <v>1.37</v>
+      </c>
+      <c r="AS319">
+        <v>1.09</v>
+      </c>
+      <c r="AT319">
+        <v>2.46</v>
+      </c>
+      <c r="AU319">
+        <v>5</v>
+      </c>
+      <c r="AV319">
+        <v>2</v>
+      </c>
+      <c r="AW319">
+        <v>6</v>
+      </c>
+      <c r="AX319">
+        <v>10</v>
+      </c>
+      <c r="AY319">
+        <v>11</v>
+      </c>
+      <c r="AZ319">
+        <v>13</v>
+      </c>
+      <c r="BA319">
+        <v>3</v>
+      </c>
+      <c r="BB319">
+        <v>0</v>
+      </c>
+      <c r="BC319">
+        <v>3</v>
+      </c>
+      <c r="BD319">
+        <v>1.41</v>
+      </c>
+      <c r="BE319">
+        <v>7</v>
+      </c>
+      <c r="BF319">
+        <v>3.3</v>
+      </c>
+      <c r="BG319">
+        <v>1.43</v>
+      </c>
+      <c r="BH319">
+        <v>2.55</v>
+      </c>
+      <c r="BI319">
+        <v>1.71</v>
+      </c>
+      <c r="BJ319">
+        <v>1.97</v>
+      </c>
+      <c r="BK319">
+        <v>2.14</v>
+      </c>
+      <c r="BL319">
+        <v>1.6</v>
+      </c>
+      <c r="BM319">
+        <v>2.75</v>
+      </c>
+      <c r="BN319">
+        <v>1.37</v>
+      </c>
+      <c r="BO319">
+        <v>3.65</v>
+      </c>
+      <c r="BP319">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="399">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1572,7 +1572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP319"/>
+  <dimension ref="A1:BP320"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ16">
         <v>1.36</v>
@@ -6235,7 +6235,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ23">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -9119,7 +9119,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ37">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR37">
         <v>1.35</v>
@@ -9734,7 +9734,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ40">
         <v>1.07</v>
@@ -13442,7 +13442,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ58">
         <v>0.93</v>
@@ -13857,7 +13857,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ60">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -17974,7 +17974,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ80">
         <v>1.07</v>
@@ -18801,7 +18801,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ84">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR84">
         <v>1.79</v>
@@ -23742,7 +23742,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ108">
         <v>1.47</v>
@@ -24363,7 +24363,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ111">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR111">
         <v>1.54</v>
@@ -28071,7 +28071,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ129">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -28892,7 +28892,7 @@
         <v>0.2</v>
       </c>
       <c r="AP133">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ133">
         <v>0.2</v>
@@ -30131,7 +30131,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ139">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>1.66</v>
@@ -31982,7 +31982,7 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ148">
         <v>1.93</v>
@@ -33427,7 +33427,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ155">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR155">
         <v>1.59</v>
@@ -35072,7 +35072,7 @@
         <v>1.43</v>
       </c>
       <c r="AP163">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ163">
         <v>1.53</v>
@@ -39401,7 +39401,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ184">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR184">
         <v>1.69</v>
@@ -41252,7 +41252,7 @@
         <v>0.89</v>
       </c>
       <c r="AP193">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ193">
         <v>1.5</v>
@@ -45372,7 +45372,7 @@
         <v>1.5</v>
       </c>
       <c r="AP213">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ213">
         <v>1.47</v>
@@ -45993,7 +45993,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ216">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR216">
         <v>1.46</v>
@@ -49289,7 +49289,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ232">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR232">
         <v>1.73</v>
@@ -49492,7 +49492,7 @@
         <v>0.55</v>
       </c>
       <c r="AP233">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ233">
         <v>0.47</v>
@@ -56499,7 +56499,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ267">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR267">
         <v>1.55</v>
@@ -58556,7 +58556,7 @@
         <v>1.25</v>
       </c>
       <c r="AP277">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ277">
         <v>1.36</v>
@@ -62267,7 +62267,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ295">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR295">
         <v>1.6</v>
@@ -63088,7 +63088,7 @@
         <v>1</v>
       </c>
       <c r="AP299">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ299">
         <v>1.13</v>
@@ -65563,7 +65563,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ311">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR311">
         <v>1.67</v>
@@ -67287,6 +67287,212 @@
       </c>
       <c r="BP319">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="320" spans="1:68">
+      <c r="A320" s="1">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>7728458</v>
+      </c>
+      <c r="C320" t="s">
+        <v>68</v>
+      </c>
+      <c r="D320" t="s">
+        <v>69</v>
+      </c>
+      <c r="E320" s="2">
+        <v>45721.66666666666</v>
+      </c>
+      <c r="F320">
+        <v>24</v>
+      </c>
+      <c r="G320" t="s">
+        <v>74</v>
+      </c>
+      <c r="H320" t="s">
+        <v>78</v>
+      </c>
+      <c r="I320">
+        <v>0</v>
+      </c>
+      <c r="J320">
+        <v>1</v>
+      </c>
+      <c r="K320">
+        <v>1</v>
+      </c>
+      <c r="L320">
+        <v>0</v>
+      </c>
+      <c r="M320">
+        <v>1</v>
+      </c>
+      <c r="N320">
+        <v>1</v>
+      </c>
+      <c r="O320" t="s">
+        <v>94</v>
+      </c>
+      <c r="P320" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q320">
+        <v>3.5</v>
+      </c>
+      <c r="R320">
+        <v>1.83</v>
+      </c>
+      <c r="S320">
+        <v>4</v>
+      </c>
+      <c r="T320">
+        <v>1.62</v>
+      </c>
+      <c r="U320">
+        <v>2.2</v>
+      </c>
+      <c r="V320">
+        <v>4</v>
+      </c>
+      <c r="W320">
+        <v>1.22</v>
+      </c>
+      <c r="X320">
+        <v>13</v>
+      </c>
+      <c r="Y320">
+        <v>1.04</v>
+      </c>
+      <c r="Z320">
+        <v>2.92</v>
+      </c>
+      <c r="AA320">
+        <v>2.93</v>
+      </c>
+      <c r="AB320">
+        <v>2.85</v>
+      </c>
+      <c r="AC320">
+        <v>1.12</v>
+      </c>
+      <c r="AD320">
+        <v>6</v>
+      </c>
+      <c r="AE320">
+        <v>1.5</v>
+      </c>
+      <c r="AF320">
+        <v>2.3</v>
+      </c>
+      <c r="AG320">
+        <v>3.09</v>
+      </c>
+      <c r="AH320">
+        <v>1.32</v>
+      </c>
+      <c r="AI320">
+        <v>2.2</v>
+      </c>
+      <c r="AJ320">
+        <v>1.62</v>
+      </c>
+      <c r="AK320">
+        <v>1.36</v>
+      </c>
+      <c r="AL320">
+        <v>1.35</v>
+      </c>
+      <c r="AM320">
+        <v>1.47</v>
+      </c>
+      <c r="AN320">
+        <v>0.64</v>
+      </c>
+      <c r="AO320">
+        <v>0.86</v>
+      </c>
+      <c r="AP320">
+        <v>0.6</v>
+      </c>
+      <c r="AQ320">
+        <v>1</v>
+      </c>
+      <c r="AR320">
+        <v>1.19</v>
+      </c>
+      <c r="AS320">
+        <v>1.23</v>
+      </c>
+      <c r="AT320">
+        <v>2.42</v>
+      </c>
+      <c r="AU320">
+        <v>4</v>
+      </c>
+      <c r="AV320">
+        <v>4</v>
+      </c>
+      <c r="AW320">
+        <v>5</v>
+      </c>
+      <c r="AX320">
+        <v>7</v>
+      </c>
+      <c r="AY320">
+        <v>11</v>
+      </c>
+      <c r="AZ320">
+        <v>12</v>
+      </c>
+      <c r="BA320">
+        <v>4</v>
+      </c>
+      <c r="BB320">
+        <v>6</v>
+      </c>
+      <c r="BC320">
+        <v>10</v>
+      </c>
+      <c r="BD320">
+        <v>1.76</v>
+      </c>
+      <c r="BE320">
+        <v>6.5</v>
+      </c>
+      <c r="BF320">
+        <v>2.3</v>
+      </c>
+      <c r="BG320">
+        <v>1.4</v>
+      </c>
+      <c r="BH320">
+        <v>2.82</v>
+      </c>
+      <c r="BI320">
+        <v>1.68</v>
+      </c>
+      <c r="BJ320">
+        <v>2.12</v>
+      </c>
+      <c r="BK320">
+        <v>2.11</v>
+      </c>
+      <c r="BL320">
+        <v>1.68</v>
+      </c>
+      <c r="BM320">
+        <v>2.75</v>
+      </c>
+      <c r="BN320">
+        <v>1.42</v>
+      </c>
+      <c r="BO320">
+        <v>3.8</v>
+      </c>
+      <c r="BP320">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="404">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -883,6 +883,24 @@
     <t>['25', '68']</t>
   </si>
   <si>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['61']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['30', '37', '74']</t>
+  </si>
+  <si>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['12', '45+5']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -896,9 +914,6 @@
   </si>
   <si>
     <t>['27', '56']</t>
-  </si>
-  <si>
-    <t>['54']</t>
   </si>
   <si>
     <t>['64']</t>
@@ -1168,9 +1183,6 @@
     <t>['42', '62', '90']</t>
   </si>
   <si>
-    <t>['6']</t>
-  </si>
-  <si>
     <t>['34']</t>
   </si>
   <si>
@@ -1211,6 +1223,9 @@
   </si>
   <si>
     <t>['90+1', '90+4']</t>
+  </si>
+  <si>
+    <t>['32', '34', '72', '79']</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP320"/>
+  <dimension ref="A1:BP326"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1828,7 +1843,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2112,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ3">
         <v>1.13</v>
@@ -2240,7 +2255,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2524,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ5">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2936,10 +2951,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3064,7 +3079,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3142,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ8">
         <v>1.53</v>
@@ -3270,7 +3285,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3351,7 +3366,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3760,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ11">
         <v>1.47</v>
@@ -4094,7 +4109,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4300,7 +4315,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4584,10 +4599,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ15">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR15">
         <v>1.13</v>
@@ -5330,7 +5345,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5411,7 +5426,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ19">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5823,7 +5838,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5948,7 +5963,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6154,7 +6169,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6360,7 +6375,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6566,7 +6581,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6647,7 +6662,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ25">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6772,7 +6787,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6978,7 +6993,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7390,7 +7405,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7471,7 +7486,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR29">
         <v>1.44</v>
@@ -7674,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ30">
         <v>0.93</v>
@@ -7880,7 +7895,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ31">
         <v>1.33</v>
@@ -8008,7 +8023,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8214,7 +8229,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8292,7 +8307,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ33">
         <v>1.53</v>
@@ -8498,7 +8513,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ34">
         <v>1.13</v>
@@ -8626,7 +8641,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8707,7 +8722,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ35">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR35">
         <v>1.42</v>
@@ -9322,10 +9337,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ38">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR38">
         <v>1.41</v>
@@ -10149,7 +10164,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ42">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR42">
         <v>1.8</v>
@@ -10352,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ43">
         <v>1.07</v>
@@ -10480,7 +10495,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11098,7 +11113,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11179,7 +11194,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ47">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR47">
         <v>1.72</v>
@@ -11382,7 +11397,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ48">
         <v>0.2</v>
@@ -12000,7 +12015,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ51">
         <v>0.93</v>
@@ -12746,7 +12761,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12824,7 +12839,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ55">
         <v>1.36</v>
@@ -12952,7 +12967,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13033,7 +13048,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ56">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR56">
         <v>1.94</v>
@@ -13158,7 +13173,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13364,7 +13379,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13651,7 +13666,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR59">
         <v>1.51</v>
@@ -13776,7 +13791,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13854,7 +13869,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -14060,7 +14075,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ61">
         <v>1.53</v>
@@ -14394,7 +14409,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14681,7 +14696,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ64">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR64">
         <v>1.39</v>
@@ -14884,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ65">
         <v>1.07</v>
@@ -15012,7 +15027,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15424,7 +15439,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15630,7 +15645,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15711,7 +15726,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ69">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR69">
         <v>1.25</v>
@@ -15914,7 +15929,7 @@
         <v>2</v>
       </c>
       <c r="AP70">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ70">
         <v>1.47</v>
@@ -16120,7 +16135,7 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ71">
         <v>1.33</v>
@@ -16248,7 +16263,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16454,7 +16469,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16535,7 +16550,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ73">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR73">
         <v>2.06</v>
@@ -16660,7 +16675,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17484,7 +17499,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17690,7 +17705,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18102,7 +18117,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18180,7 +18195,7 @@
         <v>1.67</v>
       </c>
       <c r="AP81">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ81">
         <v>1.36</v>
@@ -18308,7 +18323,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18386,7 +18401,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ82">
         <v>1</v>
@@ -18514,7 +18529,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18592,10 +18607,10 @@
         <v>3</v>
       </c>
       <c r="AP83">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ83">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR83">
         <v>1.8</v>
@@ -19210,7 +19225,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ86">
         <v>1</v>
@@ -19338,7 +19353,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19419,7 +19434,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ87">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR87">
         <v>1.47</v>
@@ -19625,7 +19640,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ88">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR88">
         <v>1.96</v>
@@ -19750,7 +19765,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19956,7 +19971,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20368,7 +20383,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20652,10 +20667,10 @@
         <v>1.33</v>
       </c>
       <c r="AP93">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ93">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR93">
         <v>1.5</v>
@@ -20780,7 +20795,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20986,7 +21001,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21067,7 +21082,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ95">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR95">
         <v>1.44</v>
@@ -21888,7 +21903,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ99">
         <v>1.47</v>
@@ -22016,7 +22031,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22094,10 +22109,10 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ100">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -22509,7 +22524,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ102">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR102">
         <v>1.13</v>
@@ -22712,10 +22727,10 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ103">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR103">
         <v>1.55</v>
@@ -23330,7 +23345,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ106">
         <v>0.8</v>
@@ -23458,7 +23473,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23539,7 +23554,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ107">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR107">
         <v>1.53</v>
@@ -23948,7 +23963,7 @@
         <v>1.25</v>
       </c>
       <c r="AP109">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -24076,7 +24091,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24154,10 +24169,10 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ110">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR110">
         <v>1.96</v>
@@ -24488,7 +24503,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24694,7 +24709,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24978,7 +24993,7 @@
         <v>1.75</v>
       </c>
       <c r="AP114">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ114">
         <v>1.21</v>
@@ -25106,7 +25121,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25930,7 +25945,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26214,7 +26229,7 @@
         <v>1.4</v>
       </c>
       <c r="AP120">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ120">
         <v>1.47</v>
@@ -26548,7 +26563,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26835,7 +26850,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ123">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR123">
         <v>1.53</v>
@@ -26960,7 +26975,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27038,7 +27053,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ124">
         <v>0.47</v>
@@ -27247,7 +27262,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ125">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR125">
         <v>1.56</v>
@@ -27372,7 +27387,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27450,10 +27465,10 @@
         <v>1.8</v>
       </c>
       <c r="AP126">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ126">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR126">
         <v>1.8</v>
@@ -27784,7 +27799,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27862,10 +27877,10 @@
         <v>3</v>
       </c>
       <c r="AP128">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ128">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR128">
         <v>1.61</v>
@@ -28068,7 +28083,7 @@
         <v>1.4</v>
       </c>
       <c r="AP129">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ129">
         <v>1</v>
@@ -28196,7 +28211,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28402,7 +28417,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28483,7 +28498,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ131">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR131">
         <v>1.16</v>
@@ -28608,7 +28623,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29020,7 +29035,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29098,7 +29113,7 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ134">
         <v>1.07</v>
@@ -29226,7 +29241,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29510,7 +29525,7 @@
         <v>1.4</v>
       </c>
       <c r="AP136">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ136">
         <v>1.21</v>
@@ -29716,7 +29731,7 @@
         <v>2.2</v>
       </c>
       <c r="AP137">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ137">
         <v>1.36</v>
@@ -29844,7 +29859,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30462,7 +30477,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30540,10 +30555,10 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ141">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR141">
         <v>1.42</v>
@@ -30668,7 +30683,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30746,7 +30761,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ142">
         <v>1.21</v>
@@ -30874,7 +30889,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31080,7 +31095,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31161,7 +31176,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ144">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR144">
         <v>1.75</v>
@@ -31492,7 +31507,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31573,7 +31588,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ146">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR146">
         <v>1.62</v>
@@ -31904,7 +31919,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -31985,7 +32000,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ148">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR148">
         <v>1.13</v>
@@ -32191,7 +32206,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ149">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR149">
         <v>1.82</v>
@@ -32394,7 +32409,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ150">
         <v>0.8</v>
@@ -32600,7 +32615,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ151">
         <v>0.93</v>
@@ -32934,7 +32949,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33552,7 +33567,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33630,7 +33645,7 @@
         <v>1.83</v>
       </c>
       <c r="AP156">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ156">
         <v>1.36</v>
@@ -34660,7 +34675,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ161">
         <v>1</v>
@@ -35200,7 +35215,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35281,7 +35296,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ164">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR164">
         <v>1.2</v>
@@ -35818,7 +35833,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36105,7 +36120,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ168">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR168">
         <v>1.29</v>
@@ -36514,7 +36529,7 @@
         <v>1.29</v>
       </c>
       <c r="AP170">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36720,10 +36735,10 @@
         <v>0.71</v>
       </c>
       <c r="AP171">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ171">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR171">
         <v>1.18</v>
@@ -36848,7 +36863,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -36929,7 +36944,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ172">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR172">
         <v>1.15</v>
@@ -37132,10 +37147,10 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ173">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR173">
         <v>1.44</v>
@@ -37466,7 +37481,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37878,7 +37893,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38162,7 +38177,7 @@
         <v>1</v>
       </c>
       <c r="AP178">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ178">
         <v>0.93</v>
@@ -38290,7 +38305,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38496,7 +38511,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39320,7 +39335,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39810,7 +39825,7 @@
         <v>0.13</v>
       </c>
       <c r="AP186">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ186">
         <v>1.13</v>
@@ -40016,7 +40031,7 @@
         <v>0.75</v>
       </c>
       <c r="AP187">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ187">
         <v>0.47</v>
@@ -40144,7 +40159,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40222,7 +40237,7 @@
         <v>1.38</v>
       </c>
       <c r="AP188">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ188">
         <v>1.53</v>
@@ -40428,7 +40443,7 @@
         <v>1.13</v>
       </c>
       <c r="AP189">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ189">
         <v>1.21</v>
@@ -40637,7 +40652,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ190">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR190">
         <v>1.74</v>
@@ -40762,7 +40777,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40840,7 +40855,7 @@
         <v>1.67</v>
       </c>
       <c r="AP191">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ191">
         <v>1.33</v>
@@ -40968,7 +40983,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41174,7 +41189,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41255,7 +41270,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ193">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR193">
         <v>1.13</v>
@@ -41380,7 +41395,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41461,7 +41476,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ194">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR194">
         <v>1.4</v>
@@ -41667,7 +41682,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ195">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR195">
         <v>1.66</v>
@@ -41873,7 +41888,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ196">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR196">
         <v>1.42</v>
@@ -42616,7 +42631,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43028,7 +43043,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43234,7 +43249,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43312,7 +43327,7 @@
         <v>1.6</v>
       </c>
       <c r="AP203">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ203">
         <v>1.33</v>
@@ -43852,7 +43867,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43930,7 +43945,7 @@
         <v>0.88</v>
       </c>
       <c r="AP206">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ206">
         <v>0.93</v>
@@ -44882,7 +44897,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45088,7 +45103,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45166,10 +45181,10 @@
         <v>1.1</v>
       </c>
       <c r="AP212">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ212">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR212">
         <v>1.69</v>
@@ -45294,7 +45309,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45375,7 +45390,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ213">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR213">
         <v>1.08</v>
@@ -45500,7 +45515,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45578,7 +45593,7 @@
         <v>1.11</v>
       </c>
       <c r="AP214">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ214">
         <v>1</v>
@@ -45787,7 +45802,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ215">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR215">
         <v>1.3</v>
@@ -45912,7 +45927,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46196,10 +46211,10 @@
         <v>2.44</v>
       </c>
       <c r="AP217">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ217">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR217">
         <v>1.61</v>
@@ -46402,10 +46417,10 @@
         <v>1.67</v>
       </c>
       <c r="AP218">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ218">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR218">
         <v>1.41</v>
@@ -47020,7 +47035,7 @@
         <v>1.56</v>
       </c>
       <c r="AP221">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ221">
         <v>1.36</v>
@@ -47148,7 +47163,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47432,7 +47447,7 @@
         <v>1.11</v>
       </c>
       <c r="AP223">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ223">
         <v>0.93</v>
@@ -47560,7 +47575,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47638,7 +47653,7 @@
         <v>0.8</v>
       </c>
       <c r="AP224">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ224">
         <v>1</v>
@@ -47972,7 +47987,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48465,7 +48480,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ228">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR228">
         <v>1.5</v>
@@ -48590,7 +48605,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48668,7 +48683,7 @@
         <v>1.22</v>
       </c>
       <c r="AP229">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ229">
         <v>1.07</v>
@@ -48796,7 +48811,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49002,7 +49017,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49826,7 +49841,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -49907,7 +49922,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ235">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR235">
         <v>1.56</v>
@@ -50113,7 +50128,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ236">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR236">
         <v>1.23</v>
@@ -50650,7 +50665,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50731,7 +50746,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ239">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR239">
         <v>1.67</v>
@@ -51140,7 +51155,7 @@
         <v>1.45</v>
       </c>
       <c r="AP241">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ241">
         <v>1.33</v>
@@ -51268,7 +51283,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51555,7 +51570,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ243">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR243">
         <v>1.18</v>
@@ -51680,7 +51695,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51964,7 +51979,7 @@
         <v>1.09</v>
       </c>
       <c r="AP245">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ245">
         <v>0.93</v>
@@ -52092,7 +52107,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52170,7 +52185,7 @@
         <v>1.3</v>
       </c>
       <c r="AP246">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ246">
         <v>1.07</v>
@@ -52916,7 +52931,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53122,7 +53137,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53200,7 +53215,7 @@
         <v>0.18</v>
       </c>
       <c r="AP251">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ251">
         <v>0.2</v>
@@ -53534,7 +53549,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53612,7 +53627,7 @@
         <v>1</v>
       </c>
       <c r="AP253">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ253">
         <v>1</v>
@@ -53818,7 +53833,7 @@
         <v>0.73</v>
       </c>
       <c r="AP254">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ254">
         <v>0.8</v>
@@ -53946,7 +53961,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54027,7 +54042,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ255">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR255">
         <v>1.61</v>
@@ -54152,7 +54167,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54230,7 +54245,7 @@
         <v>1.33</v>
       </c>
       <c r="AP256">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ256">
         <v>1.53</v>
@@ -54645,7 +54660,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ258">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR258">
         <v>1.2</v>
@@ -55057,7 +55072,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ260">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR260">
         <v>1.59</v>
@@ -55182,7 +55197,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55263,7 +55278,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ261">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR261">
         <v>1.52</v>
@@ -55388,7 +55403,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -56006,7 +56021,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56290,7 +56305,7 @@
         <v>1.27</v>
       </c>
       <c r="AP266">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ266">
         <v>1.07</v>
@@ -56496,7 +56511,7 @@
         <v>0.82</v>
       </c>
       <c r="AP267">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ267">
         <v>1</v>
@@ -56705,7 +56720,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ268">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR268">
         <v>1.8</v>
@@ -56830,7 +56845,7 @@
         <v>262</v>
       </c>
       <c r="P269" t="s">
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="Q269">
         <v>2.25</v>
@@ -57320,7 +57335,7 @@
         <v>1.33</v>
       </c>
       <c r="AP271">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ271">
         <v>1.47</v>
@@ -57448,7 +57463,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -57732,7 +57747,7 @@
         <v>1.18</v>
       </c>
       <c r="AP273">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ273">
         <v>1.21</v>
@@ -58478,7 +58493,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58559,7 +58574,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ277">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR277">
         <v>1.22</v>
@@ -59174,7 +59189,7 @@
         <v>0.67</v>
       </c>
       <c r="AP280">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ280">
         <v>0.8</v>
@@ -59380,7 +59395,7 @@
         <v>0.25</v>
       </c>
       <c r="AP281">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ281">
         <v>0.2</v>
@@ -59589,7 +59604,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ282">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR282">
         <v>1.44</v>
@@ -59714,7 +59729,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59920,7 +59935,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60204,10 +60219,10 @@
         <v>1.62</v>
       </c>
       <c r="AP285">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ285">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR285">
         <v>1.52</v>
@@ -60413,7 +60428,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ286">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR286">
         <v>1.59</v>
@@ -60538,7 +60553,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -60616,7 +60631,7 @@
         <v>1.08</v>
       </c>
       <c r="AP287">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ287">
         <v>0.93</v>
@@ -61156,7 +61171,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61362,7 +61377,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -62264,7 +62279,7 @@
         <v>0.75</v>
       </c>
       <c r="AP295">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ295">
         <v>1</v>
@@ -63216,7 +63231,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63297,7 +63312,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ300">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR300">
         <v>1.42</v>
@@ -63422,7 +63437,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63500,10 +63515,10 @@
         <v>2</v>
       </c>
       <c r="AP301">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ301">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AR301">
         <v>1.54</v>
@@ -63628,7 +63643,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -63912,10 +63927,10 @@
         <v>1.5</v>
       </c>
       <c r="AP303">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ303">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR303">
         <v>1.51</v>
@@ -64118,7 +64133,7 @@
         <v>1.5</v>
       </c>
       <c r="AP304">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ304">
         <v>1.47</v>
@@ -64324,7 +64339,7 @@
         <v>0.5</v>
       </c>
       <c r="AP305">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ305">
         <v>0.47</v>
@@ -64739,7 +64754,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ307">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR307">
         <v>1.53</v>
@@ -64945,7 +64960,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ308">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR308">
         <v>1.45</v>
@@ -65070,7 +65085,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65276,7 +65291,7 @@
         <v>281</v>
       </c>
       <c r="P310" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Q310">
         <v>2.31</v>
@@ -65766,7 +65781,7 @@
         <v>1</v>
       </c>
       <c r="AP312">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ312">
         <v>1</v>
@@ -65894,7 +65909,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66306,7 +66321,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66512,7 +66527,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -67208,7 +67223,7 @@
         <v>0.21</v>
       </c>
       <c r="AP319">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ319">
         <v>0.2</v>
@@ -67493,6 +67508,1242 @@
       </c>
       <c r="BP320">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="321" spans="1:68">
+      <c r="A321" s="1">
+        <v>320</v>
+      </c>
+      <c r="B321">
+        <v>7728518</v>
+      </c>
+      <c r="C321" t="s">
+        <v>68</v>
+      </c>
+      <c r="D321" t="s">
+        <v>69</v>
+      </c>
+      <c r="E321" s="2">
+        <v>45723.625</v>
+      </c>
+      <c r="F321">
+        <v>30</v>
+      </c>
+      <c r="G321" t="s">
+        <v>73</v>
+      </c>
+      <c r="H321" t="s">
+        <v>90</v>
+      </c>
+      <c r="I321">
+        <v>1</v>
+      </c>
+      <c r="J321">
+        <v>0</v>
+      </c>
+      <c r="K321">
+        <v>1</v>
+      </c>
+      <c r="L321">
+        <v>1</v>
+      </c>
+      <c r="M321">
+        <v>0</v>
+      </c>
+      <c r="N321">
+        <v>1</v>
+      </c>
+      <c r="O321" t="s">
+        <v>289</v>
+      </c>
+      <c r="P321" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q321">
+        <v>3.1</v>
+      </c>
+      <c r="R321">
+        <v>2.05</v>
+      </c>
+      <c r="S321">
+        <v>3.25</v>
+      </c>
+      <c r="T321">
+        <v>1.4</v>
+      </c>
+      <c r="U321">
+        <v>2.75</v>
+      </c>
+      <c r="V321">
+        <v>2.75</v>
+      </c>
+      <c r="W321">
+        <v>1.4</v>
+      </c>
+      <c r="X321">
+        <v>7.2</v>
+      </c>
+      <c r="Y321">
+        <v>1.03</v>
+      </c>
+      <c r="Z321">
+        <v>2.77</v>
+      </c>
+      <c r="AA321">
+        <v>3.29</v>
+      </c>
+      <c r="AB321">
+        <v>2.71</v>
+      </c>
+      <c r="AC321">
+        <v>1.07</v>
+      </c>
+      <c r="AD321">
+        <v>8</v>
+      </c>
+      <c r="AE321">
+        <v>1.35</v>
+      </c>
+      <c r="AF321">
+        <v>3.1</v>
+      </c>
+      <c r="AG321">
+        <v>2</v>
+      </c>
+      <c r="AH321">
+        <v>1.82</v>
+      </c>
+      <c r="AI321">
+        <v>1.73</v>
+      </c>
+      <c r="AJ321">
+        <v>1.95</v>
+      </c>
+      <c r="AK321">
+        <v>1.42</v>
+      </c>
+      <c r="AL321">
+        <v>1.3</v>
+      </c>
+      <c r="AM321">
+        <v>1.48</v>
+      </c>
+      <c r="AN321">
+        <v>1.79</v>
+      </c>
+      <c r="AO321">
+        <v>1.47</v>
+      </c>
+      <c r="AP321">
+        <v>1.87</v>
+      </c>
+      <c r="AQ321">
+        <v>1.38</v>
+      </c>
+      <c r="AR321">
+        <v>1.54</v>
+      </c>
+      <c r="AS321">
+        <v>1.6</v>
+      </c>
+      <c r="AT321">
+        <v>3.14</v>
+      </c>
+      <c r="AU321">
+        <v>6</v>
+      </c>
+      <c r="AV321">
+        <v>4</v>
+      </c>
+      <c r="AW321">
+        <v>7</v>
+      </c>
+      <c r="AX321">
+        <v>10</v>
+      </c>
+      <c r="AY321">
+        <v>15</v>
+      </c>
+      <c r="AZ321">
+        <v>17</v>
+      </c>
+      <c r="BA321">
+        <v>5</v>
+      </c>
+      <c r="BB321">
+        <v>6</v>
+      </c>
+      <c r="BC321">
+        <v>11</v>
+      </c>
+      <c r="BD321">
+        <v>1.76</v>
+      </c>
+      <c r="BE321">
+        <v>6.4</v>
+      </c>
+      <c r="BF321">
+        <v>2.3</v>
+      </c>
+      <c r="BG321">
+        <v>1.36</v>
+      </c>
+      <c r="BH321">
+        <v>2.8</v>
+      </c>
+      <c r="BI321">
+        <v>1.62</v>
+      </c>
+      <c r="BJ321">
+        <v>2.1</v>
+      </c>
+      <c r="BK321">
+        <v>2</v>
+      </c>
+      <c r="BL321">
+        <v>1.68</v>
+      </c>
+      <c r="BM321">
+        <v>2.55</v>
+      </c>
+      <c r="BN321">
+        <v>1.43</v>
+      </c>
+      <c r="BO321">
+        <v>3.4</v>
+      </c>
+      <c r="BP321">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="322" spans="1:68">
+      <c r="A322" s="1">
+        <v>321</v>
+      </c>
+      <c r="B322">
+        <v>7728522</v>
+      </c>
+      <c r="C322" t="s">
+        <v>68</v>
+      </c>
+      <c r="D322" t="s">
+        <v>69</v>
+      </c>
+      <c r="E322" s="2">
+        <v>45723.70833333334</v>
+      </c>
+      <c r="F322">
+        <v>30</v>
+      </c>
+      <c r="G322" t="s">
+        <v>75</v>
+      </c>
+      <c r="H322" t="s">
+        <v>88</v>
+      </c>
+      <c r="I322">
+        <v>0</v>
+      </c>
+      <c r="J322">
+        <v>0</v>
+      </c>
+      <c r="K322">
+        <v>0</v>
+      </c>
+      <c r="L322">
+        <v>1</v>
+      </c>
+      <c r="M322">
+        <v>1</v>
+      </c>
+      <c r="N322">
+        <v>2</v>
+      </c>
+      <c r="O322" t="s">
+        <v>290</v>
+      </c>
+      <c r="P322" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q322">
+        <v>2.6</v>
+      </c>
+      <c r="R322">
+        <v>2.05</v>
+      </c>
+      <c r="S322">
+        <v>4</v>
+      </c>
+      <c r="T322">
+        <v>1.41</v>
+      </c>
+      <c r="U322">
+        <v>2.65</v>
+      </c>
+      <c r="V322">
+        <v>2.85</v>
+      </c>
+      <c r="W322">
+        <v>1.37</v>
+      </c>
+      <c r="X322">
+        <v>7.5</v>
+      </c>
+      <c r="Y322">
+        <v>1.07</v>
+      </c>
+      <c r="Z322">
+        <v>2.04</v>
+      </c>
+      <c r="AA322">
+        <v>3.52</v>
+      </c>
+      <c r="AB322">
+        <v>3.84</v>
+      </c>
+      <c r="AC322">
+        <v>1.07</v>
+      </c>
+      <c r="AD322">
+        <v>8</v>
+      </c>
+      <c r="AE322">
+        <v>1.35</v>
+      </c>
+      <c r="AF322">
+        <v>3.1</v>
+      </c>
+      <c r="AG322">
+        <v>1.92</v>
+      </c>
+      <c r="AH322">
+        <v>1.78</v>
+      </c>
+      <c r="AI322">
+        <v>1.82</v>
+      </c>
+      <c r="AJ322">
+        <v>1.87</v>
+      </c>
+      <c r="AK322">
+        <v>1.28</v>
+      </c>
+      <c r="AL322">
+        <v>1.3</v>
+      </c>
+      <c r="AM322">
+        <v>1.75</v>
+      </c>
+      <c r="AN322">
+        <v>1.21</v>
+      </c>
+      <c r="AO322">
+        <v>1.13</v>
+      </c>
+      <c r="AP322">
+        <v>1.2</v>
+      </c>
+      <c r="AQ322">
+        <v>1.13</v>
+      </c>
+      <c r="AR322">
+        <v>1.55</v>
+      </c>
+      <c r="AS322">
+        <v>1.47</v>
+      </c>
+      <c r="AT322">
+        <v>3.02</v>
+      </c>
+      <c r="AU322">
+        <v>4</v>
+      </c>
+      <c r="AV322">
+        <v>5</v>
+      </c>
+      <c r="AW322">
+        <v>10</v>
+      </c>
+      <c r="AX322">
+        <v>9</v>
+      </c>
+      <c r="AY322">
+        <v>15</v>
+      </c>
+      <c r="AZ322">
+        <v>14</v>
+      </c>
+      <c r="BA322">
+        <v>4</v>
+      </c>
+      <c r="BB322">
+        <v>3</v>
+      </c>
+      <c r="BC322">
+        <v>7</v>
+      </c>
+      <c r="BD322">
+        <v>1.67</v>
+      </c>
+      <c r="BE322">
+        <v>6.75</v>
+      </c>
+      <c r="BF322">
+        <v>2.43</v>
+      </c>
+      <c r="BG322">
+        <v>1.27</v>
+      </c>
+      <c r="BH322">
+        <v>3.3</v>
+      </c>
+      <c r="BI322">
+        <v>1.46</v>
+      </c>
+      <c r="BJ322">
+        <v>2.45</v>
+      </c>
+      <c r="BK322">
+        <v>1.76</v>
+      </c>
+      <c r="BL322">
+        <v>1.9</v>
+      </c>
+      <c r="BM322">
+        <v>2.2</v>
+      </c>
+      <c r="BN322">
+        <v>1.57</v>
+      </c>
+      <c r="BO322">
+        <v>2.8</v>
+      </c>
+      <c r="BP322">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="323" spans="1:68">
+      <c r="A323" s="1">
+        <v>322</v>
+      </c>
+      <c r="B323">
+        <v>7728516</v>
+      </c>
+      <c r="C323" t="s">
+        <v>68</v>
+      </c>
+      <c r="D323" t="s">
+        <v>69</v>
+      </c>
+      <c r="E323" s="2">
+        <v>45724.51041666666</v>
+      </c>
+      <c r="F323">
+        <v>30</v>
+      </c>
+      <c r="G323" t="s">
+        <v>71</v>
+      </c>
+      <c r="H323" t="s">
+        <v>89</v>
+      </c>
+      <c r="I323">
+        <v>0</v>
+      </c>
+      <c r="J323">
+        <v>0</v>
+      </c>
+      <c r="K323">
+        <v>0</v>
+      </c>
+      <c r="L323">
+        <v>1</v>
+      </c>
+      <c r="M323">
+        <v>0</v>
+      </c>
+      <c r="N323">
+        <v>1</v>
+      </c>
+      <c r="O323" t="s">
+        <v>291</v>
+      </c>
+      <c r="P323" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q323">
+        <v>3.5</v>
+      </c>
+      <c r="R323">
+        <v>1.83</v>
+      </c>
+      <c r="S323">
+        <v>4</v>
+      </c>
+      <c r="T323">
+        <v>1.62</v>
+      </c>
+      <c r="U323">
+        <v>2.2</v>
+      </c>
+      <c r="V323">
+        <v>4</v>
+      </c>
+      <c r="W323">
+        <v>1.22</v>
+      </c>
+      <c r="X323">
+        <v>13</v>
+      </c>
+      <c r="Y323">
+        <v>1.04</v>
+      </c>
+      <c r="Z323">
+        <v>2.47</v>
+      </c>
+      <c r="AA323">
+        <v>3.4</v>
+      </c>
+      <c r="AB323">
+        <v>2.97</v>
+      </c>
+      <c r="AC323">
+        <v>1.11</v>
+      </c>
+      <c r="AD323">
+        <v>6.25</v>
+      </c>
+      <c r="AE323">
+        <v>1.57</v>
+      </c>
+      <c r="AF323">
+        <v>2.25</v>
+      </c>
+      <c r="AG323">
+        <v>2.57</v>
+      </c>
+      <c r="AH323">
+        <v>1.47</v>
+      </c>
+      <c r="AI323">
+        <v>2.25</v>
+      </c>
+      <c r="AJ323">
+        <v>1.57</v>
+      </c>
+      <c r="AK323">
+        <v>1.39</v>
+      </c>
+      <c r="AL323">
+        <v>1.33</v>
+      </c>
+      <c r="AM323">
+        <v>1.52</v>
+      </c>
+      <c r="AN323">
+        <v>2.4</v>
+      </c>
+      <c r="AO323">
+        <v>1.5</v>
+      </c>
+      <c r="AP323">
+        <v>2.44</v>
+      </c>
+      <c r="AQ323">
+        <v>1.4</v>
+      </c>
+      <c r="AR323">
+        <v>1.37</v>
+      </c>
+      <c r="AS323">
+        <v>1.32</v>
+      </c>
+      <c r="AT323">
+        <v>2.69</v>
+      </c>
+      <c r="AU323">
+        <v>6</v>
+      </c>
+      <c r="AV323">
+        <v>3</v>
+      </c>
+      <c r="AW323">
+        <v>9</v>
+      </c>
+      <c r="AX323">
+        <v>7</v>
+      </c>
+      <c r="AY323">
+        <v>16</v>
+      </c>
+      <c r="AZ323">
+        <v>11</v>
+      </c>
+      <c r="BA323">
+        <v>3</v>
+      </c>
+      <c r="BB323">
+        <v>3</v>
+      </c>
+      <c r="BC323">
+        <v>6</v>
+      </c>
+      <c r="BD323">
+        <v>1.8</v>
+      </c>
+      <c r="BE323">
+        <v>6.4</v>
+      </c>
+      <c r="BF323">
+        <v>2.23</v>
+      </c>
+      <c r="BG323">
+        <v>1.45</v>
+      </c>
+      <c r="BH323">
+        <v>2.48</v>
+      </c>
+      <c r="BI323">
+        <v>1.78</v>
+      </c>
+      <c r="BJ323">
+        <v>1.88</v>
+      </c>
+      <c r="BK323">
+        <v>2.25</v>
+      </c>
+      <c r="BL323">
+        <v>1.54</v>
+      </c>
+      <c r="BM323">
+        <v>2.9</v>
+      </c>
+      <c r="BN323">
+        <v>1.34</v>
+      </c>
+      <c r="BO323">
+        <v>3.9</v>
+      </c>
+      <c r="BP323">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="324" spans="1:68">
+      <c r="A324" s="1">
+        <v>323</v>
+      </c>
+      <c r="B324">
+        <v>7728521</v>
+      </c>
+      <c r="C324" t="s">
+        <v>68</v>
+      </c>
+      <c r="D324" t="s">
+        <v>69</v>
+      </c>
+      <c r="E324" s="2">
+        <v>45724.60416666666</v>
+      </c>
+      <c r="F324">
+        <v>30</v>
+      </c>
+      <c r="G324" t="s">
+        <v>79</v>
+      </c>
+      <c r="H324" t="s">
+        <v>86</v>
+      </c>
+      <c r="I324">
+        <v>2</v>
+      </c>
+      <c r="J324">
+        <v>0</v>
+      </c>
+      <c r="K324">
+        <v>2</v>
+      </c>
+      <c r="L324">
+        <v>3</v>
+      </c>
+      <c r="M324">
+        <v>1</v>
+      </c>
+      <c r="N324">
+        <v>4</v>
+      </c>
+      <c r="O324" t="s">
+        <v>292</v>
+      </c>
+      <c r="P324" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q324">
+        <v>2.35</v>
+      </c>
+      <c r="R324">
+        <v>2.1</v>
+      </c>
+      <c r="S324">
+        <v>4.6</v>
+      </c>
+      <c r="T324">
+        <v>1.41</v>
+      </c>
+      <c r="U324">
+        <v>2.65</v>
+      </c>
+      <c r="V324">
+        <v>2.9</v>
+      </c>
+      <c r="W324">
+        <v>1.36</v>
+      </c>
+      <c r="X324">
+        <v>7.75</v>
+      </c>
+      <c r="Y324">
+        <v>1.07</v>
+      </c>
+      <c r="Z324">
+        <v>1.85</v>
+      </c>
+      <c r="AA324">
+        <v>3.69</v>
+      </c>
+      <c r="AB324">
+        <v>4.5</v>
+      </c>
+      <c r="AC324">
+        <v>1.06</v>
+      </c>
+      <c r="AD324">
+        <v>8.5</v>
+      </c>
+      <c r="AE324">
+        <v>1.33</v>
+      </c>
+      <c r="AF324">
+        <v>3.25</v>
+      </c>
+      <c r="AG324">
+        <v>2.01</v>
+      </c>
+      <c r="AH324">
+        <v>1.81</v>
+      </c>
+      <c r="AI324">
+        <v>1.9</v>
+      </c>
+      <c r="AJ324">
+        <v>1.78</v>
+      </c>
+      <c r="AK324">
+        <v>1.2</v>
+      </c>
+      <c r="AL324">
+        <v>1.27</v>
+      </c>
+      <c r="AM324">
+        <v>2</v>
+      </c>
+      <c r="AN324">
+        <v>2.33</v>
+      </c>
+      <c r="AO324">
+        <v>1.36</v>
+      </c>
+      <c r="AP324">
+        <v>2.38</v>
+      </c>
+      <c r="AQ324">
+        <v>1.27</v>
+      </c>
+      <c r="AR324">
+        <v>1.69</v>
+      </c>
+      <c r="AS324">
+        <v>1.23</v>
+      </c>
+      <c r="AT324">
+        <v>2.92</v>
+      </c>
+      <c r="AU324">
+        <v>8</v>
+      </c>
+      <c r="AV324">
+        <v>6</v>
+      </c>
+      <c r="AW324">
+        <v>2</v>
+      </c>
+      <c r="AX324">
+        <v>10</v>
+      </c>
+      <c r="AY324">
+        <v>10</v>
+      </c>
+      <c r="AZ324">
+        <v>18</v>
+      </c>
+      <c r="BA324">
+        <v>2</v>
+      </c>
+      <c r="BB324">
+        <v>7</v>
+      </c>
+      <c r="BC324">
+        <v>9</v>
+      </c>
+      <c r="BD324">
+        <v>1.46</v>
+      </c>
+      <c r="BE324">
+        <v>6.75</v>
+      </c>
+      <c r="BF324">
+        <v>3.05</v>
+      </c>
+      <c r="BG324">
+        <v>1.45</v>
+      </c>
+      <c r="BH324">
+        <v>2.48</v>
+      </c>
+      <c r="BI324">
+        <v>1.76</v>
+      </c>
+      <c r="BJ324">
+        <v>1.92</v>
+      </c>
+      <c r="BK324">
+        <v>2.23</v>
+      </c>
+      <c r="BL324">
+        <v>1.56</v>
+      </c>
+      <c r="BM324">
+        <v>2.9</v>
+      </c>
+      <c r="BN324">
+        <v>1.34</v>
+      </c>
+      <c r="BO324">
+        <v>3.9</v>
+      </c>
+      <c r="BP324">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="325" spans="1:68">
+      <c r="A325" s="1">
+        <v>324</v>
+      </c>
+      <c r="B325">
+        <v>7728526</v>
+      </c>
+      <c r="C325" t="s">
+        <v>68</v>
+      </c>
+      <c r="D325" t="s">
+        <v>69</v>
+      </c>
+      <c r="E325" s="2">
+        <v>45724.60416666666</v>
+      </c>
+      <c r="F325">
+        <v>30</v>
+      </c>
+      <c r="G325" t="s">
+        <v>76</v>
+      </c>
+      <c r="H325" t="s">
+        <v>77</v>
+      </c>
+      <c r="I325">
+        <v>1</v>
+      </c>
+      <c r="J325">
+        <v>0</v>
+      </c>
+      <c r="K325">
+        <v>1</v>
+      </c>
+      <c r="L325">
+        <v>1</v>
+      </c>
+      <c r="M325">
+        <v>1</v>
+      </c>
+      <c r="N325">
+        <v>2</v>
+      </c>
+      <c r="O325" t="s">
+        <v>293</v>
+      </c>
+      <c r="P325" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q325">
+        <v>2.65</v>
+      </c>
+      <c r="R325">
+        <v>2.1</v>
+      </c>
+      <c r="S325">
+        <v>3.75</v>
+      </c>
+      <c r="T325">
+        <v>1.39</v>
+      </c>
+      <c r="U325">
+        <v>2.75</v>
+      </c>
+      <c r="V325">
+        <v>2.8</v>
+      </c>
+      <c r="W325">
+        <v>1.38</v>
+      </c>
+      <c r="X325">
+        <v>7.25</v>
+      </c>
+      <c r="Y325">
+        <v>1.08</v>
+      </c>
+      <c r="Z325">
+        <v>2.06</v>
+      </c>
+      <c r="AA325">
+        <v>3.47</v>
+      </c>
+      <c r="AB325">
+        <v>3.85</v>
+      </c>
+      <c r="AC325">
+        <v>1.06</v>
+      </c>
+      <c r="AD325">
+        <v>8.5</v>
+      </c>
+      <c r="AE325">
+        <v>1.33</v>
+      </c>
+      <c r="AF325">
+        <v>3.25</v>
+      </c>
+      <c r="AG325">
+        <v>1.9</v>
+      </c>
+      <c r="AH325">
+        <v>1.9</v>
+      </c>
+      <c r="AI325">
+        <v>1.77</v>
+      </c>
+      <c r="AJ325">
+        <v>1.93</v>
+      </c>
+      <c r="AK325">
+        <v>1.31</v>
+      </c>
+      <c r="AL325">
+        <v>1.3</v>
+      </c>
+      <c r="AM325">
+        <v>1.7</v>
+      </c>
+      <c r="AN325">
+        <v>1.67</v>
+      </c>
+      <c r="AO325">
+        <v>1.93</v>
+      </c>
+      <c r="AP325">
+        <v>1.63</v>
+      </c>
+      <c r="AQ325">
+        <v>1.87</v>
+      </c>
+      <c r="AR325">
+        <v>1.53</v>
+      </c>
+      <c r="AS325">
+        <v>1.36</v>
+      </c>
+      <c r="AT325">
+        <v>2.89</v>
+      </c>
+      <c r="AU325">
+        <v>5</v>
+      </c>
+      <c r="AV325">
+        <v>4</v>
+      </c>
+      <c r="AW325">
+        <v>7</v>
+      </c>
+      <c r="AX325">
+        <v>9</v>
+      </c>
+      <c r="AY325">
+        <v>15</v>
+      </c>
+      <c r="AZ325">
+        <v>17</v>
+      </c>
+      <c r="BA325">
+        <v>6</v>
+      </c>
+      <c r="BB325">
+        <v>6</v>
+      </c>
+      <c r="BC325">
+        <v>12</v>
+      </c>
+      <c r="BD325">
+        <v>1.76</v>
+      </c>
+      <c r="BE325">
+        <v>6.5</v>
+      </c>
+      <c r="BF325">
+        <v>2.3</v>
+      </c>
+      <c r="BG325">
+        <v>1.37</v>
+      </c>
+      <c r="BH325">
+        <v>2.75</v>
+      </c>
+      <c r="BI325">
+        <v>1.62</v>
+      </c>
+      <c r="BJ325">
+        <v>2.1</v>
+      </c>
+      <c r="BK325">
+        <v>2</v>
+      </c>
+      <c r="BL325">
+        <v>1.68</v>
+      </c>
+      <c r="BM325">
+        <v>2.55</v>
+      </c>
+      <c r="BN325">
+        <v>1.42</v>
+      </c>
+      <c r="BO325">
+        <v>3.4</v>
+      </c>
+      <c r="BP325">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="326" spans="1:68">
+      <c r="A326" s="1">
+        <v>325</v>
+      </c>
+      <c r="B326">
+        <v>7728523</v>
+      </c>
+      <c r="C326" t="s">
+        <v>68</v>
+      </c>
+      <c r="D326" t="s">
+        <v>69</v>
+      </c>
+      <c r="E326" s="2">
+        <v>45724.70833333334</v>
+      </c>
+      <c r="F326">
+        <v>30</v>
+      </c>
+      <c r="G326" t="s">
+        <v>91</v>
+      </c>
+      <c r="H326" t="s">
+        <v>80</v>
+      </c>
+      <c r="I326">
+        <v>2</v>
+      </c>
+      <c r="J326">
+        <v>2</v>
+      </c>
+      <c r="K326">
+        <v>4</v>
+      </c>
+      <c r="L326">
+        <v>2</v>
+      </c>
+      <c r="M326">
+        <v>4</v>
+      </c>
+      <c r="N326">
+        <v>6</v>
+      </c>
+      <c r="O326" t="s">
+        <v>294</v>
+      </c>
+      <c r="P326" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q326">
+        <v>2.65</v>
+      </c>
+      <c r="R326">
+        <v>1.93</v>
+      </c>
+      <c r="S326">
+        <v>4.5</v>
+      </c>
+      <c r="T326">
+        <v>1.52</v>
+      </c>
+      <c r="U326">
+        <v>2.35</v>
+      </c>
+      <c r="V326">
+        <v>3.4</v>
+      </c>
+      <c r="W326">
+        <v>1.28</v>
+      </c>
+      <c r="X326">
+        <v>9.5</v>
+      </c>
+      <c r="Y326">
+        <v>1.04</v>
+      </c>
+      <c r="Z326">
+        <v>1.98</v>
+      </c>
+      <c r="AA326">
+        <v>3.29</v>
+      </c>
+      <c r="AB326">
+        <v>4.4</v>
+      </c>
+      <c r="AC326">
+        <v>1.09</v>
+      </c>
+      <c r="AD326">
+        <v>7</v>
+      </c>
+      <c r="AE326">
+        <v>1.45</v>
+      </c>
+      <c r="AF326">
+        <v>2.7</v>
+      </c>
+      <c r="AG326">
+        <v>2.37</v>
+      </c>
+      <c r="AH326">
+        <v>1.48</v>
+      </c>
+      <c r="AI326">
+        <v>2.1</v>
+      </c>
+      <c r="AJ326">
+        <v>1.65</v>
+      </c>
+      <c r="AK326">
+        <v>1.23</v>
+      </c>
+      <c r="AL326">
+        <v>1.34</v>
+      </c>
+      <c r="AM326">
+        <v>1.78</v>
+      </c>
+      <c r="AN326">
+        <v>1.14</v>
+      </c>
+      <c r="AO326">
+        <v>0.93</v>
+      </c>
+      <c r="AP326">
+        <v>1.07</v>
+      </c>
+      <c r="AQ326">
+        <v>1.07</v>
+      </c>
+      <c r="AR326">
+        <v>1.58</v>
+      </c>
+      <c r="AS326">
+        <v>1.14</v>
+      </c>
+      <c r="AT326">
+        <v>2.72</v>
+      </c>
+      <c r="AU326">
+        <v>7</v>
+      </c>
+      <c r="AV326">
+        <v>6</v>
+      </c>
+      <c r="AW326">
+        <v>20</v>
+      </c>
+      <c r="AX326">
+        <v>7</v>
+      </c>
+      <c r="AY326">
+        <v>30</v>
+      </c>
+      <c r="AZ326">
+        <v>14</v>
+      </c>
+      <c r="BA326">
+        <v>5</v>
+      </c>
+      <c r="BB326">
+        <v>8</v>
+      </c>
+      <c r="BC326">
+        <v>13</v>
+      </c>
+      <c r="BD326">
+        <v>1.56</v>
+      </c>
+      <c r="BE326">
+        <v>6.75</v>
+      </c>
+      <c r="BF326">
+        <v>2.65</v>
+      </c>
+      <c r="BG326">
+        <v>1.38</v>
+      </c>
+      <c r="BH326">
+        <v>2.7</v>
+      </c>
+      <c r="BI326">
+        <v>1.64</v>
+      </c>
+      <c r="BJ326">
+        <v>2.08</v>
+      </c>
+      <c r="BK326">
+        <v>2.04</v>
+      </c>
+      <c r="BL326">
+        <v>1.66</v>
+      </c>
+      <c r="BM326">
+        <v>2.63</v>
+      </c>
+      <c r="BN326">
+        <v>1.41</v>
+      </c>
+      <c r="BO326">
+        <v>3.4</v>
+      </c>
+      <c r="BP326">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="408">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -901,6 +901,15 @@
     <t>['12', '45+5']</t>
   </si>
   <si>
+    <t>['9', '90+3']</t>
+  </si>
+  <si>
+    <t>['29', '71', '89']</t>
+  </si>
+  <si>
+    <t>['32', '36', '58']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1226,6 +1235,9 @@
   </si>
   <si>
     <t>['32', '34', '72', '79']</t>
+  </si>
+  <si>
+    <t>['83', '85']</t>
   </si>
 </sst>
 </file>
@@ -1587,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP326"/>
+  <dimension ref="A1:BP330"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1843,7 +1855,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1921,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ2">
         <v>0.93</v>
@@ -2255,7 +2267,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3079,7 +3091,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3285,7 +3297,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3572,7 +3584,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ10">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3778,7 +3790,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ11">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4109,7 +4121,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -5011,10 +5023,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5217,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ18">
         <v>1.07</v>
@@ -5345,7 +5357,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5423,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ19">
         <v>1.38</v>
@@ -5963,7 +5975,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6169,7 +6181,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6375,7 +6387,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6453,10 +6465,10 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ24">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR24">
         <v>2.51</v>
@@ -6581,7 +6593,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6787,7 +6799,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6993,7 +7005,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7071,7 +7083,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ27">
         <v>0.93</v>
@@ -7405,7 +7417,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7692,7 +7704,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ30">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR30">
         <v>1.73</v>
@@ -8023,7 +8035,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8104,7 +8116,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ32">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR32">
         <v>1.31</v>
@@ -8229,7 +8241,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8641,7 +8653,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8719,7 +8731,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ35">
         <v>1.87</v>
@@ -8925,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ36">
         <v>1.47</v>
@@ -10495,7 +10507,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10576,7 +10588,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ44">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -11113,7 +11125,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11191,7 +11203,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ47">
         <v>1.07</v>
@@ -11603,10 +11615,10 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ49">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR49">
         <v>1.38</v>
@@ -12224,7 +12236,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ52">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR52">
         <v>1.28</v>
@@ -12636,7 +12648,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ54">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12761,7 +12773,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12967,7 +12979,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13173,7 +13185,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13251,7 +13263,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -13379,7 +13391,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13791,7 +13803,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14281,7 +14293,7 @@
         <v>0.5</v>
       </c>
       <c r="AP62">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14409,7 +14421,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14490,7 +14502,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ63">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR63">
         <v>1.13</v>
@@ -15027,7 +15039,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15439,7 +15451,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15645,7 +15657,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15932,7 +15944,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ70">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR70">
         <v>1.04</v>
@@ -16263,7 +16275,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16341,7 +16353,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ72">
         <v>1.07</v>
@@ -16469,7 +16481,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16547,7 +16559,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ73">
         <v>1.38</v>
@@ -16675,7 +16687,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17168,7 +17180,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ76">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -17499,7 +17511,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17580,7 +17592,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ78">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR78">
         <v>1.42</v>
@@ -17705,7 +17717,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17786,7 +17798,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ79">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR79">
         <v>1.18</v>
@@ -18117,7 +18129,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18323,7 +18335,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18529,7 +18541,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19019,10 +19031,10 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ85">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -19353,7 +19365,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19637,7 +19649,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
         <v>1.4</v>
@@ -19765,7 +19777,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19971,7 +19983,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20049,7 +20061,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ90">
         <v>1.33</v>
@@ -20258,7 +20270,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ91">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20383,7 +20395,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20795,7 +20807,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -21001,7 +21013,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21491,7 +21503,7 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ97">
         <v>1.13</v>
@@ -22031,7 +22043,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22318,7 +22330,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ101">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR101">
         <v>1.58</v>
@@ -22521,7 +22533,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ102">
         <v>1.4</v>
@@ -22933,7 +22945,7 @@
         <v>0.25</v>
       </c>
       <c r="AP104">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ104">
         <v>0.2</v>
@@ -23473,7 +23485,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23760,7 +23772,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ108">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR108">
         <v>1.17</v>
@@ -24091,7 +24103,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24503,7 +24515,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24709,7 +24721,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24996,7 +25008,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ114">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -25121,7 +25133,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25945,7 +25957,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26023,7 +26035,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
         <v>1.47</v>
@@ -26232,7 +26244,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ120">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR120">
         <v>1.6</v>
@@ -26435,7 +26447,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26563,7 +26575,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26644,7 +26656,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ122">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR122">
         <v>1.4</v>
@@ -26975,7 +26987,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27056,7 +27068,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ124">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR124">
         <v>1.12</v>
@@ -27387,7 +27399,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27671,7 +27683,7 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ127">
         <v>0.8</v>
@@ -27799,7 +27811,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28211,7 +28223,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28417,7 +28429,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28623,7 +28635,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28701,7 +28713,7 @@
         <v>1.17</v>
       </c>
       <c r="AP132">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ132">
         <v>1.53</v>
@@ -29035,7 +29047,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29241,7 +29253,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29528,7 +29540,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ136">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -29859,7 +29871,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30349,7 +30361,7 @@
         <v>1</v>
       </c>
       <c r="AP140">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ140">
         <v>1.07</v>
@@ -30477,7 +30489,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30683,7 +30695,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30764,7 +30776,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ142">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR142">
         <v>1.16</v>
@@ -30889,7 +30901,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31095,7 +31107,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31173,7 +31185,7 @@
         <v>0.83</v>
       </c>
       <c r="AP144">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ144">
         <v>1.07</v>
@@ -31379,10 +31391,10 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ145">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR145">
         <v>1.15</v>
@@ -31507,7 +31519,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31919,7 +31931,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32618,7 +32630,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ151">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR151">
         <v>1.43</v>
@@ -32949,7 +32961,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33233,7 +33245,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ154">
         <v>1.07</v>
@@ -33567,7 +33579,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34472,7 +34484,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ160">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34884,7 +34896,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ162">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR162">
         <v>1.47</v>
@@ -35215,7 +35227,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35499,10 +35511,10 @@
         <v>1.14</v>
       </c>
       <c r="AP165">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ165">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR165">
         <v>1.7</v>
@@ -35833,7 +35845,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36117,7 +36129,7 @@
         <v>3</v>
       </c>
       <c r="AP168">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ168">
         <v>1.87</v>
@@ -36863,7 +36875,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37481,7 +37493,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37559,7 +37571,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ175">
         <v>1</v>
@@ -37768,7 +37780,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ176">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR176">
         <v>1.6</v>
@@ -37893,7 +37905,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -37974,7 +37986,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ177">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR177">
         <v>1.68</v>
@@ -38305,7 +38317,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38511,7 +38523,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39001,7 +39013,7 @@
         <v>1.14</v>
       </c>
       <c r="AP182">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ182">
         <v>1.07</v>
@@ -39335,7 +39347,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39413,7 +39425,7 @@
         <v>0.88</v>
       </c>
       <c r="AP184">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ184">
         <v>1</v>
@@ -39622,7 +39634,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ185">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR185">
         <v>1.42</v>
@@ -40034,7 +40046,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ187">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR187">
         <v>1.45</v>
@@ -40159,7 +40171,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40446,7 +40458,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ189">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR189">
         <v>1.53</v>
@@ -40649,7 +40661,7 @@
         <v>2.75</v>
       </c>
       <c r="AP190">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ190">
         <v>1.87</v>
@@ -40777,7 +40789,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40983,7 +40995,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41189,7 +41201,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41395,7 +41407,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41473,7 +41485,7 @@
         <v>1.56</v>
       </c>
       <c r="AP194">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ194">
         <v>1.38</v>
@@ -42631,7 +42643,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42709,7 +42721,7 @@
         <v>0.11</v>
       </c>
       <c r="AP200">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ200">
         <v>1.13</v>
@@ -43043,7 +43055,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43124,7 +43136,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ202">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR202">
         <v>1.63</v>
@@ -43249,7 +43261,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43867,7 +43879,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43948,7 +43960,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ206">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR206">
         <v>1.42</v>
@@ -44360,7 +44372,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ208">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR208">
         <v>1.46</v>
@@ -44563,10 +44575,10 @@
         <v>0.6</v>
       </c>
       <c r="AP209">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ209">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR209">
         <v>1.74</v>
@@ -44897,7 +44909,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45103,7 +45115,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45309,7 +45321,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45515,7 +45527,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45799,7 +45811,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP215">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ215">
         <v>1.07</v>
@@ -45927,7 +45939,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -47163,7 +47175,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47450,7 +47462,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ223">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR223">
         <v>1.71</v>
@@ -47575,7 +47587,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47987,7 +47999,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48274,7 +48286,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ227">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR227">
         <v>1.67</v>
@@ -48605,7 +48617,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48811,7 +48823,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48889,10 +48901,10 @@
         <v>1.3</v>
       </c>
       <c r="AP230">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ230">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR230">
         <v>1.54</v>
@@ -49017,7 +49029,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49095,7 +49107,7 @@
         <v>1.2</v>
       </c>
       <c r="AP231">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ231">
         <v>1.53</v>
@@ -49301,7 +49313,7 @@
         <v>0.8</v>
       </c>
       <c r="AP232">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ232">
         <v>1</v>
@@ -49510,7 +49522,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ233">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR233">
         <v>1.18</v>
@@ -49841,7 +49853,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50125,7 +50137,7 @@
         <v>1.5</v>
       </c>
       <c r="AP236">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ236">
         <v>1.27</v>
@@ -50331,7 +50343,7 @@
         <v>1.22</v>
       </c>
       <c r="AP237">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ237">
         <v>1.47</v>
@@ -50665,7 +50677,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51283,7 +51295,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51695,7 +51707,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51776,7 +51788,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ244">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR244">
         <v>1.4</v>
@@ -52107,7 +52119,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52391,7 +52403,7 @@
         <v>1.5</v>
       </c>
       <c r="AP247">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ247">
         <v>1.36</v>
@@ -52806,7 +52818,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ249">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR249">
         <v>1.51</v>
@@ -52931,7 +52943,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53137,7 +53149,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53424,7 +53436,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ252">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR252">
         <v>1.71</v>
@@ -53549,7 +53561,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53961,7 +53973,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54167,7 +54179,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54454,7 +54466,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ257">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR257">
         <v>1.24</v>
@@ -54657,7 +54669,7 @@
         <v>0.55</v>
       </c>
       <c r="AP258">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ258">
         <v>1.07</v>
@@ -54863,7 +54875,7 @@
         <v>1.09</v>
       </c>
       <c r="AP259">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ259">
         <v>1</v>
@@ -55197,7 +55209,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55403,7 +55415,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55481,7 +55493,7 @@
         <v>1.33</v>
       </c>
       <c r="AP262">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ262">
         <v>1.33</v>
@@ -55893,7 +55905,7 @@
         <v>1.36</v>
       </c>
       <c r="AP264">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ264">
         <v>1.47</v>
@@ -56021,7 +56033,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -57132,7 +57144,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ270">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR270">
         <v>1.69</v>
@@ -57463,7 +57475,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -57750,7 +57762,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ273">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR273">
         <v>1.65</v>
@@ -57953,7 +57965,7 @@
         <v>1.08</v>
       </c>
       <c r="AP274">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ274">
         <v>0.93</v>
@@ -58159,10 +58171,10 @@
         <v>0.91</v>
       </c>
       <c r="AP275">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ275">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR275">
         <v>1.57</v>
@@ -58493,7 +58505,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58777,7 +58789,7 @@
         <v>1.17</v>
       </c>
       <c r="AP278">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ278">
         <v>1.07</v>
@@ -58983,7 +58995,7 @@
         <v>1.46</v>
       </c>
       <c r="AP279">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ279">
         <v>1.53</v>
@@ -59729,7 +59741,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59810,7 +59822,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ283">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR283">
         <v>1.67</v>
@@ -59935,7 +59947,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60016,7 +60028,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ284">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR284">
         <v>1.39</v>
@@ -60553,7 +60565,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -60634,7 +60646,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ287">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR287">
         <v>1.29</v>
@@ -61171,7 +61183,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61252,7 +61264,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ290">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR290">
         <v>1.62</v>
@@ -61377,7 +61389,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61455,7 +61467,7 @@
         <v>0.85</v>
       </c>
       <c r="AP291">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ291">
         <v>1.13</v>
@@ -61661,7 +61673,7 @@
         <v>1</v>
       </c>
       <c r="AP292">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ292">
         <v>1</v>
@@ -62897,7 +62909,7 @@
         <v>0.23</v>
       </c>
       <c r="AP298">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ298">
         <v>0.2</v>
@@ -63231,7 +63243,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63437,7 +63449,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63643,7 +63655,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -63721,7 +63733,7 @@
         <v>1.36</v>
       </c>
       <c r="AP302">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ302">
         <v>1.33</v>
@@ -64136,7 +64148,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ304">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR304">
         <v>1.51</v>
@@ -64342,7 +64354,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ305">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR305">
         <v>1.62</v>
@@ -64545,7 +64557,7 @@
         <v>1.15</v>
       </c>
       <c r="AP306">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ306">
         <v>1.07</v>
@@ -65085,7 +65097,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65291,7 +65303,7 @@
         <v>281</v>
       </c>
       <c r="P310" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q310">
         <v>2.31</v>
@@ -65372,7 +65384,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ310">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR310">
         <v>1.27</v>
@@ -65909,7 +65921,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66321,7 +66333,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66527,7 +66539,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -66814,7 +66826,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ317">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR317">
         <v>1.53</v>
@@ -68587,7 +68599,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -68744,6 +68756,830 @@
       </c>
       <c r="BP326">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="327" spans="1:68">
+      <c r="A327" s="1">
+        <v>326</v>
+      </c>
+      <c r="B327">
+        <v>7728525</v>
+      </c>
+      <c r="C327" t="s">
+        <v>68</v>
+      </c>
+      <c r="D327" t="s">
+        <v>69</v>
+      </c>
+      <c r="E327" s="2">
+        <v>45725.41666666666</v>
+      </c>
+      <c r="F327">
+        <v>30</v>
+      </c>
+      <c r="G327" t="s">
+        <v>84</v>
+      </c>
+      <c r="H327" t="s">
+        <v>81</v>
+      </c>
+      <c r="I327">
+        <v>1</v>
+      </c>
+      <c r="J327">
+        <v>0</v>
+      </c>
+      <c r="K327">
+        <v>1</v>
+      </c>
+      <c r="L327">
+        <v>2</v>
+      </c>
+      <c r="M327">
+        <v>0</v>
+      </c>
+      <c r="N327">
+        <v>2</v>
+      </c>
+      <c r="O327" t="s">
+        <v>295</v>
+      </c>
+      <c r="P327" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q327">
+        <v>3.2</v>
+      </c>
+      <c r="R327">
+        <v>1.83</v>
+      </c>
+      <c r="S327">
+        <v>4.5</v>
+      </c>
+      <c r="T327">
+        <v>1.67</v>
+      </c>
+      <c r="U327">
+        <v>2.1</v>
+      </c>
+      <c r="V327">
+        <v>4.33</v>
+      </c>
+      <c r="W327">
+        <v>1.2</v>
+      </c>
+      <c r="X327">
+        <v>15</v>
+      </c>
+      <c r="Y327">
+        <v>1.03</v>
+      </c>
+      <c r="Z327">
+        <v>2.63</v>
+      </c>
+      <c r="AA327">
+        <v>3.29</v>
+      </c>
+      <c r="AB327">
+        <v>2.85</v>
+      </c>
+      <c r="AC327">
+        <v>1.13</v>
+      </c>
+      <c r="AD327">
+        <v>5.75</v>
+      </c>
+      <c r="AE327">
+        <v>1.65</v>
+      </c>
+      <c r="AF327">
+        <v>2.1</v>
+      </c>
+      <c r="AG327">
+        <v>2.2</v>
+      </c>
+      <c r="AH327">
+        <v>1.55</v>
+      </c>
+      <c r="AI327">
+        <v>2.5</v>
+      </c>
+      <c r="AJ327">
+        <v>1.5</v>
+      </c>
+      <c r="AK327">
+        <v>1.29</v>
+      </c>
+      <c r="AL327">
+        <v>1.39</v>
+      </c>
+      <c r="AM327">
+        <v>1.6</v>
+      </c>
+      <c r="AN327">
+        <v>1.14</v>
+      </c>
+      <c r="AO327">
+        <v>1.47</v>
+      </c>
+      <c r="AP327">
+        <v>1.27</v>
+      </c>
+      <c r="AQ327">
+        <v>1.38</v>
+      </c>
+      <c r="AR327">
+        <v>1.32</v>
+      </c>
+      <c r="AS327">
+        <v>1.03</v>
+      </c>
+      <c r="AT327">
+        <v>2.35</v>
+      </c>
+      <c r="AU327">
+        <v>8</v>
+      </c>
+      <c r="AV327">
+        <v>3</v>
+      </c>
+      <c r="AW327">
+        <v>13</v>
+      </c>
+      <c r="AX327">
+        <v>5</v>
+      </c>
+      <c r="AY327">
+        <v>23</v>
+      </c>
+      <c r="AZ327">
+        <v>9</v>
+      </c>
+      <c r="BA327">
+        <v>6</v>
+      </c>
+      <c r="BB327">
+        <v>4</v>
+      </c>
+      <c r="BC327">
+        <v>10</v>
+      </c>
+      <c r="BD327">
+        <v>1.76</v>
+      </c>
+      <c r="BE327">
+        <v>6.5</v>
+      </c>
+      <c r="BF327">
+        <v>2.28</v>
+      </c>
+      <c r="BG327">
+        <v>1.33</v>
+      </c>
+      <c r="BH327">
+        <v>2.83</v>
+      </c>
+      <c r="BI327">
+        <v>1.63</v>
+      </c>
+      <c r="BJ327">
+        <v>2.09</v>
+      </c>
+      <c r="BK327">
+        <v>2.09</v>
+      </c>
+      <c r="BL327">
+        <v>1.66</v>
+      </c>
+      <c r="BM327">
+        <v>2.78</v>
+      </c>
+      <c r="BN327">
+        <v>1.36</v>
+      </c>
+      <c r="BO327">
+        <v>3.84</v>
+      </c>
+      <c r="BP327">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="328" spans="1:68">
+      <c r="A328" s="1">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>7728519</v>
+      </c>
+      <c r="C328" t="s">
+        <v>68</v>
+      </c>
+      <c r="D328" t="s">
+        <v>69</v>
+      </c>
+      <c r="E328" s="2">
+        <v>45725.51041666666</v>
+      </c>
+      <c r="F328">
+        <v>30</v>
+      </c>
+      <c r="G328" t="s">
+        <v>83</v>
+      </c>
+      <c r="H328" t="s">
+        <v>72</v>
+      </c>
+      <c r="I328">
+        <v>0</v>
+      </c>
+      <c r="J328">
+        <v>0</v>
+      </c>
+      <c r="K328">
+        <v>0</v>
+      </c>
+      <c r="L328">
+        <v>0</v>
+      </c>
+      <c r="M328">
+        <v>2</v>
+      </c>
+      <c r="N328">
+        <v>2</v>
+      </c>
+      <c r="O328" t="s">
+        <v>94</v>
+      </c>
+      <c r="P328" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q328">
+        <v>3.3</v>
+      </c>
+      <c r="R328">
+        <v>1.9</v>
+      </c>
+      <c r="S328">
+        <v>3.45</v>
+      </c>
+      <c r="T328">
+        <v>1.53</v>
+      </c>
+      <c r="U328">
+        <v>2.38</v>
+      </c>
+      <c r="V328">
+        <v>3.75</v>
+      </c>
+      <c r="W328">
+        <v>1.25</v>
+      </c>
+      <c r="X328">
+        <v>11</v>
+      </c>
+      <c r="Y328">
+        <v>1.05</v>
+      </c>
+      <c r="Z328">
+        <v>2.74</v>
+      </c>
+      <c r="AA328">
+        <v>2.98</v>
+      </c>
+      <c r="AB328">
+        <v>2.99</v>
+      </c>
+      <c r="AC328">
+        <v>1.1</v>
+      </c>
+      <c r="AD328">
+        <v>6.5</v>
+      </c>
+      <c r="AE328">
+        <v>1.48</v>
+      </c>
+      <c r="AF328">
+        <v>2.37</v>
+      </c>
+      <c r="AG328">
+        <v>2.55</v>
+      </c>
+      <c r="AH328">
+        <v>1.51</v>
+      </c>
+      <c r="AI328">
+        <v>2.1</v>
+      </c>
+      <c r="AJ328">
+        <v>1.67</v>
+      </c>
+      <c r="AK328">
+        <v>1.4</v>
+      </c>
+      <c r="AL328">
+        <v>1.33</v>
+      </c>
+      <c r="AM328">
+        <v>1.45</v>
+      </c>
+      <c r="AN328">
+        <v>1.71</v>
+      </c>
+      <c r="AO328">
+        <v>1.21</v>
+      </c>
+      <c r="AP328">
+        <v>1.6</v>
+      </c>
+      <c r="AQ328">
+        <v>1.33</v>
+      </c>
+      <c r="AR328">
+        <v>1.38</v>
+      </c>
+      <c r="AS328">
+        <v>1.28</v>
+      </c>
+      <c r="AT328">
+        <v>2.66</v>
+      </c>
+      <c r="AU328">
+        <v>2</v>
+      </c>
+      <c r="AV328">
+        <v>3</v>
+      </c>
+      <c r="AW328">
+        <v>6</v>
+      </c>
+      <c r="AX328">
+        <v>4</v>
+      </c>
+      <c r="AY328">
+        <v>8</v>
+      </c>
+      <c r="AZ328">
+        <v>7</v>
+      </c>
+      <c r="BA328">
+        <v>5</v>
+      </c>
+      <c r="BB328">
+        <v>4</v>
+      </c>
+      <c r="BC328">
+        <v>9</v>
+      </c>
+      <c r="BD328">
+        <v>1.81</v>
+      </c>
+      <c r="BE328">
+        <v>6.25</v>
+      </c>
+      <c r="BF328">
+        <v>2.23</v>
+      </c>
+      <c r="BG328">
+        <v>1.56</v>
+      </c>
+      <c r="BH328">
+        <v>2.23</v>
+      </c>
+      <c r="BI328">
+        <v>1.93</v>
+      </c>
+      <c r="BJ328">
+        <v>1.74</v>
+      </c>
+      <c r="BK328">
+        <v>2.48</v>
+      </c>
+      <c r="BL328">
+        <v>1.45</v>
+      </c>
+      <c r="BM328">
+        <v>3.3</v>
+      </c>
+      <c r="BN328">
+        <v>1.27</v>
+      </c>
+      <c r="BO328">
+        <v>4.4</v>
+      </c>
+      <c r="BP328">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="329" spans="1:68">
+      <c r="A329" s="1">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>7728520</v>
+      </c>
+      <c r="C329" t="s">
+        <v>68</v>
+      </c>
+      <c r="D329" t="s">
+        <v>69</v>
+      </c>
+      <c r="E329" s="2">
+        <v>45725.60416666666</v>
+      </c>
+      <c r="F329">
+        <v>30</v>
+      </c>
+      <c r="G329" t="s">
+        <v>82</v>
+      </c>
+      <c r="H329" t="s">
+        <v>87</v>
+      </c>
+      <c r="I329">
+        <v>1</v>
+      </c>
+      <c r="J329">
+        <v>0</v>
+      </c>
+      <c r="K329">
+        <v>1</v>
+      </c>
+      <c r="L329">
+        <v>3</v>
+      </c>
+      <c r="M329">
+        <v>0</v>
+      </c>
+      <c r="N329">
+        <v>3</v>
+      </c>
+      <c r="O329" t="s">
+        <v>296</v>
+      </c>
+      <c r="P329" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q329">
+        <v>1.8</v>
+      </c>
+      <c r="R329">
+        <v>2.4</v>
+      </c>
+      <c r="S329">
+        <v>8.5</v>
+      </c>
+      <c r="T329">
+        <v>1.36</v>
+      </c>
+      <c r="U329">
+        <v>3</v>
+      </c>
+      <c r="V329">
+        <v>2.63</v>
+      </c>
+      <c r="W329">
+        <v>1.44</v>
+      </c>
+      <c r="X329">
+        <v>7</v>
+      </c>
+      <c r="Y329">
+        <v>1.1</v>
+      </c>
+      <c r="Z329">
+        <v>1.32</v>
+      </c>
+      <c r="AA329">
+        <v>5.5</v>
+      </c>
+      <c r="AB329">
+        <v>11</v>
+      </c>
+      <c r="AC329">
+        <v>1.04</v>
+      </c>
+      <c r="AD329">
+        <v>10</v>
+      </c>
+      <c r="AE329">
+        <v>1.25</v>
+      </c>
+      <c r="AF329">
+        <v>3.9</v>
+      </c>
+      <c r="AG329">
+        <v>1.8</v>
+      </c>
+      <c r="AH329">
+        <v>2.02</v>
+      </c>
+      <c r="AI329">
+        <v>2.2</v>
+      </c>
+      <c r="AJ329">
+        <v>1.62</v>
+      </c>
+      <c r="AK329">
+        <v>1.05</v>
+      </c>
+      <c r="AL329">
+        <v>1.17</v>
+      </c>
+      <c r="AM329">
+        <v>3.2</v>
+      </c>
+      <c r="AN329">
+        <v>1.93</v>
+      </c>
+      <c r="AO329">
+        <v>0.47</v>
+      </c>
+      <c r="AP329">
+        <v>2</v>
+      </c>
+      <c r="AQ329">
+        <v>0.44</v>
+      </c>
+      <c r="AR329">
+        <v>1.65</v>
+      </c>
+      <c r="AS329">
+        <v>0.95</v>
+      </c>
+      <c r="AT329">
+        <v>2.6</v>
+      </c>
+      <c r="AU329">
+        <v>9</v>
+      </c>
+      <c r="AV329">
+        <v>2</v>
+      </c>
+      <c r="AW329">
+        <v>10</v>
+      </c>
+      <c r="AX329">
+        <v>12</v>
+      </c>
+      <c r="AY329">
+        <v>22</v>
+      </c>
+      <c r="AZ329">
+        <v>17</v>
+      </c>
+      <c r="BA329">
+        <v>3</v>
+      </c>
+      <c r="BB329">
+        <v>4</v>
+      </c>
+      <c r="BC329">
+        <v>7</v>
+      </c>
+      <c r="BD329">
+        <v>1.24</v>
+      </c>
+      <c r="BE329">
+        <v>8</v>
+      </c>
+      <c r="BF329">
+        <v>4.4</v>
+      </c>
+      <c r="BG329">
+        <v>1.36</v>
+      </c>
+      <c r="BH329">
+        <v>2.8</v>
+      </c>
+      <c r="BI329">
+        <v>1.61</v>
+      </c>
+      <c r="BJ329">
+        <v>2.12</v>
+      </c>
+      <c r="BK329">
+        <v>2</v>
+      </c>
+      <c r="BL329">
+        <v>1.7</v>
+      </c>
+      <c r="BM329">
+        <v>2.55</v>
+      </c>
+      <c r="BN329">
+        <v>1.43</v>
+      </c>
+      <c r="BO329">
+        <v>3.3</v>
+      </c>
+      <c r="BP329">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="330" spans="1:68">
+      <c r="A330" s="1">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>7728524</v>
+      </c>
+      <c r="C330" t="s">
+        <v>68</v>
+      </c>
+      <c r="D330" t="s">
+        <v>69</v>
+      </c>
+      <c r="E330" s="2">
+        <v>45725.70833333334</v>
+      </c>
+      <c r="F330">
+        <v>30</v>
+      </c>
+      <c r="G330" t="s">
+        <v>70</v>
+      </c>
+      <c r="H330" t="s">
+        <v>74</v>
+      </c>
+      <c r="I330">
+        <v>2</v>
+      </c>
+      <c r="J330">
+        <v>0</v>
+      </c>
+      <c r="K330">
+        <v>2</v>
+      </c>
+      <c r="L330">
+        <v>3</v>
+      </c>
+      <c r="M330">
+        <v>0</v>
+      </c>
+      <c r="N330">
+        <v>3</v>
+      </c>
+      <c r="O330" t="s">
+        <v>297</v>
+      </c>
+      <c r="P330" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q330">
+        <v>2.2</v>
+      </c>
+      <c r="R330">
+        <v>2.2</v>
+      </c>
+      <c r="S330">
+        <v>6</v>
+      </c>
+      <c r="T330">
+        <v>1.44</v>
+      </c>
+      <c r="U330">
+        <v>2.63</v>
+      </c>
+      <c r="V330">
+        <v>3.25</v>
+      </c>
+      <c r="W330">
+        <v>1.33</v>
+      </c>
+      <c r="X330">
+        <v>9</v>
+      </c>
+      <c r="Y330">
+        <v>1.07</v>
+      </c>
+      <c r="Z330">
+        <v>1.74</v>
+      </c>
+      <c r="AA330">
+        <v>3.65</v>
+      </c>
+      <c r="AB330">
+        <v>5.4</v>
+      </c>
+      <c r="AC330">
+        <v>1.06</v>
+      </c>
+      <c r="AD330">
+        <v>8.5</v>
+      </c>
+      <c r="AE330">
+        <v>1.35</v>
+      </c>
+      <c r="AF330">
+        <v>3.1</v>
+      </c>
+      <c r="AG330">
+        <v>1.95</v>
+      </c>
+      <c r="AH330">
+        <v>1.7</v>
+      </c>
+      <c r="AI330">
+        <v>2.1</v>
+      </c>
+      <c r="AJ330">
+        <v>1.67</v>
+      </c>
+      <c r="AK330">
+        <v>1.14</v>
+      </c>
+      <c r="AL330">
+        <v>1.25</v>
+      </c>
+      <c r="AM330">
+        <v>2.25</v>
+      </c>
+      <c r="AN330">
+        <v>1.6</v>
+      </c>
+      <c r="AO330">
+        <v>0.93</v>
+      </c>
+      <c r="AP330">
+        <v>1.69</v>
+      </c>
+      <c r="AQ330">
+        <v>0.87</v>
+      </c>
+      <c r="AR330">
+        <v>1.67</v>
+      </c>
+      <c r="AS330">
+        <v>0.91</v>
+      </c>
+      <c r="AT330">
+        <v>2.58</v>
+      </c>
+      <c r="AU330">
+        <v>8</v>
+      </c>
+      <c r="AV330">
+        <v>4</v>
+      </c>
+      <c r="AW330">
+        <v>4</v>
+      </c>
+      <c r="AX330">
+        <v>6</v>
+      </c>
+      <c r="AY330">
+        <v>14</v>
+      </c>
+      <c r="AZ330">
+        <v>12</v>
+      </c>
+      <c r="BA330">
+        <v>8</v>
+      </c>
+      <c r="BB330">
+        <v>6</v>
+      </c>
+      <c r="BC330">
+        <v>14</v>
+      </c>
+      <c r="BD330">
+        <v>1.58</v>
+      </c>
+      <c r="BE330">
+        <v>6.25</v>
+      </c>
+      <c r="BF330">
+        <v>2.65</v>
+      </c>
+      <c r="BG330">
+        <v>1.38</v>
+      </c>
+      <c r="BH330">
+        <v>2.71</v>
+      </c>
+      <c r="BI330">
+        <v>1.7</v>
+      </c>
+      <c r="BJ330">
+        <v>2.03</v>
+      </c>
+      <c r="BK330">
+        <v>2.15</v>
+      </c>
+      <c r="BL330">
+        <v>1.59</v>
+      </c>
+      <c r="BM330">
+        <v>2.88</v>
+      </c>
+      <c r="BN330">
+        <v>1.32</v>
+      </c>
+      <c r="BO330">
+        <v>4.1</v>
+      </c>
+      <c r="BP330">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="408">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -910,6 +910,9 @@
     <t>['32', '36', '58']</t>
   </si>
   <si>
+    <t>['1']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1220,9 +1223,6 @@
   </si>
   <si>
     <t>['24', '27']</t>
-  </si>
-  <si>
-    <t>['1']</t>
   </si>
   <si>
     <t>['55', '62']</t>
@@ -1599,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP330"/>
+  <dimension ref="A1:BP331"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1855,7 +1855,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1936,7 +1936,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ2">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3091,7 +3091,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3297,7 +3297,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10">
         <v>0.44</v>
@@ -4121,7 +4121,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -5357,7 +5357,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5975,7 +5975,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6181,7 +6181,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6387,7 +6387,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6593,7 +6593,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6799,7 +6799,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7005,7 +7005,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7086,7 +7086,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ27">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR27">
         <v>1.25</v>
@@ -7417,7 +7417,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7495,7 +7495,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ29">
         <v>1.27</v>
@@ -8035,7 +8035,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8241,7 +8241,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8653,7 +8653,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -10507,7 +10507,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11125,7 +11125,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12030,7 +12030,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ51">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR51">
         <v>0.76</v>
@@ -12439,7 +12439,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12773,7 +12773,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12979,7 +12979,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13185,7 +13185,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13391,7 +13391,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13472,7 +13472,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ58">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR58">
         <v>1.22</v>
@@ -13803,7 +13803,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14421,7 +14421,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -15039,7 +15039,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15451,7 +15451,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15657,7 +15657,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16275,7 +16275,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16481,7 +16481,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16687,7 +16687,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16765,7 +16765,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ74">
         <v>1.36</v>
@@ -17511,7 +17511,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17717,7 +17717,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18129,7 +18129,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18335,7 +18335,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18541,7 +18541,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19365,7 +19365,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19777,7 +19777,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19983,7 +19983,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20395,7 +20395,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20807,7 +20807,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20888,7 +20888,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ94">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR94">
         <v>1.16</v>
@@ -21013,7 +21013,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21709,7 +21709,7 @@
         <v>0.67</v>
       </c>
       <c r="AP98">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ98">
         <v>1.07</v>
@@ -22043,7 +22043,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23485,7 +23485,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24103,7 +24103,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24515,7 +24515,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24721,7 +24721,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25133,7 +25133,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25832,7 +25832,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ118">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR118">
         <v>1.69</v>
@@ -25957,7 +25957,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26575,7 +26575,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26653,7 +26653,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ122">
         <v>0.87</v>
@@ -26987,7 +26987,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27399,7 +27399,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27811,7 +27811,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28223,7 +28223,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28429,7 +28429,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28635,7 +28635,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29047,7 +29047,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29253,7 +29253,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29871,7 +29871,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29952,7 +29952,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ138">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR138">
         <v>1.52</v>
@@ -30489,7 +30489,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30695,7 +30695,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30901,7 +30901,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31107,7 +31107,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31519,7 +31519,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31803,7 +31803,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ147">
         <v>1</v>
@@ -31931,7 +31931,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32836,7 +32836,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ152">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR152">
         <v>1.54</v>
@@ -32961,7 +32961,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33579,7 +33579,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -35227,7 +35227,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35717,7 +35717,7 @@
         <v>0.71</v>
       </c>
       <c r="AP166">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ166">
         <v>0.8</v>
@@ -35845,7 +35845,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36875,7 +36875,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37493,7 +37493,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37905,7 +37905,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38192,7 +38192,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ178">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR178">
         <v>1.71</v>
@@ -38317,7 +38317,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38523,7 +38523,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39347,7 +39347,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40171,7 +40171,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40789,7 +40789,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40995,7 +40995,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41201,7 +41201,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41407,7 +41407,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41897,7 +41897,7 @@
         <v>0.63</v>
       </c>
       <c r="AP196">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ196">
         <v>1.07</v>
@@ -42643,7 +42643,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42930,7 +42930,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ201">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR201">
         <v>1.46</v>
@@ -43055,7 +43055,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43261,7 +43261,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43879,7 +43879,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44163,7 +44163,7 @@
         <v>0.78</v>
       </c>
       <c r="AP207">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ207">
         <v>1</v>
@@ -44909,7 +44909,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45115,7 +45115,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45321,7 +45321,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45527,7 +45527,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45939,7 +45939,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46844,7 +46844,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ220">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR220">
         <v>1.23</v>
@@ -47175,7 +47175,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47587,7 +47587,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47871,7 +47871,7 @@
         <v>0.2</v>
       </c>
       <c r="AP225">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ225">
         <v>0.2</v>
@@ -47999,7 +47999,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48617,7 +48617,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48823,7 +48823,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49029,7 +49029,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49853,7 +49853,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50677,7 +50677,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51295,7 +51295,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51707,7 +51707,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51994,7 +51994,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ245">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR245">
         <v>1.49</v>
@@ -52119,7 +52119,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52609,7 +52609,7 @@
         <v>1.2</v>
       </c>
       <c r="AP248">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ248">
         <v>1.47</v>
@@ -52943,7 +52943,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53149,7 +53149,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53561,7 +53561,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53973,7 +53973,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54179,7 +54179,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -55209,7 +55209,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55415,7 +55415,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -56033,7 +56033,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -57475,7 +57475,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -57968,7 +57968,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ274">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR274">
         <v>1.29</v>
@@ -58505,7 +58505,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59613,7 +59613,7 @@
         <v>2.17</v>
       </c>
       <c r="AP282">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ282">
         <v>1.87</v>
@@ -59741,7 +59741,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59947,7 +59947,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60565,7 +60565,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61183,7 +61183,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61389,7 +61389,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -62500,7 +62500,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ296">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR296">
         <v>1.6</v>
@@ -63243,7 +63243,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63321,7 +63321,7 @@
         <v>1.38</v>
       </c>
       <c r="AP300">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ300">
         <v>1.4</v>
@@ -63449,7 +63449,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63655,7 +63655,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -65097,7 +65097,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65303,7 +65303,7 @@
         <v>281</v>
       </c>
       <c r="P310" t="s">
-        <v>402</v>
+        <v>298</v>
       </c>
       <c r="Q310">
         <v>2.31</v>
@@ -69122,13 +69122,13 @@
         <v>7</v>
       </c>
       <c r="BA328">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB328">
         <v>4</v>
       </c>
       <c r="BC328">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD328">
         <v>1.81</v>
@@ -69580,6 +69580,212 @@
       </c>
       <c r="BP330">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="331" spans="1:68">
+      <c r="A331" s="1">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>7728517</v>
+      </c>
+      <c r="C331" t="s">
+        <v>68</v>
+      </c>
+      <c r="D331" t="s">
+        <v>69</v>
+      </c>
+      <c r="E331" s="2">
+        <v>45726.6875</v>
+      </c>
+      <c r="F331">
+        <v>30</v>
+      </c>
+      <c r="G331" t="s">
+        <v>78</v>
+      </c>
+      <c r="H331" t="s">
+        <v>85</v>
+      </c>
+      <c r="I331">
+        <v>1</v>
+      </c>
+      <c r="J331">
+        <v>0</v>
+      </c>
+      <c r="K331">
+        <v>1</v>
+      </c>
+      <c r="L331">
+        <v>1</v>
+      </c>
+      <c r="M331">
+        <v>0</v>
+      </c>
+      <c r="N331">
+        <v>1</v>
+      </c>
+      <c r="O331" t="s">
+        <v>298</v>
+      </c>
+      <c r="P331" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q331">
+        <v>3</v>
+      </c>
+      <c r="R331">
+        <v>1.95</v>
+      </c>
+      <c r="S331">
+        <v>4.33</v>
+      </c>
+      <c r="T331">
+        <v>1.53</v>
+      </c>
+      <c r="U331">
+        <v>2.38</v>
+      </c>
+      <c r="V331">
+        <v>3.75</v>
+      </c>
+      <c r="W331">
+        <v>1.25</v>
+      </c>
+      <c r="X331">
+        <v>11</v>
+      </c>
+      <c r="Y331">
+        <v>1.05</v>
+      </c>
+      <c r="Z331">
+        <v>2.35</v>
+      </c>
+      <c r="AA331">
+        <v>3.28</v>
+      </c>
+      <c r="AB331">
+        <v>3.28</v>
+      </c>
+      <c r="AC331">
+        <v>1.1</v>
+      </c>
+      <c r="AD331">
+        <v>6.5</v>
+      </c>
+      <c r="AE331">
+        <v>1.5</v>
+      </c>
+      <c r="AF331">
+        <v>2.4</v>
+      </c>
+      <c r="AG331">
+        <v>2.2</v>
+      </c>
+      <c r="AH331">
+        <v>1.55</v>
+      </c>
+      <c r="AI331">
+        <v>2.1</v>
+      </c>
+      <c r="AJ331">
+        <v>1.67</v>
+      </c>
+      <c r="AK331">
+        <v>1.3</v>
+      </c>
+      <c r="AL331">
+        <v>1.3</v>
+      </c>
+      <c r="AM331">
+        <v>1.62</v>
+      </c>
+      <c r="AN331">
+        <v>1.5</v>
+      </c>
+      <c r="AO331">
+        <v>0.93</v>
+      </c>
+      <c r="AP331">
+        <v>1.6</v>
+      </c>
+      <c r="AQ331">
+        <v>0.87</v>
+      </c>
+      <c r="AR331">
+        <v>1.4</v>
+      </c>
+      <c r="AS331">
+        <v>1.25</v>
+      </c>
+      <c r="AT331">
+        <v>2.65</v>
+      </c>
+      <c r="AU331">
+        <v>4</v>
+      </c>
+      <c r="AV331">
+        <v>5</v>
+      </c>
+      <c r="AW331">
+        <v>7</v>
+      </c>
+      <c r="AX331">
+        <v>11</v>
+      </c>
+      <c r="AY331">
+        <v>12</v>
+      </c>
+      <c r="AZ331">
+        <v>21</v>
+      </c>
+      <c r="BA331">
+        <v>3</v>
+      </c>
+      <c r="BB331">
+        <v>7</v>
+      </c>
+      <c r="BC331">
+        <v>10</v>
+      </c>
+      <c r="BD331">
+        <v>1.7</v>
+      </c>
+      <c r="BE331">
+        <v>6.5</v>
+      </c>
+      <c r="BF331">
+        <v>2.4</v>
+      </c>
+      <c r="BG331">
+        <v>1.44</v>
+      </c>
+      <c r="BH331">
+        <v>2.5</v>
+      </c>
+      <c r="BI331">
+        <v>1.75</v>
+      </c>
+      <c r="BJ331">
+        <v>1.92</v>
+      </c>
+      <c r="BK331">
+        <v>2.2</v>
+      </c>
+      <c r="BL331">
+        <v>1.56</v>
+      </c>
+      <c r="BM331">
+        <v>2.9</v>
+      </c>
+      <c r="BN331">
+        <v>1.34</v>
+      </c>
+      <c r="BO331">
+        <v>3.9</v>
+      </c>
+      <c r="BP331">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="411">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -913,6 +913,15 @@
     <t>['1']</t>
   </si>
   <si>
+    <t>['3', '20']</t>
+  </si>
+  <si>
+    <t>['6', '16', '45+5', '53']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1599,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP331"/>
+  <dimension ref="A1:BP337"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1855,7 +1864,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2267,7 +2276,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2348,7 +2357,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ4">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2757,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3091,7 +3100,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3297,7 +3306,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4121,7 +4130,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4202,7 +4211,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ13">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR13">
         <v>1.32</v>
@@ -4817,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ16">
         <v>1.36</v>
@@ -5357,7 +5366,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5641,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ20">
         <v>1.07</v>
@@ -5975,7 +5984,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6053,10 +6062,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ22">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6181,7 +6190,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6259,10 +6268,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6387,7 +6396,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6593,7 +6602,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6671,7 +6680,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ25">
         <v>1.87</v>
@@ -6799,7 +6808,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7005,7 +7014,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7289,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7417,7 +7426,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7910,7 +7919,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR31">
         <v>0.48</v>
@@ -8035,7 +8044,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8241,7 +8250,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8653,7 +8662,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9146,7 +9155,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR37">
         <v>1.35</v>
@@ -9555,10 +9564,10 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR39">
         <v>1.32</v>
@@ -9761,7 +9770,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ40">
         <v>1.07</v>
@@ -9967,7 +9976,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ41">
         <v>1.53</v>
@@ -10507,7 +10516,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10791,10 +10800,10 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ45">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR45">
         <v>0.96</v>
@@ -10997,7 +11006,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ46">
         <v>1.47</v>
@@ -11125,7 +11134,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12233,7 +12242,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ52">
         <v>0.44</v>
@@ -12442,7 +12451,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR53">
         <v>1.46</v>
@@ -12773,7 +12782,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12979,7 +12988,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13057,7 +13066,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ56">
         <v>1.27</v>
@@ -13185,7 +13194,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13266,7 +13275,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -13391,7 +13400,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13469,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ58">
         <v>0.87</v>
@@ -13803,7 +13812,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13884,7 +13893,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -14421,7 +14430,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14499,7 +14508,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ63">
         <v>1.33</v>
@@ -15039,7 +15048,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15117,10 +15126,10 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ66">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR66">
         <v>1.93</v>
@@ -15451,7 +15460,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15529,7 +15538,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ68">
         <v>1.47</v>
@@ -15657,7 +15666,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16150,7 +16159,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ71">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR71">
         <v>1.44</v>
@@ -16275,7 +16284,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16481,7 +16490,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16687,7 +16696,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17177,7 +17186,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ76">
         <v>0.87</v>
@@ -17383,10 +17392,10 @@
         <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ77">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR77">
         <v>1.33</v>
@@ -17511,7 +17520,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17717,7 +17726,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18001,7 +18010,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ80">
         <v>1.07</v>
@@ -18129,7 +18138,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18335,7 +18344,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18541,7 +18550,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18825,10 +18834,10 @@
         <v>2.33</v>
       </c>
       <c r="AP84">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR84">
         <v>1.79</v>
@@ -19240,7 +19249,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19365,7 +19374,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19777,7 +19786,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19855,7 +19864,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ89">
         <v>1.13</v>
@@ -19983,7 +19992,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20064,7 +20073,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ90">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR90">
         <v>1.45</v>
@@ -20267,7 +20276,7 @@
         <v>0.33</v>
       </c>
       <c r="AP91">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ91">
         <v>0.87</v>
@@ -20395,7 +20404,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20476,7 +20485,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR92">
         <v>1.42</v>
@@ -20807,7 +20816,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -21013,7 +21022,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21091,7 +21100,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ95">
         <v>1.38</v>
@@ -22043,7 +22052,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22327,7 +22336,7 @@
         <v>1.2</v>
       </c>
       <c r="AP101">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ101">
         <v>0.44</v>
@@ -23360,7 +23369,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ106">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR106">
         <v>1.12</v>
@@ -23485,7 +23494,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23769,7 +23778,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ108">
         <v>1.38</v>
@@ -24103,7 +24112,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24387,10 +24396,10 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR111">
         <v>1.54</v>
@@ -24515,7 +24524,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24593,7 +24602,7 @@
         <v>1.25</v>
       </c>
       <c r="AP112">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ112">
         <v>1.07</v>
@@ -24721,7 +24730,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25133,7 +25142,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25214,7 +25223,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR115">
         <v>1.49</v>
@@ -25623,7 +25632,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ117">
         <v>1.07</v>
@@ -25829,7 +25838,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ118">
         <v>0.87</v>
@@ -25957,7 +25966,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26450,7 +26459,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ121">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR121">
         <v>1.32</v>
@@ -26575,7 +26584,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26987,7 +26996,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27271,7 +27280,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ125">
         <v>1.07</v>
@@ -27399,7 +27408,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27686,7 +27695,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ127">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR127">
         <v>1.1</v>
@@ -27811,7 +27820,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28098,7 +28107,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ129">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -28223,7 +28232,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28301,7 +28310,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28429,7 +28438,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28635,7 +28644,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28919,7 +28928,7 @@
         <v>0.2</v>
       </c>
       <c r="AP133">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ133">
         <v>0.2</v>
@@ -29047,7 +29056,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29253,7 +29262,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29331,7 +29340,7 @@
         <v>0.83</v>
       </c>
       <c r="AP135">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ135">
         <v>1.47</v>
@@ -29871,7 +29880,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30155,10 +30164,10 @@
         <v>1.17</v>
       </c>
       <c r="AP139">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ139">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR139">
         <v>1.66</v>
@@ -30489,7 +30498,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30695,7 +30704,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30901,7 +30910,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30982,7 +30991,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ143">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR143">
         <v>1.11</v>
@@ -31107,7 +31116,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31519,7 +31528,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31597,7 +31606,7 @@
         <v>2</v>
       </c>
       <c r="AP146">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ146">
         <v>1.27</v>
@@ -31931,7 +31940,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32009,7 +32018,7 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ148">
         <v>1.87</v>
@@ -32215,7 +32224,7 @@
         <v>1</v>
       </c>
       <c r="AP149">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ149">
         <v>1.4</v>
@@ -32424,7 +32433,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ150">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR150">
         <v>1.6</v>
@@ -32961,7 +32970,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33454,7 +33463,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ155">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR155">
         <v>1.59</v>
@@ -33579,7 +33588,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34069,7 +34078,7 @@
         <v>0.33</v>
       </c>
       <c r="AP158">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ158">
         <v>0.2</v>
@@ -34275,7 +34284,7 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ159">
         <v>1.47</v>
@@ -34481,7 +34490,7 @@
         <v>1.17</v>
       </c>
       <c r="AP160">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ160">
         <v>1.38</v>
@@ -34690,7 +34699,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ161">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR161">
         <v>1.62</v>
@@ -35099,7 +35108,7 @@
         <v>1.43</v>
       </c>
       <c r="AP163">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ163">
         <v>1.53</v>
@@ -35227,7 +35236,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35305,7 +35314,7 @@
         <v>1.38</v>
       </c>
       <c r="AP164">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ164">
         <v>1.38</v>
@@ -35720,7 +35729,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ166">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR166">
         <v>1.42</v>
@@ -35845,7 +35854,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35923,10 +35932,10 @@
         <v>1.75</v>
       </c>
       <c r="AP167">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ167">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR167">
         <v>1.65</v>
@@ -36335,7 +36344,7 @@
         <v>0.29</v>
       </c>
       <c r="AP169">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ169">
         <v>0.2</v>
@@ -36875,7 +36884,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37365,7 +37374,7 @@
         <v>0.14</v>
       </c>
       <c r="AP174">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ174">
         <v>1.13</v>
@@ -37493,7 +37502,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37574,7 +37583,7 @@
         <v>2</v>
       </c>
       <c r="AQ175">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR175">
         <v>1.58</v>
@@ -37905,7 +37914,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -37983,7 +37992,7 @@
         <v>0.88</v>
       </c>
       <c r="AP177">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ177">
         <v>1.38</v>
@@ -38317,7 +38326,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38395,7 +38404,7 @@
         <v>2</v>
       </c>
       <c r="AP179">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ179">
         <v>1.36</v>
@@ -38523,7 +38532,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39222,7 +39231,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ183">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR183">
         <v>1.63</v>
@@ -39347,7 +39356,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39428,7 +39437,7 @@
         <v>2</v>
       </c>
       <c r="AQ184">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR184">
         <v>1.69</v>
@@ -40171,7 +40180,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40789,7 +40798,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40870,7 +40879,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ191">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR191">
         <v>1.48</v>
@@ -40995,7 +41004,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41076,7 +41085,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ192">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR192">
         <v>1.15</v>
@@ -41201,7 +41210,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41279,7 +41288,7 @@
         <v>0.89</v>
       </c>
       <c r="AP193">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ193">
         <v>1.4</v>
@@ -41407,7 +41416,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41691,7 +41700,7 @@
         <v>1.75</v>
       </c>
       <c r="AP195">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ195">
         <v>1.27</v>
@@ -42103,7 +42112,7 @@
         <v>0.25</v>
       </c>
       <c r="AP197">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ197">
         <v>0.2</v>
@@ -42309,7 +42318,7 @@
         <v>1.25</v>
       </c>
       <c r="AP198">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42515,7 +42524,7 @@
         <v>1.38</v>
       </c>
       <c r="AP199">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ199">
         <v>1.07</v>
@@ -42643,7 +42652,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43055,7 +43064,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43261,7 +43270,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43342,7 +43351,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ203">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR203">
         <v>1.49</v>
@@ -43751,7 +43760,7 @@
         <v>1.75</v>
       </c>
       <c r="AP205">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ205">
         <v>1.36</v>
@@ -43879,7 +43888,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44166,7 +44175,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ207">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR207">
         <v>1.45</v>
@@ -44781,7 +44790,7 @@
         <v>1.22</v>
       </c>
       <c r="AP210">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ210">
         <v>1.53</v>
@@ -44909,7 +44918,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44987,10 +44996,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP211">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ211">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR211">
         <v>1.69</v>
@@ -45115,7 +45124,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45321,7 +45330,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45399,7 +45408,7 @@
         <v>1.5</v>
       </c>
       <c r="AP213">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ213">
         <v>1.38</v>
@@ -45527,7 +45536,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45939,7 +45948,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46020,7 +46029,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ216">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR216">
         <v>1.46</v>
@@ -46841,7 +46850,7 @@
         <v>1.1</v>
       </c>
       <c r="AP220">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ220">
         <v>0.87</v>
@@ -47175,7 +47184,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47253,7 +47262,7 @@
         <v>0.2</v>
       </c>
       <c r="AP222">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ222">
         <v>1.13</v>
@@ -47587,7 +47596,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47668,7 +47677,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ224">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR224">
         <v>1.5</v>
@@ -47999,7 +48008,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48283,7 +48292,7 @@
         <v>1</v>
       </c>
       <c r="AP227">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ227">
         <v>1.33</v>
@@ -48617,7 +48626,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48823,7 +48832,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49029,7 +49038,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49316,7 +49325,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ232">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR232">
         <v>1.73</v>
@@ -49519,7 +49528,7 @@
         <v>0.55</v>
       </c>
       <c r="AP233">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ233">
         <v>0.44</v>
@@ -49853,7 +49862,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -49931,7 +49940,7 @@
         <v>2.2</v>
       </c>
       <c r="AP235">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ235">
         <v>1.87</v>
@@ -50549,7 +50558,7 @@
         <v>1.1</v>
       </c>
       <c r="AP238">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ238">
         <v>1</v>
@@ -50677,7 +50686,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50755,7 +50764,7 @@
         <v>1.64</v>
       </c>
       <c r="AP239">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ239">
         <v>1.38</v>
@@ -51170,7 +51179,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ241">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR241">
         <v>1.63</v>
@@ -51295,7 +51304,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51376,7 +51385,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ242">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR242">
         <v>1.37</v>
@@ -51579,7 +51588,7 @@
         <v>1.27</v>
       </c>
       <c r="AP243">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ243">
         <v>1.4</v>
@@ -51707,7 +51716,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52119,7 +52128,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52943,7 +52952,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53149,7 +53158,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53433,7 +53442,7 @@
         <v>1.27</v>
       </c>
       <c r="AP252">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ252">
         <v>1.38</v>
@@ -53561,7 +53570,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53642,7 +53651,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ253">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR253">
         <v>1.15</v>
@@ -53848,7 +53857,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ254">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR254">
         <v>1.63</v>
@@ -53973,7 +53982,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54051,7 +54060,7 @@
         <v>2.09</v>
       </c>
       <c r="AP255">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ255">
         <v>1.87</v>
@@ -54179,7 +54188,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -55081,7 +55090,7 @@
         <v>1.36</v>
       </c>
       <c r="AP260">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ260">
         <v>1.27</v>
@@ -55209,7 +55218,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55287,7 +55296,7 @@
         <v>1.75</v>
       </c>
       <c r="AP261">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ261">
         <v>1.38</v>
@@ -55415,7 +55424,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55496,7 +55505,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ262">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR262">
         <v>1.34</v>
@@ -56033,7 +56042,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56526,7 +56535,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ267">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR267">
         <v>1.55</v>
@@ -56729,7 +56738,7 @@
         <v>1.42</v>
       </c>
       <c r="AP268">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ268">
         <v>1.4</v>
@@ -56938,7 +56947,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ269">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR269">
         <v>1.57</v>
@@ -57475,7 +57484,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -57553,7 +57562,7 @@
         <v>0.67</v>
       </c>
       <c r="AP272">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ272">
         <v>1.13</v>
@@ -58377,10 +58386,10 @@
         <v>1.46</v>
       </c>
       <c r="AP276">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ276">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR276">
         <v>1.54</v>
@@ -58505,7 +58514,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58583,7 +58592,7 @@
         <v>1.25</v>
       </c>
       <c r="AP277">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ277">
         <v>1.27</v>
@@ -59204,7 +59213,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ280">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR280">
         <v>1.52</v>
@@ -59741,7 +59750,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59819,7 +59828,7 @@
         <v>1.38</v>
       </c>
       <c r="AP283">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ283">
         <v>1.38</v>
@@ -59947,7 +59956,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60437,7 +60446,7 @@
         <v>0.75</v>
       </c>
       <c r="AP286">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ286">
         <v>1.07</v>
@@ -60565,7 +60574,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -60852,7 +60861,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ288">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR288">
         <v>1.7</v>
@@ -61055,10 +61064,10 @@
         <v>0.85</v>
       </c>
       <c r="AP289">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ289">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR289">
         <v>1.17</v>
@@ -61183,7 +61192,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61389,7 +61398,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -62294,7 +62303,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ295">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR295">
         <v>1.6</v>
@@ -62497,7 +62506,7 @@
         <v>1</v>
       </c>
       <c r="AP296">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ296">
         <v>0.87</v>
@@ -62703,7 +62712,7 @@
         <v>1.17</v>
       </c>
       <c r="AP297">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ297">
         <v>1.07</v>
@@ -63115,7 +63124,7 @@
         <v>1</v>
       </c>
       <c r="AP299">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ299">
         <v>1.13</v>
@@ -63243,7 +63252,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63449,7 +63458,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63655,7 +63664,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -63736,7 +63745,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ302">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR302">
         <v>1.7</v>
@@ -64763,7 +64772,7 @@
         <v>0.77</v>
       </c>
       <c r="AP307">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ307">
         <v>1.07</v>
@@ -65097,7 +65106,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65175,10 +65184,10 @@
         <v>0.64</v>
       </c>
       <c r="AP309">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AQ309">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR309">
         <v>1.18</v>
@@ -65590,7 +65599,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ311">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR311">
         <v>1.67</v>
@@ -65921,7 +65930,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -65999,10 +66008,10 @@
         <v>1</v>
       </c>
       <c r="AP313">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ313">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR313">
         <v>1.7</v>
@@ -66205,7 +66214,7 @@
         <v>1.46</v>
       </c>
       <c r="AP314">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ314">
         <v>1.36</v>
@@ -66333,7 +66342,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66411,7 +66420,7 @@
         <v>1.36</v>
       </c>
       <c r="AP315">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ315">
         <v>1.47</v>
@@ -66539,7 +66548,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -66823,7 +66832,7 @@
         <v>1.31</v>
       </c>
       <c r="AP317">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ317">
         <v>1.33</v>
@@ -67441,10 +67450,10 @@
         <v>0.86</v>
       </c>
       <c r="AP320">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AQ320">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR320">
         <v>1.19</v>
@@ -68599,7 +68608,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -69011,7 +69020,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -69786,6 +69795,1242 @@
       </c>
       <c r="BP331">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="332" spans="1:68">
+      <c r="A332" s="1">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>7728537</v>
+      </c>
+      <c r="C332" t="s">
+        <v>68</v>
+      </c>
+      <c r="D332" t="s">
+        <v>69</v>
+      </c>
+      <c r="E332" s="2">
+        <v>45730.6875</v>
+      </c>
+      <c r="F332">
+        <v>31</v>
+      </c>
+      <c r="G332" t="s">
+        <v>89</v>
+      </c>
+      <c r="H332" t="s">
+        <v>79</v>
+      </c>
+      <c r="I332">
+        <v>0</v>
+      </c>
+      <c r="J332">
+        <v>1</v>
+      </c>
+      <c r="K332">
+        <v>1</v>
+      </c>
+      <c r="L332">
+        <v>1</v>
+      </c>
+      <c r="M332">
+        <v>1</v>
+      </c>
+      <c r="N332">
+        <v>2</v>
+      </c>
+      <c r="O332" t="s">
+        <v>137</v>
+      </c>
+      <c r="P332" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q332">
+        <v>2.95</v>
+      </c>
+      <c r="R332">
+        <v>1.9</v>
+      </c>
+      <c r="S332">
+        <v>3.9</v>
+      </c>
+      <c r="T332">
+        <v>1.53</v>
+      </c>
+      <c r="U332">
+        <v>2.3</v>
+      </c>
+      <c r="V332">
+        <v>3.5</v>
+      </c>
+      <c r="W332">
+        <v>1.26</v>
+      </c>
+      <c r="X332">
+        <v>10</v>
+      </c>
+      <c r="Y332">
+        <v>1.04</v>
+      </c>
+      <c r="Z332">
+        <v>2.26</v>
+      </c>
+      <c r="AA332">
+        <v>3.07</v>
+      </c>
+      <c r="AB332">
+        <v>3.75</v>
+      </c>
+      <c r="AC332">
+        <v>1.11</v>
+      </c>
+      <c r="AD332">
+        <v>6.25</v>
+      </c>
+      <c r="AE332">
+        <v>1.48</v>
+      </c>
+      <c r="AF332">
+        <v>2.37</v>
+      </c>
+      <c r="AG332">
+        <v>2.62</v>
+      </c>
+      <c r="AH332">
+        <v>1.43</v>
+      </c>
+      <c r="AI332">
+        <v>2.15</v>
+      </c>
+      <c r="AJ332">
+        <v>1.62</v>
+      </c>
+      <c r="AK332">
+        <v>1.32</v>
+      </c>
+      <c r="AL332">
+        <v>1.35</v>
+      </c>
+      <c r="AM332">
+        <v>1.6</v>
+      </c>
+      <c r="AN332">
+        <v>1.93</v>
+      </c>
+      <c r="AO332">
+        <v>1.07</v>
+      </c>
+      <c r="AP332">
+        <v>1.88</v>
+      </c>
+      <c r="AQ332">
+        <v>1.07</v>
+      </c>
+      <c r="AR332">
+        <v>1.6</v>
+      </c>
+      <c r="AS332">
+        <v>1.26</v>
+      </c>
+      <c r="AT332">
+        <v>2.86</v>
+      </c>
+      <c r="AU332">
+        <v>2</v>
+      </c>
+      <c r="AV332">
+        <v>6</v>
+      </c>
+      <c r="AW332">
+        <v>13</v>
+      </c>
+      <c r="AX332">
+        <v>10</v>
+      </c>
+      <c r="AY332">
+        <v>17</v>
+      </c>
+      <c r="AZ332">
+        <v>18</v>
+      </c>
+      <c r="BA332">
+        <v>4</v>
+      </c>
+      <c r="BB332">
+        <v>3</v>
+      </c>
+      <c r="BC332">
+        <v>7</v>
+      </c>
+      <c r="BD332">
+        <v>1.76</v>
+      </c>
+      <c r="BE332">
+        <v>6.25</v>
+      </c>
+      <c r="BF332">
+        <v>2.3</v>
+      </c>
+      <c r="BG332">
+        <v>1.56</v>
+      </c>
+      <c r="BH332">
+        <v>2.2</v>
+      </c>
+      <c r="BI332">
+        <v>1.95</v>
+      </c>
+      <c r="BJ332">
+        <v>1.73</v>
+      </c>
+      <c r="BK332">
+        <v>2.36</v>
+      </c>
+      <c r="BL332">
+        <v>1.55</v>
+      </c>
+      <c r="BM332">
+        <v>3.3</v>
+      </c>
+      <c r="BN332">
+        <v>1.27</v>
+      </c>
+      <c r="BO332">
+        <v>4.6</v>
+      </c>
+      <c r="BP332">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="333" spans="1:68">
+      <c r="A333" s="1">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>7728536</v>
+      </c>
+      <c r="C333" t="s">
+        <v>68</v>
+      </c>
+      <c r="D333" t="s">
+        <v>69</v>
+      </c>
+      <c r="E333" s="2">
+        <v>45731.41666666666</v>
+      </c>
+      <c r="F333">
+        <v>31</v>
+      </c>
+      <c r="G333" t="s">
+        <v>74</v>
+      </c>
+      <c r="H333" t="s">
+        <v>73</v>
+      </c>
+      <c r="I333">
+        <v>0</v>
+      </c>
+      <c r="J333">
+        <v>0</v>
+      </c>
+      <c r="K333">
+        <v>0</v>
+      </c>
+      <c r="L333">
+        <v>0</v>
+      </c>
+      <c r="M333">
+        <v>0</v>
+      </c>
+      <c r="N333">
+        <v>0</v>
+      </c>
+      <c r="O333" t="s">
+        <v>94</v>
+      </c>
+      <c r="P333" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q333">
+        <v>4</v>
+      </c>
+      <c r="R333">
+        <v>1.83</v>
+      </c>
+      <c r="S333">
+        <v>3.4</v>
+      </c>
+      <c r="T333">
+        <v>1.67</v>
+      </c>
+      <c r="U333">
+        <v>2.1</v>
+      </c>
+      <c r="V333">
+        <v>4.33</v>
+      </c>
+      <c r="W333">
+        <v>1.2</v>
+      </c>
+      <c r="X333">
+        <v>15</v>
+      </c>
+      <c r="Y333">
+        <v>1.03</v>
+      </c>
+      <c r="Z333">
+        <v>3.13</v>
+      </c>
+      <c r="AA333">
+        <v>2.96</v>
+      </c>
+      <c r="AB333">
+        <v>2.65</v>
+      </c>
+      <c r="AC333">
+        <v>1.13</v>
+      </c>
+      <c r="AD333">
+        <v>5.75</v>
+      </c>
+      <c r="AE333">
+        <v>1.55</v>
+      </c>
+      <c r="AF333">
+        <v>2.2</v>
+      </c>
+      <c r="AG333">
+        <v>2.73</v>
+      </c>
+      <c r="AH333">
+        <v>1.4</v>
+      </c>
+      <c r="AI333">
+        <v>2.25</v>
+      </c>
+      <c r="AJ333">
+        <v>1.57</v>
+      </c>
+      <c r="AK333">
+        <v>1.58</v>
+      </c>
+      <c r="AL333">
+        <v>1.38</v>
+      </c>
+      <c r="AM333">
+        <v>1.29</v>
+      </c>
+      <c r="AN333">
+        <v>0.6</v>
+      </c>
+      <c r="AO333">
+        <v>0.8</v>
+      </c>
+      <c r="AP333">
+        <v>0.63</v>
+      </c>
+      <c r="AQ333">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR333">
+        <v>1.19</v>
+      </c>
+      <c r="AS333">
+        <v>1.26</v>
+      </c>
+      <c r="AT333">
+        <v>2.45</v>
+      </c>
+      <c r="AU333">
+        <v>2</v>
+      </c>
+      <c r="AV333">
+        <v>5</v>
+      </c>
+      <c r="AW333">
+        <v>5</v>
+      </c>
+      <c r="AX333">
+        <v>10</v>
+      </c>
+      <c r="AY333">
+        <v>8</v>
+      </c>
+      <c r="AZ333">
+        <v>15</v>
+      </c>
+      <c r="BA333">
+        <v>4</v>
+      </c>
+      <c r="BB333">
+        <v>3</v>
+      </c>
+      <c r="BC333">
+        <v>7</v>
+      </c>
+      <c r="BD333">
+        <v>2.19</v>
+      </c>
+      <c r="BE333">
+        <v>6.3</v>
+      </c>
+      <c r="BF333">
+        <v>2.09</v>
+      </c>
+      <c r="BG333">
+        <v>1.3</v>
+      </c>
+      <c r="BH333">
+        <v>2.97</v>
+      </c>
+      <c r="BI333">
+        <v>1.57</v>
+      </c>
+      <c r="BJ333">
+        <v>2.19</v>
+      </c>
+      <c r="BK333">
+        <v>2</v>
+      </c>
+      <c r="BL333">
+        <v>1.72</v>
+      </c>
+      <c r="BM333">
+        <v>2.6</v>
+      </c>
+      <c r="BN333">
+        <v>1.41</v>
+      </c>
+      <c r="BO333">
+        <v>3.58</v>
+      </c>
+      <c r="BP333">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="334" spans="1:68">
+      <c r="A334" s="1">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>7728527</v>
+      </c>
+      <c r="C334" t="s">
+        <v>68</v>
+      </c>
+      <c r="D334" t="s">
+        <v>69</v>
+      </c>
+      <c r="E334" s="2">
+        <v>45731.51041666666</v>
+      </c>
+      <c r="F334">
+        <v>31</v>
+      </c>
+      <c r="G334" t="s">
+        <v>85</v>
+      </c>
+      <c r="H334" t="s">
+        <v>83</v>
+      </c>
+      <c r="I334">
+        <v>2</v>
+      </c>
+      <c r="J334">
+        <v>0</v>
+      </c>
+      <c r="K334">
+        <v>2</v>
+      </c>
+      <c r="L334">
+        <v>2</v>
+      </c>
+      <c r="M334">
+        <v>0</v>
+      </c>
+      <c r="N334">
+        <v>2</v>
+      </c>
+      <c r="O334" t="s">
+        <v>299</v>
+      </c>
+      <c r="P334" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q334">
+        <v>2.75</v>
+      </c>
+      <c r="R334">
+        <v>2.05</v>
+      </c>
+      <c r="S334">
+        <v>4.5</v>
+      </c>
+      <c r="T334">
+        <v>1.5</v>
+      </c>
+      <c r="U334">
+        <v>2.5</v>
+      </c>
+      <c r="V334">
+        <v>3.4</v>
+      </c>
+      <c r="W334">
+        <v>1.3</v>
+      </c>
+      <c r="X334">
+        <v>10</v>
+      </c>
+      <c r="Y334">
+        <v>1.06</v>
+      </c>
+      <c r="Z334">
+        <v>1.71</v>
+      </c>
+      <c r="AA334">
+        <v>3.99</v>
+      </c>
+      <c r="AB334">
+        <v>5</v>
+      </c>
+      <c r="AC334">
+        <v>1.07</v>
+      </c>
+      <c r="AD334">
+        <v>8</v>
+      </c>
+      <c r="AE334">
+        <v>1.4</v>
+      </c>
+      <c r="AF334">
+        <v>2.9</v>
+      </c>
+      <c r="AG334">
+        <v>1.87</v>
+      </c>
+      <c r="AH334">
+        <v>1.94</v>
+      </c>
+      <c r="AI334">
+        <v>2</v>
+      </c>
+      <c r="AJ334">
+        <v>1.73</v>
+      </c>
+      <c r="AK334">
+        <v>1.23</v>
+      </c>
+      <c r="AL334">
+        <v>1.32</v>
+      </c>
+      <c r="AM334">
+        <v>1.82</v>
+      </c>
+      <c r="AN334">
+        <v>1.6</v>
+      </c>
+      <c r="AO334">
+        <v>1</v>
+      </c>
+      <c r="AP334">
+        <v>1.69</v>
+      </c>
+      <c r="AQ334">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR334">
+        <v>1.53</v>
+      </c>
+      <c r="AS334">
+        <v>1.19</v>
+      </c>
+      <c r="AT334">
+        <v>2.72</v>
+      </c>
+      <c r="AU334">
+        <v>4</v>
+      </c>
+      <c r="AV334">
+        <v>6</v>
+      </c>
+      <c r="AW334">
+        <v>9</v>
+      </c>
+      <c r="AX334">
+        <v>15</v>
+      </c>
+      <c r="AY334">
+        <v>16</v>
+      </c>
+      <c r="AZ334">
+        <v>25</v>
+      </c>
+      <c r="BA334">
+        <v>3</v>
+      </c>
+      <c r="BB334">
+        <v>8</v>
+      </c>
+      <c r="BC334">
+        <v>11</v>
+      </c>
+      <c r="BD334">
+        <v>1.55</v>
+      </c>
+      <c r="BE334">
+        <v>6.9</v>
+      </c>
+      <c r="BF334">
+        <v>3.3</v>
+      </c>
+      <c r="BG334">
+        <v>1.27</v>
+      </c>
+      <c r="BH334">
+        <v>3.14</v>
+      </c>
+      <c r="BI334">
+        <v>1.53</v>
+      </c>
+      <c r="BJ334">
+        <v>2.28</v>
+      </c>
+      <c r="BK334">
+        <v>1.93</v>
+      </c>
+      <c r="BL334">
+        <v>1.78</v>
+      </c>
+      <c r="BM334">
+        <v>2.51</v>
+      </c>
+      <c r="BN334">
+        <v>1.44</v>
+      </c>
+      <c r="BO334">
+        <v>3.34</v>
+      </c>
+      <c r="BP334">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="335" spans="1:68">
+      <c r="A335" s="1">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>7728535</v>
+      </c>
+      <c r="C335" t="s">
+        <v>68</v>
+      </c>
+      <c r="D335" t="s">
+        <v>69</v>
+      </c>
+      <c r="E335" s="2">
+        <v>45731.51041666666</v>
+      </c>
+      <c r="F335">
+        <v>31</v>
+      </c>
+      <c r="G335" t="s">
+        <v>87</v>
+      </c>
+      <c r="H335" t="s">
+        <v>78</v>
+      </c>
+      <c r="I335">
+        <v>0</v>
+      </c>
+      <c r="J335">
+        <v>1</v>
+      </c>
+      <c r="K335">
+        <v>1</v>
+      </c>
+      <c r="L335">
+        <v>0</v>
+      </c>
+      <c r="M335">
+        <v>1</v>
+      </c>
+      <c r="N335">
+        <v>1</v>
+      </c>
+      <c r="O335" t="s">
+        <v>94</v>
+      </c>
+      <c r="P335" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q335">
+        <v>5.5</v>
+      </c>
+      <c r="R335">
+        <v>1.91</v>
+      </c>
+      <c r="S335">
+        <v>2.75</v>
+      </c>
+      <c r="T335">
+        <v>1.62</v>
+      </c>
+      <c r="U335">
+        <v>2.2</v>
+      </c>
+      <c r="V335">
+        <v>4</v>
+      </c>
+      <c r="W335">
+        <v>1.22</v>
+      </c>
+      <c r="X335">
+        <v>13</v>
+      </c>
+      <c r="Y335">
+        <v>1.04</v>
+      </c>
+      <c r="Z335">
+        <v>3.63</v>
+      </c>
+      <c r="AA335">
+        <v>3.41</v>
+      </c>
+      <c r="AB335">
+        <v>2.15</v>
+      </c>
+      <c r="AC335">
+        <v>1.11</v>
+      </c>
+      <c r="AD335">
+        <v>6.25</v>
+      </c>
+      <c r="AE335">
+        <v>1.5</v>
+      </c>
+      <c r="AF335">
+        <v>2.3</v>
+      </c>
+      <c r="AG335">
+        <v>2.26</v>
+      </c>
+      <c r="AH335">
+        <v>1.54</v>
+      </c>
+      <c r="AI335">
+        <v>2.38</v>
+      </c>
+      <c r="AJ335">
+        <v>1.53</v>
+      </c>
+      <c r="AK335">
+        <v>1.77</v>
+      </c>
+      <c r="AL335">
+        <v>1.3</v>
+      </c>
+      <c r="AM335">
+        <v>1.22</v>
+      </c>
+      <c r="AN335">
+        <v>0.57</v>
+      </c>
+      <c r="AO335">
+        <v>1</v>
+      </c>
+      <c r="AP335">
+        <v>0.53</v>
+      </c>
+      <c r="AQ335">
+        <v>1.13</v>
+      </c>
+      <c r="AR335">
+        <v>1.16</v>
+      </c>
+      <c r="AS335">
+        <v>1.23</v>
+      </c>
+      <c r="AT335">
+        <v>2.39</v>
+      </c>
+      <c r="AU335">
+        <v>4</v>
+      </c>
+      <c r="AV335">
+        <v>2</v>
+      </c>
+      <c r="AW335">
+        <v>5</v>
+      </c>
+      <c r="AX335">
+        <v>4</v>
+      </c>
+      <c r="AY335">
+        <v>11</v>
+      </c>
+      <c r="AZ335">
+        <v>7</v>
+      </c>
+      <c r="BA335">
+        <v>2</v>
+      </c>
+      <c r="BB335">
+        <v>2</v>
+      </c>
+      <c r="BC335">
+        <v>4</v>
+      </c>
+      <c r="BD335">
+        <v>2.65</v>
+      </c>
+      <c r="BE335">
+        <v>6.4</v>
+      </c>
+      <c r="BF335">
+        <v>1.58</v>
+      </c>
+      <c r="BG335">
+        <v>1.52</v>
+      </c>
+      <c r="BH335">
+        <v>2.3</v>
+      </c>
+      <c r="BI335">
+        <v>1.87</v>
+      </c>
+      <c r="BJ335">
+        <v>1.8</v>
+      </c>
+      <c r="BK335">
+        <v>2.4</v>
+      </c>
+      <c r="BL335">
+        <v>1.48</v>
+      </c>
+      <c r="BM335">
+        <v>3.15</v>
+      </c>
+      <c r="BN335">
+        <v>1.29</v>
+      </c>
+      <c r="BO335">
+        <v>4.3</v>
+      </c>
+      <c r="BP335">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="336" spans="1:68">
+      <c r="A336" s="1">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>7728528</v>
+      </c>
+      <c r="C336" t="s">
+        <v>68</v>
+      </c>
+      <c r="D336" t="s">
+        <v>69</v>
+      </c>
+      <c r="E336" s="2">
+        <v>45731.60416666666</v>
+      </c>
+      <c r="F336">
+        <v>31</v>
+      </c>
+      <c r="G336" t="s">
+        <v>90</v>
+      </c>
+      <c r="H336" t="s">
+        <v>91</v>
+      </c>
+      <c r="I336">
+        <v>3</v>
+      </c>
+      <c r="J336">
+        <v>1</v>
+      </c>
+      <c r="K336">
+        <v>4</v>
+      </c>
+      <c r="L336">
+        <v>4</v>
+      </c>
+      <c r="M336">
+        <v>1</v>
+      </c>
+      <c r="N336">
+        <v>5</v>
+      </c>
+      <c r="O336" t="s">
+        <v>300</v>
+      </c>
+      <c r="P336" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q336">
+        <v>2.2</v>
+      </c>
+      <c r="R336">
+        <v>2.3</v>
+      </c>
+      <c r="S336">
+        <v>5</v>
+      </c>
+      <c r="T336">
+        <v>1.33</v>
+      </c>
+      <c r="U336">
+        <v>3.25</v>
+      </c>
+      <c r="V336">
+        <v>2.63</v>
+      </c>
+      <c r="W336">
+        <v>1.44</v>
+      </c>
+      <c r="X336">
+        <v>7</v>
+      </c>
+      <c r="Y336">
+        <v>1.1</v>
+      </c>
+      <c r="Z336">
+        <v>1.69</v>
+      </c>
+      <c r="AA336">
+        <v>4.1</v>
+      </c>
+      <c r="AB336">
+        <v>5.1</v>
+      </c>
+      <c r="AC336">
+        <v>1.05</v>
+      </c>
+      <c r="AD336">
+        <v>9.5</v>
+      </c>
+      <c r="AE336">
+        <v>1.25</v>
+      </c>
+      <c r="AF336">
+        <v>3.8</v>
+      </c>
+      <c r="AG336">
+        <v>1.82</v>
+      </c>
+      <c r="AH336">
+        <v>2</v>
+      </c>
+      <c r="AI336">
+        <v>1.8</v>
+      </c>
+      <c r="AJ336">
+        <v>1.91</v>
+      </c>
+      <c r="AK336">
+        <v>1.17</v>
+      </c>
+      <c r="AL336">
+        <v>1.25</v>
+      </c>
+      <c r="AM336">
+        <v>2.15</v>
+      </c>
+      <c r="AN336">
+        <v>1.79</v>
+      </c>
+      <c r="AO336">
+        <v>1.33</v>
+      </c>
+      <c r="AP336">
+        <v>1.87</v>
+      </c>
+      <c r="AQ336">
+        <v>1.25</v>
+      </c>
+      <c r="AR336">
+        <v>1.73</v>
+      </c>
+      <c r="AS336">
+        <v>1.38</v>
+      </c>
+      <c r="AT336">
+        <v>3.11</v>
+      </c>
+      <c r="AU336">
+        <v>5</v>
+      </c>
+      <c r="AV336">
+        <v>3</v>
+      </c>
+      <c r="AW336">
+        <v>11</v>
+      </c>
+      <c r="AX336">
+        <v>6</v>
+      </c>
+      <c r="AY336">
+        <v>19</v>
+      </c>
+      <c r="AZ336">
+        <v>12</v>
+      </c>
+      <c r="BA336">
+        <v>8</v>
+      </c>
+      <c r="BB336">
+        <v>3</v>
+      </c>
+      <c r="BC336">
+        <v>11</v>
+      </c>
+      <c r="BD336">
+        <v>1.48</v>
+      </c>
+      <c r="BE336">
+        <v>9</v>
+      </c>
+      <c r="BF336">
+        <v>3.26</v>
+      </c>
+      <c r="BG336">
+        <v>1.24</v>
+      </c>
+      <c r="BH336">
+        <v>3.34</v>
+      </c>
+      <c r="BI336">
+        <v>1.47</v>
+      </c>
+      <c r="BJ336">
+        <v>2.42</v>
+      </c>
+      <c r="BK336">
+        <v>1.83</v>
+      </c>
+      <c r="BL336">
+        <v>1.87</v>
+      </c>
+      <c r="BM336">
+        <v>2.32</v>
+      </c>
+      <c r="BN336">
+        <v>1.51</v>
+      </c>
+      <c r="BO336">
+        <v>3.08</v>
+      </c>
+      <c r="BP336">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="337" spans="1:68">
+      <c r="A337" s="1">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>7728531</v>
+      </c>
+      <c r="C337" t="s">
+        <v>68</v>
+      </c>
+      <c r="D337" t="s">
+        <v>69</v>
+      </c>
+      <c r="E337" s="2">
+        <v>45731.70833333334</v>
+      </c>
+      <c r="F337">
+        <v>31</v>
+      </c>
+      <c r="G337" t="s">
+        <v>88</v>
+      </c>
+      <c r="H337" t="s">
+        <v>76</v>
+      </c>
+      <c r="I337">
+        <v>1</v>
+      </c>
+      <c r="J337">
+        <v>0</v>
+      </c>
+      <c r="K337">
+        <v>1</v>
+      </c>
+      <c r="L337">
+        <v>1</v>
+      </c>
+      <c r="M337">
+        <v>1</v>
+      </c>
+      <c r="N337">
+        <v>2</v>
+      </c>
+      <c r="O337" t="s">
+        <v>301</v>
+      </c>
+      <c r="P337" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q337">
+        <v>2.88</v>
+      </c>
+      <c r="R337">
+        <v>2.05</v>
+      </c>
+      <c r="S337">
+        <v>4</v>
+      </c>
+      <c r="T337">
+        <v>1.44</v>
+      </c>
+      <c r="U337">
+        <v>2.63</v>
+      </c>
+      <c r="V337">
+        <v>3.4</v>
+      </c>
+      <c r="W337">
+        <v>1.3</v>
+      </c>
+      <c r="X337">
+        <v>10</v>
+      </c>
+      <c r="Y337">
+        <v>1.06</v>
+      </c>
+      <c r="Z337">
+        <v>2.3</v>
+      </c>
+      <c r="AA337">
+        <v>3.28</v>
+      </c>
+      <c r="AB337">
+        <v>3.39</v>
+      </c>
+      <c r="AC337">
+        <v>1.08</v>
+      </c>
+      <c r="AD337">
+        <v>7.5</v>
+      </c>
+      <c r="AE337">
+        <v>1.4</v>
+      </c>
+      <c r="AF337">
+        <v>2.9</v>
+      </c>
+      <c r="AG337">
+        <v>2.05</v>
+      </c>
+      <c r="AH337">
+        <v>1.61</v>
+      </c>
+      <c r="AI337">
+        <v>1.83</v>
+      </c>
+      <c r="AJ337">
+        <v>1.83</v>
+      </c>
+      <c r="AK337">
+        <v>1.33</v>
+      </c>
+      <c r="AL337">
+        <v>1.3</v>
+      </c>
+      <c r="AM337">
+        <v>1.62</v>
+      </c>
+      <c r="AN337">
+        <v>1.79</v>
+      </c>
+      <c r="AO337">
+        <v>1</v>
+      </c>
+      <c r="AP337">
+        <v>1.73</v>
+      </c>
+      <c r="AQ337">
+        <v>1</v>
+      </c>
+      <c r="AR337">
+        <v>1.66</v>
+      </c>
+      <c r="AS337">
+        <v>1.19</v>
+      </c>
+      <c r="AT337">
+        <v>2.85</v>
+      </c>
+      <c r="AU337">
+        <v>4</v>
+      </c>
+      <c r="AV337">
+        <v>7</v>
+      </c>
+      <c r="AW337">
+        <v>12</v>
+      </c>
+      <c r="AX337">
+        <v>2</v>
+      </c>
+      <c r="AY337">
+        <v>23</v>
+      </c>
+      <c r="AZ337">
+        <v>10</v>
+      </c>
+      <c r="BA337">
+        <v>6</v>
+      </c>
+      <c r="BB337">
+        <v>1</v>
+      </c>
+      <c r="BC337">
+        <v>7</v>
+      </c>
+      <c r="BD337">
+        <v>1.63</v>
+      </c>
+      <c r="BE337">
+        <v>6.5</v>
+      </c>
+      <c r="BF337">
+        <v>2.55</v>
+      </c>
+      <c r="BG337">
+        <v>1.36</v>
+      </c>
+      <c r="BH337">
+        <v>2.8</v>
+      </c>
+      <c r="BI337">
+        <v>1.62</v>
+      </c>
+      <c r="BJ337">
+        <v>2.1</v>
+      </c>
+      <c r="BK337">
+        <v>2.02</v>
+      </c>
+      <c r="BL337">
+        <v>1.68</v>
+      </c>
+      <c r="BM337">
+        <v>2.55</v>
+      </c>
+      <c r="BN337">
+        <v>1.43</v>
+      </c>
+      <c r="BO337">
+        <v>3.4</v>
+      </c>
+      <c r="BP337">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="415">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -922,6 +922,12 @@
     <t>['45+2']</t>
   </si>
   <si>
+    <t>['63', '90+7']</t>
+  </si>
+  <si>
+    <t>['79', '85']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1247,6 +1253,12 @@
   </si>
   <si>
     <t>['83', '85']</t>
+  </si>
+  <si>
+    <t>['49', '61']</t>
+  </si>
+  <si>
+    <t>['54', '90+1']</t>
   </si>
 </sst>
 </file>
@@ -1608,7 +1620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP337"/>
+  <dimension ref="A1:BP341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1864,7 +1876,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2276,7 +2288,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2354,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4">
         <v>1.25</v>
@@ -3100,7 +3112,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3181,7 +3193,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ8">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3306,7 +3318,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3384,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9">
         <v>1.38</v>
@@ -4002,10 +4014,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ12">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4130,7 +4142,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4208,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13">
         <v>0.8100000000000001</v>
@@ -4414,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ14">
         <v>1.47</v>
@@ -4829,7 +4841,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ16">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR16">
         <v>1.33</v>
@@ -5366,7 +5378,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5984,7 +5996,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6190,7 +6202,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6396,7 +6408,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6602,7 +6614,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6808,7 +6820,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6886,10 +6898,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ26">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR26">
         <v>1.33</v>
@@ -7014,7 +7026,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7426,7 +7438,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -8044,7 +8056,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8122,7 +8134,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ32">
         <v>0.44</v>
@@ -8250,7 +8262,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8331,7 +8343,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ33">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR33">
         <v>0.95</v>
@@ -8662,7 +8674,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9152,7 +9164,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ37">
         <v>1.13</v>
@@ -9979,7 +9991,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ41">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR41">
         <v>1</v>
@@ -10182,7 +10194,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ42">
         <v>1.38</v>
@@ -10516,7 +10528,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11134,7 +11146,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11421,7 +11433,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ48">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR48">
         <v>1.67</v>
@@ -11830,7 +11842,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -12654,7 +12666,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ54">
         <v>0.87</v>
@@ -12782,7 +12794,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12863,7 +12875,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ55">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR55">
         <v>1.39</v>
@@ -12988,7 +13000,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13194,7 +13206,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13400,7 +13412,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13684,7 +13696,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ59">
         <v>1.4</v>
@@ -13812,7 +13824,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14099,7 +14111,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ61">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -14430,7 +14442,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -15048,7 +15060,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15332,7 +15344,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ67">
         <v>1.13</v>
@@ -15460,7 +15472,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15666,7 +15678,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15744,7 +15756,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69">
         <v>1.07</v>
@@ -16284,7 +16296,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16490,7 +16502,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16696,7 +16708,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16777,7 +16789,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ74">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR74">
         <v>1.54</v>
@@ -16983,7 +16995,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ75">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR75">
         <v>1.58</v>
@@ -17520,7 +17532,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17598,7 +17610,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ78">
         <v>0.44</v>
@@ -17726,7 +17738,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17804,7 +17816,7 @@
         <v>2.33</v>
       </c>
       <c r="AP79">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ79">
         <v>1.33</v>
@@ -18138,7 +18150,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18219,7 +18231,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ81">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR81">
         <v>1.07</v>
@@ -18344,7 +18356,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18550,7 +18562,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19374,7 +19386,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19452,7 +19464,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ87">
         <v>1.27</v>
@@ -19786,7 +19798,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19992,7 +20004,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20404,7 +20416,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20482,7 +20494,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ92">
         <v>0.9399999999999999</v>
@@ -20816,7 +20828,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20894,7 +20906,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ94">
         <v>0.87</v>
@@ -21022,7 +21034,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21306,10 +21318,10 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ96">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR96">
         <v>1.53</v>
@@ -22052,7 +22064,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22957,7 +22969,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ104">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR104">
         <v>1.71</v>
@@ -23163,7 +23175,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ105">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR105">
         <v>1.64</v>
@@ -23494,7 +23506,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23572,7 +23584,7 @@
         <v>3</v>
       </c>
       <c r="AP107">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ107">
         <v>1.87</v>
@@ -24112,7 +24124,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24524,7 +24536,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24730,7 +24742,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24811,7 +24823,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ113">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -25142,7 +25154,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25220,7 +25232,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ115">
         <v>1.25</v>
@@ -25426,7 +25438,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ116">
         <v>1.13</v>
@@ -25966,7 +25978,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26584,7 +26596,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26868,7 +26880,7 @@
         <v>1.17</v>
       </c>
       <c r="AP123">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ123">
         <v>1.4</v>
@@ -26996,7 +27008,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27408,7 +27420,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27820,7 +27832,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28232,7 +28244,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28438,7 +28450,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28516,7 +28528,7 @@
         <v>1.17</v>
       </c>
       <c r="AP131">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ131">
         <v>1.38</v>
@@ -28644,7 +28656,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28725,7 +28737,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ132">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR132">
         <v>1.78</v>
@@ -28931,7 +28943,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ133">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR133">
         <v>1.15</v>
@@ -29056,7 +29068,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29262,7 +29274,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29755,7 +29767,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ137">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR137">
         <v>1.67</v>
@@ -29880,7 +29892,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29958,7 +29970,7 @@
         <v>1.17</v>
       </c>
       <c r="AP138">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ138">
         <v>0.87</v>
@@ -30498,7 +30510,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30704,7 +30716,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30910,7 +30922,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30988,7 +31000,7 @@
         <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ143">
         <v>1.25</v>
@@ -31116,7 +31128,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31528,7 +31540,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31940,7 +31952,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32842,7 +32854,7 @@
         <v>1.14</v>
       </c>
       <c r="AP152">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ152">
         <v>0.87</v>
@@ -32970,7 +32982,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33460,7 +33472,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ155">
         <v>1.13</v>
@@ -33588,7 +33600,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33669,7 +33681,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ156">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR156">
         <v>1.44</v>
@@ -33872,7 +33884,7 @@
         <v>0.17</v>
       </c>
       <c r="AP157">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ157">
         <v>1.13</v>
@@ -34081,7 +34093,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ158">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR158">
         <v>1.68</v>
@@ -34902,7 +34914,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ162">
         <v>1.38</v>
@@ -35111,7 +35123,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ163">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR163">
         <v>1.14</v>
@@ -35236,7 +35248,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35854,7 +35866,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36347,7 +36359,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ169">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR169">
         <v>1.71</v>
@@ -36884,7 +36896,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -36962,7 +36974,7 @@
         <v>1.86</v>
       </c>
       <c r="AP172">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ172">
         <v>1.27</v>
@@ -37502,7 +37514,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37914,7 +37926,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38326,7 +38338,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38407,7 +38419,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ179">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR179">
         <v>1.71</v>
@@ -38532,7 +38544,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38610,7 +38622,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ180">
         <v>1.47</v>
@@ -38816,7 +38828,7 @@
         <v>1.14</v>
       </c>
       <c r="AP181">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ181">
         <v>1.07</v>
@@ -39356,7 +39368,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39640,7 +39652,7 @@
         <v>0.86</v>
       </c>
       <c r="AP185">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ185">
         <v>0.87</v>
@@ -40180,7 +40192,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40261,7 +40273,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ188">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR188">
         <v>1.17</v>
@@ -40798,7 +40810,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -41004,7 +41016,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41082,7 +41094,7 @@
         <v>0.63</v>
       </c>
       <c r="AP192">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ192">
         <v>0.8100000000000001</v>
@@ -41210,7 +41222,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41416,7 +41428,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42115,7 +42127,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ197">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR197">
         <v>1.63</v>
@@ -42652,7 +42664,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42936,7 +42948,7 @@
         <v>1.22</v>
       </c>
       <c r="AP201">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ201">
         <v>0.87</v>
@@ -43064,7 +43076,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43270,7 +43282,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43554,7 +43566,7 @@
         <v>1.13</v>
       </c>
       <c r="AP204">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ204">
         <v>1.07</v>
@@ -43763,7 +43775,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ205">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR205">
         <v>1.69</v>
@@ -43888,7 +43900,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44378,7 +44390,7 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ208">
         <v>1.38</v>
@@ -44793,7 +44805,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ210">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR210">
         <v>1.59</v>
@@ -44918,7 +44930,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45124,7 +45136,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45330,7 +45342,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45536,7 +45548,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45948,7 +45960,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46026,7 +46038,7 @@
         <v>0.78</v>
       </c>
       <c r="AP216">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ216">
         <v>1.13</v>
@@ -46644,10 +46656,10 @@
         <v>0.22</v>
       </c>
       <c r="AP219">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ219">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR219">
         <v>1.15</v>
@@ -47059,7 +47071,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ221">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR221">
         <v>1.48</v>
@@ -47184,7 +47196,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47596,7 +47608,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47883,7 +47895,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ225">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR225">
         <v>1.43</v>
@@ -48008,7 +48020,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48498,7 +48510,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ228">
         <v>1.07</v>
@@ -48626,7 +48638,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48832,7 +48844,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49038,7 +49050,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49119,7 +49131,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ231">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR231">
         <v>1.26</v>
@@ -49734,7 +49746,7 @@
         <v>1.4</v>
       </c>
       <c r="AP234">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ234">
         <v>1.07</v>
@@ -49862,7 +49874,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50686,7 +50698,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50970,10 +50982,10 @@
         <v>1.36</v>
       </c>
       <c r="AP240">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ240">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR240">
         <v>1.44</v>
@@ -51304,7 +51316,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51382,7 +51394,7 @@
         <v>0.5</v>
       </c>
       <c r="AP242">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ242">
         <v>0.8100000000000001</v>
@@ -51716,7 +51728,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51794,7 +51806,7 @@
         <v>1</v>
       </c>
       <c r="AP244">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ244">
         <v>1.33</v>
@@ -52128,7 +52140,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52415,7 +52427,7 @@
         <v>2</v>
       </c>
       <c r="AQ247">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR247">
         <v>1.54</v>
@@ -52824,7 +52836,7 @@
         <v>1</v>
       </c>
       <c r="AP249">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ249">
         <v>0.87</v>
@@ -52952,7 +52964,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53158,7 +53170,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53239,7 +53251,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ251">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR251">
         <v>1.68</v>
@@ -53570,7 +53582,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53982,7 +53994,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54188,7 +54200,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54269,7 +54281,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ256">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR256">
         <v>1.43</v>
@@ -54472,7 +54484,7 @@
         <v>0.58</v>
       </c>
       <c r="AP257">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ257">
         <v>0.44</v>
@@ -55218,7 +55230,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55424,7 +55436,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55708,7 +55720,7 @@
         <v>1.27</v>
       </c>
       <c r="AP263">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ263">
         <v>1.07</v>
@@ -56042,7 +56054,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56120,10 +56132,10 @@
         <v>1.36</v>
       </c>
       <c r="AP265">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ265">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR265">
         <v>1.45</v>
@@ -56944,7 +56956,7 @@
         <v>0.92</v>
       </c>
       <c r="AP269">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ269">
         <v>0.9399999999999999</v>
@@ -57484,7 +57496,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -58514,7 +58526,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59007,7 +59019,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ279">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR279">
         <v>1.34</v>
@@ -59419,7 +59431,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ281">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR281">
         <v>1.65</v>
@@ -59750,7 +59762,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59956,7 +59968,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60034,7 +60046,7 @@
         <v>0.54</v>
       </c>
       <c r="AP284">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ284">
         <v>0.44</v>
@@ -60574,7 +60586,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61192,7 +61204,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61270,7 +61282,7 @@
         <v>1.17</v>
       </c>
       <c r="AP290">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ290">
         <v>1.33</v>
@@ -61398,7 +61410,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61888,7 +61900,7 @@
         <v>1.46</v>
       </c>
       <c r="AP293">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ293">
         <v>1.47</v>
@@ -62094,10 +62106,10 @@
         <v>1.5</v>
       </c>
       <c r="AP294">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ294">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR294">
         <v>1.27</v>
@@ -62921,7 +62933,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ298">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR298">
         <v>1.37</v>
@@ -63252,7 +63264,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63458,7 +63470,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63664,7 +63676,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -64978,7 +64990,7 @@
         <v>1.38</v>
       </c>
       <c r="AP308">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ308">
         <v>1.27</v>
@@ -65106,7 +65118,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65390,7 +65402,7 @@
         <v>1</v>
       </c>
       <c r="AP310">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ310">
         <v>0.87</v>
@@ -65930,7 +65942,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66217,7 +66229,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ314">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR314">
         <v>1.64</v>
@@ -66342,7 +66354,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66548,7 +66560,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -66626,10 +66638,10 @@
         <v>1.43</v>
       </c>
       <c r="AP316">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ316">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR316">
         <v>1.53</v>
@@ -67038,7 +67050,7 @@
         <v>1.15</v>
       </c>
       <c r="AP318">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ318">
         <v>1.07</v>
@@ -67247,7 +67259,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ319">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AR319">
         <v>1.37</v>
@@ -68608,7 +68620,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -69020,7 +69032,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -71031,6 +71043,830 @@
       </c>
       <c r="BP337">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="338" spans="1:68">
+      <c r="A338" s="1">
+        <v>337</v>
+      </c>
+      <c r="B338">
+        <v>7728532</v>
+      </c>
+      <c r="C338" t="s">
+        <v>68</v>
+      </c>
+      <c r="D338" t="s">
+        <v>69</v>
+      </c>
+      <c r="E338" s="2">
+        <v>45732.41666666666</v>
+      </c>
+      <c r="F338">
+        <v>31</v>
+      </c>
+      <c r="G338" t="s">
+        <v>80</v>
+      </c>
+      <c r="H338" t="s">
+        <v>71</v>
+      </c>
+      <c r="I338">
+        <v>0</v>
+      </c>
+      <c r="J338">
+        <v>0</v>
+      </c>
+      <c r="K338">
+        <v>0</v>
+      </c>
+      <c r="L338">
+        <v>2</v>
+      </c>
+      <c r="M338">
+        <v>2</v>
+      </c>
+      <c r="N338">
+        <v>4</v>
+      </c>
+      <c r="O338" t="s">
+        <v>302</v>
+      </c>
+      <c r="P338" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q338">
+        <v>3.5</v>
+      </c>
+      <c r="R338">
+        <v>1.95</v>
+      </c>
+      <c r="S338">
+        <v>3.5</v>
+      </c>
+      <c r="T338">
+        <v>1.53</v>
+      </c>
+      <c r="U338">
+        <v>2.38</v>
+      </c>
+      <c r="V338">
+        <v>3.5</v>
+      </c>
+      <c r="W338">
+        <v>1.29</v>
+      </c>
+      <c r="X338">
+        <v>11</v>
+      </c>
+      <c r="Y338">
+        <v>1.05</v>
+      </c>
+      <c r="Z338">
+        <v>2.72</v>
+      </c>
+      <c r="AA338">
+        <v>3.13</v>
+      </c>
+      <c r="AB338">
+        <v>2.88</v>
+      </c>
+      <c r="AC338">
+        <v>1.09</v>
+      </c>
+      <c r="AD338">
+        <v>7</v>
+      </c>
+      <c r="AE338">
+        <v>1.59</v>
+      </c>
+      <c r="AF338">
+        <v>2.35</v>
+      </c>
+      <c r="AG338">
+        <v>2.2</v>
+      </c>
+      <c r="AH338">
+        <v>1.53</v>
+      </c>
+      <c r="AI338">
+        <v>2</v>
+      </c>
+      <c r="AJ338">
+        <v>1.73</v>
+      </c>
+      <c r="AK338">
+        <v>1.44</v>
+      </c>
+      <c r="AL338">
+        <v>1.34</v>
+      </c>
+      <c r="AM338">
+        <v>1.46</v>
+      </c>
+      <c r="AN338">
+        <v>1.2</v>
+      </c>
+      <c r="AO338">
+        <v>1.07</v>
+      </c>
+      <c r="AP338">
+        <v>1.19</v>
+      </c>
+      <c r="AQ338">
+        <v>1.07</v>
+      </c>
+      <c r="AR338">
+        <v>1.53</v>
+      </c>
+      <c r="AS338">
+        <v>1.16</v>
+      </c>
+      <c r="AT338">
+        <v>2.69</v>
+      </c>
+      <c r="AU338">
+        <v>4</v>
+      </c>
+      <c r="AV338">
+        <v>5</v>
+      </c>
+      <c r="AW338">
+        <v>7</v>
+      </c>
+      <c r="AX338">
+        <v>5</v>
+      </c>
+      <c r="AY338">
+        <v>14</v>
+      </c>
+      <c r="AZ338">
+        <v>12</v>
+      </c>
+      <c r="BA338">
+        <v>3</v>
+      </c>
+      <c r="BB338">
+        <v>3</v>
+      </c>
+      <c r="BC338">
+        <v>6</v>
+      </c>
+      <c r="BD338">
+        <v>1.74</v>
+      </c>
+      <c r="BE338">
+        <v>6.55</v>
+      </c>
+      <c r="BF338">
+        <v>2.73</v>
+      </c>
+      <c r="BG338">
+        <v>1.28</v>
+      </c>
+      <c r="BH338">
+        <v>3.05</v>
+      </c>
+      <c r="BI338">
+        <v>1.55</v>
+      </c>
+      <c r="BJ338">
+        <v>2.23</v>
+      </c>
+      <c r="BK338">
+        <v>1.96</v>
+      </c>
+      <c r="BL338">
+        <v>1.75</v>
+      </c>
+      <c r="BM338">
+        <v>2.57</v>
+      </c>
+      <c r="BN338">
+        <v>1.42</v>
+      </c>
+      <c r="BO338">
+        <v>3.5</v>
+      </c>
+      <c r="BP338">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="339" spans="1:68">
+      <c r="A339" s="1">
+        <v>338</v>
+      </c>
+      <c r="B339">
+        <v>7728533</v>
+      </c>
+      <c r="C339" t="s">
+        <v>68</v>
+      </c>
+      <c r="D339" t="s">
+        <v>69</v>
+      </c>
+      <c r="E339" s="2">
+        <v>45732.51041666666</v>
+      </c>
+      <c r="F339">
+        <v>31</v>
+      </c>
+      <c r="G339" t="s">
+        <v>81</v>
+      </c>
+      <c r="H339" t="s">
+        <v>82</v>
+      </c>
+      <c r="I339">
+        <v>0</v>
+      </c>
+      <c r="J339">
+        <v>0</v>
+      </c>
+      <c r="K339">
+        <v>0</v>
+      </c>
+      <c r="L339">
+        <v>1</v>
+      </c>
+      <c r="M339">
+        <v>2</v>
+      </c>
+      <c r="N339">
+        <v>3</v>
+      </c>
+      <c r="O339" t="s">
+        <v>183</v>
+      </c>
+      <c r="P339" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q339">
+        <v>3.4</v>
+      </c>
+      <c r="R339">
+        <v>2</v>
+      </c>
+      <c r="S339">
+        <v>3.6</v>
+      </c>
+      <c r="T339">
+        <v>1.5</v>
+      </c>
+      <c r="U339">
+        <v>2.5</v>
+      </c>
+      <c r="V339">
+        <v>3.5</v>
+      </c>
+      <c r="W339">
+        <v>1.29</v>
+      </c>
+      <c r="X339">
+        <v>11</v>
+      </c>
+      <c r="Y339">
+        <v>1.05</v>
+      </c>
+      <c r="Z339">
+        <v>2.53</v>
+      </c>
+      <c r="AA339">
+        <v>3.03</v>
+      </c>
+      <c r="AB339">
+        <v>3.23</v>
+      </c>
+      <c r="AC339">
+        <v>1.1</v>
+      </c>
+      <c r="AD339">
+        <v>6.5</v>
+      </c>
+      <c r="AE339">
+        <v>1.45</v>
+      </c>
+      <c r="AF339">
+        <v>2.7</v>
+      </c>
+      <c r="AG339">
+        <v>2.25</v>
+      </c>
+      <c r="AH339">
+        <v>1.53</v>
+      </c>
+      <c r="AI339">
+        <v>1.91</v>
+      </c>
+      <c r="AJ339">
+        <v>1.8</v>
+      </c>
+      <c r="AK339">
+        <v>1.4</v>
+      </c>
+      <c r="AL339">
+        <v>1.36</v>
+      </c>
+      <c r="AM339">
+        <v>1.49</v>
+      </c>
+      <c r="AN339">
+        <v>2.07</v>
+      </c>
+      <c r="AO339">
+        <v>1.53</v>
+      </c>
+      <c r="AP339">
+        <v>1.93</v>
+      </c>
+      <c r="AQ339">
+        <v>1.63</v>
+      </c>
+      <c r="AR339">
+        <v>1.26</v>
+      </c>
+      <c r="AS339">
+        <v>1.27</v>
+      </c>
+      <c r="AT339">
+        <v>2.53</v>
+      </c>
+      <c r="AU339">
+        <v>5</v>
+      </c>
+      <c r="AV339">
+        <v>3</v>
+      </c>
+      <c r="AW339">
+        <v>3</v>
+      </c>
+      <c r="AX339">
+        <v>4</v>
+      </c>
+      <c r="AY339">
+        <v>8</v>
+      </c>
+      <c r="AZ339">
+        <v>8</v>
+      </c>
+      <c r="BA339">
+        <v>4</v>
+      </c>
+      <c r="BB339">
+        <v>3</v>
+      </c>
+      <c r="BC339">
+        <v>7</v>
+      </c>
+      <c r="BD339">
+        <v>2.08</v>
+      </c>
+      <c r="BE339">
+        <v>6.4</v>
+      </c>
+      <c r="BF339">
+        <v>2.19</v>
+      </c>
+      <c r="BG339">
+        <v>1.26</v>
+      </c>
+      <c r="BH339">
+        <v>3.22</v>
+      </c>
+      <c r="BI339">
+        <v>1.5</v>
+      </c>
+      <c r="BJ339">
+        <v>2.35</v>
+      </c>
+      <c r="BK339">
+        <v>1.88</v>
+      </c>
+      <c r="BL339">
+        <v>1.82</v>
+      </c>
+      <c r="BM339">
+        <v>2.42</v>
+      </c>
+      <c r="BN339">
+        <v>1.47</v>
+      </c>
+      <c r="BO339">
+        <v>3.28</v>
+      </c>
+      <c r="BP339">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="340" spans="1:68">
+      <c r="A340" s="1">
+        <v>339</v>
+      </c>
+      <c r="B340">
+        <v>7728534</v>
+      </c>
+      <c r="C340" t="s">
+        <v>68</v>
+      </c>
+      <c r="D340" t="s">
+        <v>69</v>
+      </c>
+      <c r="E340" s="2">
+        <v>45732.51041666666</v>
+      </c>
+      <c r="F340">
+        <v>31</v>
+      </c>
+      <c r="G340" t="s">
+        <v>77</v>
+      </c>
+      <c r="H340" t="s">
+        <v>84</v>
+      </c>
+      <c r="I340">
+        <v>0</v>
+      </c>
+      <c r="J340">
+        <v>0</v>
+      </c>
+      <c r="K340">
+        <v>0</v>
+      </c>
+      <c r="L340">
+        <v>2</v>
+      </c>
+      <c r="M340">
+        <v>1</v>
+      </c>
+      <c r="N340">
+        <v>3</v>
+      </c>
+      <c r="O340" t="s">
+        <v>303</v>
+      </c>
+      <c r="P340" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q340">
+        <v>2.5</v>
+      </c>
+      <c r="R340">
+        <v>2.1</v>
+      </c>
+      <c r="S340">
+        <v>5</v>
+      </c>
+      <c r="T340">
+        <v>1.44</v>
+      </c>
+      <c r="U340">
+        <v>2.63</v>
+      </c>
+      <c r="V340">
+        <v>3.25</v>
+      </c>
+      <c r="W340">
+        <v>1.33</v>
+      </c>
+      <c r="X340">
+        <v>9</v>
+      </c>
+      <c r="Y340">
+        <v>1.07</v>
+      </c>
+      <c r="Z340">
+        <v>1.83</v>
+      </c>
+      <c r="AA340">
+        <v>3.66</v>
+      </c>
+      <c r="AB340">
+        <v>4.7</v>
+      </c>
+      <c r="AC340">
+        <v>1.07</v>
+      </c>
+      <c r="AD340">
+        <v>8</v>
+      </c>
+      <c r="AE340">
+        <v>1.36</v>
+      </c>
+      <c r="AF340">
+        <v>3.1</v>
+      </c>
+      <c r="AG340">
+        <v>1.95</v>
+      </c>
+      <c r="AH340">
+        <v>1.7</v>
+      </c>
+      <c r="AI340">
+        <v>1.91</v>
+      </c>
+      <c r="AJ340">
+        <v>1.8</v>
+      </c>
+      <c r="AK340">
+        <v>1.21</v>
+      </c>
+      <c r="AL340">
+        <v>1.3</v>
+      </c>
+      <c r="AM340">
+        <v>1.9</v>
+      </c>
+      <c r="AN340">
+        <v>1.67</v>
+      </c>
+      <c r="AO340">
+        <v>0.2</v>
+      </c>
+      <c r="AP340">
+        <v>1.75</v>
+      </c>
+      <c r="AQ340">
+        <v>0.19</v>
+      </c>
+      <c r="AR340">
+        <v>1.59</v>
+      </c>
+      <c r="AS340">
+        <v>1.09</v>
+      </c>
+      <c r="AT340">
+        <v>2.68</v>
+      </c>
+      <c r="AU340">
+        <v>6</v>
+      </c>
+      <c r="AV340">
+        <v>5</v>
+      </c>
+      <c r="AW340">
+        <v>4</v>
+      </c>
+      <c r="AX340">
+        <v>7</v>
+      </c>
+      <c r="AY340">
+        <v>11</v>
+      </c>
+      <c r="AZ340">
+        <v>13</v>
+      </c>
+      <c r="BA340">
+        <v>4</v>
+      </c>
+      <c r="BB340">
+        <v>7</v>
+      </c>
+      <c r="BC340">
+        <v>11</v>
+      </c>
+      <c r="BD340">
+        <v>1.44</v>
+      </c>
+      <c r="BE340">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF340">
+        <v>3.42</v>
+      </c>
+      <c r="BG340">
+        <v>1.26</v>
+      </c>
+      <c r="BH340">
+        <v>3.22</v>
+      </c>
+      <c r="BI340">
+        <v>1.51</v>
+      </c>
+      <c r="BJ340">
+        <v>2.32</v>
+      </c>
+      <c r="BK340">
+        <v>1.9</v>
+      </c>
+      <c r="BL340">
+        <v>1.8</v>
+      </c>
+      <c r="BM340">
+        <v>2.45</v>
+      </c>
+      <c r="BN340">
+        <v>1.46</v>
+      </c>
+      <c r="BO340">
+        <v>3.28</v>
+      </c>
+      <c r="BP340">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="341" spans="1:68">
+      <c r="A341" s="1">
+        <v>340</v>
+      </c>
+      <c r="B341">
+        <v>7728529</v>
+      </c>
+      <c r="C341" t="s">
+        <v>68</v>
+      </c>
+      <c r="D341" t="s">
+        <v>69</v>
+      </c>
+      <c r="E341" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F341">
+        <v>31</v>
+      </c>
+      <c r="G341" t="s">
+        <v>72</v>
+      </c>
+      <c r="H341" t="s">
+        <v>70</v>
+      </c>
+      <c r="I341">
+        <v>1</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <v>1</v>
+      </c>
+      <c r="L341">
+        <v>1</v>
+      </c>
+      <c r="M341">
+        <v>0</v>
+      </c>
+      <c r="N341">
+        <v>1</v>
+      </c>
+      <c r="O341" t="s">
+        <v>147</v>
+      </c>
+      <c r="P341" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q341">
+        <v>3.1</v>
+      </c>
+      <c r="R341">
+        <v>1.95</v>
+      </c>
+      <c r="S341">
+        <v>4.33</v>
+      </c>
+      <c r="T341">
+        <v>1.53</v>
+      </c>
+      <c r="U341">
+        <v>2.38</v>
+      </c>
+      <c r="V341">
+        <v>3.75</v>
+      </c>
+      <c r="W341">
+        <v>1.25</v>
+      </c>
+      <c r="X341">
+        <v>11</v>
+      </c>
+      <c r="Y341">
+        <v>1.05</v>
+      </c>
+      <c r="Z341">
+        <v>2.37</v>
+      </c>
+      <c r="AA341">
+        <v>3.29</v>
+      </c>
+      <c r="AB341">
+        <v>3.23</v>
+      </c>
+      <c r="AC341">
+        <v>1.1</v>
+      </c>
+      <c r="AD341">
+        <v>6.5</v>
+      </c>
+      <c r="AE341">
+        <v>1.48</v>
+      </c>
+      <c r="AF341">
+        <v>2.6</v>
+      </c>
+      <c r="AG341">
+        <v>2.3</v>
+      </c>
+      <c r="AH341">
+        <v>1.5</v>
+      </c>
+      <c r="AI341">
+        <v>2.1</v>
+      </c>
+      <c r="AJ341">
+        <v>1.67</v>
+      </c>
+      <c r="AK341">
+        <v>1.32</v>
+      </c>
+      <c r="AL341">
+        <v>1.33</v>
+      </c>
+      <c r="AM341">
+        <v>1.62</v>
+      </c>
+      <c r="AN341">
+        <v>1.4</v>
+      </c>
+      <c r="AO341">
+        <v>1.36</v>
+      </c>
+      <c r="AP341">
+        <v>1.5</v>
+      </c>
+      <c r="AQ341">
+        <v>1.27</v>
+      </c>
+      <c r="AR341">
+        <v>1.44</v>
+      </c>
+      <c r="AS341">
+        <v>1.18</v>
+      </c>
+      <c r="AT341">
+        <v>2.62</v>
+      </c>
+      <c r="AU341">
+        <v>5</v>
+      </c>
+      <c r="AV341">
+        <v>0</v>
+      </c>
+      <c r="AW341">
+        <v>11</v>
+      </c>
+      <c r="AX341">
+        <v>10</v>
+      </c>
+      <c r="AY341">
+        <v>17</v>
+      </c>
+      <c r="AZ341">
+        <v>12</v>
+      </c>
+      <c r="BA341">
+        <v>6</v>
+      </c>
+      <c r="BB341">
+        <v>6</v>
+      </c>
+      <c r="BC341">
+        <v>12</v>
+      </c>
+      <c r="BD341">
+        <v>1.7</v>
+      </c>
+      <c r="BE341">
+        <v>6.55</v>
+      </c>
+      <c r="BF341">
+        <v>2.84</v>
+      </c>
+      <c r="BG341">
+        <v>1.31</v>
+      </c>
+      <c r="BH341">
+        <v>2.92</v>
+      </c>
+      <c r="BI341">
+        <v>1.6</v>
+      </c>
+      <c r="BJ341">
+        <v>2.14</v>
+      </c>
+      <c r="BK341">
+        <v>2.04</v>
+      </c>
+      <c r="BL341">
+        <v>1.69</v>
+      </c>
+      <c r="BM341">
+        <v>2.67</v>
+      </c>
+      <c r="BN341">
+        <v>1.39</v>
+      </c>
+      <c r="BO341">
+        <v>3.7</v>
+      </c>
+      <c r="BP341">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -70997,13 +70997,13 @@
         <v>10</v>
       </c>
       <c r="BA337">
+        <v>5</v>
+      </c>
+      <c r="BB337">
+        <v>1</v>
+      </c>
+      <c r="BC337">
         <v>6</v>
-      </c>
-      <c r="BB337">
-        <v>1</v>
-      </c>
-      <c r="BC337">
-        <v>7</v>
       </c>
       <c r="BD337">
         <v>1.63</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2114" uniqueCount="417">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -928,6 +928,9 @@
     <t>['79', '85']</t>
   </si>
   <si>
+    <t>['14', '47']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1259,6 +1262,9 @@
   </si>
   <si>
     <t>['54', '90+1']</t>
+  </si>
+  <si>
+    <t>['6', '57']</t>
   </si>
 </sst>
 </file>
@@ -1620,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP341"/>
+  <dimension ref="A1:BP342"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1876,7 +1882,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2288,7 +2294,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3112,7 +3118,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3318,7 +3324,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4142,7 +4148,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4429,7 +4435,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ14">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -5378,7 +5384,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5868,7 +5874,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ21">
         <v>1.4</v>
@@ -5996,7 +6002,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6202,7 +6208,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6408,7 +6414,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6614,7 +6620,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6820,7 +6826,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7026,7 +7032,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7438,7 +7444,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -8056,7 +8062,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8262,7 +8268,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8674,7 +8680,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8961,7 +8967,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ36">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR36">
         <v>2.09</v>
@@ -10528,7 +10534,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10606,7 +10612,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ44">
         <v>1.33</v>
@@ -11021,7 +11027,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ46">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -11146,7 +11152,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12794,7 +12800,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -13000,7 +13006,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13206,7 +13212,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13412,7 +13418,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13824,7 +13830,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14442,7 +14448,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14726,7 +14732,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ64">
         <v>1.87</v>
@@ -15060,7 +15066,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15472,7 +15478,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15553,7 +15559,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ68">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR68">
         <v>1.07</v>
@@ -15678,7 +15684,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16296,7 +16302,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16502,7 +16508,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16708,7 +16714,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16992,7 +16998,7 @@
         <v>0.33</v>
       </c>
       <c r="AP75">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ75">
         <v>0.19</v>
@@ -17532,7 +17538,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17738,7 +17744,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18150,7 +18156,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18356,7 +18362,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18562,7 +18568,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19386,7 +19392,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19798,7 +19804,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -20004,7 +20010,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20416,7 +20422,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20828,7 +20834,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -21034,7 +21040,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21939,7 +21945,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ99">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR99">
         <v>1.46</v>
@@ -22064,7 +22070,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23172,7 +23178,7 @@
         <v>1.4</v>
       </c>
       <c r="AP105">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ105">
         <v>1.63</v>
@@ -23506,7 +23512,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24124,7 +24130,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24536,7 +24542,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24742,7 +24748,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24820,7 +24826,7 @@
         <v>2</v>
       </c>
       <c r="AP113">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ113">
         <v>1.27</v>
@@ -25154,7 +25160,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25978,7 +25984,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26059,7 +26065,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR119">
         <v>1.68</v>
@@ -26596,7 +26602,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -27008,7 +27014,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27420,7 +27426,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27832,7 +27838,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28244,7 +28250,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28450,7 +28456,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28656,7 +28662,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29068,7 +29074,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29274,7 +29280,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29355,7 +29361,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ135">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR135">
         <v>1.12</v>
@@ -29892,7 +29898,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30510,7 +30516,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30716,7 +30722,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30922,7 +30928,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31128,7 +31134,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31540,7 +31546,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31952,7 +31958,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32982,7 +32988,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33060,7 +33066,7 @@
         <v>0.83</v>
       </c>
       <c r="AP153">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ153">
         <v>1.07</v>
@@ -33600,7 +33606,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34299,7 +34305,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ159">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR159">
         <v>1.75</v>
@@ -35248,7 +35254,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35866,7 +35872,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36896,7 +36902,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37514,7 +37520,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37798,7 +37804,7 @@
         <v>0.83</v>
       </c>
       <c r="AP176">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ176">
         <v>0.87</v>
@@ -37926,7 +37932,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38338,7 +38344,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38544,7 +38550,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38625,7 +38631,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ180">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR180">
         <v>1.48</v>
@@ -39240,7 +39246,7 @@
         <v>0.88</v>
       </c>
       <c r="AP183">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ183">
         <v>0.9399999999999999</v>
@@ -39368,7 +39374,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40192,7 +40198,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40810,7 +40816,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -41016,7 +41022,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41222,7 +41228,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41428,7 +41434,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42664,7 +42670,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43076,7 +43082,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43154,7 +43160,7 @@
         <v>0.67</v>
       </c>
       <c r="AP202">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ202">
         <v>0.44</v>
@@ -43282,7 +43288,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43900,7 +43906,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44930,7 +44936,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45136,7 +45142,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45342,7 +45348,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45548,7 +45554,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45960,7 +45966,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -47196,7 +47202,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47608,7 +47614,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -48020,7 +48026,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48098,7 +48104,7 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ226">
         <v>1.07</v>
@@ -48638,7 +48644,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48844,7 +48850,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49050,7 +49056,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49874,7 +49880,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50367,7 +50373,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ237">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR237">
         <v>1.37</v>
@@ -50698,7 +50704,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51316,7 +51322,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51728,7 +51734,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52140,7 +52146,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52633,7 +52639,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ248">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR248">
         <v>1.41</v>
@@ -52964,7 +52970,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53042,7 +53048,7 @@
         <v>0.45</v>
       </c>
       <c r="AP250">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ250">
         <v>1.13</v>
@@ -53170,7 +53176,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53582,7 +53588,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53994,7 +54000,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54200,7 +54206,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -55230,7 +55236,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55436,7 +55442,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55929,7 +55935,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ264">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR264">
         <v>1.24</v>
@@ -56054,7 +56060,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -57162,7 +57168,7 @@
         <v>1.25</v>
       </c>
       <c r="AP270">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ270">
         <v>1.38</v>
@@ -57371,7 +57377,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ271">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR271">
         <v>1.48</v>
@@ -57496,7 +57502,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -58526,7 +58532,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59762,7 +59768,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59968,7 +59974,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60586,7 +60592,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -60870,7 +60876,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP288">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ288">
         <v>0.8100000000000001</v>
@@ -61204,7 +61210,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61410,7 +61416,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61903,7 +61909,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ293">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR293">
         <v>1.47</v>
@@ -63264,7 +63270,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63470,7 +63476,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63676,7 +63682,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -65118,7 +65124,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65608,7 +65614,7 @@
         <v>0.92</v>
       </c>
       <c r="AP311">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ311">
         <v>1.13</v>
@@ -65942,7 +65948,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66354,7 +66360,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66435,7 +66441,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ315">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR315">
         <v>1.64</v>
@@ -66560,7 +66566,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -68620,7 +68626,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -69032,7 +69038,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -71092,7 +71098,7 @@
         <v>302</v>
       </c>
       <c r="P338" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q338">
         <v>3.5</v>
@@ -71298,7 +71304,7 @@
         <v>183</v>
       </c>
       <c r="P339" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q339">
         <v>3.4</v>
@@ -71867,6 +71873,212 @@
       </c>
       <c r="BP341">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="342" spans="1:68">
+      <c r="A342" s="1">
+        <v>341</v>
+      </c>
+      <c r="B342">
+        <v>7728530</v>
+      </c>
+      <c r="C342" t="s">
+        <v>68</v>
+      </c>
+      <c r="D342" t="s">
+        <v>69</v>
+      </c>
+      <c r="E342" s="2">
+        <v>45733.6875</v>
+      </c>
+      <c r="F342">
+        <v>31</v>
+      </c>
+      <c r="G342" t="s">
+        <v>86</v>
+      </c>
+      <c r="H342" t="s">
+        <v>75</v>
+      </c>
+      <c r="I342">
+        <v>1</v>
+      </c>
+      <c r="J342">
+        <v>1</v>
+      </c>
+      <c r="K342">
+        <v>2</v>
+      </c>
+      <c r="L342">
+        <v>2</v>
+      </c>
+      <c r="M342">
+        <v>2</v>
+      </c>
+      <c r="N342">
+        <v>4</v>
+      </c>
+      <c r="O342" t="s">
+        <v>304</v>
+      </c>
+      <c r="P342" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q342">
+        <v>2.88</v>
+      </c>
+      <c r="R342">
+        <v>2.2</v>
+      </c>
+      <c r="S342">
+        <v>3.6</v>
+      </c>
+      <c r="T342">
+        <v>1.36</v>
+      </c>
+      <c r="U342">
+        <v>3</v>
+      </c>
+      <c r="V342">
+        <v>2.75</v>
+      </c>
+      <c r="W342">
+        <v>1.4</v>
+      </c>
+      <c r="X342">
+        <v>7</v>
+      </c>
+      <c r="Y342">
+        <v>1.1</v>
+      </c>
+      <c r="Z342">
+        <v>2.15</v>
+      </c>
+      <c r="AA342">
+        <v>3.55</v>
+      </c>
+      <c r="AB342">
+        <v>3.47</v>
+      </c>
+      <c r="AC342">
+        <v>1.05</v>
+      </c>
+      <c r="AD342">
+        <v>9.5</v>
+      </c>
+      <c r="AE342">
+        <v>1.25</v>
+      </c>
+      <c r="AF342">
+        <v>3.75</v>
+      </c>
+      <c r="AG342">
+        <v>1.78</v>
+      </c>
+      <c r="AH342">
+        <v>2.04</v>
+      </c>
+      <c r="AI342">
+        <v>1.67</v>
+      </c>
+      <c r="AJ342">
+        <v>2.1</v>
+      </c>
+      <c r="AK342">
+        <v>1.35</v>
+      </c>
+      <c r="AL342">
+        <v>1.25</v>
+      </c>
+      <c r="AM342">
+        <v>1.62</v>
+      </c>
+      <c r="AN342">
+        <v>1.33</v>
+      </c>
+      <c r="AO342">
+        <v>1.47</v>
+      </c>
+      <c r="AP342">
+        <v>1.31</v>
+      </c>
+      <c r="AQ342">
+        <v>1.44</v>
+      </c>
+      <c r="AR342">
+        <v>1.68</v>
+      </c>
+      <c r="AS342">
+        <v>1.3</v>
+      </c>
+      <c r="AT342">
+        <v>2.98</v>
+      </c>
+      <c r="AU342">
+        <v>-1</v>
+      </c>
+      <c r="AV342">
+        <v>-1</v>
+      </c>
+      <c r="AW342">
+        <v>-1</v>
+      </c>
+      <c r="AX342">
+        <v>-1</v>
+      </c>
+      <c r="AY342">
+        <v>-1</v>
+      </c>
+      <c r="AZ342">
+        <v>-1</v>
+      </c>
+      <c r="BA342">
+        <v>-1</v>
+      </c>
+      <c r="BB342">
+        <v>-1</v>
+      </c>
+      <c r="BC342">
+        <v>-1</v>
+      </c>
+      <c r="BD342">
+        <v>1.71</v>
+      </c>
+      <c r="BE342">
+        <v>6.5</v>
+      </c>
+      <c r="BF342">
+        <v>2.38</v>
+      </c>
+      <c r="BG342">
+        <v>1.29</v>
+      </c>
+      <c r="BH342">
+        <v>3.15</v>
+      </c>
+      <c r="BI342">
+        <v>1.5</v>
+      </c>
+      <c r="BJ342">
+        <v>2.35</v>
+      </c>
+      <c r="BK342">
+        <v>1.81</v>
+      </c>
+      <c r="BL342">
+        <v>1.85</v>
+      </c>
+      <c r="BM342">
+        <v>2.25</v>
+      </c>
+      <c r="BN342">
+        <v>1.53</v>
+      </c>
+      <c r="BO342">
+        <v>2.9</v>
+      </c>
+      <c r="BP342">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -72015,31 +72015,31 @@
         <v>2.98</v>
       </c>
       <c r="AU342">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV342">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW342">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AX342">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY342">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AZ342">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BA342">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB342">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC342">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD342">
         <v>1.71</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2114" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="421">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -931,6 +931,18 @@
     <t>['14', '47']</t>
   </si>
   <si>
+    <t>['9', '67', '84']</t>
+  </si>
+  <si>
+    <t>['77', '85']</t>
+  </si>
+  <si>
+    <t>['51', '75']</t>
+  </si>
+  <si>
+    <t>['9', '39']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1626,7 +1638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP342"/>
+  <dimension ref="A1:BP346"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1882,7 +1894,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2166,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ3">
         <v>1.13</v>
@@ -2294,7 +2306,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3118,7 +3130,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3324,7 +3336,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3405,7 +3417,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ9">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3608,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ10">
         <v>0.44</v>
@@ -3814,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ11">
         <v>1.38</v>
@@ -4148,7 +4160,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4641,7 +4653,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ15">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>1.13</v>
@@ -5256,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ18">
         <v>1.07</v>
@@ -5384,7 +5396,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5465,7 +5477,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ19">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -6002,7 +6014,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6208,7 +6220,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6414,7 +6426,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6620,7 +6632,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6701,7 +6713,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ25">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6826,7 +6838,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7032,7 +7044,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7110,7 +7122,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ27">
         <v>0.87</v>
@@ -7444,7 +7456,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7522,7 +7534,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ29">
         <v>1.27</v>
@@ -7731,7 +7743,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ30">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR30">
         <v>1.73</v>
@@ -7934,7 +7946,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ31">
         <v>1.25</v>
@@ -8062,7 +8074,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8268,7 +8280,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8552,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ34">
         <v>1.13</v>
@@ -8680,7 +8692,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8761,7 +8773,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ35">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR35">
         <v>1.42</v>
@@ -10203,7 +10215,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ42">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR42">
         <v>1.8</v>
@@ -10534,7 +10546,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11152,7 +11164,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11233,7 +11245,7 @@
         <v>2</v>
       </c>
       <c r="AQ47">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>1.72</v>
@@ -11642,7 +11654,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ49">
         <v>1.38</v>
@@ -12054,7 +12066,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ51">
         <v>0.87</v>
@@ -12466,7 +12478,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ53">
         <v>1.25</v>
@@ -12675,7 +12687,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ54">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12800,7 +12812,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12878,7 +12890,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ55">
         <v>1.27</v>
@@ -13006,7 +13018,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13212,7 +13224,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13418,7 +13430,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13830,7 +13842,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14448,7 +14460,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14735,7 +14747,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ64">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR64">
         <v>1.39</v>
@@ -14938,7 +14950,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ65">
         <v>1.07</v>
@@ -15066,7 +15078,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15478,7 +15490,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15684,7 +15696,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15765,7 +15777,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR69">
         <v>1.25</v>
@@ -15968,7 +15980,7 @@
         <v>2</v>
       </c>
       <c r="AP70">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ70">
         <v>1.38</v>
@@ -16302,7 +16314,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16380,7 +16392,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ72">
         <v>1.07</v>
@@ -16508,7 +16520,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16589,7 +16601,7 @@
         <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR73">
         <v>2.06</v>
@@ -16714,7 +16726,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16792,7 +16804,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ74">
         <v>1.27</v>
@@ -17207,7 +17219,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ76">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -17538,7 +17550,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17744,7 +17756,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18156,7 +18168,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18234,7 +18246,7 @@
         <v>1.67</v>
       </c>
       <c r="AP81">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ81">
         <v>1.27</v>
@@ -18362,7 +18374,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18568,7 +18580,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18649,7 +18661,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ83">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR83">
         <v>1.8</v>
@@ -19392,7 +19404,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19804,7 +19816,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -20010,7 +20022,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20297,7 +20309,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ91">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20422,7 +20434,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20709,7 +20721,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ93">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.5</v>
@@ -20834,7 +20846,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -21040,7 +21052,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21121,7 +21133,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ95">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR95">
         <v>1.44</v>
@@ -21736,7 +21748,7 @@
         <v>0.67</v>
       </c>
       <c r="AP98">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ98">
         <v>1.07</v>
@@ -21942,7 +21954,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ99">
         <v>1.44</v>
@@ -22070,7 +22082,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22560,7 +22572,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ102">
         <v>1.4</v>
@@ -22769,7 +22781,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ103">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR103">
         <v>1.55</v>
@@ -23384,7 +23396,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ106">
         <v>0.8100000000000001</v>
@@ -23512,7 +23524,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23593,7 +23605,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ107">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR107">
         <v>1.53</v>
@@ -24002,7 +24014,7 @@
         <v>1.25</v>
       </c>
       <c r="AP109">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -24130,7 +24142,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24211,7 +24223,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ110">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR110">
         <v>1.96</v>
@@ -24542,7 +24554,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24748,7 +24760,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25160,7 +25172,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25984,7 +25996,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26602,7 +26614,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26680,10 +26692,10 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ122">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR122">
         <v>1.4</v>
@@ -27014,7 +27026,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27092,7 +27104,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ124">
         <v>0.44</v>
@@ -27301,7 +27313,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ125">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR125">
         <v>1.56</v>
@@ -27426,7 +27438,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27710,7 +27722,7 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ127">
         <v>0.8100000000000001</v>
@@ -27838,7 +27850,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27919,7 +27931,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ128">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR128">
         <v>1.61</v>
@@ -28122,7 +28134,7 @@
         <v>1.4</v>
       </c>
       <c r="AP129">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ129">
         <v>1.13</v>
@@ -28250,7 +28262,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28456,7 +28468,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28537,7 +28549,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ131">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR131">
         <v>1.16</v>
@@ -28662,7 +28674,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29074,7 +29086,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29280,7 +29292,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29898,7 +29910,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30516,7 +30528,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30594,10 +30606,10 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ141">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR141">
         <v>1.42</v>
@@ -30722,7 +30734,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30800,7 +30812,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ142">
         <v>1.33</v>
@@ -30928,7 +30940,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31134,7 +31146,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31215,7 +31227,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ144">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR144">
         <v>1.75</v>
@@ -31418,7 +31430,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ145">
         <v>0.44</v>
@@ -31546,7 +31558,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31830,7 +31842,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ147">
         <v>1</v>
@@ -31958,7 +31970,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32039,7 +32051,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ148">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR148">
         <v>1.13</v>
@@ -32657,7 +32669,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ151">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR151">
         <v>1.43</v>
@@ -32988,7 +33000,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33606,7 +33618,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -35254,7 +35266,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35335,7 +35347,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ164">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR164">
         <v>1.2</v>
@@ -35744,7 +35756,7 @@
         <v>0.71</v>
       </c>
       <c r="AP166">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ166">
         <v>0.8100000000000001</v>
@@ -35872,7 +35884,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36156,10 +36168,10 @@
         <v>3</v>
       </c>
       <c r="AP168">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ168">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR168">
         <v>1.29</v>
@@ -36774,10 +36786,10 @@
         <v>0.71</v>
       </c>
       <c r="AP171">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ171">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR171">
         <v>1.18</v>
@@ -36902,7 +36914,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37186,7 +37198,7 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ173">
         <v>1.4</v>
@@ -37520,7 +37532,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37807,7 +37819,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ176">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR176">
         <v>1.6</v>
@@ -37932,7 +37944,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38344,7 +38356,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38550,7 +38562,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39374,7 +39386,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39661,7 +39673,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ185">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR185">
         <v>1.42</v>
@@ -40198,7 +40210,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40276,7 +40288,7 @@
         <v>1.38</v>
       </c>
       <c r="AP188">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ188">
         <v>1.63</v>
@@ -40482,7 +40494,7 @@
         <v>1.13</v>
       </c>
       <c r="AP189">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ189">
         <v>1.33</v>
@@ -40691,7 +40703,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ190">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR190">
         <v>1.74</v>
@@ -40816,7 +40828,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -41022,7 +41034,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41228,7 +41240,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41434,7 +41446,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41512,10 +41524,10 @@
         <v>1.56</v>
       </c>
       <c r="AP194">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ194">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR194">
         <v>1.4</v>
@@ -41924,10 +41936,10 @@
         <v>0.63</v>
       </c>
       <c r="AP196">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ196">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR196">
         <v>1.42</v>
@@ -42670,7 +42682,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43082,7 +43094,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43288,7 +43300,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43906,7 +43918,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43987,7 +43999,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ206">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR206">
         <v>1.42</v>
@@ -44190,7 +44202,7 @@
         <v>0.78</v>
       </c>
       <c r="AP207">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ207">
         <v>0.9399999999999999</v>
@@ -44936,7 +44948,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45142,7 +45154,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45348,7 +45360,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45429,7 +45441,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ213">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR213">
         <v>1.08</v>
@@ -45554,7 +45566,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45632,7 +45644,7 @@
         <v>1.11</v>
       </c>
       <c r="AP214">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ214">
         <v>1</v>
@@ -45838,10 +45850,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP215">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ215">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR215">
         <v>1.3</v>
@@ -45966,7 +45978,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46250,10 +46262,10 @@
         <v>2.44</v>
       </c>
       <c r="AP217">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ217">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR217">
         <v>1.61</v>
@@ -47202,7 +47214,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47489,7 +47501,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ223">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR223">
         <v>1.71</v>
@@ -47614,7 +47626,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47898,7 +47910,7 @@
         <v>0.2</v>
       </c>
       <c r="AP225">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ225">
         <v>0.19</v>
@@ -48026,7 +48038,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48519,7 +48531,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ228">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR228">
         <v>1.5</v>
@@ -48644,7 +48656,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48850,7 +48862,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49056,7 +49068,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49880,7 +49892,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -49961,7 +49973,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ235">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR235">
         <v>1.56</v>
@@ -50370,7 +50382,7 @@
         <v>1.22</v>
       </c>
       <c r="AP237">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ237">
         <v>1.44</v>
@@ -50704,7 +50716,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50785,7 +50797,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ239">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR239">
         <v>1.67</v>
@@ -51194,7 +51206,7 @@
         <v>1.45</v>
       </c>
       <c r="AP241">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ241">
         <v>1.25</v>
@@ -51322,7 +51334,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51734,7 +51746,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52146,7 +52158,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52636,7 +52648,7 @@
         <v>1.2</v>
       </c>
       <c r="AP248">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ248">
         <v>1.44</v>
@@ -52845,7 +52857,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ249">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR249">
         <v>1.51</v>
@@ -52970,7 +52982,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53176,7 +53188,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53588,7 +53600,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53666,7 +53678,7 @@
         <v>1</v>
       </c>
       <c r="AP253">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ253">
         <v>0.9399999999999999</v>
@@ -53872,7 +53884,7 @@
         <v>0.73</v>
       </c>
       <c r="AP254">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ254">
         <v>0.8100000000000001</v>
@@ -54000,7 +54012,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54081,7 +54093,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ255">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR255">
         <v>1.61</v>
@@ -54206,7 +54218,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54699,7 +54711,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ258">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR258">
         <v>1.2</v>
@@ -55236,7 +55248,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55317,7 +55329,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ261">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR261">
         <v>1.52</v>
@@ -55442,7 +55454,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55520,7 +55532,7 @@
         <v>1.33</v>
       </c>
       <c r="AP262">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ262">
         <v>1.25</v>
@@ -56060,7 +56072,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56344,7 +56356,7 @@
         <v>1.27</v>
       </c>
       <c r="AP266">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ266">
         <v>1.07</v>
@@ -57502,7 +57514,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -58201,7 +58213,7 @@
         <v>2</v>
       </c>
       <c r="AQ275">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR275">
         <v>1.57</v>
@@ -58532,7 +58544,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59022,7 +59034,7 @@
         <v>1.46</v>
       </c>
       <c r="AP279">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ279">
         <v>1.63</v>
@@ -59434,7 +59446,7 @@
         <v>0.25</v>
       </c>
       <c r="AP281">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ281">
         <v>0.19</v>
@@ -59640,10 +59652,10 @@
         <v>2.17</v>
       </c>
       <c r="AP282">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ282">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR282">
         <v>1.44</v>
@@ -59768,7 +59780,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59974,7 +59986,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60261,7 +60273,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ285">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR285">
         <v>1.52</v>
@@ -60467,7 +60479,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ286">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR286">
         <v>1.59</v>
@@ -60592,7 +60604,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -60670,10 +60682,10 @@
         <v>1.08</v>
       </c>
       <c r="AP287">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ287">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR287">
         <v>1.29</v>
@@ -61210,7 +61222,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61416,7 +61428,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -62936,7 +62948,7 @@
         <v>0.23</v>
       </c>
       <c r="AP298">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ298">
         <v>0.19</v>
@@ -63270,7 +63282,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63348,7 +63360,7 @@
         <v>1.38</v>
       </c>
       <c r="AP300">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ300">
         <v>1.4</v>
@@ -63476,7 +63488,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63557,7 +63569,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ301">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR301">
         <v>1.54</v>
@@ -63682,7 +63694,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -63969,7 +63981,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ303">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR303">
         <v>1.51</v>
@@ -64378,7 +64390,7 @@
         <v>0.5</v>
       </c>
       <c r="AP305">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ305">
         <v>0.44</v>
@@ -64793,7 +64805,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ307">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR307">
         <v>1.53</v>
@@ -65124,7 +65136,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65411,7 +65423,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ310">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR310">
         <v>1.27</v>
@@ -65948,7 +65960,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66360,7 +66372,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66566,7 +66578,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -67262,7 +67274,7 @@
         <v>0.21</v>
       </c>
       <c r="AP319">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ319">
         <v>0.19</v>
@@ -67677,7 +67689,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ321">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR321">
         <v>1.54</v>
@@ -68086,7 +68098,7 @@
         <v>1.5</v>
       </c>
       <c r="AP323">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ323">
         <v>1.4</v>
@@ -68292,7 +68304,7 @@
         <v>1.36</v>
       </c>
       <c r="AP324">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AQ324">
         <v>1.27</v>
@@ -68501,7 +68513,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ325">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR325">
         <v>1.53</v>
@@ -68626,7 +68638,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -68707,7 +68719,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ326">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR326">
         <v>1.58</v>
@@ -69038,7 +69050,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -69116,7 +69128,7 @@
         <v>1.21</v>
       </c>
       <c r="AP328">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ328">
         <v>1.33</v>
@@ -69531,7 +69543,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ330">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR330">
         <v>1.67</v>
@@ -69734,7 +69746,7 @@
         <v>0.93</v>
       </c>
       <c r="AP331">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ331">
         <v>0.87</v>
@@ -71098,7 +71110,7 @@
         <v>302</v>
       </c>
       <c r="P338" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="Q338">
         <v>3.5</v>
@@ -71304,7 +71316,7 @@
         <v>183</v>
       </c>
       <c r="P339" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="Q339">
         <v>3.4</v>
@@ -71922,7 +71934,7 @@
         <v>304</v>
       </c>
       <c r="P342" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="Q342">
         <v>2.88</v>
@@ -72079,6 +72091,830 @@
       </c>
       <c r="BP342">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="343" spans="1:68">
+      <c r="A343" s="1">
+        <v>342</v>
+      </c>
+      <c r="B343">
+        <v>7728543</v>
+      </c>
+      <c r="C343" t="s">
+        <v>68</v>
+      </c>
+      <c r="D343" t="s">
+        <v>69</v>
+      </c>
+      <c r="E343" s="2">
+        <v>45737.6875</v>
+      </c>
+      <c r="F343">
+        <v>32</v>
+      </c>
+      <c r="G343" t="s">
+        <v>78</v>
+      </c>
+      <c r="H343" t="s">
+        <v>90</v>
+      </c>
+      <c r="I343">
+        <v>1</v>
+      </c>
+      <c r="J343">
+        <v>1</v>
+      </c>
+      <c r="K343">
+        <v>2</v>
+      </c>
+      <c r="L343">
+        <v>3</v>
+      </c>
+      <c r="M343">
+        <v>1</v>
+      </c>
+      <c r="N343">
+        <v>4</v>
+      </c>
+      <c r="O343" t="s">
+        <v>305</v>
+      </c>
+      <c r="P343" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q343">
+        <v>3.75</v>
+      </c>
+      <c r="R343">
+        <v>2</v>
+      </c>
+      <c r="S343">
+        <v>3.2</v>
+      </c>
+      <c r="T343">
+        <v>1.5</v>
+      </c>
+      <c r="U343">
+        <v>2.5</v>
+      </c>
+      <c r="V343">
+        <v>3.5</v>
+      </c>
+      <c r="W343">
+        <v>1.29</v>
+      </c>
+      <c r="X343">
+        <v>10</v>
+      </c>
+      <c r="Y343">
+        <v>1.06</v>
+      </c>
+      <c r="Z343">
+        <v>3.13</v>
+      </c>
+      <c r="AA343">
+        <v>3.29</v>
+      </c>
+      <c r="AB343">
+        <v>2.43</v>
+      </c>
+      <c r="AC343">
+        <v>1.08</v>
+      </c>
+      <c r="AD343">
+        <v>7.5</v>
+      </c>
+      <c r="AE343">
+        <v>1.42</v>
+      </c>
+      <c r="AF343">
+        <v>2.8</v>
+      </c>
+      <c r="AG343">
+        <v>1.95</v>
+      </c>
+      <c r="AH343">
+        <v>1.7</v>
+      </c>
+      <c r="AI343">
+        <v>2</v>
+      </c>
+      <c r="AJ343">
+        <v>1.73</v>
+      </c>
+      <c r="AK343">
+        <v>1.52</v>
+      </c>
+      <c r="AL343">
+        <v>1.33</v>
+      </c>
+      <c r="AM343">
+        <v>1.39</v>
+      </c>
+      <c r="AN343">
+        <v>1.6</v>
+      </c>
+      <c r="AO343">
+        <v>1.38</v>
+      </c>
+      <c r="AP343">
+        <v>1.69</v>
+      </c>
+      <c r="AQ343">
+        <v>1.29</v>
+      </c>
+      <c r="AR343">
+        <v>1.39</v>
+      </c>
+      <c r="AS343">
+        <v>1.6</v>
+      </c>
+      <c r="AT343">
+        <v>2.99</v>
+      </c>
+      <c r="AU343">
+        <v>5</v>
+      </c>
+      <c r="AV343">
+        <v>5</v>
+      </c>
+      <c r="AW343">
+        <v>2</v>
+      </c>
+      <c r="AX343">
+        <v>7</v>
+      </c>
+      <c r="AY343">
+        <v>8</v>
+      </c>
+      <c r="AZ343">
+        <v>13</v>
+      </c>
+      <c r="BA343">
+        <v>1</v>
+      </c>
+      <c r="BB343">
+        <v>3</v>
+      </c>
+      <c r="BC343">
+        <v>4</v>
+      </c>
+      <c r="BD343">
+        <v>1.9</v>
+      </c>
+      <c r="BE343">
+        <v>6.4</v>
+      </c>
+      <c r="BF343">
+        <v>2.1</v>
+      </c>
+      <c r="BG343">
+        <v>1.38</v>
+      </c>
+      <c r="BH343">
+        <v>2.65</v>
+      </c>
+      <c r="BI343">
+        <v>1.67</v>
+      </c>
+      <c r="BJ343">
+        <v>2.02</v>
+      </c>
+      <c r="BK343">
+        <v>2.1</v>
+      </c>
+      <c r="BL343">
+        <v>1.62</v>
+      </c>
+      <c r="BM343">
+        <v>2.7</v>
+      </c>
+      <c r="BN343">
+        <v>1.38</v>
+      </c>
+      <c r="BO343">
+        <v>3.65</v>
+      </c>
+      <c r="BP343">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="344" spans="1:68">
+      <c r="A344" s="1">
+        <v>343</v>
+      </c>
+      <c r="B344">
+        <v>7728539</v>
+      </c>
+      <c r="C344" t="s">
+        <v>68</v>
+      </c>
+      <c r="D344" t="s">
+        <v>69</v>
+      </c>
+      <c r="E344" s="2">
+        <v>45738.51041666666</v>
+      </c>
+      <c r="F344">
+        <v>32</v>
+      </c>
+      <c r="G344" t="s">
+        <v>79</v>
+      </c>
+      <c r="H344" t="s">
+        <v>80</v>
+      </c>
+      <c r="I344">
+        <v>0</v>
+      </c>
+      <c r="J344">
+        <v>0</v>
+      </c>
+      <c r="K344">
+        <v>0</v>
+      </c>
+      <c r="L344">
+        <v>2</v>
+      </c>
+      <c r="M344">
+        <v>0</v>
+      </c>
+      <c r="N344">
+        <v>2</v>
+      </c>
+      <c r="O344" t="s">
+        <v>306</v>
+      </c>
+      <c r="P344" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q344">
+        <v>2.25</v>
+      </c>
+      <c r="R344">
+        <v>2.1</v>
+      </c>
+      <c r="S344">
+        <v>6</v>
+      </c>
+      <c r="T344">
+        <v>1.44</v>
+      </c>
+      <c r="U344">
+        <v>2.63</v>
+      </c>
+      <c r="V344">
+        <v>3.25</v>
+      </c>
+      <c r="W344">
+        <v>1.33</v>
+      </c>
+      <c r="X344">
+        <v>10</v>
+      </c>
+      <c r="Y344">
+        <v>1.06</v>
+      </c>
+      <c r="Z344">
+        <v>1.66</v>
+      </c>
+      <c r="AA344">
+        <v>3.84</v>
+      </c>
+      <c r="AB344">
+        <v>5.8</v>
+      </c>
+      <c r="AC344">
+        <v>1.06</v>
+      </c>
+      <c r="AD344">
+        <v>8.5</v>
+      </c>
+      <c r="AE344">
+        <v>1.36</v>
+      </c>
+      <c r="AF344">
+        <v>3.1</v>
+      </c>
+      <c r="AG344">
+        <v>2.05</v>
+      </c>
+      <c r="AH344">
+        <v>1.65</v>
+      </c>
+      <c r="AI344">
+        <v>2.2</v>
+      </c>
+      <c r="AJ344">
+        <v>1.62</v>
+      </c>
+      <c r="AK344">
+        <v>1.13</v>
+      </c>
+      <c r="AL344">
+        <v>1.26</v>
+      </c>
+      <c r="AM344">
+        <v>2.25</v>
+      </c>
+      <c r="AN344">
+        <v>2.38</v>
+      </c>
+      <c r="AO344">
+        <v>1.07</v>
+      </c>
+      <c r="AP344">
+        <v>2.41</v>
+      </c>
+      <c r="AQ344">
+        <v>1</v>
+      </c>
+      <c r="AR344">
+        <v>1.67</v>
+      </c>
+      <c r="AS344">
+        <v>1.16</v>
+      </c>
+      <c r="AT344">
+        <v>2.83</v>
+      </c>
+      <c r="AU344">
+        <v>8</v>
+      </c>
+      <c r="AV344">
+        <v>2</v>
+      </c>
+      <c r="AW344">
+        <v>9</v>
+      </c>
+      <c r="AX344">
+        <v>4</v>
+      </c>
+      <c r="AY344">
+        <v>18</v>
+      </c>
+      <c r="AZ344">
+        <v>7</v>
+      </c>
+      <c r="BA344">
+        <v>5</v>
+      </c>
+      <c r="BB344">
+        <v>4</v>
+      </c>
+      <c r="BC344">
+        <v>9</v>
+      </c>
+      <c r="BD344">
+        <v>1.38</v>
+      </c>
+      <c r="BE344">
+        <v>7</v>
+      </c>
+      <c r="BF344">
+        <v>3.4</v>
+      </c>
+      <c r="BG344">
+        <v>1.4</v>
+      </c>
+      <c r="BH344">
+        <v>2.65</v>
+      </c>
+      <c r="BI344">
+        <v>1.68</v>
+      </c>
+      <c r="BJ344">
+        <v>2.02</v>
+      </c>
+      <c r="BK344">
+        <v>2.08</v>
+      </c>
+      <c r="BL344">
+        <v>1.63</v>
+      </c>
+      <c r="BM344">
+        <v>2.65</v>
+      </c>
+      <c r="BN344">
+        <v>1.4</v>
+      </c>
+      <c r="BO344">
+        <v>3.55</v>
+      </c>
+      <c r="BP344">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="345" spans="1:68">
+      <c r="A345" s="1">
+        <v>344</v>
+      </c>
+      <c r="B345">
+        <v>7728541</v>
+      </c>
+      <c r="C345" t="s">
+        <v>68</v>
+      </c>
+      <c r="D345" t="s">
+        <v>69</v>
+      </c>
+      <c r="E345" s="2">
+        <v>45738.60416666666</v>
+      </c>
+      <c r="F345">
+        <v>32</v>
+      </c>
+      <c r="G345" t="s">
+        <v>71</v>
+      </c>
+      <c r="H345" t="s">
+        <v>77</v>
+      </c>
+      <c r="I345">
+        <v>0</v>
+      </c>
+      <c r="J345">
+        <v>1</v>
+      </c>
+      <c r="K345">
+        <v>1</v>
+      </c>
+      <c r="L345">
+        <v>2</v>
+      </c>
+      <c r="M345">
+        <v>1</v>
+      </c>
+      <c r="N345">
+        <v>3</v>
+      </c>
+      <c r="O345" t="s">
+        <v>307</v>
+      </c>
+      <c r="P345" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q345">
+        <v>2.88</v>
+      </c>
+      <c r="R345">
+        <v>2.05</v>
+      </c>
+      <c r="S345">
+        <v>4</v>
+      </c>
+      <c r="T345">
+        <v>1.5</v>
+      </c>
+      <c r="U345">
+        <v>2.5</v>
+      </c>
+      <c r="V345">
+        <v>3.4</v>
+      </c>
+      <c r="W345">
+        <v>1.3</v>
+      </c>
+      <c r="X345">
+        <v>10</v>
+      </c>
+      <c r="Y345">
+        <v>1.06</v>
+      </c>
+      <c r="Z345">
+        <v>2.17</v>
+      </c>
+      <c r="AA345">
+        <v>3.29</v>
+      </c>
+      <c r="AB345">
+        <v>3.7</v>
+      </c>
+      <c r="AC345">
+        <v>1.07</v>
+      </c>
+      <c r="AD345">
+        <v>8</v>
+      </c>
+      <c r="AE345">
+        <v>1.4</v>
+      </c>
+      <c r="AF345">
+        <v>2.9</v>
+      </c>
+      <c r="AG345">
+        <v>2.13</v>
+      </c>
+      <c r="AH345">
+        <v>1.7</v>
+      </c>
+      <c r="AI345">
+        <v>2</v>
+      </c>
+      <c r="AJ345">
+        <v>1.73</v>
+      </c>
+      <c r="AK345">
+        <v>1.3</v>
+      </c>
+      <c r="AL345">
+        <v>1.32</v>
+      </c>
+      <c r="AM345">
+        <v>1.68</v>
+      </c>
+      <c r="AN345">
+        <v>2.44</v>
+      </c>
+      <c r="AO345">
+        <v>1.87</v>
+      </c>
+      <c r="AP345">
+        <v>2.47</v>
+      </c>
+      <c r="AQ345">
+        <v>1.75</v>
+      </c>
+      <c r="AR345">
+        <v>1.38</v>
+      </c>
+      <c r="AS345">
+        <v>1.36</v>
+      </c>
+      <c r="AT345">
+        <v>2.74</v>
+      </c>
+      <c r="AU345">
+        <v>10</v>
+      </c>
+      <c r="AV345">
+        <v>7</v>
+      </c>
+      <c r="AW345">
+        <v>12</v>
+      </c>
+      <c r="AX345">
+        <v>1</v>
+      </c>
+      <c r="AY345">
+        <v>26</v>
+      </c>
+      <c r="AZ345">
+        <v>8</v>
+      </c>
+      <c r="BA345">
+        <v>6</v>
+      </c>
+      <c r="BB345">
+        <v>2</v>
+      </c>
+      <c r="BC345">
+        <v>8</v>
+      </c>
+      <c r="BD345">
+        <v>1.73</v>
+      </c>
+      <c r="BE345">
+        <v>6.4</v>
+      </c>
+      <c r="BF345">
+        <v>2.33</v>
+      </c>
+      <c r="BG345">
+        <v>1.41</v>
+      </c>
+      <c r="BH345">
+        <v>2.63</v>
+      </c>
+      <c r="BI345">
+        <v>1.7</v>
+      </c>
+      <c r="BJ345">
+        <v>1.98</v>
+      </c>
+      <c r="BK345">
+        <v>2.12</v>
+      </c>
+      <c r="BL345">
+        <v>1.61</v>
+      </c>
+      <c r="BM345">
+        <v>2.8</v>
+      </c>
+      <c r="BN345">
+        <v>1.36</v>
+      </c>
+      <c r="BO345">
+        <v>3.65</v>
+      </c>
+      <c r="BP345">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="346" spans="1:68">
+      <c r="A346" s="1">
+        <v>345</v>
+      </c>
+      <c r="B346">
+        <v>7728548</v>
+      </c>
+      <c r="C346" t="s">
+        <v>68</v>
+      </c>
+      <c r="D346" t="s">
+        <v>69</v>
+      </c>
+      <c r="E346" s="2">
+        <v>45738.60416666666</v>
+      </c>
+      <c r="F346">
+        <v>32</v>
+      </c>
+      <c r="G346" t="s">
+        <v>83</v>
+      </c>
+      <c r="H346" t="s">
+        <v>74</v>
+      </c>
+      <c r="I346">
+        <v>2</v>
+      </c>
+      <c r="J346">
+        <v>0</v>
+      </c>
+      <c r="K346">
+        <v>2</v>
+      </c>
+      <c r="L346">
+        <v>2</v>
+      </c>
+      <c r="M346">
+        <v>0</v>
+      </c>
+      <c r="N346">
+        <v>2</v>
+      </c>
+      <c r="O346" t="s">
+        <v>308</v>
+      </c>
+      <c r="P346" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q346">
+        <v>2.6</v>
+      </c>
+      <c r="R346">
+        <v>1.95</v>
+      </c>
+      <c r="S346">
+        <v>5.5</v>
+      </c>
+      <c r="T346">
+        <v>1.57</v>
+      </c>
+      <c r="U346">
+        <v>2.25</v>
+      </c>
+      <c r="V346">
+        <v>3.75</v>
+      </c>
+      <c r="W346">
+        <v>1.25</v>
+      </c>
+      <c r="X346">
+        <v>13</v>
+      </c>
+      <c r="Y346">
+        <v>1.04</v>
+      </c>
+      <c r="Z346">
+        <v>1.92</v>
+      </c>
+      <c r="AA346">
+        <v>3.33</v>
+      </c>
+      <c r="AB346">
+        <v>4.7</v>
+      </c>
+      <c r="AC346">
+        <v>1.1</v>
+      </c>
+      <c r="AD346">
+        <v>6.5</v>
+      </c>
+      <c r="AE346">
+        <v>1.5</v>
+      </c>
+      <c r="AF346">
+        <v>2.4</v>
+      </c>
+      <c r="AG346">
+        <v>2.37</v>
+      </c>
+      <c r="AH346">
+        <v>1.48</v>
+      </c>
+      <c r="AI346">
+        <v>2.25</v>
+      </c>
+      <c r="AJ346">
+        <v>1.57</v>
+      </c>
+      <c r="AK346">
+        <v>1.2</v>
+      </c>
+      <c r="AL346">
+        <v>1.33</v>
+      </c>
+      <c r="AM346">
+        <v>1.85</v>
+      </c>
+      <c r="AN346">
+        <v>1.6</v>
+      </c>
+      <c r="AO346">
+        <v>0.87</v>
+      </c>
+      <c r="AP346">
+        <v>1.69</v>
+      </c>
+      <c r="AQ346">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR346">
+        <v>1.35</v>
+      </c>
+      <c r="AS346">
+        <v>0.92</v>
+      </c>
+      <c r="AT346">
+        <v>2.27</v>
+      </c>
+      <c r="AU346">
+        <v>7</v>
+      </c>
+      <c r="AV346">
+        <v>2</v>
+      </c>
+      <c r="AW346">
+        <v>2</v>
+      </c>
+      <c r="AX346">
+        <v>13</v>
+      </c>
+      <c r="AY346">
+        <v>9</v>
+      </c>
+      <c r="AZ346">
+        <v>20</v>
+      </c>
+      <c r="BA346">
+        <v>2</v>
+      </c>
+      <c r="BB346">
+        <v>2</v>
+      </c>
+      <c r="BC346">
+        <v>4</v>
+      </c>
+      <c r="BD346">
+        <v>1.52</v>
+      </c>
+      <c r="BE346">
+        <v>6.75</v>
+      </c>
+      <c r="BF346">
+        <v>2.8</v>
+      </c>
+      <c r="BG346">
+        <v>1.42</v>
+      </c>
+      <c r="BH346">
+        <v>2.55</v>
+      </c>
+      <c r="BI346">
+        <v>1.71</v>
+      </c>
+      <c r="BJ346">
+        <v>1.97</v>
+      </c>
+      <c r="BK346">
+        <v>2.16</v>
+      </c>
+      <c r="BL346">
+        <v>1.58</v>
+      </c>
+      <c r="BM346">
+        <v>2.8</v>
+      </c>
+      <c r="BN346">
+        <v>1.36</v>
+      </c>
+      <c r="BO346">
+        <v>3.65</v>
+      </c>
+      <c r="BP346">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2144" uniqueCount="421">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -943,6 +943,9 @@
     <t>['9', '39']</t>
   </si>
   <si>
+    <t>['11']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -974,9 +977,6 @@
   </si>
   <si>
     <t>['26', '54']</t>
-  </si>
-  <si>
-    <t>['11']</t>
   </si>
   <si>
     <t>['64', '69']</t>
@@ -1638,7 +1638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP346"/>
+  <dimension ref="A1:BP347"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1894,7 +1894,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ2">
         <v>0.87</v>
@@ -2306,7 +2306,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3005,7 +3005,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ7">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3130,7 +3130,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3336,7 +3336,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4160,7 +4160,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -5396,7 +5396,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5889,7 +5889,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ21">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6220,7 +6220,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6426,7 +6426,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6504,7 +6504,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ24">
         <v>1.38</v>
@@ -6632,7 +6632,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6838,7 +6838,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7044,7 +7044,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -8692,7 +8692,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8976,7 +8976,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ36">
         <v>1.44</v>
@@ -9391,7 +9391,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ38">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR38">
         <v>1.41</v>
@@ -13302,7 +13302,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ57">
         <v>0.9399999999999999</v>
@@ -13717,7 +13717,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ59">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR59">
         <v>1.51</v>
@@ -19691,7 +19691,7 @@
         <v>2</v>
       </c>
       <c r="AQ88">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR88">
         <v>1.96</v>
@@ -21542,7 +21542,7 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ97">
         <v>1.13</v>
@@ -22575,7 +22575,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ102">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR102">
         <v>1.13</v>
@@ -22984,7 +22984,7 @@
         <v>0.25</v>
       </c>
       <c r="AP104">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ104">
         <v>0.19</v>
@@ -26901,7 +26901,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ123">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR123">
         <v>1.53</v>
@@ -27026,7 +27026,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -28752,7 +28752,7 @@
         <v>1.17</v>
       </c>
       <c r="AP132">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ132">
         <v>1.63</v>
@@ -30940,7 +30940,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31224,7 +31224,7 @@
         <v>0.83</v>
       </c>
       <c r="AP144">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -32257,7 +32257,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ149">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR149">
         <v>1.82</v>
@@ -35550,7 +35550,7 @@
         <v>1.14</v>
       </c>
       <c r="AP165">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ165">
         <v>1.33</v>
@@ -37201,7 +37201,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ173">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR173">
         <v>1.44</v>
@@ -40700,7 +40700,7 @@
         <v>2.75</v>
       </c>
       <c r="AP190">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ190">
         <v>1.75</v>
@@ -41321,7 +41321,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ193">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR193">
         <v>1.13</v>
@@ -43094,7 +43094,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -44614,7 +44614,7 @@
         <v>0.6</v>
       </c>
       <c r="AP209">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ209">
         <v>0.44</v>
@@ -45235,7 +45235,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ212">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR212">
         <v>1.69</v>
@@ -49352,7 +49352,7 @@
         <v>0.8</v>
       </c>
       <c r="AP232">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ232">
         <v>1.13</v>
@@ -51621,7 +51621,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ243">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR243">
         <v>1.18</v>
@@ -54914,7 +54914,7 @@
         <v>1.09</v>
       </c>
       <c r="AP259">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ259">
         <v>1</v>
@@ -56771,7 +56771,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ268">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR268">
         <v>1.8</v>
@@ -58828,7 +58828,7 @@
         <v>1.17</v>
       </c>
       <c r="AP278">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ278">
         <v>1.07</v>
@@ -63363,7 +63363,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ300">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR300">
         <v>1.42</v>
@@ -63772,7 +63772,7 @@
         <v>1.36</v>
       </c>
       <c r="AP302">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ302">
         <v>1.25</v>
@@ -68101,7 +68101,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ323">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AR323">
         <v>1.37</v>
@@ -69540,7 +69540,7 @@
         <v>0.93</v>
       </c>
       <c r="AP330">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ330">
         <v>0.8100000000000001</v>
@@ -72915,6 +72915,212 @@
       </c>
       <c r="BP346">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="347" spans="1:68">
+      <c r="A347" s="1">
+        <v>346</v>
+      </c>
+      <c r="B347">
+        <v>7728540</v>
+      </c>
+      <c r="C347" t="s">
+        <v>68</v>
+      </c>
+      <c r="D347" t="s">
+        <v>69</v>
+      </c>
+      <c r="E347" s="2">
+        <v>45738.70833333334</v>
+      </c>
+      <c r="F347">
+        <v>32</v>
+      </c>
+      <c r="G347" t="s">
+        <v>70</v>
+      </c>
+      <c r="H347" t="s">
+        <v>89</v>
+      </c>
+      <c r="I347">
+        <v>1</v>
+      </c>
+      <c r="J347">
+        <v>0</v>
+      </c>
+      <c r="K347">
+        <v>1</v>
+      </c>
+      <c r="L347">
+        <v>1</v>
+      </c>
+      <c r="M347">
+        <v>0</v>
+      </c>
+      <c r="N347">
+        <v>1</v>
+      </c>
+      <c r="O347" t="s">
+        <v>309</v>
+      </c>
+      <c r="P347" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q347">
+        <v>3.2</v>
+      </c>
+      <c r="R347">
+        <v>1.91</v>
+      </c>
+      <c r="S347">
+        <v>4.33</v>
+      </c>
+      <c r="T347">
+        <v>1.57</v>
+      </c>
+      <c r="U347">
+        <v>2.25</v>
+      </c>
+      <c r="V347">
+        <v>3.75</v>
+      </c>
+      <c r="W347">
+        <v>1.25</v>
+      </c>
+      <c r="X347">
+        <v>13</v>
+      </c>
+      <c r="Y347">
+        <v>1.04</v>
+      </c>
+      <c r="Z347">
+        <v>2.28</v>
+      </c>
+      <c r="AA347">
+        <v>3.1</v>
+      </c>
+      <c r="AB347">
+        <v>3.66</v>
+      </c>
+      <c r="AC347">
+        <v>1.11</v>
+      </c>
+      <c r="AD347">
+        <v>6.25</v>
+      </c>
+      <c r="AE347">
+        <v>1.5</v>
+      </c>
+      <c r="AF347">
+        <v>2.4</v>
+      </c>
+      <c r="AG347">
+        <v>2.3</v>
+      </c>
+      <c r="AH347">
+        <v>1.5</v>
+      </c>
+      <c r="AI347">
+        <v>2.2</v>
+      </c>
+      <c r="AJ347">
+        <v>1.62</v>
+      </c>
+      <c r="AK347">
+        <v>1.29</v>
+      </c>
+      <c r="AL347">
+        <v>1.35</v>
+      </c>
+      <c r="AM347">
+        <v>1.65</v>
+      </c>
+      <c r="AN347">
+        <v>1.69</v>
+      </c>
+      <c r="AO347">
+        <v>1.4</v>
+      </c>
+      <c r="AP347">
+        <v>1.76</v>
+      </c>
+      <c r="AQ347">
+        <v>1.31</v>
+      </c>
+      <c r="AR347">
+        <v>1.66</v>
+      </c>
+      <c r="AS347">
+        <v>1.32</v>
+      </c>
+      <c r="AT347">
+        <v>2.98</v>
+      </c>
+      <c r="AU347">
+        <v>6</v>
+      </c>
+      <c r="AV347">
+        <v>4</v>
+      </c>
+      <c r="AW347">
+        <v>8</v>
+      </c>
+      <c r="AX347">
+        <v>6</v>
+      </c>
+      <c r="AY347">
+        <v>16</v>
+      </c>
+      <c r="AZ347">
+        <v>11</v>
+      </c>
+      <c r="BA347">
+        <v>5</v>
+      </c>
+      <c r="BB347">
+        <v>5</v>
+      </c>
+      <c r="BC347">
+        <v>10</v>
+      </c>
+      <c r="BD347">
+        <v>1.67</v>
+      </c>
+      <c r="BE347">
+        <v>6.4</v>
+      </c>
+      <c r="BF347">
+        <v>2.48</v>
+      </c>
+      <c r="BG347">
+        <v>1.5</v>
+      </c>
+      <c r="BH347">
+        <v>2.33</v>
+      </c>
+      <c r="BI347">
+        <v>1.85</v>
+      </c>
+      <c r="BJ347">
+        <v>1.81</v>
+      </c>
+      <c r="BK347">
+        <v>2.38</v>
+      </c>
+      <c r="BL347">
+        <v>1.49</v>
+      </c>
+      <c r="BM347">
+        <v>3.15</v>
+      </c>
+      <c r="BN347">
+        <v>1.29</v>
+      </c>
+      <c r="BO347">
+        <v>4.1</v>
+      </c>
+      <c r="BP347">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2144" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="423">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -946,6 +946,9 @@
     <t>['11']</t>
   </si>
   <si>
+    <t>['34', '45+3', '88']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1277,6 +1280,9 @@
   </si>
   <si>
     <t>['6', '57']</t>
+  </si>
+  <si>
+    <t>['27', '55']</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP347"/>
+  <dimension ref="A1:BP348"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1894,7 +1900,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2306,7 +2312,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2593,7 +2599,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ5">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -3130,7 +3136,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3336,7 +3342,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4160,7 +4166,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -5062,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ17">
         <v>1.33</v>
@@ -5396,7 +5402,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -6014,7 +6020,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6220,7 +6226,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6426,7 +6432,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6632,7 +6638,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6838,7 +6844,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7456,7 +7462,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7537,7 +7543,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ29">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR29">
         <v>1.44</v>
@@ -8074,7 +8080,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8280,7 +8286,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8692,7 +8698,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -10546,7 +10552,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11164,7 +11170,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11242,7 +11248,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ47">
         <v>1</v>
@@ -12812,7 +12818,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -13018,7 +13024,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13099,7 +13105,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ56">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR56">
         <v>1.94</v>
@@ -13224,7 +13230,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13430,7 +13436,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13842,7 +13848,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14460,7 +14466,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -15078,7 +15084,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15490,7 +15496,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15696,7 +15702,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16314,7 +16320,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16520,7 +16526,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16598,7 +16604,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ73">
         <v>1.29</v>
@@ -16726,7 +16732,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17550,7 +17556,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17756,7 +17762,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18168,7 +18174,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18374,7 +18380,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18580,7 +18586,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19404,7 +19410,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19485,7 +19491,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ87">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR87">
         <v>1.47</v>
@@ -19688,7 +19694,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ88">
         <v>1.31</v>
@@ -19816,7 +19822,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -20022,7 +20028,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20434,7 +20440,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20846,7 +20852,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -21052,7 +21058,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -22082,7 +22088,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22163,7 +22169,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ100">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -23524,7 +23530,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24142,7 +24148,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24554,7 +24560,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24760,7 +24766,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25172,7 +25178,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25996,7 +26002,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26074,7 +26080,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ119">
         <v>1.44</v>
@@ -26614,7 +26620,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -27026,7 +27032,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27438,7 +27444,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27519,7 +27525,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ126">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR126">
         <v>1.8</v>
@@ -27850,7 +27856,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28262,7 +28268,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28468,7 +28474,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28674,7 +28680,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29086,7 +29092,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29292,7 +29298,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29910,7 +29916,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30528,7 +30534,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30734,7 +30740,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30940,7 +30946,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31146,7 +31152,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31558,7 +31564,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31639,7 +31645,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ146">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR146">
         <v>1.62</v>
@@ -31970,7 +31976,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -33000,7 +33006,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33284,7 +33290,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ154">
         <v>1.07</v>
@@ -33618,7 +33624,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -35266,7 +35272,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35884,7 +35890,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36914,7 +36920,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -36995,7 +37001,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ172">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR172">
         <v>1.15</v>
@@ -37532,7 +37538,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37610,7 +37616,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ175">
         <v>0.9399999999999999</v>
@@ -37944,7 +37950,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38356,7 +38362,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38562,7 +38568,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39386,7 +39392,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39464,7 +39470,7 @@
         <v>0.88</v>
       </c>
       <c r="AP184">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ184">
         <v>1.13</v>
@@ -40210,7 +40216,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40828,7 +40834,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -41034,7 +41040,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41240,7 +41246,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41446,7 +41452,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41733,7 +41739,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ195">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR195">
         <v>1.66</v>
@@ -42682,7 +42688,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42760,7 +42766,7 @@
         <v>0.11</v>
       </c>
       <c r="AP200">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ200">
         <v>1.13</v>
@@ -43094,7 +43100,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43300,7 +43306,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43918,7 +43924,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44948,7 +44954,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45154,7 +45160,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45360,7 +45366,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45566,7 +45572,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45978,7 +45984,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46471,7 +46477,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ218">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR218">
         <v>1.41</v>
@@ -47214,7 +47220,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47626,7 +47632,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -48038,7 +48044,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48656,7 +48662,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48862,7 +48868,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48940,7 +48946,7 @@
         <v>1.3</v>
       </c>
       <c r="AP230">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ230">
         <v>1.38</v>
@@ -49068,7 +49074,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49892,7 +49898,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50179,7 +50185,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ236">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR236">
         <v>1.23</v>
@@ -50716,7 +50722,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51334,7 +51340,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51746,7 +51752,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52158,7 +52164,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52442,7 +52448,7 @@
         <v>1.5</v>
       </c>
       <c r="AP247">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ247">
         <v>1.27</v>
@@ -52982,7 +52988,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53188,7 +53194,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53600,7 +53606,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -54012,7 +54018,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54218,7 +54224,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -55123,7 +55129,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ260">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR260">
         <v>1.59</v>
@@ -55248,7 +55254,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55454,7 +55460,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -56072,7 +56078,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -57514,7 +57520,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -58210,7 +58216,7 @@
         <v>0.91</v>
       </c>
       <c r="AP275">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ275">
         <v>0.8100000000000001</v>
@@ -58544,7 +58550,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58625,7 +58631,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ277">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR277">
         <v>1.22</v>
@@ -59780,7 +59786,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59986,7 +59992,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60604,7 +60610,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61222,7 +61228,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61428,7 +61434,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61712,7 +61718,7 @@
         <v>1</v>
       </c>
       <c r="AP292">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ292">
         <v>1</v>
@@ -63282,7 +63288,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63488,7 +63494,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63694,7 +63700,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -64596,7 +64602,7 @@
         <v>1.15</v>
       </c>
       <c r="AP306">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ306">
         <v>1.07</v>
@@ -65011,7 +65017,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ308">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR308">
         <v>1.45</v>
@@ -65136,7 +65142,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65960,7 +65966,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66372,7 +66378,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66578,7 +66584,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -68307,7 +68313,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ324">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR324">
         <v>1.69</v>
@@ -68638,7 +68644,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -69050,7 +69056,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -69334,7 +69340,7 @@
         <v>0.47</v>
       </c>
       <c r="AP329">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ329">
         <v>0.44</v>
@@ -71110,7 +71116,7 @@
         <v>302</v>
       </c>
       <c r="P338" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q338">
         <v>3.5</v>
@@ -71316,7 +71322,7 @@
         <v>183</v>
       </c>
       <c r="P339" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q339">
         <v>3.4</v>
@@ -71934,7 +71940,7 @@
         <v>304</v>
       </c>
       <c r="P342" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q342">
         <v>2.88</v>
@@ -73121,6 +73127,212 @@
       </c>
       <c r="BP347">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="348" spans="1:68">
+      <c r="A348" s="1">
+        <v>347</v>
+      </c>
+      <c r="B348">
+        <v>7728546</v>
+      </c>
+      <c r="C348" t="s">
+        <v>68</v>
+      </c>
+      <c r="D348" t="s">
+        <v>69</v>
+      </c>
+      <c r="E348" s="2">
+        <v>45739.41666666666</v>
+      </c>
+      <c r="F348">
+        <v>32</v>
+      </c>
+      <c r="G348" t="s">
+        <v>82</v>
+      </c>
+      <c r="H348" t="s">
+        <v>86</v>
+      </c>
+      <c r="I348">
+        <v>2</v>
+      </c>
+      <c r="J348">
+        <v>1</v>
+      </c>
+      <c r="K348">
+        <v>3</v>
+      </c>
+      <c r="L348">
+        <v>3</v>
+      </c>
+      <c r="M348">
+        <v>2</v>
+      </c>
+      <c r="N348">
+        <v>5</v>
+      </c>
+      <c r="O348" t="s">
+        <v>310</v>
+      </c>
+      <c r="P348" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q348">
+        <v>2.3</v>
+      </c>
+      <c r="R348">
+        <v>2.25</v>
+      </c>
+      <c r="S348">
+        <v>4.2</v>
+      </c>
+      <c r="T348">
+        <v>1.3</v>
+      </c>
+      <c r="U348">
+        <v>3.2</v>
+      </c>
+      <c r="V348">
+        <v>2.4</v>
+      </c>
+      <c r="W348">
+        <v>1.5</v>
+      </c>
+      <c r="X348">
+        <v>5.9</v>
+      </c>
+      <c r="Y348">
+        <v>1.07</v>
+      </c>
+      <c r="Z348">
+        <v>1.73</v>
+      </c>
+      <c r="AA348">
+        <v>4.2</v>
+      </c>
+      <c r="AB348">
+        <v>4.6</v>
+      </c>
+      <c r="AC348">
+        <v>1.04</v>
+      </c>
+      <c r="AD348">
+        <v>10</v>
+      </c>
+      <c r="AE348">
+        <v>1.22</v>
+      </c>
+      <c r="AF348">
+        <v>4.2</v>
+      </c>
+      <c r="AG348">
+        <v>1.83</v>
+      </c>
+      <c r="AH348">
+        <v>1.98</v>
+      </c>
+      <c r="AI348">
+        <v>1.6</v>
+      </c>
+      <c r="AJ348">
+        <v>2.15</v>
+      </c>
+      <c r="AK348">
+        <v>1.22</v>
+      </c>
+      <c r="AL348">
+        <v>1.2</v>
+      </c>
+      <c r="AM348">
+        <v>1.95</v>
+      </c>
+      <c r="AN348">
+        <v>2</v>
+      </c>
+      <c r="AO348">
+        <v>1.27</v>
+      </c>
+      <c r="AP348">
+        <v>2.06</v>
+      </c>
+      <c r="AQ348">
+        <v>1.19</v>
+      </c>
+      <c r="AR348">
+        <v>1.69</v>
+      </c>
+      <c r="AS348">
+        <v>1.26</v>
+      </c>
+      <c r="AT348">
+        <v>2.95</v>
+      </c>
+      <c r="AU348">
+        <v>5</v>
+      </c>
+      <c r="AV348">
+        <v>5</v>
+      </c>
+      <c r="AW348">
+        <v>8</v>
+      </c>
+      <c r="AX348">
+        <v>11</v>
+      </c>
+      <c r="AY348">
+        <v>15</v>
+      </c>
+      <c r="AZ348">
+        <v>20</v>
+      </c>
+      <c r="BA348">
+        <v>4</v>
+      </c>
+      <c r="BB348">
+        <v>3</v>
+      </c>
+      <c r="BC348">
+        <v>7</v>
+      </c>
+      <c r="BD348">
+        <v>1.54</v>
+      </c>
+      <c r="BE348">
+        <v>6.75</v>
+      </c>
+      <c r="BF348">
+        <v>2.8</v>
+      </c>
+      <c r="BG348">
+        <v>1.3</v>
+      </c>
+      <c r="BH348">
+        <v>3.05</v>
+      </c>
+      <c r="BI348">
+        <v>1.54</v>
+      </c>
+      <c r="BJ348">
+        <v>2.28</v>
+      </c>
+      <c r="BK348">
+        <v>1.87</v>
+      </c>
+      <c r="BL348">
+        <v>1.79</v>
+      </c>
+      <c r="BM348">
+        <v>2.38</v>
+      </c>
+      <c r="BN348">
+        <v>1.49</v>
+      </c>
+      <c r="BO348">
+        <v>3.05</v>
+      </c>
+      <c r="BP348">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="429">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -949,6 +949,15 @@
     <t>['34', '45+3', '88']</t>
   </si>
   <si>
+    <t>['51', '56']</t>
+  </si>
+  <si>
+    <t>['25', '84']</t>
+  </si>
+  <si>
+    <t>['69', '86']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1283,6 +1292,15 @@
   </si>
   <si>
     <t>['27', '55']</t>
+  </si>
+  <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['45+6', '90+7']</t>
+  </si>
+  <si>
+    <t>['59', '76']</t>
   </si>
 </sst>
 </file>
@@ -1644,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP348"/>
+  <dimension ref="A1:BP352"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1900,7 +1918,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1981,7 +1999,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ2">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2312,7 +2330,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2596,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ5">
         <v>1.19</v>
@@ -3008,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ7">
         <v>1.31</v>
@@ -3136,7 +3154,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3214,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ8">
         <v>1.63</v>
@@ -3342,7 +3360,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3629,7 +3647,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ10">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3835,7 +3853,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ11">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4166,7 +4184,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4656,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -5071,7 +5089,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5402,7 +5420,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5480,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ19">
         <v>1.29</v>
@@ -6020,7 +6038,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6226,7 +6244,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6432,7 +6450,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6513,7 +6531,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ24">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR24">
         <v>2.51</v>
@@ -6638,7 +6656,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6844,7 +6862,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7131,7 +7149,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ27">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.25</v>
@@ -7462,7 +7480,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7746,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ30">
         <v>0.8100000000000001</v>
@@ -8080,7 +8098,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8161,7 +8179,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ32">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR32">
         <v>1.31</v>
@@ -8286,7 +8304,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8364,7 +8382,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ33">
         <v>1.63</v>
@@ -8698,7 +8716,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8776,7 +8794,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ35">
         <v>1.75</v>
@@ -9394,7 +9412,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ38">
         <v>1.31</v>
@@ -10552,7 +10570,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10633,7 +10651,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -11170,7 +11188,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11454,7 +11472,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ48">
         <v>0.19</v>
@@ -11663,7 +11681,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ49">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR49">
         <v>1.38</v>
@@ -12075,7 +12093,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ51">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>0.76</v>
@@ -12281,7 +12299,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ52">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR52">
         <v>1.28</v>
@@ -12818,7 +12836,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -13024,7 +13042,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13230,7 +13248,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13436,7 +13454,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13517,7 +13535,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ58">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR58">
         <v>1.22</v>
@@ -13848,7 +13866,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13926,7 +13944,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ60">
         <v>1.13</v>
@@ -14338,7 +14356,7 @@
         <v>0.5</v>
       </c>
       <c r="AP62">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14466,7 +14484,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14547,7 +14565,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR63">
         <v>1.13</v>
@@ -15084,7 +15102,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15496,7 +15514,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15702,7 +15720,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15989,7 +16007,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ70">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR70">
         <v>1.04</v>
@@ -16192,7 +16210,7 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ71">
         <v>1.25</v>
@@ -16320,7 +16338,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16526,7 +16544,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16732,7 +16750,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17556,7 +17574,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17637,7 +17655,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ78">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR78">
         <v>1.42</v>
@@ -17762,7 +17780,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17843,7 +17861,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ79">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR79">
         <v>1.18</v>
@@ -18174,7 +18192,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18380,7 +18398,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18458,7 +18476,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ82">
         <v>1</v>
@@ -18586,7 +18604,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19076,10 +19094,10 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ85">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -19282,7 +19300,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ86">
         <v>0.9399999999999999</v>
@@ -19410,7 +19428,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19822,7 +19840,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -20028,7 +20046,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20106,7 +20124,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ90">
         <v>1.25</v>
@@ -20440,7 +20458,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20724,7 +20742,7 @@
         <v>1.33</v>
       </c>
       <c r="AP93">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20852,7 +20870,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20933,7 +20951,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ94">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.16</v>
@@ -21058,7 +21076,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -22088,7 +22106,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22166,7 +22184,7 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ100">
         <v>1.19</v>
@@ -22375,7 +22393,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ101">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR101">
         <v>1.58</v>
@@ -22784,7 +22802,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ103">
         <v>1</v>
@@ -23530,7 +23548,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23817,7 +23835,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ108">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR108">
         <v>1.17</v>
@@ -24148,7 +24166,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24560,7 +24578,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24766,7 +24784,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25050,10 +25068,10 @@
         <v>1.75</v>
       </c>
       <c r="AP114">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ114">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -25178,7 +25196,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25877,7 +25895,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ118">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>1.69</v>
@@ -26002,7 +26020,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26286,10 +26304,10 @@
         <v>1.4</v>
       </c>
       <c r="AP120">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ120">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR120">
         <v>1.6</v>
@@ -26492,7 +26510,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ121">
         <v>0.9399999999999999</v>
@@ -26620,7 +26638,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -27032,7 +27050,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27113,7 +27131,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ124">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR124">
         <v>1.12</v>
@@ -27444,7 +27462,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27856,7 +27874,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27934,7 +27952,7 @@
         <v>3</v>
       </c>
       <c r="AP128">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ128">
         <v>1.75</v>
@@ -28268,7 +28286,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28474,7 +28492,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28680,7 +28698,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29092,7 +29110,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29170,7 +29188,7 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ134">
         <v>1.07</v>
@@ -29298,7 +29316,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29582,10 +29600,10 @@
         <v>1.4</v>
       </c>
       <c r="AP136">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ136">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -29916,7 +29934,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29997,7 +30015,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ138">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR138">
         <v>1.52</v>
@@ -30406,7 +30424,7 @@
         <v>1</v>
       </c>
       <c r="AP140">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ140">
         <v>1.07</v>
@@ -30534,7 +30552,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30740,7 +30758,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30821,7 +30839,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ142">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR142">
         <v>1.16</v>
@@ -30946,7 +30964,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31152,7 +31170,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31439,7 +31457,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ145">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR145">
         <v>1.15</v>
@@ -31564,7 +31582,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31976,7 +31994,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32466,7 +32484,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ150">
         <v>0.8100000000000001</v>
@@ -32672,7 +32690,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ151">
         <v>0.8100000000000001</v>
@@ -32881,7 +32899,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ152">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>1.54</v>
@@ -33006,7 +33024,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33624,7 +33642,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33702,7 +33720,7 @@
         <v>1.83</v>
       </c>
       <c r="AP156">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ156">
         <v>1.27</v>
@@ -34529,7 +34547,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ160">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34941,7 +34959,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ162">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR162">
         <v>1.47</v>
@@ -35272,7 +35290,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35559,7 +35577,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ165">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR165">
         <v>1.7</v>
@@ -35890,7 +35908,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36586,7 +36604,7 @@
         <v>1.29</v>
       </c>
       <c r="AP170">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36920,7 +36938,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37538,7 +37556,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37950,7 +37968,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38031,7 +38049,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ177">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR177">
         <v>1.68</v>
@@ -38237,7 +38255,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ178">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR178">
         <v>1.71</v>
@@ -38362,7 +38380,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38568,7 +38586,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39058,7 +39076,7 @@
         <v>1.14</v>
       </c>
       <c r="AP182">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ182">
         <v>1.07</v>
@@ -39392,7 +39410,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39882,7 +39900,7 @@
         <v>0.13</v>
       </c>
       <c r="AP186">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ186">
         <v>1.13</v>
@@ -40088,10 +40106,10 @@
         <v>0.75</v>
       </c>
       <c r="AP187">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ187">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR187">
         <v>1.45</v>
@@ -40216,7 +40234,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40503,7 +40521,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ189">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR189">
         <v>1.53</v>
@@ -40834,7 +40852,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40912,7 +40930,7 @@
         <v>1.67</v>
       </c>
       <c r="AP191">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ191">
         <v>1.25</v>
@@ -41040,7 +41058,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41246,7 +41264,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41452,7 +41470,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42688,7 +42706,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42975,7 +42993,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ201">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR201">
         <v>1.46</v>
@@ -43100,7 +43118,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43181,7 +43199,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ202">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR202">
         <v>1.63</v>
@@ -43306,7 +43324,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43384,7 +43402,7 @@
         <v>1.6</v>
       </c>
       <c r="AP203">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ203">
         <v>1.25</v>
@@ -43924,7 +43942,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44002,7 +44020,7 @@
         <v>0.88</v>
       </c>
       <c r="AP206">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ206">
         <v>0.8100000000000001</v>
@@ -44417,7 +44435,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ208">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR208">
         <v>1.46</v>
@@ -44623,7 +44641,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ209">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR209">
         <v>1.74</v>
@@ -44954,7 +44972,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45160,7 +45178,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45366,7 +45384,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45572,7 +45590,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45984,7 +46002,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46474,7 +46492,7 @@
         <v>1.67</v>
       </c>
       <c r="AP218">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ218">
         <v>1.19</v>
@@ -46889,7 +46907,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ220">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR220">
         <v>1.23</v>
@@ -47092,7 +47110,7 @@
         <v>1.56</v>
       </c>
       <c r="AP221">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ221">
         <v>1.27</v>
@@ -47220,7 +47238,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47632,7 +47650,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47710,7 +47728,7 @@
         <v>0.8</v>
       </c>
       <c r="AP224">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ224">
         <v>0.9399999999999999</v>
@@ -48044,7 +48062,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48331,7 +48349,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ227">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR227">
         <v>1.67</v>
@@ -48662,7 +48680,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48740,7 +48758,7 @@
         <v>1.22</v>
       </c>
       <c r="AP229">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ229">
         <v>1.07</v>
@@ -48868,7 +48886,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48949,7 +48967,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ230">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR230">
         <v>1.54</v>
@@ -49074,7 +49092,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49152,7 +49170,7 @@
         <v>1.2</v>
       </c>
       <c r="AP231">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ231">
         <v>1.63</v>
@@ -49567,7 +49585,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ233">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR233">
         <v>1.18</v>
@@ -49898,7 +49916,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50182,7 +50200,7 @@
         <v>1.5</v>
       </c>
       <c r="AP236">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ236">
         <v>1.19</v>
@@ -50722,7 +50740,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51340,7 +51358,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51752,7 +51770,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51833,7 +51851,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ244">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR244">
         <v>1.4</v>
@@ -52036,10 +52054,10 @@
         <v>1.09</v>
       </c>
       <c r="AP245">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ245">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR245">
         <v>1.49</v>
@@ -52164,7 +52182,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52242,7 +52260,7 @@
         <v>1.3</v>
       </c>
       <c r="AP246">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ246">
         <v>1.07</v>
@@ -52988,7 +53006,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53194,7 +53212,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53481,7 +53499,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ252">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR252">
         <v>1.71</v>
@@ -53606,7 +53624,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -54018,7 +54036,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54224,7 +54242,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54302,7 +54320,7 @@
         <v>1.33</v>
       </c>
       <c r="AP256">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ256">
         <v>1.63</v>
@@ -54511,7 +54529,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ257">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR257">
         <v>1.24</v>
@@ -54714,7 +54732,7 @@
         <v>0.55</v>
       </c>
       <c r="AP258">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ258">
         <v>1</v>
@@ -55254,7 +55272,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55460,7 +55478,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55950,7 +55968,7 @@
         <v>1.36</v>
       </c>
       <c r="AP264">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ264">
         <v>1.44</v>
@@ -56078,7 +56096,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56568,7 +56586,7 @@
         <v>0.82</v>
       </c>
       <c r="AP267">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ267">
         <v>1.13</v>
@@ -57189,7 +57207,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ270">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR270">
         <v>1.69</v>
@@ -57392,7 +57410,7 @@
         <v>1.33</v>
       </c>
       <c r="AP271">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ271">
         <v>1.44</v>
@@ -57520,7 +57538,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -57807,7 +57825,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ273">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR273">
         <v>1.65</v>
@@ -58010,10 +58028,10 @@
         <v>1.08</v>
       </c>
       <c r="AP274">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ274">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR274">
         <v>1.29</v>
@@ -58550,7 +58568,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59246,7 +59264,7 @@
         <v>0.67</v>
       </c>
       <c r="AP280">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ280">
         <v>0.8100000000000001</v>
@@ -59786,7 +59804,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59867,7 +59885,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ283">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR283">
         <v>1.67</v>
@@ -59992,7 +60010,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60073,7 +60091,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ284">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR284">
         <v>1.39</v>
@@ -60276,7 +60294,7 @@
         <v>1.62</v>
       </c>
       <c r="AP285">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ285">
         <v>1.29</v>
@@ -60610,7 +60628,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61228,7 +61246,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61309,7 +61327,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ290">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR290">
         <v>1.62</v>
@@ -61434,7 +61452,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61512,7 +61530,7 @@
         <v>0.85</v>
       </c>
       <c r="AP291">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ291">
         <v>1.13</v>
@@ -62545,7 +62563,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ296">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR296">
         <v>1.6</v>
@@ -63288,7 +63306,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63494,7 +63512,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63572,7 +63590,7 @@
         <v>2</v>
       </c>
       <c r="AP301">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ301">
         <v>1.75</v>
@@ -63700,7 +63718,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -63984,7 +64002,7 @@
         <v>1.5</v>
       </c>
       <c r="AP303">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ303">
         <v>1.29</v>
@@ -64190,10 +64208,10 @@
         <v>1.5</v>
       </c>
       <c r="AP304">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ304">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR304">
         <v>1.51</v>
@@ -64399,7 +64417,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ305">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR305">
         <v>1.62</v>
@@ -65142,7 +65160,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65966,7 +65984,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66378,7 +66396,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66584,7 +66602,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -66871,7 +66889,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ317">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR317">
         <v>1.53</v>
@@ -67692,7 +67710,7 @@
         <v>1.47</v>
       </c>
       <c r="AP321">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ321">
         <v>1.29</v>
@@ -67898,7 +67916,7 @@
         <v>1.13</v>
       </c>
       <c r="AP322">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ322">
         <v>1.13</v>
@@ -68516,7 +68534,7 @@
         <v>1.93</v>
       </c>
       <c r="AP325">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AQ325">
         <v>1.75</v>
@@ -68644,7 +68662,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -68928,10 +68946,10 @@
         <v>1.47</v>
       </c>
       <c r="AP327">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ327">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR327">
         <v>1.32</v>
@@ -69056,7 +69074,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -69137,7 +69155,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ328">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR328">
         <v>1.38</v>
@@ -69343,7 +69361,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ329">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AR329">
         <v>1.65</v>
@@ -69755,7 +69773,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ331">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR331">
         <v>1.4</v>
@@ -71116,7 +71134,7 @@
         <v>302</v>
       </c>
       <c r="P338" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="Q338">
         <v>3.5</v>
@@ -71322,7 +71340,7 @@
         <v>183</v>
       </c>
       <c r="P339" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="Q339">
         <v>3.4</v>
@@ -71940,7 +71958,7 @@
         <v>304</v>
       </c>
       <c r="P342" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="Q342">
         <v>2.88</v>
@@ -73176,7 +73194,7 @@
         <v>310</v>
       </c>
       <c r="P348" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Q348">
         <v>2.3</v>
@@ -73333,6 +73351,830 @@
       </c>
       <c r="BP348">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:68">
+      <c r="A349" s="1">
+        <v>348</v>
+      </c>
+      <c r="B349">
+        <v>7728538</v>
+      </c>
+      <c r="C349" t="s">
+        <v>68</v>
+      </c>
+      <c r="D349" t="s">
+        <v>69</v>
+      </c>
+      <c r="E349" s="2">
+        <v>45739.51041666666</v>
+      </c>
+      <c r="F349">
+        <v>32</v>
+      </c>
+      <c r="G349" t="s">
+        <v>73</v>
+      </c>
+      <c r="H349" t="s">
+        <v>81</v>
+      </c>
+      <c r="I349">
+        <v>0</v>
+      </c>
+      <c r="J349">
+        <v>0</v>
+      </c>
+      <c r="K349">
+        <v>0</v>
+      </c>
+      <c r="L349">
+        <v>2</v>
+      </c>
+      <c r="M349">
+        <v>1</v>
+      </c>
+      <c r="N349">
+        <v>3</v>
+      </c>
+      <c r="O349" t="s">
+        <v>311</v>
+      </c>
+      <c r="P349" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q349">
+        <v>2.6</v>
+      </c>
+      <c r="R349">
+        <v>1.91</v>
+      </c>
+      <c r="S349">
+        <v>6</v>
+      </c>
+      <c r="T349">
+        <v>1.62</v>
+      </c>
+      <c r="U349">
+        <v>2.2</v>
+      </c>
+      <c r="V349">
+        <v>4</v>
+      </c>
+      <c r="W349">
+        <v>1.22</v>
+      </c>
+      <c r="X349">
+        <v>13</v>
+      </c>
+      <c r="Y349">
+        <v>1.04</v>
+      </c>
+      <c r="Z349">
+        <v>1.93</v>
+      </c>
+      <c r="AA349">
+        <v>3.15</v>
+      </c>
+      <c r="AB349">
+        <v>5.1</v>
+      </c>
+      <c r="AC349">
+        <v>1.12</v>
+      </c>
+      <c r="AD349">
+        <v>6</v>
+      </c>
+      <c r="AE349">
+        <v>1.6</v>
+      </c>
+      <c r="AF349">
+        <v>2.1</v>
+      </c>
+      <c r="AG349">
+        <v>2.48</v>
+      </c>
+      <c r="AH349">
+        <v>1.54</v>
+      </c>
+      <c r="AI349">
+        <v>2.5</v>
+      </c>
+      <c r="AJ349">
+        <v>1.5</v>
+      </c>
+      <c r="AK349">
+        <v>1.17</v>
+      </c>
+      <c r="AL349">
+        <v>1.3</v>
+      </c>
+      <c r="AM349">
+        <v>1.91</v>
+      </c>
+      <c r="AN349">
+        <v>1.87</v>
+      </c>
+      <c r="AO349">
+        <v>1.38</v>
+      </c>
+      <c r="AP349">
+        <v>1.94</v>
+      </c>
+      <c r="AQ349">
+        <v>1.29</v>
+      </c>
+      <c r="AR349">
+        <v>1.54</v>
+      </c>
+      <c r="AS349">
+        <v>1.03</v>
+      </c>
+      <c r="AT349">
+        <v>2.57</v>
+      </c>
+      <c r="AU349">
+        <v>8</v>
+      </c>
+      <c r="AV349">
+        <v>4</v>
+      </c>
+      <c r="AW349">
+        <v>11</v>
+      </c>
+      <c r="AX349">
+        <v>2</v>
+      </c>
+      <c r="AY349">
+        <v>20</v>
+      </c>
+      <c r="AZ349">
+        <v>6</v>
+      </c>
+      <c r="BA349">
+        <v>4</v>
+      </c>
+      <c r="BB349">
+        <v>0</v>
+      </c>
+      <c r="BC349">
+        <v>4</v>
+      </c>
+      <c r="BD349">
+        <v>1.45</v>
+      </c>
+      <c r="BE349">
+        <v>6.75</v>
+      </c>
+      <c r="BF349">
+        <v>3.15</v>
+      </c>
+      <c r="BG349">
+        <v>1.4</v>
+      </c>
+      <c r="BH349">
+        <v>2.65</v>
+      </c>
+      <c r="BI349">
+        <v>1.66</v>
+      </c>
+      <c r="BJ349">
+        <v>2.04</v>
+      </c>
+      <c r="BK349">
+        <v>2.05</v>
+      </c>
+      <c r="BL349">
+        <v>1.65</v>
+      </c>
+      <c r="BM349">
+        <v>2.65</v>
+      </c>
+      <c r="BN349">
+        <v>1.4</v>
+      </c>
+      <c r="BO349">
+        <v>3.55</v>
+      </c>
+      <c r="BP349">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="350" spans="1:68">
+      <c r="A350" s="1">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>7728542</v>
+      </c>
+      <c r="C350" t="s">
+        <v>68</v>
+      </c>
+      <c r="D350" t="s">
+        <v>69</v>
+      </c>
+      <c r="E350" s="2">
+        <v>45739.51041666666</v>
+      </c>
+      <c r="F350">
+        <v>32</v>
+      </c>
+      <c r="G350" t="s">
+        <v>76</v>
+      </c>
+      <c r="H350" t="s">
+        <v>85</v>
+      </c>
+      <c r="I350">
+        <v>0</v>
+      </c>
+      <c r="J350">
+        <v>1</v>
+      </c>
+      <c r="K350">
+        <v>1</v>
+      </c>
+      <c r="L350">
+        <v>0</v>
+      </c>
+      <c r="M350">
+        <v>2</v>
+      </c>
+      <c r="N350">
+        <v>2</v>
+      </c>
+      <c r="O350" t="s">
+        <v>94</v>
+      </c>
+      <c r="P350" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q350">
+        <v>2.63</v>
+      </c>
+      <c r="R350">
+        <v>2.05</v>
+      </c>
+      <c r="S350">
+        <v>4.75</v>
+      </c>
+      <c r="T350">
+        <v>1.5</v>
+      </c>
+      <c r="U350">
+        <v>2.5</v>
+      </c>
+      <c r="V350">
+        <v>3.4</v>
+      </c>
+      <c r="W350">
+        <v>1.3</v>
+      </c>
+      <c r="X350">
+        <v>10</v>
+      </c>
+      <c r="Y350">
+        <v>1.06</v>
+      </c>
+      <c r="Z350">
+        <v>1.89</v>
+      </c>
+      <c r="AA350">
+        <v>3.57</v>
+      </c>
+      <c r="AB350">
+        <v>4.4</v>
+      </c>
+      <c r="AC350">
+        <v>1.08</v>
+      </c>
+      <c r="AD350">
+        <v>7.5</v>
+      </c>
+      <c r="AE350">
+        <v>1.42</v>
+      </c>
+      <c r="AF350">
+        <v>2.8</v>
+      </c>
+      <c r="AG350">
+        <v>2.05</v>
+      </c>
+      <c r="AH350">
+        <v>1.65</v>
+      </c>
+      <c r="AI350">
+        <v>2</v>
+      </c>
+      <c r="AJ350">
+        <v>1.73</v>
+      </c>
+      <c r="AK350">
+        <v>1.22</v>
+      </c>
+      <c r="AL350">
+        <v>1.28</v>
+      </c>
+      <c r="AM350">
+        <v>1.83</v>
+      </c>
+      <c r="AN350">
+        <v>1.63</v>
+      </c>
+      <c r="AO350">
+        <v>0.87</v>
+      </c>
+      <c r="AP350">
+        <v>1.53</v>
+      </c>
+      <c r="AQ350">
+        <v>1</v>
+      </c>
+      <c r="AR350">
+        <v>1.53</v>
+      </c>
+      <c r="AS350">
+        <v>1.29</v>
+      </c>
+      <c r="AT350">
+        <v>2.82</v>
+      </c>
+      <c r="AU350">
+        <v>5</v>
+      </c>
+      <c r="AV350">
+        <v>8</v>
+      </c>
+      <c r="AW350">
+        <v>11</v>
+      </c>
+      <c r="AX350">
+        <v>12</v>
+      </c>
+      <c r="AY350">
+        <v>21</v>
+      </c>
+      <c r="AZ350">
+        <v>25</v>
+      </c>
+      <c r="BA350">
+        <v>9</v>
+      </c>
+      <c r="BB350">
+        <v>6</v>
+      </c>
+      <c r="BC350">
+        <v>15</v>
+      </c>
+      <c r="BD350">
+        <v>1.54</v>
+      </c>
+      <c r="BE350">
+        <v>6.5</v>
+      </c>
+      <c r="BF350">
+        <v>2.8</v>
+      </c>
+      <c r="BG350">
+        <v>1.47</v>
+      </c>
+      <c r="BH350">
+        <v>2.4</v>
+      </c>
+      <c r="BI350">
+        <v>1.8</v>
+      </c>
+      <c r="BJ350">
+        <v>1.86</v>
+      </c>
+      <c r="BK350">
+        <v>2.28</v>
+      </c>
+      <c r="BL350">
+        <v>1.53</v>
+      </c>
+      <c r="BM350">
+        <v>2.95</v>
+      </c>
+      <c r="BN350">
+        <v>1.33</v>
+      </c>
+      <c r="BO350">
+        <v>4</v>
+      </c>
+      <c r="BP350">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="351" spans="1:68">
+      <c r="A351" s="1">
+        <v>350</v>
+      </c>
+      <c r="B351">
+        <v>7728544</v>
+      </c>
+      <c r="C351" t="s">
+        <v>68</v>
+      </c>
+      <c r="D351" t="s">
+        <v>69</v>
+      </c>
+      <c r="E351" s="2">
+        <v>45739.60416666666</v>
+      </c>
+      <c r="F351">
+        <v>32</v>
+      </c>
+      <c r="G351" t="s">
+        <v>84</v>
+      </c>
+      <c r="H351" t="s">
+        <v>72</v>
+      </c>
+      <c r="I351">
+        <v>1</v>
+      </c>
+      <c r="J351">
+        <v>0</v>
+      </c>
+      <c r="K351">
+        <v>1</v>
+      </c>
+      <c r="L351">
+        <v>2</v>
+      </c>
+      <c r="M351">
+        <v>1</v>
+      </c>
+      <c r="N351">
+        <v>3</v>
+      </c>
+      <c r="O351" t="s">
+        <v>312</v>
+      </c>
+      <c r="P351" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q351">
+        <v>3.4</v>
+      </c>
+      <c r="R351">
+        <v>1.91</v>
+      </c>
+      <c r="S351">
+        <v>4</v>
+      </c>
+      <c r="T351">
+        <v>1.62</v>
+      </c>
+      <c r="U351">
+        <v>2.2</v>
+      </c>
+      <c r="V351">
+        <v>4</v>
+      </c>
+      <c r="W351">
+        <v>1.22</v>
+      </c>
+      <c r="X351">
+        <v>13</v>
+      </c>
+      <c r="Y351">
+        <v>1.04</v>
+      </c>
+      <c r="Z351">
+        <v>2.55</v>
+      </c>
+      <c r="AA351">
+        <v>2.94</v>
+      </c>
+      <c r="AB351">
+        <v>3.31</v>
+      </c>
+      <c r="AC351">
+        <v>1.11</v>
+      </c>
+      <c r="AD351">
+        <v>6.25</v>
+      </c>
+      <c r="AE351">
+        <v>1.53</v>
+      </c>
+      <c r="AF351">
+        <v>2.25</v>
+      </c>
+      <c r="AG351">
+        <v>2.73</v>
+      </c>
+      <c r="AH351">
+        <v>1.4</v>
+      </c>
+      <c r="AI351">
+        <v>2.2</v>
+      </c>
+      <c r="AJ351">
+        <v>1.62</v>
+      </c>
+      <c r="AK351">
+        <v>1.35</v>
+      </c>
+      <c r="AL351">
+        <v>1.33</v>
+      </c>
+      <c r="AM351">
+        <v>1.53</v>
+      </c>
+      <c r="AN351">
+        <v>1.27</v>
+      </c>
+      <c r="AO351">
+        <v>1.33</v>
+      </c>
+      <c r="AP351">
+        <v>1.38</v>
+      </c>
+      <c r="AQ351">
+        <v>1.25</v>
+      </c>
+      <c r="AR351">
+        <v>1.38</v>
+      </c>
+      <c r="AS351">
+        <v>1.25</v>
+      </c>
+      <c r="AT351">
+        <v>2.63</v>
+      </c>
+      <c r="AU351">
+        <v>9</v>
+      </c>
+      <c r="AV351">
+        <v>6</v>
+      </c>
+      <c r="AW351">
+        <v>5</v>
+      </c>
+      <c r="AX351">
+        <v>9</v>
+      </c>
+      <c r="AY351">
+        <v>15</v>
+      </c>
+      <c r="AZ351">
+        <v>18</v>
+      </c>
+      <c r="BA351">
+        <v>6</v>
+      </c>
+      <c r="BB351">
+        <v>3</v>
+      </c>
+      <c r="BC351">
+        <v>9</v>
+      </c>
+      <c r="BD351">
+        <v>1.9</v>
+      </c>
+      <c r="BE351">
+        <v>6.25</v>
+      </c>
+      <c r="BF351">
+        <v>2.12</v>
+      </c>
+      <c r="BG351">
+        <v>1.54</v>
+      </c>
+      <c r="BH351">
+        <v>2.28</v>
+      </c>
+      <c r="BI351">
+        <v>1.89</v>
+      </c>
+      <c r="BJ351">
+        <v>1.77</v>
+      </c>
+      <c r="BK351">
+        <v>2.43</v>
+      </c>
+      <c r="BL351">
+        <v>1.46</v>
+      </c>
+      <c r="BM351">
+        <v>3.3</v>
+      </c>
+      <c r="BN351">
+        <v>1.27</v>
+      </c>
+      <c r="BO351">
+        <v>4.4</v>
+      </c>
+      <c r="BP351">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="352" spans="1:68">
+      <c r="A352" s="1">
+        <v>351</v>
+      </c>
+      <c r="B352">
+        <v>7728545</v>
+      </c>
+      <c r="C352" t="s">
+        <v>68</v>
+      </c>
+      <c r="D352" t="s">
+        <v>69</v>
+      </c>
+      <c r="E352" s="2">
+        <v>45739.60416666666</v>
+      </c>
+      <c r="F352">
+        <v>32</v>
+      </c>
+      <c r="G352" t="s">
+        <v>75</v>
+      </c>
+      <c r="H352" t="s">
+        <v>87</v>
+      </c>
+      <c r="I352">
+        <v>0</v>
+      </c>
+      <c r="J352">
+        <v>0</v>
+      </c>
+      <c r="K352">
+        <v>0</v>
+      </c>
+      <c r="L352">
+        <v>2</v>
+      </c>
+      <c r="M352">
+        <v>2</v>
+      </c>
+      <c r="N352">
+        <v>4</v>
+      </c>
+      <c r="O352" t="s">
+        <v>313</v>
+      </c>
+      <c r="P352" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q352">
+        <v>1.8</v>
+      </c>
+      <c r="R352">
+        <v>2.4</v>
+      </c>
+      <c r="S352">
+        <v>9</v>
+      </c>
+      <c r="T352">
+        <v>1.36</v>
+      </c>
+      <c r="U352">
+        <v>3</v>
+      </c>
+      <c r="V352">
+        <v>2.63</v>
+      </c>
+      <c r="W352">
+        <v>1.44</v>
+      </c>
+      <c r="X352">
+        <v>7</v>
+      </c>
+      <c r="Y352">
+        <v>1.1</v>
+      </c>
+      <c r="Z352">
+        <v>1.56</v>
+      </c>
+      <c r="AA352">
+        <v>4.1</v>
+      </c>
+      <c r="AB352">
+        <v>6.6</v>
+      </c>
+      <c r="AC352">
+        <v>1.04</v>
+      </c>
+      <c r="AD352">
+        <v>10</v>
+      </c>
+      <c r="AE352">
+        <v>1.25</v>
+      </c>
+      <c r="AF352">
+        <v>3.75</v>
+      </c>
+      <c r="AG352">
+        <v>1.85</v>
+      </c>
+      <c r="AH352">
+        <v>1.96</v>
+      </c>
+      <c r="AI352">
+        <v>2.38</v>
+      </c>
+      <c r="AJ352">
+        <v>1.53</v>
+      </c>
+      <c r="AK352">
+        <v>1.05</v>
+      </c>
+      <c r="AL352">
+        <v>1.15</v>
+      </c>
+      <c r="AM352">
+        <v>3.35</v>
+      </c>
+      <c r="AN352">
+        <v>1.2</v>
+      </c>
+      <c r="AO352">
+        <v>0.44</v>
+      </c>
+      <c r="AP352">
+        <v>1.19</v>
+      </c>
+      <c r="AQ352">
+        <v>0.47</v>
+      </c>
+      <c r="AR352">
+        <v>1.55</v>
+      </c>
+      <c r="AS352">
+        <v>0.97</v>
+      </c>
+      <c r="AT352">
+        <v>2.52</v>
+      </c>
+      <c r="AU352">
+        <v>4</v>
+      </c>
+      <c r="AV352">
+        <v>4</v>
+      </c>
+      <c r="AW352">
+        <v>8</v>
+      </c>
+      <c r="AX352">
+        <v>9</v>
+      </c>
+      <c r="AY352">
+        <v>16</v>
+      </c>
+      <c r="AZ352">
+        <v>16</v>
+      </c>
+      <c r="BA352">
+        <v>2</v>
+      </c>
+      <c r="BB352">
+        <v>6</v>
+      </c>
+      <c r="BC352">
+        <v>8</v>
+      </c>
+      <c r="BD352">
+        <v>1.2</v>
+      </c>
+      <c r="BE352">
+        <v>8.5</v>
+      </c>
+      <c r="BF352">
+        <v>4.8</v>
+      </c>
+      <c r="BG352">
+        <v>1.28</v>
+      </c>
+      <c r="BH352">
+        <v>3.25</v>
+      </c>
+      <c r="BI352">
+        <v>1.52</v>
+      </c>
+      <c r="BJ352">
+        <v>2.37</v>
+      </c>
+      <c r="BK352">
+        <v>1.87</v>
+      </c>
+      <c r="BL352">
+        <v>1.87</v>
+      </c>
+      <c r="BM352">
+        <v>2.38</v>
+      </c>
+      <c r="BN352">
+        <v>1.54</v>
+      </c>
+      <c r="BO352">
+        <v>3.12</v>
+      </c>
+      <c r="BP352">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="429">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1662,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP352"/>
+  <dimension ref="A1:BP353"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2205,7 +2205,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ34">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR34">
         <v>1.17</v>
@@ -10442,7 +10442,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ43">
         <v>1.07</v>
@@ -14150,7 +14150,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ61">
         <v>1.63</v>
@@ -15389,7 +15389,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ67">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR67">
         <v>1.16</v>
@@ -18682,7 +18682,7 @@
         <v>3</v>
       </c>
       <c r="AP83">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ83">
         <v>1.75</v>
@@ -19921,7 +19921,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ89">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -21569,7 +21569,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ97">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -24244,7 +24244,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ110">
         <v>1.29</v>
@@ -25483,7 +25483,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ116">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -27540,7 +27540,7 @@
         <v>1.8</v>
       </c>
       <c r="AP126">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ126">
         <v>1.19</v>
@@ -29806,7 +29806,7 @@
         <v>2.2</v>
       </c>
       <c r="AP137">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ137">
         <v>1.27</v>
@@ -33929,7 +33929,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ157">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR157">
         <v>1.49</v>
@@ -34750,7 +34750,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ161">
         <v>0.9399999999999999</v>
@@ -37431,7 +37431,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ174">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR174">
         <v>1.76</v>
@@ -38252,7 +38252,7 @@
         <v>1</v>
       </c>
       <c r="AP178">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ178">
         <v>1</v>
@@ -39903,7 +39903,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ186">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR186">
         <v>1.44</v>
@@ -42787,7 +42787,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ200">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR200">
         <v>1.61</v>
@@ -45256,7 +45256,7 @@
         <v>1.1</v>
       </c>
       <c r="AP212">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ212">
         <v>1.31</v>
@@ -47319,7 +47319,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ222">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR222">
         <v>1.64</v>
@@ -47522,7 +47522,7 @@
         <v>1.11</v>
       </c>
       <c r="AP223">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ223">
         <v>0.8100000000000001</v>
@@ -53087,7 +53087,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ250">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR250">
         <v>1.68</v>
@@ -53290,7 +53290,7 @@
         <v>0.18</v>
       </c>
       <c r="AP251">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ251">
         <v>0.19</v>
@@ -57619,7 +57619,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ272">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR272">
         <v>1.18</v>
@@ -57822,7 +57822,7 @@
         <v>1.18</v>
       </c>
       <c r="AP273">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ273">
         <v>1.25</v>
@@ -61533,7 +61533,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ291">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR291">
         <v>1.32</v>
@@ -62354,7 +62354,7 @@
         <v>0.75</v>
       </c>
       <c r="AP295">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ295">
         <v>1.13</v>
@@ -63181,7 +63181,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ299">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR299">
         <v>1.24</v>
@@ -65856,7 +65856,7 @@
         <v>1</v>
       </c>
       <c r="AP312">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ312">
         <v>1</v>
@@ -67919,7 +67919,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ322">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR322">
         <v>1.55</v>
@@ -68740,7 +68740,7 @@
         <v>0.93</v>
       </c>
       <c r="AP326">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ326">
         <v>1</v>
@@ -74175,6 +74175,212 @@
       </c>
       <c r="BP352">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="353" spans="1:68">
+      <c r="A353" s="1">
+        <v>352</v>
+      </c>
+      <c r="B353">
+        <v>7728547</v>
+      </c>
+      <c r="C353" t="s">
+        <v>68</v>
+      </c>
+      <c r="D353" t="s">
+        <v>69</v>
+      </c>
+      <c r="E353" s="2">
+        <v>45740.6875</v>
+      </c>
+      <c r="F353">
+        <v>32</v>
+      </c>
+      <c r="G353" t="s">
+        <v>91</v>
+      </c>
+      <c r="H353" t="s">
+        <v>88</v>
+      </c>
+      <c r="I353">
+        <v>0</v>
+      </c>
+      <c r="J353">
+        <v>0</v>
+      </c>
+      <c r="K353">
+        <v>0</v>
+      </c>
+      <c r="L353">
+        <v>1</v>
+      </c>
+      <c r="M353">
+        <v>1</v>
+      </c>
+      <c r="N353">
+        <v>2</v>
+      </c>
+      <c r="O353" t="s">
+        <v>117</v>
+      </c>
+      <c r="P353" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q353">
+        <v>2.88</v>
+      </c>
+      <c r="R353">
+        <v>2.1</v>
+      </c>
+      <c r="S353">
+        <v>4</v>
+      </c>
+      <c r="T353">
+        <v>1.44</v>
+      </c>
+      <c r="U353">
+        <v>2.63</v>
+      </c>
+      <c r="V353">
+        <v>3.25</v>
+      </c>
+      <c r="W353">
+        <v>1.33</v>
+      </c>
+      <c r="X353">
+        <v>9</v>
+      </c>
+      <c r="Y353">
+        <v>1.07</v>
+      </c>
+      <c r="Z353">
+        <v>2.26</v>
+      </c>
+      <c r="AA353">
+        <v>3.39</v>
+      </c>
+      <c r="AB353">
+        <v>3.35</v>
+      </c>
+      <c r="AC353">
+        <v>1</v>
+      </c>
+      <c r="AD353">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE353">
+        <v>1.33</v>
+      </c>
+      <c r="AF353">
+        <v>3.27</v>
+      </c>
+      <c r="AG353">
+        <v>2.03</v>
+      </c>
+      <c r="AH353">
+        <v>1.79</v>
+      </c>
+      <c r="AI353">
+        <v>1.83</v>
+      </c>
+      <c r="AJ353">
+        <v>1.83</v>
+      </c>
+      <c r="AK353">
+        <v>1.33</v>
+      </c>
+      <c r="AL353">
+        <v>1.25</v>
+      </c>
+      <c r="AM353">
+        <v>1.65</v>
+      </c>
+      <c r="AN353">
+        <v>1.07</v>
+      </c>
+      <c r="AO353">
+        <v>1.13</v>
+      </c>
+      <c r="AP353">
+        <v>1.06</v>
+      </c>
+      <c r="AQ353">
+        <v>1.12</v>
+      </c>
+      <c r="AR353">
+        <v>1.65</v>
+      </c>
+      <c r="AS353">
+        <v>1.47</v>
+      </c>
+      <c r="AT353">
+        <v>3.12</v>
+      </c>
+      <c r="AU353">
+        <v>4</v>
+      </c>
+      <c r="AV353">
+        <v>5</v>
+      </c>
+      <c r="AW353">
+        <v>10</v>
+      </c>
+      <c r="AX353">
+        <v>5</v>
+      </c>
+      <c r="AY353">
+        <v>17</v>
+      </c>
+      <c r="AZ353">
+        <v>11</v>
+      </c>
+      <c r="BA353">
+        <v>4</v>
+      </c>
+      <c r="BB353">
+        <v>5</v>
+      </c>
+      <c r="BC353">
+        <v>9</v>
+      </c>
+      <c r="BD353">
+        <v>1.71</v>
+      </c>
+      <c r="BE353">
+        <v>6.75</v>
+      </c>
+      <c r="BF353">
+        <v>2.33</v>
+      </c>
+      <c r="BG353">
+        <v>1.26</v>
+      </c>
+      <c r="BH353">
+        <v>3.22</v>
+      </c>
+      <c r="BI353">
+        <v>1.51</v>
+      </c>
+      <c r="BJ353">
+        <v>2.32</v>
+      </c>
+      <c r="BK353">
+        <v>1.9</v>
+      </c>
+      <c r="BL353">
+        <v>1.8</v>
+      </c>
+      <c r="BM353">
+        <v>2.45</v>
+      </c>
+      <c r="BN353">
+        <v>1.46</v>
+      </c>
+      <c r="BO353">
+        <v>3.28</v>
+      </c>
+      <c r="BP353">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="430">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -958,6 +958,9 @@
     <t>['69', '86']</t>
   </si>
   <si>
+    <t>['54', '78']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1662,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP353"/>
+  <dimension ref="A1:BP354"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1918,7 +1921,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2330,7 +2333,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3154,7 +3157,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3360,7 +3363,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4184,7 +4187,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4883,7 +4886,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ16">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR16">
         <v>1.33</v>
@@ -5420,7 +5423,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5498,7 +5501,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ19">
         <v>1.29</v>
@@ -6038,7 +6041,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6244,7 +6247,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6450,7 +6453,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6656,7 +6659,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6862,7 +6865,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7480,7 +7483,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -8098,7 +8101,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8304,7 +8307,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8716,7 +8719,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8794,7 +8797,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ35">
         <v>1.75</v>
@@ -10570,7 +10573,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11188,7 +11191,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12836,7 +12839,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12917,7 +12920,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ55">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR55">
         <v>1.39</v>
@@ -13042,7 +13045,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13248,7 +13251,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13454,7 +13457,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13866,7 +13869,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14356,7 +14359,7 @@
         <v>0.5</v>
       </c>
       <c r="AP62">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14484,7 +14487,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -15102,7 +15105,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15514,7 +15517,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15720,7 +15723,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16338,7 +16341,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16544,7 +16547,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16750,7 +16753,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16831,7 +16834,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ74">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR74">
         <v>1.54</v>
@@ -17574,7 +17577,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17780,7 +17783,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18192,7 +18195,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18273,7 +18276,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ81">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR81">
         <v>1.07</v>
@@ -18398,7 +18401,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18604,7 +18607,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19094,7 +19097,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ85">
         <v>0.47</v>
@@ -19428,7 +19431,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19840,7 +19843,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -20046,7 +20049,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20124,7 +20127,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ90">
         <v>1.25</v>
@@ -20458,7 +20461,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20870,7 +20873,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -21076,7 +21079,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -22106,7 +22109,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23548,7 +23551,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24166,7 +24169,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24578,7 +24581,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24784,7 +24787,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24865,7 +24868,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ113">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -25196,7 +25199,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -26020,7 +26023,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26510,7 +26513,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ121">
         <v>0.9399999999999999</v>
@@ -26638,7 +26641,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -27050,7 +27053,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27462,7 +27465,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27874,7 +27877,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28286,7 +28289,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28492,7 +28495,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28698,7 +28701,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29110,7 +29113,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29316,7 +29319,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29809,7 +29812,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ137">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR137">
         <v>1.67</v>
@@ -29934,7 +29937,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30424,7 +30427,7 @@
         <v>1</v>
       </c>
       <c r="AP140">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ140">
         <v>1.07</v>
@@ -30552,7 +30555,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30758,7 +30761,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30964,7 +30967,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31170,7 +31173,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31582,7 +31585,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31994,7 +31997,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -33024,7 +33027,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33642,7 +33645,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33723,7 +33726,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ156">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR156">
         <v>1.44</v>
@@ -35290,7 +35293,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35908,7 +35911,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36938,7 +36941,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37556,7 +37559,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37968,7 +37971,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38380,7 +38383,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38461,7 +38464,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ179">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR179">
         <v>1.71</v>
@@ -38586,7 +38589,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39076,7 +39079,7 @@
         <v>1.14</v>
       </c>
       <c r="AP182">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ182">
         <v>1.07</v>
@@ -39410,7 +39413,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40234,7 +40237,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40852,7 +40855,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -41058,7 +41061,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41264,7 +41267,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41470,7 +41473,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42706,7 +42709,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43118,7 +43121,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43324,7 +43327,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43817,7 +43820,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ205">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR205">
         <v>1.69</v>
@@ -43942,7 +43945,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44972,7 +44975,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45178,7 +45181,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45384,7 +45387,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45590,7 +45593,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -46002,7 +46005,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -47113,7 +47116,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ221">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR221">
         <v>1.48</v>
@@ -47238,7 +47241,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47650,7 +47653,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -48062,7 +48065,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48680,7 +48683,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48886,7 +48889,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49092,7 +49095,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49170,7 +49173,7 @@
         <v>1.2</v>
       </c>
       <c r="AP231">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ231">
         <v>1.63</v>
@@ -49916,7 +49919,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50200,7 +50203,7 @@
         <v>1.5</v>
       </c>
       <c r="AP236">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ236">
         <v>1.19</v>
@@ -50740,7 +50743,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51358,7 +51361,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51770,7 +51773,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52182,7 +52185,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52469,7 +52472,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ247">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR247">
         <v>1.54</v>
@@ -53006,7 +53009,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53212,7 +53215,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53624,7 +53627,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -54036,7 +54039,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54242,7 +54245,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54732,7 +54735,7 @@
         <v>0.55</v>
       </c>
       <c r="AP258">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ258">
         <v>1</v>
@@ -55272,7 +55275,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55478,7 +55481,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55968,7 +55971,7 @@
         <v>1.36</v>
       </c>
       <c r="AP264">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ264">
         <v>1.44</v>
@@ -56096,7 +56099,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56177,7 +56180,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ265">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR265">
         <v>1.45</v>
@@ -57538,7 +57541,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -58028,7 +58031,7 @@
         <v>1.08</v>
       </c>
       <c r="AP274">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ274">
         <v>1</v>
@@ -58568,7 +58571,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59804,7 +59807,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -60010,7 +60013,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60628,7 +60631,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61246,7 +61249,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61452,7 +61455,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61530,7 +61533,7 @@
         <v>0.85</v>
       </c>
       <c r="AP291">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ291">
         <v>1.12</v>
@@ -62151,7 +62154,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ294">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR294">
         <v>1.27</v>
@@ -63306,7 +63309,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63512,7 +63515,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63718,7 +63721,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -65160,7 +65163,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65984,7 +65987,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66271,7 +66274,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ314">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR314">
         <v>1.64</v>
@@ -66396,7 +66399,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66602,7 +66605,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -68662,7 +68665,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -68946,7 +68949,7 @@
         <v>1.47</v>
       </c>
       <c r="AP327">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ327">
         <v>1.29</v>
@@ -69074,7 +69077,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -71134,7 +71137,7 @@
         <v>302</v>
       </c>
       <c r="P338" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q338">
         <v>3.5</v>
@@ -71340,7 +71343,7 @@
         <v>183</v>
       </c>
       <c r="P339" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q339">
         <v>3.4</v>
@@ -71833,7 +71836,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ341">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR341">
         <v>1.44</v>
@@ -71958,7 +71961,7 @@
         <v>304</v>
       </c>
       <c r="P342" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q342">
         <v>2.88</v>
@@ -73194,7 +73197,7 @@
         <v>310</v>
       </c>
       <c r="P348" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q348">
         <v>2.3</v>
@@ -73400,7 +73403,7 @@
         <v>311</v>
       </c>
       <c r="P349" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q349">
         <v>2.6</v>
@@ -73606,7 +73609,7 @@
         <v>94</v>
       </c>
       <c r="P350" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q350">
         <v>2.63</v>
@@ -73890,7 +73893,7 @@
         <v>1.33</v>
       </c>
       <c r="AP351">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ351">
         <v>1.25</v>
@@ -74018,7 +74021,7 @@
         <v>313</v>
       </c>
       <c r="P352" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q352">
         <v>1.8</v>
@@ -74224,7 +74227,7 @@
         <v>117</v>
       </c>
       <c r="P353" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q353">
         <v>2.88</v>
@@ -74381,6 +74384,212 @@
       </c>
       <c r="BP353">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="354" spans="1:68">
+      <c r="A354" s="1">
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>7728558</v>
+      </c>
+      <c r="C354" t="s">
+        <v>68</v>
+      </c>
+      <c r="D354" t="s">
+        <v>69</v>
+      </c>
+      <c r="E354" s="2">
+        <v>45744.6875</v>
+      </c>
+      <c r="F354">
+        <v>33</v>
+      </c>
+      <c r="G354" t="s">
+        <v>84</v>
+      </c>
+      <c r="H354" t="s">
+        <v>70</v>
+      </c>
+      <c r="I354">
+        <v>0</v>
+      </c>
+      <c r="J354">
+        <v>1</v>
+      </c>
+      <c r="K354">
+        <v>1</v>
+      </c>
+      <c r="L354">
+        <v>2</v>
+      </c>
+      <c r="M354">
+        <v>1</v>
+      </c>
+      <c r="N354">
+        <v>3</v>
+      </c>
+      <c r="O354" t="s">
+        <v>314</v>
+      </c>
+      <c r="P354" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q354">
+        <v>3.4</v>
+      </c>
+      <c r="R354">
+        <v>1.91</v>
+      </c>
+      <c r="S354">
+        <v>3.75</v>
+      </c>
+      <c r="T354">
+        <v>1.57</v>
+      </c>
+      <c r="U354">
+        <v>2.25</v>
+      </c>
+      <c r="V354">
+        <v>3.75</v>
+      </c>
+      <c r="W354">
+        <v>1.25</v>
+      </c>
+      <c r="X354">
+        <v>11</v>
+      </c>
+      <c r="Y354">
+        <v>1.05</v>
+      </c>
+      <c r="Z354">
+        <v>2.62</v>
+      </c>
+      <c r="AA354">
+        <v>3.05</v>
+      </c>
+      <c r="AB354">
+        <v>3.08</v>
+      </c>
+      <c r="AC354">
+        <v>1.1</v>
+      </c>
+      <c r="AD354">
+        <v>6.5</v>
+      </c>
+      <c r="AE354">
+        <v>1.5</v>
+      </c>
+      <c r="AF354">
+        <v>2.55</v>
+      </c>
+      <c r="AG354">
+        <v>2.3</v>
+      </c>
+      <c r="AH354">
+        <v>1.5</v>
+      </c>
+      <c r="AI354">
+        <v>2.1</v>
+      </c>
+      <c r="AJ354">
+        <v>1.67</v>
+      </c>
+      <c r="AK354">
+        <v>1.38</v>
+      </c>
+      <c r="AL354">
+        <v>1.36</v>
+      </c>
+      <c r="AM354">
+        <v>1.5</v>
+      </c>
+      <c r="AN354">
+        <v>1.38</v>
+      </c>
+      <c r="AO354">
+        <v>1.27</v>
+      </c>
+      <c r="AP354">
+        <v>1.47</v>
+      </c>
+      <c r="AQ354">
+        <v>1.19</v>
+      </c>
+      <c r="AR354">
+        <v>1.4</v>
+      </c>
+      <c r="AS354">
+        <v>1.17</v>
+      </c>
+      <c r="AT354">
+        <v>2.57</v>
+      </c>
+      <c r="AU354">
+        <v>6</v>
+      </c>
+      <c r="AV354">
+        <v>5</v>
+      </c>
+      <c r="AW354">
+        <v>11</v>
+      </c>
+      <c r="AX354">
+        <v>7</v>
+      </c>
+      <c r="AY354">
+        <v>23</v>
+      </c>
+      <c r="AZ354">
+        <v>13</v>
+      </c>
+      <c r="BA354">
+        <v>7</v>
+      </c>
+      <c r="BB354">
+        <v>4</v>
+      </c>
+      <c r="BC354">
+        <v>11</v>
+      </c>
+      <c r="BD354">
+        <v>1.84</v>
+      </c>
+      <c r="BE354">
+        <v>6.25</v>
+      </c>
+      <c r="BF354">
+        <v>2.18</v>
+      </c>
+      <c r="BG354">
+        <v>1.46</v>
+      </c>
+      <c r="BH354">
+        <v>2.43</v>
+      </c>
+      <c r="BI354">
+        <v>1.77</v>
+      </c>
+      <c r="BJ354">
+        <v>1.89</v>
+      </c>
+      <c r="BK354">
+        <v>2.25</v>
+      </c>
+      <c r="BL354">
+        <v>1.55</v>
+      </c>
+      <c r="BM354">
+        <v>2.95</v>
+      </c>
+      <c r="BN354">
+        <v>1.33</v>
+      </c>
+      <c r="BO354">
+        <v>3.95</v>
+      </c>
+      <c r="BP354">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="439">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -961,6 +961,21 @@
     <t>['54', '78']</t>
   </si>
   <si>
+    <t>['3', '45+4']</t>
+  </si>
+  <si>
+    <t>['47', '68']</t>
+  </si>
+  <si>
+    <t>['74', '90+3']</t>
+  </si>
+  <si>
+    <t>['45+2', '45+8', '90+3']</t>
+  </si>
+  <si>
+    <t>['26', '47', '90+7']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1304,6 +1319,18 @@
   </si>
   <si>
     <t>['59', '76']</t>
+  </si>
+  <si>
+    <t>['47', '55']</t>
+  </si>
+  <si>
+    <t>['15', '89']</t>
+  </si>
+  <si>
+    <t>['21', '54']</t>
+  </si>
+  <si>
+    <t>['45+5', '56']</t>
   </si>
 </sst>
 </file>
@@ -1665,7 +1692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP354"/>
+  <dimension ref="A1:BP363"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1921,7 +1948,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2333,7 +2360,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2414,7 +2441,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2620,7 +2647,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2823,10 +2850,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ6">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3157,7 +3184,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3238,7 +3265,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ8">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3363,7 +3390,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3441,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ9">
         <v>1.29</v>
@@ -4059,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ12">
         <v>0.19</v>
@@ -4187,7 +4214,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4265,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ13">
         <v>0.8100000000000001</v>
@@ -4471,10 +4498,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4883,7 +4910,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ16">
         <v>1.19</v>
@@ -5298,7 +5325,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ18">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5423,7 +5450,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5707,10 +5734,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ20">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -6041,7 +6068,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6119,10 +6146,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ22">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6247,7 +6274,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6325,10 +6352,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ23">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6453,7 +6480,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6659,7 +6686,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6737,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ25">
         <v>1.75</v>
@@ -6865,7 +6892,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7355,10 +7382,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -7483,7 +7510,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7564,7 +7591,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ29">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR29">
         <v>1.44</v>
@@ -7976,7 +8003,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ31">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR31">
         <v>0.48</v>
@@ -8101,7 +8128,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8179,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ32">
         <v>0.47</v>
@@ -8307,7 +8334,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8388,7 +8415,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ33">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR33">
         <v>0.95</v>
@@ -8719,7 +8746,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9006,7 +9033,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ36">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR36">
         <v>2.09</v>
@@ -9209,10 +9236,10 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR37">
         <v>1.35</v>
@@ -9621,10 +9648,10 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ39">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR39">
         <v>1.32</v>
@@ -9827,10 +9854,10 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ40">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -10033,10 +10060,10 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ41">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR41">
         <v>1</v>
@@ -10239,7 +10266,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ42">
         <v>1.29</v>
@@ -10448,7 +10475,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ43">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR43">
         <v>0</v>
@@ -10573,7 +10600,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10857,7 +10884,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ45">
         <v>0.8100000000000001</v>
@@ -11063,10 +11090,10 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ46">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -11191,7 +11218,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11887,10 +11914,10 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR50">
         <v>1.56</v>
@@ -12299,7 +12326,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ52">
         <v>0.47</v>
@@ -12508,7 +12535,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ53">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR53">
         <v>1.46</v>
@@ -12839,7 +12866,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -13045,7 +13072,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13123,10 +13150,10 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ56">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR56">
         <v>1.94</v>
@@ -13251,7 +13278,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13332,7 +13359,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ57">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -13457,7 +13484,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13535,7 +13562,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13741,7 +13768,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ59">
         <v>1.31</v>
@@ -13869,7 +13896,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13950,7 +13977,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ60">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -14156,7 +14183,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ61">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -14362,7 +14389,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR62">
         <v>1.36</v>
@@ -14487,7 +14514,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14565,7 +14592,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ63">
         <v>1.25</v>
@@ -14980,7 +15007,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ65">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>1.25</v>
@@ -15105,7 +15132,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15183,7 +15210,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ66">
         <v>0.8100000000000001</v>
@@ -15389,7 +15416,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>1.12</v>
@@ -15517,7 +15544,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15595,10 +15622,10 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ68">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR68">
         <v>1.07</v>
@@ -15723,7 +15750,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16216,7 +16243,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ71">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR71">
         <v>1.44</v>
@@ -16341,7 +16368,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16422,7 +16449,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ72">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR72">
         <v>1.35</v>
@@ -16547,7 +16574,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16753,7 +16780,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17243,7 +17270,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ76">
         <v>0.8100000000000001</v>
@@ -17449,7 +17476,7 @@
         <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ77">
         <v>0.8100000000000001</v>
@@ -17577,7 +17604,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17655,7 +17682,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ78">
         <v>0.47</v>
@@ -17783,7 +17810,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17861,7 +17888,7 @@
         <v>2.33</v>
       </c>
       <c r="AP79">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>1.25</v>
@@ -18067,10 +18094,10 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ80">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR80">
         <v>1.23</v>
@@ -18195,7 +18222,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18401,7 +18428,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18482,7 +18509,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ82">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR82">
         <v>1.41</v>
@@ -18607,7 +18634,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18891,10 +18918,10 @@
         <v>2.33</v>
       </c>
       <c r="AP84">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ84">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR84">
         <v>1.79</v>
@@ -19306,7 +19333,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ86">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19431,7 +19458,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19509,10 +19536,10 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ87">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR87">
         <v>1.47</v>
@@ -19843,7 +19870,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19921,7 +19948,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ89">
         <v>1.12</v>
@@ -20049,7 +20076,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20130,7 +20157,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ90">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR90">
         <v>1.45</v>
@@ -20333,7 +20360,7 @@
         <v>0.33</v>
       </c>
       <c r="AP91">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ91">
         <v>0.8100000000000001</v>
@@ -20461,7 +20488,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20542,7 +20569,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ92">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR92">
         <v>1.42</v>
@@ -20873,7 +20900,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20951,7 +20978,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -21079,7 +21106,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21157,7 +21184,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ95">
         <v>1.29</v>
@@ -21363,10 +21390,10 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ96">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR96">
         <v>1.53</v>
@@ -21778,7 +21805,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ98">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR98">
         <v>1.35</v>
@@ -21984,7 +22011,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ99">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR99">
         <v>1.46</v>
@@ -22109,7 +22136,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22190,7 +22217,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ100">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -22393,7 +22420,7 @@
         <v>1.2</v>
       </c>
       <c r="AP101">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ101">
         <v>0.47</v>
@@ -23220,7 +23247,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ105">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR105">
         <v>1.64</v>
@@ -23551,7 +23578,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23835,7 +23862,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ108">
         <v>1.29</v>
@@ -24044,7 +24071,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR109">
         <v>1.4</v>
@@ -24169,7 +24196,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24453,10 +24480,10 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ111">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR111">
         <v>1.54</v>
@@ -24581,7 +24608,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24659,10 +24686,10 @@
         <v>1.25</v>
       </c>
       <c r="AP112">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ112">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>1.61</v>
@@ -24787,7 +24814,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25199,7 +25226,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25277,10 +25304,10 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ115">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR115">
         <v>1.49</v>
@@ -25483,7 +25510,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ116">
         <v>1.12</v>
@@ -25689,10 +25716,10 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ117">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR117">
         <v>1.16</v>
@@ -25895,7 +25922,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ118">
         <v>1</v>
@@ -26023,7 +26050,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26104,7 +26131,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ119">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR119">
         <v>1.68</v>
@@ -26516,7 +26543,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ121">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR121">
         <v>1.32</v>
@@ -26641,7 +26668,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -27053,7 +27080,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27337,7 +27364,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27465,7 +27492,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27546,7 +27573,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ126">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR126">
         <v>1.8</v>
@@ -27877,7 +27904,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28164,7 +28191,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ129">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -28289,7 +28316,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28367,10 +28394,10 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR130">
         <v>1.64</v>
@@ -28495,7 +28522,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28573,7 +28600,7 @@
         <v>1.17</v>
       </c>
       <c r="AP131">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
         <v>1.29</v>
@@ -28701,7 +28728,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28782,7 +28809,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ132">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR132">
         <v>1.78</v>
@@ -28985,7 +29012,7 @@
         <v>0.2</v>
       </c>
       <c r="AP133">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ133">
         <v>0.19</v>
@@ -29113,7 +29140,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29194,7 +29221,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ134">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR134">
         <v>1.4</v>
@@ -29319,7 +29346,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29397,10 +29424,10 @@
         <v>0.83</v>
       </c>
       <c r="AP135">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ135">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR135">
         <v>1.12</v>
@@ -29937,7 +29964,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30015,7 +30042,7 @@
         <v>1.17</v>
       </c>
       <c r="AP138">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -30221,10 +30248,10 @@
         <v>1.17</v>
       </c>
       <c r="AP139">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ139">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR139">
         <v>1.66</v>
@@ -30430,7 +30457,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ140">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.34</v>
@@ -30555,7 +30582,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30761,7 +30788,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30967,7 +30994,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31045,10 +31072,10 @@
         <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ143">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR143">
         <v>1.11</v>
@@ -31173,7 +31200,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31585,7 +31612,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31663,10 +31690,10 @@
         <v>2</v>
       </c>
       <c r="AP146">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ146">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR146">
         <v>1.62</v>
@@ -31872,7 +31899,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ147">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR147">
         <v>1.4</v>
@@ -31997,7 +32024,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32075,7 +32102,7 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ148">
         <v>1.75</v>
@@ -32281,7 +32308,7 @@
         <v>1</v>
       </c>
       <c r="AP149">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ149">
         <v>1.31</v>
@@ -32899,7 +32926,7 @@
         <v>1.14</v>
       </c>
       <c r="AP152">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ152">
         <v>1</v>
@@ -33027,7 +33054,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33108,7 +33135,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ153">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR153">
         <v>1.58</v>
@@ -33314,7 +33341,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ154">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR154">
         <v>1.67</v>
@@ -33517,10 +33544,10 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ155">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR155">
         <v>1.59</v>
@@ -33645,7 +33672,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34135,7 +34162,7 @@
         <v>0.33</v>
       </c>
       <c r="AP158">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ158">
         <v>0.19</v>
@@ -34341,10 +34368,10 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ159">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR159">
         <v>1.75</v>
@@ -34547,7 +34574,7 @@
         <v>1.17</v>
       </c>
       <c r="AP160">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ160">
         <v>1.29</v>
@@ -34756,7 +34783,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ161">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR161">
         <v>1.62</v>
@@ -34959,7 +34986,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ162">
         <v>1.29</v>
@@ -35165,10 +35192,10 @@
         <v>1.43</v>
       </c>
       <c r="AP163">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ163">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR163">
         <v>1.14</v>
@@ -35293,7 +35320,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35371,7 +35398,7 @@
         <v>1.38</v>
       </c>
       <c r="AP164">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ164">
         <v>1.29</v>
@@ -35911,7 +35938,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35989,10 +36016,10 @@
         <v>1.75</v>
       </c>
       <c r="AP167">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ167">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR167">
         <v>1.65</v>
@@ -36401,7 +36428,7 @@
         <v>0.29</v>
       </c>
       <c r="AP169">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ169">
         <v>0.19</v>
@@ -36610,7 +36637,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ170">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR170">
         <v>1.57</v>
@@ -36941,7 +36968,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37019,10 +37046,10 @@
         <v>1.86</v>
       </c>
       <c r="AP172">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ172">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR172">
         <v>1.15</v>
@@ -37431,7 +37458,7 @@
         <v>0.14</v>
       </c>
       <c r="AP174">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ174">
         <v>1.12</v>
@@ -37559,7 +37586,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37640,7 +37667,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ175">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR175">
         <v>1.58</v>
@@ -37971,7 +37998,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38049,7 +38076,7 @@
         <v>0.88</v>
       </c>
       <c r="AP177">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ177">
         <v>1.29</v>
@@ -38383,7 +38410,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38461,7 +38488,7 @@
         <v>2</v>
       </c>
       <c r="AP179">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ179">
         <v>1.19</v>
@@ -38589,7 +38616,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38670,7 +38697,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ180">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR180">
         <v>1.48</v>
@@ -38873,10 +38900,10 @@
         <v>1.14</v>
       </c>
       <c r="AP181">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ181">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR181">
         <v>1.48</v>
@@ -39082,7 +39109,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ182">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR182">
         <v>1.26</v>
@@ -39288,7 +39315,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ183">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR183">
         <v>1.63</v>
@@ -39413,7 +39440,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39494,7 +39521,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ184">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR184">
         <v>1.69</v>
@@ -39697,7 +39724,7 @@
         <v>0.86</v>
       </c>
       <c r="AP185">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ185">
         <v>0.8100000000000001</v>
@@ -40237,7 +40264,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40318,7 +40345,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ188">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR188">
         <v>1.17</v>
@@ -40855,7 +40882,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40936,7 +40963,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ191">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR191">
         <v>1.48</v>
@@ -41061,7 +41088,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41139,7 +41166,7 @@
         <v>0.63</v>
       </c>
       <c r="AP192">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ192">
         <v>0.8100000000000001</v>
@@ -41267,7 +41294,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41345,7 +41372,7 @@
         <v>0.89</v>
       </c>
       <c r="AP193">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ193">
         <v>1.31</v>
@@ -41473,7 +41500,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41757,10 +41784,10 @@
         <v>1.75</v>
       </c>
       <c r="AP195">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ195">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR195">
         <v>1.66</v>
@@ -42169,7 +42196,7 @@
         <v>0.25</v>
       </c>
       <c r="AP197">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ197">
         <v>0.19</v>
@@ -42375,10 +42402,10 @@
         <v>1.25</v>
       </c>
       <c r="AP198">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ198">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR198">
         <v>1.19</v>
@@ -42581,10 +42608,10 @@
         <v>1.38</v>
       </c>
       <c r="AP199">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ199">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR199">
         <v>1.74</v>
@@ -42709,7 +42736,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43121,7 +43148,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43327,7 +43354,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43408,7 +43435,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ203">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR203">
         <v>1.49</v>
@@ -43611,10 +43638,10 @@
         <v>1.13</v>
       </c>
       <c r="AP204">
+        <v>1.18</v>
+      </c>
+      <c r="AQ204">
         <v>1.19</v>
-      </c>
-      <c r="AQ204">
-        <v>1.07</v>
       </c>
       <c r="AR204">
         <v>1.41</v>
@@ -43817,7 +43844,7 @@
         <v>1.75</v>
       </c>
       <c r="AP205">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ205">
         <v>1.19</v>
@@ -43945,7 +43972,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44232,7 +44259,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ207">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR207">
         <v>1.45</v>
@@ -44435,7 +44462,7 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ208">
         <v>1.29</v>
@@ -44847,10 +44874,10 @@
         <v>1.22</v>
       </c>
       <c r="AP210">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ210">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR210">
         <v>1.59</v>
@@ -44975,7 +45002,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45053,7 +45080,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP211">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ211">
         <v>0.8100000000000001</v>
@@ -45181,7 +45208,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45387,7 +45414,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45465,7 +45492,7 @@
         <v>1.5</v>
       </c>
       <c r="AP213">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ213">
         <v>1.29</v>
@@ -45593,7 +45620,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45674,7 +45701,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ214">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR214">
         <v>1.17</v>
@@ -46005,7 +46032,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46086,7 +46113,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ216">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR216">
         <v>1.46</v>
@@ -46498,7 +46525,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ218">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR218">
         <v>1.41</v>
@@ -46701,7 +46728,7 @@
         <v>0.22</v>
       </c>
       <c r="AP219">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ219">
         <v>0.19</v>
@@ -46907,7 +46934,7 @@
         <v>1.1</v>
       </c>
       <c r="AP220">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ220">
         <v>1</v>
@@ -47241,7 +47268,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47319,7 +47346,7 @@
         <v>0.2</v>
       </c>
       <c r="AP222">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ222">
         <v>1.12</v>
@@ -47653,7 +47680,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47734,7 +47761,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ224">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR224">
         <v>1.5</v>
@@ -48065,7 +48092,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48146,7 +48173,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ226">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR226">
         <v>1.73</v>
@@ -48349,7 +48376,7 @@
         <v>1</v>
       </c>
       <c r="AP227">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ227">
         <v>1.25</v>
@@ -48555,7 +48582,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ228">
         <v>1</v>
@@ -48683,7 +48710,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48764,7 +48791,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ229">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR229">
         <v>1.48</v>
@@ -48889,7 +48916,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49095,7 +49122,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49176,7 +49203,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ231">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR231">
         <v>1.26</v>
@@ -49382,7 +49409,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ232">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR232">
         <v>1.73</v>
@@ -49585,7 +49612,7 @@
         <v>0.55</v>
       </c>
       <c r="AP233">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ233">
         <v>0.47</v>
@@ -49791,10 +49818,10 @@
         <v>1.4</v>
       </c>
       <c r="AP234">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ234">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR234">
         <v>1.16</v>
@@ -49919,7 +49946,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -49997,7 +50024,7 @@
         <v>2.2</v>
       </c>
       <c r="AP235">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ235">
         <v>1.75</v>
@@ -50206,7 +50233,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ236">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR236">
         <v>1.23</v>
@@ -50412,7 +50439,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ237">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR237">
         <v>1.37</v>
@@ -50615,10 +50642,10 @@
         <v>1.1</v>
       </c>
       <c r="AP238">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ238">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR238">
         <v>1.62</v>
@@ -50743,7 +50770,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50821,7 +50848,7 @@
         <v>1.64</v>
       </c>
       <c r="AP239">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ239">
         <v>1.29</v>
@@ -51030,7 +51057,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ240">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR240">
         <v>1.44</v>
@@ -51236,7 +51263,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ241">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR241">
         <v>1.63</v>
@@ -51361,7 +51388,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51439,7 +51466,7 @@
         <v>0.5</v>
       </c>
       <c r="AP242">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ242">
         <v>0.8100000000000001</v>
@@ -51645,7 +51672,7 @@
         <v>1.27</v>
       </c>
       <c r="AP243">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ243">
         <v>1.31</v>
@@ -51773,7 +51800,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51851,7 +51878,7 @@
         <v>1</v>
       </c>
       <c r="AP244">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ244">
         <v>1.25</v>
@@ -52185,7 +52212,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52266,7 +52293,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ246">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR246">
         <v>1.56</v>
@@ -52678,7 +52705,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ248">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR248">
         <v>1.41</v>
@@ -52881,7 +52908,7 @@
         <v>1</v>
       </c>
       <c r="AP249">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ249">
         <v>0.8100000000000001</v>
@@ -53009,7 +53036,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53215,7 +53242,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53499,7 +53526,7 @@
         <v>1.27</v>
       </c>
       <c r="AP252">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ252">
         <v>1.29</v>
@@ -53627,7 +53654,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53708,7 +53735,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ253">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR253">
         <v>1.15</v>
@@ -54039,7 +54066,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54117,7 +54144,7 @@
         <v>2.09</v>
       </c>
       <c r="AP255">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ255">
         <v>1.75</v>
@@ -54245,7 +54272,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54326,7 +54353,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ256">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR256">
         <v>1.43</v>
@@ -54529,7 +54556,7 @@
         <v>0.58</v>
       </c>
       <c r="AP257">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ257">
         <v>0.47</v>
@@ -54944,7 +54971,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ259">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR259">
         <v>1.7</v>
@@ -55147,10 +55174,10 @@
         <v>1.36</v>
       </c>
       <c r="AP260">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ260">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR260">
         <v>1.59</v>
@@ -55275,7 +55302,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55353,7 +55380,7 @@
         <v>1.75</v>
       </c>
       <c r="AP261">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ261">
         <v>1.29</v>
@@ -55481,7 +55508,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55562,7 +55589,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ262">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR262">
         <v>1.34</v>
@@ -55768,7 +55795,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ263">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR263">
         <v>1.43</v>
@@ -55974,7 +56001,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ264">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR264">
         <v>1.24</v>
@@ -56099,7 +56126,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56177,7 +56204,7 @@
         <v>1.36</v>
       </c>
       <c r="AP265">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ265">
         <v>1.19</v>
@@ -56386,7 +56413,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ266">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR266">
         <v>1.24</v>
@@ -56592,7 +56619,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ267">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR267">
         <v>1.55</v>
@@ -56795,7 +56822,7 @@
         <v>1.42</v>
       </c>
       <c r="AP268">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ268">
         <v>1.31</v>
@@ -57001,10 +57028,10 @@
         <v>0.92</v>
       </c>
       <c r="AP269">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ269">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR269">
         <v>1.57</v>
@@ -57416,7 +57443,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ271">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR271">
         <v>1.48</v>
@@ -57541,7 +57568,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -57619,7 +57646,7 @@
         <v>0.67</v>
       </c>
       <c r="AP272">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ272">
         <v>1.12</v>
@@ -58443,10 +58470,10 @@
         <v>1.46</v>
       </c>
       <c r="AP276">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ276">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR276">
         <v>1.54</v>
@@ -58571,7 +58598,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58649,10 +58676,10 @@
         <v>1.25</v>
       </c>
       <c r="AP277">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ277">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR277">
         <v>1.22</v>
@@ -58858,7 +58885,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ278">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR278">
         <v>1.69</v>
@@ -59064,7 +59091,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ279">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR279">
         <v>1.34</v>
@@ -59807,7 +59834,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59885,7 +59912,7 @@
         <v>1.38</v>
       </c>
       <c r="AP283">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ283">
         <v>1.29</v>
@@ -60013,7 +60040,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60503,7 +60530,7 @@
         <v>0.75</v>
       </c>
       <c r="AP286">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ286">
         <v>1</v>
@@ -60631,7 +60658,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61121,10 +61148,10 @@
         <v>0.85</v>
       </c>
       <c r="AP289">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ289">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR289">
         <v>1.17</v>
@@ -61249,7 +61276,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61327,7 +61354,7 @@
         <v>1.17</v>
       </c>
       <c r="AP290">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ290">
         <v>1.25</v>
@@ -61455,7 +61482,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61742,7 +61769,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ292">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR292">
         <v>1.67</v>
@@ -61945,10 +61972,10 @@
         <v>1.46</v>
       </c>
       <c r="AP293">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ293">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR293">
         <v>1.47</v>
@@ -62151,7 +62178,7 @@
         <v>1.5</v>
       </c>
       <c r="AP294">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ294">
         <v>1.19</v>
@@ -62360,7 +62387,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ295">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR295">
         <v>1.6</v>
@@ -62563,7 +62590,7 @@
         <v>1</v>
       </c>
       <c r="AP296">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ296">
         <v>1</v>
@@ -62769,10 +62796,10 @@
         <v>1.17</v>
       </c>
       <c r="AP297">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ297">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR297">
         <v>1.76</v>
@@ -63181,7 +63208,7 @@
         <v>1</v>
       </c>
       <c r="AP299">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ299">
         <v>1.12</v>
@@ -63309,7 +63336,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63515,7 +63542,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63721,7 +63748,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -63802,7 +63829,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ302">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR302">
         <v>1.7</v>
@@ -64626,7 +64653,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ306">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR306">
         <v>1.68</v>
@@ -64829,7 +64856,7 @@
         <v>0.77</v>
       </c>
       <c r="AP307">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ307">
         <v>1</v>
@@ -65038,7 +65065,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ308">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR308">
         <v>1.45</v>
@@ -65163,7 +65190,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65241,7 +65268,7 @@
         <v>0.64</v>
       </c>
       <c r="AP309">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ309">
         <v>0.8100000000000001</v>
@@ -65447,7 +65474,7 @@
         <v>1</v>
       </c>
       <c r="AP310">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ310">
         <v>0.8100000000000001</v>
@@ -65656,7 +65683,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ311">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR311">
         <v>1.67</v>
@@ -65862,7 +65889,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ312">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR312">
         <v>1.54</v>
@@ -65987,7 +66014,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66065,10 +66092,10 @@
         <v>1</v>
       </c>
       <c r="AP313">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ313">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR313">
         <v>1.7</v>
@@ -66271,7 +66298,7 @@
         <v>1.46</v>
       </c>
       <c r="AP314">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ314">
         <v>1.19</v>
@@ -66399,7 +66426,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66477,10 +66504,10 @@
         <v>1.36</v>
       </c>
       <c r="AP315">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ315">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR315">
         <v>1.64</v>
@@ -66605,7 +66632,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -66683,10 +66710,10 @@
         <v>1.43</v>
       </c>
       <c r="AP316">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ316">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR316">
         <v>1.53</v>
@@ -66889,7 +66916,7 @@
         <v>1.31</v>
       </c>
       <c r="AP317">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ317">
         <v>1.25</v>
@@ -67095,10 +67122,10 @@
         <v>1.15</v>
       </c>
       <c r="AP318">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ318">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR318">
         <v>1.61</v>
@@ -67507,10 +67534,10 @@
         <v>0.86</v>
       </c>
       <c r="AP320">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ320">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR320">
         <v>1.19</v>
@@ -68334,7 +68361,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ324">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR324">
         <v>1.69</v>
@@ -68665,7 +68692,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -69077,7 +69104,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -69979,10 +70006,10 @@
         <v>1.07</v>
       </c>
       <c r="AP332">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ332">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR332">
         <v>1.6</v>
@@ -70185,7 +70212,7 @@
         <v>0.8</v>
       </c>
       <c r="AP333">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AQ333">
         <v>0.8100000000000001</v>
@@ -70391,10 +70418,10 @@
         <v>1</v>
       </c>
       <c r="AP334">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ334">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR334">
         <v>1.53</v>
@@ -70597,10 +70624,10 @@
         <v>1</v>
       </c>
       <c r="AP335">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ335">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR335">
         <v>1.16</v>
@@ -70803,10 +70830,10 @@
         <v>1.33</v>
       </c>
       <c r="AP336">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ336">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR336">
         <v>1.73</v>
@@ -71009,10 +71036,10 @@
         <v>1</v>
       </c>
       <c r="AP337">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ337">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR337">
         <v>1.66</v>
@@ -71137,7 +71164,7 @@
         <v>302</v>
       </c>
       <c r="P338" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="Q338">
         <v>3.5</v>
@@ -71215,10 +71242,10 @@
         <v>1.07</v>
       </c>
       <c r="AP338">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ338">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR338">
         <v>1.53</v>
@@ -71343,7 +71370,7 @@
         <v>183</v>
       </c>
       <c r="P339" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="Q339">
         <v>3.4</v>
@@ -71421,10 +71448,10 @@
         <v>1.53</v>
       </c>
       <c r="AP339">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ339">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AR339">
         <v>1.26</v>
@@ -71627,7 +71654,7 @@
         <v>0.2</v>
       </c>
       <c r="AP340">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ340">
         <v>0.19</v>
@@ -71961,7 +71988,7 @@
         <v>304</v>
       </c>
       <c r="P342" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="Q342">
         <v>2.88</v>
@@ -72042,7 +72069,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ342">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR342">
         <v>1.68</v>
@@ -73197,7 +73224,7 @@
         <v>310</v>
       </c>
       <c r="P348" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="Q348">
         <v>2.3</v>
@@ -73278,7 +73305,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ348">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AR348">
         <v>1.69</v>
@@ -73403,7 +73430,7 @@
         <v>311</v>
       </c>
       <c r="P349" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="Q349">
         <v>2.6</v>
@@ -73609,7 +73636,7 @@
         <v>94</v>
       </c>
       <c r="P350" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="Q350">
         <v>2.63</v>
@@ -74021,7 +74048,7 @@
         <v>313</v>
       </c>
       <c r="P352" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="Q352">
         <v>1.8</v>
@@ -74227,7 +74254,7 @@
         <v>117</v>
       </c>
       <c r="P353" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q353">
         <v>2.88</v>
@@ -74590,6 +74617,1860 @@
       </c>
       <c r="BP354">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="355" spans="1:68">
+      <c r="A355" s="1">
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>7728556</v>
+      </c>
+      <c r="C355" t="s">
+        <v>68</v>
+      </c>
+      <c r="D355" t="s">
+        <v>69</v>
+      </c>
+      <c r="E355" s="2">
+        <v>45745.41666666666</v>
+      </c>
+      <c r="F355">
+        <v>33</v>
+      </c>
+      <c r="G355" t="s">
+        <v>80</v>
+      </c>
+      <c r="H355" t="s">
+        <v>78</v>
+      </c>
+      <c r="I355">
+        <v>0</v>
+      </c>
+      <c r="J355">
+        <v>0</v>
+      </c>
+      <c r="K355">
+        <v>0</v>
+      </c>
+      <c r="L355">
+        <v>0</v>
+      </c>
+      <c r="M355">
+        <v>0</v>
+      </c>
+      <c r="N355">
+        <v>0</v>
+      </c>
+      <c r="O355" t="s">
+        <v>94</v>
+      </c>
+      <c r="P355" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q355">
+        <v>3.25</v>
+      </c>
+      <c r="R355">
+        <v>1.83</v>
+      </c>
+      <c r="S355">
+        <v>4</v>
+      </c>
+      <c r="T355">
+        <v>1.62</v>
+      </c>
+      <c r="U355">
+        <v>2.2</v>
+      </c>
+      <c r="V355">
+        <v>4</v>
+      </c>
+      <c r="W355">
+        <v>1.22</v>
+      </c>
+      <c r="X355">
+        <v>13</v>
+      </c>
+      <c r="Y355">
+        <v>1.04</v>
+      </c>
+      <c r="Z355">
+        <v>2.38</v>
+      </c>
+      <c r="AA355">
+        <v>3.06</v>
+      </c>
+      <c r="AB355">
+        <v>3.47</v>
+      </c>
+      <c r="AC355">
+        <v>1.12</v>
+      </c>
+      <c r="AD355">
+        <v>6</v>
+      </c>
+      <c r="AE355">
+        <v>1.48</v>
+      </c>
+      <c r="AF355">
+        <v>2.37</v>
+      </c>
+      <c r="AG355">
+        <v>2.85</v>
+      </c>
+      <c r="AH355">
+        <v>1.37</v>
+      </c>
+      <c r="AI355">
+        <v>2.2</v>
+      </c>
+      <c r="AJ355">
+        <v>1.62</v>
+      </c>
+      <c r="AK355">
+        <v>1.33</v>
+      </c>
+      <c r="AL355">
+        <v>1.36</v>
+      </c>
+      <c r="AM355">
+        <v>1.57</v>
+      </c>
+      <c r="AN355">
+        <v>1.19</v>
+      </c>
+      <c r="AO355">
+        <v>1.13</v>
+      </c>
+      <c r="AP355">
+        <v>1.18</v>
+      </c>
+      <c r="AQ355">
+        <v>1.12</v>
+      </c>
+      <c r="AR355">
+        <v>1.52</v>
+      </c>
+      <c r="AS355">
+        <v>1.2</v>
+      </c>
+      <c r="AT355">
+        <v>2.72</v>
+      </c>
+      <c r="AU355">
+        <v>7</v>
+      </c>
+      <c r="AV355">
+        <v>3</v>
+      </c>
+      <c r="AW355">
+        <v>13</v>
+      </c>
+      <c r="AX355">
+        <v>4</v>
+      </c>
+      <c r="AY355">
+        <v>20</v>
+      </c>
+      <c r="AZ355">
+        <v>8</v>
+      </c>
+      <c r="BA355">
+        <v>6</v>
+      </c>
+      <c r="BB355">
+        <v>3</v>
+      </c>
+      <c r="BC355">
+        <v>9</v>
+      </c>
+      <c r="BD355">
+        <v>1.74</v>
+      </c>
+      <c r="BE355">
+        <v>6.4</v>
+      </c>
+      <c r="BF355">
+        <v>2.32</v>
+      </c>
+      <c r="BG355">
+        <v>1.4</v>
+      </c>
+      <c r="BH355">
+        <v>2.65</v>
+      </c>
+      <c r="BI355">
+        <v>1.65</v>
+      </c>
+      <c r="BJ355">
+        <v>2.06</v>
+      </c>
+      <c r="BK355">
+        <v>2.04</v>
+      </c>
+      <c r="BL355">
+        <v>1.66</v>
+      </c>
+      <c r="BM355">
+        <v>2.65</v>
+      </c>
+      <c r="BN355">
+        <v>1.4</v>
+      </c>
+      <c r="BO355">
+        <v>3.4</v>
+      </c>
+      <c r="BP355">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="356" spans="1:68">
+      <c r="A356" s="1">
+        <v>355</v>
+      </c>
+      <c r="B356">
+        <v>7728557</v>
+      </c>
+      <c r="C356" t="s">
+        <v>68</v>
+      </c>
+      <c r="D356" t="s">
+        <v>69</v>
+      </c>
+      <c r="E356" s="2">
+        <v>45745.51041666666</v>
+      </c>
+      <c r="F356">
+        <v>33</v>
+      </c>
+      <c r="G356" t="s">
+        <v>74</v>
+      </c>
+      <c r="H356" t="s">
+        <v>75</v>
+      </c>
+      <c r="I356">
+        <v>0</v>
+      </c>
+      <c r="J356">
+        <v>1</v>
+      </c>
+      <c r="K356">
+        <v>1</v>
+      </c>
+      <c r="L356">
+        <v>0</v>
+      </c>
+      <c r="M356">
+        <v>1</v>
+      </c>
+      <c r="N356">
+        <v>1</v>
+      </c>
+      <c r="O356" t="s">
+        <v>94</v>
+      </c>
+      <c r="P356" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q356">
+        <v>4.33</v>
+      </c>
+      <c r="R356">
+        <v>1.95</v>
+      </c>
+      <c r="S356">
+        <v>3</v>
+      </c>
+      <c r="T356">
+        <v>1.53</v>
+      </c>
+      <c r="U356">
+        <v>2.38</v>
+      </c>
+      <c r="V356">
+        <v>3.75</v>
+      </c>
+      <c r="W356">
+        <v>1.25</v>
+      </c>
+      <c r="X356">
+        <v>11</v>
+      </c>
+      <c r="Y356">
+        <v>1.05</v>
+      </c>
+      <c r="Z356">
+        <v>3.6</v>
+      </c>
+      <c r="AA356">
+        <v>3.18</v>
+      </c>
+      <c r="AB356">
+        <v>2.26</v>
+      </c>
+      <c r="AC356">
+        <v>1.1</v>
+      </c>
+      <c r="AD356">
+        <v>6.5</v>
+      </c>
+      <c r="AE356">
+        <v>1.48</v>
+      </c>
+      <c r="AF356">
+        <v>2.6</v>
+      </c>
+      <c r="AG356">
+        <v>2.3</v>
+      </c>
+      <c r="AH356">
+        <v>1.5</v>
+      </c>
+      <c r="AI356">
+        <v>2.1</v>
+      </c>
+      <c r="AJ356">
+        <v>1.67</v>
+      </c>
+      <c r="AK356">
+        <v>1.65</v>
+      </c>
+      <c r="AL356">
+        <v>1.34</v>
+      </c>
+      <c r="AM356">
+        <v>1.29</v>
+      </c>
+      <c r="AN356">
+        <v>0.63</v>
+      </c>
+      <c r="AO356">
+        <v>1.44</v>
+      </c>
+      <c r="AP356">
+        <v>0.59</v>
+      </c>
+      <c r="AQ356">
+        <v>1.53</v>
+      </c>
+      <c r="AR356">
+        <v>1.18</v>
+      </c>
+      <c r="AS356">
+        <v>1.3</v>
+      </c>
+      <c r="AT356">
+        <v>2.48</v>
+      </c>
+      <c r="AU356">
+        <v>3</v>
+      </c>
+      <c r="AV356">
+        <v>5</v>
+      </c>
+      <c r="AW356">
+        <v>7</v>
+      </c>
+      <c r="AX356">
+        <v>3</v>
+      </c>
+      <c r="AY356">
+        <v>11</v>
+      </c>
+      <c r="AZ356">
+        <v>8</v>
+      </c>
+      <c r="BA356">
+        <v>7</v>
+      </c>
+      <c r="BB356">
+        <v>3</v>
+      </c>
+      <c r="BC356">
+        <v>10</v>
+      </c>
+      <c r="BD356">
+        <v>2.1</v>
+      </c>
+      <c r="BE356">
+        <v>6.5</v>
+      </c>
+      <c r="BF356">
+        <v>1.88</v>
+      </c>
+      <c r="BG356">
+        <v>1.32</v>
+      </c>
+      <c r="BH356">
+        <v>3</v>
+      </c>
+      <c r="BI356">
+        <v>1.54</v>
+      </c>
+      <c r="BJ356">
+        <v>2.25</v>
+      </c>
+      <c r="BK356">
+        <v>1.88</v>
+      </c>
+      <c r="BL356">
+        <v>1.78</v>
+      </c>
+      <c r="BM356">
+        <v>2.38</v>
+      </c>
+      <c r="BN356">
+        <v>1.48</v>
+      </c>
+      <c r="BO356">
+        <v>3.1</v>
+      </c>
+      <c r="BP356">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="357" spans="1:68">
+      <c r="A357" s="1">
+        <v>356</v>
+      </c>
+      <c r="B357">
+        <v>7728552</v>
+      </c>
+      <c r="C357" t="s">
+        <v>68</v>
+      </c>
+      <c r="D357" t="s">
+        <v>69</v>
+      </c>
+      <c r="E357" s="2">
+        <v>45745.60416666666</v>
+      </c>
+      <c r="F357">
+        <v>33</v>
+      </c>
+      <c r="G357" t="s">
+        <v>87</v>
+      </c>
+      <c r="H357" t="s">
+        <v>86</v>
+      </c>
+      <c r="I357">
+        <v>2</v>
+      </c>
+      <c r="J357">
+        <v>0</v>
+      </c>
+      <c r="K357">
+        <v>2</v>
+      </c>
+      <c r="L357">
+        <v>2</v>
+      </c>
+      <c r="M357">
+        <v>2</v>
+      </c>
+      <c r="N357">
+        <v>4</v>
+      </c>
+      <c r="O357" t="s">
+        <v>315</v>
+      </c>
+      <c r="P357" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q357">
+        <v>4.6</v>
+      </c>
+      <c r="R357">
+        <v>2.1</v>
+      </c>
+      <c r="S357">
+        <v>2.35</v>
+      </c>
+      <c r="T357">
+        <v>1.4</v>
+      </c>
+      <c r="U357">
+        <v>2.7</v>
+      </c>
+      <c r="V357">
+        <v>2.8</v>
+      </c>
+      <c r="W357">
+        <v>1.37</v>
+      </c>
+      <c r="X357">
+        <v>7.25</v>
+      </c>
+      <c r="Y357">
+        <v>1.08</v>
+      </c>
+      <c r="Z357">
+        <v>4.7</v>
+      </c>
+      <c r="AA357">
+        <v>3.78</v>
+      </c>
+      <c r="AB357">
+        <v>1.79</v>
+      </c>
+      <c r="AC357">
+        <v>1.05</v>
+      </c>
+      <c r="AD357">
+        <v>9</v>
+      </c>
+      <c r="AE357">
+        <v>1.33</v>
+      </c>
+      <c r="AF357">
+        <v>3.3</v>
+      </c>
+      <c r="AG357">
+        <v>1.85</v>
+      </c>
+      <c r="AH357">
+        <v>1.85</v>
+      </c>
+      <c r="AI357">
+        <v>1.85</v>
+      </c>
+      <c r="AJ357">
+        <v>1.83</v>
+      </c>
+      <c r="AK357">
+        <v>2</v>
+      </c>
+      <c r="AL357">
+        <v>1.27</v>
+      </c>
+      <c r="AM357">
+        <v>1.2</v>
+      </c>
+      <c r="AN357">
+        <v>0.53</v>
+      </c>
+      <c r="AO357">
+        <v>1.19</v>
+      </c>
+      <c r="AP357">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ357">
+        <v>1.18</v>
+      </c>
+      <c r="AR357">
+        <v>1.16</v>
+      </c>
+      <c r="AS357">
+        <v>1.29</v>
+      </c>
+      <c r="AT357">
+        <v>2.45</v>
+      </c>
+      <c r="AU357">
+        <v>4</v>
+      </c>
+      <c r="AV357">
+        <v>11</v>
+      </c>
+      <c r="AW357">
+        <v>2</v>
+      </c>
+      <c r="AX357">
+        <v>12</v>
+      </c>
+      <c r="AY357">
+        <v>6</v>
+      </c>
+      <c r="AZ357">
+        <v>27</v>
+      </c>
+      <c r="BA357">
+        <v>1</v>
+      </c>
+      <c r="BB357">
+        <v>8</v>
+      </c>
+      <c r="BC357">
+        <v>9</v>
+      </c>
+      <c r="BD357">
+        <v>3.05</v>
+      </c>
+      <c r="BE357">
+        <v>7</v>
+      </c>
+      <c r="BF357">
+        <v>1.45</v>
+      </c>
+      <c r="BG357">
+        <v>1.34</v>
+      </c>
+      <c r="BH357">
+        <v>2.9</v>
+      </c>
+      <c r="BI357">
+        <v>1.57</v>
+      </c>
+      <c r="BJ357">
+        <v>2.2</v>
+      </c>
+      <c r="BK357">
+        <v>1.91</v>
+      </c>
+      <c r="BL357">
+        <v>1.76</v>
+      </c>
+      <c r="BM357">
+        <v>2.4</v>
+      </c>
+      <c r="BN357">
+        <v>1.48</v>
+      </c>
+      <c r="BO357">
+        <v>3.15</v>
+      </c>
+      <c r="BP357">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="358" spans="1:68">
+      <c r="A358" s="1">
+        <v>357</v>
+      </c>
+      <c r="B358">
+        <v>7728555</v>
+      </c>
+      <c r="C358" t="s">
+        <v>68</v>
+      </c>
+      <c r="D358" t="s">
+        <v>69</v>
+      </c>
+      <c r="E358" s="2">
+        <v>45745.60416666666</v>
+      </c>
+      <c r="F358">
+        <v>33</v>
+      </c>
+      <c r="G358" t="s">
+        <v>77</v>
+      </c>
+      <c r="H358" t="s">
+        <v>91</v>
+      </c>
+      <c r="I358">
+        <v>0</v>
+      </c>
+      <c r="J358">
+        <v>0</v>
+      </c>
+      <c r="K358">
+        <v>0</v>
+      </c>
+      <c r="L358">
+        <v>2</v>
+      </c>
+      <c r="M358">
+        <v>0</v>
+      </c>
+      <c r="N358">
+        <v>2</v>
+      </c>
+      <c r="O358" t="s">
+        <v>316</v>
+      </c>
+      <c r="P358" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q358">
+        <v>2.6</v>
+      </c>
+      <c r="R358">
+        <v>2.2</v>
+      </c>
+      <c r="S358">
+        <v>4.33</v>
+      </c>
+      <c r="T358">
+        <v>1.4</v>
+      </c>
+      <c r="U358">
+        <v>2.75</v>
+      </c>
+      <c r="V358">
+        <v>3</v>
+      </c>
+      <c r="W358">
+        <v>1.36</v>
+      </c>
+      <c r="X358">
+        <v>8</v>
+      </c>
+      <c r="Y358">
+        <v>1.08</v>
+      </c>
+      <c r="Z358">
+        <v>1.93</v>
+      </c>
+      <c r="AA358">
+        <v>3.74</v>
+      </c>
+      <c r="AB358">
+        <v>4</v>
+      </c>
+      <c r="AC358">
+        <v>1.05</v>
+      </c>
+      <c r="AD358">
+        <v>9</v>
+      </c>
+      <c r="AE358">
+        <v>1.3</v>
+      </c>
+      <c r="AF358">
+        <v>3.4</v>
+      </c>
+      <c r="AG358">
+        <v>1.96</v>
+      </c>
+      <c r="AH358">
+        <v>1.85</v>
+      </c>
+      <c r="AI358">
+        <v>1.8</v>
+      </c>
+      <c r="AJ358">
+        <v>1.91</v>
+      </c>
+      <c r="AK358">
+        <v>1.24</v>
+      </c>
+      <c r="AL358">
+        <v>1.29</v>
+      </c>
+      <c r="AM358">
+        <v>1.83</v>
+      </c>
+      <c r="AN358">
+        <v>1.75</v>
+      </c>
+      <c r="AO358">
+        <v>1.25</v>
+      </c>
+      <c r="AP358">
+        <v>1.82</v>
+      </c>
+      <c r="AQ358">
+        <v>1.18</v>
+      </c>
+      <c r="AR358">
+        <v>1.58</v>
+      </c>
+      <c r="AS358">
+        <v>1.37</v>
+      </c>
+      <c r="AT358">
+        <v>2.95</v>
+      </c>
+      <c r="AU358">
+        <v>4</v>
+      </c>
+      <c r="AV358">
+        <v>2</v>
+      </c>
+      <c r="AW358">
+        <v>18</v>
+      </c>
+      <c r="AX358">
+        <v>3</v>
+      </c>
+      <c r="AY358">
+        <v>31</v>
+      </c>
+      <c r="AZ358">
+        <v>6</v>
+      </c>
+      <c r="BA358">
+        <v>9</v>
+      </c>
+      <c r="BB358">
+        <v>4</v>
+      </c>
+      <c r="BC358">
+        <v>13</v>
+      </c>
+      <c r="BD358">
+        <v>1.57</v>
+      </c>
+      <c r="BE358">
+        <v>6.75</v>
+      </c>
+      <c r="BF358">
+        <v>2.65</v>
+      </c>
+      <c r="BG358">
+        <v>1.35</v>
+      </c>
+      <c r="BH358">
+        <v>2.85</v>
+      </c>
+      <c r="BI358">
+        <v>1.6</v>
+      </c>
+      <c r="BJ358">
+        <v>2.14</v>
+      </c>
+      <c r="BK358">
+        <v>1.98</v>
+      </c>
+      <c r="BL358">
+        <v>1.7</v>
+      </c>
+      <c r="BM358">
+        <v>2.5</v>
+      </c>
+      <c r="BN358">
+        <v>1.44</v>
+      </c>
+      <c r="BO358">
+        <v>3.3</v>
+      </c>
+      <c r="BP358">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="359" spans="1:68">
+      <c r="A359" s="1">
+        <v>358</v>
+      </c>
+      <c r="B359">
+        <v>7728550</v>
+      </c>
+      <c r="C359" t="s">
+        <v>68</v>
+      </c>
+      <c r="D359" t="s">
+        <v>69</v>
+      </c>
+      <c r="E359" s="2">
+        <v>45745.70833333334</v>
+      </c>
+      <c r="F359">
+        <v>33</v>
+      </c>
+      <c r="G359" t="s">
+        <v>90</v>
+      </c>
+      <c r="H359" t="s">
+        <v>82</v>
+      </c>
+      <c r="I359">
+        <v>0</v>
+      </c>
+      <c r="J359">
+        <v>0</v>
+      </c>
+      <c r="K359">
+        <v>0</v>
+      </c>
+      <c r="L359">
+        <v>1</v>
+      </c>
+      <c r="M359">
+        <v>0</v>
+      </c>
+      <c r="N359">
+        <v>1</v>
+      </c>
+      <c r="O359" t="s">
+        <v>159</v>
+      </c>
+      <c r="P359" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q359">
+        <v>2.55</v>
+      </c>
+      <c r="R359">
+        <v>2.1</v>
+      </c>
+      <c r="S359">
+        <v>3.9</v>
+      </c>
+      <c r="T359">
+        <v>1.36</v>
+      </c>
+      <c r="U359">
+        <v>2.87</v>
+      </c>
+      <c r="V359">
+        <v>2.6</v>
+      </c>
+      <c r="W359">
+        <v>1.43</v>
+      </c>
+      <c r="X359">
+        <v>6.5</v>
+      </c>
+      <c r="Y359">
+        <v>1.1</v>
+      </c>
+      <c r="Z359">
+        <v>1.88</v>
+      </c>
+      <c r="AA359">
+        <v>3.82</v>
+      </c>
+      <c r="AB359">
+        <v>4.2</v>
+      </c>
+      <c r="AC359">
+        <v>1.06</v>
+      </c>
+      <c r="AD359">
+        <v>8.5</v>
+      </c>
+      <c r="AE359">
+        <v>1.28</v>
+      </c>
+      <c r="AF359">
+        <v>3.65</v>
+      </c>
+      <c r="AG359">
+        <v>1.89</v>
+      </c>
+      <c r="AH359">
+        <v>1.92</v>
+      </c>
+      <c r="AI359">
+        <v>1.68</v>
+      </c>
+      <c r="AJ359">
+        <v>2.05</v>
+      </c>
+      <c r="AK359">
+        <v>1.28</v>
+      </c>
+      <c r="AL359">
+        <v>1.3</v>
+      </c>
+      <c r="AM359">
+        <v>1.75</v>
+      </c>
+      <c r="AN359">
+        <v>1.87</v>
+      </c>
+      <c r="AO359">
+        <v>1.63</v>
+      </c>
+      <c r="AP359">
+        <v>1.94</v>
+      </c>
+      <c r="AQ359">
+        <v>1.53</v>
+      </c>
+      <c r="AR359">
+        <v>1.73</v>
+      </c>
+      <c r="AS359">
+        <v>1.25</v>
+      </c>
+      <c r="AT359">
+        <v>2.98</v>
+      </c>
+      <c r="AU359">
+        <v>5</v>
+      </c>
+      <c r="AV359">
+        <v>2</v>
+      </c>
+      <c r="AW359">
+        <v>11</v>
+      </c>
+      <c r="AX359">
+        <v>7</v>
+      </c>
+      <c r="AY359">
+        <v>18</v>
+      </c>
+      <c r="AZ359">
+        <v>10</v>
+      </c>
+      <c r="BA359">
+        <v>10</v>
+      </c>
+      <c r="BB359">
+        <v>4</v>
+      </c>
+      <c r="BC359">
+        <v>14</v>
+      </c>
+      <c r="BD359">
+        <v>1.61</v>
+      </c>
+      <c r="BE359">
+        <v>6.75</v>
+      </c>
+      <c r="BF359">
+        <v>2.55</v>
+      </c>
+      <c r="BG359">
+        <v>1.3</v>
+      </c>
+      <c r="BH359">
+        <v>3.05</v>
+      </c>
+      <c r="BI359">
+        <v>1.54</v>
+      </c>
+      <c r="BJ359">
+        <v>2.25</v>
+      </c>
+      <c r="BK359">
+        <v>1.87</v>
+      </c>
+      <c r="BL359">
+        <v>1.79</v>
+      </c>
+      <c r="BM359">
+        <v>2.35</v>
+      </c>
+      <c r="BN359">
+        <v>1.5</v>
+      </c>
+      <c r="BO359">
+        <v>3.05</v>
+      </c>
+      <c r="BP359">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="360" spans="1:68">
+      <c r="A360" s="1">
+        <v>359</v>
+      </c>
+      <c r="B360">
+        <v>7728553</v>
+      </c>
+      <c r="C360" t="s">
+        <v>68</v>
+      </c>
+      <c r="D360" t="s">
+        <v>69</v>
+      </c>
+      <c r="E360" s="2">
+        <v>45746.375</v>
+      </c>
+      <c r="F360">
+        <v>33</v>
+      </c>
+      <c r="G360" t="s">
+        <v>88</v>
+      </c>
+      <c r="H360" t="s">
+        <v>79</v>
+      </c>
+      <c r="I360">
+        <v>1</v>
+      </c>
+      <c r="J360">
+        <v>1</v>
+      </c>
+      <c r="K360">
+        <v>2</v>
+      </c>
+      <c r="L360">
+        <v>1</v>
+      </c>
+      <c r="M360">
+        <v>2</v>
+      </c>
+      <c r="N360">
+        <v>3</v>
+      </c>
+      <c r="O360" t="s">
+        <v>147</v>
+      </c>
+      <c r="P360" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q360">
+        <v>3.25</v>
+      </c>
+      <c r="R360">
+        <v>2.05</v>
+      </c>
+      <c r="S360">
+        <v>3.5</v>
+      </c>
+      <c r="T360">
+        <v>1.5</v>
+      </c>
+      <c r="U360">
+        <v>2.5</v>
+      </c>
+      <c r="V360">
+        <v>3.4</v>
+      </c>
+      <c r="W360">
+        <v>1.3</v>
+      </c>
+      <c r="X360">
+        <v>10</v>
+      </c>
+      <c r="Y360">
+        <v>1.06</v>
+      </c>
+      <c r="Z360">
+        <v>2.63</v>
+      </c>
+      <c r="AA360">
+        <v>3.4</v>
+      </c>
+      <c r="AB360">
+        <v>2.77</v>
+      </c>
+      <c r="AC360">
+        <v>1.07</v>
+      </c>
+      <c r="AD360">
+        <v>8</v>
+      </c>
+      <c r="AE360">
+        <v>1.4</v>
+      </c>
+      <c r="AF360">
+        <v>2.9</v>
+      </c>
+      <c r="AG360">
+        <v>1.95</v>
+      </c>
+      <c r="AH360">
+        <v>1.73</v>
+      </c>
+      <c r="AI360">
+        <v>1.83</v>
+      </c>
+      <c r="AJ360">
+        <v>1.83</v>
+      </c>
+      <c r="AK360">
+        <v>1.42</v>
+      </c>
+      <c r="AL360">
+        <v>1.34</v>
+      </c>
+      <c r="AM360">
+        <v>1.49</v>
+      </c>
+      <c r="AN360">
+        <v>1.73</v>
+      </c>
+      <c r="AO360">
+        <v>1.07</v>
+      </c>
+      <c r="AP360">
+        <v>1.63</v>
+      </c>
+      <c r="AQ360">
+        <v>1.19</v>
+      </c>
+      <c r="AR360">
+        <v>1.68</v>
+      </c>
+      <c r="AS360">
+        <v>1.29</v>
+      </c>
+      <c r="AT360">
+        <v>2.97</v>
+      </c>
+      <c r="AU360">
+        <v>9</v>
+      </c>
+      <c r="AV360">
+        <v>5</v>
+      </c>
+      <c r="AW360">
+        <v>12</v>
+      </c>
+      <c r="AX360">
+        <v>4</v>
+      </c>
+      <c r="AY360">
+        <v>26</v>
+      </c>
+      <c r="AZ360">
+        <v>9</v>
+      </c>
+      <c r="BA360">
+        <v>11</v>
+      </c>
+      <c r="BB360">
+        <v>2</v>
+      </c>
+      <c r="BC360">
+        <v>13</v>
+      </c>
+      <c r="BD360">
+        <v>1.83</v>
+      </c>
+      <c r="BE360">
+        <v>6.4</v>
+      </c>
+      <c r="BF360">
+        <v>2.18</v>
+      </c>
+      <c r="BG360">
+        <v>1.4</v>
+      </c>
+      <c r="BH360">
+        <v>2.65</v>
+      </c>
+      <c r="BI360">
+        <v>1.68</v>
+      </c>
+      <c r="BJ360">
+        <v>2</v>
+      </c>
+      <c r="BK360">
+        <v>2.12</v>
+      </c>
+      <c r="BL360">
+        <v>1.61</v>
+      </c>
+      <c r="BM360">
+        <v>2.7</v>
+      </c>
+      <c r="BN360">
+        <v>1.38</v>
+      </c>
+      <c r="BO360">
+        <v>3.65</v>
+      </c>
+      <c r="BP360">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="361" spans="1:68">
+      <c r="A361" s="1">
+        <v>360</v>
+      </c>
+      <c r="B361">
+        <v>7728559</v>
+      </c>
+      <c r="C361" t="s">
+        <v>68</v>
+      </c>
+      <c r="D361" t="s">
+        <v>69</v>
+      </c>
+      <c r="E361" s="2">
+        <v>45746.46875</v>
+      </c>
+      <c r="F361">
+        <v>33</v>
+      </c>
+      <c r="G361" t="s">
+        <v>89</v>
+      </c>
+      <c r="H361" t="s">
+        <v>83</v>
+      </c>
+      <c r="I361">
+        <v>0</v>
+      </c>
+      <c r="J361">
+        <v>0</v>
+      </c>
+      <c r="K361">
+        <v>0</v>
+      </c>
+      <c r="L361">
+        <v>2</v>
+      </c>
+      <c r="M361">
+        <v>1</v>
+      </c>
+      <c r="N361">
+        <v>3</v>
+      </c>
+      <c r="O361" t="s">
+        <v>317</v>
+      </c>
+      <c r="P361" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q361">
+        <v>2.3</v>
+      </c>
+      <c r="R361">
+        <v>2</v>
+      </c>
+      <c r="S361">
+        <v>5.25</v>
+      </c>
+      <c r="T361">
+        <v>1.48</v>
+      </c>
+      <c r="U361">
+        <v>2.45</v>
+      </c>
+      <c r="V361">
+        <v>3.3</v>
+      </c>
+      <c r="W361">
+        <v>1.28</v>
+      </c>
+      <c r="X361">
+        <v>9.6</v>
+      </c>
+      <c r="Y361">
+        <v>1.04</v>
+      </c>
+      <c r="Z361">
+        <v>1.69</v>
+      </c>
+      <c r="AA361">
+        <v>3.73</v>
+      </c>
+      <c r="AB361">
+        <v>5.7</v>
+      </c>
+      <c r="AC361">
+        <v>1.08</v>
+      </c>
+      <c r="AD361">
+        <v>7.5</v>
+      </c>
+      <c r="AE361">
+        <v>1.45</v>
+      </c>
+      <c r="AF361">
+        <v>2.7</v>
+      </c>
+      <c r="AG361">
+        <v>2.25</v>
+      </c>
+      <c r="AH361">
+        <v>1.5</v>
+      </c>
+      <c r="AI361">
+        <v>2.2</v>
+      </c>
+      <c r="AJ361">
+        <v>1.57</v>
+      </c>
+      <c r="AK361">
+        <v>1.15</v>
+      </c>
+      <c r="AL361">
+        <v>1.22</v>
+      </c>
+      <c r="AM361">
+        <v>2.1</v>
+      </c>
+      <c r="AN361">
+        <v>1.88</v>
+      </c>
+      <c r="AO361">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AP361">
+        <v>1.94</v>
+      </c>
+      <c r="AQ361">
+        <v>0.88</v>
+      </c>
+      <c r="AR361">
+        <v>1.6</v>
+      </c>
+      <c r="AS361">
+        <v>1.26</v>
+      </c>
+      <c r="AT361">
+        <v>2.86</v>
+      </c>
+      <c r="AU361">
+        <v>6</v>
+      </c>
+      <c r="AV361">
+        <v>3</v>
+      </c>
+      <c r="AW361">
+        <v>10</v>
+      </c>
+      <c r="AX361">
+        <v>5</v>
+      </c>
+      <c r="AY361">
+        <v>19</v>
+      </c>
+      <c r="AZ361">
+        <v>11</v>
+      </c>
+      <c r="BA361">
+        <v>4</v>
+      </c>
+      <c r="BB361">
+        <v>8</v>
+      </c>
+      <c r="BC361">
+        <v>12</v>
+      </c>
+      <c r="BD361">
+        <v>1.45</v>
+      </c>
+      <c r="BE361">
+        <v>7</v>
+      </c>
+      <c r="BF361">
+        <v>3.05</v>
+      </c>
+      <c r="BG361">
+        <v>1.34</v>
+      </c>
+      <c r="BH361">
+        <v>2.9</v>
+      </c>
+      <c r="BI361">
+        <v>1.57</v>
+      </c>
+      <c r="BJ361">
+        <v>2.2</v>
+      </c>
+      <c r="BK361">
+        <v>1.92</v>
+      </c>
+      <c r="BL361">
+        <v>1.75</v>
+      </c>
+      <c r="BM361">
+        <v>2.43</v>
+      </c>
+      <c r="BN361">
+        <v>1.47</v>
+      </c>
+      <c r="BO361">
+        <v>3.15</v>
+      </c>
+      <c r="BP361">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="362" spans="1:68">
+      <c r="A362" s="1">
+        <v>361</v>
+      </c>
+      <c r="B362">
+        <v>7728554</v>
+      </c>
+      <c r="C362" t="s">
+        <v>68</v>
+      </c>
+      <c r="D362" t="s">
+        <v>69</v>
+      </c>
+      <c r="E362" s="2">
+        <v>45746.5625</v>
+      </c>
+      <c r="F362">
+        <v>33</v>
+      </c>
+      <c r="G362" t="s">
+        <v>81</v>
+      </c>
+      <c r="H362" t="s">
+        <v>76</v>
+      </c>
+      <c r="I362">
+        <v>2</v>
+      </c>
+      <c r="J362">
+        <v>1</v>
+      </c>
+      <c r="K362">
+        <v>3</v>
+      </c>
+      <c r="L362">
+        <v>3</v>
+      </c>
+      <c r="M362">
+        <v>2</v>
+      </c>
+      <c r="N362">
+        <v>5</v>
+      </c>
+      <c r="O362" t="s">
+        <v>318</v>
+      </c>
+      <c r="P362" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q362">
+        <v>3.1</v>
+      </c>
+      <c r="R362">
+        <v>1.83</v>
+      </c>
+      <c r="S362">
+        <v>3.95</v>
+      </c>
+      <c r="T362">
+        <v>1.6</v>
+      </c>
+      <c r="U362">
+        <v>2.2</v>
+      </c>
+      <c r="V362">
+        <v>3.7</v>
+      </c>
+      <c r="W362">
+        <v>1.22</v>
+      </c>
+      <c r="X362">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y362">
+        <v>1</v>
+      </c>
+      <c r="Z362">
+        <v>2.51</v>
+      </c>
+      <c r="AA362">
+        <v>2.95</v>
+      </c>
+      <c r="AB362">
+        <v>3.35</v>
+      </c>
+      <c r="AC362">
+        <v>1.12</v>
+      </c>
+      <c r="AD362">
+        <v>6</v>
+      </c>
+      <c r="AE362">
+        <v>1.5</v>
+      </c>
+      <c r="AF362">
+        <v>2.25</v>
+      </c>
+      <c r="AG362">
+        <v>2.62</v>
+      </c>
+      <c r="AH362">
+        <v>1.43</v>
+      </c>
+      <c r="AI362">
+        <v>2.1</v>
+      </c>
+      <c r="AJ362">
+        <v>1.62</v>
+      </c>
+      <c r="AK362">
+        <v>1.33</v>
+      </c>
+      <c r="AL362">
+        <v>1.33</v>
+      </c>
+      <c r="AM362">
+        <v>1.55</v>
+      </c>
+      <c r="AN362">
+        <v>1.93</v>
+      </c>
+      <c r="AO362">
+        <v>1</v>
+      </c>
+      <c r="AP362">
+        <v>2</v>
+      </c>
+      <c r="AQ362">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR362">
+        <v>1.26</v>
+      </c>
+      <c r="AS362">
+        <v>1.21</v>
+      </c>
+      <c r="AT362">
+        <v>2.47</v>
+      </c>
+      <c r="AU362">
+        <v>7</v>
+      </c>
+      <c r="AV362">
+        <v>5</v>
+      </c>
+      <c r="AW362">
+        <v>16</v>
+      </c>
+      <c r="AX362">
+        <v>6</v>
+      </c>
+      <c r="AY362">
+        <v>27</v>
+      </c>
+      <c r="AZ362">
+        <v>12</v>
+      </c>
+      <c r="BA362">
+        <v>8</v>
+      </c>
+      <c r="BB362">
+        <v>2</v>
+      </c>
+      <c r="BC362">
+        <v>10</v>
+      </c>
+      <c r="BD362">
+        <v>1.96</v>
+      </c>
+      <c r="BE362">
+        <v>6.75</v>
+      </c>
+      <c r="BF362">
+        <v>2</v>
+      </c>
+      <c r="BG362">
+        <v>1.29</v>
+      </c>
+      <c r="BH362">
+        <v>3.15</v>
+      </c>
+      <c r="BI362">
+        <v>1.5</v>
+      </c>
+      <c r="BJ362">
+        <v>2.33</v>
+      </c>
+      <c r="BK362">
+        <v>1.82</v>
+      </c>
+      <c r="BL362">
+        <v>1.84</v>
+      </c>
+      <c r="BM362">
+        <v>2.28</v>
+      </c>
+      <c r="BN362">
+        <v>1.53</v>
+      </c>
+      <c r="BO362">
+        <v>2.95</v>
+      </c>
+      <c r="BP362">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="363" spans="1:68">
+      <c r="A363" s="1">
+        <v>362</v>
+      </c>
+      <c r="B363">
+        <v>7728549</v>
+      </c>
+      <c r="C363" t="s">
+        <v>68</v>
+      </c>
+      <c r="D363" t="s">
+        <v>69</v>
+      </c>
+      <c r="E363" s="2">
+        <v>45746.5625</v>
+      </c>
+      <c r="F363">
+        <v>33</v>
+      </c>
+      <c r="G363" t="s">
+        <v>85</v>
+      </c>
+      <c r="H363" t="s">
+        <v>71</v>
+      </c>
+      <c r="I363">
+        <v>1</v>
+      </c>
+      <c r="J363">
+        <v>1</v>
+      </c>
+      <c r="K363">
+        <v>2</v>
+      </c>
+      <c r="L363">
+        <v>3</v>
+      </c>
+      <c r="M363">
+        <v>2</v>
+      </c>
+      <c r="N363">
+        <v>5</v>
+      </c>
+      <c r="O363" t="s">
+        <v>319</v>
+      </c>
+      <c r="P363" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q363">
+        <v>3.25</v>
+      </c>
+      <c r="R363">
+        <v>1.91</v>
+      </c>
+      <c r="S363">
+        <v>3.45</v>
+      </c>
+      <c r="T363">
+        <v>1.5</v>
+      </c>
+      <c r="U363">
+        <v>2.4</v>
+      </c>
+      <c r="V363">
+        <v>3.3</v>
+      </c>
+      <c r="W363">
+        <v>1.28</v>
+      </c>
+      <c r="X363">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y363">
+        <v>1</v>
+      </c>
+      <c r="Z363">
+        <v>2.66</v>
+      </c>
+      <c r="AA363">
+        <v>3.16</v>
+      </c>
+      <c r="AB363">
+        <v>2.91</v>
+      </c>
+      <c r="AC363">
+        <v>1.1</v>
+      </c>
+      <c r="AD363">
+        <v>6.5</v>
+      </c>
+      <c r="AE363">
+        <v>1.48</v>
+      </c>
+      <c r="AF363">
+        <v>2.62</v>
+      </c>
+      <c r="AG363">
+        <v>2.25</v>
+      </c>
+      <c r="AH363">
+        <v>1.53</v>
+      </c>
+      <c r="AI363">
+        <v>1.95</v>
+      </c>
+      <c r="AJ363">
+        <v>1.73</v>
+      </c>
+      <c r="AK363">
+        <v>1.4</v>
+      </c>
+      <c r="AL363">
+        <v>1.3</v>
+      </c>
+      <c r="AM363">
+        <v>1.48</v>
+      </c>
+      <c r="AN363">
+        <v>1.69</v>
+      </c>
+      <c r="AO363">
+        <v>1.07</v>
+      </c>
+      <c r="AP363">
+        <v>1.76</v>
+      </c>
+      <c r="AQ363">
+        <v>1</v>
+      </c>
+      <c r="AR363">
+        <v>1.53</v>
+      </c>
+      <c r="AS363">
+        <v>1.18</v>
+      </c>
+      <c r="AT363">
+        <v>2.71</v>
+      </c>
+      <c r="AU363">
+        <v>7</v>
+      </c>
+      <c r="AV363">
+        <v>4</v>
+      </c>
+      <c r="AW363">
+        <v>5</v>
+      </c>
+      <c r="AX363">
+        <v>8</v>
+      </c>
+      <c r="AY363">
+        <v>14</v>
+      </c>
+      <c r="AZ363">
+        <v>13</v>
+      </c>
+      <c r="BA363">
+        <v>5</v>
+      </c>
+      <c r="BB363">
+        <v>6</v>
+      </c>
+      <c r="BC363">
+        <v>11</v>
+      </c>
+      <c r="BD363">
+        <v>1.72</v>
+      </c>
+      <c r="BE363">
+        <v>6.75</v>
+      </c>
+      <c r="BF363">
+        <v>2.35</v>
+      </c>
+      <c r="BG363">
+        <v>1.34</v>
+      </c>
+      <c r="BH363">
+        <v>2.88</v>
+      </c>
+      <c r="BI363">
+        <v>1.58</v>
+      </c>
+      <c r="BJ363">
+        <v>2.18</v>
+      </c>
+      <c r="BK363">
+        <v>1.93</v>
+      </c>
+      <c r="BL363">
+        <v>1.74</v>
+      </c>
+      <c r="BM363">
+        <v>2.43</v>
+      </c>
+      <c r="BN363">
+        <v>1.46</v>
+      </c>
+      <c r="BO363">
+        <v>3.15</v>
+      </c>
+      <c r="BP363">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="439">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1692,7 +1692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP363"/>
+  <dimension ref="A1:BP364"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ4">
         <v>1.18</v>
@@ -4295,7 +4295,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ13">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR13">
         <v>1.32</v>
@@ -6970,7 +6970,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ26">
         <v>0.19</v>
@@ -10887,7 +10887,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ45">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR45">
         <v>0.96</v>
@@ -12738,7 +12738,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ54">
         <v>0.8100000000000001</v>
@@ -15213,7 +15213,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ66">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR66">
         <v>1.93</v>
@@ -15828,7 +15828,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ69">
         <v>1</v>
@@ -17479,7 +17479,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ77">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR77">
         <v>1.33</v>
@@ -20566,7 +20566,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ92">
         <v>0.88</v>
@@ -23453,7 +23453,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ106">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR106">
         <v>1.12</v>
@@ -23656,7 +23656,7 @@
         <v>3</v>
       </c>
       <c r="AP107">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ107">
         <v>1.75</v>
@@ -26952,7 +26952,7 @@
         <v>1.17</v>
       </c>
       <c r="AP123">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ123">
         <v>1.31</v>
@@ -27779,7 +27779,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ127">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR127">
         <v>1.1</v>
@@ -32517,7 +32517,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ150">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR150">
         <v>1.6</v>
@@ -33956,7 +33956,7 @@
         <v>0.17</v>
       </c>
       <c r="AP157">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ157">
         <v>1.12</v>
@@ -35813,7 +35813,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ166">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR166">
         <v>1.42</v>
@@ -38694,7 +38694,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ180">
         <v>1.53</v>
@@ -41169,7 +41169,7 @@
         <v>2</v>
       </c>
       <c r="AQ192">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR192">
         <v>1.15</v>
@@ -43020,7 +43020,7 @@
         <v>1.22</v>
       </c>
       <c r="AP201">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ201">
         <v>1</v>
@@ -45083,7 +45083,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ211">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR211">
         <v>1.69</v>
@@ -46110,7 +46110,7 @@
         <v>0.78</v>
       </c>
       <c r="AP216">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ216">
         <v>1.12</v>
@@ -51054,7 +51054,7 @@
         <v>1.36</v>
       </c>
       <c r="AP240">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ240">
         <v>1.53</v>
@@ -51469,7 +51469,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ242">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR242">
         <v>1.37</v>
@@ -53941,7 +53941,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ254">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR254">
         <v>1.63</v>
@@ -55792,7 +55792,7 @@
         <v>1.27</v>
       </c>
       <c r="AP263">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ263">
         <v>1</v>
@@ -59297,7 +59297,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ280">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR280">
         <v>1.52</v>
@@ -60118,7 +60118,7 @@
         <v>0.54</v>
       </c>
       <c r="AP284">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ284">
         <v>0.47</v>
@@ -60945,7 +60945,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ288">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR288">
         <v>1.7</v>
@@ -65062,7 +65062,7 @@
         <v>1.38</v>
       </c>
       <c r="AP308">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ308">
         <v>1.18</v>
@@ -65271,7 +65271,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ309">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR309">
         <v>1.18</v>
@@ -70215,7 +70215,7 @@
         <v>0.59</v>
       </c>
       <c r="AQ333">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AR333">
         <v>1.19</v>
@@ -71860,7 +71860,7 @@
         <v>1.36</v>
       </c>
       <c r="AP341">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ341">
         <v>1.19</v>
@@ -76471,6 +76471,212 @@
       </c>
       <c r="BP363">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="364" spans="1:68">
+      <c r="A364" s="1">
+        <v>363</v>
+      </c>
+      <c r="B364">
+        <v>7728551</v>
+      </c>
+      <c r="C364" t="s">
+        <v>68</v>
+      </c>
+      <c r="D364" t="s">
+        <v>69</v>
+      </c>
+      <c r="E364" s="2">
+        <v>45747.64583333334</v>
+      </c>
+      <c r="F364">
+        <v>33</v>
+      </c>
+      <c r="G364" t="s">
+        <v>72</v>
+      </c>
+      <c r="H364" t="s">
+        <v>73</v>
+      </c>
+      <c r="I364">
+        <v>0</v>
+      </c>
+      <c r="J364">
+        <v>0</v>
+      </c>
+      <c r="K364">
+        <v>0</v>
+      </c>
+      <c r="L364">
+        <v>0</v>
+      </c>
+      <c r="M364">
+        <v>0</v>
+      </c>
+      <c r="N364">
+        <v>0</v>
+      </c>
+      <c r="O364" t="s">
+        <v>94</v>
+      </c>
+      <c r="P364" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q364">
+        <v>3.1</v>
+      </c>
+      <c r="R364">
+        <v>1.91</v>
+      </c>
+      <c r="S364">
+        <v>4.5</v>
+      </c>
+      <c r="T364">
+        <v>1.62</v>
+      </c>
+      <c r="U364">
+        <v>2.2</v>
+      </c>
+      <c r="V364">
+        <v>4</v>
+      </c>
+      <c r="W364">
+        <v>1.22</v>
+      </c>
+      <c r="X364">
+        <v>13</v>
+      </c>
+      <c r="Y364">
+        <v>1.04</v>
+      </c>
+      <c r="Z364">
+        <v>2.31</v>
+      </c>
+      <c r="AA364">
+        <v>3.04</v>
+      </c>
+      <c r="AB364">
+        <v>3.67</v>
+      </c>
+      <c r="AC364">
+        <v>1.12</v>
+      </c>
+      <c r="AD364">
+        <v>6</v>
+      </c>
+      <c r="AE364">
+        <v>1.53</v>
+      </c>
+      <c r="AF364">
+        <v>2.25</v>
+      </c>
+      <c r="AG364">
+        <v>2.45</v>
+      </c>
+      <c r="AH364">
+        <v>1.55</v>
+      </c>
+      <c r="AI364">
+        <v>2.2</v>
+      </c>
+      <c r="AJ364">
+        <v>1.62</v>
+      </c>
+      <c r="AK364">
+        <v>1.28</v>
+      </c>
+      <c r="AL364">
+        <v>1.35</v>
+      </c>
+      <c r="AM364">
+        <v>1.6</v>
+      </c>
+      <c r="AN364">
+        <v>1.5</v>
+      </c>
+      <c r="AO364">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AP364">
+        <v>1.47</v>
+      </c>
+      <c r="AQ364">
+        <v>0.82</v>
+      </c>
+      <c r="AR364">
+        <v>1.46</v>
+      </c>
+      <c r="AS364">
+        <v>1.29</v>
+      </c>
+      <c r="AT364">
+        <v>2.75</v>
+      </c>
+      <c r="AU364">
+        <v>6</v>
+      </c>
+      <c r="AV364">
+        <v>3</v>
+      </c>
+      <c r="AW364">
+        <v>4</v>
+      </c>
+      <c r="AX364">
+        <v>8</v>
+      </c>
+      <c r="AY364">
+        <v>12</v>
+      </c>
+      <c r="AZ364">
+        <v>13</v>
+      </c>
+      <c r="BA364">
+        <v>3</v>
+      </c>
+      <c r="BB364">
+        <v>3</v>
+      </c>
+      <c r="BC364">
+        <v>6</v>
+      </c>
+      <c r="BD364">
+        <v>1.82</v>
+      </c>
+      <c r="BE364">
+        <v>7.5</v>
+      </c>
+      <c r="BF364">
+        <v>2.42</v>
+      </c>
+      <c r="BG364">
+        <v>1.43</v>
+      </c>
+      <c r="BH364">
+        <v>2.63</v>
+      </c>
+      <c r="BI364">
+        <v>1.74</v>
+      </c>
+      <c r="BJ364">
+        <v>2.02</v>
+      </c>
+      <c r="BK364">
+        <v>2.22</v>
+      </c>
+      <c r="BL364">
+        <v>1.62</v>
+      </c>
+      <c r="BM364">
+        <v>2.85</v>
+      </c>
+      <c r="BN364">
+        <v>1.37</v>
+      </c>
+      <c r="BO364">
+        <v>3.9</v>
+      </c>
+      <c r="BP364">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="441">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -976,6 +976,9 @@
     <t>['26', '47', '90+7']</t>
   </si>
   <si>
+    <t>['7', '83']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1331,6 +1334,9 @@
   </si>
   <si>
     <t>['45+5', '56']</t>
+  </si>
+  <si>
+    <t>['2', '38']</t>
   </si>
 </sst>
 </file>
@@ -1692,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP364"/>
+  <dimension ref="A1:BP365"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1948,7 +1954,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2360,7 +2366,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3184,7 +3190,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3390,7 +3396,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4214,7 +4220,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -5450,7 +5456,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5940,7 +5946,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21">
         <v>1.31</v>
@@ -6068,7 +6074,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6274,7 +6280,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6480,7 +6486,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6686,7 +6692,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6892,7 +6898,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7510,7 +7516,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -8128,7 +8134,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8334,7 +8340,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8746,7 +8752,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -10600,7 +10606,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10678,7 +10684,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ44">
         <v>1.25</v>
@@ -11218,7 +11224,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12866,7 +12872,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -13072,7 +13078,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13278,7 +13284,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13484,7 +13490,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13896,7 +13902,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14514,7 +14520,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14798,7 +14804,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ64">
         <v>1.75</v>
@@ -15132,7 +15138,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15544,7 +15550,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15750,7 +15756,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16368,7 +16374,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16574,7 +16580,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16780,7 +16786,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17064,7 +17070,7 @@
         <v>0.33</v>
       </c>
       <c r="AP75">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ75">
         <v>0.19</v>
@@ -17604,7 +17610,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17810,7 +17816,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18222,7 +18228,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18428,7 +18434,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18634,7 +18640,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19458,7 +19464,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19870,7 +19876,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -20076,7 +20082,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20488,7 +20494,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20900,7 +20906,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -21106,7 +21112,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -22136,7 +22142,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23244,7 +23250,7 @@
         <v>1.4</v>
       </c>
       <c r="AP105">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ105">
         <v>1.53</v>
@@ -23578,7 +23584,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24196,7 +24202,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24608,7 +24614,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24814,7 +24820,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24892,7 +24898,7 @@
         <v>2</v>
       </c>
       <c r="AP113">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ113">
         <v>1.19</v>
@@ -25226,7 +25232,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -26050,7 +26056,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26668,7 +26674,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -27080,7 +27086,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27492,7 +27498,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27904,7 +27910,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28316,7 +28322,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28522,7 +28528,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28728,7 +28734,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29140,7 +29146,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29346,7 +29352,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29964,7 +29970,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30582,7 +30588,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30788,7 +30794,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30994,7 +31000,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31200,7 +31206,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31612,7 +31618,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -32024,7 +32030,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -33054,7 +33060,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33132,7 +33138,7 @@
         <v>0.83</v>
       </c>
       <c r="AP153">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ153">
         <v>1</v>
@@ -33672,7 +33678,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -35320,7 +35326,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35938,7 +35944,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36968,7 +36974,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37586,7 +37592,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37870,7 +37876,7 @@
         <v>0.83</v>
       </c>
       <c r="AP176">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ176">
         <v>0.8100000000000001</v>
@@ -37998,7 +38004,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38410,7 +38416,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38616,7 +38622,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39312,7 +39318,7 @@
         <v>0.88</v>
       </c>
       <c r="AP183">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ183">
         <v>0.88</v>
@@ -39440,7 +39446,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40264,7 +40270,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40882,7 +40888,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -41088,7 +41094,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41294,7 +41300,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41500,7 +41506,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42736,7 +42742,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43148,7 +43154,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43226,7 +43232,7 @@
         <v>0.67</v>
       </c>
       <c r="AP202">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ202">
         <v>0.47</v>
@@ -43354,7 +43360,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43972,7 +43978,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -45002,7 +45008,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45208,7 +45214,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45414,7 +45420,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45620,7 +45626,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -46032,7 +46038,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -47268,7 +47274,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47680,7 +47686,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -48092,7 +48098,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48170,7 +48176,7 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ226">
         <v>1.19</v>
@@ -48710,7 +48716,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48916,7 +48922,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49122,7 +49128,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49946,7 +49952,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50770,7 +50776,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51388,7 +51394,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51800,7 +51806,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52212,7 +52218,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -53036,7 +53042,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53114,7 +53120,7 @@
         <v>0.45</v>
       </c>
       <c r="AP250">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ250">
         <v>1.12</v>
@@ -53242,7 +53248,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53654,7 +53660,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -54066,7 +54072,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54272,7 +54278,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -55302,7 +55308,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55508,7 +55514,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -56126,7 +56132,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -57234,7 +57240,7 @@
         <v>1.25</v>
       </c>
       <c r="AP270">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ270">
         <v>1.29</v>
@@ -57568,7 +57574,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -58598,7 +58604,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -59834,7 +59840,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -60040,7 +60046,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60658,7 +60664,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -60942,7 +60948,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP288">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ288">
         <v>0.82</v>
@@ -61276,7 +61282,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61482,7 +61488,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -63336,7 +63342,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63542,7 +63548,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63748,7 +63754,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -65190,7 +65196,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65680,7 +65686,7 @@
         <v>0.92</v>
       </c>
       <c r="AP311">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ311">
         <v>1.12</v>
@@ -66014,7 +66020,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66426,7 +66432,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66632,7 +66638,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -68692,7 +68698,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -69104,7 +69110,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -71164,7 +71170,7 @@
         <v>302</v>
       </c>
       <c r="P338" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q338">
         <v>3.5</v>
@@ -71370,7 +71376,7 @@
         <v>183</v>
       </c>
       <c r="P339" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q339">
         <v>3.4</v>
@@ -71988,7 +71994,7 @@
         <v>304</v>
       </c>
       <c r="P342" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q342">
         <v>2.88</v>
@@ -72066,7 +72072,7 @@
         <v>1.47</v>
       </c>
       <c r="AP342">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ342">
         <v>1.53</v>
@@ -73224,7 +73230,7 @@
         <v>310</v>
       </c>
       <c r="P348" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q348">
         <v>2.3</v>
@@ -73430,7 +73436,7 @@
         <v>311</v>
       </c>
       <c r="P349" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q349">
         <v>2.6</v>
@@ -73636,7 +73642,7 @@
         <v>94</v>
       </c>
       <c r="P350" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q350">
         <v>2.63</v>
@@ -74048,7 +74054,7 @@
         <v>313</v>
       </c>
       <c r="P352" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q352">
         <v>1.8</v>
@@ -74254,7 +74260,7 @@
         <v>117</v>
       </c>
       <c r="P353" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q353">
         <v>2.88</v>
@@ -75078,7 +75084,7 @@
         <v>315</v>
       </c>
       <c r="P357" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q357">
         <v>4.6</v>
@@ -75696,7 +75702,7 @@
         <v>147</v>
       </c>
       <c r="P360" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q360">
         <v>3.25</v>
@@ -76108,7 +76114,7 @@
         <v>318</v>
       </c>
       <c r="P362" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q362">
         <v>3.1</v>
@@ -76314,7 +76320,7 @@
         <v>319</v>
       </c>
       <c r="P363" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q363">
         <v>3.25</v>
@@ -76677,6 +76683,212 @@
       </c>
       <c r="BP364">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="365" spans="1:68">
+      <c r="A365" s="1">
+        <v>364</v>
+      </c>
+      <c r="B365">
+        <v>7728565</v>
+      </c>
+      <c r="C365" t="s">
+        <v>68</v>
+      </c>
+      <c r="D365" t="s">
+        <v>69</v>
+      </c>
+      <c r="E365" s="2">
+        <v>45751.64583333334</v>
+      </c>
+      <c r="F365">
+        <v>34</v>
+      </c>
+      <c r="G365" t="s">
+        <v>86</v>
+      </c>
+      <c r="H365" t="s">
+        <v>85</v>
+      </c>
+      <c r="I365">
+        <v>1</v>
+      </c>
+      <c r="J365">
+        <v>2</v>
+      </c>
+      <c r="K365">
+        <v>3</v>
+      </c>
+      <c r="L365">
+        <v>2</v>
+      </c>
+      <c r="M365">
+        <v>2</v>
+      </c>
+      <c r="N365">
+        <v>4</v>
+      </c>
+      <c r="O365" t="s">
+        <v>320</v>
+      </c>
+      <c r="P365" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q365">
+        <v>2.38</v>
+      </c>
+      <c r="R365">
+        <v>2.3</v>
+      </c>
+      <c r="S365">
+        <v>4.5</v>
+      </c>
+      <c r="T365">
+        <v>1.33</v>
+      </c>
+      <c r="U365">
+        <v>3.25</v>
+      </c>
+      <c r="V365">
+        <v>2.63</v>
+      </c>
+      <c r="W365">
+        <v>1.44</v>
+      </c>
+      <c r="X365">
+        <v>6.5</v>
+      </c>
+      <c r="Y365">
+        <v>1.11</v>
+      </c>
+      <c r="Z365">
+        <v>1.87</v>
+      </c>
+      <c r="AA365">
+        <v>3.82</v>
+      </c>
+      <c r="AB365">
+        <v>4.2</v>
+      </c>
+      <c r="AC365">
+        <v>1.04</v>
+      </c>
+      <c r="AD365">
+        <v>10</v>
+      </c>
+      <c r="AE365">
+        <v>1.22</v>
+      </c>
+      <c r="AF365">
+        <v>4.2</v>
+      </c>
+      <c r="AG365">
+        <v>1.82</v>
+      </c>
+      <c r="AH365">
+        <v>2</v>
+      </c>
+      <c r="AI365">
+        <v>1.67</v>
+      </c>
+      <c r="AJ365">
+        <v>2.1</v>
+      </c>
+      <c r="AK365">
+        <v>1.21</v>
+      </c>
+      <c r="AL365">
+        <v>1.25</v>
+      </c>
+      <c r="AM365">
+        <v>2.05</v>
+      </c>
+      <c r="AN365">
+        <v>1.31</v>
+      </c>
+      <c r="AO365">
+        <v>1</v>
+      </c>
+      <c r="AP365">
+        <v>1.29</v>
+      </c>
+      <c r="AQ365">
+        <v>1</v>
+      </c>
+      <c r="AR365">
+        <v>1.71</v>
+      </c>
+      <c r="AS365">
+        <v>1.34</v>
+      </c>
+      <c r="AT365">
+        <v>3.05</v>
+      </c>
+      <c r="AU365">
+        <v>9</v>
+      </c>
+      <c r="AV365">
+        <v>6</v>
+      </c>
+      <c r="AW365">
+        <v>26</v>
+      </c>
+      <c r="AX365">
+        <v>2</v>
+      </c>
+      <c r="AY365">
+        <v>41</v>
+      </c>
+      <c r="AZ365">
+        <v>9</v>
+      </c>
+      <c r="BA365">
+        <v>10</v>
+      </c>
+      <c r="BB365">
+        <v>1</v>
+      </c>
+      <c r="BC365">
+        <v>11</v>
+      </c>
+      <c r="BD365">
+        <v>1.54</v>
+      </c>
+      <c r="BE365">
+        <v>6.75</v>
+      </c>
+      <c r="BF365">
+        <v>2.7</v>
+      </c>
+      <c r="BG365">
+        <v>1.36</v>
+      </c>
+      <c r="BH365">
+        <v>2.8</v>
+      </c>
+      <c r="BI365">
+        <v>1.61</v>
+      </c>
+      <c r="BJ365">
+        <v>2.12</v>
+      </c>
+      <c r="BK365">
+        <v>2</v>
+      </c>
+      <c r="BL365">
+        <v>1.7</v>
+      </c>
+      <c r="BM365">
+        <v>2.55</v>
+      </c>
+      <c r="BN365">
+        <v>1.43</v>
+      </c>
+      <c r="BO365">
+        <v>3.3</v>
+      </c>
+      <c r="BP365">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="443">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -979,6 +979,9 @@
     <t>['7', '83']</t>
   </si>
   <si>
+    <t>['10', '78', '85']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1337,6 +1340,9 @@
   </si>
   <si>
     <t>['2', '38']</t>
+  </si>
+  <si>
+    <t>['69', '71', '84']</t>
   </si>
 </sst>
 </file>
@@ -1698,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP365"/>
+  <dimension ref="A1:BP369"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1954,7 +1960,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2032,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -2366,7 +2372,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2650,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ5">
         <v>1.18</v>
@@ -3065,7 +3071,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ7">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3190,7 +3196,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3268,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ8">
         <v>1.53</v>
@@ -3396,7 +3402,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3477,7 +3483,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ9">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -4095,7 +4101,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ12">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4220,7 +4226,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4710,10 +4716,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR15">
         <v>1.13</v>
@@ -5456,7 +5462,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5537,7 +5543,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ19">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5949,7 +5955,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ21">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6074,7 +6080,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6152,7 +6158,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ22">
         <v>1.18</v>
@@ -6280,7 +6286,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6486,7 +6492,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6564,7 +6570,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ24">
         <v>1.29</v>
@@ -6692,7 +6698,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6898,7 +6904,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6979,7 +6985,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ26">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR26">
         <v>1.33</v>
@@ -7516,7 +7522,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -8134,7 +8140,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8340,7 +8346,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8418,7 +8424,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ33">
         <v>1.53</v>
@@ -8752,7 +8758,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9036,7 +9042,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ36">
         <v>1.53</v>
@@ -9448,10 +9454,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ38">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR38">
         <v>1.41</v>
@@ -10066,7 +10072,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ41">
         <v>1.53</v>
@@ -10275,7 +10281,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ42">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR42">
         <v>1.8</v>
@@ -10606,7 +10612,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -11224,7 +11230,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11305,7 +11311,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR47">
         <v>1.72</v>
@@ -11508,10 +11514,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ48">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR48">
         <v>1.67</v>
@@ -12872,7 +12878,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -13078,7 +13084,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13284,7 +13290,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13362,7 +13368,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ57">
         <v>0.88</v>
@@ -13490,7 +13496,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13777,7 +13783,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ59">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR59">
         <v>1.51</v>
@@ -13902,7 +13908,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14520,7 +14526,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14598,7 +14604,7 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ63">
         <v>1.25</v>
@@ -15138,7 +15144,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15550,7 +15556,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15756,7 +15762,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15837,7 +15843,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ69">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR69">
         <v>1.25</v>
@@ -16246,7 +16252,7 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ71">
         <v>1.18</v>
@@ -16374,7 +16380,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16580,7 +16586,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16661,7 +16667,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ73">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR73">
         <v>2.06</v>
@@ -16786,7 +16792,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17073,7 +17079,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ75">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR75">
         <v>1.58</v>
@@ -17610,7 +17616,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17816,7 +17822,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -18228,7 +18234,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18434,7 +18440,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18512,7 +18518,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ82">
         <v>0.9399999999999999</v>
@@ -18640,7 +18646,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19464,7 +19470,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19751,7 +19757,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ88">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR88">
         <v>1.96</v>
@@ -19876,7 +19882,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -20082,7 +20088,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20366,7 +20372,7 @@
         <v>0.33</v>
       </c>
       <c r="AP91">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ91">
         <v>0.8100000000000001</v>
@@ -20494,7 +20500,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20778,10 +20784,10 @@
         <v>1.33</v>
       </c>
       <c r="AP93">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR93">
         <v>1.5</v>
@@ -20906,7 +20912,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -21112,7 +21118,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21193,7 +21199,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ95">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR95">
         <v>1.44</v>
@@ -21602,7 +21608,7 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ97">
         <v>1.12</v>
@@ -22142,7 +22148,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22220,7 +22226,7 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ100">
         <v>1.18</v>
@@ -22635,7 +22641,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ102">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR102">
         <v>1.13</v>
@@ -22841,7 +22847,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ103">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR103">
         <v>1.55</v>
@@ -23044,10 +23050,10 @@
         <v>0.25</v>
       </c>
       <c r="AP104">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ104">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR104">
         <v>1.71</v>
@@ -23584,7 +23590,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -24202,7 +24208,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24283,7 +24289,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ110">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR110">
         <v>1.96</v>
@@ -24614,7 +24620,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24820,7 +24826,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25104,7 +25110,7 @@
         <v>1.75</v>
       </c>
       <c r="AP114">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ114">
         <v>1.25</v>
@@ -25232,7 +25238,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25722,7 +25728,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ117">
         <v>1.19</v>
@@ -26056,7 +26062,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26340,7 +26346,7 @@
         <v>1.4</v>
       </c>
       <c r="AP120">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ120">
         <v>1.29</v>
@@ -26674,7 +26680,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26961,7 +26967,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ123">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR123">
         <v>1.53</v>
@@ -27086,7 +27092,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27373,7 +27379,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ125">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR125">
         <v>1.56</v>
@@ -27498,7 +27504,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27910,7 +27916,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28322,7 +28328,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28528,7 +28534,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28609,7 +28615,7 @@
         <v>2</v>
       </c>
       <c r="AQ131">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR131">
         <v>1.16</v>
@@ -28734,7 +28740,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28812,7 +28818,7 @@
         <v>1.17</v>
       </c>
       <c r="AP132">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ132">
         <v>1.53</v>
@@ -29021,7 +29027,7 @@
         <v>0.59</v>
       </c>
       <c r="AQ133">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR133">
         <v>1.15</v>
@@ -29146,7 +29152,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29224,7 +29230,7 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ134">
         <v>1.19</v>
@@ -29352,7 +29358,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29430,7 +29436,7 @@
         <v>0.83</v>
       </c>
       <c r="AP135">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ135">
         <v>1.53</v>
@@ -29636,7 +29642,7 @@
         <v>1.4</v>
       </c>
       <c r="AP136">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ136">
         <v>1.25</v>
@@ -29970,7 +29976,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30588,7 +30594,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30669,7 +30675,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ141">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR141">
         <v>1.42</v>
@@ -30794,7 +30800,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -31000,7 +31006,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31206,7 +31212,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31284,10 +31290,10 @@
         <v>0.83</v>
       </c>
       <c r="AP144">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ144">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR144">
         <v>1.75</v>
@@ -31618,7 +31624,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -32030,7 +32036,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32317,7 +32323,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ149">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR149">
         <v>1.82</v>
@@ -32726,7 +32732,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ151">
         <v>0.8100000000000001</v>
@@ -33060,7 +33066,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33678,7 +33684,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33756,7 +33762,7 @@
         <v>1.83</v>
       </c>
       <c r="AP156">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ156">
         <v>1.19</v>
@@ -34171,7 +34177,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ158">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR158">
         <v>1.68</v>
@@ -34580,7 +34586,7 @@
         <v>1.17</v>
       </c>
       <c r="AP160">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ160">
         <v>1.29</v>
@@ -35326,7 +35332,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35404,10 +35410,10 @@
         <v>1.38</v>
       </c>
       <c r="AP164">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ164">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR164">
         <v>1.2</v>
@@ -35610,7 +35616,7 @@
         <v>1.14</v>
       </c>
       <c r="AP165">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ165">
         <v>1.25</v>
@@ -35944,7 +35950,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36437,7 +36443,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ169">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR169">
         <v>1.71</v>
@@ -36849,7 +36855,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ171">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR171">
         <v>1.18</v>
@@ -36974,7 +36980,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37261,7 +37267,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ173">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR173">
         <v>1.44</v>
@@ -37592,7 +37598,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -38004,7 +38010,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38416,7 +38422,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38622,7 +38628,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39446,7 +39452,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39936,7 +39942,7 @@
         <v>0.13</v>
       </c>
       <c r="AP186">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ186">
         <v>1.12</v>
@@ -40142,7 +40148,7 @@
         <v>0.75</v>
       </c>
       <c r="AP187">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ187">
         <v>0.47</v>
@@ -40270,7 +40276,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40760,7 +40766,7 @@
         <v>2.75</v>
       </c>
       <c r="AP190">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ190">
         <v>1.75</v>
@@ -40888,7 +40894,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -41094,7 +41100,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41300,7 +41306,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41381,7 +41387,7 @@
         <v>0.59</v>
       </c>
       <c r="AQ193">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR193">
         <v>1.13</v>
@@ -41506,7 +41512,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41587,7 +41593,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ194">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR194">
         <v>1.4</v>
@@ -41999,7 +42005,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ196">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR196">
         <v>1.42</v>
@@ -42205,7 +42211,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ197">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR197">
         <v>1.63</v>
@@ -42408,7 +42414,7 @@
         <v>1.25</v>
       </c>
       <c r="AP198">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ198">
         <v>0.9399999999999999</v>
@@ -42742,7 +42748,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -43154,7 +43160,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43360,7 +43366,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43438,7 +43444,7 @@
         <v>1.6</v>
       </c>
       <c r="AP203">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ203">
         <v>1.18</v>
@@ -43978,7 +43984,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44056,7 +44062,7 @@
         <v>0.88</v>
       </c>
       <c r="AP206">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ206">
         <v>0.8100000000000001</v>
@@ -44674,7 +44680,7 @@
         <v>0.6</v>
       </c>
       <c r="AP209">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ209">
         <v>0.47</v>
@@ -45008,7 +45014,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45214,7 +45220,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45295,7 +45301,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ212">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR212">
         <v>1.69</v>
@@ -45420,7 +45426,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45501,7 +45507,7 @@
         <v>0.59</v>
       </c>
       <c r="AQ213">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR213">
         <v>1.08</v>
@@ -45626,7 +45632,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45913,7 +45919,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ215">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR215">
         <v>1.3</v>
@@ -46038,7 +46044,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46737,7 +46743,7 @@
         <v>2</v>
       </c>
       <c r="AQ219">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR219">
         <v>1.15</v>
@@ -46940,7 +46946,7 @@
         <v>1.1</v>
       </c>
       <c r="AP220">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ220">
         <v>1</v>
@@ -47146,7 +47152,7 @@
         <v>1.56</v>
       </c>
       <c r="AP221">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ221">
         <v>1.19</v>
@@ -47274,7 +47280,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47686,7 +47692,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47764,7 +47770,7 @@
         <v>0.8</v>
       </c>
       <c r="AP224">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ224">
         <v>0.88</v>
@@ -47973,7 +47979,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ225">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR225">
         <v>1.43</v>
@@ -48098,7 +48104,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48591,7 +48597,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ228">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR228">
         <v>1.5</v>
@@ -48716,7 +48722,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48922,7 +48928,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49128,7 +49134,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49412,7 +49418,7 @@
         <v>0.8</v>
       </c>
       <c r="AP232">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ232">
         <v>1.12</v>
@@ -49952,7 +49958,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50776,7 +50782,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50857,7 +50863,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ239">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR239">
         <v>1.67</v>
@@ -51394,7 +51400,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51678,10 +51684,10 @@
         <v>1.27</v>
       </c>
       <c r="AP243">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ243">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR243">
         <v>1.18</v>
@@ -51806,7 +51812,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52090,7 +52096,7 @@
         <v>1.09</v>
       </c>
       <c r="AP245">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ245">
         <v>1</v>
@@ -52218,7 +52224,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52296,7 +52302,7 @@
         <v>1.3</v>
       </c>
       <c r="AP246">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ246">
         <v>1.19</v>
@@ -53042,7 +53048,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53248,7 +53254,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53329,7 +53335,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ251">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR251">
         <v>1.68</v>
@@ -53660,7 +53666,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -54072,7 +54078,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54278,7 +54284,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54771,7 +54777,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ258">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR258">
         <v>1.2</v>
@@ -54974,7 +54980,7 @@
         <v>1.09</v>
       </c>
       <c r="AP259">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ259">
         <v>0.9399999999999999</v>
@@ -55308,7 +55314,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55389,7 +55395,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ261">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR261">
         <v>1.52</v>
@@ -55514,7 +55520,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -56132,7 +56138,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56622,7 +56628,7 @@
         <v>0.82</v>
       </c>
       <c r="AP267">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ267">
         <v>1.12</v>
@@ -56831,7 +56837,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ268">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR268">
         <v>1.8</v>
@@ -57446,7 +57452,7 @@
         <v>1.33</v>
       </c>
       <c r="AP271">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ271">
         <v>1.53</v>
@@ -57574,7 +57580,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -57652,7 +57658,7 @@
         <v>0.67</v>
       </c>
       <c r="AP272">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ272">
         <v>1.12</v>
@@ -58604,7 +58610,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58888,7 +58894,7 @@
         <v>1.17</v>
       </c>
       <c r="AP278">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ278">
         <v>1</v>
@@ -59300,7 +59306,7 @@
         <v>0.67</v>
       </c>
       <c r="AP280">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ280">
         <v>0.82</v>
@@ -59509,7 +59515,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ281">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR281">
         <v>1.65</v>
@@ -59840,7 +59846,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -60046,7 +60052,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60333,7 +60339,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ285">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR285">
         <v>1.52</v>
@@ -60539,7 +60545,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ286">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR286">
         <v>1.59</v>
@@ -60664,7 +60670,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61154,7 +61160,7 @@
         <v>0.85</v>
       </c>
       <c r="AP289">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ289">
         <v>0.88</v>
@@ -61282,7 +61288,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61488,7 +61494,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -63011,7 +63017,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ298">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR298">
         <v>1.37</v>
@@ -63342,7 +63348,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63423,7 +63429,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ300">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR300">
         <v>1.42</v>
@@ -63548,7 +63554,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63626,7 +63632,7 @@
         <v>2</v>
       </c>
       <c r="AP301">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ301">
         <v>1.75</v>
@@ -63754,7 +63760,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -63832,7 +63838,7 @@
         <v>1.36</v>
       </c>
       <c r="AP302">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ302">
         <v>1.18</v>
@@ -64038,10 +64044,10 @@
         <v>1.5</v>
       </c>
       <c r="AP303">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ303">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR303">
         <v>1.51</v>
@@ -64865,7 +64871,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ307">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR307">
         <v>1.53</v>
@@ -65196,7 +65202,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65274,7 +65280,7 @@
         <v>0.64</v>
       </c>
       <c r="AP309">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ309">
         <v>0.82</v>
@@ -66020,7 +66026,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66432,7 +66438,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66638,7 +66644,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -67337,7 +67343,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ319">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR319">
         <v>1.37</v>
@@ -67746,10 +67752,10 @@
         <v>1.47</v>
       </c>
       <c r="AP321">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ321">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR321">
         <v>1.54</v>
@@ -68161,7 +68167,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ323">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR323">
         <v>1.37</v>
@@ -68570,7 +68576,7 @@
         <v>1.93</v>
       </c>
       <c r="AP325">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ325">
         <v>1.75</v>
@@ -68698,7 +68704,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -68779,7 +68785,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ326">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR326">
         <v>1.58</v>
@@ -69110,7 +69116,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -69600,7 +69606,7 @@
         <v>0.93</v>
       </c>
       <c r="AP330">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ330">
         <v>0.8100000000000001</v>
@@ -70630,7 +70636,7 @@
         <v>1</v>
       </c>
       <c r="AP335">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ335">
         <v>1.12</v>
@@ -71170,7 +71176,7 @@
         <v>302</v>
       </c>
       <c r="P338" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q338">
         <v>3.5</v>
@@ -71376,7 +71382,7 @@
         <v>183</v>
       </c>
       <c r="P339" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q339">
         <v>3.4</v>
@@ -71663,7 +71669,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ340">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="AR340">
         <v>1.59</v>
@@ -71994,7 +72000,7 @@
         <v>304</v>
       </c>
       <c r="P342" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q342">
         <v>2.88</v>
@@ -72281,7 +72287,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ343">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR343">
         <v>1.39</v>
@@ -72487,7 +72493,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ344">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR344">
         <v>1.67</v>
@@ -73102,10 +73108,10 @@
         <v>1.4</v>
       </c>
       <c r="AP347">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ347">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR347">
         <v>1.66</v>
@@ -73230,7 +73236,7 @@
         <v>310</v>
       </c>
       <c r="P348" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q348">
         <v>2.3</v>
@@ -73436,7 +73442,7 @@
         <v>311</v>
       </c>
       <c r="P349" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q349">
         <v>2.6</v>
@@ -73514,7 +73520,7 @@
         <v>1.38</v>
       </c>
       <c r="AP349">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ349">
         <v>1.29</v>
@@ -73642,7 +73648,7 @@
         <v>94</v>
       </c>
       <c r="P350" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q350">
         <v>2.63</v>
@@ -73720,7 +73726,7 @@
         <v>0.87</v>
       </c>
       <c r="AP350">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ350">
         <v>1</v>
@@ -74054,7 +74060,7 @@
         <v>313</v>
       </c>
       <c r="P352" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q352">
         <v>1.8</v>
@@ -74260,7 +74266,7 @@
         <v>117</v>
       </c>
       <c r="P353" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q353">
         <v>2.88</v>
@@ -75084,7 +75090,7 @@
         <v>315</v>
       </c>
       <c r="P357" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q357">
         <v>4.6</v>
@@ -75162,7 +75168,7 @@
         <v>1.19</v>
       </c>
       <c r="AP357">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AQ357">
         <v>1.18</v>
@@ -75702,7 +75708,7 @@
         <v>147</v>
       </c>
       <c r="P360" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q360">
         <v>3.25</v>
@@ -76114,7 +76120,7 @@
         <v>318</v>
       </c>
       <c r="P362" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q362">
         <v>3.1</v>
@@ -76320,7 +76326,7 @@
         <v>319</v>
       </c>
       <c r="P363" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q363">
         <v>3.25</v>
@@ -76732,7 +76738,7 @@
         <v>320</v>
       </c>
       <c r="P365" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q365">
         <v>2.38</v>
@@ -76889,6 +76895,830 @@
       </c>
       <c r="BP365">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="366" spans="1:68">
+      <c r="A366" s="1">
+        <v>365</v>
+      </c>
+      <c r="B366">
+        <v>7728561</v>
+      </c>
+      <c r="C366" t="s">
+        <v>68</v>
+      </c>
+      <c r="D366" t="s">
+        <v>69</v>
+      </c>
+      <c r="E366" s="2">
+        <v>45752.46875</v>
+      </c>
+      <c r="F366">
+        <v>34</v>
+      </c>
+      <c r="G366" t="s">
+        <v>73</v>
+      </c>
+      <c r="H366" t="s">
+        <v>89</v>
+      </c>
+      <c r="I366">
+        <v>0</v>
+      </c>
+      <c r="J366">
+        <v>0</v>
+      </c>
+      <c r="K366">
+        <v>0</v>
+      </c>
+      <c r="L366">
+        <v>1</v>
+      </c>
+      <c r="M366">
+        <v>1</v>
+      </c>
+      <c r="N366">
+        <v>2</v>
+      </c>
+      <c r="O366" t="s">
+        <v>244</v>
+      </c>
+      <c r="P366" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q366">
+        <v>3.4</v>
+      </c>
+      <c r="R366">
+        <v>1.91</v>
+      </c>
+      <c r="S366">
+        <v>4</v>
+      </c>
+      <c r="T366">
+        <v>1.62</v>
+      </c>
+      <c r="U366">
+        <v>2.2</v>
+      </c>
+      <c r="V366">
+        <v>4</v>
+      </c>
+      <c r="W366">
+        <v>1.22</v>
+      </c>
+      <c r="X366">
+        <v>13</v>
+      </c>
+      <c r="Y366">
+        <v>1.04</v>
+      </c>
+      <c r="Z366">
+        <v>2.51</v>
+      </c>
+      <c r="AA366">
+        <v>2.98</v>
+      </c>
+      <c r="AB366">
+        <v>3.33</v>
+      </c>
+      <c r="AC366">
+        <v>1.12</v>
+      </c>
+      <c r="AD366">
+        <v>5.75</v>
+      </c>
+      <c r="AE366">
+        <v>1.5</v>
+      </c>
+      <c r="AF366">
+        <v>2.3</v>
+      </c>
+      <c r="AG366">
+        <v>2.81</v>
+      </c>
+      <c r="AH366">
+        <v>1.38</v>
+      </c>
+      <c r="AI366">
+        <v>2.2</v>
+      </c>
+      <c r="AJ366">
+        <v>1.62</v>
+      </c>
+      <c r="AK366">
+        <v>1.32</v>
+      </c>
+      <c r="AL366">
+        <v>1.39</v>
+      </c>
+      <c r="AM366">
+        <v>1.55</v>
+      </c>
+      <c r="AN366">
+        <v>1.94</v>
+      </c>
+      <c r="AO366">
+        <v>1.31</v>
+      </c>
+      <c r="AP366">
+        <v>1.88</v>
+      </c>
+      <c r="AQ366">
+        <v>1.29</v>
+      </c>
+      <c r="AR366">
+        <v>1.59</v>
+      </c>
+      <c r="AS366">
+        <v>1.31</v>
+      </c>
+      <c r="AT366">
+        <v>2.9</v>
+      </c>
+      <c r="AU366">
+        <v>5</v>
+      </c>
+      <c r="AV366">
+        <v>5</v>
+      </c>
+      <c r="AW366">
+        <v>9</v>
+      </c>
+      <c r="AX366">
+        <v>5</v>
+      </c>
+      <c r="AY366">
+        <v>16</v>
+      </c>
+      <c r="AZ366">
+        <v>11</v>
+      </c>
+      <c r="BA366">
+        <v>7</v>
+      </c>
+      <c r="BB366">
+        <v>1</v>
+      </c>
+      <c r="BC366">
+        <v>8</v>
+      </c>
+      <c r="BD366">
+        <v>1.65</v>
+      </c>
+      <c r="BE366">
+        <v>6.25</v>
+      </c>
+      <c r="BF366">
+        <v>2.7</v>
+      </c>
+      <c r="BG366">
+        <v>1.36</v>
+      </c>
+      <c r="BH366">
+        <v>2.8</v>
+      </c>
+      <c r="BI366">
+        <v>1.68</v>
+      </c>
+      <c r="BJ366">
+        <v>2</v>
+      </c>
+      <c r="BK366">
+        <v>2.2</v>
+      </c>
+      <c r="BL366">
+        <v>1.57</v>
+      </c>
+      <c r="BM366">
+        <v>3</v>
+      </c>
+      <c r="BN366">
+        <v>1.31</v>
+      </c>
+      <c r="BO366">
+        <v>3.98</v>
+      </c>
+      <c r="BP366">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="367" spans="1:68">
+      <c r="A367" s="1">
+        <v>366</v>
+      </c>
+      <c r="B367">
+        <v>7728560</v>
+      </c>
+      <c r="C367" t="s">
+        <v>68</v>
+      </c>
+      <c r="D367" t="s">
+        <v>69</v>
+      </c>
+      <c r="E367" s="2">
+        <v>45752.5625</v>
+      </c>
+      <c r="F367">
+        <v>34</v>
+      </c>
+      <c r="G367" t="s">
+        <v>87</v>
+      </c>
+      <c r="H367" t="s">
+        <v>80</v>
+      </c>
+      <c r="I367">
+        <v>0</v>
+      </c>
+      <c r="J367">
+        <v>0</v>
+      </c>
+      <c r="K367">
+        <v>0</v>
+      </c>
+      <c r="L367">
+        <v>0</v>
+      </c>
+      <c r="M367">
+        <v>1</v>
+      </c>
+      <c r="N367">
+        <v>1</v>
+      </c>
+      <c r="O367" t="s">
+        <v>94</v>
+      </c>
+      <c r="P367" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q367">
+        <v>5</v>
+      </c>
+      <c r="R367">
+        <v>1.95</v>
+      </c>
+      <c r="S367">
+        <v>2.75</v>
+      </c>
+      <c r="T367">
+        <v>1.57</v>
+      </c>
+      <c r="U367">
+        <v>2.25</v>
+      </c>
+      <c r="V367">
+        <v>3.75</v>
+      </c>
+      <c r="W367">
+        <v>1.25</v>
+      </c>
+      <c r="X367">
+        <v>11</v>
+      </c>
+      <c r="Y367">
+        <v>1.05</v>
+      </c>
+      <c r="Z367">
+        <v>4</v>
+      </c>
+      <c r="AA367">
+        <v>3.19</v>
+      </c>
+      <c r="AB367">
+        <v>2.12</v>
+      </c>
+      <c r="AC367">
+        <v>1.09</v>
+      </c>
+      <c r="AD367">
+        <v>7</v>
+      </c>
+      <c r="AE367">
+        <v>1.48</v>
+      </c>
+      <c r="AF367">
+        <v>2.6</v>
+      </c>
+      <c r="AG367">
+        <v>2.3</v>
+      </c>
+      <c r="AH367">
+        <v>1.5</v>
+      </c>
+      <c r="AI367">
+        <v>2.2</v>
+      </c>
+      <c r="AJ367">
+        <v>1.62</v>
+      </c>
+      <c r="AK367">
+        <v>2</v>
+      </c>
+      <c r="AL367">
+        <v>1.31</v>
+      </c>
+      <c r="AM367">
+        <v>1.17</v>
+      </c>
+      <c r="AN367">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO367">
+        <v>1</v>
+      </c>
+      <c r="AP367">
+        <v>0.53</v>
+      </c>
+      <c r="AQ367">
+        <v>1.12</v>
+      </c>
+      <c r="AR367">
+        <v>1.14</v>
+      </c>
+      <c r="AS367">
+        <v>1.13</v>
+      </c>
+      <c r="AT367">
+        <v>2.27</v>
+      </c>
+      <c r="AU367">
+        <v>4</v>
+      </c>
+      <c r="AV367">
+        <v>5</v>
+      </c>
+      <c r="AW367">
+        <v>6</v>
+      </c>
+      <c r="AX367">
+        <v>18</v>
+      </c>
+      <c r="AY367">
+        <v>11</v>
+      </c>
+      <c r="AZ367">
+        <v>27</v>
+      </c>
+      <c r="BA367">
+        <v>3</v>
+      </c>
+      <c r="BB367">
+        <v>5</v>
+      </c>
+      <c r="BC367">
+        <v>8</v>
+      </c>
+      <c r="BD367">
+        <v>2.4</v>
+      </c>
+      <c r="BE367">
+        <v>6.25</v>
+      </c>
+      <c r="BF367">
+        <v>1.8</v>
+      </c>
+      <c r="BG367">
+        <v>1.27</v>
+      </c>
+      <c r="BH367">
+        <v>3.25</v>
+      </c>
+      <c r="BI367">
+        <v>1.51</v>
+      </c>
+      <c r="BJ367">
+        <v>2.3</v>
+      </c>
+      <c r="BK367">
+        <v>1.9</v>
+      </c>
+      <c r="BL367">
+        <v>1.75</v>
+      </c>
+      <c r="BM367">
+        <v>2.5</v>
+      </c>
+      <c r="BN367">
+        <v>1.43</v>
+      </c>
+      <c r="BO367">
+        <v>3.6</v>
+      </c>
+      <c r="BP367">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="368" spans="1:68">
+      <c r="A368" s="1">
+        <v>367</v>
+      </c>
+      <c r="B368">
+        <v>7728566</v>
+      </c>
+      <c r="C368" t="s">
+        <v>68</v>
+      </c>
+      <c r="D368" t="s">
+        <v>69</v>
+      </c>
+      <c r="E368" s="2">
+        <v>45752.5625</v>
+      </c>
+      <c r="F368">
+        <v>34</v>
+      </c>
+      <c r="G368" t="s">
+        <v>70</v>
+      </c>
+      <c r="H368" t="s">
+        <v>90</v>
+      </c>
+      <c r="I368">
+        <v>1</v>
+      </c>
+      <c r="J368">
+        <v>0</v>
+      </c>
+      <c r="K368">
+        <v>1</v>
+      </c>
+      <c r="L368">
+        <v>3</v>
+      </c>
+      <c r="M368">
+        <v>1</v>
+      </c>
+      <c r="N368">
+        <v>4</v>
+      </c>
+      <c r="O368" t="s">
+        <v>321</v>
+      </c>
+      <c r="P368" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q368">
+        <v>3.2</v>
+      </c>
+      <c r="R368">
+        <v>2.1</v>
+      </c>
+      <c r="S368">
+        <v>3.4</v>
+      </c>
+      <c r="T368">
+        <v>1.4</v>
+      </c>
+      <c r="U368">
+        <v>2.75</v>
+      </c>
+      <c r="V368">
+        <v>3</v>
+      </c>
+      <c r="W368">
+        <v>1.36</v>
+      </c>
+      <c r="X368">
+        <v>8</v>
+      </c>
+      <c r="Y368">
+        <v>1.08</v>
+      </c>
+      <c r="Z368">
+        <v>2.68</v>
+      </c>
+      <c r="AA368">
+        <v>3.39</v>
+      </c>
+      <c r="AB368">
+        <v>2.73</v>
+      </c>
+      <c r="AC368">
+        <v>1.06</v>
+      </c>
+      <c r="AD368">
+        <v>8.5</v>
+      </c>
+      <c r="AE368">
+        <v>1.3</v>
+      </c>
+      <c r="AF368">
+        <v>3.4</v>
+      </c>
+      <c r="AG368">
+        <v>1.93</v>
+      </c>
+      <c r="AH368">
+        <v>1.88</v>
+      </c>
+      <c r="AI368">
+        <v>1.73</v>
+      </c>
+      <c r="AJ368">
+        <v>2</v>
+      </c>
+      <c r="AK368">
+        <v>1.4</v>
+      </c>
+      <c r="AL368">
+        <v>1.32</v>
+      </c>
+      <c r="AM368">
+        <v>1.53</v>
+      </c>
+      <c r="AN368">
+        <v>1.76</v>
+      </c>
+      <c r="AO368">
+        <v>1.29</v>
+      </c>
+      <c r="AP368">
+        <v>1.83</v>
+      </c>
+      <c r="AQ368">
+        <v>1.22</v>
+      </c>
+      <c r="AR368">
+        <v>1.66</v>
+      </c>
+      <c r="AS368">
+        <v>1.59</v>
+      </c>
+      <c r="AT368">
+        <v>3.25</v>
+      </c>
+      <c r="AU368">
+        <v>8</v>
+      </c>
+      <c r="AV368">
+        <v>9</v>
+      </c>
+      <c r="AW368">
+        <v>8</v>
+      </c>
+      <c r="AX368">
+        <v>15</v>
+      </c>
+      <c r="AY368">
+        <v>21</v>
+      </c>
+      <c r="AZ368">
+        <v>29</v>
+      </c>
+      <c r="BA368">
+        <v>4</v>
+      </c>
+      <c r="BB368">
+        <v>4</v>
+      </c>
+      <c r="BC368">
+        <v>8</v>
+      </c>
+      <c r="BD368">
+        <v>1.78</v>
+      </c>
+      <c r="BE368">
+        <v>6.75</v>
+      </c>
+      <c r="BF368">
+        <v>2.35</v>
+      </c>
+      <c r="BG368">
+        <v>1.2</v>
+      </c>
+      <c r="BH368">
+        <v>4</v>
+      </c>
+      <c r="BI368">
+        <v>1.38</v>
+      </c>
+      <c r="BJ368">
+        <v>2.7</v>
+      </c>
+      <c r="BK368">
+        <v>1.68</v>
+      </c>
+      <c r="BL368">
+        <v>1.98</v>
+      </c>
+      <c r="BM368">
+        <v>2.15</v>
+      </c>
+      <c r="BN368">
+        <v>1.57</v>
+      </c>
+      <c r="BO368">
+        <v>2.95</v>
+      </c>
+      <c r="BP368">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="369" spans="1:68">
+      <c r="A369" s="1">
+        <v>368</v>
+      </c>
+      <c r="B369">
+        <v>7728564</v>
+      </c>
+      <c r="C369" t="s">
+        <v>68</v>
+      </c>
+      <c r="D369" t="s">
+        <v>69</v>
+      </c>
+      <c r="E369" s="2">
+        <v>45752.66666666666</v>
+      </c>
+      <c r="F369">
+        <v>34</v>
+      </c>
+      <c r="G369" t="s">
+        <v>76</v>
+      </c>
+      <c r="H369" t="s">
+        <v>84</v>
+      </c>
+      <c r="I369">
+        <v>0</v>
+      </c>
+      <c r="J369">
+        <v>0</v>
+      </c>
+      <c r="K369">
+        <v>0</v>
+      </c>
+      <c r="L369">
+        <v>1</v>
+      </c>
+      <c r="M369">
+        <v>3</v>
+      </c>
+      <c r="N369">
+        <v>4</v>
+      </c>
+      <c r="O369" t="s">
+        <v>283</v>
+      </c>
+      <c r="P369" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q369">
+        <v>2.75</v>
+      </c>
+      <c r="R369">
+        <v>1.95</v>
+      </c>
+      <c r="S369">
+        <v>4.75</v>
+      </c>
+      <c r="T369">
+        <v>1.53</v>
+      </c>
+      <c r="U369">
+        <v>2.38</v>
+      </c>
+      <c r="V369">
+        <v>3.75</v>
+      </c>
+      <c r="W369">
+        <v>1.25</v>
+      </c>
+      <c r="X369">
+        <v>11</v>
+      </c>
+      <c r="Y369">
+        <v>1.05</v>
+      </c>
+      <c r="Z369">
+        <v>1.96</v>
+      </c>
+      <c r="AA369">
+        <v>3.34</v>
+      </c>
+      <c r="AB369">
+        <v>4.4</v>
+      </c>
+      <c r="AC369">
+        <v>1.09</v>
+      </c>
+      <c r="AD369">
+        <v>7</v>
+      </c>
+      <c r="AE369">
+        <v>1.48</v>
+      </c>
+      <c r="AF369">
+        <v>2.37</v>
+      </c>
+      <c r="AG369">
+        <v>2.4</v>
+      </c>
+      <c r="AH369">
+        <v>1.57</v>
+      </c>
+      <c r="AI369">
+        <v>2.1</v>
+      </c>
+      <c r="AJ369">
+        <v>1.67</v>
+      </c>
+      <c r="AK369">
+        <v>1.26</v>
+      </c>
+      <c r="AL369">
+        <v>1.34</v>
+      </c>
+      <c r="AM369">
+        <v>1.72</v>
+      </c>
+      <c r="AN369">
+        <v>1.53</v>
+      </c>
+      <c r="AO369">
+        <v>0.19</v>
+      </c>
+      <c r="AP369">
+        <v>1.44</v>
+      </c>
+      <c r="AQ369">
+        <v>0.35</v>
+      </c>
+      <c r="AR369">
+        <v>1.54</v>
+      </c>
+      <c r="AS369">
+        <v>1.12</v>
+      </c>
+      <c r="AT369">
+        <v>2.66</v>
+      </c>
+      <c r="AU369">
+        <v>2</v>
+      </c>
+      <c r="AV369">
+        <v>5</v>
+      </c>
+      <c r="AW369">
+        <v>9</v>
+      </c>
+      <c r="AX369">
+        <v>9</v>
+      </c>
+      <c r="AY369">
+        <v>15</v>
+      </c>
+      <c r="AZ369">
+        <v>14</v>
+      </c>
+      <c r="BA369">
+        <v>6</v>
+      </c>
+      <c r="BB369">
+        <v>12</v>
+      </c>
+      <c r="BC369">
+        <v>18</v>
+      </c>
+      <c r="BD369">
+        <v>1.43</v>
+      </c>
+      <c r="BE369">
+        <v>7</v>
+      </c>
+      <c r="BF369">
+        <v>3.15</v>
+      </c>
+      <c r="BG369">
+        <v>1.43</v>
+      </c>
+      <c r="BH369">
+        <v>2.55</v>
+      </c>
+      <c r="BI369">
+        <v>1.7</v>
+      </c>
+      <c r="BJ369">
+        <v>1.98</v>
+      </c>
+      <c r="BK369">
+        <v>2.14</v>
+      </c>
+      <c r="BL369">
+        <v>1.6</v>
+      </c>
+      <c r="BM369">
+        <v>2.75</v>
+      </c>
+      <c r="BN369">
+        <v>1.37</v>
+      </c>
+      <c r="BO369">
+        <v>3.65</v>
+      </c>
+      <c r="BP369">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="445">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -982,6 +982,15 @@
     <t>['10', '78', '85']</t>
   </si>
   <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['16', '46', '90+7']</t>
+  </si>
+  <si>
+    <t>['39', '70']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1316,9 +1325,6 @@
   </si>
   <si>
     <t>['27', '55']</t>
-  </si>
-  <si>
-    <t>['78']</t>
   </si>
   <si>
     <t>['45+6', '90+7']</t>
@@ -1704,7 +1710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP369"/>
+  <dimension ref="A1:BP374"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1960,7 +1966,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2247,7 +2253,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ3">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2372,7 +2378,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -3068,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7">
         <v>1.29</v>
@@ -3196,7 +3202,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3402,7 +3408,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3686,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ10">
         <v>0.47</v>
@@ -3895,7 +3901,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ11">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4226,7 +4232,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -5128,10 +5134,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ17">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5334,10 +5340,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5462,7 +5468,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -6080,7 +6086,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6286,7 +6292,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6492,7 +6498,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6573,7 +6579,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ24">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR24">
         <v>2.51</v>
@@ -6698,7 +6704,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6779,7 +6785,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ25">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6904,7 +6910,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -7188,7 +7194,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7522,7 +7528,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7600,7 +7606,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ29">
         <v>1.18</v>
@@ -7806,7 +7812,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ30">
         <v>0.8100000000000001</v>
@@ -8140,7 +8146,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8346,7 +8352,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8633,7 +8639,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ34">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR34">
         <v>1.17</v>
@@ -8758,7 +8764,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8839,7 +8845,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ35">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR35">
         <v>1.42</v>
@@ -9869,7 +9875,7 @@
         <v>0.59</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -10484,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ43">
         <v>1.19</v>
@@ -10612,7 +10618,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10693,7 +10699,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ44">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -11230,7 +11236,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11308,7 +11314,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ47">
         <v>1.12</v>
@@ -11720,10 +11726,10 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ49">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR49">
         <v>1.38</v>
@@ -12544,7 +12550,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ53">
         <v>1.18</v>
@@ -12878,7 +12884,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -13084,7 +13090,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13290,7 +13296,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13496,7 +13502,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13908,7 +13914,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13986,7 +13992,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ60">
         <v>1.12</v>
@@ -14192,7 +14198,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ61">
         <v>1.53</v>
@@ -14526,7 +14532,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14607,7 +14613,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ63">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR63">
         <v>1.13</v>
@@ -14813,7 +14819,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ64">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR64">
         <v>1.39</v>
@@ -15019,7 +15025,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR65">
         <v>1.25</v>
@@ -15144,7 +15150,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15431,7 +15437,7 @@
         <v>2</v>
       </c>
       <c r="AQ67">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR67">
         <v>1.16</v>
@@ -15556,7 +15562,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15762,7 +15768,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16049,7 +16055,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ70">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR70">
         <v>1.04</v>
@@ -16380,7 +16386,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16458,7 +16464,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ72">
         <v>1.19</v>
@@ -16586,7 +16592,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16664,7 +16670,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ73">
         <v>1.22</v>
@@ -16792,7 +16798,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16870,7 +16876,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ74">
         <v>1.19</v>
@@ -17616,7 +17622,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17822,7 +17828,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17903,7 +17909,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR79">
         <v>1.18</v>
@@ -18234,7 +18240,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18440,7 +18446,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18646,7 +18652,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18724,10 +18730,10 @@
         <v>3</v>
       </c>
       <c r="AP83">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ83">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR83">
         <v>1.8</v>
@@ -19342,7 +19348,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ86">
         <v>0.88</v>
@@ -19470,7 +19476,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19754,7 +19760,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ88">
         <v>1.29</v>
@@ -19882,7 +19888,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19963,7 +19969,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ89">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -20088,7 +20094,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20500,7 +20506,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20912,7 +20918,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -21118,7 +21124,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21611,7 +21617,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ97">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -21814,10 +21820,10 @@
         <v>0.67</v>
       </c>
       <c r="AP98">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ98">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR98">
         <v>1.35</v>
@@ -22148,7 +22154,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22638,7 +22644,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ102">
         <v>1.29</v>
@@ -22844,7 +22850,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ103">
         <v>1.12</v>
@@ -23590,7 +23596,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23671,7 +23677,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ107">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR107">
         <v>1.53</v>
@@ -23877,7 +23883,7 @@
         <v>0.59</v>
       </c>
       <c r="AQ108">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR108">
         <v>1.17</v>
@@ -24208,7 +24214,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24286,7 +24292,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ110">
         <v>1.22</v>
@@ -24620,7 +24626,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24701,7 +24707,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR112">
         <v>1.61</v>
@@ -24826,7 +24832,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -25113,7 +25119,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ114">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -25238,7 +25244,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25525,7 +25531,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ116">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -26062,7 +26068,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26140,7 +26146,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ119">
         <v>1.53</v>
@@ -26349,7 +26355,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ120">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR120">
         <v>1.6</v>
@@ -26680,7 +26686,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26758,7 +26764,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ122">
         <v>0.8100000000000001</v>
@@ -27092,7 +27098,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27504,7 +27510,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27582,7 +27588,7 @@
         <v>1.8</v>
       </c>
       <c r="AP126">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ126">
         <v>1.18</v>
@@ -27788,7 +27794,7 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ127">
         <v>0.82</v>
@@ -27916,7 +27922,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27994,10 +28000,10 @@
         <v>3</v>
       </c>
       <c r="AP128">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ128">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR128">
         <v>1.61</v>
@@ -28328,7 +28334,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28534,7 +28540,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28740,7 +28746,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -29152,7 +29158,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29358,7 +29364,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29645,7 +29651,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ136">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -29848,7 +29854,7 @@
         <v>2.2</v>
       </c>
       <c r="AP137">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ137">
         <v>1.19</v>
@@ -29976,7 +29982,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30469,7 +30475,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR140">
         <v>1.34</v>
@@ -30594,7 +30600,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30800,7 +30806,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30881,7 +30887,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ142">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR142">
         <v>1.16</v>
@@ -31006,7 +31012,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -31212,7 +31218,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31496,7 +31502,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ145">
         <v>0.47</v>
@@ -31624,7 +31630,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31908,7 +31914,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ147">
         <v>0.9399999999999999</v>
@@ -32036,7 +32042,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32117,7 +32123,7 @@
         <v>0.59</v>
       </c>
       <c r="AQ148">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR148">
         <v>1.13</v>
@@ -32526,7 +32532,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ150">
         <v>0.82</v>
@@ -33066,7 +33072,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33147,7 +33153,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ153">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR153">
         <v>1.58</v>
@@ -33350,7 +33356,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ154">
         <v>1.19</v>
@@ -33684,7 +33690,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33971,7 +33977,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ157">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR157">
         <v>1.49</v>
@@ -34589,7 +34595,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ160">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34792,7 +34798,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ161">
         <v>0.88</v>
@@ -35001,7 +35007,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ162">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR162">
         <v>1.47</v>
@@ -35332,7 +35338,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35619,7 +35625,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ165">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR165">
         <v>1.7</v>
@@ -35822,7 +35828,7 @@
         <v>0.71</v>
       </c>
       <c r="AP166">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ166">
         <v>0.82</v>
@@ -35950,7 +35956,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36234,10 +36240,10 @@
         <v>3</v>
       </c>
       <c r="AP168">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ168">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR168">
         <v>1.29</v>
@@ -36646,7 +36652,7 @@
         <v>1.29</v>
       </c>
       <c r="AP170">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ170">
         <v>0.9399999999999999</v>
@@ -36980,7 +36986,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37473,7 +37479,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ174">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR174">
         <v>1.76</v>
@@ -37598,7 +37604,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37676,7 +37682,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ175">
         <v>0.88</v>
@@ -38010,7 +38016,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38091,7 +38097,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ177">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR177">
         <v>1.68</v>
@@ -38294,7 +38300,7 @@
         <v>1</v>
       </c>
       <c r="AP178">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ178">
         <v>1</v>
@@ -38422,7 +38428,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38628,7 +38634,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38915,7 +38921,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ181">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR181">
         <v>1.48</v>
@@ -39452,7 +39458,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39530,7 +39536,7 @@
         <v>0.88</v>
       </c>
       <c r="AP184">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ184">
         <v>1.12</v>
@@ -39945,7 +39951,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ186">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR186">
         <v>1.44</v>
@@ -40276,7 +40282,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40563,7 +40569,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ189">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR189">
         <v>1.53</v>
@@ -40769,7 +40775,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ190">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR190">
         <v>1.74</v>
@@ -40894,7 +40900,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40972,7 +40978,7 @@
         <v>1.67</v>
       </c>
       <c r="AP191">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ191">
         <v>1.18</v>
@@ -41100,7 +41106,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41306,7 +41312,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41512,7 +41518,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41590,7 +41596,7 @@
         <v>1.56</v>
       </c>
       <c r="AP194">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ194">
         <v>1.22</v>
@@ -42002,7 +42008,7 @@
         <v>0.63</v>
       </c>
       <c r="AP196">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ196">
         <v>1.12</v>
@@ -42623,7 +42629,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ199">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR199">
         <v>1.74</v>
@@ -42748,7 +42754,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42826,10 +42832,10 @@
         <v>0.11</v>
       </c>
       <c r="AP200">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ200">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR200">
         <v>1.61</v>
@@ -43160,7 +43166,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43366,7 +43372,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43984,7 +43990,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44268,7 +44274,7 @@
         <v>0.78</v>
       </c>
       <c r="AP207">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ207">
         <v>0.88</v>
@@ -44477,7 +44483,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ208">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR208">
         <v>1.46</v>
@@ -45014,7 +45020,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -45220,7 +45226,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45298,7 +45304,7 @@
         <v>1.1</v>
       </c>
       <c r="AP212">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ212">
         <v>1.29</v>
@@ -45426,7 +45432,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45632,7 +45638,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45916,7 +45922,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP215">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ215">
         <v>1.12</v>
@@ -46044,7 +46050,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46331,7 +46337,7 @@
         <v>2.41</v>
       </c>
       <c r="AQ217">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR217">
         <v>1.61</v>
@@ -46534,7 +46540,7 @@
         <v>1.67</v>
       </c>
       <c r="AP218">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ218">
         <v>1.18</v>
@@ -47280,7 +47286,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47361,7 +47367,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ222">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR222">
         <v>1.64</v>
@@ -47564,7 +47570,7 @@
         <v>1.11</v>
       </c>
       <c r="AP223">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ223">
         <v>0.8100000000000001</v>
@@ -47692,7 +47698,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47976,7 +47982,7 @@
         <v>0.2</v>
       </c>
       <c r="AP225">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ225">
         <v>0.35</v>
@@ -48104,7 +48110,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48391,7 +48397,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ227">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR227">
         <v>1.67</v>
@@ -48722,7 +48728,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48800,10 +48806,10 @@
         <v>1.22</v>
       </c>
       <c r="AP229">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ229">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR229">
         <v>1.48</v>
@@ -48928,7 +48934,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49006,10 +49012,10 @@
         <v>1.3</v>
       </c>
       <c r="AP230">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ230">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR230">
         <v>1.54</v>
@@ -49134,7 +49140,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49833,7 +49839,7 @@
         <v>2</v>
       </c>
       <c r="AQ234">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR234">
         <v>1.16</v>
@@ -49958,7 +49964,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50039,7 +50045,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ235">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR235">
         <v>1.56</v>
@@ -50448,7 +50454,7 @@
         <v>1.22</v>
       </c>
       <c r="AP237">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ237">
         <v>1.53</v>
@@ -50782,7 +50788,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51400,7 +51406,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51812,7 +51818,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51893,7 +51899,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ244">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR244">
         <v>1.4</v>
@@ -52224,7 +52230,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52508,7 +52514,7 @@
         <v>1.5</v>
       </c>
       <c r="AP247">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ247">
         <v>1.19</v>
@@ -52714,7 +52720,7 @@
         <v>1.2</v>
       </c>
       <c r="AP248">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ248">
         <v>1.53</v>
@@ -53048,7 +53054,7 @@
         <v>124</v>
       </c>
       <c r="P250" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -53129,7 +53135,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ250">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR250">
         <v>1.68</v>
@@ -53254,7 +53260,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53332,7 +53338,7 @@
         <v>0.18</v>
       </c>
       <c r="AP251">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ251">
         <v>0.35</v>
@@ -53541,7 +53547,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ252">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR252">
         <v>1.71</v>
@@ -53666,7 +53672,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -54078,7 +54084,7 @@
         <v>254</v>
       </c>
       <c r="P255" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="Q255">
         <v>2.75</v>
@@ -54159,7 +54165,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ255">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR255">
         <v>1.61</v>
@@ -54284,7 +54290,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="Q256">
         <v>2.8</v>
@@ -54362,7 +54368,7 @@
         <v>1.33</v>
       </c>
       <c r="AP256">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ256">
         <v>1.53</v>
@@ -55314,7 +55320,7 @@
         <v>257</v>
       </c>
       <c r="P261" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q261">
         <v>3.45</v>
@@ -55520,7 +55526,7 @@
         <v>258</v>
       </c>
       <c r="P262" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55598,7 +55604,7 @@
         <v>1.33</v>
       </c>
       <c r="AP262">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ262">
         <v>1.18</v>
@@ -55807,7 +55813,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ263">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR263">
         <v>1.43</v>
@@ -56138,7 +56144,7 @@
         <v>94</v>
       </c>
       <c r="P265" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -57249,7 +57255,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ270">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR270">
         <v>1.69</v>
@@ -57580,7 +57586,7 @@
         <v>94</v>
       </c>
       <c r="P272" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Q272">
         <v>4</v>
@@ -57661,7 +57667,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ272">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR272">
         <v>1.18</v>
@@ -57864,10 +57870,10 @@
         <v>1.18</v>
       </c>
       <c r="AP273">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ273">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR273">
         <v>1.65</v>
@@ -58276,7 +58282,7 @@
         <v>0.91</v>
       </c>
       <c r="AP275">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ275">
         <v>0.8100000000000001</v>
@@ -58610,7 +58616,7 @@
         <v>265</v>
       </c>
       <c r="P277" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58897,7 +58903,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ278">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR278">
         <v>1.69</v>
@@ -59100,7 +59106,7 @@
         <v>1.46</v>
       </c>
       <c r="AP279">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ279">
         <v>1.53</v>
@@ -59718,10 +59724,10 @@
         <v>2.17</v>
       </c>
       <c r="AP282">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ282">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR282">
         <v>1.44</v>
@@ -59846,7 +59852,7 @@
         <v>186</v>
       </c>
       <c r="P283" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Q283">
         <v>2.75</v>
@@ -59927,7 +59933,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ283">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR283">
         <v>1.67</v>
@@ -60052,7 +60058,7 @@
         <v>267</v>
       </c>
       <c r="P284" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Q284">
         <v>2.05</v>
@@ -60336,7 +60342,7 @@
         <v>1.62</v>
       </c>
       <c r="AP285">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ285">
         <v>1.22</v>
@@ -60670,7 +60676,7 @@
         <v>269</v>
       </c>
       <c r="P287" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q287">
         <v>2.4</v>
@@ -61288,7 +61294,7 @@
         <v>271</v>
       </c>
       <c r="P290" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61369,7 +61375,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ290">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR290">
         <v>1.62</v>
@@ -61494,7 +61500,7 @@
         <v>272</v>
       </c>
       <c r="P291" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="Q291">
         <v>2.75</v>
@@ -61575,7 +61581,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ291">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR291">
         <v>1.32</v>
@@ -61778,7 +61784,7 @@
         <v>1</v>
       </c>
       <c r="AP292">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ292">
         <v>0.9399999999999999</v>
@@ -62396,7 +62402,7 @@
         <v>0.75</v>
       </c>
       <c r="AP295">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ295">
         <v>1.12</v>
@@ -63014,7 +63020,7 @@
         <v>0.23</v>
       </c>
       <c r="AP298">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ298">
         <v>0.35</v>
@@ -63223,7 +63229,7 @@
         <v>0.59</v>
       </c>
       <c r="AQ299">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR299">
         <v>1.24</v>
@@ -63348,7 +63354,7 @@
         <v>147</v>
       </c>
       <c r="P300" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63426,7 +63432,7 @@
         <v>1.38</v>
       </c>
       <c r="AP300">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ300">
         <v>1.29</v>
@@ -63554,7 +63560,7 @@
         <v>278</v>
       </c>
       <c r="P301" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Q301">
         <v>2.85</v>
@@ -63635,7 +63641,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ301">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR301">
         <v>1.54</v>
@@ -63760,7 +63766,7 @@
         <v>279</v>
       </c>
       <c r="P302" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="Q302">
         <v>2.6</v>
@@ -64250,10 +64256,10 @@
         <v>1.5</v>
       </c>
       <c r="AP304">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ304">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR304">
         <v>1.51</v>
@@ -64662,10 +64668,10 @@
         <v>1.15</v>
       </c>
       <c r="AP306">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ306">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR306">
         <v>1.68</v>
@@ -65202,7 +65208,7 @@
         <v>94</v>
       </c>
       <c r="P309" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Q309">
         <v>4.8</v>
@@ -65898,7 +65904,7 @@
         <v>1</v>
       </c>
       <c r="AP312">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ312">
         <v>0.9399999999999999</v>
@@ -66026,7 +66032,7 @@
         <v>284</v>
       </c>
       <c r="P313" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="Q313">
         <v>1.92</v>
@@ -66438,7 +66444,7 @@
         <v>138</v>
       </c>
       <c r="P315" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="Q315">
         <v>2.49</v>
@@ -66644,7 +66650,7 @@
         <v>130</v>
       </c>
       <c r="P316" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q316">
         <v>3.45</v>
@@ -66931,7 +66937,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ317">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR317">
         <v>1.53</v>
@@ -67958,10 +67964,10 @@
         <v>1.13</v>
       </c>
       <c r="AP322">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ322">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR322">
         <v>1.55</v>
@@ -68579,7 +68585,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ325">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR325">
         <v>1.53</v>
@@ -68704,7 +68710,7 @@
         <v>294</v>
       </c>
       <c r="P326" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="Q326">
         <v>2.65</v>
@@ -68782,7 +68788,7 @@
         <v>0.93</v>
       </c>
       <c r="AP326">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ326">
         <v>1.12</v>
@@ -68991,7 +68997,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ327">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR327">
         <v>1.32</v>
@@ -69116,7 +69122,7 @@
         <v>94</v>
       </c>
       <c r="P328" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="Q328">
         <v>3.3</v>
@@ -69194,10 +69200,10 @@
         <v>1.21</v>
       </c>
       <c r="AP328">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ328">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR328">
         <v>1.38</v>
@@ -69400,7 +69406,7 @@
         <v>0.47</v>
       </c>
       <c r="AP329">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ329">
         <v>0.47</v>
@@ -69812,7 +69818,7 @@
         <v>0.93</v>
       </c>
       <c r="AP331">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ331">
         <v>1</v>
@@ -71176,7 +71182,7 @@
         <v>302</v>
       </c>
       <c r="P338" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="Q338">
         <v>3.5</v>
@@ -71257,7 +71263,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ338">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR338">
         <v>1.53</v>
@@ -71382,7 +71388,7 @@
         <v>183</v>
       </c>
       <c r="P339" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Q339">
         <v>3.4</v>
@@ -72000,7 +72006,7 @@
         <v>304</v>
       </c>
       <c r="P342" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="Q342">
         <v>2.88</v>
@@ -72284,7 +72290,7 @@
         <v>1.38</v>
       </c>
       <c r="AP343">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AQ343">
         <v>1.22</v>
@@ -72699,7 +72705,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ345">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AR345">
         <v>1.38</v>
@@ -72902,7 +72908,7 @@
         <v>0.87</v>
       </c>
       <c r="AP346">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ346">
         <v>0.8100000000000001</v>
@@ -73236,7 +73242,7 @@
         <v>310</v>
       </c>
       <c r="P348" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="Q348">
         <v>2.3</v>
@@ -73314,7 +73320,7 @@
         <v>1.27</v>
       </c>
       <c r="AP348">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ348">
         <v>1.18</v>
@@ -73442,7 +73448,7 @@
         <v>311</v>
       </c>
       <c r="P349" t="s">
-        <v>434</v>
+        <v>322</v>
       </c>
       <c r="Q349">
         <v>2.6</v>
@@ -73523,7 +73529,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ349">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AR349">
         <v>1.54</v>
@@ -73648,7 +73654,7 @@
         <v>94</v>
       </c>
       <c r="P350" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q350">
         <v>2.63</v>
@@ -73935,7 +73941,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ351">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR351">
         <v>1.38</v>
@@ -74060,7 +74066,7 @@
         <v>313</v>
       </c>
       <c r="P352" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q352">
         <v>1.8</v>
@@ -74138,7 +74144,7 @@
         <v>0.44</v>
       </c>
       <c r="AP352">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ352">
         <v>0.47</v>
@@ -74266,7 +74272,7 @@
         <v>117</v>
       </c>
       <c r="P353" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q353">
         <v>2.88</v>
@@ -74344,10 +74350,10 @@
         <v>1.13</v>
       </c>
       <c r="AP353">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AQ353">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AR353">
         <v>1.65</v>
@@ -75090,7 +75096,7 @@
         <v>315</v>
       </c>
       <c r="P357" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q357">
         <v>4.6</v>
@@ -75708,7 +75714,7 @@
         <v>147</v>
       </c>
       <c r="P360" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q360">
         <v>3.25</v>
@@ -76120,7 +76126,7 @@
         <v>318</v>
       </c>
       <c r="P362" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Q362">
         <v>3.1</v>
@@ -76326,7 +76332,7 @@
         <v>319</v>
       </c>
       <c r="P363" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="Q363">
         <v>3.25</v>
@@ -76407,7 +76413,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ363">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR363">
         <v>1.53</v>
@@ -76738,7 +76744,7 @@
         <v>320</v>
       </c>
       <c r="P365" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Q365">
         <v>2.38</v>
@@ -76944,7 +76950,7 @@
         <v>244</v>
       </c>
       <c r="P366" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q366">
         <v>3.4</v>
@@ -77562,7 +77568,7 @@
         <v>283</v>
       </c>
       <c r="P369" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Q369">
         <v>2.75</v>
@@ -77676,10 +77682,10 @@
         <v>6</v>
       </c>
       <c r="BB369">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC369">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD369">
         <v>1.43</v>
@@ -77718,6 +77724,1036 @@
         <v>3.65</v>
       </c>
       <c r="BP369">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="370" spans="1:68">
+      <c r="A370" s="1">
+        <v>369</v>
+      </c>
+      <c r="B370">
+        <v>7728569</v>
+      </c>
+      <c r="C370" t="s">
+        <v>68</v>
+      </c>
+      <c r="D370" t="s">
+        <v>69</v>
+      </c>
+      <c r="E370" s="2">
+        <v>45753.375</v>
+      </c>
+      <c r="F370">
+        <v>34</v>
+      </c>
+      <c r="G370" t="s">
+        <v>91</v>
+      </c>
+      <c r="H370" t="s">
+        <v>71</v>
+      </c>
+      <c r="I370">
+        <v>0</v>
+      </c>
+      <c r="J370">
+        <v>0</v>
+      </c>
+      <c r="K370">
+        <v>0</v>
+      </c>
+      <c r="L370">
+        <v>1</v>
+      </c>
+      <c r="M370">
+        <v>0</v>
+      </c>
+      <c r="N370">
+        <v>1</v>
+      </c>
+      <c r="O370" t="s">
+        <v>322</v>
+      </c>
+      <c r="P370" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q370">
+        <v>3.4</v>
+      </c>
+      <c r="R370">
+        <v>1.91</v>
+      </c>
+      <c r="S370">
+        <v>4</v>
+      </c>
+      <c r="T370">
+        <v>1.62</v>
+      </c>
+      <c r="U370">
+        <v>2.2</v>
+      </c>
+      <c r="V370">
+        <v>4</v>
+      </c>
+      <c r="W370">
+        <v>1.22</v>
+      </c>
+      <c r="X370">
+        <v>13</v>
+      </c>
+      <c r="Y370">
+        <v>1.04</v>
+      </c>
+      <c r="Z370">
+        <v>2.37</v>
+      </c>
+      <c r="AA370">
+        <v>3.12</v>
+      </c>
+      <c r="AB370">
+        <v>3.41</v>
+      </c>
+      <c r="AC370">
+        <v>1.11</v>
+      </c>
+      <c r="AD370">
+        <v>6.25</v>
+      </c>
+      <c r="AE370">
+        <v>1.5</v>
+      </c>
+      <c r="AF370">
+        <v>2.3</v>
+      </c>
+      <c r="AG370">
+        <v>2.62</v>
+      </c>
+      <c r="AH370">
+        <v>1.43</v>
+      </c>
+      <c r="AI370">
+        <v>2.2</v>
+      </c>
+      <c r="AJ370">
+        <v>1.62</v>
+      </c>
+      <c r="AK370">
+        <v>1.33</v>
+      </c>
+      <c r="AL370">
+        <v>1.33</v>
+      </c>
+      <c r="AM370">
+        <v>1.53</v>
+      </c>
+      <c r="AN370">
+        <v>1.06</v>
+      </c>
+      <c r="AO370">
+        <v>1</v>
+      </c>
+      <c r="AP370">
+        <v>1.18</v>
+      </c>
+      <c r="AQ370">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR370">
+        <v>1.63</v>
+      </c>
+      <c r="AS370">
+        <v>1.2</v>
+      </c>
+      <c r="AT370">
+        <v>2.83</v>
+      </c>
+      <c r="AU370">
+        <v>3</v>
+      </c>
+      <c r="AV370">
+        <v>3</v>
+      </c>
+      <c r="AW370">
+        <v>7</v>
+      </c>
+      <c r="AX370">
+        <v>7</v>
+      </c>
+      <c r="AY370">
+        <v>11</v>
+      </c>
+      <c r="AZ370">
+        <v>12</v>
+      </c>
+      <c r="BA370">
+        <v>4</v>
+      </c>
+      <c r="BB370">
+        <v>2</v>
+      </c>
+      <c r="BC370">
+        <v>6</v>
+      </c>
+      <c r="BD370">
+        <v>1.73</v>
+      </c>
+      <c r="BE370">
+        <v>6.4</v>
+      </c>
+      <c r="BF370">
+        <v>2.38</v>
+      </c>
+      <c r="BG370">
+        <v>1.46</v>
+      </c>
+      <c r="BH370">
+        <v>2.45</v>
+      </c>
+      <c r="BI370">
+        <v>1.77</v>
+      </c>
+      <c r="BJ370">
+        <v>1.89</v>
+      </c>
+      <c r="BK370">
+        <v>2.23</v>
+      </c>
+      <c r="BL370">
+        <v>1.56</v>
+      </c>
+      <c r="BM370">
+        <v>2.9</v>
+      </c>
+      <c r="BN370">
+        <v>1.34</v>
+      </c>
+      <c r="BO370">
+        <v>3.9</v>
+      </c>
+      <c r="BP370">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="371" spans="1:68">
+      <c r="A371" s="1">
+        <v>370</v>
+      </c>
+      <c r="B371">
+        <v>7728563</v>
+      </c>
+      <c r="C371" t="s">
+        <v>68</v>
+      </c>
+      <c r="D371" t="s">
+        <v>69</v>
+      </c>
+      <c r="E371" s="2">
+        <v>45753.46875</v>
+      </c>
+      <c r="F371">
+        <v>34</v>
+      </c>
+      <c r="G371" t="s">
+        <v>82</v>
+      </c>
+      <c r="H371" t="s">
+        <v>77</v>
+      </c>
+      <c r="I371">
+        <v>1</v>
+      </c>
+      <c r="J371">
+        <v>0</v>
+      </c>
+      <c r="K371">
+        <v>1</v>
+      </c>
+      <c r="L371">
+        <v>3</v>
+      </c>
+      <c r="M371">
+        <v>1</v>
+      </c>
+      <c r="N371">
+        <v>4</v>
+      </c>
+      <c r="O371" t="s">
+        <v>323</v>
+      </c>
+      <c r="P371" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q371">
+        <v>2.5</v>
+      </c>
+      <c r="R371">
+        <v>2.25</v>
+      </c>
+      <c r="S371">
+        <v>4.33</v>
+      </c>
+      <c r="T371">
+        <v>1.36</v>
+      </c>
+      <c r="U371">
+        <v>3</v>
+      </c>
+      <c r="V371">
+        <v>2.63</v>
+      </c>
+      <c r="W371">
+        <v>1.44</v>
+      </c>
+      <c r="X371">
+        <v>7</v>
+      </c>
+      <c r="Y371">
+        <v>1.1</v>
+      </c>
+      <c r="Z371">
+        <v>1.98</v>
+      </c>
+      <c r="AA371">
+        <v>3.33</v>
+      </c>
+      <c r="AB371">
+        <v>4.33</v>
+      </c>
+      <c r="AC371">
+        <v>1.05</v>
+      </c>
+      <c r="AD371">
+        <v>9</v>
+      </c>
+      <c r="AE371">
+        <v>1.25</v>
+      </c>
+      <c r="AF371">
+        <v>3.75</v>
+      </c>
+      <c r="AG371">
+        <v>1.87</v>
+      </c>
+      <c r="AH371">
+        <v>1.94</v>
+      </c>
+      <c r="AI371">
+        <v>1.67</v>
+      </c>
+      <c r="AJ371">
+        <v>2.1</v>
+      </c>
+      <c r="AK371">
+        <v>1.25</v>
+      </c>
+      <c r="AL371">
+        <v>1.25</v>
+      </c>
+      <c r="AM371">
+        <v>1.8</v>
+      </c>
+      <c r="AN371">
+        <v>2.06</v>
+      </c>
+      <c r="AO371">
+        <v>1.75</v>
+      </c>
+      <c r="AP371">
+        <v>2.12</v>
+      </c>
+      <c r="AQ371">
+        <v>1.65</v>
+      </c>
+      <c r="AR371">
+        <v>1.67</v>
+      </c>
+      <c r="AS371">
+        <v>1.34</v>
+      </c>
+      <c r="AT371">
+        <v>3.01</v>
+      </c>
+      <c r="AU371">
+        <v>10</v>
+      </c>
+      <c r="AV371">
+        <v>5</v>
+      </c>
+      <c r="AW371">
+        <v>7</v>
+      </c>
+      <c r="AX371">
+        <v>9</v>
+      </c>
+      <c r="AY371">
+        <v>19</v>
+      </c>
+      <c r="AZ371">
+        <v>16</v>
+      </c>
+      <c r="BA371">
+        <v>4</v>
+      </c>
+      <c r="BB371">
+        <v>6</v>
+      </c>
+      <c r="BC371">
+        <v>10</v>
+      </c>
+      <c r="BD371">
+        <v>1.58</v>
+      </c>
+      <c r="BE371">
+        <v>6.5</v>
+      </c>
+      <c r="BF371">
+        <v>2.65</v>
+      </c>
+      <c r="BG371">
+        <v>1.36</v>
+      </c>
+      <c r="BH371">
+        <v>2.8</v>
+      </c>
+      <c r="BI371">
+        <v>1.62</v>
+      </c>
+      <c r="BJ371">
+        <v>2.12</v>
+      </c>
+      <c r="BK371">
+        <v>2</v>
+      </c>
+      <c r="BL371">
+        <v>1.68</v>
+      </c>
+      <c r="BM371">
+        <v>2.55</v>
+      </c>
+      <c r="BN371">
+        <v>1.42</v>
+      </c>
+      <c r="BO371">
+        <v>3.4</v>
+      </c>
+      <c r="BP371">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="372" spans="1:68">
+      <c r="A372" s="1">
+        <v>371</v>
+      </c>
+      <c r="B372">
+        <v>7728568</v>
+      </c>
+      <c r="C372" t="s">
+        <v>68</v>
+      </c>
+      <c r="D372" t="s">
+        <v>69</v>
+      </c>
+      <c r="E372" s="2">
+        <v>45753.5625</v>
+      </c>
+      <c r="F372">
+        <v>34</v>
+      </c>
+      <c r="G372" t="s">
+        <v>83</v>
+      </c>
+      <c r="H372" t="s">
+        <v>88</v>
+      </c>
+      <c r="I372">
+        <v>0</v>
+      </c>
+      <c r="J372">
+        <v>0</v>
+      </c>
+      <c r="K372">
+        <v>0</v>
+      </c>
+      <c r="L372">
+        <v>0</v>
+      </c>
+      <c r="M372">
+        <v>1</v>
+      </c>
+      <c r="N372">
+        <v>1</v>
+      </c>
+      <c r="O372" t="s">
+        <v>94</v>
+      </c>
+      <c r="P372" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q372">
+        <v>3.25</v>
+      </c>
+      <c r="R372">
+        <v>2</v>
+      </c>
+      <c r="S372">
+        <v>3.6</v>
+      </c>
+      <c r="T372">
+        <v>1.5</v>
+      </c>
+      <c r="U372">
+        <v>2.5</v>
+      </c>
+      <c r="V372">
+        <v>3.4</v>
+      </c>
+      <c r="W372">
+        <v>1.3</v>
+      </c>
+      <c r="X372">
+        <v>10</v>
+      </c>
+      <c r="Y372">
+        <v>1.06</v>
+      </c>
+      <c r="Z372">
+        <v>2.63</v>
+      </c>
+      <c r="AA372">
+        <v>3.12</v>
+      </c>
+      <c r="AB372">
+        <v>2.99</v>
+      </c>
+      <c r="AC372">
+        <v>1.08</v>
+      </c>
+      <c r="AD372">
+        <v>7.5</v>
+      </c>
+      <c r="AE372">
+        <v>1.42</v>
+      </c>
+      <c r="AF372">
+        <v>2.85</v>
+      </c>
+      <c r="AG372">
+        <v>2.1</v>
+      </c>
+      <c r="AH372">
+        <v>1.6</v>
+      </c>
+      <c r="AI372">
+        <v>1.83</v>
+      </c>
+      <c r="AJ372">
+        <v>1.83</v>
+      </c>
+      <c r="AK372">
+        <v>1.4</v>
+      </c>
+      <c r="AL372">
+        <v>1.3</v>
+      </c>
+      <c r="AM372">
+        <v>1.5</v>
+      </c>
+      <c r="AN372">
+        <v>1.69</v>
+      </c>
+      <c r="AO372">
+        <v>1.12</v>
+      </c>
+      <c r="AP372">
+        <v>1.59</v>
+      </c>
+      <c r="AQ372">
+        <v>1.22</v>
+      </c>
+      <c r="AR372">
+        <v>1.35</v>
+      </c>
+      <c r="AS372">
+        <v>1.47</v>
+      </c>
+      <c r="AT372">
+        <v>2.82</v>
+      </c>
+      <c r="AU372">
+        <v>3</v>
+      </c>
+      <c r="AV372">
+        <v>5</v>
+      </c>
+      <c r="AW372">
+        <v>5</v>
+      </c>
+      <c r="AX372">
+        <v>4</v>
+      </c>
+      <c r="AY372">
+        <v>13</v>
+      </c>
+      <c r="AZ372">
+        <v>14</v>
+      </c>
+      <c r="BA372">
+        <v>5</v>
+      </c>
+      <c r="BB372">
+        <v>10</v>
+      </c>
+      <c r="BC372">
+        <v>15</v>
+      </c>
+      <c r="BD372">
+        <v>1.84</v>
+      </c>
+      <c r="BE372">
+        <v>6.4</v>
+      </c>
+      <c r="BF372">
+        <v>2.15</v>
+      </c>
+      <c r="BG372">
+        <v>1.33</v>
+      </c>
+      <c r="BH372">
+        <v>2.95</v>
+      </c>
+      <c r="BI372">
+        <v>1.56</v>
+      </c>
+      <c r="BJ372">
+        <v>2.23</v>
+      </c>
+      <c r="BK372">
+        <v>1.89</v>
+      </c>
+      <c r="BL372">
+        <v>1.77</v>
+      </c>
+      <c r="BM372">
+        <v>2.4</v>
+      </c>
+      <c r="BN372">
+        <v>1.48</v>
+      </c>
+      <c r="BO372">
+        <v>3.05</v>
+      </c>
+      <c r="BP372">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="373" spans="1:68">
+      <c r="A373" s="1">
+        <v>372</v>
+      </c>
+      <c r="B373">
+        <v>7728845</v>
+      </c>
+      <c r="C373" t="s">
+        <v>68</v>
+      </c>
+      <c r="D373" t="s">
+        <v>69</v>
+      </c>
+      <c r="E373" s="2">
+        <v>45753.5625</v>
+      </c>
+      <c r="F373">
+        <v>34</v>
+      </c>
+      <c r="G373" t="s">
+        <v>78</v>
+      </c>
+      <c r="H373" t="s">
+        <v>81</v>
+      </c>
+      <c r="I373">
+        <v>1</v>
+      </c>
+      <c r="J373">
+        <v>0</v>
+      </c>
+      <c r="K373">
+        <v>1</v>
+      </c>
+      <c r="L373">
+        <v>2</v>
+      </c>
+      <c r="M373">
+        <v>1</v>
+      </c>
+      <c r="N373">
+        <v>3</v>
+      </c>
+      <c r="O373" t="s">
+        <v>324</v>
+      </c>
+      <c r="P373" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q373">
+        <v>3.1</v>
+      </c>
+      <c r="R373">
+        <v>1.8</v>
+      </c>
+      <c r="S373">
+        <v>5</v>
+      </c>
+      <c r="T373">
+        <v>1.73</v>
+      </c>
+      <c r="U373">
+        <v>2</v>
+      </c>
+      <c r="V373">
+        <v>5</v>
+      </c>
+      <c r="W373">
+        <v>1.17</v>
+      </c>
+      <c r="X373">
+        <v>17</v>
+      </c>
+      <c r="Y373">
+        <v>1.03</v>
+      </c>
+      <c r="Z373">
+        <v>2.19</v>
+      </c>
+      <c r="AA373">
+        <v>3.01</v>
+      </c>
+      <c r="AB373">
+        <v>4.1</v>
+      </c>
+      <c r="AC373">
+        <v>1.15</v>
+      </c>
+      <c r="AD373">
+        <v>5.25</v>
+      </c>
+      <c r="AE373">
+        <v>1.79</v>
+      </c>
+      <c r="AF373">
+        <v>2.03</v>
+      </c>
+      <c r="AG373">
+        <v>3.09</v>
+      </c>
+      <c r="AH373">
+        <v>1.32</v>
+      </c>
+      <c r="AI373">
+        <v>2.63</v>
+      </c>
+      <c r="AJ373">
+        <v>1.44</v>
+      </c>
+      <c r="AK373">
+        <v>1.25</v>
+      </c>
+      <c r="AL373">
+        <v>1.36</v>
+      </c>
+      <c r="AM373">
+        <v>1.62</v>
+      </c>
+      <c r="AN373">
+        <v>1.69</v>
+      </c>
+      <c r="AO373">
+        <v>1.29</v>
+      </c>
+      <c r="AP373">
+        <v>1.76</v>
+      </c>
+      <c r="AQ373">
+        <v>1.22</v>
+      </c>
+      <c r="AR373">
+        <v>1.37</v>
+      </c>
+      <c r="AS373">
+        <v>1.02</v>
+      </c>
+      <c r="AT373">
+        <v>2.39</v>
+      </c>
+      <c r="AU373">
+        <v>3</v>
+      </c>
+      <c r="AV373">
+        <v>3</v>
+      </c>
+      <c r="AW373">
+        <v>6</v>
+      </c>
+      <c r="AX373">
+        <v>5</v>
+      </c>
+      <c r="AY373">
+        <v>9</v>
+      </c>
+      <c r="AZ373">
+        <v>8</v>
+      </c>
+      <c r="BA373">
+        <v>4</v>
+      </c>
+      <c r="BB373">
+        <v>4</v>
+      </c>
+      <c r="BC373">
+        <v>8</v>
+      </c>
+      <c r="BD373">
+        <v>1.53</v>
+      </c>
+      <c r="BE373">
+        <v>6.75</v>
+      </c>
+      <c r="BF373">
+        <v>2.8</v>
+      </c>
+      <c r="BG373">
+        <v>1.4</v>
+      </c>
+      <c r="BH373">
+        <v>2.65</v>
+      </c>
+      <c r="BI373">
+        <v>1.68</v>
+      </c>
+      <c r="BJ373">
+        <v>2</v>
+      </c>
+      <c r="BK373">
+        <v>2.1</v>
+      </c>
+      <c r="BL373">
+        <v>1.62</v>
+      </c>
+      <c r="BM373">
+        <v>2.65</v>
+      </c>
+      <c r="BN373">
+        <v>1.4</v>
+      </c>
+      <c r="BO373">
+        <v>3.55</v>
+      </c>
+      <c r="BP373">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="374" spans="1:68">
+      <c r="A374" s="1">
+        <v>373</v>
+      </c>
+      <c r="B374">
+        <v>7728567</v>
+      </c>
+      <c r="C374" t="s">
+        <v>68</v>
+      </c>
+      <c r="D374" t="s">
+        <v>69</v>
+      </c>
+      <c r="E374" s="2">
+        <v>45753.66666666666</v>
+      </c>
+      <c r="F374">
+        <v>34</v>
+      </c>
+      <c r="G374" t="s">
+        <v>75</v>
+      </c>
+      <c r="H374" t="s">
+        <v>72</v>
+      </c>
+      <c r="I374">
+        <v>0</v>
+      </c>
+      <c r="J374">
+        <v>0</v>
+      </c>
+      <c r="K374">
+        <v>0</v>
+      </c>
+      <c r="L374">
+        <v>1</v>
+      </c>
+      <c r="M374">
+        <v>0</v>
+      </c>
+      <c r="N374">
+        <v>1</v>
+      </c>
+      <c r="O374" t="s">
+        <v>159</v>
+      </c>
+      <c r="P374" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q374">
+        <v>2.88</v>
+      </c>
+      <c r="R374">
+        <v>2.05</v>
+      </c>
+      <c r="S374">
+        <v>4</v>
+      </c>
+      <c r="T374">
+        <v>1.5</v>
+      </c>
+      <c r="U374">
+        <v>2.5</v>
+      </c>
+      <c r="V374">
+        <v>3.4</v>
+      </c>
+      <c r="W374">
+        <v>1.3</v>
+      </c>
+      <c r="X374">
+        <v>10</v>
+      </c>
+      <c r="Y374">
+        <v>1.06</v>
+      </c>
+      <c r="Z374">
+        <v>2.09</v>
+      </c>
+      <c r="AA374">
+        <v>3.45</v>
+      </c>
+      <c r="AB374">
+        <v>3.73</v>
+      </c>
+      <c r="AC374">
+        <v>1.05</v>
+      </c>
+      <c r="AD374">
+        <v>7.5</v>
+      </c>
+      <c r="AE374">
+        <v>1.33</v>
+      </c>
+      <c r="AF374">
+        <v>3</v>
+      </c>
+      <c r="AG374">
+        <v>2.33</v>
+      </c>
+      <c r="AH374">
+        <v>1.58</v>
+      </c>
+      <c r="AI374">
+        <v>1.91</v>
+      </c>
+      <c r="AJ374">
+        <v>1.8</v>
+      </c>
+      <c r="AK374">
+        <v>1.29</v>
+      </c>
+      <c r="AL374">
+        <v>1.32</v>
+      </c>
+      <c r="AM374">
+        <v>1.74</v>
+      </c>
+      <c r="AN374">
+        <v>1.19</v>
+      </c>
+      <c r="AO374">
+        <v>1.25</v>
+      </c>
+      <c r="AP374">
+        <v>1.29</v>
+      </c>
+      <c r="AQ374">
+        <v>1.18</v>
+      </c>
+      <c r="AR374">
+        <v>1.54</v>
+      </c>
+      <c r="AS374">
+        <v>1.28</v>
+      </c>
+      <c r="AT374">
+        <v>2.82</v>
+      </c>
+      <c r="AU374">
+        <v>7</v>
+      </c>
+      <c r="AV374">
+        <v>6</v>
+      </c>
+      <c r="AW374">
+        <v>12</v>
+      </c>
+      <c r="AX374">
+        <v>12</v>
+      </c>
+      <c r="AY374">
+        <v>24</v>
+      </c>
+      <c r="AZ374">
+        <v>20</v>
+      </c>
+      <c r="BA374">
+        <v>9</v>
+      </c>
+      <c r="BB374">
+        <v>6</v>
+      </c>
+      <c r="BC374">
+        <v>15</v>
+      </c>
+      <c r="BD374">
+        <v>1.65</v>
+      </c>
+      <c r="BE374">
+        <v>6.5</v>
+      </c>
+      <c r="BF374">
+        <v>2.5</v>
+      </c>
+      <c r="BG374">
+        <v>1.41</v>
+      </c>
+      <c r="BH374">
+        <v>2.63</v>
+      </c>
+      <c r="BI374">
+        <v>1.68</v>
+      </c>
+      <c r="BJ374">
+        <v>2</v>
+      </c>
+      <c r="BK374">
+        <v>2.12</v>
+      </c>
+      <c r="BL374">
+        <v>1.61</v>
+      </c>
+      <c r="BM374">
+        <v>2.7</v>
+      </c>
+      <c r="BN374">
+        <v>1.38</v>
+      </c>
+      <c r="BO374">
+        <v>3.65</v>
+      </c>
+      <c r="BP374">
         <v>1.22</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="445">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1710,7 +1710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP374"/>
+  <dimension ref="A1:BP375"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ11">
         <v>1.22</v>
@@ -7815,7 +7815,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ30">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR30">
         <v>1.73</v>
@@ -8636,7 +8636,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ34">
         <v>1.22</v>
@@ -12759,7 +12759,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ54">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12962,7 +12962,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ55">
         <v>1.19</v>
@@ -15022,7 +15022,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ65">
         <v>0.9399999999999999</v>
@@ -17291,7 +17291,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ76">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -20381,7 +20381,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ91">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -22026,7 +22026,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ99">
         <v>1.53</v>
@@ -24086,7 +24086,7 @@
         <v>1.25</v>
       </c>
       <c r="AP109">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ109">
         <v>0.9399999999999999</v>
@@ -26767,7 +26767,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ122">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR122">
         <v>1.4</v>
@@ -28206,7 +28206,7 @@
         <v>1.4</v>
       </c>
       <c r="AP129">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ129">
         <v>1.12</v>
@@ -30678,7 +30678,7 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ141">
         <v>1.22</v>
@@ -32741,7 +32741,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ151">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR151">
         <v>1.43</v>
@@ -37270,7 +37270,7 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ173">
         <v>1.29</v>
@@ -37891,7 +37891,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ176">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR176">
         <v>1.6</v>
@@ -39745,7 +39745,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ185">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR185">
         <v>1.42</v>
@@ -40566,7 +40566,7 @@
         <v>1.13</v>
       </c>
       <c r="AP189">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ189">
         <v>1.18</v>
@@ -44071,7 +44071,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ206">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR206">
         <v>1.42</v>
@@ -46334,7 +46334,7 @@
         <v>2.44</v>
       </c>
       <c r="AP217">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ217">
         <v>1.65</v>
@@ -47573,7 +47573,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ223">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR223">
         <v>1.71</v>
@@ -51278,7 +51278,7 @@
         <v>1.45</v>
       </c>
       <c r="AP241">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ241">
         <v>1.18</v>
@@ -52929,7 +52929,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ249">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR249">
         <v>1.51</v>
@@ -53956,7 +53956,7 @@
         <v>0.73</v>
       </c>
       <c r="AP254">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ254">
         <v>0.82</v>
@@ -58285,7 +58285,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ275">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR275">
         <v>1.57</v>
@@ -59518,7 +59518,7 @@
         <v>0.25</v>
       </c>
       <c r="AP281">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ281">
         <v>0.35</v>
@@ -60757,7 +60757,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ287">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR287">
         <v>1.29</v>
@@ -64462,7 +64462,7 @@
         <v>0.5</v>
       </c>
       <c r="AP305">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ305">
         <v>0.47</v>
@@ -65495,7 +65495,7 @@
         <v>2</v>
       </c>
       <c r="AQ310">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR310">
         <v>1.27</v>
@@ -68376,7 +68376,7 @@
         <v>1.36</v>
       </c>
       <c r="AP324">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ324">
         <v>1.18</v>
@@ -69615,7 +69615,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ330">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR330">
         <v>1.67</v>
@@ -72496,7 +72496,7 @@
         <v>1.07</v>
       </c>
       <c r="AP344">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AQ344">
         <v>1.12</v>
@@ -72911,7 +72911,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ346">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR346">
         <v>1.35</v>
@@ -78754,6 +78754,212 @@
         <v>3.65</v>
       </c>
       <c r="BP374">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="375" spans="1:68">
+      <c r="A375" s="1">
+        <v>374</v>
+      </c>
+      <c r="B375">
+        <v>7728562</v>
+      </c>
+      <c r="C375" t="s">
+        <v>68</v>
+      </c>
+      <c r="D375" t="s">
+        <v>69</v>
+      </c>
+      <c r="E375" s="2">
+        <v>45754.64583333334</v>
+      </c>
+      <c r="F375">
+        <v>34</v>
+      </c>
+      <c r="G375" t="s">
+        <v>79</v>
+      </c>
+      <c r="H375" t="s">
+        <v>74</v>
+      </c>
+      <c r="I375">
+        <v>1</v>
+      </c>
+      <c r="J375">
+        <v>0</v>
+      </c>
+      <c r="K375">
+        <v>1</v>
+      </c>
+      <c r="L375">
+        <v>1</v>
+      </c>
+      <c r="M375">
+        <v>0</v>
+      </c>
+      <c r="N375">
+        <v>1</v>
+      </c>
+      <c r="O375" t="s">
+        <v>138</v>
+      </c>
+      <c r="P375" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q375">
+        <v>1.91</v>
+      </c>
+      <c r="R375">
+        <v>2.2</v>
+      </c>
+      <c r="S375">
+        <v>10</v>
+      </c>
+      <c r="T375">
+        <v>1.44</v>
+      </c>
+      <c r="U375">
+        <v>2.63</v>
+      </c>
+      <c r="V375">
+        <v>3.25</v>
+      </c>
+      <c r="W375">
+        <v>1.33</v>
+      </c>
+      <c r="X375">
+        <v>10</v>
+      </c>
+      <c r="Y375">
+        <v>1.06</v>
+      </c>
+      <c r="Z375">
+        <v>1.33</v>
+      </c>
+      <c r="AA375">
+        <v>5.1</v>
+      </c>
+      <c r="AB375">
+        <v>11</v>
+      </c>
+      <c r="AC375">
+        <v>1.01</v>
+      </c>
+      <c r="AD375">
+        <v>8.5</v>
+      </c>
+      <c r="AE375">
+        <v>1.33</v>
+      </c>
+      <c r="AF375">
+        <v>2.9</v>
+      </c>
+      <c r="AG375">
+        <v>2.1</v>
+      </c>
+      <c r="AH375">
+        <v>1.61</v>
+      </c>
+      <c r="AI375">
+        <v>3</v>
+      </c>
+      <c r="AJ375">
+        <v>1.36</v>
+      </c>
+      <c r="AK375">
+        <v>1.06</v>
+      </c>
+      <c r="AL375">
+        <v>1.2</v>
+      </c>
+      <c r="AM375">
+        <v>3.25</v>
+      </c>
+      <c r="AN375">
+        <v>2.41</v>
+      </c>
+      <c r="AO375">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AP375">
+        <v>2.44</v>
+      </c>
+      <c r="AQ375">
+        <v>0.76</v>
+      </c>
+      <c r="AR375">
+        <v>1.7</v>
+      </c>
+      <c r="AS375">
+        <v>0.95</v>
+      </c>
+      <c r="AT375">
+        <v>2.65</v>
+      </c>
+      <c r="AU375">
+        <v>4</v>
+      </c>
+      <c r="AV375">
+        <v>3</v>
+      </c>
+      <c r="AW375">
+        <v>6</v>
+      </c>
+      <c r="AX375">
+        <v>5</v>
+      </c>
+      <c r="AY375">
+        <v>13</v>
+      </c>
+      <c r="AZ375">
+        <v>11</v>
+      </c>
+      <c r="BA375">
+        <v>3</v>
+      </c>
+      <c r="BB375">
+        <v>4</v>
+      </c>
+      <c r="BC375">
+        <v>7</v>
+      </c>
+      <c r="BD375">
+        <v>1.25</v>
+      </c>
+      <c r="BE375">
+        <v>7.5</v>
+      </c>
+      <c r="BF375">
+        <v>4.3</v>
+      </c>
+      <c r="BG375">
+        <v>1.42</v>
+      </c>
+      <c r="BH375">
+        <v>2.55</v>
+      </c>
+      <c r="BI375">
+        <v>1.72</v>
+      </c>
+      <c r="BJ375">
+        <v>1.95</v>
+      </c>
+      <c r="BK375">
+        <v>2.15</v>
+      </c>
+      <c r="BL375">
+        <v>1.6</v>
+      </c>
+      <c r="BM375">
+        <v>2.75</v>
+      </c>
+      <c r="BN375">
+        <v>1.37</v>
+      </c>
+      <c r="BO375">
+        <v>3.65</v>
+      </c>
+      <c r="BP375">
         <v>1.22</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -77476,10 +77476,10 @@
         <v>4</v>
       </c>
       <c r="BB368">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC368">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD368">
         <v>1.78</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -96441,19 +96441,19 @@
         <v>2.85</v>
       </c>
       <c r="AU459">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV459">
         <v>7</v>
       </c>
       <c r="AW459">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX459">
         <v>2</v>
       </c>
       <c r="AY459">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ459">
         <v>9</v>
@@ -96462,10 +96462,10 @@
         <v>2</v>
       </c>
       <c r="BB459">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BC459">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD459">
         <v>2.9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain Segunda División_20242025.xlsx
@@ -1144,7 +1144,7 @@
     <t>['16', '60', '81']</t>
   </si>
   <si>
-    <t>['10', '9006']</t>
+    <t>['10', '90+6']</t>
   </si>
   <si>
     <t>['8', '57']</t>
@@ -1588,7 +1588,7 @@
     <t>['4', '25', '32', '89']</t>
   </si>
   <si>
-    <t>['38', '4503', '70']</t>
+    <t>['38', '45+3', '70']</t>
   </si>
 </sst>
 </file>
